--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -149,19 +149,19 @@
     <t>POS</t>
   </si>
   <si>
-    <t>CURRENCYINR</t>
+    <t>CurrencyInr</t>
   </si>
   <si>
     <t>INR</t>
   </si>
   <si>
-    <t>POHTYPE</t>
+    <t>PohType</t>
   </si>
   <si>
     <t>PO - GENERAL</t>
   </si>
   <si>
-    <t>UOMNOS</t>
+    <t>UomNos</t>
   </si>
   <si>
     <t>NOS</t>
@@ -177,6 +177,36 @@
   </si>
   <si>
     <t>PO - SERVICE</t>
+  </si>
+  <si>
+    <t>DissimilarItem</t>
+  </si>
+  <si>
+    <t>GWL_ITEM_DISIMILAR_UOM</t>
+  </si>
+  <si>
+    <t>PR_Service</t>
+  </si>
+  <si>
+    <t>PR - SERVICES</t>
+  </si>
+  <si>
+    <t>Prefix_PRGWL</t>
+  </si>
+  <si>
+    <t>PRGWL</t>
+  </si>
+  <si>
+    <t>GwlItem_Service</t>
+  </si>
+  <si>
+    <t>GWL_SERVICES_02</t>
+  </si>
+  <si>
+    <t>CancelStatus</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
   </si>
 </sst>
 </file>
@@ -1354,24 +1384,44 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
+      <c r="A27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
+      <c r="A28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
+      <c r="A29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2"/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>Cancelled</t>
+  </si>
+  <si>
+    <t>PRtemplate1Line</t>
+  </si>
+  <si>
+    <t>PRTemplateSingleLine.csv</t>
   </si>
 </sst>
 </file>
@@ -1169,10 +1175,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1424,8 +1430,12 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2"/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="17231" windowHeight="8064"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <oleSize ref="A1:B33"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -213,6 +214,24 @@
   </si>
   <si>
     <t>PRTemplateSingleLine.csv</t>
+  </si>
+  <si>
+    <t>WalmartSupplier</t>
+  </si>
+  <si>
+    <t>WALMART</t>
+  </si>
+  <si>
+    <t>CurrencyUsd</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>DissimilarService</t>
+  </si>
+  <si>
+    <t>GWL_Dissimilar_Services</t>
   </si>
 </sst>
 </file>
@@ -1174,11 +1193,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
-    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
+    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1438,8 +1457,28 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+      <c r="A33" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,13 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17231" windowHeight="8064"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <oleSize ref="A1:B33"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -232,6 +231,18 @@
   </si>
   <si>
     <t>GWL_Dissimilar_Services</t>
+  </si>
+  <si>
+    <t>PostedStatus</t>
+  </si>
+  <si>
+    <t>Posted</t>
+  </si>
+  <si>
+    <t>RefText_Test</t>
+  </si>
+  <si>
+    <t>TEST</t>
   </si>
 </sst>
 </file>
@@ -1193,11 +1204,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1480,6 +1491,22 @@
         <v>67</v>
       </c>
     </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,13 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17231" windowHeight="8064"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <oleSize ref="A1:B33"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -232,6 +231,60 @@
   </si>
   <si>
     <t>GWL_Dissimilar_Services</t>
+  </si>
+  <si>
+    <t>Location02</t>
+  </si>
+  <si>
+    <t>L0002</t>
+  </si>
+  <si>
+    <t>StockTransferSelect</t>
+  </si>
+  <si>
+    <t>POT</t>
+  </si>
+  <si>
+    <t>U1Supplier</t>
+  </si>
+  <si>
+    <t>SUP00325</t>
+  </si>
+  <si>
+    <t>St_Item_Similar</t>
+  </si>
+  <si>
+    <t>GWL_CHECKING_ST</t>
+  </si>
+  <si>
+    <t>Po_Stock_Transfer</t>
+  </si>
+  <si>
+    <t>PO - STOCK TRANSFER</t>
+  </si>
+  <si>
+    <t>Stock_Item_Dissimilar</t>
+  </si>
+  <si>
+    <t>GWL_Dissimilar_ST_Check</t>
+  </si>
+  <si>
+    <t>DoubleDecimal</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>PackingCharges</t>
+  </si>
+  <si>
+    <t>TVS-CH-00003</t>
+  </si>
+  <si>
+    <t>GlAccDescription</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE EXPENES</t>
   </si>
 </sst>
 </file>
@@ -868,12 +921,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1193,7 +1247,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
@@ -1473,11 +1527,83 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s">
+      <c r="A35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -182,7 +182,7 @@
     <t>DissimilarItem</t>
   </si>
   <si>
-    <t>GWL_ITEM_DISIMILAR_UOM</t>
+    <t>GWL_ITEM_DISSIMILAR_UOM</t>
   </si>
   <si>
     <t>PR_Service</t>
@@ -243,6 +243,12 @@
   </si>
   <si>
     <t>TEST</t>
+  </si>
+  <si>
+    <t>Kgs</t>
+  </si>
+  <si>
+    <t>KGS</t>
   </si>
 </sst>
 </file>
@@ -1204,11 +1210,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
-    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
+    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1484,28 +1490,40 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s">
+      <c r="A35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" t="s">
+      <c r="A36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" t="s">
+      <c r="A37" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>71</v>
       </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="11471" windowHeight="8520"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -249,6 +249,60 @@
   </si>
   <si>
     <t>KGS</t>
+  </si>
+  <si>
+    <t>Location02</t>
+  </si>
+  <si>
+    <t>L0002</t>
+  </si>
+  <si>
+    <t>StockTransferSelect</t>
+  </si>
+  <si>
+    <t>POT</t>
+  </si>
+  <si>
+    <t>U1Supplier</t>
+  </si>
+  <si>
+    <t>SUP00325</t>
+  </si>
+  <si>
+    <t>St_Item_Similar</t>
+  </si>
+  <si>
+    <t>GWL_CHECKING_ST</t>
+  </si>
+  <si>
+    <t>Po_Stock_Transfer</t>
+  </si>
+  <si>
+    <t>PO - STOCK TRANSFER</t>
+  </si>
+  <si>
+    <t>Stock_Item_Dissimilar</t>
+  </si>
+  <si>
+    <t>GWL_Dissimilar_ST_Check</t>
+  </si>
+  <si>
+    <t>DoubleDecimal</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>PackingCharges</t>
+  </si>
+  <si>
+    <t>TVS-CH-00003</t>
+  </si>
+  <si>
+    <t>GlAccDescription</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE EXPENES</t>
   </si>
 </sst>
 </file>
@@ -885,12 +939,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1210,7 +1265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
@@ -1522,8 +1577,76 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
+      <c r="A39" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11471" windowHeight="8520"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>ADMINISTRATIVE EXPENES</t>
+  </si>
+  <si>
+    <t>Unit_100</t>
+  </si>
+  <si>
+    <t>U100</t>
   </si>
 </sst>
 </file>
@@ -939,13 +945,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1265,11 +1272,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1648,6 +1655,14 @@
         <v>91</v>
       </c>
     </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>U100</t>
+  </si>
+  <si>
+    <t>FiveValue</t>
   </si>
 </sst>
 </file>
@@ -1272,11 +1275,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
-    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
+    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1656,11 +1659,19 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="2" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="4">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="96">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>FiveValue</t>
+  </si>
+  <si>
+    <t>Zero</t>
   </si>
 </sst>
 </file>
@@ -948,14 +951,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1275,7 +1277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
@@ -1667,11 +1669,19 @@
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="2">
         <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -315,6 +315,18 @@
   </si>
   <si>
     <t>Zero</t>
+  </si>
+  <si>
+    <t>Similar_Item_02</t>
+  </si>
+  <si>
+    <t>GWL_Item_Similar_02</t>
+  </si>
+  <si>
+    <t>HSN2022</t>
+  </si>
+  <si>
+    <t>(2022)</t>
   </si>
 </sst>
 </file>
@@ -951,11 +963,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
@@ -1277,7 +1291,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
@@ -1684,6 +1698,22 @@
         <v>87</v>
       </c>
     </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="188">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -327,6 +327,270 @@
   </si>
   <si>
     <t>(2022)</t>
+  </si>
+  <si>
+    <t>Emp_Salution</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>Emp_FName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GWL Emp - </t>
+  </si>
+  <si>
+    <t>Emp_LName</t>
+  </si>
+  <si>
+    <t>Automation</t>
+  </si>
+  <si>
+    <t>Emp_MaleGender</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Emp_DOB</t>
+  </si>
+  <si>
+    <t>16-02-2000</t>
+  </si>
+  <si>
+    <t>Emp_DOJ</t>
+  </si>
+  <si>
+    <t>16-02-2024</t>
+  </si>
+  <si>
+    <t>Emp_GeneralShift</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Emp_1to31Calendar</t>
+  </si>
+  <si>
+    <t>1 TO 30/31</t>
+  </si>
+  <si>
+    <t>Emp_GeneralZone</t>
+  </si>
+  <si>
+    <t>GENERAL</t>
+  </si>
+  <si>
+    <t>Emp_SalesCompanyCategory</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>Emp_SalaryAcc-AccountCategory</t>
+  </si>
+  <si>
+    <t>SALARY ACCOUNT</t>
+  </si>
+  <si>
+    <t>Emp_CleanerPayrollGroup</t>
+  </si>
+  <si>
+    <t>CLEANER</t>
+  </si>
+  <si>
+    <t>Emp_NoticePeriod-30</t>
+  </si>
+  <si>
+    <t>Emp_City</t>
+  </si>
+  <si>
+    <t>PLAIN CITY</t>
+  </si>
+  <si>
+    <t>Emp_Qualification</t>
+  </si>
+  <si>
+    <t>B.Tech</t>
+  </si>
+  <si>
+    <t>Emp_BranchofStudy</t>
+  </si>
+  <si>
+    <t>COMPUTER SCIENCE</t>
+  </si>
+  <si>
+    <t>Emp_YearOfPassing</t>
+  </si>
+  <si>
+    <t>Emp_Skill</t>
+  </si>
+  <si>
+    <t>PUNCHUALITY</t>
+  </si>
+  <si>
+    <t>Emp_Level</t>
+  </si>
+  <si>
+    <t>EXCELLENT</t>
+  </si>
+  <si>
+    <t>Emp_SalaryDesignation</t>
+  </si>
+  <si>
+    <t>FINANCE MANAGER</t>
+  </si>
+  <si>
+    <t>Emp_SalaryDepartment</t>
+  </si>
+  <si>
+    <t>PRODUCTION</t>
+  </si>
+  <si>
+    <t>Emp_SalaryGrade</t>
+  </si>
+  <si>
+    <t>GRADE A</t>
+  </si>
+  <si>
+    <t>Emp_AdjmntElement</t>
+  </si>
+  <si>
+    <t>ENCASH</t>
+  </si>
+  <si>
+    <t>Emp_AdjmntStartYear</t>
+  </si>
+  <si>
+    <t>Emp_AdjmntPeriod</t>
+  </si>
+  <si>
+    <t>DEC</t>
+  </si>
+  <si>
+    <t>Emp_AdjmntTotalPeriod</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Emp_AdjmntPeriodAmnt</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>LeaveElgblLeave</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>LeaveElgblDays</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>EmpLeaveElgblEvery</t>
+  </si>
+  <si>
+    <t>Year(s)</t>
+  </si>
+  <si>
+    <t>EmpLeaveElgblEligibileDays</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>EmpLeaveElgblRoundOff</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>EmpLeaveElgblMaxCarryFreq</t>
+  </si>
+  <si>
+    <t>Yearly</t>
+  </si>
+  <si>
+    <t>EmpLeaveElgblMaxCarryDay</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>EmpLeaveElgblEffYear</t>
+  </si>
+  <si>
+    <t>202324</t>
+  </si>
+  <si>
+    <t>EmpLeaveElgblMaxDay</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>EmpLeaveElgblMinDay</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>EmployeeDurai</t>
+  </si>
+  <si>
+    <t>DURAIRAJ  R</t>
+  </si>
+  <si>
+    <t>PermFromDate</t>
+  </si>
+  <si>
+    <t>24-05-2024</t>
+  </si>
+  <si>
+    <t>PermissionTimeFrom</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>PermissionTimeTo</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>PermissionReference</t>
+  </si>
+  <si>
+    <t>Permission</t>
+  </si>
+  <si>
+    <t>PermissionType</t>
+  </si>
+  <si>
+    <t>On-Duty (Day)</t>
+  </si>
+  <si>
+    <t>OnDutyFindType</t>
+  </si>
+  <si>
+    <t>On - Duty(Day)</t>
+  </si>
+  <si>
+    <t>OnDutyFromDate</t>
+  </si>
+  <si>
+    <t>25-05-2024</t>
+  </si>
+  <si>
+    <t>PermissionFindType</t>
   </si>
 </sst>
 </file>
@@ -339,7 +603,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,6 +618,17 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -833,145 +1108,158 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1291,418 +1579,418 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B98"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="5">
         <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="5" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="5" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="5" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="5" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="5" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="5" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="5" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="5" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="5" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="5" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="5" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1712,6 +2000,374 @@
       </c>
       <c r="B52" s="5" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B69" s="8">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B76" s="8">
+        <v>202425</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="220">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -591,6 +591,102 @@
   </si>
   <si>
     <t>PermissionFindType</t>
+  </si>
+  <si>
+    <t>PO_NUMBER</t>
+  </si>
+  <si>
+    <t>PO100/00010/24-25</t>
+  </si>
+  <si>
+    <t>ITEM_ID</t>
+  </si>
+  <si>
+    <t>LotNo</t>
+  </si>
+  <si>
+    <t>RM1001</t>
+  </si>
+  <si>
+    <t>serial</t>
+  </si>
+  <si>
+    <t>HK-FIFO-SER-BATCH-10001</t>
+  </si>
+  <si>
+    <t>Serial No</t>
+  </si>
+  <si>
+    <t>DomSupplier_ID</t>
+  </si>
+  <si>
+    <t>ARAVIND AGENCY</t>
+  </si>
+  <si>
+    <t>SimItem_ID</t>
+  </si>
+  <si>
+    <t>TVS-RM-KDK-18</t>
+  </si>
+  <si>
+    <t>Disc_Value</t>
+  </si>
+  <si>
+    <t>ImpSupplier_ID</t>
+  </si>
+  <si>
+    <t>AFT PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>DissimItem_ID</t>
+  </si>
+  <si>
+    <t>TVS-RM-KPK-12</t>
+  </si>
+  <si>
+    <t>Cost_Value</t>
+  </si>
+  <si>
+    <t>Gwl_Service_Item_03</t>
+  </si>
+  <si>
+    <t>GWL_ITem_service_03</t>
+  </si>
+  <si>
+    <t>EMPNAME</t>
+  </si>
+  <si>
+    <t>EMP01</t>
+  </si>
+  <si>
+    <t>CUSName</t>
+  </si>
+  <si>
+    <t>C014</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>TVS-FG-00059</t>
+  </si>
+  <si>
+    <t>CUSName_OSO</t>
+  </si>
+  <si>
+    <t>CU0060</t>
+  </si>
+  <si>
+    <t>ITEM_OSO</t>
+  </si>
+  <si>
+    <t>TVS-FG-100768</t>
+  </si>
+  <si>
+    <t>HodValue</t>
+  </si>
+  <si>
+    <t>ZeroValue</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1187,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -1237,8 +1333,10 @@
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1260,8 +1358,15 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -1311,6 +1416,8 @@
     <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal 2" xfId="49"/>
+    <cellStyle name="Normal 3" xfId="50"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1579,11 +1686,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B98"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B117"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
-    <col min="2" max="2" width="27.1090909090909" style="1" customWidth="1"/>
+    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="27.1111111111111" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2370,6 +2477,158 @@
         <v>180</v>
       </c>
     </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B103" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B105" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B106" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B107" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B109" s="15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B111" s="17" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B112" s="17" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B117" s="4">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="279">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -687,6 +687,183 @@
   </si>
   <si>
     <t>ZeroValue</t>
+  </si>
+  <si>
+    <t>Sales_Invoice</t>
+  </si>
+  <si>
+    <t>Sales Invoice</t>
+  </si>
+  <si>
+    <t>SI_Type</t>
+  </si>
+  <si>
+    <t>SI - GENERAL</t>
+  </si>
+  <si>
+    <t>CustomerName</t>
+  </si>
+  <si>
+    <t>MURUGAN TRADERS</t>
+  </si>
+  <si>
+    <t>InvoicePrefix</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Item_ID</t>
+  </si>
+  <si>
+    <t>TVSFG004</t>
+  </si>
+  <si>
+    <t>CPC_Code</t>
+  </si>
+  <si>
+    <t>InvoiceQty</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>UnitPrice</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>SalesGL_Acct</t>
+  </si>
+  <si>
+    <t>4010101001</t>
+  </si>
+  <si>
+    <t>HSNcode_SI</t>
+  </si>
+  <si>
+    <t>88363222</t>
+  </si>
+  <si>
+    <t>SI_HOD</t>
+  </si>
+  <si>
+    <t>Export_Customer_Name</t>
+  </si>
+  <si>
+    <t>FRANCE FOREIGN TRADERS</t>
+  </si>
+  <si>
+    <t>LUT_No</t>
+  </si>
+  <si>
+    <t>2321311</t>
+  </si>
+  <si>
+    <t>Domestic_RC_Customer_Name</t>
+  </si>
+  <si>
+    <t>AJK ENTERPRISES</t>
+  </si>
+  <si>
+    <t>Domestic_RC_Item_ID</t>
+  </si>
+  <si>
+    <t>RC_DOMESTIC_001</t>
+  </si>
+  <si>
+    <t>Export_RC_Customer_Name</t>
+  </si>
+  <si>
+    <t>Export_RC_Item_ID</t>
+  </si>
+  <si>
+    <t>RC_Export_001</t>
+  </si>
+  <si>
+    <t>UD_Disimilar_Domestic_Item_ID</t>
+  </si>
+  <si>
+    <t>UD_Disimilar_Domestic_002</t>
+  </si>
+  <si>
+    <t>Domestic_RC_Item_ID_Disimilar</t>
+  </si>
+  <si>
+    <t>Export_RC_Item_ID_Disimilar</t>
+  </si>
+  <si>
+    <t>Domestic_PL_Item_ID</t>
+  </si>
+  <si>
+    <t>Export_PL_Item_ID</t>
+  </si>
+  <si>
+    <t>Domestic_PL_Item_ID_Disimilar</t>
+  </si>
+  <si>
+    <t>Export_PL_Item_ID_Disimilar</t>
+  </si>
+  <si>
+    <t>Domestic_SP_Item_ID</t>
+  </si>
+  <si>
+    <t>Export_SP_Item_ID</t>
+  </si>
+  <si>
+    <t>Domestic_SP_Item_ID_Disimalar</t>
+  </si>
+  <si>
+    <t>Export_SP_Item_ID_Disimalar</t>
+  </si>
+  <si>
+    <t>Domestic_CG_Item_ID</t>
+  </si>
+  <si>
+    <t>Export_CG_Item_ID</t>
+  </si>
+  <si>
+    <t>Domestic_CG_Item_ID_Disimalar</t>
+  </si>
+  <si>
+    <t>Export_CG_Item_ID_Disimalar</t>
+  </si>
+  <si>
+    <t>EmpAddInfo_HomeType</t>
+  </si>
+  <si>
+    <t>Rent</t>
+  </si>
+  <si>
+    <t>EmpAddInfo_StayType</t>
+  </si>
+  <si>
+    <t>Hosteller</t>
+  </si>
+  <si>
+    <t>EmpAddInfo_VehicleFlag</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>EmpDependentRelation</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>EmpDependentRelationDOB</t>
+  </si>
+  <si>
+    <t>20-05-1998</t>
+  </si>
+  <si>
+    <t>Emp_MaritalStatus</t>
+  </si>
+  <si>
+    <t>Single</t>
   </si>
 </sst>
 </file>
@@ -699,7 +876,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -723,6 +900,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -1204,139 +1387,139 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1365,6 +1548,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1686,11 +1874,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B117"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B155"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2629,6 +2817,310 @@
         <v>0</v>
       </c>
     </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B129" s="19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="B134" s="19" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="B137" s="19" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="B138" s="19" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="B144" s="19" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B147" s="19" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B148" s="19" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="B153" s="19" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="B154" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="B155" s="19" t="s">
+        <v>278</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="293">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -864,6 +864,48 @@
   </si>
   <si>
     <t>Single</t>
+  </si>
+  <si>
+    <t>LotItem</t>
+  </si>
+  <si>
+    <t>HK-LOT-FIFO-LOT-10001</t>
+  </si>
+  <si>
+    <t>POSupplier</t>
+  </si>
+  <si>
+    <t>JJ AUTOMOBILES</t>
+  </si>
+  <si>
+    <t>NAItem</t>
+  </si>
+  <si>
+    <t>HK-NA-MAC-10001</t>
+  </si>
+  <si>
+    <t>IssuedStatus</t>
+  </si>
+  <si>
+    <t>Issued</t>
+  </si>
+  <si>
+    <t>Rtgs</t>
+  </si>
+  <si>
+    <t>RTGS</t>
+  </si>
+  <si>
+    <t>Axisbank</t>
+  </si>
+  <si>
+    <t>AXIS BANK</t>
+  </si>
+  <si>
+    <t>BankofBaroda</t>
+  </si>
+  <si>
+    <t>7151922222222265</t>
   </si>
 </sst>
 </file>
@@ -876,7 +918,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -907,6 +949,23 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1387,139 +1446,139 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1553,6 +1612,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1874,11 +1946,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B155"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B162"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
-    <col min="2" max="2" width="27.1090909090909" style="1" customWidth="1"/>
+    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="27.1111111111111" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3121,6 +3193,62 @@
         <v>278</v>
       </c>
     </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B156" s="22" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B158" s="23" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="B160" s="25" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="B161" s="27" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="B162" s="27" t="s">
+        <v>292</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="341">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -906,6 +906,150 @@
   </si>
   <si>
     <t>7151922222222265</t>
+  </si>
+  <si>
+    <t>OpenSOItem</t>
+  </si>
+  <si>
+    <t>GWL_OpenSO_Item</t>
+  </si>
+  <si>
+    <t>ERPPrivateLimitedID</t>
+  </si>
+  <si>
+    <t>CUS0000056</t>
+  </si>
+  <si>
+    <t>ERPPrivateLimitedName</t>
+  </si>
+  <si>
+    <t>ERP PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Prefix_OP100</t>
+  </si>
+  <si>
+    <t>OP100</t>
+  </si>
+  <si>
+    <t>Type_Standard</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>HSN2022-5%</t>
+  </si>
+  <si>
+    <t>(2022)5%</t>
+  </si>
+  <si>
+    <t>Sales_Order</t>
+  </si>
+  <si>
+    <t>Sales Order</t>
+  </si>
+  <si>
+    <t>SO_General</t>
+  </si>
+  <si>
+    <t>SO - GENERAL</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>CUS0015</t>
+  </si>
+  <si>
+    <t>SO_Similar_Item</t>
+  </si>
+  <si>
+    <t>HK-FIFO-LOT-BATCH-10001(FG)</t>
+  </si>
+  <si>
+    <t>SO_Qty</t>
+  </si>
+  <si>
+    <t>SO_UnitCost</t>
+  </si>
+  <si>
+    <t>2800</t>
+  </si>
+  <si>
+    <t>SO_HSNCode</t>
+  </si>
+  <si>
+    <t>772213</t>
+  </si>
+  <si>
+    <t>SO_HOD_Value</t>
+  </si>
+  <si>
+    <t>SO_PriceBasis</t>
+  </si>
+  <si>
+    <t>User Defined</t>
+  </si>
+  <si>
+    <t>SO_Export_Customer</t>
+  </si>
+  <si>
+    <t>SO_DisSimilarItem</t>
+  </si>
+  <si>
+    <t>HK-FG-DISSIMILAR-10001</t>
+  </si>
+  <si>
+    <t>SO_Similar_Item_Rate_Contract</t>
+  </si>
+  <si>
+    <t>HK-LOT-MAC-10001(FG)</t>
+  </si>
+  <si>
+    <t>SO_Similar_Item_PriceList</t>
+  </si>
+  <si>
+    <t>HK-LOT-FIFO-LOT-10001(FG)</t>
+  </si>
+  <si>
+    <t>SO_Similar_Item_Catalog</t>
+  </si>
+  <si>
+    <t>HK-FIFO-SER-BATCH-10001(FG)</t>
+  </si>
+  <si>
+    <t>SO_Similar_Item_StandardPrice</t>
+  </si>
+  <si>
+    <t>HK-SER-MAC-10001(FG)</t>
+  </si>
+  <si>
+    <t>SO_DisSimilar_Item_Rate_Contract</t>
+  </si>
+  <si>
+    <t>HK-FG-RC-DISSIMILAR ITEM-10001</t>
+  </si>
+  <si>
+    <t>FinishedGoodWH</t>
+  </si>
+  <si>
+    <t>FINISHED GOODS WH U100</t>
+  </si>
+  <si>
+    <t>SinglePaymentType</t>
+  </si>
+  <si>
+    <t>BankReceipt_BankType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank </t>
+  </si>
+  <si>
+    <t>NEFTText</t>
+  </si>
+  <si>
+    <t>NEFT</t>
   </si>
 </sst>
 </file>
@@ -918,7 +1062,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -954,17 +1098,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
@@ -1446,139 +1579,139 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1616,13 +1749,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1946,11 +2080,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B188"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3210,7 +3344,7 @@
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="4" t="s">
+      <c r="A158" s="9" t="s">
         <v>283</v>
       </c>
       <c r="B158" s="23" t="s">
@@ -3218,35 +3352,243 @@
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="4" t="s">
+      <c r="A159" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="B159" s="5" t="s">
+      <c r="B159" s="24" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="24" t="s">
+      <c r="A160" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="B160" s="25" t="s">
+      <c r="B160" s="9" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="26" t="s">
+      <c r="A161" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="B161" s="27" t="s">
+      <c r="B161" s="24" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="26" t="s">
+      <c r="A162" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="B162" s="27" t="s">
+      <c r="B162" s="24" t="s">
         <v>292</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="B163" s="25" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="B164" s="25" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="B165" s="26" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="B166" s="26" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="B167" s="25" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="B168" s="25" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="B169" s="26" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="B170" s="26" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="B171" s="26" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="B172" s="26" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="B173" s="26" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="B174" s="26" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="B175" s="26" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="B176" s="26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="B177" s="26" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="B178" s="26" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="B179" s="26" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="B180" s="26" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="B181" s="26" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="B182" s="26" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="B183" s="26" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="B184" s="26" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="B185" s="25" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="B186" s="25" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="B187" s="26" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="B188" s="25" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="343">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1050,6 +1050,12 @@
   </si>
   <si>
     <t>NEFT</t>
+  </si>
+  <si>
+    <t>InvoicedStatus</t>
+  </si>
+  <si>
+    <t>Invoiced</t>
   </si>
 </sst>
 </file>
@@ -2080,7 +2086,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B188"/>
+  <dimension ref="A1:B189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
@@ -3384,211 +3390,219 @@
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="25" t="s">
+      <c r="A163" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="B163" s="25" t="s">
+      <c r="B163" s="9" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="25" t="s">
+      <c r="A164" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="B164" s="25" t="s">
+      <c r="B164" s="9" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="25" t="s">
+      <c r="A165" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="B165" s="26" t="s">
+      <c r="B165" s="24" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="25" t="s">
+      <c r="A166" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B166" s="26" t="s">
+      <c r="B166" s="24" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="25" t="s">
+      <c r="A167" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="B167" s="25" t="s">
+      <c r="B167" s="9" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="25" t="s">
+      <c r="A168" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="B168" s="25" t="s">
+      <c r="B168" s="9" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="25" t="s">
+      <c r="A169" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="B169" s="26" t="s">
+      <c r="B169" s="24" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="25" t="s">
+      <c r="A170" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="B170" s="26" t="s">
+      <c r="B170" s="24" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="25" t="s">
+      <c r="A171" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="B171" s="26" t="s">
+      <c r="B171" s="24" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="25" t="s">
+      <c r="A172" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="B172" s="26" t="s">
+      <c r="B172" s="24" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="25" t="s">
+      <c r="A173" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="B173" s="26" t="s">
+      <c r="B173" s="24" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="25" t="s">
+      <c r="A174" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="B174" s="26" t="s">
+      <c r="B174" s="24" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="25" t="s">
+      <c r="A175" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="B175" s="26" t="s">
+      <c r="B175" s="24" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="25" t="s">
+      <c r="A176" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="B176" s="26" t="s">
+      <c r="B176" s="24" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="25" t="s">
+      <c r="A177" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="B177" s="26" t="s">
+      <c r="B177" s="24" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="25" t="s">
+      <c r="A178" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="B178" s="26" t="s">
+      <c r="B178" s="24" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="25" t="s">
+      <c r="A179" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="B179" s="26" t="s">
+      <c r="B179" s="24" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="25" t="s">
+      <c r="A180" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="B180" s="26" t="s">
+      <c r="B180" s="24" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="25" t="s">
+      <c r="A181" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B181" s="26" t="s">
+      <c r="B181" s="24" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="25" t="s">
+      <c r="A182" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="B182" s="26" t="s">
+      <c r="B182" s="24" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="25" t="s">
+      <c r="A183" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="B183" s="26" t="s">
+      <c r="B183" s="24" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="25" t="s">
+      <c r="A184" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="B184" s="26" t="s">
+      <c r="B184" s="24" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="25" t="s">
+      <c r="A185" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="B185" s="25" t="s">
+      <c r="B185" s="9" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="25" t="s">
+      <c r="A186" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="B186" s="25" t="s">
+      <c r="B186" s="9" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="25" t="s">
+      <c r="A187" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="B187" s="26" t="s">
+      <c r="B187" s="24" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="25" t="s">
+      <c r="A188" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="B188" s="25" t="s">
+      <c r="B188" s="9" t="s">
         <v>340</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="B189" s="26" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="14388" windowHeight="7200"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="387">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1056,6 +1056,138 @@
   </si>
   <si>
     <t>Invoiced</t>
+  </si>
+  <si>
+    <t>GWL_Item_Lot</t>
+  </si>
+  <si>
+    <t>GWL_ITEM-Lot_01</t>
+  </si>
+  <si>
+    <t>TVS-RM-KDK-64</t>
+  </si>
+  <si>
+    <t>TVS-RM-KPK-25</t>
+  </si>
+  <si>
+    <t>Efffrom_Date</t>
+  </si>
+  <si>
+    <t>12-02-2025</t>
+  </si>
+  <si>
+    <t>Effto_Date</t>
+  </si>
+  <si>
+    <t>15-02-2025</t>
+  </si>
+  <si>
+    <t>Close_Date</t>
+  </si>
+  <si>
+    <t>13-02-2025</t>
+  </si>
+  <si>
+    <t>Amdcost_Value</t>
+  </si>
+  <si>
+    <t>AmdDisc_Value</t>
+  </si>
+  <si>
+    <t>Rfqitem_ID</t>
+  </si>
+  <si>
+    <t>TVS-RM-KDK-01</t>
+  </si>
+  <si>
+    <t>Cost_Value1</t>
+  </si>
+  <si>
+    <t>Cost_Value2</t>
+  </si>
+  <si>
+    <t>DomSupplier_ID1</t>
+  </si>
+  <si>
+    <t>ACTIVE GARMENTS</t>
+  </si>
+  <si>
+    <t>Hsn_code</t>
+  </si>
+  <si>
+    <t>Trd_Discount</t>
+  </si>
+  <si>
+    <t>Spcl_Discount</t>
+  </si>
+  <si>
+    <t>Cash_Discount</t>
+  </si>
+  <si>
+    <t>AmdSimItem_ID</t>
+  </si>
+  <si>
+    <t>TVS-AMD-SIM-02</t>
+  </si>
+  <si>
+    <t>AmdDissimItem_ID</t>
+  </si>
+  <si>
+    <t>TVS-AMD-DIS-02</t>
+  </si>
+  <si>
+    <t>CnclSimItem_ID</t>
+  </si>
+  <si>
+    <t>TVS-AMD-CANCL-02</t>
+  </si>
+  <si>
+    <t>Perc_1</t>
+  </si>
+  <si>
+    <t>Perc_2</t>
+  </si>
+  <si>
+    <t>Amnd_Reason</t>
+  </si>
+  <si>
+    <t>L0001</t>
+  </si>
+  <si>
+    <t>OpenPOSupplier</t>
+  </si>
+  <si>
+    <t>ARUN PACKS (P) LTD</t>
+  </si>
+  <si>
+    <t>LotSerialDate</t>
+  </si>
+  <si>
+    <t>20.10.2027</t>
+  </si>
+  <si>
+    <t>Lot</t>
+  </si>
+  <si>
+    <t>LOT</t>
+  </si>
+  <si>
+    <t>Na</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Serial</t>
+  </si>
+  <si>
+    <t>SERIAL</t>
+  </si>
+  <si>
+    <t>RateContractServiceItem</t>
+  </si>
+  <si>
+    <t>PK-SERV-MAC-NA-01</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1200,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1105,6 +1237,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1446,7 +1584,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1467,6 +1605,19 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1585,139 +1736,139 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1761,10 +1912,12 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2086,11 +2239,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B189"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B224"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.1090909090909" customWidth="1"/>
-    <col min="2" max="2" width="27.1090909090909" style="1" customWidth="1"/>
+    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="27.1111111111111" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3598,11 +3751,291 @@
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="25" t="s">
+      <c r="A189" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="B189" s="26" t="s">
+      <c r="B189" s="24" t="s">
         <v>342</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B190" s="25" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="B191" s="26" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="B192" s="27" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B193" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="B194" s="26" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="B195" s="11" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="B196" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B197" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="B198" s="28" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="26" t="s">
+        <v>349</v>
+      </c>
+      <c r="B199" s="28" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="26" t="s">
+        <v>351</v>
+      </c>
+      <c r="B200" s="28" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="26" t="s">
+        <v>353</v>
+      </c>
+      <c r="B201" s="12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="26" t="s">
+        <v>354</v>
+      </c>
+      <c r="B202" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B204" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B205" s="12">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="B206" s="12" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B207" s="12">
+        <v>123562</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B208" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B209" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="B210" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="B211" s="27" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B212" s="11" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B213" s="27" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B214" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B215" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B216" s="27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="B218" s="21" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="B221" s="21" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="29" t="s">
+        <v>381</v>
+      </c>
+      <c r="B222" s="21" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="B223" s="30" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="29" t="s">
+        <v>385</v>
+      </c>
+      <c r="B224" s="29" t="s">
+        <v>386</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14388" windowHeight="7200"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="423">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1188,6 +1188,114 @@
   </si>
   <si>
     <t>PK-SERV-MAC-NA-01</t>
+  </si>
+  <si>
+    <t>SO_DisSimilar_Item_Catalog</t>
+  </si>
+  <si>
+    <t>HK-FG-CATALOG-DISSIMILAR-10001</t>
+  </si>
+  <si>
+    <t>SO_DisSimilar_Item_StandardPrice</t>
+  </si>
+  <si>
+    <t>HK-FG-STD-PRICE-DISSIMILAR ITEM-10001</t>
+  </si>
+  <si>
+    <t>SO_Trade_Disc</t>
+  </si>
+  <si>
+    <t>SO_Special_Disc</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>SO_Cash_Disc</t>
+  </si>
+  <si>
+    <t>CUS151113</t>
+  </si>
+  <si>
+    <t>OsoamdReason</t>
+  </si>
+  <si>
+    <t>WRONG ENTRY MOVED</t>
+  </si>
+  <si>
+    <t>Revisised_Price</t>
+  </si>
+  <si>
+    <t>787</t>
+  </si>
+  <si>
+    <t>MRP_Price</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>EFF_DATE</t>
+  </si>
+  <si>
+    <t>18-04-2023</t>
+  </si>
+  <si>
+    <t>EFF_TO</t>
+  </si>
+  <si>
+    <t>18-04-2027</t>
+  </si>
+  <si>
+    <t>Cat_Name</t>
+  </si>
+  <si>
+    <t>Catalog</t>
+  </si>
+  <si>
+    <t>Price_Class</t>
+  </si>
+  <si>
+    <t>DOMESTIC</t>
+  </si>
+  <si>
+    <t>Price_basis</t>
+  </si>
+  <si>
+    <t>Price_Class_OSOA</t>
+  </si>
+  <si>
+    <t>INTER STATE</t>
+  </si>
+  <si>
+    <t>Item_Add_Type</t>
+  </si>
+  <si>
+    <t>TVS-FG-00006</t>
+  </si>
+  <si>
+    <t>Disc_Perent</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Hsn_Code</t>
+  </si>
+  <si>
+    <t>Cust_id</t>
+  </si>
+  <si>
+    <t>CUSEX01</t>
+  </si>
+  <si>
+    <t>oso_Docnum</t>
+  </si>
+  <si>
+    <t>OPSO1/00092/24-25</t>
+  </si>
+  <si>
+    <t>Customer_Name</t>
   </si>
 </sst>
 </file>
@@ -1868,7 +1976,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1918,6 +2026,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2239,11 +2350,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B224"/>
+  <dimension ref="A1:B249"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.6666666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4038,6 +4149,206 @@
         <v>386</v>
       </c>
     </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" t="s">
+        <v>210</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" t="s">
+        <v>212</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" t="s">
+        <v>214</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" t="s">
+        <v>216</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" t="s">
+        <v>218</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" t="s">
+        <v>396</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" t="s">
+        <v>398</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" t="s">
+        <v>400</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" t="s">
+        <v>402</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" t="s">
+        <v>404</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" t="s">
+        <v>406</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" t="s">
+        <v>408</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" t="s">
+        <v>410</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" t="s">
+        <v>411</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" t="s">
+        <v>413</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" t="s">
+        <v>415</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" t="s">
+        <v>417</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" t="s">
+        <v>418</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" t="s">
+        <v>420</v>
+      </c>
+      <c r="B248" s="31" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" t="s">
+        <v>422</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="469">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1296,6 +1296,144 @@
   </si>
   <si>
     <t>Customer_Name</t>
+  </si>
+  <si>
+    <t>PI_Type</t>
+  </si>
+  <si>
+    <t>PROFORMA INVOICE (DIRECT)</t>
+  </si>
+  <si>
+    <t>PI_Domestic_Customer</t>
+  </si>
+  <si>
+    <t>PI_Loc_Id</t>
+  </si>
+  <si>
+    <t>Proforma_Inv_Pfx</t>
+  </si>
+  <si>
+    <t>PIR0</t>
+  </si>
+  <si>
+    <t>PI_Item_ID</t>
+  </si>
+  <si>
+    <t>PI_Inv_Qty</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>PI_Inv_UnitCost</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>PI_Inv_Discount</t>
+  </si>
+  <si>
+    <t>PI_HSN_code</t>
+  </si>
+  <si>
+    <t>(740410)-18%</t>
+  </si>
+  <si>
+    <t>PI_SO_Ref_Advance</t>
+  </si>
+  <si>
+    <t>HK-FG-RC-DISSIMILAR ITEM-10001-so100-SO100/00228/24-25-1</t>
+  </si>
+  <si>
+    <t>PI_SO_Ref_Advance_Item_ID</t>
+  </si>
+  <si>
+    <t>PI_Advance_Type</t>
+  </si>
+  <si>
+    <t>PROFORMA INVOICE (ADVANCE)</t>
+  </si>
+  <si>
+    <t>PI_PreDispatch_Type</t>
+  </si>
+  <si>
+    <t>PROFORMA INVOICE (PRE DESPATCH)</t>
+  </si>
+  <si>
+    <t>Proforma_Inv_Adv_Pfx</t>
+  </si>
+  <si>
+    <t>PIA</t>
+  </si>
+  <si>
+    <t>Proforma_Inv_PreDisp_Pfx</t>
+  </si>
+  <si>
+    <t>PIP0</t>
+  </si>
+  <si>
+    <t>PI_SO_Ref_Advance_Export</t>
+  </si>
+  <si>
+    <t>HK-FG-RC-DISSIMILAR ITEM-10001-so100-SO100/00227/24-25-1</t>
+  </si>
+  <si>
+    <t>PI_SO_Ref_Advance_Export_Item_ID</t>
+  </si>
+  <si>
+    <t>PI_Pend_Domestic_SO_No</t>
+  </si>
+  <si>
+    <t>SO100/00254/24-25</t>
+  </si>
+  <si>
+    <t>PI_Pend_Export_SO_No</t>
+  </si>
+  <si>
+    <t>SO100/00251/24-25</t>
+  </si>
+  <si>
+    <t>SI_Domestic_Local_Customer</t>
+  </si>
+  <si>
+    <t>ARUN PVT LTD.</t>
+  </si>
+  <si>
+    <t>SI_Domestic_InterState_Customer</t>
+  </si>
+  <si>
+    <t>PANDI PVT. LTD</t>
+  </si>
+  <si>
+    <t>SI_Domestic_UTGST_Customer</t>
+  </si>
+  <si>
+    <t>PRAKASH PVT. LTD.</t>
+  </si>
+  <si>
+    <t>SI_Domestic_SEZ_Customer</t>
+  </si>
+  <si>
+    <t>CHENNAI SEZ</t>
+  </si>
+  <si>
+    <t>SI_Pend_Domestic_SO_No</t>
+  </si>
+  <si>
+    <t>SO100/00608/24-25</t>
+  </si>
+  <si>
+    <t>Ship_From</t>
+  </si>
+  <si>
+    <t>Exp_Status</t>
+  </si>
+  <si>
+    <t>HSN_SEZ</t>
+  </si>
+  <si>
+    <t>(765)12%</t>
   </si>
 </sst>
 </file>
@@ -1976,7 +2114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2026,7 +2164,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2350,11 +2492,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B249"/>
+  <dimension ref="A1:B276"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="39.6666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="59.8888888888889" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4190,163 +4332,379 @@
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" t="s">
+      <c r="A230" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="B230" s="1" t="s">
+      <c r="B230" s="32" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" t="s">
+      <c r="A231" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B231" s="1" t="s">
+      <c r="B231" s="32" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" t="s">
+      <c r="A232" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="B232" s="1" t="s">
+      <c r="B232" s="32" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" t="s">
+      <c r="A233" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="B233" s="1" t="s">
+      <c r="B233" s="32" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="234" spans="1:2">
-      <c r="A234" t="s">
+      <c r="A234" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="B234" s="1" t="s">
+      <c r="B234" s="32" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="235" spans="1:2">
-      <c r="A235" t="s">
+      <c r="A235" s="31" t="s">
         <v>396</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="B235" s="32" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="236" spans="1:2">
-      <c r="A236" t="s">
+      <c r="A236" s="31" t="s">
         <v>398</v>
       </c>
-      <c r="B236" s="1" t="s">
+      <c r="B236" s="32" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="237" spans="1:2">
-      <c r="A237" t="s">
+      <c r="A237" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="B237" s="32" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="238" spans="1:2">
-      <c r="A238" t="s">
+      <c r="A238" s="31" t="s">
         <v>402</v>
       </c>
-      <c r="B238" s="1" t="s">
+      <c r="B238" s="32" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="239" spans="1:2">
-      <c r="A239" t="s">
+      <c r="A239" s="31" t="s">
         <v>404</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="B239" s="32" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="240" spans="1:2">
-      <c r="A240" t="s">
+      <c r="A240" s="31" t="s">
         <v>406</v>
       </c>
-      <c r="B240" s="1" t="s">
+      <c r="B240" s="32" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="241" spans="1:2">
-      <c r="A241" t="s">
+      <c r="A241" s="31" t="s">
         <v>408</v>
       </c>
-      <c r="B241" s="1" t="s">
+      <c r="B241" s="32" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="242" spans="1:2">
-      <c r="A242" t="s">
+      <c r="A242" s="31" t="s">
         <v>410</v>
       </c>
-      <c r="B242" s="1" t="s">
+      <c r="B242" s="32" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="243" spans="1:2">
-      <c r="A243" t="s">
+      <c r="A243" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B243" s="1" t="s">
+      <c r="B243" s="32" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="244" spans="1:2">
-      <c r="A244" t="s">
+      <c r="A244" s="31" t="s">
         <v>413</v>
       </c>
-      <c r="B244" s="1" t="s">
+      <c r="B244" s="32" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="245" spans="1:2">
-      <c r="A245" t="s">
+      <c r="A245" s="31" t="s">
         <v>415</v>
       </c>
-      <c r="B245" s="1" t="s">
+      <c r="B245" s="32" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="246" spans="1:2">
-      <c r="A246" t="s">
+      <c r="A246" s="31" t="s">
         <v>417</v>
       </c>
-      <c r="B246" s="1" t="s">
+      <c r="B246" s="32" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="247" spans="1:2">
-      <c r="A247" t="s">
+      <c r="A247" s="31" t="s">
         <v>418</v>
       </c>
-      <c r="B247" s="1" t="s">
+      <c r="B247" s="32" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="248" spans="1:2">
-      <c r="A248" t="s">
+      <c r="A248" s="31" t="s">
         <v>420</v>
       </c>
-      <c r="B248" s="31" t="s">
+      <c r="B248" s="33" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="249" spans="1:2">
-      <c r="A249" t="s">
+      <c r="A249" s="31" t="s">
         <v>422</v>
       </c>
-      <c r="B249" s="1" t="s">
+      <c r="B249" s="32" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="B250" s="32" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="31" t="s">
+        <v>425</v>
+      </c>
+      <c r="B251" s="32" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="31" t="s">
+        <v>426</v>
+      </c>
+      <c r="B252" s="32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="31" t="s">
+        <v>427</v>
+      </c>
+      <c r="B253" s="32" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="31" t="s">
+        <v>429</v>
+      </c>
+      <c r="B254" s="32" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="31" t="s">
+        <v>430</v>
+      </c>
+      <c r="B255" s="32" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="31" t="s">
+        <v>432</v>
+      </c>
+      <c r="B256" s="32" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="31" t="s">
+        <v>434</v>
+      </c>
+      <c r="B257" s="32" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="31" t="s">
+        <v>435</v>
+      </c>
+      <c r="B258" s="32" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="31" t="s">
+        <v>437</v>
+      </c>
+      <c r="B259" s="32" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="31" t="s">
+        <v>439</v>
+      </c>
+      <c r="B260" s="32" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="31" t="s">
+        <v>440</v>
+      </c>
+      <c r="B261" s="32" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="31" t="s">
+        <v>442</v>
+      </c>
+      <c r="B262" s="32" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="31" t="s">
+        <v>444</v>
+      </c>
+      <c r="B263" s="32" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="B264" s="32" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="B265" s="32" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="31" t="s">
+        <v>450</v>
+      </c>
+      <c r="B266" s="32" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="31" t="s">
+        <v>451</v>
+      </c>
+      <c r="B267" s="32" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="31" t="s">
+        <v>453</v>
+      </c>
+      <c r="B268" s="32" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="31" t="s">
+        <v>455</v>
+      </c>
+      <c r="B269" s="32" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="31" t="s">
+        <v>457</v>
+      </c>
+      <c r="B270" s="32" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="31" t="s">
+        <v>459</v>
+      </c>
+      <c r="B271" s="32" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="31" t="s">
+        <v>461</v>
+      </c>
+      <c r="B272" s="32" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="31" t="s">
+        <v>463</v>
+      </c>
+      <c r="B273" s="32" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="31" t="s">
+        <v>465</v>
+      </c>
+      <c r="B274" s="32" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="B275" s="32" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="31" t="s">
+        <v>467</v>
+      </c>
+      <c r="B276" s="32" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15030" windowHeight="6540"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="471">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1434,19 +1435,19 @@
   </si>
   <si>
     <t>(765)12%</t>
+  </si>
+  <si>
+    <t>Cancel_Note_Alert</t>
+  </si>
+  <si>
+    <t>Document is cancelled.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1492,151 +1493,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1649,188 +1513,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1866,253 +1550,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2136,12 +1578,12 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2159,9 +1601,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2172,59 +1614,12 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal 2" xfId="49"/>
-    <cellStyle name="Normal 3" xfId="50"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="2"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2486,17 +1881,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B276"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B278"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="59.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4707,8 +4102,23 @@
         <v>468</v>
       </c>
     </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="B277" s="31" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B278" s="31" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15030" windowHeight="6540"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
+    <sheet name="DBData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <oleSize ref="A1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="507">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1441,13 +1441,263 @@
   </si>
   <si>
     <t>Document is cancelled.</t>
+  </si>
+  <si>
+    <t>TDSValue</t>
+  </si>
+  <si>
+    <t>194C</t>
+  </si>
+  <si>
+    <t>PRNO</t>
+  </si>
+  <si>
+    <t>${PRNO}</t>
+  </si>
+  <si>
+    <t>ExptPRNo</t>
+  </si>
+  <si>
+    <t>PR12122-00013</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>ExpectedPcrNo</t>
+  </si>
+  <si>
+    <t>PCRQ-2425-00002</t>
+  </si>
+  <si>
+    <t>UnitValue</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>LocationValue</t>
+  </si>
+  <si>
+    <t>PRH_PLNT_LOC_ID</t>
+  </si>
+  <si>
+    <t>SourceValue</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>PrhValue</t>
+  </si>
+  <si>
+    <t>PRH_RQST_PFX</t>
+  </si>
+  <si>
+    <t>CCCode</t>
+  </si>
+  <si>
+    <t>PRH_CC_CODE</t>
+  </si>
+  <si>
+    <t>DeptValue</t>
+  </si>
+  <si>
+    <t>dept_desc</t>
+  </si>
+  <si>
+    <t>RequestorValue</t>
+  </si>
+  <si>
+    <t>Requestor</t>
+  </si>
+  <si>
+    <t>FG-10001-Item</t>
+  </si>
+  <si>
+    <t>HK-TVS-FG-10001</t>
+  </si>
+  <si>
+    <t>RM-10001-Item</t>
+  </si>
+  <si>
+    <t>HK-TVS-RM-10001</t>
+  </si>
+  <si>
+    <t>ReleasedStatus</t>
+  </si>
+  <si>
+    <t>Released</t>
+  </si>
+  <si>
+    <t>UnreleasedStatus</t>
+  </si>
+  <si>
+    <t>Unreleased</t>
+  </si>
+  <si>
+    <t>PRHeaderQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT prh_plant "Unit",
+       (SELECT bup_name1
+          FROM bus_unit_plants
+         WHERE bup_bu = prh_bu AND bup_plant_id = prh_plant)
+          UNIT,
+       prh_rqst_pfx,
+       PRH_RQST_DEPT_ID,
+       (SELECT NVL (dept_name1, dept_name2)
+          FROM departments
+         WHERE dept_bu = prh_bu AND dept_id = PRH_RQST_DEPT_ID)
+          "dept_desc",
+       prh_rqst_no "Pfx.No.",
+       prh_rqst_date,
+       prh_reqstr_name "Requestor",
+       prh_narration "Narration",
+       prh_status,
+       DECODE (prh_status,
+               'A', 'Approved',
+               'E', 'Draft',
+               'C', 'Cancelled',
+               'R', 'Entry Completed',
+               'L', 'Closeshorted',
+               'R', 'RECEIVED',
+               'P', 'PARTIAL')
+          STATUS,
+       (SELECT DISTINCT apst_sub_type_desc
+          FROM appl_vou_sub_types
+         WHERE     apst_bu = prh_bu
+               AND apst_vou_type = 'PR'
+               AND apst_sub_type = prh_rec_source)
+          "Source",
+       prh_narration "Reference",
+       prh_plnt_loc_id,
+       prh_cc_code,
+       (SELECT pcc_desc
+          FROM profit_cost_centers
+         WHERE     pcc_bu = prh_bu
+               AND pcc_ac_plnt = prh_plant
+               AND pcc_cc_code = prh_cc_code)
+          "CPC Code Desc."
+  FROM pur_req_hd
+  WHERE PRH_RQST_NO ='${PRNO}'
+</t>
+  </si>
+  <si>
+    <t>PRLineQuery</t>
+  </si>
+  <si>
+    <t>SELECT PRH_RQST_NO,
+       prl_prod_id "Item",
+       prl_prod_desc1 "Item Desc.",
+       prl_prod_rev "Rev.",
+       prod_ext_desc1,
+       prl_uom "UOM",
+       prl_class_desc "Item Class",
+       prl_sub_cls_desc "Item SubClass",
+       prl_conv_factor "Conv. Factor",
+       prl_store_name "WH/Dept.",
+       prl_so_schld_desc "SO/Prj. Ref.",
+       prl_required_date prls_required_date,
+       CASE
+          WHEN prl_status = 'E' THEN 'Draft'
+          WHEN prl_status = 'N' THEN 'Entry Completed'
+          WHEN prl_status = 'A' THEN 'Approved'
+          WHEN prl_status = 'C' THEN 'Cancelled'
+          WHEN prl_status = 'L' THEN 'Closeshort'
+       END
+          prl_status,
+       DECODE (prl_status,
+               'A', 'Approved',
+               'E', 'Draft',
+               'C', 'Cancelled',
+               'R', 'Entry Completed',
+               'L', 'Closeshorted',
+               'R', 'RECEIVED',
+               'P', 'PARTIAL')
+          ln_STATUS,
+       prl_pur_acct,
+       prl_cc_code,
+       (SELECT glac_acct_desc1
+          FROM gl_accts
+         WHERE glac_bu = prl_bu AND glac_acct = prl_pur_acct)
+          "GL Acct. Desc.",
+       (SELECT pcc_desc
+          FROM profit_cost_centers
+         WHERE     pcc_bu = prl_bu
+               AND pcc_ac_plnt = prl_plnt
+               AND pcc_cc_code = prl_cc_code)
+          "CPC Code Desc.",
+       (SELECT DISTINCT DECODE (
+                  applctrl_desc_level,
+                  1,    emp_first_name1
+                     || ' '
+                     || emp_middle_name1
+                     || ' '
+                     || emp_last_name1,
+                  NVL (
+                        emp_first_name2
+                     || ' '
+                     || emp_middle_name2
+                     || ' '
+                     || emp_last_name2,
+                        emp_first_name1
+                     || ' '
+                     || emp_middle_name1
+                     || ' '
+                     || emp_last_name1))
+                  AS buyer_desc
+          FROM buyers,
+               employees,
+               appl_control,
+               emp_active_infos
+         WHERE     buyer_bu = emp_bu
+               AND buyer_emp_id = emp_emp_id
+               AND buyer_bu = applctrl_bu
+               AND emp_bu = empai_bu
+               AND emp_emp_id = empai_emp_id
+               AND buyer_bu = prl_bu
+               AND buyer_id = prl_buyer_id)
+          buyer,
+          prh_mrp_no,
+          PRL_SUGG_SUPLR_ID,
+          prl_work_ord_no,
+          PRL_SERV_PROD_ID,
+          PRL_SERV_PROD_DESC "Serv. Item desc",
+          prl_amc_start_date,
+          prl_amc_end_date,
+          PRL_MRP_REL_QTY,
+          (SELECT NVL(suplr_name1,suplr_name2)
+             FROM suppliers
+            WHERE suplr_bu = prl_bu
+            AND suplr_suplr_id = PRL_SUGG_SUPLR_ID) "Supplr. desc",
+       DECODE(prl_qc_required,'Y','Free Pass','N','Always')prl_qc_required
+  FROM pur_req_hd,
+       pur_req_ln,
+       products
+ WHERE  prh_bu ='TVSA'
+   AND PRH_RQST_NO ='${PRNO}'
+       AND prh_bu = prl_bu
+       AND prh_rqst_no = prl_rqst_no
+       AND prl_bu = prod_bu
+       AND prl_prod_id = prod_id
+       AND prl_prod_rev = prod_rev</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1493,14 +1743,156 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1509,12 +1901,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1550,24 +2128,272 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1578,12 +2404,12 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1601,25 +2427,74 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 3" xfId="2"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal 2" xfId="49"/>
+    <cellStyle name="Normal 3" xfId="50"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1881,1997 +2756,1997 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B278"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B294"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="34.287037037037" customWidth="1"/>
+    <col min="2" max="2" width="59.8518518518519" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="7">
         <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="7" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="7" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="7" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="7" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="7" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="7" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="7" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="7" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="7" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="7" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="7" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="9" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="9" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="9" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="9" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="9" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="9" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="9" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="9" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="9" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="9">
         <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="10" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="10" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="10" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="8">
+      <c r="B69" s="10">
         <v>2012</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="10" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="10" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="10" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="10" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="10">
         <v>202425</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="10" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="10" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="10" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="12" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="11" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="12" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="11" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="11" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="12" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="9" t="s">
+      <c r="A87" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B87" s="12" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" s="12" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="10" t="s">
+      <c r="A89" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="12" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="10" t="s">
+      <c r="A90" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B90" s="12" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="10" t="s">
+      <c r="A91" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" s="12" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="10" t="s">
+      <c r="A92" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="12" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="10" t="s">
+      <c r="A93" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B93" s="12" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="10" t="s">
+      <c r="A94" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B94" s="12" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="10" t="s">
+      <c r="A95" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B95" s="12" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="10" t="s">
+      <c r="A96" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B96" s="12" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="10" t="s">
+      <c r="A97" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B97" s="12" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B98" s="12" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="11" t="s">
+      <c r="A99" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="13" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="11" t="s">
+      <c r="A100" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="11" t="s">
+      <c r="A101" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="13" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="11" t="s">
+      <c r="A102" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="B102" s="11" t="s">
+      <c r="B102" s="13" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="11" t="s">
+      <c r="A103" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="B103" s="12">
+      <c r="B103" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="13" t="s">
+      <c r="A104" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="B104" s="13" t="s">
+      <c r="B104" s="15" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="13" t="s">
+      <c r="A105" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="B105" s="14" t="s">
+      <c r="B105" s="16" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="13" t="s">
+      <c r="A106" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="B106" s="15">
+      <c r="B106" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="13" t="s">
+      <c r="A107" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="B107" s="13" t="s">
+      <c r="B107" s="15" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="13" t="s">
+      <c r="A108" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="B108" s="16" t="s">
+      <c r="B108" s="18" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="13" t="s">
+      <c r="A109" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B109" s="17">
         <v>100</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="17" t="s">
+      <c r="A111" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="B111" s="17" t="s">
+      <c r="B111" s="19" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="17" t="s">
+      <c r="A112" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="B112" s="17" t="s">
+      <c r="B112" s="19" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="17" t="s">
+      <c r="A113" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="2" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="17" t="s">
+      <c r="A114" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="2" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="17" t="s">
+      <c r="A115" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="2" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="18" t="s">
+      <c r="A118" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="B118" s="19" t="s">
+      <c r="B118" s="21" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="18" t="s">
+      <c r="A119" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="B119" s="19" t="s">
+      <c r="B119" s="21" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="18" t="s">
+      <c r="A120" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="B120" s="19" t="s">
+      <c r="B120" s="21" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="18" t="s">
+      <c r="A121" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="B121" s="19" t="s">
+      <c r="B121" s="21" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="18" t="s">
+      <c r="A122" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="B122" s="19" t="s">
+      <c r="B122" s="21" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="18" t="s">
+      <c r="A123" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="B123" s="19" t="s">
+      <c r="B123" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="18" t="s">
+      <c r="A124" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="B124" s="19" t="s">
+      <c r="B124" s="21" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="18" t="s">
+      <c r="A125" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="B125" s="19" t="s">
+      <c r="B125" s="21" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="18" t="s">
+      <c r="A126" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="B126" s="19" t="s">
+      <c r="B126" s="21" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="18" t="s">
+      <c r="A127" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="B127" s="19" t="s">
+      <c r="B127" s="21" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="18" t="s">
+      <c r="A128" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="B128" s="19" t="s">
+      <c r="B128" s="21" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="18" t="s">
+      <c r="A129" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="B129" s="19" t="s">
+      <c r="B129" s="21" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="18" t="s">
+      <c r="A130" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="B130" s="19" t="s">
+      <c r="B130" s="21" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="18" t="s">
+      <c r="A131" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="B131" s="19" t="s">
+      <c r="B131" s="21" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="18" t="s">
+      <c r="A132" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="B132" s="19" t="s">
+      <c r="B132" s="21" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="18" t="s">
+      <c r="A133" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="B133" s="19" t="s">
+      <c r="B133" s="21" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="18" t="s">
+      <c r="A134" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="B134" s="19" t="s">
+      <c r="B134" s="21" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="18" t="s">
+      <c r="A135" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="B135" s="19" t="s">
+      <c r="B135" s="21" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="18" t="s">
+      <c r="A136" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="B136" s="19" t="s">
+      <c r="B136" s="21" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="18" t="s">
+      <c r="A137" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="B137" s="19" t="s">
+      <c r="B137" s="21" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="18" t="s">
+      <c r="A138" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="B138" s="19" t="s">
+      <c r="B138" s="21" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="18" t="s">
+      <c r="A139" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="B139" s="19" t="s">
+      <c r="B139" s="21" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="18" t="s">
+      <c r="A140" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="B140" s="19" t="s">
+      <c r="B140" s="21" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="18" t="s">
+      <c r="A141" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="B141" s="19" t="s">
+      <c r="B141" s="21" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="18" t="s">
+      <c r="A142" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="B142" s="19" t="s">
+      <c r="B142" s="21" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="18" t="s">
+      <c r="A143" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="B143" s="19" t="s">
+      <c r="B143" s="21" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="18" t="s">
+      <c r="A144" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="B144" s="19" t="s">
+      <c r="B144" s="21" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="18" t="s">
+      <c r="A145" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="B145" s="19" t="s">
+      <c r="B145" s="21" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="18" t="s">
+      <c r="A146" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="B146" s="19" t="s">
+      <c r="B146" s="21" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="18" t="s">
+      <c r="A147" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="B147" s="19" t="s">
+      <c r="B147" s="21" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="18" t="s">
+      <c r="A148" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="B148" s="19" t="s">
+      <c r="B148" s="21" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="18" t="s">
+      <c r="A149" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="B149" s="19" t="s">
+      <c r="B149" s="21" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="20" t="s">
+      <c r="A150" s="22" t="s">
         <v>267</v>
       </c>
-      <c r="B150" s="19" t="s">
+      <c r="B150" s="21" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="20" t="s">
+      <c r="A151" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="B151" s="19" t="s">
+      <c r="B151" s="21" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="20" t="s">
+      <c r="A152" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="B152" s="19" t="s">
+      <c r="B152" s="21" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="20" t="s">
+      <c r="A153" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="B153" s="19" t="s">
+      <c r="B153" s="21" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="20" t="s">
+      <c r="A154" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="B154" s="19" t="s">
+      <c r="B154" s="21" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="20" t="s">
+      <c r="A155" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="B155" s="19" t="s">
+      <c r="B155" s="21" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="21" t="s">
+      <c r="A156" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="B156" s="22" t="s">
+      <c r="B156" s="24" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B157" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="9" t="s">
+      <c r="A158" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="B158" s="23" t="s">
+      <c r="B158" s="25" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="9" t="s">
+      <c r="A159" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="B159" s="24" t="s">
+      <c r="B159" s="26" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="9" t="s">
+      <c r="A160" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="B160" s="9" t="s">
+      <c r="B160" s="11" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="9" t="s">
+      <c r="A161" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="B161" s="24" t="s">
+      <c r="B161" s="26" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="9" t="s">
+      <c r="A162" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B162" s="24" t="s">
+      <c r="B162" s="26" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="9" t="s">
+      <c r="A163" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="B163" s="9" t="s">
+      <c r="B163" s="11" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="9" t="s">
+      <c r="A164" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="B164" s="9" t="s">
+      <c r="B164" s="11" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="9" t="s">
+      <c r="A165" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="B165" s="24" t="s">
+      <c r="B165" s="26" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="9" t="s">
+      <c r="A166" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B166" s="24" t="s">
+      <c r="B166" s="26" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="9" t="s">
+      <c r="A167" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B167" s="9" t="s">
+      <c r="B167" s="11" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="9" t="s">
+      <c r="A168" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="B168" s="9" t="s">
+      <c r="B168" s="11" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="9" t="s">
+      <c r="A169" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="B169" s="24" t="s">
+      <c r="B169" s="26" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="9" t="s">
+      <c r="A170" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="B170" s="24" t="s">
+      <c r="B170" s="26" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="9" t="s">
+      <c r="A171" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="B171" s="24" t="s">
+      <c r="B171" s="26" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="9" t="s">
+      <c r="A172" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="B172" s="24" t="s">
+      <c r="B172" s="26" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="9" t="s">
+      <c r="A173" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B173" s="24" t="s">
+      <c r="B173" s="26" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="9" t="s">
+      <c r="A174" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="B174" s="24" t="s">
+      <c r="B174" s="26" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="9" t="s">
+      <c r="A175" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="B175" s="24" t="s">
+      <c r="B175" s="26" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="9" t="s">
+      <c r="A176" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="B176" s="24" t="s">
+      <c r="B176" s="26" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="9" t="s">
+      <c r="A177" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="B177" s="24" t="s">
+      <c r="B177" s="26" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="9" t="s">
+      <c r="A178" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="B178" s="24" t="s">
+      <c r="B178" s="26" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="9" t="s">
+      <c r="A179" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="B179" s="24" t="s">
+      <c r="B179" s="26" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="9" t="s">
+      <c r="A180" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="B180" s="24" t="s">
+      <c r="B180" s="26" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="9" t="s">
+      <c r="A181" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="B181" s="24" t="s">
+      <c r="B181" s="26" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="9" t="s">
+      <c r="A182" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="B182" s="24" t="s">
+      <c r="B182" s="26" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="9" t="s">
+      <c r="A183" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="B183" s="24" t="s">
+      <c r="B183" s="26" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="9" t="s">
+      <c r="A184" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="B184" s="24" t="s">
+      <c r="B184" s="26" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="9" t="s">
+      <c r="A185" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="B185" s="9" t="s">
+      <c r="B185" s="11" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="9" t="s">
+      <c r="A186" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="B186" s="9" t="s">
+      <c r="B186" s="11" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="9" t="s">
+      <c r="A187" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B187" s="24" t="s">
+      <c r="B187" s="26" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="9" t="s">
+      <c r="A188" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B188" s="9" t="s">
+      <c r="B188" s="11" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="9" t="s">
+      <c r="A189" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="B189" s="24" t="s">
+      <c r="B189" s="26" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="4" t="s">
+      <c r="A190" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B190" s="25" t="s">
+      <c r="B190" s="27" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="26" t="s">
+      <c r="A191" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="B191" s="26" t="s">
+      <c r="B191" s="28" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="26" t="s">
+      <c r="A192" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="B192" s="27" t="s">
+      <c r="B192" s="29" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="26" t="s">
+      <c r="A193" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="B193" s="12">
+      <c r="B193" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="26" t="s">
+      <c r="A194" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="B194" s="26" t="s">
+      <c r="B194" s="28" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="26" t="s">
+      <c r="A195" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="B195" s="11" t="s">
+      <c r="B195" s="13" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="26" t="s">
+      <c r="A196" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="B196" s="12">
+      <c r="B196" s="14">
         <v>100</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="26" t="s">
+      <c r="A197" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="B197" s="12" t="s">
+      <c r="B197" s="14" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="26" t="s">
+      <c r="A198" s="28" t="s">
         <v>347</v>
       </c>
-      <c r="B198" s="28" t="s">
+      <c r="B198" s="30" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="26" t="s">
+      <c r="A199" s="28" t="s">
         <v>349</v>
       </c>
-      <c r="B199" s="28" t="s">
+      <c r="B199" s="30" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="26" t="s">
+      <c r="A200" s="28" t="s">
         <v>351</v>
       </c>
-      <c r="B200" s="28" t="s">
+      <c r="B200" s="30" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="26" t="s">
+      <c r="A201" s="28" t="s">
         <v>353</v>
       </c>
-      <c r="B201" s="12">
+      <c r="B201" s="14">
         <v>200</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="26" t="s">
+      <c r="A202" s="28" t="s">
         <v>354</v>
       </c>
-      <c r="B202" s="12">
+      <c r="B202" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="26" t="s">
+      <c r="A203" s="28" t="s">
         <v>355</v>
       </c>
-      <c r="B203" s="12" t="s">
+      <c r="B203" s="14" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="12" t="s">
+      <c r="A204" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="B204" s="12">
+      <c r="B204" s="14">
         <v>150</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="12" t="s">
+      <c r="A205" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="B205" s="12">
+      <c r="B205" s="14">
         <v>250</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="12" t="s">
+      <c r="A206" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="B206" s="12" t="s">
+      <c r="B206" s="14" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="12" t="s">
+      <c r="A207" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="B207" s="12">
+      <c r="B207" s="14">
         <v>123562</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="12" t="s">
+      <c r="A208" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="B208" s="12">
+      <c r="B208" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="12" t="s">
+      <c r="A209" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="B209" s="12">
+      <c r="B209" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="12" t="s">
+      <c r="A210" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="B210" s="12">
+      <c r="B210" s="14">
         <v>4</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="12" t="s">
+      <c r="A211" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="B211" s="27" t="s">
+      <c r="B211" s="29" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="12" t="s">
+      <c r="A212" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="B212" s="11" t="s">
+      <c r="B212" s="13" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="12" t="s">
+      <c r="A213" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="B213" s="27" t="s">
+      <c r="B213" s="29" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="12" t="s">
+      <c r="A214" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="B214" s="12">
+      <c r="B214" s="14">
         <v>50</v>
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="12" t="s">
+      <c r="A215" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="B215" s="12">
+      <c r="B215" s="14">
         <v>50</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="12" t="s">
+      <c r="A216" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="B216" s="27" t="s">
+      <c r="B216" s="29" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="4" t="s">
+      <c r="A217" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="B217" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="21" t="s">
+      <c r="A218" s="23" t="s">
         <v>374</v>
       </c>
-      <c r="B218" s="21" t="s">
+      <c r="B218" s="23" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="21" t="s">
+      <c r="A219" s="23" t="s">
         <v>375</v>
       </c>
-      <c r="B219" s="4" t="s">
+      <c r="B219" s="2" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="21" t="s">
+      <c r="A220" s="23" t="s">
         <v>377</v>
       </c>
-      <c r="B220" s="4" t="s">
+      <c r="B220" s="2" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="29" t="s">
+      <c r="A221" s="31" t="s">
         <v>379</v>
       </c>
-      <c r="B221" s="21" t="s">
+      <c r="B221" s="23" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="29" t="s">
+      <c r="A222" s="31" t="s">
         <v>381</v>
       </c>
-      <c r="B222" s="21" t="s">
+      <c r="B222" s="23" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="30" t="s">
+      <c r="A223" s="32" t="s">
         <v>383</v>
       </c>
-      <c r="B223" s="30" t="s">
+      <c r="B223" s="32" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="29" t="s">
+      <c r="A224" s="31" t="s">
         <v>385</v>
       </c>
-      <c r="B224" s="29" t="s">
+      <c r="B224" s="31" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="4" t="s">
+      <c r="A225" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B225" s="5" t="s">
+      <c r="B225" s="7" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="4" t="s">
+      <c r="A226" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B226" s="5" t="s">
+      <c r="B226" s="7" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="4" t="s">
+      <c r="A227" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B227" s="5" t="s">
+      <c r="B227" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="4" t="s">
+      <c r="A228" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B228" s="5" t="s">
+      <c r="B228" s="7" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="4" t="s">
+      <c r="A229" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B229" s="5" t="s">
+      <c r="B229" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="31" t="s">
+      <c r="A230" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B230" s="32" t="s">
+      <c r="B230" s="7" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="31" t="s">
+      <c r="A231" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B231" s="32" t="s">
+      <c r="B231" s="7" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="31" t="s">
+      <c r="A232" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B232" s="32" t="s">
+      <c r="B232" s="7" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="31" t="s">
+      <c r="A233" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B233" s="32" t="s">
+      <c r="B233" s="7" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="234" spans="1:2">
-      <c r="A234" s="31" t="s">
+      <c r="A234" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B234" s="32" t="s">
+      <c r="B234" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="235" spans="1:2">
-      <c r="A235" s="31" t="s">
+      <c r="A235" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B235" s="32" t="s">
+      <c r="B235" s="7" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="236" spans="1:2">
-      <c r="A236" s="31" t="s">
+      <c r="A236" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B236" s="32" t="s">
+      <c r="B236" s="7" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="237" spans="1:2">
-      <c r="A237" s="31" t="s">
+      <c r="A237" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B237" s="32" t="s">
+      <c r="B237" s="7" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="238" spans="1:2">
-      <c r="A238" s="31" t="s">
+      <c r="A238" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B238" s="32" t="s">
+      <c r="B238" s="7" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="239" spans="1:2">
-      <c r="A239" s="31" t="s">
+      <c r="A239" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B239" s="32" t="s">
+      <c r="B239" s="7" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="240" spans="1:2">
-      <c r="A240" s="31" t="s">
+      <c r="A240" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B240" s="32" t="s">
+      <c r="B240" s="7" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="241" spans="1:2">
-      <c r="A241" s="31" t="s">
+      <c r="A241" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B241" s="32" t="s">
+      <c r="B241" s="7" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="242" spans="1:2">
-      <c r="A242" s="31" t="s">
+      <c r="A242" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B242" s="32" t="s">
+      <c r="B242" s="7" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="243" spans="1:2">
-      <c r="A243" s="31" t="s">
+      <c r="A243" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B243" s="32" t="s">
+      <c r="B243" s="7" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="244" spans="1:2">
-      <c r="A244" s="31" t="s">
+      <c r="A244" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B244" s="32" t="s">
+      <c r="B244" s="7" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="245" spans="1:2">
-      <c r="A245" s="31" t="s">
+      <c r="A245" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B245" s="32" t="s">
+      <c r="B245" s="7" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="246" spans="1:2">
-      <c r="A246" s="31" t="s">
+      <c r="A246" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B246" s="32" t="s">
+      <c r="B246" s="7" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="247" spans="1:2">
-      <c r="A247" s="31" t="s">
+      <c r="A247" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B247" s="32" t="s">
+      <c r="B247" s="7" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="248" spans="1:2">
-      <c r="A248" s="31" t="s">
+      <c r="A248" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B248" s="33" t="s">
@@ -3879,246 +4754,475 @@
       </c>
     </row>
     <row r="249" spans="1:2">
-      <c r="A249" s="31" t="s">
+      <c r="A249" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B249" s="32" t="s">
+      <c r="B249" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="250" spans="1:2">
-      <c r="A250" s="31" t="s">
+      <c r="A250" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B250" s="32" t="s">
+      <c r="B250" s="7" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="251" spans="1:2">
-      <c r="A251" s="31" t="s">
+      <c r="A251" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B251" s="32" t="s">
+      <c r="B251" s="7" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="252" spans="1:2">
-      <c r="A252" s="31" t="s">
+      <c r="A252" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B252" s="32" t="s">
+      <c r="B252" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="253" spans="1:2">
-      <c r="A253" s="31" t="s">
+      <c r="A253" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B253" s="32" t="s">
+      <c r="B253" s="7" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="254" spans="1:2">
-      <c r="A254" s="31" t="s">
+      <c r="A254" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B254" s="32" t="s">
+      <c r="B254" s="7" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="255" spans="1:2">
-      <c r="A255" s="31" t="s">
+      <c r="A255" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B255" s="32" t="s">
+      <c r="B255" s="7" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="256" spans="1:2">
-      <c r="A256" s="31" t="s">
+      <c r="A256" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B256" s="32" t="s">
+      <c r="B256" s="7" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="257" spans="1:2">
-      <c r="A257" s="31" t="s">
+      <c r="A257" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B257" s="32" t="s">
+      <c r="B257" s="7" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="258" spans="1:2">
-      <c r="A258" s="31" t="s">
+      <c r="A258" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B258" s="32" t="s">
+      <c r="B258" s="7" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="259" spans="1:2">
-      <c r="A259" s="31" t="s">
+      <c r="A259" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B259" s="32" t="s">
+      <c r="B259" s="7" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="260" spans="1:2">
-      <c r="A260" s="31" t="s">
+      <c r="A260" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="B260" s="32" t="s">
+      <c r="B260" s="7" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="261" spans="1:2">
-      <c r="A261" s="31" t="s">
+      <c r="A261" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="B261" s="32" t="s">
+      <c r="B261" s="7" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="262" spans="1:2">
-      <c r="A262" s="31" t="s">
+      <c r="A262" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="B262" s="32" t="s">
+      <c r="B262" s="7" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="263" spans="1:2">
-      <c r="A263" s="31" t="s">
+      <c r="A263" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B263" s="32" t="s">
+      <c r="B263" s="7" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="264" spans="1:2">
-      <c r="A264" s="31" t="s">
+      <c r="A264" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B264" s="32" t="s">
+      <c r="B264" s="7" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="265" spans="1:2">
-      <c r="A265" s="31" t="s">
+      <c r="A265" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B265" s="32" t="s">
+      <c r="B265" s="7" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="266" spans="1:2">
-      <c r="A266" s="31" t="s">
+      <c r="A266" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="B266" s="32" t="s">
+      <c r="B266" s="7" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="267" spans="1:2">
-      <c r="A267" s="31" t="s">
+      <c r="A267" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B267" s="32" t="s">
+      <c r="B267" s="7" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="268" spans="1:2">
-      <c r="A268" s="31" t="s">
+      <c r="A268" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B268" s="32" t="s">
+      <c r="B268" s="7" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="269" spans="1:2">
-      <c r="A269" s="31" t="s">
+      <c r="A269" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B269" s="32" t="s">
+      <c r="B269" s="7" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="270" spans="1:2">
-      <c r="A270" s="31" t="s">
+      <c r="A270" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="B270" s="32" t="s">
+      <c r="B270" s="7" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="271" spans="1:2">
-      <c r="A271" s="31" t="s">
+      <c r="A271" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B271" s="32" t="s">
+      <c r="B271" s="7" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="272" spans="1:2">
-      <c r="A272" s="31" t="s">
+      <c r="A272" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B272" s="32" t="s">
+      <c r="B272" s="7" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="273" spans="1:2">
-      <c r="A273" s="31" t="s">
+      <c r="A273" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B273" s="32" t="s">
+      <c r="B273" s="7" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="274" spans="1:2">
-      <c r="A274" s="31" t="s">
+      <c r="A274" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B274" s="32" t="s">
+      <c r="B274" s="7" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="275" spans="1:2">
-      <c r="A275" s="31" t="s">
+      <c r="A275" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="B275" s="32" t="s">
+      <c r="B275" s="7" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="276" spans="1:2">
-      <c r="A276" s="31" t="s">
+      <c r="A276" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B276" s="32" t="s">
+      <c r="B276" s="7" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="277" spans="1:2">
-      <c r="A277" s="17" t="s">
+      <c r="A277" s="19" t="s">
         <v>469</v>
       </c>
-      <c r="B277" s="31" t="s">
+      <c r="B277" s="2" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="278" spans="1:2">
-      <c r="A278" s="31" t="s">
+      <c r="A278" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B278" s="31" t="s">
+      <c r="B278" s="2" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B279" s="7" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="B280" s="9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="B281" s="9" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="B282" s="9" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="B283" s="34" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="35" t="s">
+        <v>481</v>
+      </c>
+      <c r="B284" s="7" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="35" t="s">
+        <v>483</v>
+      </c>
+      <c r="B285" s="7" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="35" t="s">
+        <v>485</v>
+      </c>
+      <c r="B286" s="7" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="35" t="s">
+        <v>487</v>
+      </c>
+      <c r="B287" s="7" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="B288" s="7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="35" t="s">
+        <v>491</v>
+      </c>
+      <c r="B289" s="7" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="35" t="s">
+        <v>493</v>
+      </c>
+      <c r="B290" s="7" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="36" t="s">
+        <v>495</v>
+      </c>
+      <c r="B291" s="37" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="36" t="s">
+        <v>497</v>
+      </c>
+      <c r="B292" s="37" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="36" t="s">
+        <v>499</v>
+      </c>
+      <c r="B293" s="37" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="36" t="s">
+        <v>501</v>
+      </c>
+      <c r="B294" s="37" t="s">
+        <v>502</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="19.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="65" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="109" customHeight="1" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3" ht="114" customHeight="1" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="528">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1537,6 +1537,69 @@
   </si>
   <si>
     <t>Unreleased</t>
+  </si>
+  <si>
+    <t>oso_Docnum_PCC_Local</t>
+  </si>
+  <si>
+    <t>oso_Docnum_Delete</t>
+  </si>
+  <si>
+    <t>OPSO1/00001/24-25</t>
+  </si>
+  <si>
+    <t>oso_Docnum_PC_Local</t>
+  </si>
+  <si>
+    <t>oso_Docnum_Add_Local</t>
+  </si>
+  <si>
+    <t>OSOD-2425-00240</t>
+  </si>
+  <si>
+    <t>oso_Docnum_Cancel</t>
+  </si>
+  <si>
+    <t>OSO30-2425-00005</t>
+  </si>
+  <si>
+    <t>oso_Docnum_PC_IS</t>
+  </si>
+  <si>
+    <t>OPSO1/00110/24-25</t>
+  </si>
+  <si>
+    <t>oso_Docnum_PCC_IS</t>
+  </si>
+  <si>
+    <t>oso_Docnum_Add_IS</t>
+  </si>
+  <si>
+    <t>OPSO1/00132/24-25</t>
+  </si>
+  <si>
+    <t>oso_Docnum_Delete_IS</t>
+  </si>
+  <si>
+    <t>oso_Docnum_PC_EX</t>
+  </si>
+  <si>
+    <t>OPSO1/00134/24-25</t>
+  </si>
+  <si>
+    <t>oso_Docnum_PCC_EX</t>
+  </si>
+  <si>
+    <t>oso_Docnum_Add_EX</t>
+  </si>
+  <si>
+    <t>OPSO1/00115/24-25</t>
+  </si>
+  <si>
+    <t>oso_Docnum_Delete_EX</t>
+  </si>
+  <si>
+    <t>OPSO1/00135/24-25</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2762,11 +2825,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B294"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B307"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="34.287037037037" customWidth="1"/>
-    <col min="2" max="2" width="59.8518518518519" style="4" customWidth="1"/>
+    <col min="1" max="1" width="34.2909090909091" customWidth="1"/>
+    <col min="2" max="2" width="59.8545454545455" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5090,35 +5153,139 @@
       </c>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="36" t="s">
+      <c r="A291" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B291" s="37" t="s">
+      <c r="B291" s="7" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="292" spans="1:2">
-      <c r="A292" s="36" t="s">
+      <c r="A292" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B292" s="37" t="s">
+      <c r="B292" s="7" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="293" spans="1:2">
-      <c r="A293" s="36" t="s">
+      <c r="A293" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="B293" s="37" t="s">
+      <c r="B293" s="7" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="294" spans="1:2">
-      <c r="A294" s="36" t="s">
+      <c r="A294" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B294" s="37" t="s">
+      <c r="B294" s="7" t="s">
         <v>502</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="36" t="s">
+        <v>503</v>
+      </c>
+      <c r="B295" s="37" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="36" t="s">
+        <v>504</v>
+      </c>
+      <c r="B296" s="37" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="B297" s="37" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="B298" s="37" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="36" t="s">
+        <v>509</v>
+      </c>
+      <c r="B299" s="37" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="36" t="s">
+        <v>511</v>
+      </c>
+      <c r="B300" s="37" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="36" t="s">
+        <v>513</v>
+      </c>
+      <c r="B301" s="37" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="36" t="s">
+        <v>514</v>
+      </c>
+      <c r="B302" s="37" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="36" t="s">
+        <v>516</v>
+      </c>
+      <c r="B303" s="37" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="36" t="s">
+        <v>517</v>
+      </c>
+      <c r="B304" s="37" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="36" t="s">
+        <v>519</v>
+      </c>
+      <c r="B305" s="37" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="36" t="s">
+        <v>520</v>
+      </c>
+      <c r="B306" s="37" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="36" t="s">
+        <v>522</v>
+      </c>
+      <c r="B307" s="37" t="s">
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -5131,9 +5298,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="19.8909090909091" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5147,18 +5314,18 @@
     </row>
     <row r="2" ht="109" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="546">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1600,6 +1600,60 @@
   </si>
   <si>
     <t>OPSO1/00135/24-25</t>
+  </si>
+  <si>
+    <t>ClassValue</t>
+  </si>
+  <si>
+    <t>Item Class</t>
+  </si>
+  <si>
+    <t>SubClassValue</t>
+  </si>
+  <si>
+    <t>Item SubClass</t>
+  </si>
+  <si>
+    <t>WHValue</t>
+  </si>
+  <si>
+    <t>WH/Dept.</t>
+  </si>
+  <si>
+    <t>ConvValue</t>
+  </si>
+  <si>
+    <t>Conv. Factor</t>
+  </si>
+  <si>
+    <t>UOMValue</t>
+  </si>
+  <si>
+    <t>UOM</t>
+  </si>
+  <si>
+    <t>GLValue</t>
+  </si>
+  <si>
+    <t>PRL_PUR_ACCT</t>
+  </si>
+  <si>
+    <t>GLDescValue</t>
+  </si>
+  <si>
+    <t>GL Acct. Desc.</t>
+  </si>
+  <si>
+    <t>CCCodeLineValue</t>
+  </si>
+  <si>
+    <t>PRL_CC_CODE</t>
+  </si>
+  <si>
+    <t>CCDescValue</t>
+  </si>
+  <si>
+    <t>CPC Code Desc.</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2439,7 +2493,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2500,10 +2554,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2825,11 +2875,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B307"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B316"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="34.2909090909091" customWidth="1"/>
-    <col min="2" max="2" width="59.8545454545455" style="4" customWidth="1"/>
+    <col min="1" max="1" width="34.287037037037" customWidth="1"/>
+    <col min="2" max="2" width="59.8518518518519" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5185,107 +5235,179 @@
       </c>
     </row>
     <row r="295" spans="1:2">
-      <c r="A295" s="36" t="s">
+      <c r="A295" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B295" s="37" t="s">
+      <c r="B295" s="7" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="296" spans="1:2">
-      <c r="A296" s="36" t="s">
+      <c r="A296" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="B296" s="37" t="s">
+      <c r="B296" s="7" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="297" spans="1:2">
-      <c r="A297" s="36" t="s">
+      <c r="A297" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B297" s="37" t="s">
+      <c r="B297" s="7" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="298" spans="1:2">
-      <c r="A298" s="36" t="s">
+      <c r="A298" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="B298" s="37" t="s">
+      <c r="B298" s="7" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="299" spans="1:2">
-      <c r="A299" s="36" t="s">
+      <c r="A299" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="B299" s="37" t="s">
+      <c r="B299" s="7" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="300" spans="1:2">
-      <c r="A300" s="36" t="s">
+      <c r="A300" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="B300" s="37" t="s">
+      <c r="B300" s="7" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="301" spans="1:2">
-      <c r="A301" s="36" t="s">
+      <c r="A301" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B301" s="37" t="s">
+      <c r="B301" s="7" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="302" spans="1:2">
-      <c r="A302" s="36" t="s">
+      <c r="A302" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B302" s="37" t="s">
+      <c r="B302" s="7" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="303" spans="1:2">
-      <c r="A303" s="36" t="s">
+      <c r="A303" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="B303" s="37" t="s">
+      <c r="B303" s="7" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="304" spans="1:2">
-      <c r="A304" s="36" t="s">
+      <c r="A304" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="B304" s="37" t="s">
+      <c r="B304" s="7" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="305" spans="1:2">
-      <c r="A305" s="36" t="s">
+      <c r="A305" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="B305" s="37" t="s">
+      <c r="B305" s="7" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="306" spans="1:2">
-      <c r="A306" s="36" t="s">
+      <c r="A306" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="B306" s="37" t="s">
+      <c r="B306" s="7" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="307" spans="1:2">
-      <c r="A307" s="36" t="s">
+      <c r="A307" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B307" s="37" t="s">
+      <c r="B307" s="7" t="s">
         <v>523</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B308" s="7" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B310" s="7" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B311" s="7" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B312" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B314" s="7" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B315" s="7" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B316" s="7" t="s">
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -5298,9 +5420,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.8909090909091" customWidth="1"/>
+    <col min="1" max="1" width="19.8888888888889" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5314,18 +5436,18 @@
     </row>
     <row r="2" ht="109" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="550">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1539,13 +1539,67 @@
     <t>Unreleased</t>
   </si>
   <si>
+    <t>ClassValue</t>
+  </si>
+  <si>
+    <t>Item Class</t>
+  </si>
+  <si>
+    <t>SubClassValue</t>
+  </si>
+  <si>
+    <t>Item SubClass</t>
+  </si>
+  <si>
+    <t>WHValue</t>
+  </si>
+  <si>
+    <t>WH/Dept.</t>
+  </si>
+  <si>
+    <t>ConvValue</t>
+  </si>
+  <si>
+    <t>Conv. Factor</t>
+  </si>
+  <si>
+    <t>UOMValue</t>
+  </si>
+  <si>
+    <t>UOM</t>
+  </si>
+  <si>
+    <t>GLValue</t>
+  </si>
+  <si>
+    <t>PRL_PUR_ACCT</t>
+  </si>
+  <si>
+    <t>GLDescValue</t>
+  </si>
+  <si>
+    <t>GL Acct. Desc.</t>
+  </si>
+  <si>
+    <t>CCCodeLineValue</t>
+  </si>
+  <si>
+    <t>PRL_CC_CODE</t>
+  </si>
+  <si>
+    <t>CCDescValue</t>
+  </si>
+  <si>
+    <t>CPC Code Desc.</t>
+  </si>
+  <si>
     <t>oso_Docnum_PCC_Local</t>
   </si>
   <si>
     <t>oso_Docnum_Delete</t>
   </si>
   <si>
-    <t>OPSO1/00001/24-25</t>
+    <t>OSOD-2425-00202</t>
   </si>
   <si>
     <t>oso_Docnum_PC_Local</t>
@@ -1575,12 +1629,12 @@
     <t>oso_Docnum_Add_IS</t>
   </si>
   <si>
-    <t>OPSO1/00132/24-25</t>
-  </si>
-  <si>
     <t>oso_Docnum_Delete_IS</t>
   </si>
   <si>
+    <t>OPSO1/00145/24-25</t>
+  </si>
+  <si>
     <t>oso_Docnum_PC_EX</t>
   </si>
   <si>
@@ -1599,61 +1653,19 @@
     <t>oso_Docnum_Delete_EX</t>
   </si>
   <si>
-    <t>OPSO1/00135/24-25</t>
-  </si>
-  <si>
-    <t>ClassValue</t>
-  </si>
-  <si>
-    <t>Item Class</t>
-  </si>
-  <si>
-    <t>SubClassValue</t>
-  </si>
-  <si>
-    <t>Item SubClass</t>
-  </si>
-  <si>
-    <t>WHValue</t>
-  </si>
-  <si>
-    <t>WH/Dept.</t>
-  </si>
-  <si>
-    <t>ConvValue</t>
-  </si>
-  <si>
-    <t>Conv. Factor</t>
-  </si>
-  <si>
-    <t>UOMValue</t>
-  </si>
-  <si>
-    <t>UOM</t>
-  </si>
-  <si>
-    <t>GLValue</t>
-  </si>
-  <si>
-    <t>PRL_PUR_ACCT</t>
-  </si>
-  <si>
-    <t>GLDescValue</t>
-  </si>
-  <si>
-    <t>GL Acct. Desc.</t>
-  </si>
-  <si>
-    <t>CCCodeLineValue</t>
-  </si>
-  <si>
-    <t>PRL_CC_CODE</t>
-  </si>
-  <si>
-    <t>CCDescValue</t>
-  </si>
-  <si>
-    <t>CPC Code Desc.</t>
+    <t>OSOD-2425-00284</t>
+  </si>
+  <si>
+    <t>PI_PaymentTerm</t>
+  </si>
+  <si>
+    <t>T002</t>
+  </si>
+  <si>
+    <t>IntraTransfer</t>
+  </si>
+  <si>
+    <t>Intra Transfer</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2493,7 +2505,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2554,6 +2566,8 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2875,7 +2889,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B316"/>
+  <dimension ref="A1:B318"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="34.287037037037" customWidth="1"/>
@@ -5239,159 +5253,159 @@
         <v>503</v>
       </c>
       <c r="B295" s="7" t="s">
-        <v>421</v>
+        <v>504</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B296" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>421</v>
+        <v>508</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B298" s="7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B299" s="7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B300" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B302" s="7" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B304" s="7" t="s">
-        <v>518</v>
+        <v>421</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B305" s="7" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B306" s="7" t="s">
-        <v>521</v>
+        <v>421</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B308" s="7" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B309" s="7" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B310" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B311" s="7" t="s">
         <v>530</v>
-      </c>
-      <c r="B311" s="7" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B312" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B313" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B314" s="7" t="s">
         <v>536</v>
-      </c>
-      <c r="B314" s="7" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5408,6 +5422,22 @@
       </c>
       <c r="B316" s="7" t="s">
         <v>541</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B317" s="7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="36" t="s">
+        <v>544</v>
+      </c>
+      <c r="B318" s="37" t="s">
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -5436,18 +5466,18 @@
     </row>
     <row r="2" ht="109" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="567">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -177,7 +177,7 @@
     <t>ServiceType</t>
   </si>
   <si>
-    <t>PO - SERVICE</t>
+    <t>PO - SERVICES</t>
   </si>
   <si>
     <t>DissimilarItem</t>
@@ -1666,6 +1666,57 @@
   </si>
   <si>
     <t>Intra Transfer</t>
+  </si>
+  <si>
+    <t>Warehouse100</t>
+  </si>
+  <si>
+    <t>FG WAREHOUSE 100</t>
+  </si>
+  <si>
+    <t>Vinoth</t>
+  </si>
+  <si>
+    <t>VINOTH</t>
+  </si>
+  <si>
+    <t>ManualValue</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>EntryStatus</t>
+  </si>
+  <si>
+    <t>Entry Completed</t>
+  </si>
+  <si>
+    <t>L30</t>
+  </si>
+  <si>
+    <t>Dis</t>
+  </si>
+  <si>
+    <t>TVS-DIS-</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>TVS-SIM-</t>
+  </si>
+  <si>
+    <t>Amd_Sim</t>
+  </si>
+  <si>
+    <t>TVS-AMD-SIM-</t>
+  </si>
+  <si>
+    <t>Amd_Dis</t>
+  </si>
+  <si>
+    <t>TVS-AMD-DIS-</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2567,7 +2618,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2889,7 +2942,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B318"/>
+  <dimension ref="A1:B327"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="34.287037037037" customWidth="1"/>
@@ -5433,11 +5486,83 @@
       </c>
     </row>
     <row r="318" spans="1:2">
-      <c r="A318" s="36" t="s">
+      <c r="A318" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="B318" s="37" t="s">
+      <c r="B318" s="8" t="s">
         <v>545</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B322" s="7" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B323" s="7" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="36" t="s">
+        <v>555</v>
+      </c>
+      <c r="B324" s="37" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="B325" s="37" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="36" t="s">
+        <v>559</v>
+      </c>
+      <c r="B326" s="37" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="36" t="s">
+        <v>561</v>
+      </c>
+      <c r="B327" s="37" t="s">
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -5466,18 +5591,18 @@
     </row>
     <row r="2" ht="109" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="570">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -549,10 +549,10 @@
     <t>DURAIRAJ  R</t>
   </si>
   <si>
-    <t>PermFromDate</t>
-  </si>
-  <si>
-    <t>24-05-2024</t>
+    <t>PermFromDate1</t>
+  </si>
+  <si>
+    <t>07-12-2024</t>
   </si>
   <si>
     <t>PermissionTimeFrom</t>
@@ -1717,6 +1717,15 @@
   </si>
   <si>
     <t>TVS-AMD-DIS-</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>ExpiryDate</t>
+  </si>
+  <si>
+    <t>08-02-2027</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2556,7 +2565,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2618,9 +2627,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2942,7 +2948,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B327"/>
+  <dimension ref="A1:B329"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="34.287037037037" customWidth="1"/>
@@ -5534,35 +5540,51 @@
       </c>
     </row>
     <row r="324" spans="1:2">
-      <c r="A324" s="36" t="s">
+      <c r="A324" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="B324" s="37" t="s">
+      <c r="B324" s="7" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="325" spans="1:2">
-      <c r="A325" s="36" t="s">
+      <c r="A325" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B325" s="37" t="s">
+      <c r="B325" s="7" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="326" spans="1:2">
-      <c r="A326" s="36" t="s">
+      <c r="A326" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B326" s="37" t="s">
+      <c r="B326" s="7" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="327" spans="1:2">
-      <c r="A327" s="36" t="s">
+      <c r="A327" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B327" s="37" t="s">
+      <c r="B327" s="7" t="s">
         <v>562</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B328" s="7" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="36" t="s">
+        <v>564</v>
+      </c>
+      <c r="B329" s="7" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
@@ -5591,18 +5613,18 @@
     </row>
     <row r="2" ht="109" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="571">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1726,6 +1726,9 @@
   </si>
   <si>
     <t>08-02-2027</t>
+  </si>
+  <si>
+    <t>Draft</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2565,7 +2568,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2627,6 +2630,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2948,7 +2954,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B329"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="34.287037037037" customWidth="1"/>
@@ -5580,11 +5586,19 @@
       </c>
     </row>
     <row r="329" spans="1:2">
-      <c r="A329" s="36" t="s">
+      <c r="A329" s="2" t="s">
         <v>564</v>
       </c>
       <c r="B329" s="7" t="s">
         <v>565</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="36" t="s">
+        <v>566</v>
+      </c>
+      <c r="B330" s="37" t="s">
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -5613,18 +5627,18 @@
     </row>
     <row r="2" ht="109" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="611">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -486,7 +486,7 @@
     <t>LeaveElgblLeave</t>
   </si>
   <si>
-    <t>CL</t>
+    <t>PL</t>
   </si>
   <si>
     <t>LeaveElgblDays</t>
@@ -504,9 +504,6 @@
     <t>EmpLeaveElgblEligibileDays</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>EmpLeaveElgblRoundOff</t>
   </si>
   <si>
@@ -522,690 +519,687 @@
     <t>EmpLeaveElgblMaxCarryDay</t>
   </si>
   <si>
+    <t>EmpLeaveElgblEffYear</t>
+  </si>
+  <si>
+    <t>202324</t>
+  </si>
+  <si>
+    <t>EmpLeaveElgblMaxDay</t>
+  </si>
+  <si>
+    <t>EmpLeaveElgblMinDay</t>
+  </si>
+  <si>
+    <t>EmpLeaveElgblMinEncashDay</t>
+  </si>
+  <si>
+    <t>EmployeeDurai</t>
+  </si>
+  <si>
+    <t>DURAIRAJ  R</t>
+  </si>
+  <si>
+    <t>PermFromDate1</t>
+  </si>
+  <si>
+    <t>07-12-2024</t>
+  </si>
+  <si>
+    <t>PermissionTimeFrom</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>PermissionTimeTo</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>PermissionReference</t>
+  </si>
+  <si>
+    <t>Permission</t>
+  </si>
+  <si>
+    <t>PermissionType</t>
+  </si>
+  <si>
+    <t>On-Duty (Day)</t>
+  </si>
+  <si>
+    <t>OnDutyFindType</t>
+  </si>
+  <si>
+    <t>On - Duty(Day)</t>
+  </si>
+  <si>
+    <t>OnDutyFromDate</t>
+  </si>
+  <si>
+    <t>25-05-2024</t>
+  </si>
+  <si>
+    <t>PermissionFindType</t>
+  </si>
+  <si>
+    <t>PO_NUMBER</t>
+  </si>
+  <si>
+    <t>PO100/00010/24-25</t>
+  </si>
+  <si>
+    <t>ITEM_ID</t>
+  </si>
+  <si>
+    <t>LotNo</t>
+  </si>
+  <si>
+    <t>RM1001</t>
+  </si>
+  <si>
+    <t>serial</t>
+  </si>
+  <si>
+    <t>HK-FIFO-SER-BATCH-10001</t>
+  </si>
+  <si>
+    <t>Serial No</t>
+  </si>
+  <si>
+    <t>DomSupplier_ID</t>
+  </si>
+  <si>
+    <t>ARAVIND AGENCY</t>
+  </si>
+  <si>
+    <t>SimItem_ID</t>
+  </si>
+  <si>
+    <t>TVS-RM-KDK-18</t>
+  </si>
+  <si>
+    <t>Disc_Value</t>
+  </si>
+  <si>
+    <t>ImpSupplier_ID</t>
+  </si>
+  <si>
+    <t>AFT PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>DissimItem_ID</t>
+  </si>
+  <si>
+    <t>TVS-RM-KPK-12</t>
+  </si>
+  <si>
+    <t>Cost_Value</t>
+  </si>
+  <si>
+    <t>Gwl_Service_Item_03</t>
+  </si>
+  <si>
+    <t>GWL_ITem_service_03</t>
+  </si>
+  <si>
+    <t>EMPNAME</t>
+  </si>
+  <si>
+    <t>EMP01</t>
+  </si>
+  <si>
+    <t>CUSName</t>
+  </si>
+  <si>
+    <t>C014</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>TVS-FG-00059</t>
+  </si>
+  <si>
+    <t>CUSName_OSO</t>
+  </si>
+  <si>
+    <t>CU0060</t>
+  </si>
+  <si>
+    <t>ITEM_OSO</t>
+  </si>
+  <si>
+    <t>TVS-FG-100768</t>
+  </si>
+  <si>
+    <t>HodValue</t>
+  </si>
+  <si>
+    <t>ZeroValue</t>
+  </si>
+  <si>
+    <t>Sales_Invoice</t>
+  </si>
+  <si>
+    <t>Sales Invoice</t>
+  </si>
+  <si>
+    <t>SI_Type</t>
+  </si>
+  <si>
+    <t>SI - GENERAL</t>
+  </si>
+  <si>
+    <t>CustomerName</t>
+  </si>
+  <si>
+    <t>MURUGAN TRADERS</t>
+  </si>
+  <si>
+    <t>InvoicePrefix</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Item_ID</t>
+  </si>
+  <si>
+    <t>TVSFG004</t>
+  </si>
+  <si>
+    <t>CPC_Code</t>
+  </si>
+  <si>
+    <t>InvoiceQty</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>UnitPrice</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>SalesGL_Acct</t>
+  </si>
+  <si>
+    <t>4010101001</t>
+  </si>
+  <si>
+    <t>HSNcode_SI</t>
+  </si>
+  <si>
+    <t>88363222</t>
+  </si>
+  <si>
+    <t>SI_HOD</t>
+  </si>
+  <si>
+    <t>Export_Customer_Name</t>
+  </si>
+  <si>
+    <t>FRANCE FOREIGN TRADERS</t>
+  </si>
+  <si>
+    <t>LUT_No</t>
+  </si>
+  <si>
+    <t>2321311</t>
+  </si>
+  <si>
+    <t>Domestic_RC_Customer_Name</t>
+  </si>
+  <si>
+    <t>AJK ENTERPRISES</t>
+  </si>
+  <si>
+    <t>Domestic_RC_Item_ID</t>
+  </si>
+  <si>
+    <t>RC_DOMESTIC_001</t>
+  </si>
+  <si>
+    <t>Export_RC_Customer_Name</t>
+  </si>
+  <si>
+    <t>Export_RC_Item_ID</t>
+  </si>
+  <si>
+    <t>RC_Export_001</t>
+  </si>
+  <si>
+    <t>UD_Disimilar_Domestic_Item_ID</t>
+  </si>
+  <si>
+    <t>UD_Disimilar_Domestic_002</t>
+  </si>
+  <si>
+    <t>Domestic_RC_Item_ID_Disimilar</t>
+  </si>
+  <si>
+    <t>Export_RC_Item_ID_Disimilar</t>
+  </si>
+  <si>
+    <t>Domestic_PL_Item_ID</t>
+  </si>
+  <si>
+    <t>Export_PL_Item_ID</t>
+  </si>
+  <si>
+    <t>Domestic_PL_Item_ID_Disimilar</t>
+  </si>
+  <si>
+    <t>Export_PL_Item_ID_Disimilar</t>
+  </si>
+  <si>
+    <t>Domestic_SP_Item_ID</t>
+  </si>
+  <si>
+    <t>Export_SP_Item_ID</t>
+  </si>
+  <si>
+    <t>Domestic_SP_Item_ID_Disimalar</t>
+  </si>
+  <si>
+    <t>Export_SP_Item_ID_Disimalar</t>
+  </si>
+  <si>
+    <t>Domestic_CG_Item_ID</t>
+  </si>
+  <si>
+    <t>Export_CG_Item_ID</t>
+  </si>
+  <si>
+    <t>Domestic_CG_Item_ID_Disimalar</t>
+  </si>
+  <si>
+    <t>Export_CG_Item_ID_Disimalar</t>
+  </si>
+  <si>
+    <t>EmpAddInfo_HomeType</t>
+  </si>
+  <si>
+    <t>Rent</t>
+  </si>
+  <si>
+    <t>EmpAddInfo_StayType</t>
+  </si>
+  <si>
+    <t>Hosteller</t>
+  </si>
+  <si>
+    <t>EmpAddInfo_VehicleFlag</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>EmpDependentRelation</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>EmpDependentRelationDOB</t>
+  </si>
+  <si>
+    <t>20-05-1998</t>
+  </si>
+  <si>
+    <t>Emp_MaritalStatus</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>LotItem</t>
+  </si>
+  <si>
+    <t>HK-LOT-FIFO-LOT-10001</t>
+  </si>
+  <si>
+    <t>POSupplier</t>
+  </si>
+  <si>
+    <t>JJ AUTOMOBILES</t>
+  </si>
+  <si>
+    <t>NAItem</t>
+  </si>
+  <si>
+    <t>HK-NA-MAC-10001</t>
+  </si>
+  <si>
+    <t>IssuedStatus</t>
+  </si>
+  <si>
+    <t>Issued</t>
+  </si>
+  <si>
+    <t>Rtgs</t>
+  </si>
+  <si>
+    <t>RTGS</t>
+  </si>
+  <si>
+    <t>Axisbank</t>
+  </si>
+  <si>
+    <t>AXIS BANK</t>
+  </si>
+  <si>
+    <t>BankofBaroda</t>
+  </si>
+  <si>
+    <t>7151922222222265</t>
+  </si>
+  <si>
+    <t>OpenSOItem</t>
+  </si>
+  <si>
+    <t>GWL_OpenSO_Item</t>
+  </si>
+  <si>
+    <t>ERPPrivateLimitedID</t>
+  </si>
+  <si>
+    <t>CUS0000056</t>
+  </si>
+  <si>
+    <t>ERPPrivateLimitedName</t>
+  </si>
+  <si>
+    <t>ERP PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Prefix_OP100</t>
+  </si>
+  <si>
+    <t>OP100</t>
+  </si>
+  <si>
+    <t>Type_Standard</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>HSN2022-5%</t>
+  </si>
+  <si>
+    <t>(2022)5%</t>
+  </si>
+  <si>
+    <t>Sales_Order</t>
+  </si>
+  <si>
+    <t>Sales Order</t>
+  </si>
+  <si>
+    <t>SO_General</t>
+  </si>
+  <si>
+    <t>SO - GENERAL</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>CUS0015</t>
+  </si>
+  <si>
+    <t>SO_Similar_Item</t>
+  </si>
+  <si>
+    <t>HK-FIFO-LOT-BATCH-10001(FG)</t>
+  </si>
+  <si>
+    <t>SO_Qty</t>
+  </si>
+  <si>
+    <t>SO_UnitCost</t>
+  </si>
+  <si>
+    <t>2800</t>
+  </si>
+  <si>
+    <t>SO_HSNCode</t>
+  </si>
+  <si>
+    <t>772213</t>
+  </si>
+  <si>
+    <t>SO_HOD_Value</t>
+  </si>
+  <si>
+    <t>SO_PriceBasis</t>
+  </si>
+  <si>
+    <t>User Defined</t>
+  </si>
+  <si>
+    <t>SO_Export_Customer</t>
+  </si>
+  <si>
+    <t>SO_DisSimilarItem</t>
+  </si>
+  <si>
+    <t>HK-FG-DISSIMILAR-10001</t>
+  </si>
+  <si>
+    <t>SO_Similar_Item_Rate_Contract</t>
+  </si>
+  <si>
+    <t>HK-LOT-MAC-10001(FG)</t>
+  </si>
+  <si>
+    <t>SO_Similar_Item_PriceList</t>
+  </si>
+  <si>
+    <t>HK-LOT-FIFO-LOT-10001(FG)</t>
+  </si>
+  <si>
+    <t>SO_Similar_Item_Catalog</t>
+  </si>
+  <si>
+    <t>HK-FIFO-SER-BATCH-10001(FG)</t>
+  </si>
+  <si>
+    <t>SO_Similar_Item_StandardPrice</t>
+  </si>
+  <si>
+    <t>HK-SER-MAC-10001(FG)</t>
+  </si>
+  <si>
+    <t>SO_DisSimilar_Item_Rate_Contract</t>
+  </si>
+  <si>
+    <t>HK-FG-RC-DISSIMILAR ITEM-10001</t>
+  </si>
+  <si>
+    <t>FinishedGoodWH</t>
+  </si>
+  <si>
+    <t>FINISHED GOODS WH U100</t>
+  </si>
+  <si>
+    <t>SinglePaymentType</t>
+  </si>
+  <si>
+    <t>BankReceipt_BankType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank </t>
+  </si>
+  <si>
+    <t>NEFTText</t>
+  </si>
+  <si>
+    <t>NEFT</t>
+  </si>
+  <si>
+    <t>InvoicedStatus</t>
+  </si>
+  <si>
+    <t>Invoiced</t>
+  </si>
+  <si>
+    <t>GWL_Item_Lot</t>
+  </si>
+  <si>
+    <t>GWL_ITEM-Lot_01</t>
+  </si>
+  <si>
+    <t>TVS-RM-KDK-64</t>
+  </si>
+  <si>
+    <t>TVS-RM-KPK-25</t>
+  </si>
+  <si>
+    <t>Efffrom_Date</t>
+  </si>
+  <si>
+    <t>12-02-2025</t>
+  </si>
+  <si>
+    <t>Effto_Date</t>
+  </si>
+  <si>
+    <t>15-02-2025</t>
+  </si>
+  <si>
+    <t>Close_Date</t>
+  </si>
+  <si>
+    <t>13-02-2025</t>
+  </si>
+  <si>
+    <t>Amdcost_Value</t>
+  </si>
+  <si>
+    <t>AmdDisc_Value</t>
+  </si>
+  <si>
+    <t>Rfqitem_ID</t>
+  </si>
+  <si>
+    <t>TVS-RM-KDK-01</t>
+  </si>
+  <si>
+    <t>Cost_Value1</t>
+  </si>
+  <si>
+    <t>Cost_Value2</t>
+  </si>
+  <si>
+    <t>DomSupplier_ID1</t>
+  </si>
+  <si>
+    <t>ACTIVE GARMENTS</t>
+  </si>
+  <si>
+    <t>Hsn_code</t>
+  </si>
+  <si>
+    <t>Trd_Discount</t>
+  </si>
+  <si>
+    <t>Spcl_Discount</t>
+  </si>
+  <si>
+    <t>Cash_Discount</t>
+  </si>
+  <si>
+    <t>AmdSimItem_ID</t>
+  </si>
+  <si>
+    <t>TVS-AMD-SIM-02</t>
+  </si>
+  <si>
+    <t>AmdDissimItem_ID</t>
+  </si>
+  <si>
+    <t>TVS-AMD-DIS-02</t>
+  </si>
+  <si>
+    <t>CnclSimItem_ID</t>
+  </si>
+  <si>
+    <t>TVS-AMD-CANCL-02</t>
+  </si>
+  <si>
+    <t>Perc_1</t>
+  </si>
+  <si>
+    <t>Perc_2</t>
+  </si>
+  <si>
+    <t>Amnd_Reason</t>
+  </si>
+  <si>
+    <t>L0001</t>
+  </si>
+  <si>
+    <t>OpenPOSupplier</t>
+  </si>
+  <si>
+    <t>ARUN PACKS (P) LTD</t>
+  </si>
+  <si>
+    <t>LotSerialDate</t>
+  </si>
+  <si>
+    <t>20.10.2027</t>
+  </si>
+  <si>
+    <t>Lot</t>
+  </si>
+  <si>
+    <t>LOT</t>
+  </si>
+  <si>
+    <t>Na</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Serial</t>
+  </si>
+  <si>
+    <t>SERIAL</t>
+  </si>
+  <si>
+    <t>RateContractServiceItem</t>
+  </si>
+  <si>
+    <t>PK-SERV-MAC-NA-01</t>
+  </si>
+  <si>
+    <t>SO_DisSimilar_Item_Catalog</t>
+  </si>
+  <si>
+    <t>HK-FG-CATALOG-DISSIMILAR-10001</t>
+  </si>
+  <si>
+    <t>SO_DisSimilar_Item_StandardPrice</t>
+  </si>
+  <si>
+    <t>HK-FG-STD-PRICE-DISSIMILAR ITEM-10001</t>
+  </si>
+  <si>
+    <t>SO_Trade_Disc</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>EmpLeaveElgblEffYear</t>
-  </si>
-  <si>
-    <t>202324</t>
-  </si>
-  <si>
-    <t>EmpLeaveElgblMaxDay</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>EmpLeaveElgblMinDay</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>EmployeeDurai</t>
-  </si>
-  <si>
-    <t>DURAIRAJ  R</t>
-  </si>
-  <si>
-    <t>PermFromDate1</t>
-  </si>
-  <si>
-    <t>07-12-2024</t>
-  </si>
-  <si>
-    <t>PermissionTimeFrom</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>PermissionTimeTo</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>PermissionReference</t>
-  </si>
-  <si>
-    <t>Permission</t>
-  </si>
-  <si>
-    <t>PermissionType</t>
-  </si>
-  <si>
-    <t>On-Duty (Day)</t>
-  </si>
-  <si>
-    <t>OnDutyFindType</t>
-  </si>
-  <si>
-    <t>On - Duty(Day)</t>
-  </si>
-  <si>
-    <t>OnDutyFromDate</t>
-  </si>
-  <si>
-    <t>25-05-2024</t>
-  </si>
-  <si>
-    <t>PermissionFindType</t>
-  </si>
-  <si>
-    <t>PO_NUMBER</t>
-  </si>
-  <si>
-    <t>PO100/00010/24-25</t>
-  </si>
-  <si>
-    <t>ITEM_ID</t>
-  </si>
-  <si>
-    <t>LotNo</t>
-  </si>
-  <si>
-    <t>RM1001</t>
-  </si>
-  <si>
-    <t>serial</t>
-  </si>
-  <si>
-    <t>HK-FIFO-SER-BATCH-10001</t>
-  </si>
-  <si>
-    <t>Serial No</t>
-  </si>
-  <si>
-    <t>DomSupplier_ID</t>
-  </si>
-  <si>
-    <t>ARAVIND AGENCY</t>
-  </si>
-  <si>
-    <t>SimItem_ID</t>
-  </si>
-  <si>
-    <t>TVS-RM-KDK-18</t>
-  </si>
-  <si>
-    <t>Disc_Value</t>
-  </si>
-  <si>
-    <t>ImpSupplier_ID</t>
-  </si>
-  <si>
-    <t>AFT PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>DissimItem_ID</t>
-  </si>
-  <si>
-    <t>TVS-RM-KPK-12</t>
-  </si>
-  <si>
-    <t>Cost_Value</t>
-  </si>
-  <si>
-    <t>Gwl_Service_Item_03</t>
-  </si>
-  <si>
-    <t>GWL_ITem_service_03</t>
-  </si>
-  <si>
-    <t>EMPNAME</t>
-  </si>
-  <si>
-    <t>EMP01</t>
-  </si>
-  <si>
-    <t>CUSName</t>
-  </si>
-  <si>
-    <t>C014</t>
-  </si>
-  <si>
-    <t>ITEM</t>
-  </si>
-  <si>
-    <t>TVS-FG-00059</t>
-  </si>
-  <si>
-    <t>CUSName_OSO</t>
-  </si>
-  <si>
-    <t>CU0060</t>
-  </si>
-  <si>
-    <t>ITEM_OSO</t>
-  </si>
-  <si>
-    <t>TVS-FG-100768</t>
-  </si>
-  <si>
-    <t>HodValue</t>
-  </si>
-  <si>
-    <t>ZeroValue</t>
-  </si>
-  <si>
-    <t>Sales_Invoice</t>
-  </si>
-  <si>
-    <t>Sales Invoice</t>
-  </si>
-  <si>
-    <t>SI_Type</t>
-  </si>
-  <si>
-    <t>SI - GENERAL</t>
-  </si>
-  <si>
-    <t>CustomerName</t>
-  </si>
-  <si>
-    <t>MURUGAN TRADERS</t>
-  </si>
-  <si>
-    <t>InvoicePrefix</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Item_ID</t>
-  </si>
-  <si>
-    <t>TVSFG004</t>
-  </si>
-  <si>
-    <t>CPC_Code</t>
-  </si>
-  <si>
-    <t>InvoiceQty</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>UnitPrice</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>SalesGL_Acct</t>
-  </si>
-  <si>
-    <t>4010101001</t>
-  </si>
-  <si>
-    <t>HSNcode_SI</t>
-  </si>
-  <si>
-    <t>88363222</t>
-  </si>
-  <si>
-    <t>SI_HOD</t>
-  </si>
-  <si>
-    <t>Export_Customer_Name</t>
-  </si>
-  <si>
-    <t>FRANCE FOREIGN TRADERS</t>
-  </si>
-  <si>
-    <t>LUT_No</t>
-  </si>
-  <si>
-    <t>2321311</t>
-  </si>
-  <si>
-    <t>Domestic_RC_Customer_Name</t>
-  </si>
-  <si>
-    <t>AJK ENTERPRISES</t>
-  </si>
-  <si>
-    <t>Domestic_RC_Item_ID</t>
-  </si>
-  <si>
-    <t>RC_DOMESTIC_001</t>
-  </si>
-  <si>
-    <t>Export_RC_Customer_Name</t>
-  </si>
-  <si>
-    <t>Export_RC_Item_ID</t>
-  </si>
-  <si>
-    <t>RC_Export_001</t>
-  </si>
-  <si>
-    <t>UD_Disimilar_Domestic_Item_ID</t>
-  </si>
-  <si>
-    <t>UD_Disimilar_Domestic_002</t>
-  </si>
-  <si>
-    <t>Domestic_RC_Item_ID_Disimilar</t>
-  </si>
-  <si>
-    <t>Export_RC_Item_ID_Disimilar</t>
-  </si>
-  <si>
-    <t>Domestic_PL_Item_ID</t>
-  </si>
-  <si>
-    <t>Export_PL_Item_ID</t>
-  </si>
-  <si>
-    <t>Domestic_PL_Item_ID_Disimilar</t>
-  </si>
-  <si>
-    <t>Export_PL_Item_ID_Disimilar</t>
-  </si>
-  <si>
-    <t>Domestic_SP_Item_ID</t>
-  </si>
-  <si>
-    <t>Export_SP_Item_ID</t>
-  </si>
-  <si>
-    <t>Domestic_SP_Item_ID_Disimalar</t>
-  </si>
-  <si>
-    <t>Export_SP_Item_ID_Disimalar</t>
-  </si>
-  <si>
-    <t>Domestic_CG_Item_ID</t>
-  </si>
-  <si>
-    <t>Export_CG_Item_ID</t>
-  </si>
-  <si>
-    <t>Domestic_CG_Item_ID_Disimalar</t>
-  </si>
-  <si>
-    <t>Export_CG_Item_ID_Disimalar</t>
-  </si>
-  <si>
-    <t>EmpAddInfo_HomeType</t>
-  </si>
-  <si>
-    <t>Rent</t>
-  </si>
-  <si>
-    <t>EmpAddInfo_StayType</t>
-  </si>
-  <si>
-    <t>Hosteller</t>
-  </si>
-  <si>
-    <t>EmpAddInfo_VehicleFlag</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>EmpDependentRelation</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>EmpDependentRelationDOB</t>
-  </si>
-  <si>
-    <t>20-05-1998</t>
-  </si>
-  <si>
-    <t>Emp_MaritalStatus</t>
-  </si>
-  <si>
-    <t>Single</t>
-  </si>
-  <si>
-    <t>LotItem</t>
-  </si>
-  <si>
-    <t>HK-LOT-FIFO-LOT-10001</t>
-  </si>
-  <si>
-    <t>POSupplier</t>
-  </si>
-  <si>
-    <t>JJ AUTOMOBILES</t>
-  </si>
-  <si>
-    <t>NAItem</t>
-  </si>
-  <si>
-    <t>HK-NA-MAC-10001</t>
-  </si>
-  <si>
-    <t>IssuedStatus</t>
-  </si>
-  <si>
-    <t>Issued</t>
-  </si>
-  <si>
-    <t>Rtgs</t>
-  </si>
-  <si>
-    <t>RTGS</t>
-  </si>
-  <si>
-    <t>Axisbank</t>
-  </si>
-  <si>
-    <t>AXIS BANK</t>
-  </si>
-  <si>
-    <t>BankofBaroda</t>
-  </si>
-  <si>
-    <t>7151922222222265</t>
-  </si>
-  <si>
-    <t>OpenSOItem</t>
-  </si>
-  <si>
-    <t>GWL_OpenSO_Item</t>
-  </si>
-  <si>
-    <t>ERPPrivateLimitedID</t>
-  </si>
-  <si>
-    <t>CUS0000056</t>
-  </si>
-  <si>
-    <t>ERPPrivateLimitedName</t>
-  </si>
-  <si>
-    <t>ERP PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Prefix_OP100</t>
-  </si>
-  <si>
-    <t>OP100</t>
-  </si>
-  <si>
-    <t>Type_Standard</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>HSN2022-5%</t>
-  </si>
-  <si>
-    <t>(2022)5%</t>
-  </si>
-  <si>
-    <t>Sales_Order</t>
-  </si>
-  <si>
-    <t>Sales Order</t>
-  </si>
-  <si>
-    <t>SO_General</t>
-  </si>
-  <si>
-    <t>SO - GENERAL</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>CUS0015</t>
-  </si>
-  <si>
-    <t>SO_Similar_Item</t>
-  </si>
-  <si>
-    <t>HK-FIFO-LOT-BATCH-10001(FG)</t>
-  </si>
-  <si>
-    <t>SO_Qty</t>
-  </si>
-  <si>
-    <t>SO_UnitCost</t>
-  </si>
-  <si>
-    <t>2800</t>
-  </si>
-  <si>
-    <t>SO_HSNCode</t>
-  </si>
-  <si>
-    <t>772213</t>
-  </si>
-  <si>
-    <t>SO_HOD_Value</t>
-  </si>
-  <si>
-    <t>SO_PriceBasis</t>
-  </si>
-  <si>
-    <t>User Defined</t>
-  </si>
-  <si>
-    <t>SO_Export_Customer</t>
-  </si>
-  <si>
-    <t>SO_DisSimilarItem</t>
-  </si>
-  <si>
-    <t>HK-FG-DISSIMILAR-10001</t>
-  </si>
-  <si>
-    <t>SO_Similar_Item_Rate_Contract</t>
-  </si>
-  <si>
-    <t>HK-LOT-MAC-10001(FG)</t>
-  </si>
-  <si>
-    <t>SO_Similar_Item_PriceList</t>
-  </si>
-  <si>
-    <t>HK-LOT-FIFO-LOT-10001(FG)</t>
-  </si>
-  <si>
-    <t>SO_Similar_Item_Catalog</t>
-  </si>
-  <si>
-    <t>HK-FIFO-SER-BATCH-10001(FG)</t>
-  </si>
-  <si>
-    <t>SO_Similar_Item_StandardPrice</t>
-  </si>
-  <si>
-    <t>HK-SER-MAC-10001(FG)</t>
-  </si>
-  <si>
-    <t>SO_DisSimilar_Item_Rate_Contract</t>
-  </si>
-  <si>
-    <t>HK-FG-RC-DISSIMILAR ITEM-10001</t>
-  </si>
-  <si>
-    <t>FinishedGoodWH</t>
-  </si>
-  <si>
-    <t>FINISHED GOODS WH U100</t>
-  </si>
-  <si>
-    <t>SinglePaymentType</t>
-  </si>
-  <si>
-    <t>BankReceipt_BankType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank </t>
-  </si>
-  <si>
-    <t>NEFTText</t>
-  </si>
-  <si>
-    <t>NEFT</t>
-  </si>
-  <si>
-    <t>InvoicedStatus</t>
-  </si>
-  <si>
-    <t>Invoiced</t>
-  </si>
-  <si>
-    <t>GWL_Item_Lot</t>
-  </si>
-  <si>
-    <t>GWL_ITEM-Lot_01</t>
-  </si>
-  <si>
-    <t>TVS-RM-KDK-64</t>
-  </si>
-  <si>
-    <t>TVS-RM-KPK-25</t>
-  </si>
-  <si>
-    <t>Efffrom_Date</t>
-  </si>
-  <si>
-    <t>12-02-2025</t>
-  </si>
-  <si>
-    <t>Effto_Date</t>
-  </si>
-  <si>
-    <t>15-02-2025</t>
-  </si>
-  <si>
-    <t>Close_Date</t>
-  </si>
-  <si>
-    <t>13-02-2025</t>
-  </si>
-  <si>
-    <t>Amdcost_Value</t>
-  </si>
-  <si>
-    <t>AmdDisc_Value</t>
-  </si>
-  <si>
-    <t>Rfqitem_ID</t>
-  </si>
-  <si>
-    <t>TVS-RM-KDK-01</t>
-  </si>
-  <si>
-    <t>Cost_Value1</t>
-  </si>
-  <si>
-    <t>Cost_Value2</t>
-  </si>
-  <si>
-    <t>DomSupplier_ID1</t>
-  </si>
-  <si>
-    <t>ACTIVE GARMENTS</t>
-  </si>
-  <si>
-    <t>Hsn_code</t>
-  </si>
-  <si>
-    <t>Trd_Discount</t>
-  </si>
-  <si>
-    <t>Spcl_Discount</t>
-  </si>
-  <si>
-    <t>Cash_Discount</t>
-  </si>
-  <si>
-    <t>AmdSimItem_ID</t>
-  </si>
-  <si>
-    <t>TVS-AMD-SIM-02</t>
-  </si>
-  <si>
-    <t>AmdDissimItem_ID</t>
-  </si>
-  <si>
-    <t>TVS-AMD-DIS-02</t>
-  </si>
-  <si>
-    <t>CnclSimItem_ID</t>
-  </si>
-  <si>
-    <t>TVS-AMD-CANCL-02</t>
-  </si>
-  <si>
-    <t>Perc_1</t>
-  </si>
-  <si>
-    <t>Perc_2</t>
-  </si>
-  <si>
-    <t>Amnd_Reason</t>
-  </si>
-  <si>
-    <t>L0001</t>
-  </si>
-  <si>
-    <t>OpenPOSupplier</t>
-  </si>
-  <si>
-    <t>ARUN PACKS (P) LTD</t>
-  </si>
-  <si>
-    <t>LotSerialDate</t>
-  </si>
-  <si>
-    <t>20.10.2027</t>
-  </si>
-  <si>
-    <t>Lot</t>
-  </si>
-  <si>
-    <t>LOT</t>
-  </si>
-  <si>
-    <t>Na</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Serial</t>
-  </si>
-  <si>
-    <t>SERIAL</t>
-  </si>
-  <si>
-    <t>RateContractServiceItem</t>
-  </si>
-  <si>
-    <t>PK-SERV-MAC-NA-01</t>
-  </si>
-  <si>
-    <t>SO_DisSimilar_Item_Catalog</t>
-  </si>
-  <si>
-    <t>HK-FG-CATALOG-DISSIMILAR-10001</t>
-  </si>
-  <si>
-    <t>SO_DisSimilar_Item_StandardPrice</t>
-  </si>
-  <si>
-    <t>HK-FG-STD-PRICE-DISSIMILAR ITEM-10001</t>
-  </si>
-  <si>
-    <t>SO_Trade_Disc</t>
-  </si>
-  <si>
     <t>SO_Special_Disc</t>
   </si>
   <si>
@@ -1729,6 +1723,132 @@
   </si>
   <si>
     <t>Draft</t>
+  </si>
+  <si>
+    <t>CompletedStatus</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>WIPU100_WH</t>
+  </si>
+  <si>
+    <t>WORK IN PROGRESS WH U100</t>
+  </si>
+  <si>
+    <t>RMU100_WH</t>
+  </si>
+  <si>
+    <t>RAW MATERIAL WH U100</t>
+  </si>
+  <si>
+    <t>Shift_100</t>
+  </si>
+  <si>
+    <t>SHIFT 100</t>
+  </si>
+  <si>
+    <t>MouldingProcess</t>
+  </si>
+  <si>
+    <t>MOULDING</t>
+  </si>
+  <si>
+    <t>Cus_Local</t>
+  </si>
+  <si>
+    <t>Cus_Interstate</t>
+  </si>
+  <si>
+    <t>Cus_Export</t>
+  </si>
+  <si>
+    <t>oso_Docnum_PC_UTGST</t>
+  </si>
+  <si>
+    <t>OSO7-2425-00010</t>
+  </si>
+  <si>
+    <t>oso_Docnum_PCC_UTGST</t>
+  </si>
+  <si>
+    <t>oso_Docnum_ADD_UTGST</t>
+  </si>
+  <si>
+    <t>FS_Invoice_Pfx</t>
+  </si>
+  <si>
+    <t>SIFS1</t>
+  </si>
+  <si>
+    <t>SI_FS_Type</t>
+  </si>
+  <si>
+    <t>SI - FREE SAMPLE</t>
+  </si>
+  <si>
+    <t>SI_FS_Local_Customer</t>
+  </si>
+  <si>
+    <t>INKSPLASH PRINTING</t>
+  </si>
+  <si>
+    <t>FR_Invoice_Pfx</t>
+  </si>
+  <si>
+    <t>SIFR1</t>
+  </si>
+  <si>
+    <t>SI_FR_Type</t>
+  </si>
+  <si>
+    <t>SI - FREE REPLACEMENT</t>
+  </si>
+  <si>
+    <t>SI_FR_Local_Customer</t>
+  </si>
+  <si>
+    <t>MALAR TRADERS</t>
+  </si>
+  <si>
+    <t>SCR_Invoice_Pfx</t>
+  </si>
+  <si>
+    <t>SISCR</t>
+  </si>
+  <si>
+    <t>SI_Scrarp_Type</t>
+  </si>
+  <si>
+    <t>SI - SCRAP</t>
+  </si>
+  <si>
+    <t>SI_Scarp_Local_Customer</t>
+  </si>
+  <si>
+    <t>URBAN ENTERPRISES</t>
+  </si>
+  <si>
+    <t>SI_Scrarp_Item</t>
+  </si>
+  <si>
+    <t>HK-TVS-SCRAP-10001</t>
+  </si>
+  <si>
+    <t>SI_Ship_From_WH</t>
+  </si>
+  <si>
+    <t>SCRAP WAREHOUSE</t>
+  </si>
+  <si>
+    <t>SI_Cancel_Reason</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>Exp_Cancel_Status</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2568,7 +2688,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2596,6 +2716,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFill="1" applyBorder="1"/>
@@ -2954,11 +3075,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B330"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B355"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="34.287037037037" customWidth="1"/>
-    <col min="2" max="2" width="59.8518518518519" style="4" customWidth="1"/>
+    <col min="1" max="1" width="34.2909090909091" customWidth="1"/>
+    <col min="2" max="2" width="59.8545454545455" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3622,1276 +3743,1276 @@
         <v>157</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B84" s="11" t="s">
         <v>159</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B85" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="12" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="12" t="s">
-        <v>171</v>
+      <c r="A90" s="13" t="s">
+        <v>167</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="12" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="12" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="12" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="B98" s="12" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="13" t="s">
+      <c r="B101" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B102" s="14" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="13" t="s">
+    <row r="103" spans="1:2">
+      <c r="A103" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="B100" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="13" t="s">
+      <c r="B103" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B101" s="13" t="s">
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="14" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="13" t="s">
+      <c r="B104" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B105" s="16" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="13" t="s">
+    <row r="106" spans="1:2">
+      <c r="A106" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="B103" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="15" t="s">
+      <c r="B106" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="B104" s="15" t="s">
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="16" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="15" t="s">
+      <c r="B107" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="B105" s="16" t="s">
+      <c r="B108" s="16" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="15" t="s">
+    <row r="109" spans="1:2">
+      <c r="A109" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="B106" s="17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="15" t="s">
+      <c r="B109" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="B107" s="15" t="s">
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="16" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="15" t="s">
+      <c r="B110" s="18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B108" s="18" t="s">
+      <c r="B111" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="15" t="s">
+    <row r="112" spans="1:2">
+      <c r="A112" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="B109" s="17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="2" t="s">
+      <c r="B112" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="B110" s="2" t="s">
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="20" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="19" t="s">
+      <c r="B113" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="B111" s="19" t="s">
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="20" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="19" t="s">
+      <c r="B114" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B112" s="19" t="s">
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="20" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="19" t="s">
+      <c r="B115" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B113" s="2" t="s">
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="20" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="19" t="s">
+      <c r="B116" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B118" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B119" s="22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="B117" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="20" t="s">
+      <c r="B120" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="B118" s="21" t="s">
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="21" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="20" t="s">
+      <c r="B121" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="B119" s="21" t="s">
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="21" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="20" t="s">
+      <c r="B122" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="B120" s="21" t="s">
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="21" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="20" t="s">
+      <c r="B123" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="B121" s="21" t="s">
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="21" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="20" t="s">
+      <c r="B124" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="B122" s="21" t="s">
+      <c r="B125" s="22" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="20" t="s">
+    <row r="126" spans="1:2">
+      <c r="A126" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="B123" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="20" t="s">
+      <c r="B126" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="B124" s="21" t="s">
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="21" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="20" t="s">
+      <c r="B127" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="B125" s="21" t="s">
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="21" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="20" t="s">
+      <c r="B128" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="B126" s="21" t="s">
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="21" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="20" t="s">
+      <c r="B129" s="22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="B127" s="21" t="s">
+      <c r="B130" s="22" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="20" t="s">
+    <row r="131" spans="1:2">
+      <c r="A131" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="B128" s="21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="20" t="s">
+      <c r="B131" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="B129" s="21" t="s">
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="21" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="20" t="s">
+      <c r="B132" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="B130" s="21" t="s">
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="21" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="20" t="s">
+      <c r="B133" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="B131" s="21" t="s">
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="21" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="20" t="s">
+      <c r="B134" s="22" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="B132" s="21" t="s">
+      <c r="B135" s="22" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="20" t="s">
+    <row r="136" spans="1:2">
+      <c r="A136" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="B133" s="21" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="20" t="s">
+      <c r="B136" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="B134" s="21" t="s">
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="21" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="20" t="s">
+      <c r="B137" s="22" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="B135" s="21" t="s">
+      <c r="B138" s="22" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="21" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="20" t="s">
+      <c r="B139" s="22" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="B136" s="21" t="s">
+      <c r="B140" s="22" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="20" t="s">
+    <row r="141" spans="1:2">
+      <c r="A141" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="B137" s="21" t="s">
+      <c r="B141" s="22" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="20" t="s">
+    <row r="142" spans="1:2">
+      <c r="A142" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="B138" s="21" t="s">
+      <c r="B142" s="22" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="20" t="s">
+    <row r="143" spans="1:2">
+      <c r="A143" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B139" s="21" t="s">
+      <c r="B143" s="22" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="20" t="s">
+    <row r="144" spans="1:2">
+      <c r="A144" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="B140" s="21" t="s">
+      <c r="B144" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="20" t="s">
+    <row r="145" spans="1:2">
+      <c r="A145" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="B141" s="21" t="s">
+      <c r="B145" s="22" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="20" t="s">
+    <row r="146" spans="1:2">
+      <c r="A146" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="B142" s="21" t="s">
+      <c r="B146" s="22" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="20" t="s">
+    <row r="147" spans="1:2">
+      <c r="A147" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="B143" s="21" t="s">
+      <c r="B147" s="22" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="20" t="s">
+    <row r="148" spans="1:2">
+      <c r="A148" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="B144" s="21" t="s">
+      <c r="B148" s="22" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="20" t="s">
+    <row r="149" spans="1:2">
+      <c r="A149" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="B145" s="21" t="s">
+      <c r="B149" s="22" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="20" t="s">
+    <row r="150" spans="1:2">
+      <c r="A150" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="B146" s="21" t="s">
+      <c r="B150" s="22" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="20" t="s">
+    <row r="151" spans="1:2">
+      <c r="A151" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="B147" s="21" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="20" t="s">
+      <c r="B151" s="22" t="s">
         <v>265</v>
       </c>
-      <c r="B148" s="21" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="20" t="s">
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="B149" s="21" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="22" t="s">
+      <c r="B152" s="22" t="s">
         <v>267</v>
       </c>
-      <c r="B150" s="21" t="s">
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="23" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="22" t="s">
+      <c r="B153" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="B151" s="21" t="s">
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="23" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="22" t="s">
+      <c r="B154" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="B152" s="21" t="s">
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="23" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="22" t="s">
+      <c r="B155" s="22" t="s">
         <v>273</v>
-      </c>
-      <c r="B153" s="21" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="B154" s="21" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="B155" s="21" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="B156" s="22" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="B157" s="25" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="B156" s="24" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="B158" s="25" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="11" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B159" s="26" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="B160" s="11" t="s">
-        <v>288</v>
+        <v>282</v>
+      </c>
+      <c r="B160" s="27" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="B161" s="26" t="s">
-        <v>290</v>
+        <v>284</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B162" s="26" t="s">
-        <v>292</v>
+        <v>286</v>
+      </c>
+      <c r="B162" s="27" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="B163" s="11" t="s">
-        <v>294</v>
+        <v>288</v>
+      </c>
+      <c r="B163" s="27" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="11" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="B165" s="26" t="s">
-        <v>298</v>
+        <v>292</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="B166" s="26" t="s">
-        <v>300</v>
+        <v>294</v>
+      </c>
+      <c r="B166" s="27" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="B167" s="11" t="s">
-        <v>302</v>
+        <v>296</v>
+      </c>
+      <c r="B167" s="27" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="11" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="B169" s="26" t="s">
-        <v>306</v>
+        <v>300</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="B170" s="26" t="s">
-        <v>308</v>
+        <v>302</v>
+      </c>
+      <c r="B170" s="27" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="B171" s="26" t="s">
-        <v>310</v>
+        <v>304</v>
+      </c>
+      <c r="B171" s="27" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="B172" s="26" t="s">
-        <v>312</v>
+        <v>306</v>
+      </c>
+      <c r="B172" s="27" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B173" s="26" t="s">
-        <v>227</v>
+        <v>308</v>
+      </c>
+      <c r="B173" s="27" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="B174" s="26" t="s">
-        <v>315</v>
+        <v>310</v>
+      </c>
+      <c r="B174" s="27" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="B175" s="26" t="s">
-        <v>317</v>
+        <v>311</v>
+      </c>
+      <c r="B175" s="27" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="B176" s="26" t="s">
-        <v>17</v>
+        <v>313</v>
+      </c>
+      <c r="B176" s="27" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="B177" s="26" t="s">
-        <v>320</v>
+        <v>315</v>
+      </c>
+      <c r="B177" s="27" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="B178" s="26" t="s">
-        <v>215</v>
+        <v>316</v>
+      </c>
+      <c r="B178" s="27" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="B179" s="26" t="s">
-        <v>323</v>
+        <v>318</v>
+      </c>
+      <c r="B179" s="27" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="B180" s="26" t="s">
-        <v>325</v>
+        <v>319</v>
+      </c>
+      <c r="B180" s="27" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="B181" s="26" t="s">
-        <v>327</v>
+        <v>321</v>
+      </c>
+      <c r="B181" s="27" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="B182" s="26" t="s">
-        <v>329</v>
+        <v>323</v>
+      </c>
+      <c r="B182" s="27" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B183" s="26" t="s">
-        <v>331</v>
+        <v>325</v>
+      </c>
+      <c r="B183" s="27" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="B184" s="26" t="s">
-        <v>333</v>
+        <v>327</v>
+      </c>
+      <c r="B184" s="27" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="B185" s="11" t="s">
-        <v>335</v>
+        <v>329</v>
+      </c>
+      <c r="B185" s="27" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="11" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>278</v>
+        <v>332</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="B187" s="26" t="s">
-        <v>338</v>
+        <v>333</v>
+      </c>
+      <c r="B187" s="11" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="B188" s="11" t="s">
-        <v>340</v>
+        <v>334</v>
+      </c>
+      <c r="B188" s="27" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="B189" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="B190" s="27" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B191" s="28" t="s">
         <v>341</v>
       </c>
-      <c r="B189" s="26" t="s">
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="B192" s="29" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="B193" s="30" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="2" t="s">
+    <row r="194" spans="1:2">
+      <c r="A194" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="B194" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B195" s="29" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="B196" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="B190" s="27" t="s">
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="B197" s="15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B198" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="29" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="B191" s="28" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B192" s="29" t="s">
+      <c r="B199" s="31" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="28" t="s">
+    <row r="200" spans="1:2">
+      <c r="A200" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="B200" s="31" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="B201" s="31" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="B202" s="15">
         <v>200</v>
       </c>
-      <c r="B193" s="14">
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="B203" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="B204" s="15" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="B205" s="15">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="B206" s="15">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="B207" s="15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="B208" s="15">
+        <v>123562</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="B209" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
-      <c r="A194" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="B194" s="28" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2">
-      <c r="A195" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="B195" s="13" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2">
-      <c r="A196" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="B196" s="14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2">
-      <c r="A197" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="B197" s="14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2">
-      <c r="A198" s="28" t="s">
-        <v>347</v>
-      </c>
-      <c r="B198" s="30" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2">
-      <c r="A199" s="28" t="s">
-        <v>349</v>
-      </c>
-      <c r="B199" s="30" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2">
-      <c r="A200" s="28" t="s">
-        <v>351</v>
-      </c>
-      <c r="B200" s="30" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2">
-      <c r="A201" s="28" t="s">
-        <v>353</v>
-      </c>
-      <c r="B201" s="14">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2">
-      <c r="A202" s="28" t="s">
-        <v>354</v>
-      </c>
-      <c r="B202" s="14">
+    <row r="210" spans="1:2">
+      <c r="A210" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="B210" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
-      <c r="A203" s="28" t="s">
-        <v>355</v>
-      </c>
-      <c r="B203" s="14" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2">
-      <c r="A204" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="B204" s="14">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2">
-      <c r="A205" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="B205" s="14">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2">
-      <c r="A206" s="14" t="s">
-        <v>359</v>
-      </c>
-      <c r="B206" s="14" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2">
-      <c r="A207" s="14" t="s">
+    <row r="211" spans="1:2">
+      <c r="A211" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="B207" s="14">
-        <v>123562</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2">
-      <c r="A208" s="14" t="s">
+      <c r="B211" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="15" t="s">
         <v>362</v>
       </c>
-      <c r="B208" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2">
-      <c r="A209" s="14" t="s">
+      <c r="B212" s="30" t="s">
         <v>363</v>
       </c>
-      <c r="B209" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2">
-      <c r="A210" s="14" t="s">
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="B210" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2">
-      <c r="A211" s="14" t="s">
+      <c r="B213" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="B211" s="29" t="s">
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="212" spans="1:2">
-      <c r="A212" s="14" t="s">
+      <c r="B214" s="30" t="s">
         <v>367</v>
       </c>
-      <c r="B212" s="13" t="s">
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="15" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="213" spans="1:2">
-      <c r="A213" s="14" t="s">
+      <c r="B215" s="15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="B213" s="29" t="s">
+      <c r="B216" s="15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="15" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="214" spans="1:2">
-      <c r="A214" s="14" t="s">
+      <c r="B217" s="30" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="24" t="s">
         <v>371</v>
       </c>
-      <c r="B214" s="14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2">
-      <c r="A215" s="14" t="s">
+      <c r="B219" s="24" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="24" t="s">
         <v>372</v>
       </c>
-      <c r="B215" s="14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
-      <c r="A216" s="14" t="s">
+      <c r="B220" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B216" s="29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2">
-      <c r="A217" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2">
-      <c r="A218" s="23" t="s">
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="24" t="s">
         <v>374</v>
       </c>
-      <c r="B218" s="23" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2">
-      <c r="A219" s="23" t="s">
+      <c r="B221" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B219" s="2" t="s">
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="32" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="220" spans="1:2">
-      <c r="A220" s="23" t="s">
+      <c r="B222" s="24" t="s">
         <v>377</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2">
-      <c r="A221" s="31" t="s">
-        <v>379</v>
-      </c>
-      <c r="B221" s="23" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2">
-      <c r="A222" s="31" t="s">
-        <v>381</v>
-      </c>
-      <c r="B222" s="23" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="B223" s="24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="B224" s="33" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="B225" s="32" t="s">
         <v>383</v>
-      </c>
-      <c r="B223" s="32" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2">
-      <c r="A224" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="B224" s="31" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2">
-      <c r="A225" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B225" s="7" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B228" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>154</v>
+        <v>391</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" s="2" t="s">
-        <v>210</v>
+        <v>392</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>395</v>
+        <v>154</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>213</v>
+        <v>393</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B232" s="7" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B233" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>17</v>
+        <v>214</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" s="2" t="s">
-        <v>396</v>
+        <v>215</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>397</v>
+        <v>17</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B238" s="7" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B239" s="7" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B242" s="7" t="s">
         <v>407</v>
@@ -4899,706 +5020,906 @@
     </row>
     <row r="243" spans="1:2">
       <c r="A243" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B243" s="7" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B245" s="7" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>238</v>
+        <v>414</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B247" s="7" t="s">
-        <v>419</v>
+        <v>235</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B248" s="33" t="s">
-        <v>421</v>
+        <v>416</v>
+      </c>
+      <c r="B248" s="7" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B249" s="7" t="s">
-        <v>65</v>
+        <v>418</v>
+      </c>
+      <c r="B249" s="34" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B250" s="7" t="s">
-        <v>424</v>
+        <v>65</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B251" s="7" t="s">
-        <v>225</v>
+        <v>422</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>7</v>
+        <v>222</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>428</v>
+        <v>7</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B254" s="7" t="s">
-        <v>229</v>
+        <v>426</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B255" s="7" t="s">
-        <v>431</v>
+        <v>226</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B256" s="7" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>436</v>
+        <v>391</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B259" s="7" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B260" s="7" t="s">
-        <v>333</v>
+        <v>436</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>441</v>
+        <v>330</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B262" s="7" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B263" s="7" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B264" s="7" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B265" s="7" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B266" s="7" t="s">
-        <v>333</v>
+        <v>447</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B267" s="7" t="s">
-        <v>452</v>
+        <v>330</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B268" s="7" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B270" s="7" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B271" s="7" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B272" s="7" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B273" s="7" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B274" s="7" t="s">
-        <v>335</v>
+        <v>462</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B275" s="7" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B276" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B277" s="7" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="20" t="s">
         <v>467</v>
       </c>
-      <c r="B276" s="7" t="s">
+      <c r="B278" s="2" t="s">
         <v>468</v>
-      </c>
-    </row>
-    <row r="277" spans="1:2">
-      <c r="A277" s="19" t="s">
-        <v>469</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2">
-      <c r="A278" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="B279" s="7" t="s">
-        <v>472</v>
+        <v>58</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="280" spans="1:2">
-      <c r="A280" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="B280" s="9" t="s">
-        <v>474</v>
+      <c r="A280" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B280" s="7" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" s="8" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B281" s="9" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" s="8" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B282" s="9" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="B283" s="9" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="B284" s="35" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="36" t="s">
         <v>479</v>
       </c>
-      <c r="B283" s="34" t="s">
+      <c r="B285" s="7" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="284" spans="1:2">
-      <c r="A284" s="35" t="s">
+    <row r="286" spans="1:2">
+      <c r="A286" s="36" t="s">
         <v>481</v>
       </c>
-      <c r="B284" s="7" t="s">
+      <c r="B286" s="7" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="285" spans="1:2">
-      <c r="A285" s="35" t="s">
+    <row r="287" spans="1:2">
+      <c r="A287" s="36" t="s">
         <v>483</v>
       </c>
-      <c r="B285" s="7" t="s">
+      <c r="B287" s="7" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="286" spans="1:2">
-      <c r="A286" s="35" t="s">
+    <row r="288" spans="1:2">
+      <c r="A288" s="36" t="s">
         <v>485</v>
       </c>
-      <c r="B286" s="7" t="s">
+      <c r="B288" s="7" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="287" spans="1:2">
-      <c r="A287" s="35" t="s">
+    <row r="289" spans="1:2">
+      <c r="A289" s="36" t="s">
         <v>487</v>
       </c>
-      <c r="B287" s="7" t="s">
+      <c r="B289" s="7" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="288" spans="1:2">
-      <c r="A288" s="35" t="s">
+    <row r="290" spans="1:2">
+      <c r="A290" s="36" t="s">
         <v>489</v>
       </c>
-      <c r="B288" s="7" t="s">
+      <c r="B290" s="7" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
-      <c r="A289" s="35" t="s">
+    <row r="291" spans="1:2">
+      <c r="A291" s="36" t="s">
         <v>491</v>
       </c>
-      <c r="B289" s="7" t="s">
+      <c r="B291" s="7" t="s">
         <v>492</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2">
-      <c r="A290" s="35" t="s">
-        <v>493</v>
-      </c>
-      <c r="B290" s="7" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2">
-      <c r="A291" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="B291" s="7" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B292" s="7" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B293" s="7" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B294" s="7" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B295" s="7" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B296" s="7" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B298" s="7" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B299" s="7" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B300" s="7" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B302" s="7" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B304" s="7" t="s">
-        <v>421</v>
+        <v>518</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B305" s="7" t="s">
-        <v>523</v>
+        <v>419</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B306" s="7" t="s">
-        <v>421</v>
+        <v>521</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>526</v>
+        <v>419</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B308" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B309" s="7" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B310" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B311" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B312" s="7" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B313" s="7" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B314" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B315" s="7" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B316" s="7" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B317" s="7" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="B318" s="8" t="s">
-        <v>545</v>
+        <v>540</v>
+      </c>
+      <c r="B318" s="7" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="B319" s="7" t="s">
-        <v>547</v>
+        <v>542</v>
+      </c>
+      <c r="B319" s="8" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B320" s="7" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B322" s="7" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B323" s="7" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B324" s="7" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B325" s="7" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B326" s="7" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" s="2" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B327" s="7" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B328" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B329" s="7" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B330" s="7" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="B329" s="7" t="s">
+      <c r="B331" s="7" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="330" spans="1:2">
-      <c r="A330" s="36" t="s">
+      <c r="B332" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="B330" s="37" t="s">
-        <v>566</v>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B333" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B334" s="7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B335" s="7" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="23" t="s">
+        <v>573</v>
+      </c>
+      <c r="B336" s="22" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="23" t="s">
+        <v>575</v>
+      </c>
+      <c r="B337" s="22" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="B338" s="22" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="23" t="s">
+        <v>577</v>
+      </c>
+      <c r="B339" s="22" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="23" t="s">
+        <v>578</v>
+      </c>
+      <c r="B340" s="22" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="23" t="s">
+        <v>580</v>
+      </c>
+      <c r="B341" s="22" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="23" t="s">
+        <v>581</v>
+      </c>
+      <c r="B342" s="22" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="37" t="s">
+        <v>582</v>
+      </c>
+      <c r="B343" s="38" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="37" t="s">
+        <v>584</v>
+      </c>
+      <c r="B344" s="38" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="37" t="s">
+        <v>586</v>
+      </c>
+      <c r="B345" s="38" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="37" t="s">
+        <v>588</v>
+      </c>
+      <c r="B346" s="38" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="37" t="s">
+        <v>590</v>
+      </c>
+      <c r="B347" s="38" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="37" t="s">
+        <v>592</v>
+      </c>
+      <c r="B348" s="38" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="37" t="s">
+        <v>594</v>
+      </c>
+      <c r="B349" s="38" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="37" t="s">
+        <v>596</v>
+      </c>
+      <c r="B350" s="38" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="37" t="s">
+        <v>598</v>
+      </c>
+      <c r="B351" s="38" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="37" t="s">
+        <v>600</v>
+      </c>
+      <c r="B352" s="38" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="37" t="s">
+        <v>602</v>
+      </c>
+      <c r="B353" s="38" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="37" t="s">
+        <v>604</v>
+      </c>
+      <c r="B354" s="38" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="37" t="s">
+        <v>606</v>
+      </c>
+      <c r="B355" s="38" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -5611,9 +5932,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="19.8909090909091" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5627,18 +5948,18 @@
     </row>
     <row r="2" ht="109" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>567</v>
+        <v>607</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>568</v>
+        <v>608</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>569</v>
+        <v>609</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>570</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
     <sheet name="DBData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
+  <oleSize ref="A1:E17"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="715">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1998,18 +1999,462 @@
        AND prl_prod_id = prod_id
        AND prl_prod_rev = prod_rev</t>
   </si>
+  <si>
+    <t>EDP MANAGER</t>
+  </si>
+  <si>
+    <t>SO_DisSimilar_Item_PriceList</t>
+  </si>
+  <si>
+    <t>HK-FG-PRICELIST-DISSIMILAR UOM-10001</t>
+  </si>
+  <si>
+    <t>ItemDelete</t>
+  </si>
+  <si>
+    <t>SK0001</t>
+  </si>
+  <si>
+    <t>SOHeaderQuery</t>
+  </si>
+  <si>
+    <t>SELECT soh_cust_id "Customer ID",
+       soh_cust_name "Customer Description",
+       soh_currency "Currency",
+       soh_exchange_rate "Exchange Rate",
+       soh_term_id "Payment Term",
+       soh_fob_id "INCO Term",
+       soh_shipvia_id "Ship VIA",
+       (  SELECT DECODE (applctrl_desc_level, 1, sv_desc1, sv_desc2)Shipvis_Description
+    FROM ship_vias, appl_control
+   WHERE sv_bu = soh_bu AND applctrl_bu = soh_bu AND sv_shipvia_id  = soh_shipvia_id)"Ship VIA Desc.",
+   ( SELECT TERM_EXT_DESC Term_Description
+    FROM terms_hd
+   WHERE term_bu = soh_bu
+     AND term_term_id =soh_term_id )"Payment Term Desc1.",
+     ( SELECT TERM_DESC1 Term_Description1
+    FROM terms_hd
+   WHERE term_bu = soh_bu
+     AND term_term_id =soh_term_id )"Payment Term Desc2.",
+     ( SELECT DECODE (applctrl_desc_level, 1, fob_desc1, fob_desc2) Fob_Description
+    FROM fobs, appl_control
+   WHERE fob_bu = soh_bu AND applctrl_bu = soh_bu AND fob_fob_id =soh_fob_id )"INCO Term Desc.",
+       soh_cc_id "CPC Code",
+       (SELECT pcc_desc
+          FROM profit_cost_centers
+         WHERE pcc_bu = soh_bu AND pcc_cc_code = soh_cc_id)
+          "CPC Code Desc",
+       NVL (suplr_prnt_capn, soh_cust_name) "Customer Print Name",
+       soh_sales_person "Sales Person",
+       soh_sub_terr_id "Sub Territory",
+       soh_terr_id "Sales Zone",
+       soh_sales_area "Sales Region",
+       soh_te_mgr_id "Sales Zone Manager",
+       suplr_group_id "Customer Group",
+       suplr_subgroup "Customer Sub Group",
+       soh_plnt_loc_id "Location ID",
+       soh_plant "Unit ID",
+       soh_order_type "Sub Voucher Type",
+       soh_order_pfx "SO prefix",
+       soh_order_no "SO Number",
+         (SELECT DISTINCT apst_sub_type_desc
+             FROM appl_vou_sub_types
+            WHERE     apst_bu = soh_bu
+                  AND apst_vou_type = soh_vou_type
+                  AND apst_sub_type = soh_order_type)"Sub Voucher Desc",
+                    (SELECT sa_area_desc1
+             FROM sales_areas
+            WHERE sa_bu = soh_bu AND sa_area = soh_sales_area)"Area",
+                (SELECT sat_terr_desc1
+             FROM sales_area_terr
+            WHERE sat_bu = soh_bu AND sat_terr_id = soh_terr_id) "Territory",
+                     (SELECT sst_desc1
+             FROM sales_sub_terr
+            WHERE sst_bu = soh_bu AND sst_sub_terr_id = soh_sub_terr_id) "Sub Territory",
+              (SELECT sp_person_name1
+             FROM sales_persons
+            WHERE sp_bu = soh_bu AND sp_person = soh_sales_person) "Sales Person",
+              (SELECT DISTINCT supgrp_desc1
+             FROM supplier_groups, suppliers
+            WHERE     supgrp_bu = soh_bu
+                  AND supgrp_group_id = suplr_group_id
+                  AND supgrp_bu = suplr_bu
+                  AND suplr_bu = soh_bu
+                  AND suplr_suplr_id = soh_cust_id) "Group",
+                   (SELECT DISTINCT supsubgroup_desc1
+             FROM supplier_subgroup, suppliers
+            WHERE     supsubgroup_bu = soh_bu
+                  AND supsubgroup_type_id = suplr_subgroup
+                  AND supsubgroup_bu = suplr_bu
+                  AND suplr_bu = soh_bu
+                  AND suplr_suplr_id = soh_cust_id) "SubGroup",
+                  func_find_employee_desc(soh_bu ,SOH_TE_MGR_ID,1) "Sales Zone Mgr"   
+  FROM sales_order_hd, suppliers
+ WHERE     soh_bu = suplr_bu
+       AND soh_cust_id = suplr_suplr_id
+       AND suplr_status = 'A'
+       AND soh_bu = 'TVSA'
+       AND soh_order_no ='${SONO}'</t>
+  </si>
+  <si>
+    <t>SOLineQuery</t>
+  </si>
+  <si>
+    <t>SELECT soq_prod_id "Item ID",soq_prod_rev "Item Rev",
+       soq_prod_desc1 "Item Desc",
+       soq_uom "Sale UOM",
+       soq_hsn_code "HSN Code",
+       soq_tax_pct "Tax Percentage",
+       soq_price_basis "Price Basis Type",
+       DECODE (soq_price_basis,
+               'C', 'Open Order',
+               'L', 'Catalog Price',
+               'P', 'Price List',
+               'S', 'Standard Price',
+               'U', 'User Defined')
+          "Price Basis Desc",
+       soq_cont_cat_no "Contract Number",
+       soq_catalog_no "Catalog / Price List Number",
+       soq_prod_uom "Stock UOM",
+       soq_conv_factor "Conversion Factor",
+       soq_tolr_type "Tolerance Type",
+       soq_cust_prod_id "Customer Item ID",
+       soq_cust_prod_desc "Customer Item Desc",
+       (SELECT store_desc1
+          FROM stores
+         WHERE store_bu = soq_bu AND store_id = soq_store_id
+        UNION ALL
+        SELECT dept_name1
+          FROM departments
+         WHERE dept_bu = soq_bu AND dept_id = soq_store_id)
+          "Warehouse Description",
+       soq_prod_subcls_desc "SubClass Desc",
+       soq_prod_cls_desc "Class Desc",
+       (SELECT spc_class_desc
+          FROM sales_price_classes
+         WHERE spc_bu = soq_bu AND spc_class_id = soq_sales_price_class)
+          "Price Class",
+       soq_promotion_flag "Promotional",
+       soq_trd_assbl_val "Trade Ass. Val.",
+       soq_disc_pct "Trade Disc. %",
+       soq_disc_amt "Trade Disc. Amt.",
+       soq_spl_assbl_val "Spl. Ass. Val.",
+       soq_spl_disc_pct "Spl. Disc. %",
+       soq_spl_disc_amt "Spl. Disc. Amt.",
+       soq_cash_assbl_val "Cash Ass. Val.",
+       soq_cash_disc_pct "Cash Disc. %",
+       soq_cash_disc_amt "Cash Disc. Amt.",
+       soq_gross_amt "Gross Amt.",
+       soq_disc_amt_per_qty "Disc. Amt. / Qty.",
+       soq_tax_amt "Tax Amt.",
+       soq_net_amt "Net Amt.",
+       soq_gross_amt "Gross Amt.",
+       soq_disc_amt_per_qty "Disc. Amt. / Qty.",
+       soq_tax_amt "Tax Amt.",
+       soq_net_amt "Net Amt.",
+       soq_qty_ordered "Ord. Qty.",
+       soq_price "Unit Price",
+       soq_tot_disc_amt "Disc. Amt.",
+       soq_igst_amt "IGST Amt.",
+       soq_sgst_amt "SGST Amt.",
+       soq_cgst_amt "CGST Amt."
+  FROM sales_order_hd, sales_order_qtys
+ WHERE     soh_bu = soq_bu
+       AND soh_order_no = soq_order_no
+       AND soh_bu = 'TVSA'
+       AND soh_order_no = '${SONO}'</t>
+  </si>
+  <si>
+    <t>ChargesBasis</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>ChargeItem</t>
+  </si>
+  <si>
+    <t>TVS-CH-00002</t>
+  </si>
+  <si>
+    <t>ChargesPercentage</t>
+  </si>
+  <si>
+    <t>ChargesValue</t>
+  </si>
+  <si>
+    <t>AdvancePercentage</t>
+  </si>
+  <si>
+    <t>AdavanceAmount</t>
+  </si>
+  <si>
+    <t>SONumber</t>
+  </si>
+  <si>
+    <t>SO100/00831/24-25</t>
+  </si>
+  <si>
+    <t>AdvancePaymentTerm</t>
+  </si>
+  <si>
+    <t>25%ADVANCE AND 75%INVOICE</t>
+  </si>
+  <si>
+    <t>BankName</t>
+  </si>
+  <si>
+    <t>STATE BANK OF INDIA - 30305325953</t>
+  </si>
+  <si>
+    <t>AdvDocNumber</t>
+  </si>
+  <si>
+    <t>Reference Number</t>
+  </si>
+  <si>
+    <t>6374-0001</t>
+  </si>
+  <si>
+    <t>BRVDocumentStatus</t>
+  </si>
+  <si>
+    <t>Received</t>
+  </si>
+  <si>
+    <t>SONO</t>
+  </si>
+  <si>
+    <t>${SONO}</t>
+  </si>
+  <si>
+    <t>SoDBLocationColumnName</t>
+  </si>
+  <si>
+    <t>Location ID</t>
+  </si>
+  <si>
+    <t>SoDBUnitColumnName</t>
+  </si>
+  <si>
+    <t>Unit ID</t>
+  </si>
+  <si>
+    <t>SoDBCustomerIDColumnName</t>
+  </si>
+  <si>
+    <t>Customer ID</t>
+  </si>
+  <si>
+    <t>SoDBCustomerDescColumnName</t>
+  </si>
+  <si>
+    <t>Customer Description</t>
+  </si>
+  <si>
+    <t>SoDBCusrrencyColumnName</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>CustomerDesc</t>
+  </si>
+  <si>
+    <t>SOSubVoucherTypeDBColumnName</t>
+  </si>
+  <si>
+    <t>Sub Voucher Desc</t>
+  </si>
+  <si>
+    <t>SODBPrefixColumnName</t>
+  </si>
+  <si>
+    <t>SO prefix</t>
+  </si>
+  <si>
+    <t>SODBDocNumberColumnName</t>
+  </si>
+  <si>
+    <t>SO Number</t>
+  </si>
+  <si>
+    <t>SODBCurrencyColumnName</t>
+  </si>
+  <si>
+    <t>SODBExchangeRateColumnName</t>
+  </si>
+  <si>
+    <t>Exchange Rate</t>
+  </si>
+  <si>
+    <t>SODBCpcCodeIDColumnName</t>
+  </si>
+  <si>
+    <t>CPC Code</t>
+  </si>
+  <si>
+    <t>SODBCpcCodeDescColumnName</t>
+  </si>
+  <si>
+    <t>CPC Code Desc</t>
+  </si>
+  <si>
+    <t>SODBItemIDColumnName</t>
+  </si>
+  <si>
+    <t>Item ID</t>
+  </si>
+  <si>
+    <t>SODBItemRevColumnName</t>
+  </si>
+  <si>
+    <t>Item Rev</t>
+  </si>
+  <si>
+    <t>SODBItemDescColumnName</t>
+  </si>
+  <si>
+    <t>Item Desc</t>
+  </si>
+  <si>
+    <t>SODBSaleUOMColumnName</t>
+  </si>
+  <si>
+    <t>Sale UOM</t>
+  </si>
+  <si>
+    <t>SODBHSNCodeColumnName</t>
+  </si>
+  <si>
+    <t>HSN Code</t>
+  </si>
+  <si>
+    <t>SODBTradeAssesableValueColumnName</t>
+  </si>
+  <si>
+    <t>Trade Ass. Val.</t>
+  </si>
+  <si>
+    <t>SODBTradeDiscountPercentageColumnName</t>
+  </si>
+  <si>
+    <t>Trade Disc. %</t>
+  </si>
+  <si>
+    <t>SODBTradeDiscountAmountColumnName</t>
+  </si>
+  <si>
+    <t>Trade Disc. Amt.</t>
+  </si>
+  <si>
+    <t>SODBSpecialAssesableValueColumnName</t>
+  </si>
+  <si>
+    <t>Spl. Ass. Val.</t>
+  </si>
+  <si>
+    <t>SODBSpecialDiscountPercentageColumnName</t>
+  </si>
+  <si>
+    <t>Spl. Disc. %</t>
+  </si>
+  <si>
+    <t>SODBSpecialDiscountAmountColumnName</t>
+  </si>
+  <si>
+    <t>Spl. Disc. Amt.</t>
+  </si>
+  <si>
+    <t>SODBCashAssesableValueColumnName</t>
+  </si>
+  <si>
+    <t>Cash Ass. Val.</t>
+  </si>
+  <si>
+    <t>SODBCashDiscountPercentageColumnName</t>
+  </si>
+  <si>
+    <t>Cash Disc. %</t>
+  </si>
+  <si>
+    <t>SODBCashDiscountAmountColumnName</t>
+  </si>
+  <si>
+    <t>Cash Disc. Amt.</t>
+  </si>
+  <si>
+    <t>SODBDiscountAmountPerQtyColumnName</t>
+  </si>
+  <si>
+    <t>Disc. Amt. / Qty.</t>
+  </si>
+  <si>
+    <t>SODBGrossAmountColumnName</t>
+  </si>
+  <si>
+    <t>Gross Amt.</t>
+  </si>
+  <si>
+    <t>SODBTotalDiscountAmountColumnName</t>
+  </si>
+  <si>
+    <t>Disc. Amt.</t>
+  </si>
+  <si>
+    <t>SODBTaxAmountColumnName</t>
+  </si>
+  <si>
+    <t>Tax Amt.</t>
+  </si>
+  <si>
+    <t>SODBPriceBasisColumnName</t>
+  </si>
+  <si>
+    <t>Price Basis Desc</t>
+  </si>
+  <si>
+    <t>SODBContractNumberFieldColumnName</t>
+  </si>
+  <si>
+    <t>Contract Number</t>
+  </si>
+  <si>
+    <t>SODBCatalog_PriceListNumberFieldColumnName</t>
+  </si>
+  <si>
+    <t>Catalog / Price List Number</t>
+  </si>
+  <si>
+    <t>SODBNetAmountColumnName</t>
+  </si>
+  <si>
+    <t>Net Amt.</t>
+  </si>
+  <si>
+    <t>SODBPaymentTermColumnName</t>
+  </si>
+  <si>
+    <t>Payment Term Desc2.</t>
+  </si>
+  <si>
+    <t>SODBINCOTermColumnName</t>
+  </si>
+  <si>
+    <t>INCO Term Desc.</t>
+  </si>
+  <si>
+    <t>SODBShipViaColumnName</t>
+  </si>
+  <si>
+    <t>Ship VIA Desc.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2060,151 +2505,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2223,188 +2531,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2440,255 +2568,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2717,12 +2603,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2740,9 +2626,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -2754,60 +2640,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal 2" xfId="49"/>
-    <cellStyle name="Normal 3" xfId="50"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="2"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3069,17 +2909,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B355"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B408"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.2909090909091" customWidth="1"/>
-    <col min="2" max="2" width="59.8545454545455" style="4" customWidth="1"/>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="59.85546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4014,8 +3854,8 @@
       <c r="A117" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>17</v>
+      <c r="B117" s="37" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -4111,7 +3951,7 @@
         <v>236</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>17</v>
+        <v>611</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4495,7 +4335,7 @@
         <v>315</v>
       </c>
       <c r="B177" s="27" t="s">
-        <v>17</v>
+        <v>611</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -5922,19 +5762,441 @@
         <v>59</v>
       </c>
     </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="37" t="s">
+        <v>612</v>
+      </c>
+      <c r="B356" s="37" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="37" t="s">
+        <v>614</v>
+      </c>
+      <c r="B357" s="38" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="B358" s="20" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="20" t="s">
+        <v>622</v>
+      </c>
+      <c r="B359" s="20" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="B360" s="37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="B361" s="37">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="20" t="s">
+        <v>626</v>
+      </c>
+      <c r="B362" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="20" t="s">
+        <v>627</v>
+      </c>
+      <c r="B363" s="37">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="B364" s="37" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="B365" s="37" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="20" t="s">
+        <v>632</v>
+      </c>
+      <c r="B366" s="37" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="20" t="s">
+        <v>634</v>
+      </c>
+      <c r="B367" s="37">
+        <v>10000039</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="20" t="s">
+        <v>635</v>
+      </c>
+      <c r="B368" s="20" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="20" t="s">
+        <v>637</v>
+      </c>
+      <c r="B369" s="20" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="B370" s="38" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="B371" s="38" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="B372" s="38" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="20" t="s">
+        <v>645</v>
+      </c>
+      <c r="B373" s="38" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="B374" s="38" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="B375" s="38" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="B376" s="38" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="B377" s="38" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="B378" s="38" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="20" t="s">
+        <v>656</v>
+      </c>
+      <c r="B379" s="38" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="20" t="s">
+        <v>658</v>
+      </c>
+      <c r="B380" s="38" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="20" t="s">
+        <v>659</v>
+      </c>
+      <c r="B381" s="38" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="20" t="s">
+        <v>661</v>
+      </c>
+      <c r="B382" s="38" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="B383" s="38" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="20" t="s">
+        <v>665</v>
+      </c>
+      <c r="B384" s="38" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="20" t="s">
+        <v>667</v>
+      </c>
+      <c r="B385" s="38" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="B386" s="38" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="B387" s="38" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="20" t="s">
+        <v>673</v>
+      </c>
+      <c r="B388" s="38" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="B389" s="38" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="20" t="s">
+        <v>677</v>
+      </c>
+      <c r="B390" s="38" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="20" t="s">
+        <v>679</v>
+      </c>
+      <c r="B391" s="38" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="B392" s="38" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="20" t="s">
+        <v>683</v>
+      </c>
+      <c r="B393" s="38" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="20" t="s">
+        <v>685</v>
+      </c>
+      <c r="B394" s="38" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="20" t="s">
+        <v>687</v>
+      </c>
+      <c r="B395" s="38" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="20" t="s">
+        <v>689</v>
+      </c>
+      <c r="B396" s="38" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="20" t="s">
+        <v>691</v>
+      </c>
+      <c r="B397" s="38" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="20" t="s">
+        <v>693</v>
+      </c>
+      <c r="B398" s="38" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="20" t="s">
+        <v>695</v>
+      </c>
+      <c r="B399" s="38" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="B400" s="38" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="B401" s="38" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="20" t="s">
+        <v>701</v>
+      </c>
+      <c r="B402" s="38" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="20" t="s">
+        <v>703</v>
+      </c>
+      <c r="B403" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="20" t="s">
+        <v>705</v>
+      </c>
+      <c r="B404" s="38" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="20" t="s">
+        <v>707</v>
+      </c>
+      <c r="B405" s="38" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="20" t="s">
+        <v>709</v>
+      </c>
+      <c r="B406" s="38" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="20" t="s">
+        <v>711</v>
+      </c>
+      <c r="B407" s="38" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="20" t="s">
+        <v>713</v>
+      </c>
+      <c r="B408" s="38" t="s">
+        <v>714</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.8909090909091" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5946,7 +6208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="109" customHeight="1" spans="1:2">
+    <row r="2" spans="1:2" ht="108.95" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>607</v>
       </c>
@@ -5954,7 +6216,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="3" ht="114" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="114" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>609</v>
       </c>
@@ -5962,13 +6224,21 @@
         <v>610</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+    <row r="4" spans="1:2" ht="80.25" customHeight="1">
+      <c r="A4" s="37" t="s">
+        <v>616</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="69.75" customHeight="1">
+      <c r="A5" s="37" t="s">
+        <v>618</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>619</v>
+      </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2"/>
@@ -6024,6 +6294,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -1,17 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
     <sheet name="DBData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <oleSize ref="A1:E17"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="742">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -82,7 +81,7 @@
     <t>PR_Requester</t>
   </si>
   <si>
-    <t>HEAD OF DEPARTMENTS</t>
+    <t>EDP MANAGER</t>
   </si>
   <si>
     <t>PRDataDir</t>
@@ -1850,6 +1849,387 @@
   </si>
   <si>
     <t>Exp_Cancel_Status</t>
+  </si>
+  <si>
+    <t>SO_DisSimilar_Item_PriceList</t>
+  </si>
+  <si>
+    <t>HK-FG-PRICELIST-DISSIMILAR UOM-10001</t>
+  </si>
+  <si>
+    <t>ItemDelete</t>
+  </si>
+  <si>
+    <t>SK0001</t>
+  </si>
+  <si>
+    <t>ChargesBasis</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>ChargeItem</t>
+  </si>
+  <si>
+    <t>TVS-CH-00002</t>
+  </si>
+  <si>
+    <t>ChargesPercentage</t>
+  </si>
+  <si>
+    <t>ChargesValue</t>
+  </si>
+  <si>
+    <t>AdvancePercentage</t>
+  </si>
+  <si>
+    <t>AdavanceAmount</t>
+  </si>
+  <si>
+    <t>SONumber</t>
+  </si>
+  <si>
+    <t>SO100/00831/24-25</t>
+  </si>
+  <si>
+    <t>AdvancePaymentTerm</t>
+  </si>
+  <si>
+    <t>25%ADVANCE AND 75%INVOICE</t>
+  </si>
+  <si>
+    <t>BankName</t>
+  </si>
+  <si>
+    <t>STATE BANK OF INDIA - 30305325953</t>
+  </si>
+  <si>
+    <t>AdvDocNumber</t>
+  </si>
+  <si>
+    <t>Reference Number</t>
+  </si>
+  <si>
+    <t>6374-0001</t>
+  </si>
+  <si>
+    <t>BRVDocumentStatus</t>
+  </si>
+  <si>
+    <t>Received</t>
+  </si>
+  <si>
+    <t>SONO</t>
+  </si>
+  <si>
+    <t>${SONO}</t>
+  </si>
+  <si>
+    <t>SoDBLocationColumnName</t>
+  </si>
+  <si>
+    <t>Location ID</t>
+  </si>
+  <si>
+    <t>SoDBUnitColumnName</t>
+  </si>
+  <si>
+    <t>Unit ID</t>
+  </si>
+  <si>
+    <t>SoDBCustomerIDColumnName</t>
+  </si>
+  <si>
+    <t>Customer ID</t>
+  </si>
+  <si>
+    <t>SoDBCustomerDescColumnName</t>
+  </si>
+  <si>
+    <t>Customer Description</t>
+  </si>
+  <si>
+    <t>SoDBCusrrencyColumnName</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>CustomerDesc</t>
+  </si>
+  <si>
+    <t>SOSubVoucherTypeDBColumnName</t>
+  </si>
+  <si>
+    <t>Sub Voucher Desc</t>
+  </si>
+  <si>
+    <t>SODBPrefixColumnName</t>
+  </si>
+  <si>
+    <t>SO prefix</t>
+  </si>
+  <si>
+    <t>SODBDocNumberColumnName</t>
+  </si>
+  <si>
+    <t>SO Number</t>
+  </si>
+  <si>
+    <t>SODBCurrencyColumnName</t>
+  </si>
+  <si>
+    <t>SODBExchangeRateColumnName</t>
+  </si>
+  <si>
+    <t>Exchange Rate</t>
+  </si>
+  <si>
+    <t>SODBCpcCodeIDColumnName</t>
+  </si>
+  <si>
+    <t>CPC Code</t>
+  </si>
+  <si>
+    <t>SODBCpcCodeDescColumnName</t>
+  </si>
+  <si>
+    <t>CPC Code Desc</t>
+  </si>
+  <si>
+    <t>SODBItemIDColumnName</t>
+  </si>
+  <si>
+    <t>Item ID</t>
+  </si>
+  <si>
+    <t>SODBItemRevColumnName</t>
+  </si>
+  <si>
+    <t>Item Rev</t>
+  </si>
+  <si>
+    <t>SODBItemDescColumnName</t>
+  </si>
+  <si>
+    <t>Item Desc</t>
+  </si>
+  <si>
+    <t>SODBSaleUOMColumnName</t>
+  </si>
+  <si>
+    <t>Sale UOM</t>
+  </si>
+  <si>
+    <t>SODBHSNCodeColumnName</t>
+  </si>
+  <si>
+    <t>HSN Code</t>
+  </si>
+  <si>
+    <t>SODBTradeAssesableValueColumnName</t>
+  </si>
+  <si>
+    <t>Trade Ass. Val.</t>
+  </si>
+  <si>
+    <t>SODBTradeDiscountPercentageColumnName</t>
+  </si>
+  <si>
+    <t>Trade Disc. %</t>
+  </si>
+  <si>
+    <t>SODBTradeDiscountAmountColumnName</t>
+  </si>
+  <si>
+    <t>Trade Disc. Amt.</t>
+  </si>
+  <si>
+    <t>SODBSpecialAssesableValueColumnName</t>
+  </si>
+  <si>
+    <t>Spl. Ass. Val.</t>
+  </si>
+  <si>
+    <t>SODBSpecialDiscountPercentageColumnName</t>
+  </si>
+  <si>
+    <t>Spl. Disc. %</t>
+  </si>
+  <si>
+    <t>SODBSpecialDiscountAmountColumnName</t>
+  </si>
+  <si>
+    <t>Spl. Disc. Amt.</t>
+  </si>
+  <si>
+    <t>SODBCashAssesableValueColumnName</t>
+  </si>
+  <si>
+    <t>Cash Ass. Val.</t>
+  </si>
+  <si>
+    <t>SODBCashDiscountPercentageColumnName</t>
+  </si>
+  <si>
+    <t>Cash Disc. %</t>
+  </si>
+  <si>
+    <t>SODBCashDiscountAmountColumnName</t>
+  </si>
+  <si>
+    <t>Cash Disc. Amt.</t>
+  </si>
+  <si>
+    <t>SODBDiscountAmountPerQtyColumnName</t>
+  </si>
+  <si>
+    <t>Disc. Amt. / Qty.</t>
+  </si>
+  <si>
+    <t>SODBGrossAmountColumnName</t>
+  </si>
+  <si>
+    <t>Gross Amt.</t>
+  </si>
+  <si>
+    <t>SODBTotalDiscountAmountColumnName</t>
+  </si>
+  <si>
+    <t>Disc. Amt.</t>
+  </si>
+  <si>
+    <t>SODBTaxAmountColumnName</t>
+  </si>
+  <si>
+    <t>Tax Amt.</t>
+  </si>
+  <si>
+    <t>SODBPriceBasisColumnName</t>
+  </si>
+  <si>
+    <t>Price Basis Desc</t>
+  </si>
+  <si>
+    <t>SODBContractNumberFieldColumnName</t>
+  </si>
+  <si>
+    <t>Contract Number</t>
+  </si>
+  <si>
+    <t>SODBCatalog_PriceListNumberFieldColumnName</t>
+  </si>
+  <si>
+    <t>Catalog / Price List Number</t>
+  </si>
+  <si>
+    <t>SODBNetAmountColumnName</t>
+  </si>
+  <si>
+    <t>Net Amt.</t>
+  </si>
+  <si>
+    <t>SODBPaymentTermColumnName</t>
+  </si>
+  <si>
+    <t>Payment Term Desc2.</t>
+  </si>
+  <si>
+    <t>SODBINCOTermColumnName</t>
+  </si>
+  <si>
+    <t>INCO Term Desc.</t>
+  </si>
+  <si>
+    <t>SODBShipViaColumnName</t>
+  </si>
+  <si>
+    <t>Ship VIA Desc.</t>
+  </si>
+  <si>
+    <t>FGWareHouse</t>
+  </si>
+  <si>
+    <t>FG W/H</t>
+  </si>
+  <si>
+    <t>MinusTwo</t>
+  </si>
+  <si>
+    <t>-2</t>
+  </si>
+  <si>
+    <t>Two</t>
+  </si>
+  <si>
+    <t>Inter Transfer</t>
+  </si>
+  <si>
+    <t>EmpWareHouse</t>
+  </si>
+  <si>
+    <t>AURANGABAD DEPOT</t>
+  </si>
+  <si>
+    <t>EmpWareHouseId</t>
+  </si>
+  <si>
+    <t>WH0011</t>
+  </si>
+  <si>
+    <t>Prod100</t>
+  </si>
+  <si>
+    <t>PRODUCTION  100</t>
+  </si>
+  <si>
+    <t>DepartmentValue</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>IssCodeValue</t>
+  </si>
+  <si>
+    <t>Production100</t>
+  </si>
+  <si>
+    <t>PRODUCTION 100</t>
+  </si>
+  <si>
+    <t>MRToMRVWipSheet</t>
+  </si>
+  <si>
+    <t>MRTOMRVWip Data</t>
+  </si>
+  <si>
+    <t>WipType</t>
+  </si>
+  <si>
+    <t>WIP</t>
+  </si>
+  <si>
+    <t>WIP100</t>
+  </si>
+  <si>
+    <t>WorkInProgressWH</t>
+  </si>
+  <si>
+    <t>Subcontractor</t>
+  </si>
+  <si>
+    <t>MDWip</t>
+  </si>
+  <si>
+    <t>MLD WIP</t>
+  </si>
+  <si>
+    <t>MouldingWipWh</t>
+  </si>
+  <si>
+    <t>MOULDING WIP WH -100</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2000,21 +2380,6 @@
        AND prl_prod_rev = prod_rev</t>
   </si>
   <si>
-    <t>EDP MANAGER</t>
-  </si>
-  <si>
-    <t>SO_DisSimilar_Item_PriceList</t>
-  </si>
-  <si>
-    <t>HK-FG-PRICELIST-DISSIMILAR UOM-10001</t>
-  </si>
-  <si>
-    <t>ItemDelete</t>
-  </si>
-  <si>
-    <t>SK0001</t>
-  </si>
-  <si>
     <t>SOHeaderQuery</t>
   </si>
   <si>
@@ -2164,297 +2529,18 @@
        AND soh_bu = 'TVSA'
        AND soh_order_no = '${SONO}'</t>
   </si>
-  <si>
-    <t>ChargesBasis</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>ChargeItem</t>
-  </si>
-  <si>
-    <t>TVS-CH-00002</t>
-  </si>
-  <si>
-    <t>ChargesPercentage</t>
-  </si>
-  <si>
-    <t>ChargesValue</t>
-  </si>
-  <si>
-    <t>AdvancePercentage</t>
-  </si>
-  <si>
-    <t>AdavanceAmount</t>
-  </si>
-  <si>
-    <t>SONumber</t>
-  </si>
-  <si>
-    <t>SO100/00831/24-25</t>
-  </si>
-  <si>
-    <t>AdvancePaymentTerm</t>
-  </si>
-  <si>
-    <t>25%ADVANCE AND 75%INVOICE</t>
-  </si>
-  <si>
-    <t>BankName</t>
-  </si>
-  <si>
-    <t>STATE BANK OF INDIA - 30305325953</t>
-  </si>
-  <si>
-    <t>AdvDocNumber</t>
-  </si>
-  <si>
-    <t>Reference Number</t>
-  </si>
-  <si>
-    <t>6374-0001</t>
-  </si>
-  <si>
-    <t>BRVDocumentStatus</t>
-  </si>
-  <si>
-    <t>Received</t>
-  </si>
-  <si>
-    <t>SONO</t>
-  </si>
-  <si>
-    <t>${SONO}</t>
-  </si>
-  <si>
-    <t>SoDBLocationColumnName</t>
-  </si>
-  <si>
-    <t>Location ID</t>
-  </si>
-  <si>
-    <t>SoDBUnitColumnName</t>
-  </si>
-  <si>
-    <t>Unit ID</t>
-  </si>
-  <si>
-    <t>SoDBCustomerIDColumnName</t>
-  </si>
-  <si>
-    <t>Customer ID</t>
-  </si>
-  <si>
-    <t>SoDBCustomerDescColumnName</t>
-  </si>
-  <si>
-    <t>Customer Description</t>
-  </si>
-  <si>
-    <t>SoDBCusrrencyColumnName</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>CustomerDesc</t>
-  </si>
-  <si>
-    <t>SOSubVoucherTypeDBColumnName</t>
-  </si>
-  <si>
-    <t>Sub Voucher Desc</t>
-  </si>
-  <si>
-    <t>SODBPrefixColumnName</t>
-  </si>
-  <si>
-    <t>SO prefix</t>
-  </si>
-  <si>
-    <t>SODBDocNumberColumnName</t>
-  </si>
-  <si>
-    <t>SO Number</t>
-  </si>
-  <si>
-    <t>SODBCurrencyColumnName</t>
-  </si>
-  <si>
-    <t>SODBExchangeRateColumnName</t>
-  </si>
-  <si>
-    <t>Exchange Rate</t>
-  </si>
-  <si>
-    <t>SODBCpcCodeIDColumnName</t>
-  </si>
-  <si>
-    <t>CPC Code</t>
-  </si>
-  <si>
-    <t>SODBCpcCodeDescColumnName</t>
-  </si>
-  <si>
-    <t>CPC Code Desc</t>
-  </si>
-  <si>
-    <t>SODBItemIDColumnName</t>
-  </si>
-  <si>
-    <t>Item ID</t>
-  </si>
-  <si>
-    <t>SODBItemRevColumnName</t>
-  </si>
-  <si>
-    <t>Item Rev</t>
-  </si>
-  <si>
-    <t>SODBItemDescColumnName</t>
-  </si>
-  <si>
-    <t>Item Desc</t>
-  </si>
-  <si>
-    <t>SODBSaleUOMColumnName</t>
-  </si>
-  <si>
-    <t>Sale UOM</t>
-  </si>
-  <si>
-    <t>SODBHSNCodeColumnName</t>
-  </si>
-  <si>
-    <t>HSN Code</t>
-  </si>
-  <si>
-    <t>SODBTradeAssesableValueColumnName</t>
-  </si>
-  <si>
-    <t>Trade Ass. Val.</t>
-  </si>
-  <si>
-    <t>SODBTradeDiscountPercentageColumnName</t>
-  </si>
-  <si>
-    <t>Trade Disc. %</t>
-  </si>
-  <si>
-    <t>SODBTradeDiscountAmountColumnName</t>
-  </si>
-  <si>
-    <t>Trade Disc. Amt.</t>
-  </si>
-  <si>
-    <t>SODBSpecialAssesableValueColumnName</t>
-  </si>
-  <si>
-    <t>Spl. Ass. Val.</t>
-  </si>
-  <si>
-    <t>SODBSpecialDiscountPercentageColumnName</t>
-  </si>
-  <si>
-    <t>Spl. Disc. %</t>
-  </si>
-  <si>
-    <t>SODBSpecialDiscountAmountColumnName</t>
-  </si>
-  <si>
-    <t>Spl. Disc. Amt.</t>
-  </si>
-  <si>
-    <t>SODBCashAssesableValueColumnName</t>
-  </si>
-  <si>
-    <t>Cash Ass. Val.</t>
-  </si>
-  <si>
-    <t>SODBCashDiscountPercentageColumnName</t>
-  </si>
-  <si>
-    <t>Cash Disc. %</t>
-  </si>
-  <si>
-    <t>SODBCashDiscountAmountColumnName</t>
-  </si>
-  <si>
-    <t>Cash Disc. Amt.</t>
-  </si>
-  <si>
-    <t>SODBDiscountAmountPerQtyColumnName</t>
-  </si>
-  <si>
-    <t>Disc. Amt. / Qty.</t>
-  </si>
-  <si>
-    <t>SODBGrossAmountColumnName</t>
-  </si>
-  <si>
-    <t>Gross Amt.</t>
-  </si>
-  <si>
-    <t>SODBTotalDiscountAmountColumnName</t>
-  </si>
-  <si>
-    <t>Disc. Amt.</t>
-  </si>
-  <si>
-    <t>SODBTaxAmountColumnName</t>
-  </si>
-  <si>
-    <t>Tax Amt.</t>
-  </si>
-  <si>
-    <t>SODBPriceBasisColumnName</t>
-  </si>
-  <si>
-    <t>Price Basis Desc</t>
-  </si>
-  <si>
-    <t>SODBContractNumberFieldColumnName</t>
-  </si>
-  <si>
-    <t>Contract Number</t>
-  </si>
-  <si>
-    <t>SODBCatalog_PriceListNumberFieldColumnName</t>
-  </si>
-  <si>
-    <t>Catalog / Price List Number</t>
-  </si>
-  <si>
-    <t>SODBNetAmountColumnName</t>
-  </si>
-  <si>
-    <t>Net Amt.</t>
-  </si>
-  <si>
-    <t>SODBPaymentTermColumnName</t>
-  </si>
-  <si>
-    <t>Payment Term Desc2.</t>
-  </si>
-  <si>
-    <t>SODBINCOTermColumnName</t>
-  </si>
-  <si>
-    <t>INCO Term Desc.</t>
-  </si>
-  <si>
-    <t>SODBShipViaColumnName</t>
-  </si>
-  <si>
-    <t>Ship VIA Desc.</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2505,14 +2591,151 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2531,8 +2754,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2568,13 +2971,255 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2603,12 +3248,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2626,9 +3271,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -2636,18 +3281,61 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 3" xfId="2"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal 2" xfId="49"/>
+    <cellStyle name="Normal 3" xfId="50"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2909,17 +3597,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B408"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B425"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" customWidth="1"/>
-    <col min="2" max="2" width="59.85546875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="34.287037037037" customWidth="1"/>
+    <col min="2" max="2" width="59.8518518518519" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3854,8 +4542,8 @@
       <c r="A117" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B117" s="37" t="s">
-        <v>611</v>
+      <c r="B117" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3951,7 +4639,7 @@
         <v>236</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>611</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4335,7 +5023,7 @@
         <v>315</v>
       </c>
       <c r="B177" s="27" t="s">
-        <v>611</v>
+        <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -5659,544 +6347,682 @@
       </c>
     </row>
     <row r="343" spans="1:2">
-      <c r="A343" s="37" t="s">
+      <c r="A343" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="B343" s="38" t="s">
+      <c r="B343" s="7" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="344" spans="1:2">
-      <c r="A344" s="37" t="s">
+      <c r="A344" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B344" s="38" t="s">
+      <c r="B344" s="7" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="345" spans="1:2">
-      <c r="A345" s="37" t="s">
+      <c r="A345" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="B345" s="38" t="s">
+      <c r="B345" s="7" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="346" spans="1:2">
-      <c r="A346" s="37" t="s">
+      <c r="A346" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="B346" s="38" t="s">
+      <c r="B346" s="7" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="347" spans="1:2">
-      <c r="A347" s="37" t="s">
+      <c r="A347" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="B347" s="38" t="s">
+      <c r="B347" s="7" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="348" spans="1:2">
-      <c r="A348" s="37" t="s">
+      <c r="A348" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B348" s="38" t="s">
+      <c r="B348" s="7" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="349" spans="1:2">
-      <c r="A349" s="37" t="s">
+      <c r="A349" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="B349" s="38" t="s">
+      <c r="B349" s="7" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="350" spans="1:2">
-      <c r="A350" s="37" t="s">
+      <c r="A350" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="B350" s="38" t="s">
+      <c r="B350" s="7" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="351" spans="1:2">
-      <c r="A351" s="37" t="s">
+      <c r="A351" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B351" s="38" t="s">
+      <c r="B351" s="7" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="352" spans="1:2">
-      <c r="A352" s="37" t="s">
+      <c r="A352" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="B352" s="38" t="s">
+      <c r="B352" s="7" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="353" spans="1:2">
-      <c r="A353" s="37" t="s">
+      <c r="A353" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B353" s="38" t="s">
+      <c r="B353" s="7" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="354" spans="1:2">
-      <c r="A354" s="37" t="s">
+      <c r="A354" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B354" s="38" t="s">
+      <c r="B354" s="7" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="355" spans="1:2">
-      <c r="A355" s="37" t="s">
+      <c r="A355" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B355" s="38" t="s">
+      <c r="B355" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="356" spans="1:2">
-      <c r="A356" s="37" t="s">
-        <v>612</v>
-      </c>
-      <c r="B356" s="37" t="s">
-        <v>613</v>
+      <c r="A356" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="357" spans="1:2">
-      <c r="A357" s="37" t="s">
-        <v>614</v>
-      </c>
-      <c r="B357" s="38" t="s">
-        <v>615</v>
+      <c r="A357" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B357" s="7" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" s="20" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="B358" s="20" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" s="20" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="B359" s="20" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" s="20" t="s">
-        <v>624</v>
-      </c>
-      <c r="B360" s="37">
+        <v>615</v>
+      </c>
+      <c r="B360" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" s="20" t="s">
-        <v>625</v>
-      </c>
-      <c r="B361" s="37">
+        <v>616</v>
+      </c>
+      <c r="B361" s="2">
         <v>1000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" s="20" t="s">
-        <v>626</v>
-      </c>
-      <c r="B362" s="39">
+        <v>617</v>
+      </c>
+      <c r="B362" s="37">
         <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" s="20" t="s">
-        <v>627</v>
-      </c>
-      <c r="B363" s="37">
+        <v>618</v>
+      </c>
+      <c r="B363" s="2">
         <v>1000</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" s="20" t="s">
-        <v>628</v>
-      </c>
-      <c r="B364" s="37" t="s">
-        <v>629</v>
+        <v>619</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="365" spans="1:2">
       <c r="A365" s="20" t="s">
-        <v>630</v>
-      </c>
-      <c r="B365" s="37" t="s">
-        <v>631</v>
+        <v>621</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" s="20" t="s">
-        <v>632</v>
-      </c>
-      <c r="B366" s="37" t="s">
-        <v>633</v>
+        <v>623</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="B367" s="37">
+        <v>625</v>
+      </c>
+      <c r="B367" s="2">
         <v>10000039</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" s="20" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="B368" s="20" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
     </row>
     <row r="369" spans="1:2">
       <c r="A369" s="20" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="B369" s="20" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" s="20" t="s">
-        <v>639</v>
-      </c>
-      <c r="B370" s="38" t="s">
-        <v>640</v>
+        <v>630</v>
+      </c>
+      <c r="B370" s="7" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" s="20" t="s">
-        <v>641</v>
-      </c>
-      <c r="B371" s="38" t="s">
-        <v>642</v>
+        <v>632</v>
+      </c>
+      <c r="B371" s="7" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" s="20" t="s">
-        <v>643</v>
-      </c>
-      <c r="B372" s="38" t="s">
-        <v>644</v>
+        <v>634</v>
+      </c>
+      <c r="B372" s="7" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" s="20" t="s">
-        <v>645</v>
-      </c>
-      <c r="B373" s="38" t="s">
-        <v>646</v>
+        <v>636</v>
+      </c>
+      <c r="B373" s="7" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" s="20" t="s">
-        <v>647</v>
-      </c>
-      <c r="B374" s="38" t="s">
-        <v>648</v>
+        <v>638</v>
+      </c>
+      <c r="B374" s="7" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" s="20" t="s">
-        <v>649</v>
-      </c>
-      <c r="B375" s="38" t="s">
-        <v>650</v>
+        <v>640</v>
+      </c>
+      <c r="B375" s="7" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="376" spans="1:2">
       <c r="A376" s="20" t="s">
-        <v>651</v>
-      </c>
-      <c r="B376" s="38" t="s">
+        <v>642</v>
+      </c>
+      <c r="B376" s="7" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" s="20" t="s">
-        <v>652</v>
-      </c>
-      <c r="B377" s="38" t="s">
-        <v>653</v>
+        <v>643</v>
+      </c>
+      <c r="B377" s="7" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" s="20" t="s">
-        <v>654</v>
-      </c>
-      <c r="B378" s="38" t="s">
-        <v>655</v>
+        <v>645</v>
+      </c>
+      <c r="B378" s="7" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" s="20" t="s">
-        <v>656</v>
-      </c>
-      <c r="B379" s="38" t="s">
-        <v>657</v>
+        <v>647</v>
+      </c>
+      <c r="B379" s="7" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" s="20" t="s">
-        <v>658</v>
-      </c>
-      <c r="B380" s="38" t="s">
-        <v>650</v>
+        <v>649</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" s="20" t="s">
-        <v>659</v>
-      </c>
-      <c r="B381" s="38" t="s">
-        <v>660</v>
+        <v>650</v>
+      </c>
+      <c r="B381" s="7" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" s="20" t="s">
-        <v>661</v>
-      </c>
-      <c r="B382" s="38" t="s">
-        <v>662</v>
+        <v>652</v>
+      </c>
+      <c r="B382" s="7" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" s="20" t="s">
-        <v>663</v>
-      </c>
-      <c r="B383" s="38" t="s">
-        <v>664</v>
+        <v>654</v>
+      </c>
+      <c r="B383" s="7" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" s="20" t="s">
-        <v>665</v>
-      </c>
-      <c r="B384" s="38" t="s">
-        <v>666</v>
+        <v>656</v>
+      </c>
+      <c r="B384" s="7" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" s="20" t="s">
-        <v>667</v>
-      </c>
-      <c r="B385" s="38" t="s">
-        <v>668</v>
+        <v>658</v>
+      </c>
+      <c r="B385" s="7" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" s="20" t="s">
-        <v>669</v>
-      </c>
-      <c r="B386" s="38" t="s">
-        <v>670</v>
+        <v>660</v>
+      </c>
+      <c r="B386" s="7" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" s="20" t="s">
-        <v>671</v>
-      </c>
-      <c r="B387" s="38" t="s">
-        <v>672</v>
+        <v>662</v>
+      </c>
+      <c r="B387" s="7" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" s="20" t="s">
-        <v>673</v>
-      </c>
-      <c r="B388" s="38" t="s">
-        <v>674</v>
+        <v>664</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" s="20" t="s">
-        <v>675</v>
-      </c>
-      <c r="B389" s="38" t="s">
-        <v>676</v>
+        <v>666</v>
+      </c>
+      <c r="B389" s="7" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" s="20" t="s">
-        <v>677</v>
-      </c>
-      <c r="B390" s="38" t="s">
-        <v>678</v>
+        <v>668</v>
+      </c>
+      <c r="B390" s="7" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" s="20" t="s">
-        <v>679</v>
-      </c>
-      <c r="B391" s="38" t="s">
-        <v>680</v>
+        <v>670</v>
+      </c>
+      <c r="B391" s="7" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" s="20" t="s">
-        <v>681</v>
-      </c>
-      <c r="B392" s="38" t="s">
-        <v>682</v>
+        <v>672</v>
+      </c>
+      <c r="B392" s="7" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" s="20" t="s">
-        <v>683</v>
-      </c>
-      <c r="B393" s="38" t="s">
-        <v>684</v>
+        <v>674</v>
+      </c>
+      <c r="B393" s="7" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" s="20" t="s">
-        <v>685</v>
-      </c>
-      <c r="B394" s="38" t="s">
-        <v>686</v>
+        <v>676</v>
+      </c>
+      <c r="B394" s="7" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" s="20" t="s">
-        <v>687</v>
-      </c>
-      <c r="B395" s="38" t="s">
-        <v>688</v>
+        <v>678</v>
+      </c>
+      <c r="B395" s="7" t="s">
+        <v>679</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" s="20" t="s">
-        <v>689</v>
-      </c>
-      <c r="B396" s="38" t="s">
-        <v>690</v>
+        <v>680</v>
+      </c>
+      <c r="B396" s="7" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" s="20" t="s">
-        <v>691</v>
-      </c>
-      <c r="B397" s="38" t="s">
-        <v>692</v>
+        <v>682</v>
+      </c>
+      <c r="B397" s="7" t="s">
+        <v>683</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" s="20" t="s">
-        <v>693</v>
-      </c>
-      <c r="B398" s="38" t="s">
-        <v>694</v>
+        <v>684</v>
+      </c>
+      <c r="B398" s="7" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" s="20" t="s">
-        <v>695</v>
-      </c>
-      <c r="B399" s="38" t="s">
-        <v>696</v>
+        <v>686</v>
+      </c>
+      <c r="B399" s="7" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" s="20" t="s">
-        <v>697</v>
-      </c>
-      <c r="B400" s="38" t="s">
-        <v>698</v>
+        <v>688</v>
+      </c>
+      <c r="B400" s="7" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" s="20" t="s">
-        <v>699</v>
-      </c>
-      <c r="B401" s="38" t="s">
-        <v>700</v>
+        <v>690</v>
+      </c>
+      <c r="B401" s="7" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" s="20" t="s">
-        <v>701</v>
-      </c>
-      <c r="B402" s="38" t="s">
-        <v>702</v>
+        <v>692</v>
+      </c>
+      <c r="B402" s="7" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" s="20" t="s">
-        <v>703</v>
-      </c>
-      <c r="B403" s="38" t="s">
-        <v>704</v>
+        <v>694</v>
+      </c>
+      <c r="B403" s="7" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" s="20" t="s">
-        <v>705</v>
-      </c>
-      <c r="B404" s="38" t="s">
-        <v>706</v>
+        <v>696</v>
+      </c>
+      <c r="B404" s="7" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" s="20" t="s">
-        <v>707</v>
-      </c>
-      <c r="B405" s="38" t="s">
-        <v>708</v>
+        <v>698</v>
+      </c>
+      <c r="B405" s="7" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" s="20" t="s">
-        <v>709</v>
-      </c>
-      <c r="B406" s="38" t="s">
-        <v>710</v>
+        <v>700</v>
+      </c>
+      <c r="B406" s="7" t="s">
+        <v>701</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" s="20" t="s">
-        <v>711</v>
-      </c>
-      <c r="B407" s="38" t="s">
-        <v>712</v>
+        <v>702</v>
+      </c>
+      <c r="B407" s="7" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" s="20" t="s">
+        <v>704</v>
+      </c>
+      <c r="B408" s="7" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B409" s="7" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B410" s="7" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B411" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B412" s="7" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B413" s="7" t="s">
         <v>713</v>
       </c>
-      <c r="B408" s="38" t="s">
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2" t="s">
         <v>714</v>
+      </c>
+      <c r="B414" s="7" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B415" s="7" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B416" s="7" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B417" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B418" s="7" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B419" s="7" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B420" s="7" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B421" s="7" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B422" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B423" s="7" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B424" s="7" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B425" s="7" t="s">
+        <v>733</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.8518518518519" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6208,36 +7034,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="108.95" customHeight="1">
+    <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>607</v>
+        <v>734</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="114" customHeight="1">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>609</v>
+        <v>736</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="80.25" customHeight="1">
-      <c r="A4" s="37" t="s">
-        <v>616</v>
+        <v>737</v>
+      </c>
+    </row>
+    <row r="4" ht="80.25" customHeight="1" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>738</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="69.75" customHeight="1">
-      <c r="A5" s="37" t="s">
-        <v>618</v>
+        <v>739</v>
+      </c>
+    </row>
+    <row r="5" ht="69.75" customHeight="1" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>740</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>619</v>
+        <v>741</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6294,5 +7120,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="800">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -2230,6 +2230,180 @@
   </si>
   <si>
     <t>MOULDING WIP WH -100</t>
+  </si>
+  <si>
+    <t>GwlBomItem1001</t>
+  </si>
+  <si>
+    <t>GWL - BOM ITEM - 1001</t>
+  </si>
+  <si>
+    <t>GwlProcess1</t>
+  </si>
+  <si>
+    <t>GWLPROCESS-01</t>
+  </si>
+  <si>
+    <t>GwlProcess2</t>
+  </si>
+  <si>
+    <t>GWLPROCESS-02</t>
+  </si>
+  <si>
+    <t>GwlProcess3</t>
+  </si>
+  <si>
+    <t>GWLPROCESS-03</t>
+  </si>
+  <si>
+    <t>GwlAutomationArea</t>
+  </si>
+  <si>
+    <t>GWL AUTOMATION AREA</t>
+  </si>
+  <si>
+    <t>InsideType</t>
+  </si>
+  <si>
+    <t>Inside</t>
+  </si>
+  <si>
+    <t>AutomationResource</t>
+  </si>
+  <si>
+    <t>AUTOMATION</t>
+  </si>
+  <si>
+    <t>RunnerRaiserOption</t>
+  </si>
+  <si>
+    <t>Runner/Raiser</t>
+  </si>
+  <si>
+    <t>PrimaryType</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>ActiveStatus</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>PRD0Prefix</t>
+  </si>
+  <si>
+    <t>PRD0</t>
+  </si>
+  <si>
+    <t>ProdOrderStandard</t>
+  </si>
+  <si>
+    <t>Production Order - Standard</t>
+  </si>
+  <si>
+    <t>ManufactureType</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>ResourceText</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>KishoreValue</t>
+  </si>
+  <si>
+    <t>KSRADMIN</t>
+  </si>
+  <si>
+    <t>PriceListSupplier</t>
+  </si>
+  <si>
+    <t>GPONumber</t>
+  </si>
+  <si>
+    <t>POM49/00002/24-25</t>
+  </si>
+  <si>
+    <t>DcNumberField</t>
+  </si>
+  <si>
+    <t>POM49/000</t>
+  </si>
+  <si>
+    <t>SupplierBillNumber</t>
+  </si>
+  <si>
+    <t>VehicleNumber</t>
+  </si>
+  <si>
+    <t>DriverName</t>
+  </si>
+  <si>
+    <t>Prem.k</t>
+  </si>
+  <si>
+    <t>ReferenceField</t>
+  </si>
+  <si>
+    <t>As PerRequired</t>
+  </si>
+  <si>
+    <t>EwayBillNumber</t>
+  </si>
+  <si>
+    <t>POM49</t>
+  </si>
+  <si>
+    <t>L49</t>
+  </si>
+  <si>
+    <t>LOC49</t>
+  </si>
+  <si>
+    <t>StockTransferSupplier</t>
+  </si>
+  <si>
+    <t>TVS ARGOMM PVT. LTD. - MADURAI PLANT - UNIT 1</t>
+  </si>
+  <si>
+    <t>StockTransferValue</t>
+  </si>
+  <si>
+    <t>STTYPE</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>StockTransferCustomer</t>
+  </si>
+  <si>
+    <t>SUP00326</t>
+  </si>
+  <si>
+    <t>StockTransferInvoice</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>Stock Transfer</t>
+  </si>
+  <si>
+    <t>SAIN-2425-00794</t>
+  </si>
+  <si>
+    <t>GrnPurchase</t>
+  </si>
+  <si>
+    <t>GRL10/00429/24-25</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2540,7 +2714,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2588,6 +2762,18 @@
     <font>
       <sz val="10"/>
       <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2735,7 +2921,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2751,6 +2937,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3087,139 +3279,139 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3244,17 +3436,46 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3262,26 +3483,73 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3603,11 +3871,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B425"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B461"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="34.287037037037" customWidth="1"/>
-    <col min="2" max="2" width="59.8518518518519" style="4" customWidth="1"/>
+    <col min="1" max="1" width="34.2909090909091" customWidth="1"/>
+    <col min="2" max="2" width="59.8545454545455" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4179,7 +4447,7 @@
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="11" t="s">
         <v>136</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -4187,7 +4455,7 @@
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="11" t="s">
         <v>138</v>
       </c>
       <c r="B73" s="10" t="s">
@@ -4195,7 +4463,7 @@
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="11" t="s">
         <v>140</v>
       </c>
       <c r="B74" s="10" t="s">
@@ -4203,7 +4471,7 @@
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="11" t="s">
         <v>142</v>
       </c>
       <c r="B75" s="10" t="s">
@@ -4211,7 +4479,7 @@
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="11" t="s">
         <v>144</v>
       </c>
       <c r="B76" s="10">
@@ -4219,7 +4487,7 @@
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="11" t="s">
         <v>145</v>
       </c>
       <c r="B77" s="10" t="s">
@@ -4227,7 +4495,7 @@
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="11" t="s">
         <v>147</v>
       </c>
       <c r="B78" s="10" t="s">
@@ -4235,7 +4503,7 @@
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="11" t="s">
         <v>149</v>
       </c>
       <c r="B79" s="10" t="s">
@@ -4243,250 +4511,250 @@
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="13" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B81" s="12" t="s">
+      <c r="B81" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="14" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="14" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="14" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="13" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="12" t="s">
+      <c r="A88" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="12" t="s">
+      <c r="A89" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="12" t="s">
+      <c r="A91" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="B91" s="13" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="12" t="s">
+      <c r="A92" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="13" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="12" t="s">
+      <c r="A93" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="13" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="12" t="s">
+      <c r="A94" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="13" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="12" t="s">
+      <c r="A95" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="B95" s="13" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="12" t="s">
+      <c r="A96" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="13" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="12" t="s">
+      <c r="A97" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B97" s="12" t="s">
+      <c r="B97" s="13" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="12" t="s">
+      <c r="A98" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="13" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="12" t="s">
+      <c r="A99" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="13" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="14" t="s">
+      <c r="A100" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B100" s="14" t="s">
+      <c r="B100" s="18" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="14" t="s">
+      <c r="A101" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B101" s="15" t="s">
+      <c r="B101" s="19" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="14" t="s">
+      <c r="A102" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="B102" s="14" t="s">
+      <c r="B102" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="14" t="s">
+      <c r="A103" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B103" s="18" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="14" t="s">
+      <c r="A104" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="B104" s="15">
+      <c r="B104" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="16" t="s">
+      <c r="A105" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="B105" s="16" t="s">
+      <c r="B105" s="21" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="16" t="s">
+      <c r="A106" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="B106" s="17" t="s">
+      <c r="B106" s="22" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="16" t="s">
+      <c r="A107" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="B107" s="18">
+      <c r="B107" s="23">
         <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="16" t="s">
+      <c r="A108" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="B108" s="16" t="s">
+      <c r="B108" s="21" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="16" t="s">
+      <c r="A109" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="B109" s="19" t="s">
+      <c r="B109" s="24" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="16" t="s">
+      <c r="A110" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="B110" s="18">
+      <c r="B110" s="23">
         <v>100</v>
       </c>
     </row>
@@ -4494,47 +4762,47 @@
       <c r="A111" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="25" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="20" t="s">
+      <c r="A112" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="B112" s="20" t="s">
+      <c r="B112" s="27" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="20" t="s">
+      <c r="A113" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="B113" s="20" t="s">
+      <c r="B113" s="27" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="20" t="s">
+      <c r="A114" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="25" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="20" t="s">
+      <c r="A115" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="25" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="20" t="s">
+      <c r="A116" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="25" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4542,7 +4810,7 @@
       <c r="A117" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4550,319 +4818,319 @@
       <c r="A118" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="21" t="s">
+      <c r="A119" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="B119" s="22" t="s">
+      <c r="B119" s="29" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="21" t="s">
+      <c r="A120" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="B120" s="22" t="s">
+      <c r="B120" s="29" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="21" t="s">
+      <c r="A121" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="B121" s="22" t="s">
+      <c r="B121" s="29" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="21" t="s">
+      <c r="A122" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="B122" s="22" t="s">
+      <c r="B122" s="29" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="21" t="s">
+      <c r="A123" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="B123" s="22" t="s">
+      <c r="B123" s="29" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="21" t="s">
+      <c r="A124" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="B124" s="22" t="s">
+      <c r="B124" s="29" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="21" t="s">
+      <c r="A125" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="B125" s="22" t="s">
+      <c r="B125" s="29" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="21" t="s">
+      <c r="A126" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="B126" s="22" t="s">
+      <c r="B126" s="29" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="21" t="s">
+      <c r="A127" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="B127" s="22" t="s">
+      <c r="B127" s="29" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="21" t="s">
+      <c r="A128" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="B128" s="22" t="s">
+      <c r="B128" s="29" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="21" t="s">
+      <c r="A129" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="B129" s="22" t="s">
+      <c r="B129" s="29" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="21" t="s">
+      <c r="A130" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="B130" s="22" t="s">
+      <c r="B130" s="29" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="21" t="s">
+      <c r="A131" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="B131" s="22" t="s">
+      <c r="B131" s="29" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="21" t="s">
+      <c r="A132" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="B132" s="22" t="s">
+      <c r="B132" s="29" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="21" t="s">
+      <c r="A133" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="B133" s="22" t="s">
+      <c r="B133" s="29" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="21" t="s">
+      <c r="A134" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="B134" s="22" t="s">
+      <c r="B134" s="29" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="21" t="s">
+      <c r="A135" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="B135" s="22" t="s">
+      <c r="B135" s="29" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="21" t="s">
+      <c r="A136" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="B136" s="22" t="s">
+      <c r="B136" s="29" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="21" t="s">
+      <c r="A137" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="B137" s="22" t="s">
+      <c r="B137" s="29" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="21" t="s">
+      <c r="A138" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="B138" s="22" t="s">
+      <c r="B138" s="29" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="21" t="s">
+      <c r="A139" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="B139" s="22" t="s">
+      <c r="B139" s="29" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="21" t="s">
+      <c r="A140" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="B140" s="22" t="s">
+      <c r="B140" s="29" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="21" t="s">
+      <c r="A141" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="B141" s="22" t="s">
+      <c r="B141" s="29" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="21" t="s">
+      <c r="A142" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="B142" s="22" t="s">
+      <c r="B142" s="29" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="21" t="s">
+      <c r="A143" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="B143" s="22" t="s">
+      <c r="B143" s="29" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="21" t="s">
+      <c r="A144" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="B144" s="22" t="s">
+      <c r="B144" s="29" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="21" t="s">
+      <c r="A145" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="B145" s="22" t="s">
+      <c r="B145" s="29" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="21" t="s">
+      <c r="A146" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="B146" s="22" t="s">
+      <c r="B146" s="29" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="21" t="s">
+      <c r="A147" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="B147" s="22" t="s">
+      <c r="B147" s="29" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="21" t="s">
+      <c r="A148" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="B148" s="22" t="s">
+      <c r="B148" s="29" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="21" t="s">
+      <c r="A149" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="B149" s="22" t="s">
+      <c r="B149" s="29" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="21" t="s">
+      <c r="A150" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="B150" s="22" t="s">
+      <c r="B150" s="29" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="23" t="s">
+      <c r="A151" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="B151" s="22" t="s">
+      <c r="B151" s="29" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="23" t="s">
+      <c r="A152" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="B152" s="22" t="s">
+      <c r="B152" s="29" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="23" t="s">
+      <c r="A153" s="30" t="s">
         <v>268</v>
       </c>
-      <c r="B153" s="22" t="s">
+      <c r="B153" s="29" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="23" t="s">
+      <c r="A154" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="B154" s="22" t="s">
+      <c r="B154" s="29" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="23" t="s">
+      <c r="A155" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="B155" s="22" t="s">
+      <c r="B155" s="29" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="23" t="s">
+      <c r="A156" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="B156" s="22" t="s">
+      <c r="B156" s="29" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="24" t="s">
+      <c r="A157" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="B157" s="25" t="s">
+      <c r="B157" s="32" t="s">
         <v>277</v>
       </c>
     </row>
@@ -4870,263 +5138,263 @@
       <c r="A158" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="B158" s="25" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="11" t="s">
+      <c r="A159" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="B159" s="26" t="s">
+      <c r="B159" s="33" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="11" t="s">
+      <c r="A160" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="B160" s="27" t="s">
+      <c r="B160" s="34" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="11" t="s">
+      <c r="A161" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="B161" s="11" t="s">
+      <c r="B161" s="14" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="11" t="s">
+      <c r="A162" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="B162" s="27" t="s">
+      <c r="B162" s="34" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="11" t="s">
+      <c r="A163" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="B163" s="27" t="s">
+      <c r="B163" s="34" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="11" t="s">
+      <c r="A164" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="B164" s="11" t="s">
+      <c r="B164" s="14" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="11" t="s">
+      <c r="A165" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="B165" s="11" t="s">
+      <c r="B165" s="14" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="11" t="s">
+      <c r="A166" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="B166" s="27" t="s">
+      <c r="B166" s="34" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="11" t="s">
+      <c r="A167" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="B167" s="27" t="s">
+      <c r="B167" s="34" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="11" t="s">
+      <c r="A168" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="B168" s="11" t="s">
+      <c r="B168" s="14" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="11" t="s">
+      <c r="A169" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="B169" s="11" t="s">
+      <c r="B169" s="14" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="11" t="s">
+      <c r="A170" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="B170" s="27" t="s">
+      <c r="B170" s="34" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="11" t="s">
+      <c r="A171" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B171" s="27" t="s">
+      <c r="B171" s="34" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="11" t="s">
+      <c r="A172" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="B172" s="27" t="s">
+      <c r="B172" s="34" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="11" t="s">
+      <c r="A173" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="B173" s="27" t="s">
+      <c r="B173" s="34" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="11" t="s">
+      <c r="A174" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="B174" s="27" t="s">
+      <c r="B174" s="34" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="11" t="s">
+      <c r="A175" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="B175" s="27" t="s">
+      <c r="B175" s="34" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="11" t="s">
+      <c r="A176" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="B176" s="27" t="s">
+      <c r="B176" s="34" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="11" t="s">
+      <c r="A177" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="B177" s="27" t="s">
+      <c r="B177" s="34" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="11" t="s">
+      <c r="A178" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="B178" s="27" t="s">
+      <c r="B178" s="34" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="11" t="s">
+      <c r="A179" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="B179" s="27" t="s">
+      <c r="B179" s="34" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="11" t="s">
+      <c r="A180" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="B180" s="27" t="s">
+      <c r="B180" s="34" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="11" t="s">
+      <c r="A181" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="B181" s="27" t="s">
+      <c r="B181" s="34" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="11" t="s">
+      <c r="A182" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="B182" s="27" t="s">
+      <c r="B182" s="34" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="11" t="s">
+      <c r="A183" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="B183" s="27" t="s">
+      <c r="B183" s="34" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="11" t="s">
+      <c r="A184" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="B184" s="27" t="s">
+      <c r="B184" s="34" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="11" t="s">
+      <c r="A185" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B185" s="27" t="s">
+      <c r="B185" s="34" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="11" t="s">
+      <c r="A186" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="B186" s="11" t="s">
+      <c r="B186" s="14" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="11" t="s">
+      <c r="A187" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B187" s="11" t="s">
+      <c r="B187" s="14" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="11" t="s">
+      <c r="A188" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="B188" s="27" t="s">
+      <c r="B188" s="34" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="11" t="s">
+      <c r="A189" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="B189" s="11" t="s">
+      <c r="B189" s="14" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="11" t="s">
+      <c r="A190" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="B190" s="27" t="s">
+      <c r="B190" s="34" t="s">
         <v>339</v>
       </c>
     </row>
@@ -5134,215 +5402,215 @@
       <c r="A191" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B191" s="28" t="s">
+      <c r="B191" s="35" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="29" t="s">
+      <c r="A192" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="B192" s="29" t="s">
+      <c r="B192" s="37" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="29" t="s">
+      <c r="A193" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="B193" s="30" t="s">
+      <c r="B193" s="38" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="29" t="s">
+      <c r="A194" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="B194" s="15">
+      <c r="B194" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="29" t="s">
+      <c r="A195" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="B195" s="29" t="s">
+      <c r="B195" s="37" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="29" t="s">
+      <c r="A196" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="B196" s="14" t="s">
+      <c r="B196" s="18" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="29" t="s">
+      <c r="A197" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="B197" s="15">
+      <c r="B197" s="19">
         <v>100</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="29" t="s">
+      <c r="A198" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="B198" s="15" t="s">
+      <c r="B198" s="19" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="29" t="s">
+      <c r="A199" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="B199" s="31" t="s">
+      <c r="B199" s="39" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="29" t="s">
+      <c r="A200" s="36" t="s">
         <v>346</v>
       </c>
-      <c r="B200" s="31" t="s">
+      <c r="B200" s="39" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="29" t="s">
+      <c r="A201" s="36" t="s">
         <v>348</v>
       </c>
-      <c r="B201" s="31" t="s">
+      <c r="B201" s="39" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="29" t="s">
+      <c r="A202" s="36" t="s">
         <v>350</v>
       </c>
-      <c r="B202" s="15">
+      <c r="B202" s="19">
         <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="29" t="s">
+      <c r="A203" s="36" t="s">
         <v>351</v>
       </c>
-      <c r="B203" s="15">
+      <c r="B203" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="29" t="s">
+      <c r="A204" s="36" t="s">
         <v>352</v>
       </c>
-      <c r="B204" s="15" t="s">
+      <c r="B204" s="19" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="15" t="s">
+      <c r="A205" s="40" t="s">
         <v>354</v>
       </c>
-      <c r="B205" s="15">
+      <c r="B205" s="19">
         <v>150</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="15" t="s">
+      <c r="A206" s="40" t="s">
         <v>355</v>
       </c>
-      <c r="B206" s="15">
+      <c r="B206" s="19">
         <v>250</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="15" t="s">
+      <c r="A207" s="40" t="s">
         <v>356</v>
       </c>
-      <c r="B207" s="15" t="s">
+      <c r="B207" s="19" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="15" t="s">
+      <c r="A208" s="40" t="s">
         <v>358</v>
       </c>
-      <c r="B208" s="15">
+      <c r="B208" s="19">
         <v>123562</v>
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="15" t="s">
+      <c r="A209" s="40" t="s">
         <v>359</v>
       </c>
-      <c r="B209" s="15">
+      <c r="B209" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="15" t="s">
+      <c r="A210" s="40" t="s">
         <v>360</v>
       </c>
-      <c r="B210" s="15">
+      <c r="B210" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="15" t="s">
+      <c r="A211" s="40" t="s">
         <v>361</v>
       </c>
-      <c r="B211" s="15">
+      <c r="B211" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="15" t="s">
+      <c r="A212" s="40" t="s">
         <v>362</v>
       </c>
-      <c r="B212" s="30" t="s">
+      <c r="B212" s="38" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="15" t="s">
+      <c r="A213" s="40" t="s">
         <v>364</v>
       </c>
-      <c r="B213" s="14" t="s">
+      <c r="B213" s="18" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="15" t="s">
+      <c r="A214" s="40" t="s">
         <v>366</v>
       </c>
-      <c r="B214" s="30" t="s">
+      <c r="B214" s="38" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="15" t="s">
+      <c r="A215" s="40" t="s">
         <v>368</v>
       </c>
-      <c r="B215" s="15">
+      <c r="B215" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="15" t="s">
+      <c r="A216" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="B216" s="15">
+      <c r="B216" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="15" t="s">
+      <c r="A217" s="40" t="s">
         <v>370</v>
       </c>
-      <c r="B217" s="30" t="s">
+      <c r="B217" s="38" t="s">
         <v>71</v>
       </c>
     </row>
@@ -5350,63 +5618,63 @@
       <c r="A218" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B218" s="2" t="s">
+      <c r="B218" s="25" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="24" t="s">
+      <c r="A219" s="31" t="s">
         <v>371</v>
       </c>
-      <c r="B219" s="24" t="s">
+      <c r="B219" s="41" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="24" t="s">
+      <c r="A220" s="31" t="s">
         <v>372</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="B220" s="25" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="24" t="s">
+      <c r="A221" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="B221" s="2" t="s">
+      <c r="B221" s="25" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="32" t="s">
+      <c r="A222" s="42" t="s">
         <v>376</v>
       </c>
-      <c r="B222" s="24" t="s">
+      <c r="B222" s="41" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="32" t="s">
+      <c r="A223" s="42" t="s">
         <v>378</v>
       </c>
-      <c r="B223" s="24" t="s">
+      <c r="B223" s="41" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="33" t="s">
+      <c r="A224" s="43" t="s">
         <v>380</v>
       </c>
-      <c r="B224" s="33" t="s">
+      <c r="B224" s="44" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="32" t="s">
+      <c r="A225" s="42" t="s">
         <v>382</v>
       </c>
-      <c r="B225" s="32" t="s">
+      <c r="B225" s="45" t="s">
         <v>383</v>
       </c>
     </row>
@@ -5598,7 +5866,7 @@
       <c r="A249" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B249" s="34" t="s">
+      <c r="B249" s="46" t="s">
         <v>419</v>
       </c>
     </row>
@@ -5827,10 +6095,10 @@
       </c>
     </row>
     <row r="278" spans="1:2">
-      <c r="A278" s="20" t="s">
+      <c r="A278" s="26" t="s">
         <v>467</v>
       </c>
-      <c r="B278" s="2" t="s">
+      <c r="B278" s="25" t="s">
         <v>468</v>
       </c>
     </row>
@@ -5838,7 +6106,7 @@
       <c r="A279" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B279" s="2" t="s">
+      <c r="B279" s="25" t="s">
         <v>59</v>
       </c>
     </row>
@@ -5878,12 +6146,12 @@
       <c r="A284" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="B284" s="35" t="s">
+      <c r="B284" s="47" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="285" spans="1:2">
-      <c r="A285" s="36" t="s">
+      <c r="A285" s="48" t="s">
         <v>479</v>
       </c>
       <c r="B285" s="7" t="s">
@@ -5891,7 +6159,7 @@
       </c>
     </row>
     <row r="286" spans="1:2">
-      <c r="A286" s="36" t="s">
+      <c r="A286" s="48" t="s">
         <v>481</v>
       </c>
       <c r="B286" s="7" t="s">
@@ -5899,7 +6167,7 @@
       </c>
     </row>
     <row r="287" spans="1:2">
-      <c r="A287" s="36" t="s">
+      <c r="A287" s="48" t="s">
         <v>483</v>
       </c>
       <c r="B287" s="7" t="s">
@@ -5907,7 +6175,7 @@
       </c>
     </row>
     <row r="288" spans="1:2">
-      <c r="A288" s="36" t="s">
+      <c r="A288" s="48" t="s">
         <v>485</v>
       </c>
       <c r="B288" s="7" t="s">
@@ -5915,7 +6183,7 @@
       </c>
     </row>
     <row r="289" spans="1:2">
-      <c r="A289" s="36" t="s">
+      <c r="A289" s="48" t="s">
         <v>487</v>
       </c>
       <c r="B289" s="7" t="s">
@@ -5923,7 +6191,7 @@
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="36" t="s">
+      <c r="A290" s="48" t="s">
         <v>489</v>
       </c>
       <c r="B290" s="7" t="s">
@@ -5931,7 +6199,7 @@
       </c>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="36" t="s">
+      <c r="A291" s="48" t="s">
         <v>491</v>
       </c>
       <c r="B291" s="7" t="s">
@@ -6158,7 +6426,7 @@
       <c r="A319" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B319" s="8" t="s">
+      <c r="B319" s="49" t="s">
         <v>543</v>
       </c>
     </row>
@@ -6291,58 +6559,58 @@
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="23" t="s">
+      <c r="A336" s="30" t="s">
         <v>573</v>
       </c>
-      <c r="B336" s="22" t="s">
+      <c r="B336" s="29" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="337" spans="1:2">
-      <c r="A337" s="23" t="s">
+      <c r="A337" s="30" t="s">
         <v>575</v>
       </c>
-      <c r="B337" s="22" t="s">
+      <c r="B337" s="29" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="338" spans="1:2">
-      <c r="A338" s="23" t="s">
+      <c r="A338" s="30" t="s">
         <v>576</v>
       </c>
-      <c r="B338" s="22" t="s">
+      <c r="B338" s="29" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="339" spans="1:2">
-      <c r="A339" s="23" t="s">
+      <c r="A339" s="30" t="s">
         <v>577</v>
       </c>
-      <c r="B339" s="22" t="s">
+      <c r="B339" s="29" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="340" spans="1:2">
-      <c r="A340" s="23" t="s">
+      <c r="A340" s="30" t="s">
         <v>578</v>
       </c>
-      <c r="B340" s="22" t="s">
+      <c r="B340" s="29" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="341" spans="1:2">
-      <c r="A341" s="23" t="s">
+      <c r="A341" s="30" t="s">
         <v>580</v>
       </c>
-      <c r="B341" s="22" t="s">
+      <c r="B341" s="29" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="342" spans="1:2">
-      <c r="A342" s="23" t="s">
+      <c r="A342" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="B342" s="22" t="s">
+      <c r="B342" s="29" t="s">
         <v>579</v>
       </c>
     </row>
@@ -6454,7 +6722,7 @@
       <c r="A356" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B356" s="2" t="s">
+      <c r="B356" s="25" t="s">
         <v>608</v>
       </c>
     </row>
@@ -6467,103 +6735,103 @@
       </c>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="20" t="s">
+      <c r="A358" s="26" t="s">
         <v>611</v>
       </c>
-      <c r="B358" s="20" t="s">
+      <c r="B358" s="27" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="359" spans="1:2">
-      <c r="A359" s="20" t="s">
+      <c r="A359" s="26" t="s">
         <v>613</v>
       </c>
-      <c r="B359" s="20" t="s">
+      <c r="B359" s="27" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="360" spans="1:2">
-      <c r="A360" s="20" t="s">
+      <c r="A360" s="26" t="s">
         <v>615</v>
       </c>
-      <c r="B360" s="2">
+      <c r="B360" s="25">
         <v>10</v>
       </c>
     </row>
     <row r="361" spans="1:2">
-      <c r="A361" s="20" t="s">
+      <c r="A361" s="26" t="s">
         <v>616</v>
       </c>
-      <c r="B361" s="2">
+      <c r="B361" s="25">
         <v>1000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
-      <c r="A362" s="20" t="s">
+      <c r="A362" s="26" t="s">
         <v>617</v>
       </c>
-      <c r="B362" s="37">
+      <c r="B362" s="50">
         <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:2">
-      <c r="A363" s="20" t="s">
+      <c r="A363" s="26" t="s">
         <v>618</v>
       </c>
-      <c r="B363" s="2">
+      <c r="B363" s="25">
         <v>1000</v>
       </c>
     </row>
     <row r="364" spans="1:2">
-      <c r="A364" s="20" t="s">
+      <c r="A364" s="26" t="s">
         <v>619</v>
       </c>
-      <c r="B364" s="2" t="s">
+      <c r="B364" s="25" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="20" t="s">
+      <c r="A365" s="26" t="s">
         <v>621</v>
       </c>
-      <c r="B365" s="2" t="s">
+      <c r="B365" s="25" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="20" t="s">
+      <c r="A366" s="26" t="s">
         <v>623</v>
       </c>
-      <c r="B366" s="2" t="s">
+      <c r="B366" s="25" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" s="20" t="s">
+      <c r="A367" s="26" t="s">
         <v>625</v>
       </c>
-      <c r="B367" s="2">
+      <c r="B367" s="25">
         <v>10000039</v>
       </c>
     </row>
     <row r="368" spans="1:2">
-      <c r="A368" s="20" t="s">
+      <c r="A368" s="26" t="s">
         <v>626</v>
       </c>
-      <c r="B368" s="20" t="s">
+      <c r="B368" s="27" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="369" spans="1:2">
-      <c r="A369" s="20" t="s">
+      <c r="A369" s="26" t="s">
         <v>628</v>
       </c>
-      <c r="B369" s="20" t="s">
+      <c r="B369" s="27" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="20" t="s">
+      <c r="A370" s="26" t="s">
         <v>630</v>
       </c>
       <c r="B370" s="7" t="s">
@@ -6571,7 +6839,7 @@
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="20" t="s">
+      <c r="A371" s="26" t="s">
         <v>632</v>
       </c>
       <c r="B371" s="7" t="s">
@@ -6579,7 +6847,7 @@
       </c>
     </row>
     <row r="372" spans="1:2">
-      <c r="A372" s="20" t="s">
+      <c r="A372" s="26" t="s">
         <v>634</v>
       </c>
       <c r="B372" s="7" t="s">
@@ -6587,7 +6855,7 @@
       </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="20" t="s">
+      <c r="A373" s="26" t="s">
         <v>636</v>
       </c>
       <c r="B373" s="7" t="s">
@@ -6595,7 +6863,7 @@
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="20" t="s">
+      <c r="A374" s="26" t="s">
         <v>638</v>
       </c>
       <c r="B374" s="7" t="s">
@@ -6603,7 +6871,7 @@
       </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="20" t="s">
+      <c r="A375" s="26" t="s">
         <v>640</v>
       </c>
       <c r="B375" s="7" t="s">
@@ -6611,7 +6879,7 @@
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="20" t="s">
+      <c r="A376" s="26" t="s">
         <v>642</v>
       </c>
       <c r="B376" s="7" t="s">
@@ -6619,7 +6887,7 @@
       </c>
     </row>
     <row r="377" spans="1:2">
-      <c r="A377" s="20" t="s">
+      <c r="A377" s="26" t="s">
         <v>643</v>
       </c>
       <c r="B377" s="7" t="s">
@@ -6627,7 +6895,7 @@
       </c>
     </row>
     <row r="378" spans="1:2">
-      <c r="A378" s="20" t="s">
+      <c r="A378" s="26" t="s">
         <v>645</v>
       </c>
       <c r="B378" s="7" t="s">
@@ -6635,7 +6903,7 @@
       </c>
     </row>
     <row r="379" spans="1:2">
-      <c r="A379" s="20" t="s">
+      <c r="A379" s="26" t="s">
         <v>647</v>
       </c>
       <c r="B379" s="7" t="s">
@@ -6643,7 +6911,7 @@
       </c>
     </row>
     <row r="380" spans="1:2">
-      <c r="A380" s="20" t="s">
+      <c r="A380" s="26" t="s">
         <v>649</v>
       </c>
       <c r="B380" s="7" t="s">
@@ -6651,7 +6919,7 @@
       </c>
     </row>
     <row r="381" spans="1:2">
-      <c r="A381" s="20" t="s">
+      <c r="A381" s="26" t="s">
         <v>650</v>
       </c>
       <c r="B381" s="7" t="s">
@@ -6659,7 +6927,7 @@
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="20" t="s">
+      <c r="A382" s="26" t="s">
         <v>652</v>
       </c>
       <c r="B382" s="7" t="s">
@@ -6667,7 +6935,7 @@
       </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="20" t="s">
+      <c r="A383" s="26" t="s">
         <v>654</v>
       </c>
       <c r="B383" s="7" t="s">
@@ -6675,7 +6943,7 @@
       </c>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="20" t="s">
+      <c r="A384" s="26" t="s">
         <v>656</v>
       </c>
       <c r="B384" s="7" t="s">
@@ -6683,7 +6951,7 @@
       </c>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="20" t="s">
+      <c r="A385" s="26" t="s">
         <v>658</v>
       </c>
       <c r="B385" s="7" t="s">
@@ -6691,7 +6959,7 @@
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="20" t="s">
+      <c r="A386" s="26" t="s">
         <v>660</v>
       </c>
       <c r="B386" s="7" t="s">
@@ -6699,7 +6967,7 @@
       </c>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="20" t="s">
+      <c r="A387" s="26" t="s">
         <v>662</v>
       </c>
       <c r="B387" s="7" t="s">
@@ -6707,7 +6975,7 @@
       </c>
     </row>
     <row r="388" spans="1:2">
-      <c r="A388" s="20" t="s">
+      <c r="A388" s="26" t="s">
         <v>664</v>
       </c>
       <c r="B388" s="7" t="s">
@@ -6715,7 +6983,7 @@
       </c>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" s="20" t="s">
+      <c r="A389" s="26" t="s">
         <v>666</v>
       </c>
       <c r="B389" s="7" t="s">
@@ -6723,7 +6991,7 @@
       </c>
     </row>
     <row r="390" spans="1:2">
-      <c r="A390" s="20" t="s">
+      <c r="A390" s="26" t="s">
         <v>668</v>
       </c>
       <c r="B390" s="7" t="s">
@@ -6731,7 +6999,7 @@
       </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="20" t="s">
+      <c r="A391" s="26" t="s">
         <v>670</v>
       </c>
       <c r="B391" s="7" t="s">
@@ -6739,7 +7007,7 @@
       </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="20" t="s">
+      <c r="A392" s="26" t="s">
         <v>672</v>
       </c>
       <c r="B392" s="7" t="s">
@@ -6747,7 +7015,7 @@
       </c>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393" s="20" t="s">
+      <c r="A393" s="26" t="s">
         <v>674</v>
       </c>
       <c r="B393" s="7" t="s">
@@ -6755,7 +7023,7 @@
       </c>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="20" t="s">
+      <c r="A394" s="26" t="s">
         <v>676</v>
       </c>
       <c r="B394" s="7" t="s">
@@ -6763,7 +7031,7 @@
       </c>
     </row>
     <row r="395" spans="1:2">
-      <c r="A395" s="20" t="s">
+      <c r="A395" s="26" t="s">
         <v>678</v>
       </c>
       <c r="B395" s="7" t="s">
@@ -6771,7 +7039,7 @@
       </c>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396" s="20" t="s">
+      <c r="A396" s="26" t="s">
         <v>680</v>
       </c>
       <c r="B396" s="7" t="s">
@@ -6779,7 +7047,7 @@
       </c>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="20" t="s">
+      <c r="A397" s="26" t="s">
         <v>682</v>
       </c>
       <c r="B397" s="7" t="s">
@@ -6787,7 +7055,7 @@
       </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="20" t="s">
+      <c r="A398" s="26" t="s">
         <v>684</v>
       </c>
       <c r="B398" s="7" t="s">
@@ -6795,7 +7063,7 @@
       </c>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="20" t="s">
+      <c r="A399" s="26" t="s">
         <v>686</v>
       </c>
       <c r="B399" s="7" t="s">
@@ -6803,7 +7071,7 @@
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="20" t="s">
+      <c r="A400" s="26" t="s">
         <v>688</v>
       </c>
       <c r="B400" s="7" t="s">
@@ -6811,7 +7079,7 @@
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="20" t="s">
+      <c r="A401" s="26" t="s">
         <v>690</v>
       </c>
       <c r="B401" s="7" t="s">
@@ -6819,7 +7087,7 @@
       </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="20" t="s">
+      <c r="A402" s="26" t="s">
         <v>692</v>
       </c>
       <c r="B402" s="7" t="s">
@@ -6827,7 +7095,7 @@
       </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="20" t="s">
+      <c r="A403" s="26" t="s">
         <v>694</v>
       </c>
       <c r="B403" s="7" t="s">
@@ -6835,7 +7103,7 @@
       </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="20" t="s">
+      <c r="A404" s="26" t="s">
         <v>696</v>
       </c>
       <c r="B404" s="7" t="s">
@@ -6843,7 +7111,7 @@
       </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="20" t="s">
+      <c r="A405" s="26" t="s">
         <v>698</v>
       </c>
       <c r="B405" s="7" t="s">
@@ -6851,7 +7119,7 @@
       </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="20" t="s">
+      <c r="A406" s="26" t="s">
         <v>700</v>
       </c>
       <c r="B406" s="7" t="s">
@@ -6859,7 +7127,7 @@
       </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="20" t="s">
+      <c r="A407" s="26" t="s">
         <v>702</v>
       </c>
       <c r="B407" s="7" t="s">
@@ -6867,7 +7135,7 @@
       </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="20" t="s">
+      <c r="A408" s="26" t="s">
         <v>704</v>
       </c>
       <c r="B408" s="7" t="s">
@@ -7008,6 +7276,294 @@
       </c>
       <c r="B425" s="7" t="s">
         <v>733</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="B426" s="14" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="B427" s="14" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="12" t="s">
+        <v>738</v>
+      </c>
+      <c r="B428" s="14" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="12" t="s">
+        <v>740</v>
+      </c>
+      <c r="B429" s="14" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="12" t="s">
+        <v>742</v>
+      </c>
+      <c r="B430" s="14" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="B431" s="14" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="12" t="s">
+        <v>746</v>
+      </c>
+      <c r="B432" s="14" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="12" t="s">
+        <v>748</v>
+      </c>
+      <c r="B433" s="14" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="12" t="s">
+        <v>750</v>
+      </c>
+      <c r="B434" s="14" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="B435" s="14" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B436" s="14" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="12" t="s">
+        <v>756</v>
+      </c>
+      <c r="B437" s="14" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="12" t="s">
+        <v>758</v>
+      </c>
+      <c r="B438" s="14" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="12" t="s">
+        <v>760</v>
+      </c>
+      <c r="B439" s="14" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="30" t="s">
+        <v>762</v>
+      </c>
+      <c r="B440" s="29" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="51" t="s">
+        <v>764</v>
+      </c>
+      <c r="B441" s="52" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="51" t="s">
+        <v>765</v>
+      </c>
+      <c r="B442" s="53" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="51" t="s">
+        <v>767</v>
+      </c>
+      <c r="B443" s="53" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="51" t="s">
+        <v>769</v>
+      </c>
+      <c r="B444" s="53" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="51" t="s">
+        <v>770</v>
+      </c>
+      <c r="B445" s="53" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="51" t="s">
+        <v>771</v>
+      </c>
+      <c r="B446" s="54" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="51" t="s">
+        <v>773</v>
+      </c>
+      <c r="B447" s="54" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="51" t="s">
+        <v>775</v>
+      </c>
+      <c r="B448" s="53" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="51" t="s">
+        <v>777</v>
+      </c>
+      <c r="B449" s="53" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="B450" s="55" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="51" t="s">
+        <v>561</v>
+      </c>
+      <c r="B451" s="55" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="B452" s="57" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="56" t="s">
+        <v>779</v>
+      </c>
+      <c r="B453" s="57" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="51" t="s">
+        <v>781</v>
+      </c>
+      <c r="B454" s="58" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="51" t="s">
+        <v>782</v>
+      </c>
+      <c r="B455" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="59" t="s">
+        <v>371</v>
+      </c>
+      <c r="B456" s="55" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="59" t="s">
+        <v>783</v>
+      </c>
+      <c r="B457" s="55" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="59" t="s">
+        <v>784</v>
+      </c>
+      <c r="B458" s="55" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="59" t="s">
+        <v>786</v>
+      </c>
+      <c r="B459" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="51" t="s">
+        <v>788</v>
+      </c>
+      <c r="B460" s="53" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="51" t="s">
+        <v>790</v>
+      </c>
+      <c r="B461" s="53" t="s">
+        <v>791</v>
       </c>
     </row>
   </sheetData>
@@ -7020,9 +7576,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.85454545454546" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.8518518518519" customWidth="1"/>
+    <col min="1" max="1" width="19.8545454545455" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7036,34 +7592,34 @@
     </row>
     <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>734</v>
+        <v>792</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>735</v>
+        <v>793</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>736</v>
+        <v>794</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>737</v>
+        <v>795</v>
       </c>
     </row>
     <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>738</v>
+        <v>796</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>739</v>
+        <v>797</v>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>740</v>
+        <v>798</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>741</v>
+        <v>799</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="832">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -2404,6 +2404,102 @@
   </si>
   <si>
     <t>GRL10/00429/24-25</t>
+  </si>
+  <si>
+    <t>SubcontractorName</t>
+  </si>
+  <si>
+    <t>ACT ON FINISHING (P) LTD</t>
+  </si>
+  <si>
+    <t>GeneralExpense</t>
+  </si>
+  <si>
+    <t>GENERAL EXPENSE</t>
+  </si>
+  <si>
+    <t>ScoItem</t>
+  </si>
+  <si>
+    <t>HK-FIFO-LOT-BATCH-SO-10001(FG)</t>
+  </si>
+  <si>
+    <t>PEELING</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>RawMaterialSco</t>
+  </si>
+  <si>
+    <t>StandardProd</t>
+  </si>
+  <si>
+    <t>Pro</t>
+  </si>
+  <si>
+    <t>PRC 0</t>
+  </si>
+  <si>
+    <t>SaleOrderNumber</t>
+  </si>
+  <si>
+    <t>SO100/00019/24-25</t>
+  </si>
+  <si>
+    <t>Orderreleases</t>
+  </si>
+  <si>
+    <t>Order Release</t>
+  </si>
+  <si>
+    <t>Inprogress</t>
+  </si>
+  <si>
+    <t>ComQty</t>
+  </si>
+  <si>
+    <t>Completion Quantity</t>
+  </si>
+  <si>
+    <t>NoDataFound</t>
+  </si>
+  <si>
+    <t>No data found</t>
+  </si>
+  <si>
+    <t>AllocatedValue</t>
+  </si>
+  <si>
+    <t>FirstDcNumber</t>
+  </si>
+  <si>
+    <t>DC10-2425-01357</t>
+  </si>
+  <si>
+    <t>FreePass</t>
+  </si>
+  <si>
+    <t>Free Pass</t>
+  </si>
+  <si>
+    <t>DcDetails</t>
+  </si>
+  <si>
+    <t>Select 1 row in the master region</t>
+  </si>
+  <si>
+    <t>FG-WH-KD</t>
+  </si>
+  <si>
+    <t>FG WH KD</t>
+  </si>
+  <si>
+    <t>OrderReleaseOption</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2714,7 +2810,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2762,18 +2858,6 @@
     <font>
       <sz val="10"/>
       <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3262,7 +3346,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -3279,139 +3363,141 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3433,9 +3519,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3488,9 +3571,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3529,29 +3609,28 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="51" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -3603,6 +3682,8 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
     <cellStyle name="Normal 2" xfId="49"/>
     <cellStyle name="Normal 3" xfId="50"/>
+    <cellStyle name="Normal 2 2" xfId="51"/>
+    <cellStyle name="Normal 2 3" xfId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3871,11 +3952,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B461"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B487"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="34.2909090909091" customWidth="1"/>
-    <col min="2" max="2" width="59.8545454545455" style="4" customWidth="1"/>
+    <col min="1" max="1" width="34.287037037037" customWidth="1"/>
+    <col min="2" max="2" width="59.8518518518519" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4402,7 +4483,7 @@
       <c r="A66" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="9" t="s">
         <v>126</v>
       </c>
     </row>
@@ -4410,7 +4491,7 @@
       <c r="A67" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="9" t="s">
         <v>128</v>
       </c>
     </row>
@@ -4418,7 +4499,7 @@
       <c r="A68" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="9" t="s">
         <v>130</v>
       </c>
     </row>
@@ -4426,7 +4507,7 @@
       <c r="A69" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="9">
         <v>2012</v>
       </c>
     </row>
@@ -4434,7 +4515,7 @@
       <c r="A70" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="9" t="s">
         <v>133</v>
       </c>
     </row>
@@ -4442,319 +4523,319 @@
       <c r="A71" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="9" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B73" s="9" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="9" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="9" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="9">
         <v>202425</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="9" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="9" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="12" t="s">
+      <c r="A80" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="12" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="13" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="12" t="s">
+      <c r="A83" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="12" t="s">
+      <c r="A84" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="13" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="12" t="s">
+      <c r="A85" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="13" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="12" t="s">
+      <c r="A86" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="12" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="15" t="s">
+      <c r="A88" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="15" t="s">
+      <c r="A89" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="16" t="s">
+      <c r="A90" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="15" t="s">
+      <c r="A91" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="12" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="15" t="s">
+      <c r="A92" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="12" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="15" t="s">
+      <c r="A93" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="15" t="s">
+      <c r="A94" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="12" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="15" t="s">
+      <c r="A95" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B95" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="15" t="s">
+      <c r="A96" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="12" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="15" t="s">
+      <c r="A97" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="12" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="15" t="s">
+      <c r="A98" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="12" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="15" t="s">
+      <c r="A99" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="17" t="s">
+      <c r="A100" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="B100" s="18" t="s">
+      <c r="B100" s="17" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="17" t="s">
+      <c r="A101" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="B101" s="19" t="s">
+      <c r="B101" s="18" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="17" t="s">
+      <c r="A102" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B102" s="18" t="s">
+      <c r="B102" s="17" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="17" t="s">
+      <c r="A103" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B103" s="18" t="s">
+      <c r="B103" s="17" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B104" s="19">
+      <c r="B104" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="20" t="s">
+      <c r="A105" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="B105" s="21" t="s">
+      <c r="B105" s="20" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="20" t="s">
+      <c r="A106" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="B106" s="22" t="s">
+      <c r="B106" s="21" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="20" t="s">
+      <c r="A107" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="B107" s="23">
+      <c r="B107" s="22">
         <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="20" t="s">
+      <c r="A108" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="B108" s="21" t="s">
+      <c r="B108" s="20" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="20" t="s">
+      <c r="A109" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="B109" s="24" t="s">
+      <c r="B109" s="23" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="20" t="s">
+      <c r="A110" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="B110" s="23">
+      <c r="B110" s="22">
         <v>100</v>
       </c>
     </row>
@@ -4762,47 +4843,47 @@
       <c r="A111" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B111" s="25" t="s">
+      <c r="B111" s="24" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="26" t="s">
+      <c r="A112" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="B112" s="27" t="s">
+      <c r="B112" s="26" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="26" t="s">
+      <c r="A113" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="B113" s="27" t="s">
+      <c r="B113" s="26" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="26" t="s">
+      <c r="A114" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="B114" s="25" t="s">
+      <c r="B114" s="24" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="B115" s="25" t="s">
+      <c r="B115" s="24" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="26" t="s">
+      <c r="A116" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="B116" s="25" t="s">
+      <c r="B116" s="24" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4810,7 +4891,7 @@
       <c r="A117" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B117" s="25" t="s">
+      <c r="B117" s="24" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4818,319 +4899,319 @@
       <c r="A118" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B118" s="25">
+      <c r="B118" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="28" t="s">
+      <c r="A119" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="B119" s="29" t="s">
+      <c r="B119" s="28" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="28" t="s">
+      <c r="A120" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="B120" s="29" t="s">
+      <c r="B120" s="28" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="28" t="s">
+      <c r="A121" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="B121" s="29" t="s">
+      <c r="B121" s="28" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="28" t="s">
+      <c r="A122" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="B122" s="29" t="s">
+      <c r="B122" s="28" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="28" t="s">
+      <c r="A123" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="B123" s="29" t="s">
+      <c r="B123" s="28" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="28" t="s">
+      <c r="A124" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="B124" s="29" t="s">
+      <c r="B124" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="28" t="s">
+      <c r="A125" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="B125" s="29" t="s">
+      <c r="B125" s="28" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="28" t="s">
+      <c r="A126" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="B126" s="29" t="s">
+      <c r="B126" s="28" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="28" t="s">
+      <c r="A127" s="27" t="s">
         <v>232</v>
       </c>
-      <c r="B127" s="29" t="s">
+      <c r="B127" s="28" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="28" t="s">
+      <c r="A128" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="B128" s="29" t="s">
+      <c r="B128" s="28" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="28" t="s">
+      <c r="A129" s="27" t="s">
         <v>236</v>
       </c>
-      <c r="B129" s="29" t="s">
+      <c r="B129" s="28" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="28" t="s">
+      <c r="A130" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="B130" s="29" t="s">
+      <c r="B130" s="28" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="28" t="s">
+      <c r="A131" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="B131" s="29" t="s">
+      <c r="B131" s="28" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="28" t="s">
+      <c r="A132" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="B132" s="29" t="s">
+      <c r="B132" s="28" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="28" t="s">
+      <c r="A133" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="B133" s="29" t="s">
+      <c r="B133" s="28" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="28" t="s">
+      <c r="A134" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="B134" s="29" t="s">
+      <c r="B134" s="28" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="28" t="s">
+      <c r="A135" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="B135" s="29" t="s">
+      <c r="B135" s="28" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="28" t="s">
+      <c r="A136" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="B136" s="29" t="s">
+      <c r="B136" s="28" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="28" t="s">
+      <c r="A137" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="B137" s="29" t="s">
+      <c r="B137" s="28" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="28" t="s">
+      <c r="A138" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="B138" s="29" t="s">
+      <c r="B138" s="28" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="28" t="s">
+      <c r="A139" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="B139" s="29" t="s">
+      <c r="B139" s="28" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="28" t="s">
+      <c r="A140" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="B140" s="29" t="s">
+      <c r="B140" s="28" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="28" t="s">
+      <c r="A141" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="B141" s="29" t="s">
+      <c r="B141" s="28" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="28" t="s">
+      <c r="A142" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="B142" s="29" t="s">
+      <c r="B142" s="28" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="28" t="s">
+      <c r="A143" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="B143" s="29" t="s">
+      <c r="B143" s="28" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="28" t="s">
+      <c r="A144" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="B144" s="29" t="s">
+      <c r="B144" s="28" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="28" t="s">
+      <c r="A145" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="B145" s="29" t="s">
+      <c r="B145" s="28" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="28" t="s">
+      <c r="A146" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="B146" s="29" t="s">
+      <c r="B146" s="28" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="28" t="s">
+      <c r="A147" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="B147" s="29" t="s">
+      <c r="B147" s="28" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="28" t="s">
+      <c r="A148" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="B148" s="29" t="s">
+      <c r="B148" s="28" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="28" t="s">
+      <c r="A149" s="27" t="s">
         <v>262</v>
       </c>
-      <c r="B149" s="29" t="s">
+      <c r="B149" s="28" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="28" t="s">
+      <c r="A150" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="B150" s="29" t="s">
+      <c r="B150" s="28" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="30" t="s">
+      <c r="A151" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="B151" s="29" t="s">
+      <c r="B151" s="28" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="30" t="s">
+      <c r="A152" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="B152" s="29" t="s">
+      <c r="B152" s="28" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="30" t="s">
+      <c r="A153" s="29" t="s">
         <v>268</v>
       </c>
-      <c r="B153" s="29" t="s">
+      <c r="B153" s="28" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="30" t="s">
+      <c r="A154" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="B154" s="29" t="s">
+      <c r="B154" s="28" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="30" t="s">
+      <c r="A155" s="29" t="s">
         <v>272</v>
       </c>
-      <c r="B155" s="29" t="s">
+      <c r="B155" s="28" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="30" t="s">
+      <c r="A156" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="B156" s="29" t="s">
+      <c r="B156" s="28" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="31" t="s">
+      <c r="A157" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="B157" s="32" t="s">
+      <c r="B157" s="31" t="s">
         <v>277</v>
       </c>
     </row>
@@ -5138,263 +5219,263 @@
       <c r="A158" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B158" s="25" t="s">
+      <c r="B158" s="24" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="12" t="s">
+      <c r="A159" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="B159" s="33" t="s">
+      <c r="B159" s="32" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="12" t="s">
+      <c r="A160" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B160" s="34" t="s">
+      <c r="B160" s="12" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="12" t="s">
+      <c r="A161" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="B161" s="14" t="s">
+      <c r="B161" s="13" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="12" t="s">
+      <c r="A162" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="B162" s="34" t="s">
+      <c r="B162" s="12" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="12" t="s">
+      <c r="A163" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B163" s="34" t="s">
+      <c r="B163" s="12" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="12" t="s">
+      <c r="A164" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="B164" s="14" t="s">
+      <c r="B164" s="13" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="12" t="s">
+      <c r="A165" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="B165" s="14" t="s">
+      <c r="B165" s="13" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="12" t="s">
+      <c r="A166" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B166" s="34" t="s">
+      <c r="B166" s="12" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="12" t="s">
+      <c r="A167" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="B167" s="34" t="s">
+      <c r="B167" s="12" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="12" t="s">
+      <c r="A168" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="B168" s="14" t="s">
+      <c r="B168" s="13" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="12" t="s">
+      <c r="A169" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="B169" s="14" t="s">
+      <c r="B169" s="13" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="12" t="s">
+      <c r="A170" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="B170" s="34" t="s">
+      <c r="B170" s="12" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="12" t="s">
+      <c r="A171" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="B171" s="34" t="s">
+      <c r="B171" s="12" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="12" t="s">
+      <c r="A172" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="B172" s="34" t="s">
+      <c r="B172" s="12" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="12" t="s">
+      <c r="A173" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="B173" s="34" t="s">
+      <c r="B173" s="12" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="12" t="s">
+      <c r="A174" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="B174" s="34" t="s">
+      <c r="B174" s="12" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="12" t="s">
+      <c r="A175" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="B175" s="34" t="s">
+      <c r="B175" s="12" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="12" t="s">
+      <c r="A176" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B176" s="34" t="s">
+      <c r="B176" s="12" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="12" t="s">
+      <c r="A177" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="B177" s="34" t="s">
+      <c r="B177" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="12" t="s">
+      <c r="A178" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="B178" s="34" t="s">
+      <c r="B178" s="12" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="12" t="s">
+      <c r="A179" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="B179" s="34" t="s">
+      <c r="B179" s="12" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="12" t="s">
+      <c r="A180" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="B180" s="34" t="s">
+      <c r="B180" s="12" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="12" t="s">
+      <c r="A181" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="B181" s="34" t="s">
+      <c r="B181" s="12" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="12" t="s">
+      <c r="A182" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="B182" s="34" t="s">
+      <c r="B182" s="12" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="12" t="s">
+      <c r="A183" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="B183" s="34" t="s">
+      <c r="B183" s="12" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="12" t="s">
+      <c r="A184" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="B184" s="34" t="s">
+      <c r="B184" s="12" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="12" t="s">
+      <c r="A185" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="B185" s="34" t="s">
+      <c r="B185" s="12" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="12" t="s">
+      <c r="A186" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="B186" s="14" t="s">
+      <c r="B186" s="13" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="12" t="s">
+      <c r="A187" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="B187" s="14" t="s">
+      <c r="B187" s="13" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="12" t="s">
+      <c r="A188" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="B188" s="34" t="s">
+      <c r="B188" s="12" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="12" t="s">
+      <c r="A189" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="B189" s="14" t="s">
+      <c r="B189" s="13" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="12" t="s">
+      <c r="A190" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="B190" s="34" t="s">
+      <c r="B190" s="12" t="s">
         <v>339</v>
       </c>
     </row>
@@ -5402,215 +5483,215 @@
       <c r="A191" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B191" s="35" t="s">
+      <c r="B191" s="33" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="36" t="s">
+      <c r="A192" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="B192" s="37" t="s">
+      <c r="B192" s="35" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="36" t="s">
+      <c r="A193" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="B193" s="38" t="s">
+      <c r="B193" s="36" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="36" t="s">
+      <c r="A194" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="B194" s="19">
+      <c r="B194" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="36" t="s">
+      <c r="A195" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="B195" s="37" t="s">
+      <c r="B195" s="35" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="36" t="s">
+      <c r="A196" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="B196" s="18" t="s">
+      <c r="B196" s="17" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="36" t="s">
+      <c r="A197" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="B197" s="19">
+      <c r="B197" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="36" t="s">
+      <c r="A198" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="B198" s="19" t="s">
+      <c r="B198" s="18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="36" t="s">
+      <c r="A199" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="B199" s="39" t="s">
+      <c r="B199" s="37" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="36" t="s">
+      <c r="A200" s="34" t="s">
         <v>346</v>
       </c>
-      <c r="B200" s="39" t="s">
+      <c r="B200" s="37" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="36" t="s">
+      <c r="A201" s="34" t="s">
         <v>348</v>
       </c>
-      <c r="B201" s="39" t="s">
+      <c r="B201" s="37" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="36" t="s">
+      <c r="A202" s="34" t="s">
         <v>350</v>
       </c>
-      <c r="B202" s="19">
+      <c r="B202" s="18">
         <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="36" t="s">
+      <c r="A203" s="34" t="s">
         <v>351</v>
       </c>
-      <c r="B203" s="19">
+      <c r="B203" s="18">
         <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="36" t="s">
+      <c r="A204" s="34" t="s">
         <v>352</v>
       </c>
-      <c r="B204" s="19" t="s">
+      <c r="B204" s="18" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="40" t="s">
+      <c r="A205" s="38" t="s">
         <v>354</v>
       </c>
-      <c r="B205" s="19">
+      <c r="B205" s="18">
         <v>150</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="40" t="s">
+      <c r="A206" s="38" t="s">
         <v>355</v>
       </c>
-      <c r="B206" s="19">
+      <c r="B206" s="18">
         <v>250</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="40" t="s">
+      <c r="A207" s="38" t="s">
         <v>356</v>
       </c>
-      <c r="B207" s="19" t="s">
+      <c r="B207" s="18" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="40" t="s">
+      <c r="A208" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="B208" s="19">
+      <c r="B208" s="18">
         <v>123562</v>
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="40" t="s">
+      <c r="A209" s="38" t="s">
         <v>359</v>
       </c>
-      <c r="B209" s="19">
+      <c r="B209" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="40" t="s">
+      <c r="A210" s="38" t="s">
         <v>360</v>
       </c>
-      <c r="B210" s="19">
+      <c r="B210" s="18">
         <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="40" t="s">
+      <c r="A211" s="38" t="s">
         <v>361</v>
       </c>
-      <c r="B211" s="19">
+      <c r="B211" s="18">
         <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="40" t="s">
+      <c r="A212" s="38" t="s">
         <v>362</v>
       </c>
-      <c r="B212" s="38" t="s">
+      <c r="B212" s="36" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="40" t="s">
+      <c r="A213" s="38" t="s">
         <v>364</v>
       </c>
-      <c r="B213" s="18" t="s">
+      <c r="B213" s="17" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="40" t="s">
+      <c r="A214" s="38" t="s">
         <v>366</v>
       </c>
-      <c r="B214" s="38" t="s">
+      <c r="B214" s="36" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="40" t="s">
+      <c r="A215" s="38" t="s">
         <v>368</v>
       </c>
-      <c r="B215" s="19">
+      <c r="B215" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="40" t="s">
+      <c r="A216" s="38" t="s">
         <v>369</v>
       </c>
-      <c r="B216" s="19">
+      <c r="B216" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="40" t="s">
+      <c r="A217" s="38" t="s">
         <v>370</v>
       </c>
-      <c r="B217" s="38" t="s">
+      <c r="B217" s="36" t="s">
         <v>71</v>
       </c>
     </row>
@@ -5618,63 +5699,63 @@
       <c r="A218" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B218" s="25" t="s">
+      <c r="B218" s="24" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="31" t="s">
+      <c r="A219" s="30" t="s">
         <v>371</v>
       </c>
-      <c r="B219" s="41" t="s">
+      <c r="B219" s="39" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="31" t="s">
+      <c r="A220" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="B220" s="25" t="s">
+      <c r="B220" s="24" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="31" t="s">
+      <c r="A221" s="30" t="s">
         <v>374</v>
       </c>
-      <c r="B221" s="25" t="s">
+      <c r="B221" s="24" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="42" t="s">
+      <c r="A222" s="40" t="s">
         <v>376</v>
       </c>
-      <c r="B222" s="41" t="s">
+      <c r="B222" s="39" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="42" t="s">
+      <c r="A223" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="B223" s="41" t="s">
+      <c r="B223" s="39" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="43" t="s">
+      <c r="A224" s="41" t="s">
         <v>380</v>
       </c>
-      <c r="B224" s="44" t="s">
+      <c r="B224" s="42" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="42" t="s">
+      <c r="A225" s="40" t="s">
         <v>382</v>
       </c>
-      <c r="B225" s="45" t="s">
+      <c r="B225" s="43" t="s">
         <v>383</v>
       </c>
     </row>
@@ -5866,7 +5947,7 @@
       <c r="A249" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B249" s="46" t="s">
+      <c r="B249" s="44" t="s">
         <v>419</v>
       </c>
     </row>
@@ -6095,10 +6176,10 @@
       </c>
     </row>
     <row r="278" spans="1:2">
-      <c r="A278" s="26" t="s">
+      <c r="A278" s="25" t="s">
         <v>467</v>
       </c>
-      <c r="B278" s="25" t="s">
+      <c r="B278" s="24" t="s">
         <v>468</v>
       </c>
     </row>
@@ -6106,7 +6187,7 @@
       <c r="A279" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B279" s="25" t="s">
+      <c r="B279" s="24" t="s">
         <v>59</v>
       </c>
     </row>
@@ -6146,12 +6227,12 @@
       <c r="A284" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="B284" s="47" t="s">
+      <c r="B284" s="45" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="285" spans="1:2">
-      <c r="A285" s="48" t="s">
+      <c r="A285" s="46" t="s">
         <v>479</v>
       </c>
       <c r="B285" s="7" t="s">
@@ -6159,7 +6240,7 @@
       </c>
     </row>
     <row r="286" spans="1:2">
-      <c r="A286" s="48" t="s">
+      <c r="A286" s="46" t="s">
         <v>481</v>
       </c>
       <c r="B286" s="7" t="s">
@@ -6167,7 +6248,7 @@
       </c>
     </row>
     <row r="287" spans="1:2">
-      <c r="A287" s="48" t="s">
+      <c r="A287" s="46" t="s">
         <v>483</v>
       </c>
       <c r="B287" s="7" t="s">
@@ -6175,7 +6256,7 @@
       </c>
     </row>
     <row r="288" spans="1:2">
-      <c r="A288" s="48" t="s">
+      <c r="A288" s="46" t="s">
         <v>485</v>
       </c>
       <c r="B288" s="7" t="s">
@@ -6183,7 +6264,7 @@
       </c>
     </row>
     <row r="289" spans="1:2">
-      <c r="A289" s="48" t="s">
+      <c r="A289" s="46" t="s">
         <v>487</v>
       </c>
       <c r="B289" s="7" t="s">
@@ -6191,7 +6272,7 @@
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="48" t="s">
+      <c r="A290" s="46" t="s">
         <v>489</v>
       </c>
       <c r="B290" s="7" t="s">
@@ -6199,7 +6280,7 @@
       </c>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="48" t="s">
+      <c r="A291" s="46" t="s">
         <v>491</v>
       </c>
       <c r="B291" s="7" t="s">
@@ -6426,7 +6507,7 @@
       <c r="A319" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B319" s="49" t="s">
+      <c r="B319" s="47" t="s">
         <v>543</v>
       </c>
     </row>
@@ -6559,58 +6640,58 @@
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="30" t="s">
+      <c r="A336" s="29" t="s">
         <v>573</v>
       </c>
-      <c r="B336" s="29" t="s">
+      <c r="B336" s="28" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="337" spans="1:2">
-      <c r="A337" s="30" t="s">
+      <c r="A337" s="29" t="s">
         <v>575</v>
       </c>
-      <c r="B337" s="29" t="s">
+      <c r="B337" s="28" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="338" spans="1:2">
-      <c r="A338" s="30" t="s">
+      <c r="A338" s="29" t="s">
         <v>576</v>
       </c>
-      <c r="B338" s="29" t="s">
+      <c r="B338" s="28" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="339" spans="1:2">
-      <c r="A339" s="30" t="s">
+      <c r="A339" s="29" t="s">
         <v>577</v>
       </c>
-      <c r="B339" s="29" t="s">
+      <c r="B339" s="28" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="340" spans="1:2">
-      <c r="A340" s="30" t="s">
+      <c r="A340" s="29" t="s">
         <v>578</v>
       </c>
-      <c r="B340" s="29" t="s">
+      <c r="B340" s="28" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="341" spans="1:2">
-      <c r="A341" s="30" t="s">
+      <c r="A341" s="29" t="s">
         <v>580</v>
       </c>
-      <c r="B341" s="29" t="s">
+      <c r="B341" s="28" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="342" spans="1:2">
-      <c r="A342" s="30" t="s">
+      <c r="A342" s="29" t="s">
         <v>581</v>
       </c>
-      <c r="B342" s="29" t="s">
+      <c r="B342" s="28" t="s">
         <v>579</v>
       </c>
     </row>
@@ -6722,7 +6803,7 @@
       <c r="A356" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B356" s="25" t="s">
+      <c r="B356" s="24" t="s">
         <v>608</v>
       </c>
     </row>
@@ -6735,103 +6816,103 @@
       </c>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="26" t="s">
+      <c r="A358" s="25" t="s">
         <v>611</v>
       </c>
-      <c r="B358" s="27" t="s">
+      <c r="B358" s="26" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="359" spans="1:2">
-      <c r="A359" s="26" t="s">
+      <c r="A359" s="25" t="s">
         <v>613</v>
       </c>
-      <c r="B359" s="27" t="s">
+      <c r="B359" s="26" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="360" spans="1:2">
-      <c r="A360" s="26" t="s">
+      <c r="A360" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="B360" s="25">
+      <c r="B360" s="24">
         <v>10</v>
       </c>
     </row>
     <row r="361" spans="1:2">
-      <c r="A361" s="26" t="s">
+      <c r="A361" s="25" t="s">
         <v>616</v>
       </c>
-      <c r="B361" s="25">
+      <c r="B361" s="24">
         <v>1000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
-      <c r="A362" s="26" t="s">
+      <c r="A362" s="25" t="s">
         <v>617</v>
       </c>
-      <c r="B362" s="50">
+      <c r="B362" s="48">
         <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:2">
-      <c r="A363" s="26" t="s">
+      <c r="A363" s="25" t="s">
         <v>618</v>
       </c>
-      <c r="B363" s="25">
+      <c r="B363" s="24">
         <v>1000</v>
       </c>
     </row>
     <row r="364" spans="1:2">
-      <c r="A364" s="26" t="s">
+      <c r="A364" s="25" t="s">
         <v>619</v>
       </c>
-      <c r="B364" s="25" t="s">
+      <c r="B364" s="24" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="26" t="s">
+      <c r="A365" s="25" t="s">
         <v>621</v>
       </c>
-      <c r="B365" s="25" t="s">
+      <c r="B365" s="24" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="26" t="s">
+      <c r="A366" s="25" t="s">
         <v>623</v>
       </c>
-      <c r="B366" s="25" t="s">
+      <c r="B366" s="24" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" s="26" t="s">
+      <c r="A367" s="25" t="s">
         <v>625</v>
       </c>
-      <c r="B367" s="25">
+      <c r="B367" s="24">
         <v>10000039</v>
       </c>
     </row>
     <row r="368" spans="1:2">
-      <c r="A368" s="26" t="s">
+      <c r="A368" s="25" t="s">
         <v>626</v>
       </c>
-      <c r="B368" s="27" t="s">
+      <c r="B368" s="26" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="369" spans="1:2">
-      <c r="A369" s="26" t="s">
+      <c r="A369" s="25" t="s">
         <v>628</v>
       </c>
-      <c r="B369" s="27" t="s">
+      <c r="B369" s="26" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="26" t="s">
+      <c r="A370" s="25" t="s">
         <v>630</v>
       </c>
       <c r="B370" s="7" t="s">
@@ -6839,7 +6920,7 @@
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="26" t="s">
+      <c r="A371" s="25" t="s">
         <v>632</v>
       </c>
       <c r="B371" s="7" t="s">
@@ -6847,7 +6928,7 @@
       </c>
     </row>
     <row r="372" spans="1:2">
-      <c r="A372" s="26" t="s">
+      <c r="A372" s="25" t="s">
         <v>634</v>
       </c>
       <c r="B372" s="7" t="s">
@@ -6855,7 +6936,7 @@
       </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="26" t="s">
+      <c r="A373" s="25" t="s">
         <v>636</v>
       </c>
       <c r="B373" s="7" t="s">
@@ -6863,7 +6944,7 @@
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="26" t="s">
+      <c r="A374" s="25" t="s">
         <v>638</v>
       </c>
       <c r="B374" s="7" t="s">
@@ -6871,7 +6952,7 @@
       </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="26" t="s">
+      <c r="A375" s="25" t="s">
         <v>640</v>
       </c>
       <c r="B375" s="7" t="s">
@@ -6879,7 +6960,7 @@
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="26" t="s">
+      <c r="A376" s="25" t="s">
         <v>642</v>
       </c>
       <c r="B376" s="7" t="s">
@@ -6887,7 +6968,7 @@
       </c>
     </row>
     <row r="377" spans="1:2">
-      <c r="A377" s="26" t="s">
+      <c r="A377" s="25" t="s">
         <v>643</v>
       </c>
       <c r="B377" s="7" t="s">
@@ -6895,7 +6976,7 @@
       </c>
     </row>
     <row r="378" spans="1:2">
-      <c r="A378" s="26" t="s">
+      <c r="A378" s="25" t="s">
         <v>645</v>
       </c>
       <c r="B378" s="7" t="s">
@@ -6903,7 +6984,7 @@
       </c>
     </row>
     <row r="379" spans="1:2">
-      <c r="A379" s="26" t="s">
+      <c r="A379" s="25" t="s">
         <v>647</v>
       </c>
       <c r="B379" s="7" t="s">
@@ -6911,7 +6992,7 @@
       </c>
     </row>
     <row r="380" spans="1:2">
-      <c r="A380" s="26" t="s">
+      <c r="A380" s="25" t="s">
         <v>649</v>
       </c>
       <c r="B380" s="7" t="s">
@@ -6919,7 +7000,7 @@
       </c>
     </row>
     <row r="381" spans="1:2">
-      <c r="A381" s="26" t="s">
+      <c r="A381" s="25" t="s">
         <v>650</v>
       </c>
       <c r="B381" s="7" t="s">
@@ -6927,7 +7008,7 @@
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="26" t="s">
+      <c r="A382" s="25" t="s">
         <v>652</v>
       </c>
       <c r="B382" s="7" t="s">
@@ -6935,7 +7016,7 @@
       </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="26" t="s">
+      <c r="A383" s="25" t="s">
         <v>654</v>
       </c>
       <c r="B383" s="7" t="s">
@@ -6943,7 +7024,7 @@
       </c>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="26" t="s">
+      <c r="A384" s="25" t="s">
         <v>656</v>
       </c>
       <c r="B384" s="7" t="s">
@@ -6951,7 +7032,7 @@
       </c>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="26" t="s">
+      <c r="A385" s="25" t="s">
         <v>658</v>
       </c>
       <c r="B385" s="7" t="s">
@@ -6959,7 +7040,7 @@
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="26" t="s">
+      <c r="A386" s="25" t="s">
         <v>660</v>
       </c>
       <c r="B386" s="7" t="s">
@@ -6967,7 +7048,7 @@
       </c>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="26" t="s">
+      <c r="A387" s="25" t="s">
         <v>662</v>
       </c>
       <c r="B387" s="7" t="s">
@@ -6975,7 +7056,7 @@
       </c>
     </row>
     <row r="388" spans="1:2">
-      <c r="A388" s="26" t="s">
+      <c r="A388" s="25" t="s">
         <v>664</v>
       </c>
       <c r="B388" s="7" t="s">
@@ -6983,7 +7064,7 @@
       </c>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" s="26" t="s">
+      <c r="A389" s="25" t="s">
         <v>666</v>
       </c>
       <c r="B389" s="7" t="s">
@@ -6991,7 +7072,7 @@
       </c>
     </row>
     <row r="390" spans="1:2">
-      <c r="A390" s="26" t="s">
+      <c r="A390" s="25" t="s">
         <v>668</v>
       </c>
       <c r="B390" s="7" t="s">
@@ -6999,7 +7080,7 @@
       </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="26" t="s">
+      <c r="A391" s="25" t="s">
         <v>670</v>
       </c>
       <c r="B391" s="7" t="s">
@@ -7007,7 +7088,7 @@
       </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="26" t="s">
+      <c r="A392" s="25" t="s">
         <v>672</v>
       </c>
       <c r="B392" s="7" t="s">
@@ -7015,7 +7096,7 @@
       </c>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393" s="26" t="s">
+      <c r="A393" s="25" t="s">
         <v>674</v>
       </c>
       <c r="B393" s="7" t="s">
@@ -7023,7 +7104,7 @@
       </c>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="26" t="s">
+      <c r="A394" s="25" t="s">
         <v>676</v>
       </c>
       <c r="B394" s="7" t="s">
@@ -7031,7 +7112,7 @@
       </c>
     </row>
     <row r="395" spans="1:2">
-      <c r="A395" s="26" t="s">
+      <c r="A395" s="25" t="s">
         <v>678</v>
       </c>
       <c r="B395" s="7" t="s">
@@ -7039,7 +7120,7 @@
       </c>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396" s="26" t="s">
+      <c r="A396" s="25" t="s">
         <v>680</v>
       </c>
       <c r="B396" s="7" t="s">
@@ -7047,7 +7128,7 @@
       </c>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="26" t="s">
+      <c r="A397" s="25" t="s">
         <v>682</v>
       </c>
       <c r="B397" s="7" t="s">
@@ -7055,7 +7136,7 @@
       </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="26" t="s">
+      <c r="A398" s="25" t="s">
         <v>684</v>
       </c>
       <c r="B398" s="7" t="s">
@@ -7063,7 +7144,7 @@
       </c>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="26" t="s">
+      <c r="A399" s="25" t="s">
         <v>686</v>
       </c>
       <c r="B399" s="7" t="s">
@@ -7071,7 +7152,7 @@
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="26" t="s">
+      <c r="A400" s="25" t="s">
         <v>688</v>
       </c>
       <c r="B400" s="7" t="s">
@@ -7079,7 +7160,7 @@
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="26" t="s">
+      <c r="A401" s="25" t="s">
         <v>690</v>
       </c>
       <c r="B401" s="7" t="s">
@@ -7087,7 +7168,7 @@
       </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="26" t="s">
+      <c r="A402" s="25" t="s">
         <v>692</v>
       </c>
       <c r="B402" s="7" t="s">
@@ -7095,7 +7176,7 @@
       </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="26" t="s">
+      <c r="A403" s="25" t="s">
         <v>694</v>
       </c>
       <c r="B403" s="7" t="s">
@@ -7103,7 +7184,7 @@
       </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="26" t="s">
+      <c r="A404" s="25" t="s">
         <v>696</v>
       </c>
       <c r="B404" s="7" t="s">
@@ -7111,7 +7192,7 @@
       </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="26" t="s">
+      <c r="A405" s="25" t="s">
         <v>698</v>
       </c>
       <c r="B405" s="7" t="s">
@@ -7119,7 +7200,7 @@
       </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="26" t="s">
+      <c r="A406" s="25" t="s">
         <v>700</v>
       </c>
       <c r="B406" s="7" t="s">
@@ -7127,7 +7208,7 @@
       </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="26" t="s">
+      <c r="A407" s="25" t="s">
         <v>702</v>
       </c>
       <c r="B407" s="7" t="s">
@@ -7135,7 +7216,7 @@
       </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="26" t="s">
+      <c r="A408" s="25" t="s">
         <v>704</v>
       </c>
       <c r="B408" s="7" t="s">
@@ -7279,291 +7360,499 @@
       </c>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="12" t="s">
+      <c r="A426" s="11" t="s">
         <v>734</v>
       </c>
-      <c r="B426" s="14" t="s">
+      <c r="B426" s="13" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="427" spans="1:2">
-      <c r="A427" s="12" t="s">
+      <c r="A427" s="11" t="s">
         <v>736</v>
       </c>
-      <c r="B427" s="14" t="s">
+      <c r="B427" s="13" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="12" t="s">
+      <c r="A428" s="11" t="s">
         <v>738</v>
       </c>
-      <c r="B428" s="14" t="s">
+      <c r="B428" s="13" t="s">
         <v>739</v>
       </c>
     </row>
     <row r="429" spans="1:2">
-      <c r="A429" s="12" t="s">
+      <c r="A429" s="11" t="s">
         <v>740</v>
       </c>
-      <c r="B429" s="14" t="s">
+      <c r="B429" s="13" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="430" spans="1:2">
-      <c r="A430" s="12" t="s">
+      <c r="A430" s="11" t="s">
         <v>742</v>
       </c>
-      <c r="B430" s="14" t="s">
+      <c r="B430" s="13" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="12" t="s">
+      <c r="A431" s="11" t="s">
         <v>744</v>
       </c>
-      <c r="B431" s="14" t="s">
+      <c r="B431" s="13" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="432" spans="1:2">
-      <c r="A432" s="12" t="s">
+      <c r="A432" s="11" t="s">
         <v>746</v>
       </c>
-      <c r="B432" s="14" t="s">
+      <c r="B432" s="13" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="433" spans="1:2">
-      <c r="A433" s="12" t="s">
+      <c r="A433" s="11" t="s">
         <v>748</v>
       </c>
-      <c r="B433" s="14" t="s">
+      <c r="B433" s="13" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="434" spans="1:2">
-      <c r="A434" s="12" t="s">
+      <c r="A434" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="B434" s="14" t="s">
+      <c r="B434" s="13" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="435" spans="1:2">
-      <c r="A435" s="12" t="s">
+      <c r="A435" s="11" t="s">
         <v>752</v>
       </c>
-      <c r="B435" s="14" t="s">
+      <c r="B435" s="13" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="436" spans="1:2">
-      <c r="A436" s="12" t="s">
+      <c r="A436" s="11" t="s">
         <v>754</v>
       </c>
-      <c r="B436" s="14" t="s">
+      <c r="B436" s="13" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="437" spans="1:2">
-      <c r="A437" s="12" t="s">
+      <c r="A437" s="11" t="s">
         <v>756</v>
       </c>
-      <c r="B437" s="14" t="s">
+      <c r="B437" s="13" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="438" spans="1:2">
-      <c r="A438" s="12" t="s">
+      <c r="A438" s="11" t="s">
         <v>758</v>
       </c>
-      <c r="B438" s="14" t="s">
+      <c r="B438" s="13" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="439" spans="1:2">
-      <c r="A439" s="12" t="s">
+      <c r="A439" s="11" t="s">
         <v>760</v>
       </c>
-      <c r="B439" s="14" t="s">
+      <c r="B439" s="13" t="s">
         <v>761</v>
       </c>
     </row>
     <row r="440" spans="1:2">
-      <c r="A440" s="30" t="s">
+      <c r="A440" s="29" t="s">
         <v>762</v>
       </c>
-      <c r="B440" s="29" t="s">
+      <c r="B440" s="28" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="441" spans="1:2">
-      <c r="A441" s="51" t="s">
+      <c r="A441" s="49" t="s">
         <v>764</v>
       </c>
-      <c r="B441" s="52" t="s">
+      <c r="B441" s="50" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="442" spans="1:2">
-      <c r="A442" s="51" t="s">
+      <c r="A442" s="49" t="s">
         <v>765</v>
       </c>
-      <c r="B442" s="53" t="s">
+      <c r="B442" s="50" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="443" spans="1:2">
-      <c r="A443" s="51" t="s">
+      <c r="A443" s="49" t="s">
         <v>767</v>
       </c>
-      <c r="B443" s="53" t="s">
+      <c r="B443" s="50" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="444" spans="1:2">
-      <c r="A444" s="51" t="s">
+      <c r="A444" s="49" t="s">
         <v>769</v>
       </c>
-      <c r="B444" s="53" t="s">
+      <c r="B444" s="50" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="445" spans="1:2">
-      <c r="A445" s="51" t="s">
+      <c r="A445" s="49" t="s">
         <v>770</v>
       </c>
-      <c r="B445" s="53" t="s">
+      <c r="B445" s="50" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="446" spans="1:2">
-      <c r="A446" s="51" t="s">
+      <c r="A446" s="49" t="s">
         <v>771</v>
       </c>
-      <c r="B446" s="54" t="s">
+      <c r="B446" s="51" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="447" spans="1:2">
-      <c r="A447" s="51" t="s">
+      <c r="A447" s="49" t="s">
         <v>773</v>
       </c>
-      <c r="B447" s="54" t="s">
+      <c r="B447" s="51" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="448" spans="1:2">
-      <c r="A448" s="51" t="s">
+      <c r="A448" s="49" t="s">
         <v>775</v>
       </c>
-      <c r="B448" s="53" t="s">
+      <c r="B448" s="50" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="449" spans="1:2">
-      <c r="A449" s="51" t="s">
+      <c r="A449" s="49" t="s">
         <v>777</v>
       </c>
-      <c r="B449" s="53" t="s">
+      <c r="B449" s="50" t="s">
         <v>778</v>
       </c>
     </row>
     <row r="450" spans="1:2">
-      <c r="A450" s="51" t="s">
+      <c r="A450" s="49" t="s">
         <v>564</v>
       </c>
-      <c r="B450" s="55" t="s">
+      <c r="B450" s="51" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="451" spans="1:2">
-      <c r="A451" s="51" t="s">
+      <c r="A451" s="49" t="s">
         <v>561</v>
       </c>
-      <c r="B451" s="55" t="s">
+      <c r="B451" s="51" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="452" spans="1:2">
-      <c r="A452" s="56" t="s">
+      <c r="A452" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="B452" s="57" t="s">
+      <c r="B452" s="53" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="453" spans="1:2">
-      <c r="A453" s="56" t="s">
+      <c r="A453" s="52" t="s">
         <v>779</v>
       </c>
-      <c r="B453" s="57" t="s">
+      <c r="B453" s="53" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="454" spans="1:2">
-      <c r="A454" s="51" t="s">
+      <c r="A454" s="49" t="s">
         <v>781</v>
       </c>
-      <c r="B454" s="58" t="s">
+      <c r="B454" s="54" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="455" spans="1:2">
-      <c r="A455" s="51" t="s">
+      <c r="A455" s="49" t="s">
         <v>782</v>
       </c>
-      <c r="B455" s="58" t="s">
+      <c r="B455" s="54" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="456" spans="1:2">
-      <c r="A456" s="59" t="s">
+      <c r="A456" s="49" t="s">
         <v>371</v>
       </c>
-      <c r="B456" s="55" t="s">
+      <c r="B456" s="51" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="457" spans="1:2">
-      <c r="A457" s="59" t="s">
+      <c r="A457" s="49" t="s">
         <v>783</v>
       </c>
-      <c r="B457" s="55" t="s">
+      <c r="B457" s="51" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="458" spans="1:2">
-      <c r="A458" s="59" t="s">
+      <c r="A458" s="49" t="s">
         <v>784</v>
       </c>
-      <c r="B458" s="55" t="s">
+      <c r="B458" s="51" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="459" spans="1:2">
-      <c r="A459" s="59" t="s">
+      <c r="A459" s="49" t="s">
         <v>786</v>
       </c>
-      <c r="B459" s="52" t="s">
+      <c r="B459" s="50" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="460" spans="1:2">
-      <c r="A460" s="51" t="s">
+      <c r="A460" s="49" t="s">
         <v>788</v>
       </c>
-      <c r="B460" s="53" t="s">
+      <c r="B460" s="50" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="461" spans="1:2">
-      <c r="A461" s="51" t="s">
+      <c r="A461" s="49" t="s">
         <v>790</v>
       </c>
-      <c r="B461" s="53" t="s">
+      <c r="B461" s="50" t="s">
         <v>791</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="55" t="s">
+        <v>359</v>
+      </c>
+      <c r="B462" s="55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="55" t="s">
+        <v>360</v>
+      </c>
+      <c r="B463" s="55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="55" t="s">
+        <v>361</v>
+      </c>
+      <c r="B464" s="55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="56" t="s">
+        <v>354</v>
+      </c>
+      <c r="B465" s="56">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="56" t="s">
+        <v>355</v>
+      </c>
+      <c r="B466" s="56">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B467" s="7" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="B468" s="7" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B469" s="7" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B470" s="7" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B471" s="7" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B472" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="B473" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="B474" s="7" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B475" s="7" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="B476" s="7" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B477" s="7" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B478" s="7" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B479" s="44" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B480" s="7" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B481" s="7" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="B482" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B483" s="7" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B484" s="7" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B485" s="7" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="57" t="s">
+        <v>821</v>
+      </c>
+      <c r="B486" s="58" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="57" t="s">
+        <v>823</v>
+      </c>
+      <c r="B487" s="58" t="s">
+        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -7576,9 +7865,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.85454545454546" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.8545454545455" customWidth="1"/>
+    <col min="1" max="1" width="19.8518518518519" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7592,34 +7881,34 @@
     </row>
     <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>792</v>
+        <v>824</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>793</v>
+        <v>825</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>794</v>
+        <v>826</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>795</v>
+        <v>827</v>
       </c>
     </row>
     <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>796</v>
+        <v>828</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>797</v>
+        <v>829</v>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>798</v>
+        <v>830</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>799</v>
+        <v>831</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="835">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -2427,10 +2427,13 @@
     <t>PEELING</t>
   </si>
   <si>
+    <t>SourcePEELING</t>
+  </si>
+  <si>
     <t>00</t>
   </si>
   <si>
-    <t>Target</t>
+    <t>TargetPEELING</t>
   </si>
   <si>
     <t>RawMaterialSco</t>
@@ -2500,6 +2503,12 @@
   </si>
   <si>
     <t>OrderReleaseOption</t>
+  </si>
+  <si>
+    <t>SourceSLICING</t>
+  </si>
+  <si>
+    <t>TargetSLICING</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -3497,7 +3506,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3625,10 +3634,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="51" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3952,7 +3957,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B487"/>
+  <dimension ref="A1:B489"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="34.287037037037" customWidth="1"/>
@@ -7721,15 +7726,15 @@
     </row>
     <row r="471" spans="1:2">
       <c r="A471" s="2" t="s">
-        <v>484</v>
+        <v>799</v>
       </c>
       <c r="B471" s="7" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B472" s="7" t="s">
         <v>229</v>
@@ -7737,7 +7742,7 @@
     </row>
     <row r="473" spans="1:2">
       <c r="A473" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B473" s="7" t="s">
         <v>281</v>
@@ -7745,7 +7750,7 @@
     </row>
     <row r="474" spans="1:2">
       <c r="A474" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B474" s="7" t="s">
         <v>757</v>
@@ -7753,10 +7758,10 @@
     </row>
     <row r="475" spans="1:2">
       <c r="A475" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B475" s="7" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -7769,47 +7774,47 @@
     </row>
     <row r="477" spans="1:2">
       <c r="A477" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B477" s="7" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B479" s="44" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B481" s="7" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B482" s="7" t="s">
         <v>229</v>
@@ -7817,42 +7822,58 @@
     </row>
     <row r="483" spans="1:2">
       <c r="A483" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B483" s="7" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B484" s="7" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B485" s="7" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="486" spans="1:2">
-      <c r="A486" s="57" t="s">
-        <v>821</v>
-      </c>
-      <c r="B486" s="58" t="s">
+      <c r="A486" s="2" t="s">
         <v>822</v>
       </c>
+      <c r="B486" s="7" t="s">
+        <v>823</v>
+      </c>
     </row>
     <row r="487" spans="1:2">
-      <c r="A487" s="57" t="s">
-        <v>823</v>
-      </c>
-      <c r="B487" s="58" t="s">
-        <v>808</v>
+      <c r="A487" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B487" s="7" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B488" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B489" s="7" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -7881,34 +7902,34 @@
     </row>
     <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="834">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -2407,9 +2407,6 @@
   </si>
   <si>
     <t>SubcontractorName</t>
-  </si>
-  <si>
-    <t>ACT ON FINISHING (P) LTD</t>
   </si>
   <si>
     <t>GeneralExpense</t>
@@ -7697,44 +7694,44 @@
         <v>792</v>
       </c>
       <c r="B467" s="7" t="s">
-        <v>793</v>
+        <v>357</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B468" s="7" t="s">
         <v>794</v>
-      </c>
-      <c r="B468" s="7" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B469" s="7" t="s">
         <v>796</v>
-      </c>
-      <c r="B469" s="7" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B470" s="7" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B471" s="7" t="s">
         <v>799</v>
-      </c>
-      <c r="B471" s="7" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B472" s="7" t="s">
         <v>229</v>
@@ -7742,7 +7739,7 @@
     </row>
     <row r="473" spans="1:2">
       <c r="A473" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B473" s="7" t="s">
         <v>281</v>
@@ -7750,7 +7747,7 @@
     </row>
     <row r="474" spans="1:2">
       <c r="A474" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B474" s="7" t="s">
         <v>757</v>
@@ -7758,10 +7755,10 @@
     </row>
     <row r="475" spans="1:2">
       <c r="A475" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B475" s="7" t="s">
         <v>804</v>
-      </c>
-      <c r="B475" s="7" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -7774,47 +7771,47 @@
     </row>
     <row r="477" spans="1:2">
       <c r="A477" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B477" s="7" t="s">
         <v>806</v>
-      </c>
-      <c r="B477" s="7" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B478" s="7" t="s">
         <v>808</v>
-      </c>
-      <c r="B478" s="7" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B479" s="44" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B480" s="7" t="s">
         <v>811</v>
-      </c>
-      <c r="B480" s="7" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B481" s="7" t="s">
         <v>813</v>
-      </c>
-      <c r="B481" s="7" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B482" s="7" t="s">
         <v>229</v>
@@ -7822,47 +7819,47 @@
     </row>
     <row r="483" spans="1:2">
       <c r="A483" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B483" s="7" t="s">
         <v>816</v>
-      </c>
-      <c r="B483" s="7" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B484" s="7" t="s">
         <v>818</v>
-      </c>
-      <c r="B484" s="7" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B485" s="7" t="s">
         <v>820</v>
-      </c>
-      <c r="B485" s="7" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B486" s="7" t="s">
         <v>822</v>
-      </c>
-      <c r="B486" s="7" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B487" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B488" s="7" t="s">
         <v>229</v>
@@ -7870,7 +7867,7 @@
     </row>
     <row r="489" spans="1:2">
       <c r="A489" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B489" s="7" t="s">
         <v>148</v>
@@ -7902,34 +7899,34 @@
     </row>
     <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>827</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>829</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>831</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>833</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="23040" windowHeight="9120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="876">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -2506,6 +2506,126 @@
   </si>
   <si>
     <t>TargetSLICING</t>
+  </si>
+  <si>
+    <t>OSOANO</t>
+  </si>
+  <si>
+    <t>${OSOANO}</t>
+  </si>
+  <si>
+    <t>OSOADbLocutionColumnName</t>
+  </si>
+  <si>
+    <t>loc id</t>
+  </si>
+  <si>
+    <t>OSOADbUnitColumnName</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>OSOADbDocNoColumnName</t>
+  </si>
+  <si>
+    <t>SRCAHD_CONTR_NO</t>
+  </si>
+  <si>
+    <t>OSOADbAmdNumberColumnName</t>
+  </si>
+  <si>
+    <t>Amd. No.</t>
+  </si>
+  <si>
+    <t>OSOADbCustomerIdColumnName</t>
+  </si>
+  <si>
+    <t>customer id</t>
+  </si>
+  <si>
+    <t>OSOADbCustomerNameColumnName</t>
+  </si>
+  <si>
+    <t>customer name</t>
+  </si>
+  <si>
+    <t>OSOADbItemID</t>
+  </si>
+  <si>
+    <t>item id</t>
+  </si>
+  <si>
+    <t>OSOADbItemDescripition</t>
+  </si>
+  <si>
+    <t>item descripition</t>
+  </si>
+  <si>
+    <t>OSOADbItemUom</t>
+  </si>
+  <si>
+    <t>uom</t>
+  </si>
+  <si>
+    <t>OSOADbRevisieValue</t>
+  </si>
+  <si>
+    <t>new_price</t>
+  </si>
+  <si>
+    <t>OSOADbTaxPercent</t>
+  </si>
+  <si>
+    <t>Tax Percent</t>
+  </si>
+  <si>
+    <t>OSOADbIgstAmount</t>
+  </si>
+  <si>
+    <t>IGST</t>
+  </si>
+  <si>
+    <t>OSOADbSgstAmount</t>
+  </si>
+  <si>
+    <t>SGST</t>
+  </si>
+  <si>
+    <t>OSOADbCgstAmount</t>
+  </si>
+  <si>
+    <t>CGST</t>
+  </si>
+  <si>
+    <t>OSOADbUTgstAmount</t>
+  </si>
+  <si>
+    <t>UTGST</t>
+  </si>
+  <si>
+    <t>LOCATION100</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>PL100</t>
+  </si>
+  <si>
+    <t>CUSTOMER_ID</t>
+  </si>
+  <si>
+    <t>ITEMPL</t>
+  </si>
+  <si>
+    <t>SK0006</t>
+  </si>
+  <si>
+    <t>Sales_Value</t>
+  </si>
+  <si>
+    <t>109</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2804,6 +2924,24 @@
        AND soh_order_no = soq_order_no
        AND soh_bu = 'TVSA'
        AND soh_order_no = '${SONO}'</t>
+  </si>
+  <si>
+    <t>StockQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT stock_qty_hand,
+      (SELECT stcost_cost
+  FROM stock_costs
+ WHERE stcost_bu = 'TVSA'
+   AND stcost_store_id = stock_store_id
+   AND stcost_prod_id = stock_prod_id
+   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
+  FROM stocks
+ WHERE stock_bu = 'TVSA'
+   AND stock_store_id = '${SONO}'
+   AND stock_prod_id = 'TVS-RM-KDK-10'
+   AND stock_prod_rev = '0'
+</t>
   </si>
 </sst>
 </file>
@@ -3503,12 +3641,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3631,6 +3772,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="51" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3954,18 +4099,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B489"/>
+  <dimension ref="A1:B510"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="34.287037037037" customWidth="1"/>
-    <col min="2" max="2" width="59.8518518518519" style="4" customWidth="1"/>
+    <col min="2" max="2" width="59.8518518518519" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3973,7 +4118,7 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3981,7 +4126,7 @@
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3989,7 +4134,7 @@
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3997,7 +4142,7 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4005,7 +4150,7 @@
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4013,7 +4158,7 @@
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4021,7 +4166,7 @@
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4029,7 +4174,7 @@
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4037,7 +4182,7 @@
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4045,7 +4190,7 @@
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4053,7 +4198,7 @@
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>23</v>
       </c>
     </row>
@@ -4061,7 +4206,7 @@
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>25</v>
       </c>
     </row>
@@ -4069,7 +4214,7 @@
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4077,7 +4222,7 @@
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <v>5</v>
       </c>
     </row>
@@ -4085,7 +4230,7 @@
       <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <v>150</v>
       </c>
     </row>
@@ -4093,7 +4238,7 @@
       <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4101,7 +4246,7 @@
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4109,7 +4254,7 @@
       <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4117,7 +4262,7 @@
       <c r="A20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4125,7 +4270,7 @@
       <c r="A21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4133,7 +4278,7 @@
       <c r="A22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4141,7 +4286,7 @@
       <c r="A23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4149,7 +4294,7 @@
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="8" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4157,7 +4302,7 @@
       <c r="A25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="8" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4165,7 +4310,7 @@
       <c r="A26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="8" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4173,7 +4318,7 @@
       <c r="A27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="8" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4181,7 +4326,7 @@
       <c r="A28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="8" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4189,7 +4334,7 @@
       <c r="A29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4197,7 +4342,7 @@
       <c r="A30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="8" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4205,7 +4350,7 @@
       <c r="A31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="8" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4213,7 +4358,7 @@
       <c r="A32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="8" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4221,7 +4366,7 @@
       <c r="A33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="8" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4229,7 +4374,7 @@
       <c r="A34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4237,7 +4382,7 @@
       <c r="A35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="8" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4245,7 +4390,7 @@
       <c r="A36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="8" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4253,7 +4398,7 @@
       <c r="A37" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="8" t="s">
         <v>71</v>
       </c>
     </row>
@@ -4261,7 +4406,7 @@
       <c r="A38" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="8" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4269,7 +4414,7 @@
       <c r="A39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="8" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4277,7 +4422,7 @@
       <c r="A40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="8" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4285,7 +4430,7 @@
       <c r="A41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="8" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4293,7 +4438,7 @@
       <c r="A42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="8" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4301,7 +4446,7 @@
       <c r="A43" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="8" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4309,7 +4454,7 @@
       <c r="A44" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="8" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4317,7 +4462,7 @@
       <c r="A45" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="8" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4325,7 +4470,7 @@
       <c r="A46" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="8" t="s">
         <v>89</v>
       </c>
     </row>
@@ -4333,7 +4478,7 @@
       <c r="A47" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="8" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4341,7 +4486,7 @@
       <c r="A48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="8" t="s">
         <v>93</v>
       </c>
     </row>
@@ -4349,7 +4494,7 @@
       <c r="A49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="8">
         <v>5</v>
       </c>
     </row>
@@ -4357,7 +4502,7 @@
       <c r="A50" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="8" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4365,7 +4510,7 @@
       <c r="A51" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="8" t="s">
         <v>97</v>
       </c>
     </row>
@@ -4373,471 +4518,471 @@
       <c r="A52" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="8" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="10" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="10" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="10" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="10" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="10" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="10" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="10" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="10" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="10">
         <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="10" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="10" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="10" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="10">
         <v>2012</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="10" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="10" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="10" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="10" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="10">
         <v>202425</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="10" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="10" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="10" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="13" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B81" s="12" t="s">
+      <c r="B81" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="14" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="14" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="B85" s="14" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="13" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="14" t="s">
+      <c r="A89" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="15" t="s">
+      <c r="A90" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="14" t="s">
+      <c r="A91" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="B91" s="13" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="14" t="s">
+      <c r="A92" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="13" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="14" t="s">
+      <c r="A93" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="13" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="14" t="s">
+      <c r="A94" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="13" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="14" t="s">
+      <c r="A95" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="B95" s="13" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="14" t="s">
+      <c r="A96" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="13" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="14" t="s">
+      <c r="A97" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B97" s="12" t="s">
+      <c r="B97" s="13" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="14" t="s">
+      <c r="A98" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="13" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="14" t="s">
+      <c r="A99" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="13" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="16" t="s">
+      <c r="A100" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B100" s="17" t="s">
+      <c r="B100" s="18" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="16" t="s">
+      <c r="A101" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B101" s="18" t="s">
+      <c r="B101" s="19" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="16" t="s">
+      <c r="A102" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="B102" s="17" t="s">
+      <c r="B102" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B103" s="17" t="s">
+      <c r="B103" s="18" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="16" t="s">
+      <c r="A104" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="B104" s="18">
+      <c r="B104" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="19" t="s">
+      <c r="A105" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="B105" s="20" t="s">
+      <c r="B105" s="21" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="19" t="s">
+      <c r="A106" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="B106" s="21" t="s">
+      <c r="B106" s="22" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="19" t="s">
+      <c r="A107" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="B107" s="22">
+      <c r="B107" s="23">
         <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="19" t="s">
+      <c r="A108" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="B108" s="20" t="s">
+      <c r="B108" s="21" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="19" t="s">
+      <c r="A109" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="B109" s="23" t="s">
+      <c r="B109" s="24" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="19" t="s">
+      <c r="A110" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="B110" s="22">
+      <c r="B110" s="23">
         <v>100</v>
       </c>
     </row>
@@ -4845,47 +4990,47 @@
       <c r="A111" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B111" s="24" t="s">
+      <c r="B111" s="25" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="25" t="s">
+      <c r="A112" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="B112" s="26" t="s">
+      <c r="B112" s="27" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="25" t="s">
+      <c r="A113" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="B113" s="26" t="s">
+      <c r="B113" s="27" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="25" t="s">
+      <c r="A114" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="B114" s="24" t="s">
+      <c r="B114" s="25" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="25" t="s">
+      <c r="A115" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="B115" s="24" t="s">
+      <c r="B115" s="25" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="25" t="s">
+      <c r="A116" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="B116" s="24" t="s">
+      <c r="B116" s="25" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4893,7 +5038,7 @@
       <c r="A117" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B117" s="24" t="s">
+      <c r="B117" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4901,319 +5046,319 @@
       <c r="A118" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B118" s="24">
+      <c r="B118" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="27" t="s">
+      <c r="A119" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="B119" s="28" t="s">
+      <c r="B119" s="29" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="27" t="s">
+      <c r="A120" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="B120" s="28" t="s">
+      <c r="B120" s="29" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="27" t="s">
+      <c r="A121" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="B121" s="28" t="s">
+      <c r="B121" s="29" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="27" t="s">
+      <c r="A122" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="B122" s="28" t="s">
+      <c r="B122" s="29" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="27" t="s">
+      <c r="A123" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="B123" s="28" t="s">
+      <c r="B123" s="29" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="27" t="s">
+      <c r="A124" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="B124" s="28" t="s">
+      <c r="B124" s="29" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="27" t="s">
+      <c r="A125" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="B125" s="28" t="s">
+      <c r="B125" s="29" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="27" t="s">
+      <c r="A126" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="B126" s="28" t="s">
+      <c r="B126" s="29" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="27" t="s">
+      <c r="A127" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="B127" s="28" t="s">
+      <c r="B127" s="29" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="27" t="s">
+      <c r="A128" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="B128" s="28" t="s">
+      <c r="B128" s="29" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="27" t="s">
+      <c r="A129" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="B129" s="28" t="s">
+      <c r="B129" s="29" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="27" t="s">
+      <c r="A130" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="B130" s="28" t="s">
+      <c r="B130" s="29" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="27" t="s">
+      <c r="A131" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="B131" s="28" t="s">
+      <c r="B131" s="29" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="27" t="s">
+      <c r="A132" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="B132" s="28" t="s">
+      <c r="B132" s="29" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="27" t="s">
+      <c r="A133" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="B133" s="28" t="s">
+      <c r="B133" s="29" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="27" t="s">
+      <c r="A134" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="B134" s="28" t="s">
+      <c r="B134" s="29" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="27" t="s">
+      <c r="A135" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="B135" s="28" t="s">
+      <c r="B135" s="29" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="27" t="s">
+      <c r="A136" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="B136" s="28" t="s">
+      <c r="B136" s="29" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="27" t="s">
+      <c r="A137" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="B137" s="28" t="s">
+      <c r="B137" s="29" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="27" t="s">
+      <c r="A138" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="B138" s="28" t="s">
+      <c r="B138" s="29" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="27" t="s">
+      <c r="A139" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="B139" s="28" t="s">
+      <c r="B139" s="29" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="27" t="s">
+      <c r="A140" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="B140" s="28" t="s">
+      <c r="B140" s="29" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="27" t="s">
+      <c r="A141" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="B141" s="28" t="s">
+      <c r="B141" s="29" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="27" t="s">
+      <c r="A142" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="B142" s="28" t="s">
+      <c r="B142" s="29" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="27" t="s">
+      <c r="A143" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="B143" s="28" t="s">
+      <c r="B143" s="29" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="27" t="s">
+      <c r="A144" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="B144" s="28" t="s">
+      <c r="B144" s="29" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="27" t="s">
+      <c r="A145" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="B145" s="28" t="s">
+      <c r="B145" s="29" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="27" t="s">
+      <c r="A146" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="B146" s="28" t="s">
+      <c r="B146" s="29" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="27" t="s">
+      <c r="A147" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="B147" s="28" t="s">
+      <c r="B147" s="29" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="27" t="s">
+      <c r="A148" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="B148" s="28" t="s">
+      <c r="B148" s="29" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="27" t="s">
+      <c r="A149" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="B149" s="28" t="s">
+      <c r="B149" s="29" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="27" t="s">
+      <c r="A150" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="B150" s="28" t="s">
+      <c r="B150" s="29" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="29" t="s">
+      <c r="A151" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="B151" s="28" t="s">
+      <c r="B151" s="29" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="29" t="s">
+      <c r="A152" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="B152" s="28" t="s">
+      <c r="B152" s="29" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="29" t="s">
+      <c r="A153" s="30" t="s">
         <v>268</v>
       </c>
-      <c r="B153" s="28" t="s">
+      <c r="B153" s="29" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="29" t="s">
+      <c r="A154" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="B154" s="28" t="s">
+      <c r="B154" s="29" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="29" t="s">
+      <c r="A155" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="B155" s="28" t="s">
+      <c r="B155" s="29" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="29" t="s">
+      <c r="A156" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="B156" s="28" t="s">
+      <c r="B156" s="29" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="30" t="s">
+      <c r="A157" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="B157" s="31" t="s">
+      <c r="B157" s="32" t="s">
         <v>277</v>
       </c>
     </row>
@@ -5221,263 +5366,263 @@
       <c r="A158" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B158" s="24" t="s">
+      <c r="B158" s="25" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="11" t="s">
+      <c r="A159" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="B159" s="32" t="s">
+      <c r="B159" s="33" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="11" t="s">
+      <c r="A160" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="B160" s="12" t="s">
+      <c r="B160" s="13" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="11" t="s">
+      <c r="A161" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="B161" s="13" t="s">
+      <c r="B161" s="14" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="11" t="s">
+      <c r="A162" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="B162" s="12" t="s">
+      <c r="B162" s="13" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="11" t="s">
+      <c r="A163" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="B163" s="12" t="s">
+      <c r="B163" s="13" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="11" t="s">
+      <c r="A164" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="B164" s="13" t="s">
+      <c r="B164" s="14" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="11" t="s">
+      <c r="A165" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="B165" s="13" t="s">
+      <c r="B165" s="14" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="11" t="s">
+      <c r="A166" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="B166" s="12" t="s">
+      <c r="B166" s="13" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="11" t="s">
+      <c r="A167" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="B167" s="12" t="s">
+      <c r="B167" s="13" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="11" t="s">
+      <c r="A168" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="B168" s="13" t="s">
+      <c r="B168" s="14" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="11" t="s">
+      <c r="A169" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="B169" s="13" t="s">
+      <c r="B169" s="14" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="11" t="s">
+      <c r="A170" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="B170" s="12" t="s">
+      <c r="B170" s="13" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="11" t="s">
+      <c r="A171" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B171" s="12" t="s">
+      <c r="B171" s="13" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="11" t="s">
+      <c r="A172" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="B172" s="12" t="s">
+      <c r="B172" s="13" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="11" t="s">
+      <c r="A173" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="B173" s="12" t="s">
+      <c r="B173" s="13" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="11" t="s">
+      <c r="A174" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="B174" s="12" t="s">
+      <c r="B174" s="13" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="11" t="s">
+      <c r="A175" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="B175" s="12" t="s">
+      <c r="B175" s="13" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="11" t="s">
+      <c r="A176" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="B176" s="12" t="s">
+      <c r="B176" s="13" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="11" t="s">
+      <c r="A177" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="B177" s="12" t="s">
+      <c r="B177" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="11" t="s">
+      <c r="A178" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="B178" s="12" t="s">
+      <c r="B178" s="13" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="11" t="s">
+      <c r="A179" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="B179" s="12" t="s">
+      <c r="B179" s="13" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="11" t="s">
+      <c r="A180" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="B180" s="12" t="s">
+      <c r="B180" s="13" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="11" t="s">
+      <c r="A181" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="B181" s="12" t="s">
+      <c r="B181" s="13" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="11" t="s">
+      <c r="A182" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="B182" s="12" t="s">
+      <c r="B182" s="13" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="11" t="s">
+      <c r="A183" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="B183" s="12" t="s">
+      <c r="B183" s="13" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="11" t="s">
+      <c r="A184" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="B184" s="12" t="s">
+      <c r="B184" s="13" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="11" t="s">
+      <c r="A185" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B185" s="12" t="s">
+      <c r="B185" s="13" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="11" t="s">
+      <c r="A186" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="B186" s="13" t="s">
+      <c r="B186" s="14" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="11" t="s">
+      <c r="A187" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B187" s="13" t="s">
+      <c r="B187" s="14" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="11" t="s">
+      <c r="A188" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="B188" s="12" t="s">
+      <c r="B188" s="13" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="11" t="s">
+      <c r="A189" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="B189" s="13" t="s">
+      <c r="B189" s="14" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="11" t="s">
+      <c r="A190" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="B190" s="12" t="s">
+      <c r="B190" s="13" t="s">
         <v>339</v>
       </c>
     </row>
@@ -5485,215 +5630,215 @@
       <c r="A191" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B191" s="33" t="s">
+      <c r="B191" s="34" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="34" t="s">
+      <c r="A192" s="35" t="s">
         <v>193</v>
       </c>
-      <c r="B192" s="35" t="s">
+      <c r="B192" s="36" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="34" t="s">
+      <c r="A193" s="35" t="s">
         <v>195</v>
       </c>
-      <c r="B193" s="36" t="s">
+      <c r="B193" s="37" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="34" t="s">
+      <c r="A194" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="B194" s="18">
+      <c r="B194" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="34" t="s">
+      <c r="A195" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="B195" s="35" t="s">
+      <c r="B195" s="36" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="34" t="s">
+      <c r="A196" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="B196" s="17" t="s">
+      <c r="B196" s="18" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="34" t="s">
+      <c r="A197" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="B197" s="18">
+      <c r="B197" s="19">
         <v>100</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="34" t="s">
+      <c r="A198" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="B198" s="18" t="s">
+      <c r="B198" s="19" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="34" t="s">
+      <c r="A199" s="35" t="s">
         <v>344</v>
       </c>
-      <c r="B199" s="37" t="s">
+      <c r="B199" s="38" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="34" t="s">
+      <c r="A200" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="B200" s="37" t="s">
+      <c r="B200" s="38" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="34" t="s">
+      <c r="A201" s="35" t="s">
         <v>348</v>
       </c>
-      <c r="B201" s="37" t="s">
+      <c r="B201" s="38" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="34" t="s">
+      <c r="A202" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="B202" s="18">
+      <c r="B202" s="19">
         <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="34" t="s">
+      <c r="A203" s="35" t="s">
         <v>351</v>
       </c>
-      <c r="B203" s="18">
+      <c r="B203" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="34" t="s">
+      <c r="A204" s="35" t="s">
         <v>352</v>
       </c>
-      <c r="B204" s="18" t="s">
+      <c r="B204" s="19" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="38" t="s">
+      <c r="A205" s="39" t="s">
         <v>354</v>
       </c>
-      <c r="B205" s="18">
+      <c r="B205" s="19">
         <v>150</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="38" t="s">
+      <c r="A206" s="39" t="s">
         <v>355</v>
       </c>
-      <c r="B206" s="18">
+      <c r="B206" s="19">
         <v>250</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="38" t="s">
+      <c r="A207" s="39" t="s">
         <v>356</v>
       </c>
-      <c r="B207" s="18" t="s">
+      <c r="B207" s="19" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="38" t="s">
+      <c r="A208" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="B208" s="18">
+      <c r="B208" s="19">
         <v>123562</v>
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="38" t="s">
+      <c r="A209" s="39" t="s">
         <v>359</v>
       </c>
-      <c r="B209" s="18">
+      <c r="B209" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="38" t="s">
+      <c r="A210" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="B210" s="18">
+      <c r="B210" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="38" t="s">
+      <c r="A211" s="39" t="s">
         <v>361</v>
       </c>
-      <c r="B211" s="18">
+      <c r="B211" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="38" t="s">
+      <c r="A212" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="B212" s="36" t="s">
+      <c r="B212" s="37" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="38" t="s">
+      <c r="A213" s="39" t="s">
         <v>364</v>
       </c>
-      <c r="B213" s="17" t="s">
+      <c r="B213" s="18" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="38" t="s">
+      <c r="A214" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="B214" s="36" t="s">
+      <c r="B214" s="37" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="38" t="s">
+      <c r="A215" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="B215" s="18">
+      <c r="B215" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="38" t="s">
+      <c r="A216" s="39" t="s">
         <v>369</v>
       </c>
-      <c r="B216" s="18">
+      <c r="B216" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="38" t="s">
+      <c r="A217" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="B217" s="36" t="s">
+      <c r="B217" s="37" t="s">
         <v>71</v>
       </c>
     </row>
@@ -5701,63 +5846,63 @@
       <c r="A218" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B218" s="24" t="s">
+      <c r="B218" s="25" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="30" t="s">
+      <c r="A219" s="31" t="s">
         <v>371</v>
       </c>
-      <c r="B219" s="39" t="s">
+      <c r="B219" s="40" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="30" t="s">
+      <c r="A220" s="31" t="s">
         <v>372</v>
       </c>
-      <c r="B220" s="24" t="s">
+      <c r="B220" s="25" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="30" t="s">
+      <c r="A221" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="B221" s="24" t="s">
+      <c r="B221" s="25" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="40" t="s">
+      <c r="A222" s="41" t="s">
         <v>376</v>
       </c>
-      <c r="B222" s="39" t="s">
+      <c r="B222" s="40" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="40" t="s">
+      <c r="A223" s="41" t="s">
         <v>378</v>
       </c>
-      <c r="B223" s="39" t="s">
+      <c r="B223" s="40" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="41" t="s">
+      <c r="A224" s="42" t="s">
         <v>380</v>
       </c>
-      <c r="B224" s="42" t="s">
+      <c r="B224" s="43" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="40" t="s">
+      <c r="A225" s="41" t="s">
         <v>382</v>
       </c>
-      <c r="B225" s="43" t="s">
+      <c r="B225" s="44" t="s">
         <v>383</v>
       </c>
     </row>
@@ -5765,7 +5910,7 @@
       <c r="A226" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B226" s="8" t="s">
         <v>385</v>
       </c>
     </row>
@@ -5773,7 +5918,7 @@
       <c r="A227" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B227" s="7" t="s">
+      <c r="B227" s="8" t="s">
         <v>387</v>
       </c>
     </row>
@@ -5781,7 +5926,7 @@
       <c r="A228" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B228" s="7" t="s">
+      <c r="B228" s="8" t="s">
         <v>389</v>
       </c>
     </row>
@@ -5789,7 +5934,7 @@
       <c r="A229" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B229" s="7" t="s">
+      <c r="B229" s="8" t="s">
         <v>391</v>
       </c>
     </row>
@@ -5797,7 +5942,7 @@
       <c r="A230" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B230" s="7" t="s">
+      <c r="B230" s="8" t="s">
         <v>154</v>
       </c>
     </row>
@@ -5805,7 +5950,7 @@
       <c r="A231" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B231" s="7" t="s">
+      <c r="B231" s="8" t="s">
         <v>393</v>
       </c>
     </row>
@@ -5813,7 +5958,7 @@
       <c r="A232" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B232" s="7" t="s">
+      <c r="B232" s="8" t="s">
         <v>210</v>
       </c>
     </row>
@@ -5821,7 +5966,7 @@
       <c r="A233" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B233" s="7" t="s">
+      <c r="B233" s="8" t="s">
         <v>212</v>
       </c>
     </row>
@@ -5829,7 +5974,7 @@
       <c r="A234" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B234" s="7" t="s">
+      <c r="B234" s="8" t="s">
         <v>214</v>
       </c>
     </row>
@@ -5837,7 +5982,7 @@
       <c r="A235" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B235" s="7" t="s">
+      <c r="B235" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5845,7 +5990,7 @@
       <c r="A236" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B236" s="7" t="s">
+      <c r="B236" s="8" t="s">
         <v>395</v>
       </c>
     </row>
@@ -5853,7 +5998,7 @@
       <c r="A237" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B237" s="7" t="s">
+      <c r="B237" s="8" t="s">
         <v>397</v>
       </c>
     </row>
@@ -5861,7 +6006,7 @@
       <c r="A238" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B238" s="7" t="s">
+      <c r="B238" s="8" t="s">
         <v>399</v>
       </c>
     </row>
@@ -5869,7 +6014,7 @@
       <c r="A239" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B239" s="7" t="s">
+      <c r="B239" s="8" t="s">
         <v>401</v>
       </c>
     </row>
@@ -5877,7 +6022,7 @@
       <c r="A240" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B240" s="7" t="s">
+      <c r="B240" s="8" t="s">
         <v>403</v>
       </c>
     </row>
@@ -5885,7 +6030,7 @@
       <c r="A241" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B241" s="7" t="s">
+      <c r="B241" s="8" t="s">
         <v>405</v>
       </c>
     </row>
@@ -5893,7 +6038,7 @@
       <c r="A242" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B242" s="7" t="s">
+      <c r="B242" s="8" t="s">
         <v>407</v>
       </c>
     </row>
@@ -5901,7 +6046,7 @@
       <c r="A243" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B243" s="7" t="s">
+      <c r="B243" s="8" t="s">
         <v>405</v>
       </c>
     </row>
@@ -5909,7 +6054,7 @@
       <c r="A244" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B244" s="7" t="s">
+      <c r="B244" s="8" t="s">
         <v>410</v>
       </c>
     </row>
@@ -5917,7 +6062,7 @@
       <c r="A245" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B245" s="7" t="s">
+      <c r="B245" s="8" t="s">
         <v>412</v>
       </c>
     </row>
@@ -5925,7 +6070,7 @@
       <c r="A246" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B246" s="7" t="s">
+      <c r="B246" s="8" t="s">
         <v>414</v>
       </c>
     </row>
@@ -5933,7 +6078,7 @@
       <c r="A247" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B247" s="7" t="s">
+      <c r="B247" s="8" t="s">
         <v>235</v>
       </c>
     </row>
@@ -5941,7 +6086,7 @@
       <c r="A248" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B248" s="7" t="s">
+      <c r="B248" s="8" t="s">
         <v>417</v>
       </c>
     </row>
@@ -5949,7 +6094,7 @@
       <c r="A249" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B249" s="44" t="s">
+      <c r="B249" s="45" t="s">
         <v>419</v>
       </c>
     </row>
@@ -5957,7 +6102,7 @@
       <c r="A250" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="B250" s="7" t="s">
+      <c r="B250" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5965,7 +6110,7 @@
       <c r="A251" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="B251" s="7" t="s">
+      <c r="B251" s="8" t="s">
         <v>422</v>
       </c>
     </row>
@@ -5973,7 +6118,7 @@
       <c r="A252" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B252" s="7" t="s">
+      <c r="B252" s="8" t="s">
         <v>222</v>
       </c>
     </row>
@@ -5981,7 +6126,7 @@
       <c r="A253" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B253" s="7" t="s">
+      <c r="B253" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -5989,7 +6134,7 @@
       <c r="A254" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B254" s="7" t="s">
+      <c r="B254" s="8" t="s">
         <v>426</v>
       </c>
     </row>
@@ -5997,7 +6142,7 @@
       <c r="A255" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B255" s="7" t="s">
+      <c r="B255" s="8" t="s">
         <v>226</v>
       </c>
     </row>
@@ -6005,7 +6150,7 @@
       <c r="A256" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B256" s="7" t="s">
+      <c r="B256" s="8" t="s">
         <v>429</v>
       </c>
     </row>
@@ -6013,7 +6158,7 @@
       <c r="A257" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B257" s="7" t="s">
+      <c r="B257" s="8" t="s">
         <v>431</v>
       </c>
     </row>
@@ -6021,7 +6166,7 @@
       <c r="A258" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B258" s="7" t="s">
+      <c r="B258" s="8" t="s">
         <v>391</v>
       </c>
     </row>
@@ -6029,7 +6174,7 @@
       <c r="A259" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="B259" s="7" t="s">
+      <c r="B259" s="8" t="s">
         <v>434</v>
       </c>
     </row>
@@ -6037,7 +6182,7 @@
       <c r="A260" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B260" s="7" t="s">
+      <c r="B260" s="8" t="s">
         <v>436</v>
       </c>
     </row>
@@ -6045,7 +6190,7 @@
       <c r="A261" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B261" s="7" t="s">
+      <c r="B261" s="8" t="s">
         <v>330</v>
       </c>
     </row>
@@ -6053,7 +6198,7 @@
       <c r="A262" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="B262" s="7" t="s">
+      <c r="B262" s="8" t="s">
         <v>439</v>
       </c>
     </row>
@@ -6061,7 +6206,7 @@
       <c r="A263" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="B263" s="7" t="s">
+      <c r="B263" s="8" t="s">
         <v>441</v>
       </c>
     </row>
@@ -6069,7 +6214,7 @@
       <c r="A264" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="B264" s="7" t="s">
+      <c r="B264" s="8" t="s">
         <v>443</v>
       </c>
     </row>
@@ -6077,7 +6222,7 @@
       <c r="A265" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B265" s="7" t="s">
+      <c r="B265" s="8" t="s">
         <v>445</v>
       </c>
     </row>
@@ -6085,7 +6230,7 @@
       <c r="A266" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B266" s="7" t="s">
+      <c r="B266" s="8" t="s">
         <v>447</v>
       </c>
     </row>
@@ -6093,7 +6238,7 @@
       <c r="A267" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B267" s="7" t="s">
+      <c r="B267" s="8" t="s">
         <v>330</v>
       </c>
     </row>
@@ -6101,7 +6246,7 @@
       <c r="A268" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B268" s="7" t="s">
+      <c r="B268" s="8" t="s">
         <v>450</v>
       </c>
     </row>
@@ -6109,7 +6254,7 @@
       <c r="A269" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B269" s="7" t="s">
+      <c r="B269" s="8" t="s">
         <v>452</v>
       </c>
     </row>
@@ -6117,7 +6262,7 @@
       <c r="A270" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B270" s="7" t="s">
+      <c r="B270" s="8" t="s">
         <v>454</v>
       </c>
     </row>
@@ -6125,7 +6270,7 @@
       <c r="A271" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B271" s="7" t="s">
+      <c r="B271" s="8" t="s">
         <v>456</v>
       </c>
     </row>
@@ -6133,7 +6278,7 @@
       <c r="A272" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="B272" s="7" t="s">
+      <c r="B272" s="8" t="s">
         <v>458</v>
       </c>
     </row>
@@ -6141,7 +6286,7 @@
       <c r="A273" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B273" s="7" t="s">
+      <c r="B273" s="8" t="s">
         <v>460</v>
       </c>
     </row>
@@ -6149,7 +6294,7 @@
       <c r="A274" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B274" s="7" t="s">
+      <c r="B274" s="8" t="s">
         <v>462</v>
       </c>
     </row>
@@ -6157,7 +6302,7 @@
       <c r="A275" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B275" s="7" t="s">
+      <c r="B275" s="8" t="s">
         <v>332</v>
       </c>
     </row>
@@ -6165,7 +6310,7 @@
       <c r="A276" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="B276" s="7" t="s">
+      <c r="B276" s="8" t="s">
         <v>339</v>
       </c>
     </row>
@@ -6173,15 +6318,15 @@
       <c r="A277" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B277" s="7" t="s">
+      <c r="B277" s="8" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="278" spans="1:2">
-      <c r="A278" s="25" t="s">
+      <c r="A278" s="26" t="s">
         <v>467</v>
       </c>
-      <c r="B278" s="24" t="s">
+      <c r="B278" s="25" t="s">
         <v>468</v>
       </c>
     </row>
@@ -6189,7 +6334,7 @@
       <c r="A279" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B279" s="24" t="s">
+      <c r="B279" s="25" t="s">
         <v>59</v>
       </c>
     </row>
@@ -6197,95 +6342,95 @@
       <c r="A280" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="B280" s="7" t="s">
+      <c r="B280" s="8" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="281" spans="1:2">
-      <c r="A281" s="8" t="s">
+      <c r="A281" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="B281" s="9" t="s">
+      <c r="B281" s="10" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="282" spans="1:2">
-      <c r="A282" s="8" t="s">
+      <c r="A282" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="B282" s="9" t="s">
+      <c r="B282" s="10" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="283" spans="1:2">
-      <c r="A283" s="8" t="s">
+      <c r="A283" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="B283" s="9" t="s">
+      <c r="B283" s="10" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="284" spans="1:2">
-      <c r="A284" s="8" t="s">
+      <c r="A284" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="B284" s="45" t="s">
+      <c r="B284" s="46" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="285" spans="1:2">
-      <c r="A285" s="46" t="s">
+      <c r="A285" s="47" t="s">
         <v>479</v>
       </c>
-      <c r="B285" s="7" t="s">
+      <c r="B285" s="8" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="286" spans="1:2">
-      <c r="A286" s="46" t="s">
+      <c r="A286" s="47" t="s">
         <v>481</v>
       </c>
-      <c r="B286" s="7" t="s">
+      <c r="B286" s="8" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="287" spans="1:2">
-      <c r="A287" s="46" t="s">
+      <c r="A287" s="47" t="s">
         <v>483</v>
       </c>
-      <c r="B287" s="7" t="s">
+      <c r="B287" s="8" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="288" spans="1:2">
-      <c r="A288" s="46" t="s">
+      <c r="A288" s="47" t="s">
         <v>485</v>
       </c>
-      <c r="B288" s="7" t="s">
+      <c r="B288" s="8" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="289" spans="1:2">
-      <c r="A289" s="46" t="s">
+      <c r="A289" s="47" t="s">
         <v>487</v>
       </c>
-      <c r="B289" s="7" t="s">
+      <c r="B289" s="8" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="46" t="s">
+      <c r="A290" s="47" t="s">
         <v>489</v>
       </c>
-      <c r="B290" s="7" t="s">
+      <c r="B290" s="8" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="46" t="s">
+      <c r="A291" s="47" t="s">
         <v>491</v>
       </c>
-      <c r="B291" s="7" t="s">
+      <c r="B291" s="8" t="s">
         <v>492</v>
       </c>
     </row>
@@ -6293,7 +6438,7 @@
       <c r="A292" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B292" s="7" t="s">
+      <c r="B292" s="8" t="s">
         <v>494</v>
       </c>
     </row>
@@ -6301,7 +6446,7 @@
       <c r="A293" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B293" s="7" t="s">
+      <c r="B293" s="8" t="s">
         <v>496</v>
       </c>
     </row>
@@ -6309,7 +6454,7 @@
       <c r="A294" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B294" s="7" t="s">
+      <c r="B294" s="8" t="s">
         <v>498</v>
       </c>
     </row>
@@ -6317,7 +6462,7 @@
       <c r="A295" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="B295" s="7" t="s">
+      <c r="B295" s="8" t="s">
         <v>500</v>
       </c>
     </row>
@@ -6325,7 +6470,7 @@
       <c r="A296" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B296" s="7" t="s">
+      <c r="B296" s="8" t="s">
         <v>502</v>
       </c>
     </row>
@@ -6333,7 +6478,7 @@
       <c r="A297" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B297" s="7" t="s">
+      <c r="B297" s="8" t="s">
         <v>504</v>
       </c>
     </row>
@@ -6341,7 +6486,7 @@
       <c r="A298" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="B298" s="7" t="s">
+      <c r="B298" s="8" t="s">
         <v>506</v>
       </c>
     </row>
@@ -6349,7 +6494,7 @@
       <c r="A299" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="B299" s="7" t="s">
+      <c r="B299" s="8" t="s">
         <v>508</v>
       </c>
     </row>
@@ -6357,7 +6502,7 @@
       <c r="A300" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="B300" s="7" t="s">
+      <c r="B300" s="8" t="s">
         <v>510</v>
       </c>
     </row>
@@ -6365,7 +6510,7 @@
       <c r="A301" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="B301" s="7" t="s">
+      <c r="B301" s="8" t="s">
         <v>512</v>
       </c>
     </row>
@@ -6373,7 +6518,7 @@
       <c r="A302" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B302" s="7" t="s">
+      <c r="B302" s="8" t="s">
         <v>514</v>
       </c>
     </row>
@@ -6381,7 +6526,7 @@
       <c r="A303" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="B303" s="7" t="s">
+      <c r="B303" s="8" t="s">
         <v>516</v>
       </c>
     </row>
@@ -6389,7 +6534,7 @@
       <c r="A304" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="B304" s="7" t="s">
+      <c r="B304" s="8" t="s">
         <v>518</v>
       </c>
     </row>
@@ -6397,7 +6542,7 @@
       <c r="A305" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="B305" s="7" t="s">
+      <c r="B305" s="8" t="s">
         <v>419</v>
       </c>
     </row>
@@ -6405,7 +6550,7 @@
       <c r="A306" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="B306" s="7" t="s">
+      <c r="B306" s="8" t="s">
         <v>521</v>
       </c>
     </row>
@@ -6413,7 +6558,7 @@
       <c r="A307" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B307" s="7" t="s">
+      <c r="B307" s="8" t="s">
         <v>419</v>
       </c>
     </row>
@@ -6421,7 +6566,7 @@
       <c r="A308" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="B308" s="7" t="s">
+      <c r="B308" s="8" t="s">
         <v>524</v>
       </c>
     </row>
@@ -6429,7 +6574,7 @@
       <c r="A309" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="B309" s="7" t="s">
+      <c r="B309" s="8" t="s">
         <v>526</v>
       </c>
     </row>
@@ -6437,7 +6582,7 @@
       <c r="A310" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="B310" s="7" t="s">
+      <c r="B310" s="8" t="s">
         <v>528</v>
       </c>
     </row>
@@ -6445,7 +6590,7 @@
       <c r="A311" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B311" s="7" t="s">
+      <c r="B311" s="8" t="s">
         <v>528</v>
       </c>
     </row>
@@ -6453,7 +6598,7 @@
       <c r="A312" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B312" s="7" t="s">
+      <c r="B312" s="8" t="s">
         <v>528</v>
       </c>
     </row>
@@ -6461,7 +6606,7 @@
       <c r="A313" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="B313" s="7" t="s">
+      <c r="B313" s="8" t="s">
         <v>532</v>
       </c>
     </row>
@@ -6469,7 +6614,7 @@
       <c r="A314" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="B314" s="7" t="s">
+      <c r="B314" s="8" t="s">
         <v>534</v>
       </c>
     </row>
@@ -6477,7 +6622,7 @@
       <c r="A315" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B315" s="7" t="s">
+      <c r="B315" s="8" t="s">
         <v>534</v>
       </c>
     </row>
@@ -6485,7 +6630,7 @@
       <c r="A316" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="B316" s="7" t="s">
+      <c r="B316" s="8" t="s">
         <v>537</v>
       </c>
     </row>
@@ -6493,7 +6638,7 @@
       <c r="A317" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B317" s="7" t="s">
+      <c r="B317" s="8" t="s">
         <v>539</v>
       </c>
     </row>
@@ -6501,7 +6646,7 @@
       <c r="A318" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="B318" s="7" t="s">
+      <c r="B318" s="8" t="s">
         <v>541</v>
       </c>
     </row>
@@ -6509,7 +6654,7 @@
       <c r="A319" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B319" s="47" t="s">
+      <c r="B319" s="48" t="s">
         <v>543</v>
       </c>
     </row>
@@ -6517,7 +6662,7 @@
       <c r="A320" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="B320" s="7" t="s">
+      <c r="B320" s="8" t="s">
         <v>545</v>
       </c>
     </row>
@@ -6525,7 +6670,7 @@
       <c r="A321" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="B321" s="7" t="s">
+      <c r="B321" s="8" t="s">
         <v>547</v>
       </c>
     </row>
@@ -6533,7 +6678,7 @@
       <c r="A322" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="B322" s="7" t="s">
+      <c r="B322" s="8" t="s">
         <v>549</v>
       </c>
     </row>
@@ -6541,7 +6686,7 @@
       <c r="A323" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="B323" s="7" t="s">
+      <c r="B323" s="8" t="s">
         <v>551</v>
       </c>
     </row>
@@ -6549,7 +6694,7 @@
       <c r="A324" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="B324" s="7" t="s">
+      <c r="B324" s="8" t="s">
         <v>552</v>
       </c>
     </row>
@@ -6557,7 +6702,7 @@
       <c r="A325" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B325" s="7" t="s">
+      <c r="B325" s="8" t="s">
         <v>554</v>
       </c>
     </row>
@@ -6565,7 +6710,7 @@
       <c r="A326" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="B326" s="7" t="s">
+      <c r="B326" s="8" t="s">
         <v>556</v>
       </c>
     </row>
@@ -6573,7 +6718,7 @@
       <c r="A327" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B327" s="7" t="s">
+      <c r="B327" s="8" t="s">
         <v>558</v>
       </c>
     </row>
@@ -6581,7 +6726,7 @@
       <c r="A328" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B328" s="7" t="s">
+      <c r="B328" s="8" t="s">
         <v>560</v>
       </c>
     </row>
@@ -6589,7 +6734,7 @@
       <c r="A329" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B329" s="7" t="s">
+      <c r="B329" s="8" t="s">
         <v>561</v>
       </c>
     </row>
@@ -6597,7 +6742,7 @@
       <c r="A330" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="B330" s="7" t="s">
+      <c r="B330" s="8" t="s">
         <v>563</v>
       </c>
     </row>
@@ -6605,7 +6750,7 @@
       <c r="A331" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="B331" s="7" t="s">
+      <c r="B331" s="8" t="s">
         <v>564</v>
       </c>
     </row>
@@ -6613,7 +6758,7 @@
       <c r="A332" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="B332" s="7" t="s">
+      <c r="B332" s="8" t="s">
         <v>566</v>
       </c>
     </row>
@@ -6621,7 +6766,7 @@
       <c r="A333" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="B333" s="7" t="s">
+      <c r="B333" s="8" t="s">
         <v>568</v>
       </c>
     </row>
@@ -6629,7 +6774,7 @@
       <c r="A334" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B334" s="7" t="s">
+      <c r="B334" s="8" t="s">
         <v>570</v>
       </c>
     </row>
@@ -6637,63 +6782,63 @@
       <c r="A335" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B335" s="7" t="s">
+      <c r="B335" s="8" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="29" t="s">
+      <c r="A336" s="30" t="s">
         <v>573</v>
       </c>
-      <c r="B336" s="28" t="s">
+      <c r="B336" s="29" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="337" spans="1:2">
-      <c r="A337" s="29" t="s">
+      <c r="A337" s="30" t="s">
         <v>575</v>
       </c>
-      <c r="B337" s="28" t="s">
+      <c r="B337" s="29" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="338" spans="1:2">
-      <c r="A338" s="29" t="s">
+      <c r="A338" s="30" t="s">
         <v>576</v>
       </c>
-      <c r="B338" s="28" t="s">
+      <c r="B338" s="29" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="339" spans="1:2">
-      <c r="A339" s="29" t="s">
+      <c r="A339" s="30" t="s">
         <v>577</v>
       </c>
-      <c r="B339" s="28" t="s">
+      <c r="B339" s="29" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="340" spans="1:2">
-      <c r="A340" s="29" t="s">
+      <c r="A340" s="30" t="s">
         <v>578</v>
       </c>
-      <c r="B340" s="28" t="s">
+      <c r="B340" s="29" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="341" spans="1:2">
-      <c r="A341" s="29" t="s">
+      <c r="A341" s="30" t="s">
         <v>580</v>
       </c>
-      <c r="B341" s="28" t="s">
+      <c r="B341" s="29" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="342" spans="1:2">
-      <c r="A342" s="29" t="s">
+      <c r="A342" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="B342" s="28" t="s">
+      <c r="B342" s="29" t="s">
         <v>579</v>
       </c>
     </row>
@@ -6701,7 +6846,7 @@
       <c r="A343" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="B343" s="7" t="s">
+      <c r="B343" s="8" t="s">
         <v>583</v>
       </c>
     </row>
@@ -6709,7 +6854,7 @@
       <c r="A344" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B344" s="7" t="s">
+      <c r="B344" s="8" t="s">
         <v>585</v>
       </c>
     </row>
@@ -6717,7 +6862,7 @@
       <c r="A345" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="B345" s="7" t="s">
+      <c r="B345" s="8" t="s">
         <v>587</v>
       </c>
     </row>
@@ -6725,7 +6870,7 @@
       <c r="A346" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="B346" s="7" t="s">
+      <c r="B346" s="8" t="s">
         <v>589</v>
       </c>
     </row>
@@ -6733,7 +6878,7 @@
       <c r="A347" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="B347" s="7" t="s">
+      <c r="B347" s="8" t="s">
         <v>591</v>
       </c>
     </row>
@@ -6741,7 +6886,7 @@
       <c r="A348" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B348" s="7" t="s">
+      <c r="B348" s="8" t="s">
         <v>593</v>
       </c>
     </row>
@@ -6749,7 +6894,7 @@
       <c r="A349" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="B349" s="7" t="s">
+      <c r="B349" s="8" t="s">
         <v>595</v>
       </c>
     </row>
@@ -6757,7 +6902,7 @@
       <c r="A350" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="B350" s="7" t="s">
+      <c r="B350" s="8" t="s">
         <v>597</v>
       </c>
     </row>
@@ -6765,7 +6910,7 @@
       <c r="A351" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B351" s="7" t="s">
+      <c r="B351" s="8" t="s">
         <v>599</v>
       </c>
     </row>
@@ -6773,7 +6918,7 @@
       <c r="A352" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="B352" s="7" t="s">
+      <c r="B352" s="8" t="s">
         <v>601</v>
       </c>
     </row>
@@ -6781,7 +6926,7 @@
       <c r="A353" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B353" s="7" t="s">
+      <c r="B353" s="8" t="s">
         <v>603</v>
       </c>
     </row>
@@ -6789,7 +6934,7 @@
       <c r="A354" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B354" s="7" t="s">
+      <c r="B354" s="8" t="s">
         <v>605</v>
       </c>
     </row>
@@ -6797,7 +6942,7 @@
       <c r="A355" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B355" s="7" t="s">
+      <c r="B355" s="8" t="s">
         <v>59</v>
       </c>
     </row>
@@ -6805,7 +6950,7 @@
       <c r="A356" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B356" s="24" t="s">
+      <c r="B356" s="25" t="s">
         <v>608</v>
       </c>
     </row>
@@ -6813,415 +6958,415 @@
       <c r="A357" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="B357" s="7" t="s">
+      <c r="B357" s="8" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="25" t="s">
+      <c r="A358" s="26" t="s">
         <v>611</v>
       </c>
-      <c r="B358" s="26" t="s">
+      <c r="B358" s="27" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="359" spans="1:2">
-      <c r="A359" s="25" t="s">
+      <c r="A359" s="26" t="s">
         <v>613</v>
       </c>
-      <c r="B359" s="26" t="s">
+      <c r="B359" s="27" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="360" spans="1:2">
-      <c r="A360" s="25" t="s">
+      <c r="A360" s="26" t="s">
         <v>615</v>
       </c>
-      <c r="B360" s="24">
+      <c r="B360" s="25">
         <v>10</v>
       </c>
     </row>
     <row r="361" spans="1:2">
-      <c r="A361" s="25" t="s">
+      <c r="A361" s="26" t="s">
         <v>616</v>
       </c>
-      <c r="B361" s="24">
+      <c r="B361" s="25">
         <v>1000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
-      <c r="A362" s="25" t="s">
+      <c r="A362" s="26" t="s">
         <v>617</v>
       </c>
-      <c r="B362" s="48">
+      <c r="B362" s="49">
         <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:2">
-      <c r="A363" s="25" t="s">
+      <c r="A363" s="26" t="s">
         <v>618</v>
       </c>
-      <c r="B363" s="24">
+      <c r="B363" s="25">
         <v>1000</v>
       </c>
     </row>
     <row r="364" spans="1:2">
-      <c r="A364" s="25" t="s">
+      <c r="A364" s="26" t="s">
         <v>619</v>
       </c>
-      <c r="B364" s="24" t="s">
+      <c r="B364" s="25" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="25" t="s">
+      <c r="A365" s="26" t="s">
         <v>621</v>
       </c>
-      <c r="B365" s="24" t="s">
+      <c r="B365" s="25" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="25" t="s">
+      <c r="A366" s="26" t="s">
         <v>623</v>
       </c>
-      <c r="B366" s="24" t="s">
+      <c r="B366" s="25" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" s="25" t="s">
+      <c r="A367" s="26" t="s">
         <v>625</v>
       </c>
-      <c r="B367" s="24">
+      <c r="B367" s="25">
         <v>10000039</v>
       </c>
     </row>
     <row r="368" spans="1:2">
-      <c r="A368" s="25" t="s">
+      <c r="A368" s="26" t="s">
         <v>626</v>
       </c>
-      <c r="B368" s="26" t="s">
+      <c r="B368" s="27" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="369" spans="1:2">
-      <c r="A369" s="25" t="s">
+      <c r="A369" s="26" t="s">
         <v>628</v>
       </c>
-      <c r="B369" s="26" t="s">
+      <c r="B369" s="27" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="25" t="s">
+      <c r="A370" s="26" t="s">
         <v>630</v>
       </c>
-      <c r="B370" s="7" t="s">
+      <c r="B370" s="8" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="25" t="s">
+      <c r="A371" s="26" t="s">
         <v>632</v>
       </c>
-      <c r="B371" s="7" t="s">
+      <c r="B371" s="8" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="372" spans="1:2">
-      <c r="A372" s="25" t="s">
+      <c r="A372" s="26" t="s">
         <v>634</v>
       </c>
-      <c r="B372" s="7" t="s">
+      <c r="B372" s="8" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="25" t="s">
+      <c r="A373" s="26" t="s">
         <v>636</v>
       </c>
-      <c r="B373" s="7" t="s">
+      <c r="B373" s="8" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="25" t="s">
+      <c r="A374" s="26" t="s">
         <v>638</v>
       </c>
-      <c r="B374" s="7" t="s">
+      <c r="B374" s="8" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="25" t="s">
+      <c r="A375" s="26" t="s">
         <v>640</v>
       </c>
-      <c r="B375" s="7" t="s">
+      <c r="B375" s="8" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="25" t="s">
+      <c r="A376" s="26" t="s">
         <v>642</v>
       </c>
-      <c r="B376" s="7" t="s">
+      <c r="B376" s="8" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="377" spans="1:2">
-      <c r="A377" s="25" t="s">
+      <c r="A377" s="26" t="s">
         <v>643</v>
       </c>
-      <c r="B377" s="7" t="s">
+      <c r="B377" s="8" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="378" spans="1:2">
-      <c r="A378" s="25" t="s">
+      <c r="A378" s="26" t="s">
         <v>645</v>
       </c>
-      <c r="B378" s="7" t="s">
+      <c r="B378" s="8" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="379" spans="1:2">
-      <c r="A379" s="25" t="s">
+      <c r="A379" s="26" t="s">
         <v>647</v>
       </c>
-      <c r="B379" s="7" t="s">
+      <c r="B379" s="8" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="380" spans="1:2">
-      <c r="A380" s="25" t="s">
+      <c r="A380" s="26" t="s">
         <v>649</v>
       </c>
-      <c r="B380" s="7" t="s">
+      <c r="B380" s="8" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="381" spans="1:2">
-      <c r="A381" s="25" t="s">
+      <c r="A381" s="26" t="s">
         <v>650</v>
       </c>
-      <c r="B381" s="7" t="s">
+      <c r="B381" s="8" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="25" t="s">
+      <c r="A382" s="26" t="s">
         <v>652</v>
       </c>
-      <c r="B382" s="7" t="s">
+      <c r="B382" s="8" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="25" t="s">
+      <c r="A383" s="26" t="s">
         <v>654</v>
       </c>
-      <c r="B383" s="7" t="s">
+      <c r="B383" s="8" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="25" t="s">
+      <c r="A384" s="26" t="s">
         <v>656</v>
       </c>
-      <c r="B384" s="7" t="s">
+      <c r="B384" s="8" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="25" t="s">
+      <c r="A385" s="26" t="s">
         <v>658</v>
       </c>
-      <c r="B385" s="7" t="s">
+      <c r="B385" s="8" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="25" t="s">
+      <c r="A386" s="26" t="s">
         <v>660</v>
       </c>
-      <c r="B386" s="7" t="s">
+      <c r="B386" s="8" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="25" t="s">
+      <c r="A387" s="26" t="s">
         <v>662</v>
       </c>
-      <c r="B387" s="7" t="s">
+      <c r="B387" s="8" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="388" spans="1:2">
-      <c r="A388" s="25" t="s">
+      <c r="A388" s="26" t="s">
         <v>664</v>
       </c>
-      <c r="B388" s="7" t="s">
+      <c r="B388" s="8" t="s">
         <v>665</v>
       </c>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" s="25" t="s">
+      <c r="A389" s="26" t="s">
         <v>666</v>
       </c>
-      <c r="B389" s="7" t="s">
+      <c r="B389" s="8" t="s">
         <v>667</v>
       </c>
     </row>
     <row r="390" spans="1:2">
-      <c r="A390" s="25" t="s">
+      <c r="A390" s="26" t="s">
         <v>668</v>
       </c>
-      <c r="B390" s="7" t="s">
+      <c r="B390" s="8" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="25" t="s">
+      <c r="A391" s="26" t="s">
         <v>670</v>
       </c>
-      <c r="B391" s="7" t="s">
+      <c r="B391" s="8" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="25" t="s">
+      <c r="A392" s="26" t="s">
         <v>672</v>
       </c>
-      <c r="B392" s="7" t="s">
+      <c r="B392" s="8" t="s">
         <v>673</v>
       </c>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393" s="25" t="s">
+      <c r="A393" s="26" t="s">
         <v>674</v>
       </c>
-      <c r="B393" s="7" t="s">
+      <c r="B393" s="8" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="25" t="s">
+      <c r="A394" s="26" t="s">
         <v>676</v>
       </c>
-      <c r="B394" s="7" t="s">
+      <c r="B394" s="8" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="395" spans="1:2">
-      <c r="A395" s="25" t="s">
+      <c r="A395" s="26" t="s">
         <v>678</v>
       </c>
-      <c r="B395" s="7" t="s">
+      <c r="B395" s="8" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396" s="25" t="s">
+      <c r="A396" s="26" t="s">
         <v>680</v>
       </c>
-      <c r="B396" s="7" t="s">
+      <c r="B396" s="8" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="25" t="s">
+      <c r="A397" s="26" t="s">
         <v>682</v>
       </c>
-      <c r="B397" s="7" t="s">
+      <c r="B397" s="8" t="s">
         <v>683</v>
       </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="25" t="s">
+      <c r="A398" s="26" t="s">
         <v>684</v>
       </c>
-      <c r="B398" s="7" t="s">
+      <c r="B398" s="8" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="25" t="s">
+      <c r="A399" s="26" t="s">
         <v>686</v>
       </c>
-      <c r="B399" s="7" t="s">
+      <c r="B399" s="8" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="25" t="s">
+      <c r="A400" s="26" t="s">
         <v>688</v>
       </c>
-      <c r="B400" s="7" t="s">
+      <c r="B400" s="8" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="25" t="s">
+      <c r="A401" s="26" t="s">
         <v>690</v>
       </c>
-      <c r="B401" s="7" t="s">
+      <c r="B401" s="8" t="s">
         <v>691</v>
       </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="25" t="s">
+      <c r="A402" s="26" t="s">
         <v>692</v>
       </c>
-      <c r="B402" s="7" t="s">
+      <c r="B402" s="8" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="25" t="s">
+      <c r="A403" s="26" t="s">
         <v>694</v>
       </c>
-      <c r="B403" s="7" t="s">
+      <c r="B403" s="8" t="s">
         <v>695</v>
       </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="25" t="s">
+      <c r="A404" s="26" t="s">
         <v>696</v>
       </c>
-      <c r="B404" s="7" t="s">
+      <c r="B404" s="8" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="25" t="s">
+      <c r="A405" s="26" t="s">
         <v>698</v>
       </c>
-      <c r="B405" s="7" t="s">
+      <c r="B405" s="8" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="25" t="s">
+      <c r="A406" s="26" t="s">
         <v>700</v>
       </c>
-      <c r="B406" s="7" t="s">
+      <c r="B406" s="8" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="25" t="s">
+      <c r="A407" s="26" t="s">
         <v>702</v>
       </c>
-      <c r="B407" s="7" t="s">
+      <c r="B407" s="8" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="25" t="s">
+      <c r="A408" s="26" t="s">
         <v>704</v>
       </c>
-      <c r="B408" s="7" t="s">
+      <c r="B408" s="8" t="s">
         <v>705</v>
       </c>
     </row>
@@ -7229,7 +7374,7 @@
       <c r="A409" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="B409" s="7" t="s">
+      <c r="B409" s="8" t="s">
         <v>707</v>
       </c>
     </row>
@@ -7237,7 +7382,7 @@
       <c r="A410" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="B410" s="7" t="s">
+      <c r="B410" s="8" t="s">
         <v>709</v>
       </c>
     </row>
@@ -7245,7 +7390,7 @@
       <c r="A411" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="B411" s="7" t="s">
+      <c r="B411" s="8" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7253,7 +7398,7 @@
       <c r="A412" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="B412" s="7" t="s">
+      <c r="B412" s="8" t="s">
         <v>711</v>
       </c>
     </row>
@@ -7261,7 +7406,7 @@
       <c r="A413" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="B413" s="7" t="s">
+      <c r="B413" s="8" t="s">
         <v>713</v>
       </c>
     </row>
@@ -7269,7 +7414,7 @@
       <c r="A414" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="B414" s="7" t="s">
+      <c r="B414" s="8" t="s">
         <v>715</v>
       </c>
     </row>
@@ -7277,7 +7422,7 @@
       <c r="A415" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="B415" s="7" t="s">
+      <c r="B415" s="8" t="s">
         <v>717</v>
       </c>
     </row>
@@ -7285,7 +7430,7 @@
       <c r="A416" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B416" s="7" t="s">
+      <c r="B416" s="8" t="s">
         <v>719</v>
       </c>
     </row>
@@ -7293,7 +7438,7 @@
       <c r="A417" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="B417" s="7" t="s">
+      <c r="B417" s="8" t="s">
         <v>117</v>
       </c>
     </row>
@@ -7301,7 +7446,7 @@
       <c r="A418" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B418" s="7" t="s">
+      <c r="B418" s="8" t="s">
         <v>722</v>
       </c>
     </row>
@@ -7309,7 +7454,7 @@
       <c r="A419" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="B419" s="7" t="s">
+      <c r="B419" s="8" t="s">
         <v>724</v>
       </c>
     </row>
@@ -7317,7 +7462,7 @@
       <c r="A420" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="B420" s="7" t="s">
+      <c r="B420" s="8" t="s">
         <v>726</v>
       </c>
     </row>
@@ -7325,7 +7470,7 @@
       <c r="A421" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="B421" s="7" t="s">
+      <c r="B421" s="8" t="s">
         <v>727</v>
       </c>
     </row>
@@ -7333,7 +7478,7 @@
       <c r="A422" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="B422" s="7" t="s">
+      <c r="B422" s="8" t="s">
         <v>568</v>
       </c>
     </row>
@@ -7341,7 +7486,7 @@
       <c r="A423" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="B423" s="7" t="s">
+      <c r="B423" s="8" t="s">
         <v>729</v>
       </c>
     </row>
@@ -7349,7 +7494,7 @@
       <c r="A424" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="B424" s="7" t="s">
+      <c r="B424" s="8" t="s">
         <v>731</v>
       </c>
     </row>
@@ -7357,335 +7502,335 @@
       <c r="A425" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="B425" s="7" t="s">
+      <c r="B425" s="8" t="s">
         <v>733</v>
       </c>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="11" t="s">
+      <c r="A426" s="12" t="s">
         <v>734</v>
       </c>
-      <c r="B426" s="13" t="s">
+      <c r="B426" s="14" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="427" spans="1:2">
-      <c r="A427" s="11" t="s">
+      <c r="A427" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="B427" s="13" t="s">
+      <c r="B427" s="14" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="11" t="s">
+      <c r="A428" s="12" t="s">
         <v>738</v>
       </c>
-      <c r="B428" s="13" t="s">
+      <c r="B428" s="14" t="s">
         <v>739</v>
       </c>
     </row>
     <row r="429" spans="1:2">
-      <c r="A429" s="11" t="s">
+      <c r="A429" s="12" t="s">
         <v>740</v>
       </c>
-      <c r="B429" s="13" t="s">
+      <c r="B429" s="14" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="430" spans="1:2">
-      <c r="A430" s="11" t="s">
+      <c r="A430" s="12" t="s">
         <v>742</v>
       </c>
-      <c r="B430" s="13" t="s">
+      <c r="B430" s="14" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="11" t="s">
+      <c r="A431" s="12" t="s">
         <v>744</v>
       </c>
-      <c r="B431" s="13" t="s">
+      <c r="B431" s="14" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="432" spans="1:2">
-      <c r="A432" s="11" t="s">
+      <c r="A432" s="12" t="s">
         <v>746</v>
       </c>
-      <c r="B432" s="13" t="s">
+      <c r="B432" s="14" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="433" spans="1:2">
-      <c r="A433" s="11" t="s">
+      <c r="A433" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="B433" s="13" t="s">
+      <c r="B433" s="14" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="434" spans="1:2">
-      <c r="A434" s="11" t="s">
+      <c r="A434" s="12" t="s">
         <v>750</v>
       </c>
-      <c r="B434" s="13" t="s">
+      <c r="B434" s="14" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="435" spans="1:2">
-      <c r="A435" s="11" t="s">
+      <c r="A435" s="12" t="s">
         <v>752</v>
       </c>
-      <c r="B435" s="13" t="s">
+      <c r="B435" s="14" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="436" spans="1:2">
-      <c r="A436" s="11" t="s">
+      <c r="A436" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="B436" s="13" t="s">
+      <c r="B436" s="14" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="437" spans="1:2">
-      <c r="A437" s="11" t="s">
+      <c r="A437" s="12" t="s">
         <v>756</v>
       </c>
-      <c r="B437" s="13" t="s">
+      <c r="B437" s="14" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="438" spans="1:2">
-      <c r="A438" s="11" t="s">
+      <c r="A438" s="12" t="s">
         <v>758</v>
       </c>
-      <c r="B438" s="13" t="s">
+      <c r="B438" s="14" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="439" spans="1:2">
-      <c r="A439" s="11" t="s">
+      <c r="A439" s="12" t="s">
         <v>760</v>
       </c>
-      <c r="B439" s="13" t="s">
+      <c r="B439" s="14" t="s">
         <v>761</v>
       </c>
     </row>
     <row r="440" spans="1:2">
-      <c r="A440" s="29" t="s">
+      <c r="A440" s="30" t="s">
         <v>762</v>
       </c>
-      <c r="B440" s="28" t="s">
+      <c r="B440" s="29" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="441" spans="1:2">
-      <c r="A441" s="49" t="s">
+      <c r="A441" s="50" t="s">
         <v>764</v>
       </c>
-      <c r="B441" s="50" t="s">
+      <c r="B441" s="51" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="442" spans="1:2">
-      <c r="A442" s="49" t="s">
+      <c r="A442" s="50" t="s">
         <v>765</v>
       </c>
-      <c r="B442" s="50" t="s">
+      <c r="B442" s="51" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="443" spans="1:2">
-      <c r="A443" s="49" t="s">
+      <c r="A443" s="50" t="s">
         <v>767</v>
       </c>
-      <c r="B443" s="50" t="s">
+      <c r="B443" s="51" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="444" spans="1:2">
-      <c r="A444" s="49" t="s">
+      <c r="A444" s="50" t="s">
         <v>769</v>
       </c>
-      <c r="B444" s="50" t="s">
+      <c r="B444" s="51" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="445" spans="1:2">
-      <c r="A445" s="49" t="s">
+      <c r="A445" s="50" t="s">
         <v>770</v>
       </c>
-      <c r="B445" s="50" t="s">
+      <c r="B445" s="51" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="446" spans="1:2">
-      <c r="A446" s="49" t="s">
+      <c r="A446" s="50" t="s">
         <v>771</v>
       </c>
-      <c r="B446" s="51" t="s">
+      <c r="B446" s="52" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="447" spans="1:2">
-      <c r="A447" s="49" t="s">
+      <c r="A447" s="50" t="s">
         <v>773</v>
       </c>
-      <c r="B447" s="51" t="s">
+      <c r="B447" s="52" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="448" spans="1:2">
-      <c r="A448" s="49" t="s">
+      <c r="A448" s="50" t="s">
         <v>775</v>
       </c>
-      <c r="B448" s="50" t="s">
+      <c r="B448" s="51" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="449" spans="1:2">
-      <c r="A449" s="49" t="s">
+      <c r="A449" s="50" t="s">
         <v>777</v>
       </c>
-      <c r="B449" s="50" t="s">
+      <c r="B449" s="51" t="s">
         <v>778</v>
       </c>
     </row>
     <row r="450" spans="1:2">
-      <c r="A450" s="49" t="s">
+      <c r="A450" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="B450" s="51" t="s">
+      <c r="B450" s="52" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="451" spans="1:2">
-      <c r="A451" s="49" t="s">
+      <c r="A451" s="50" t="s">
         <v>561</v>
       </c>
-      <c r="B451" s="51" t="s">
+      <c r="B451" s="52" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="452" spans="1:2">
-      <c r="A452" s="52" t="s">
+      <c r="A452" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="B452" s="53" t="s">
+      <c r="B452" s="54" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="453" spans="1:2">
-      <c r="A453" s="52" t="s">
+      <c r="A453" s="53" t="s">
         <v>779</v>
       </c>
-      <c r="B453" s="53" t="s">
+      <c r="B453" s="54" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="454" spans="1:2">
-      <c r="A454" s="49" t="s">
+      <c r="A454" s="50" t="s">
         <v>781</v>
       </c>
-      <c r="B454" s="54" t="s">
+      <c r="B454" s="55" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="455" spans="1:2">
-      <c r="A455" s="49" t="s">
+      <c r="A455" s="50" t="s">
         <v>782</v>
       </c>
-      <c r="B455" s="54" t="s">
+      <c r="B455" s="55" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="456" spans="1:2">
-      <c r="A456" s="49" t="s">
+      <c r="A456" s="50" t="s">
         <v>371</v>
       </c>
-      <c r="B456" s="51" t="s">
+      <c r="B456" s="52" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="457" spans="1:2">
-      <c r="A457" s="49" t="s">
+      <c r="A457" s="50" t="s">
         <v>783</v>
       </c>
-      <c r="B457" s="51" t="s">
+      <c r="B457" s="52" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="458" spans="1:2">
-      <c r="A458" s="49" t="s">
+      <c r="A458" s="50" t="s">
         <v>784</v>
       </c>
-      <c r="B458" s="51" t="s">
+      <c r="B458" s="52" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="459" spans="1:2">
-      <c r="A459" s="49" t="s">
+      <c r="A459" s="50" t="s">
         <v>786</v>
       </c>
-      <c r="B459" s="50" t="s">
+      <c r="B459" s="51" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="460" spans="1:2">
-      <c r="A460" s="49" t="s">
+      <c r="A460" s="50" t="s">
         <v>788</v>
       </c>
-      <c r="B460" s="50" t="s">
+      <c r="B460" s="51" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="461" spans="1:2">
-      <c r="A461" s="49" t="s">
+      <c r="A461" s="50" t="s">
         <v>790</v>
       </c>
-      <c r="B461" s="50" t="s">
+      <c r="B461" s="51" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="462" spans="1:2">
-      <c r="A462" s="55" t="s">
+      <c r="A462" s="56" t="s">
         <v>359</v>
       </c>
-      <c r="B462" s="55">
+      <c r="B462" s="56">
         <v>2</v>
       </c>
     </row>
     <row r="463" spans="1:2">
-      <c r="A463" s="55" t="s">
+      <c r="A463" s="56" t="s">
         <v>360</v>
       </c>
-      <c r="B463" s="55">
+      <c r="B463" s="56">
         <v>3</v>
       </c>
     </row>
     <row r="464" spans="1:2">
-      <c r="A464" s="55" t="s">
+      <c r="A464" s="56" t="s">
         <v>361</v>
       </c>
-      <c r="B464" s="55">
+      <c r="B464" s="56">
         <v>4</v>
       </c>
     </row>
     <row r="465" spans="1:2">
-      <c r="A465" s="56" t="s">
+      <c r="A465" s="57" t="s">
         <v>354</v>
       </c>
-      <c r="B465" s="56">
+      <c r="B465" s="57">
         <v>150</v>
       </c>
     </row>
     <row r="466" spans="1:2">
-      <c r="A466" s="56" t="s">
+      <c r="A466" s="57" t="s">
         <v>355</v>
       </c>
-      <c r="B466" s="56">
+      <c r="B466" s="57">
         <v>250</v>
       </c>
     </row>
@@ -7693,7 +7838,7 @@
       <c r="A467" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="B467" s="7" t="s">
+      <c r="B467" s="8" t="s">
         <v>357</v>
       </c>
     </row>
@@ -7701,7 +7846,7 @@
       <c r="A468" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B468" s="7" t="s">
+      <c r="B468" s="8" t="s">
         <v>794</v>
       </c>
     </row>
@@ -7709,7 +7854,7 @@
       <c r="A469" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="B469" s="7" t="s">
+      <c r="B469" s="8" t="s">
         <v>796</v>
       </c>
     </row>
@@ -7717,7 +7862,7 @@
       <c r="A470" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="B470" s="7" t="s">
+      <c r="B470" s="8" t="s">
         <v>797</v>
       </c>
     </row>
@@ -7725,7 +7870,7 @@
       <c r="A471" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="B471" s="7" t="s">
+      <c r="B471" s="8" t="s">
         <v>799</v>
       </c>
     </row>
@@ -7733,7 +7878,7 @@
       <c r="A472" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="B472" s="7" t="s">
+      <c r="B472" s="8" t="s">
         <v>229</v>
       </c>
     </row>
@@ -7741,7 +7886,7 @@
       <c r="A473" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="B473" s="7" t="s">
+      <c r="B473" s="8" t="s">
         <v>281</v>
       </c>
     </row>
@@ -7749,7 +7894,7 @@
       <c r="A474" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="B474" s="7" t="s">
+      <c r="B474" s="8" t="s">
         <v>757</v>
       </c>
     </row>
@@ -7757,7 +7902,7 @@
       <c r="A475" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="B475" s="7" t="s">
+      <c r="B475" s="8" t="s">
         <v>804</v>
       </c>
     </row>
@@ -7765,7 +7910,7 @@
       <c r="A476" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="B476" s="7" t="s">
+      <c r="B476" s="8" t="s">
         <v>759</v>
       </c>
     </row>
@@ -7773,7 +7918,7 @@
       <c r="A477" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="B477" s="7" t="s">
+      <c r="B477" s="8" t="s">
         <v>806</v>
       </c>
     </row>
@@ -7781,7 +7926,7 @@
       <c r="A478" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="B478" s="7" t="s">
+      <c r="B478" s="8" t="s">
         <v>808</v>
       </c>
     </row>
@@ -7789,7 +7934,7 @@
       <c r="A479" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="B479" s="44" t="s">
+      <c r="B479" s="45" t="s">
         <v>809</v>
       </c>
     </row>
@@ -7797,7 +7942,7 @@
       <c r="A480" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="B480" s="7" t="s">
+      <c r="B480" s="8" t="s">
         <v>811</v>
       </c>
     </row>
@@ -7805,7 +7950,7 @@
       <c r="A481" s="2" t="s">
         <v>812</v>
       </c>
-      <c r="B481" s="7" t="s">
+      <c r="B481" s="8" t="s">
         <v>813</v>
       </c>
     </row>
@@ -7813,7 +7958,7 @@
       <c r="A482" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="B482" s="7" t="s">
+      <c r="B482" s="8" t="s">
         <v>229</v>
       </c>
     </row>
@@ -7821,7 +7966,7 @@
       <c r="A483" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="B483" s="7" t="s">
+      <c r="B483" s="8" t="s">
         <v>816</v>
       </c>
     </row>
@@ -7829,7 +7974,7 @@
       <c r="A484" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="B484" s="7" t="s">
+      <c r="B484" s="8" t="s">
         <v>818</v>
       </c>
     </row>
@@ -7837,7 +7982,7 @@
       <c r="A485" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="B485" s="7" t="s">
+      <c r="B485" s="8" t="s">
         <v>820</v>
       </c>
     </row>
@@ -7845,7 +7990,7 @@
       <c r="A486" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="B486" s="7" t="s">
+      <c r="B486" s="8" t="s">
         <v>822</v>
       </c>
     </row>
@@ -7853,7 +7998,7 @@
       <c r="A487" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="B487" s="7" t="s">
+      <c r="B487" s="8" t="s">
         <v>808</v>
       </c>
     </row>
@@ -7861,7 +8006,7 @@
       <c r="A488" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="B488" s="7" t="s">
+      <c r="B488" s="8" t="s">
         <v>229</v>
       </c>
     </row>
@@ -7869,8 +8014,176 @@
       <c r="A489" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="B489" s="7" t="s">
+      <c r="B489" s="8" t="s">
         <v>148</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="58" t="s">
+        <v>826</v>
+      </c>
+      <c r="B490" s="59" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" s="58" t="s">
+        <v>828</v>
+      </c>
+      <c r="B491" s="59" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" s="58" t="s">
+        <v>830</v>
+      </c>
+      <c r="B492" s="59" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" s="58" t="s">
+        <v>832</v>
+      </c>
+      <c r="B493" s="59" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" s="58" t="s">
+        <v>834</v>
+      </c>
+      <c r="B494" s="59" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" s="58" t="s">
+        <v>836</v>
+      </c>
+      <c r="B495" s="59" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" s="58" t="s">
+        <v>838</v>
+      </c>
+      <c r="B496" s="59" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" s="58" t="s">
+        <v>840</v>
+      </c>
+      <c r="B497" s="59" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" s="58" t="s">
+        <v>842</v>
+      </c>
+      <c r="B498" s="59" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" s="58" t="s">
+        <v>844</v>
+      </c>
+      <c r="B499" s="59" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" s="58" t="s">
+        <v>846</v>
+      </c>
+      <c r="B500" s="59" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" s="58" t="s">
+        <v>848</v>
+      </c>
+      <c r="B501" s="59" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" s="58" t="s">
+        <v>850</v>
+      </c>
+      <c r="B502" s="59" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" s="58" t="s">
+        <v>852</v>
+      </c>
+      <c r="B503" s="59" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" s="58" t="s">
+        <v>854</v>
+      </c>
+      <c r="B504" s="59" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" s="58" t="s">
+        <v>856</v>
+      </c>
+      <c r="B505" s="59" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" s="58" t="s">
+        <v>858</v>
+      </c>
+      <c r="B506" s="59" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" s="58" t="s">
+        <v>859</v>
+      </c>
+      <c r="B507" s="59" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" s="58" t="s">
+        <v>861</v>
+      </c>
+      <c r="B508" s="59" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" s="58" t="s">
+        <v>862</v>
+      </c>
+      <c r="B509" s="59" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" s="58" t="s">
+        <v>864</v>
+      </c>
+      <c r="B510" s="59" t="s">
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -7899,39 +8212,43 @@
     </row>
     <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>826</v>
+        <v>866</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>827</v>
+        <v>867</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>828</v>
+        <v>868</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>829</v>
+        <v>869</v>
       </c>
     </row>
     <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>830</v>
+        <v>870</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>831</v>
+        <v>871</v>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>832</v>
+        <v>872</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+        <v>873</v>
+      </c>
+    </row>
+    <row r="6" ht="187.2" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>875</v>
+      </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2"/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="878">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -2942,6 +2942,45 @@
    AND stock_prod_id = 'TVS-RM-KDK-10'
    AND stock_prod_rev = '0'
 </t>
+  </si>
+  <si>
+    <t>OsoaQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT srcahd_plnt_loc_id "loc id",
+       srcahd_plnt "unit",
+       srcahd_doc_no "Doc. No.",
+       srcahd_amd_no "Amd. No.",
+       srcahd_cust_id "customer id",
+       (SELECT suplr_name1
+          FROM suppliers
+         WHERE suplr_bu = srcahd_bu AND suplr_suplr_id = srcahd_cust_id)
+          "customer name",
+       srcaln_prod_id "item id",
+       srcaln_prod_rev "item rev",
+       (SELECT prod_desc11
+          FROM products
+         WHERE     prod_bu = srcaln_bu
+               AND prod_id = srcaln_prod_id
+               AND prod_rev = srcaln_prod_rev)
+          "item descripition",
+       srcaln_uom "uom",
+       srcaln_disc_pct "disc_pct",
+       srcaln_old_price "Existing Price",
+       srcaln_new_price "new_price",
+       srcaln_mrp_price "MRP Price",
+       srcaln_hsn_code "HSN code",
+       srcaln_tax_pct "Tax Percent",
+       srcaln_cgst_amt "CGST",
+       srcaln_sgst_amt "SGST",
+       srcaln_igst_amt "IGST",
+       srcaln_utgst_amt "UTGST"
+  FROM sales_rate_contr_ament_hd, sales_rate_contr_ament_ln
+ WHERE     srcahd_bu = srcaln_bu
+       AND srcahd_plnt = srcaln_plnt
+       AND srcahd_doc_no = '${OSOANO}'
+    AND srcahd_doc_no = srcaln_doc_no
+       AND srcahd_bu =  'TVSA' </t>
   </si>
 </sst>
 </file>
@@ -3641,7 +3680,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3772,10 +3811,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="51" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8019,170 +8054,170 @@
       </c>
     </row>
     <row r="490" spans="1:2">
-      <c r="A490" s="58" t="s">
+      <c r="A490" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="B490" s="59" t="s">
+      <c r="B490" s="8" t="s">
         <v>827</v>
       </c>
     </row>
     <row r="491" spans="1:2">
-      <c r="A491" s="58" t="s">
+      <c r="A491" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="B491" s="59" t="s">
+      <c r="B491" s="8" t="s">
         <v>829</v>
       </c>
     </row>
     <row r="492" spans="1:2">
-      <c r="A492" s="58" t="s">
+      <c r="A492" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="B492" s="59" t="s">
+      <c r="B492" s="8" t="s">
         <v>831</v>
       </c>
     </row>
     <row r="493" spans="1:2">
-      <c r="A493" s="58" t="s">
+      <c r="A493" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="B493" s="59" t="s">
+      <c r="B493" s="8" t="s">
         <v>833</v>
       </c>
     </row>
     <row r="494" spans="1:2">
-      <c r="A494" s="58" t="s">
+      <c r="A494" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="B494" s="59" t="s">
+      <c r="B494" s="8" t="s">
         <v>835</v>
       </c>
     </row>
     <row r="495" spans="1:2">
-      <c r="A495" s="58" t="s">
+      <c r="A495" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="B495" s="59" t="s">
+      <c r="B495" s="8" t="s">
         <v>837</v>
       </c>
     </row>
     <row r="496" spans="1:2">
-      <c r="A496" s="58" t="s">
+      <c r="A496" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="B496" s="59" t="s">
+      <c r="B496" s="8" t="s">
         <v>839</v>
       </c>
     </row>
     <row r="497" spans="1:2">
-      <c r="A497" s="58" t="s">
+      <c r="A497" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="B497" s="59" t="s">
+      <c r="B497" s="8" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="498" spans="1:2">
-      <c r="A498" s="58" t="s">
+      <c r="A498" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="B498" s="59" t="s">
+      <c r="B498" s="8" t="s">
         <v>843</v>
       </c>
     </row>
     <row r="499" spans="1:2">
-      <c r="A499" s="58" t="s">
+      <c r="A499" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="B499" s="59" t="s">
+      <c r="B499" s="8" t="s">
         <v>845</v>
       </c>
     </row>
     <row r="500" spans="1:2">
-      <c r="A500" s="58" t="s">
+      <c r="A500" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="B500" s="59" t="s">
+      <c r="B500" s="8" t="s">
         <v>847</v>
       </c>
     </row>
     <row r="501" spans="1:2">
-      <c r="A501" s="58" t="s">
+      <c r="A501" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="B501" s="59" t="s">
+      <c r="B501" s="8" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="502" spans="1:2">
-      <c r="A502" s="58" t="s">
+      <c r="A502" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="B502" s="59" t="s">
+      <c r="B502" s="8" t="s">
         <v>851</v>
       </c>
     </row>
     <row r="503" spans="1:2">
-      <c r="A503" s="58" t="s">
+      <c r="A503" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="B503" s="59" t="s">
+      <c r="B503" s="8" t="s">
         <v>853</v>
       </c>
     </row>
     <row r="504" spans="1:2">
-      <c r="A504" s="58" t="s">
+      <c r="A504" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="B504" s="59" t="s">
+      <c r="B504" s="8" t="s">
         <v>855</v>
       </c>
     </row>
     <row r="505" spans="1:2">
-      <c r="A505" s="58" t="s">
+      <c r="A505" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="B505" s="59" t="s">
+      <c r="B505" s="8" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="506" spans="1:2">
-      <c r="A506" s="58" t="s">
+      <c r="A506" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="B506" s="59" t="s">
+      <c r="B506" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="507" spans="1:2">
-      <c r="A507" s="58" t="s">
+      <c r="A507" s="2" t="s">
         <v>859</v>
       </c>
-      <c r="B507" s="59" t="s">
+      <c r="B507" s="8" t="s">
         <v>860</v>
       </c>
     </row>
     <row r="508" spans="1:2">
-      <c r="A508" s="58" t="s">
+      <c r="A508" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="B508" s="59" t="s">
+      <c r="B508" s="8" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="509" spans="1:2">
-      <c r="A509" s="58" t="s">
+      <c r="A509" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="B509" s="59" t="s">
+      <c r="B509" s="8" t="s">
         <v>863</v>
       </c>
     </row>
     <row r="510" spans="1:2">
-      <c r="A510" s="58" t="s">
+      <c r="A510" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="B510" s="59" t="s">
+      <c r="B510" s="8" t="s">
         <v>865</v>
       </c>
     </row>
@@ -8246,13 +8281,17 @@
       <c r="A6" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+    <row r="7" ht="409.5" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2"/>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="5130"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
     <sheet name="DBData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="994">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1864,9 +1864,6 @@
   </si>
   <si>
     <t>ChargesBasis</t>
-  </si>
-  <si>
-    <t>V</t>
   </si>
   <si>
     <t>ChargeItem</t>
@@ -2926,24 +2923,6 @@
        AND soh_order_no = '${SONO}'</t>
   </si>
   <si>
-    <t>StockQuery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT stock_qty_hand,
-      (SELECT stcost_cost
-  FROM stock_costs
- WHERE stcost_bu = 'TVSA'
-   AND stcost_store_id = stock_store_id
-   AND stcost_prod_id = stock_prod_id
-   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
-  FROM stocks
- WHERE stock_bu = 'TVSA'
-   AND stock_store_id = '${SONO}'
-   AND stock_prod_id = 'TVS-RM-KDK-10'
-   AND stock_prod_rev = '0'
-</t>
-  </si>
-  <si>
     <t>OsoaQuery</t>
   </si>
   <si>
@@ -2982,23 +2961,509 @@
     AND srcahd_doc_no = srcaln_doc_no
        AND srcahd_bu =  'TVSA' </t>
   </si>
+  <si>
+    <t>SOAdvanceQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   SELECT soh_adv_pct,
+       soh_adv_rcvd,
+       soh_adv_tax_pct,
+       soh_adv_req_flag,
+       soh_adv_to_rcvd,
+       soh_adv_rcpt_inprg,
+SOH_ADV_DOC_NO
+  FROM sales_order_hd
+  WHERE soh_bu = 'TVSA'
+  and soh_order_no = '${SONO}'</t>
+  </si>
+  <si>
+    <t>SOCustomerDetailsQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  SELECT (SELECT NVL(state_name1,state_name2) FROM states WHERE state_bu = suplr_bu AND state_id = suplr_state)"Customer State"
+       FROM suppliers
+       WHERE suplr_bu = 'TVSA'
+       AND suplr_suplr_id = '${SONO}'</t>
+  </si>
+  <si>
+    <t>SOUnitDetailsQuery</t>
+  </si>
+  <si>
+    <t>SELECT  (SELECT NVL(state_name1,state_name2) FROM states WHERE state_bu = bup_bu AND state_id = BUP_STATE)"Unit State"
+      FROM bus_unit_plants
+     WHERE bup_bu ='TVSA'
+       AND bup_plant_id ='${SONO}'</t>
+  </si>
+  <si>
+    <t>SOLineDetails1&amp;2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  select soq_cess_pct,soq_cess_amt,SOQ_GST_EXEMPT_FLAG,SOQ_GST_INPUT_TYPE,SOQ_SAL_ACCT_ID,SOQ_SAL_CC_ID,SOQ_DISC_ACCT_ID,SOQ_DISC_CC_ID,SOQ_CUST_PO_NO,SOQ_CUST_PO_REV,SOQ_CUST_PO_DATE,
+  SOQ_PO_SL_SEQ_NO,SOQ_SQ_PFX,SOQ_SQ_NO,SOQ_SQ_SEQ_NO,SOQ_SQ_REV,SOQ_OPO_PO_NO,SOQ_OPO_PO_DATE,SOQ_PO_SEQ_NO,SOQ_CONT_CAT_NO,SOQ_PO_REF,SOQ_CATALOG_NO,
+  SOQ_CUST_PROD_ID,SOQ_CUST_PROD_DESC,SOQ_STORE_NAME,SOQ_PROD_EXT_DESC,SOQ_DESP_DATE,SOQ_RQRD_DATE,SOQ_PROMOTION_FLAG,SOQ_SALES_PRICE_CLASS,SOQ_SCHLD_DESC,SOQ_TOLERANCE_PCT,
+  SOQ_PROD_UOM,SOQ_CONV_FACTOR,SOQ_TOLR_QTY,SOQ_TOLR_TYPE,SOQ_BOM_NO,SOQ_BOM_NAME,SOQ_BOM_REVISION_NUM,SOQ_MARGIN_PCT,SOQ_LIST_PRICE,SOQ_MRP_PRICE,SOQ_SQ_PRICE,SOQ_INSTL_RQRD_FLAG
+         from sales_order_qtys
+         where soq_bu ='TVSA'
+           and soq_order_no ='${SONO}'</t>
+  </si>
+  <si>
+    <t>PaymentTermQuery</t>
+  </si>
+  <si>
+    <t>SELECT term_desc1,
+       trln_mtrl_pct,
+       trln_tax_pct,
+       TRLN_CLAIM_TYPE
+  FROM terms_ln,
+       terms_hd
+ WHERE  term_bu = trln_bu
+   AND term_bu = 'TVSA'
+   AND  TRLN_CLAIM_TYPE ='A'
+  AND term_term_id = trln_term_id
+  AND  term_desc1 = '${SONO}'</t>
+  </si>
+  <si>
+    <t>AdvanceReceiptQuery</t>
+  </si>
+  <si>
+    <t>SELECT
+        pard_doc_no Doc_no,
+        pard_plnt Unit,
+        pard_ord_pfx ord_pfx,
+        pard_ord_no ord_no,
+        pard_party_id Party_id,
+        pard_prop_adv_pct Adv_Percentage,
+        pard_prop_adv_amt Adv_Amt,
+        pard_curcy_id Curcy,
+        pard_ord_amt Ord_amt,
+        pard_rct_inprog_amt Rcpt_inprog_amt,
+        pard_rct_amt Rcpt_Amt,
+        pard_close_amt Closed_amt
+   FROM prop_adv_rct_doc
+  WHERE pard_bu = 'TVSA'
+    AND pard_doc_no ='${SONO}'</t>
+  </si>
+  <si>
+    <t>Stock Query</t>
+  </si>
+  <si>
+    <t>SELECT stock_qty_hand,
+      (SELECT stcost_cost
+  FROM stock_costs
+ WHERE stcost_bu = 'TVSA'
+   AND stcost_store_id = stock_store_id
+   AND stcost_prod_id = stock_prod_id
+   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
+  FROM stocks
+ WHERE stock_bu = 'TVSA'
+   AND stock_store_id = '${SONO}'
+   AND stock_prod_id = 'TVS-RM-KDK-10'
+   AND stock_prod_rev = '0'</t>
+  </si>
+  <si>
+    <t>Stock Query1</t>
+  </si>
+  <si>
+    <t>SELECT stock_qty_hand,
+      (SELECT stcost_cost
+  FROM stock_costs
+ WHERE stcost_bu = 'TVSA'
+   AND stcost_store_id = stock_store_id
+   AND stcost_prod_id = stock_prod_id
+   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
+  FROM stocks
+ WHERE stock_bu = 'TVSA'
+   AND stock_store_id = '${SONO}'
+   AND stock_prod_id ='${PONO}'
+   AND stock_prod_rev = '0'</t>
+  </si>
+  <si>
+    <t>SalesOrderChargesQuery</t>
+  </si>
+  <si>
+    <t>SELECT
+       sotc_bu,
+       sotc_ord_no,
+       sotc_seq_no,
+       sotc_prod_id,
+       (SELECT prod_desc11
+          FROM products
+         WHERE prod_bu ='TVSA'
+           AND prod_id = sotc_prod_id
+           AND prod_rev = sotc_prod_rev)ITEM_DESC,
+       sotc_prod_rev,
+       sotc_hsn_code,
+       sotc_qty,
+       sotc_chrg_basis,
+       sotc_chrg_pct,
+       sotc_chrg_pct sotc_chrg_pct1,
+       sotc_chrg_amt,
+       sotc_chrg_amt sotc_chrg_amt1,
+       sotc_gst_exempt_flag,
+       sotc_gst_input_type,
+       sotc_cre_by,
+       sotc_cre_ip_addr,
+       sotc_cre_os_user,
+       sotc_cre_date,
+       sotc_upd_by,
+       sotc_upd_ip_addr,
+       sotc_upd_os_user,
+       sotc_upd_date,
+       sotc_cre_emp_id,
+       sotc_upd_emp_id,
+       sotc_tcs_avail_flag,
+       sotc_sal_acct_id,
+       sotc_sal_cc_id,
+       sotc_tariff_code,
+       sotc_cgst_pct,
+       sotc_sgst_pct,
+       sotc_utgst_pct,
+       sotc_cess_pct,
+       sotc_igst_amt,
+       sotc_cgst_amt,
+       sotc_sgst_amt,
+       sotc_utgst_amt,
+       sotc_cess_amt,
+       sotc_tax_pct
+  FROM so_oth_tax_charges
+  WHERE sotc_bu = 'TVSA'
+    AND sotc_ord_no ='${SONO}'</t>
+  </si>
+  <si>
+    <t>ItemShipSetQuery</t>
+  </si>
+  <si>
+    <t>SELECT PS_SS_PROD_ID, PS_SS_PROD_REV,
+       ( SELECT prod_desc11
+          FROM products
+         WHERE prod_bu  = ps_bu
+           AND prod_id  = PS_SS_PROD_ID
+           AND prod_rev = PS_SS_PROD_REV) PSI_SS_PROD_DESC,
+           PS_SS_QTY,
+           (SELECT PROD_UOM
+             FROM products
+            WHERE prod_bu  = ps_bu
+              AND prod_id  = PS_SS_PROD_ID
+              AND prod_rev = PS_SS_PROD_REV)UOM
+FROM PROD_SHIPSET
+  where   PS_BU =  'TVSA'
+    and   PS_FG_PROD_ID  = '${SONO}'</t>
+  </si>
+  <si>
+    <t>SODBincludeAdvFlagColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_REQ_FLAG</t>
+  </si>
+  <si>
+    <t>SODBAdvToBeReceivedColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_TO_RCVD</t>
+  </si>
+  <si>
+    <t>SODBAdvPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_PCT</t>
+  </si>
+  <si>
+    <t>SODBAdvanceReceivedColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_RCVD</t>
+  </si>
+  <si>
+    <t>SODBAdvTaxPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_TAX_PCT</t>
+  </si>
+  <si>
+    <t>SODBAdvReceiptInProgressColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_RCPT_INPRG</t>
+  </si>
+  <si>
+    <t>SODBAdvDocumentNumberColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_DOC_NO</t>
+  </si>
+  <si>
+    <t>SODBUnitAddessColumnName</t>
+  </si>
+  <si>
+    <t>Unit State</t>
+  </si>
+  <si>
+    <t>SODBCustomerAddessColumnName</t>
+  </si>
+  <si>
+    <t>Customer State</t>
+  </si>
+  <si>
+    <t>SODBCessAmtColumnName</t>
+  </si>
+  <si>
+    <t>SOQ_CESS_AMT</t>
+  </si>
+  <si>
+    <t>SODBPaymentTermMaterialPercentageColumnName</t>
+  </si>
+  <si>
+    <t>TRLN_MTRL_PCT</t>
+  </si>
+  <si>
+    <t>SODBPaymentTermTaxPercentageColumnName</t>
+  </si>
+  <si>
+    <t>TRLN_TAX_PCT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBDOCNumberColumnName</t>
+  </si>
+  <si>
+    <t>DOC_NO</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderUnitColumnName</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderPrefixColumnName</t>
+  </si>
+  <si>
+    <t>ORD_PFX</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderNumberColumnName</t>
+  </si>
+  <si>
+    <t>ORD_NO</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderPartyIDColumnName</t>
+  </si>
+  <si>
+    <t>PARTY_ID</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderPercentageColumnName</t>
+  </si>
+  <si>
+    <t>ADV_PERCENTAGE</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderAdvAmountColumnName</t>
+  </si>
+  <si>
+    <t>ADV_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderCurrencyColumnName</t>
+  </si>
+  <si>
+    <t>CURCY</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderAmountColumnName</t>
+  </si>
+  <si>
+    <t>ORD_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderInProgressAmountColumnName</t>
+  </si>
+  <si>
+    <t>RCPT_INPROG_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderReceivedAmountColumnName</t>
+  </si>
+  <si>
+    <t>RCPT_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderClosedAmountColumnName</t>
+  </si>
+  <si>
+    <t>CLOSED_AMT</t>
+  </si>
+  <si>
+    <t>SODBHeaderDocumentStatusColumnName</t>
+  </si>
+  <si>
+    <t>SOH_STATUS</t>
+  </si>
+  <si>
+    <t>StockQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>STOCK_QTY_HAND</t>
+  </si>
+  <si>
+    <t>WH</t>
+  </si>
+  <si>
+    <t>RM KD</t>
+  </si>
+  <si>
+    <t>StockCostDBColumnName</t>
+  </si>
+  <si>
+    <t>STCOST_COST</t>
+  </si>
+  <si>
+    <t>PRRequestedQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>PRL_REQUESTED_QTY</t>
+  </si>
+  <si>
+    <t>PROrderedQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>PRL_ORDERED_QTY</t>
+  </si>
+  <si>
+    <t>SODBCGSTColumnName</t>
+  </si>
+  <si>
+    <t>CGST Amt.</t>
+  </si>
+  <si>
+    <t>SODBSGSTColumnName</t>
+  </si>
+  <si>
+    <t>SGST Amt.</t>
+  </si>
+  <si>
+    <t>SODBIGSTColumnName</t>
+  </si>
+  <si>
+    <t>IGST Amt.</t>
+  </si>
+  <si>
+    <t>PONO</t>
+  </si>
+  <si>
+    <t>${PONO}</t>
+  </si>
+  <si>
+    <t>SO_FREE_SAMPLE</t>
+  </si>
+  <si>
+    <t>SO - FREE SAMPLE</t>
+  </si>
+  <si>
+    <t>SO_FREE_REPLACEMENT</t>
+  </si>
+  <si>
+    <t>SO - FREE REPLACEMENT</t>
+  </si>
+  <si>
+    <t>SO_SCRAP</t>
+  </si>
+  <si>
+    <t>SO - SCRAP</t>
+  </si>
+  <si>
+    <t>SO_SERVICE</t>
+  </si>
+  <si>
+    <t>SO - SERVICE</t>
+  </si>
+  <si>
+    <t>SO_Local_Customer</t>
+  </si>
+  <si>
+    <t>CUS10002</t>
+  </si>
+  <si>
+    <t>SO_Local_Customer_Desc</t>
+  </si>
+  <si>
+    <t>SO_SEZ_CUSTOMER</t>
+  </si>
+  <si>
+    <t>CUS10005</t>
+  </si>
+  <si>
+    <t>SO_SEZ_CUSTOMER_DESC</t>
+  </si>
+  <si>
+    <t>SO_Demo_Exhibition</t>
+  </si>
+  <si>
+    <t>SO - DEMO / EXHN.</t>
+  </si>
+  <si>
+    <t>SODBCESSPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOQ_CESS_PCT</t>
+  </si>
+  <si>
+    <t>SODBCESSAmountColumnName</t>
+  </si>
+  <si>
+    <t>CESS_HSN_CODE</t>
+  </si>
+  <si>
+    <t>0074</t>
+  </si>
+  <si>
+    <t>SODBChargeAmountColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_CHRG_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeIGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_IGST_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeCGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_CGST_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeSGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_SGST_AMT</t>
+  </si>
+  <si>
+    <t>EntryCompletedStatus</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3044,151 +3509,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3213,188 +3541,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3430,259 +3578,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="53">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -3695,47 +3601,47 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3745,32 +3651,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3785,88 +3691,46 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="51" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="53">
+  <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal 2" xfId="49"/>
-    <cellStyle name="Normal 3" xfId="50"/>
-    <cellStyle name="Normal 2 2" xfId="51"/>
-    <cellStyle name="Normal 2 3" xfId="52"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2 2" xfId="3"/>
+    <cellStyle name="Normal 2 3" xfId="4"/>
+    <cellStyle name="Normal 3" xfId="2"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4128,17 +3992,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B510"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B562"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.287037037037" customWidth="1"/>
-    <col min="2" max="2" width="59.8518518518519" style="5" customWidth="1"/>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="59.85546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7002,20 +6866,20 @@
         <v>611</v>
       </c>
       <c r="B358" s="27" t="s">
-        <v>612</v>
+        <v>993</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" s="26" t="s">
+        <v>612</v>
+      </c>
+      <c r="B359" s="27" t="s">
         <v>613</v>
-      </c>
-      <c r="B359" s="27" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" s="26" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B360" s="25">
         <v>10</v>
@@ -7023,7 +6887,7 @@
     </row>
     <row r="361" spans="1:2">
       <c r="A361" s="26" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B361" s="25">
         <v>1000</v>
@@ -7031,7 +6895,7 @@
     </row>
     <row r="362" spans="1:2">
       <c r="A362" s="26" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B362" s="49">
         <v>5</v>
@@ -7039,7 +6903,7 @@
     </row>
     <row r="363" spans="1:2">
       <c r="A363" s="26" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B363" s="25">
         <v>1000</v>
@@ -7047,31 +6911,31 @@
     </row>
     <row r="364" spans="1:2">
       <c r="A364" s="26" t="s">
+        <v>618</v>
+      </c>
+      <c r="B364" s="25" t="s">
         <v>619</v>
-      </c>
-      <c r="B364" s="25" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="365" spans="1:2">
       <c r="A365" s="26" t="s">
+        <v>620</v>
+      </c>
+      <c r="B365" s="25" t="s">
         <v>621</v>
-      </c>
-      <c r="B365" s="25" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" s="26" t="s">
+        <v>622</v>
+      </c>
+      <c r="B366" s="25" t="s">
         <v>623</v>
-      </c>
-      <c r="B366" s="25" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" s="26" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B367" s="25">
         <v>10000039</v>
@@ -7079,71 +6943,71 @@
     </row>
     <row r="368" spans="1:2">
       <c r="A368" s="26" t="s">
+        <v>625</v>
+      </c>
+      <c r="B368" s="27" t="s">
         <v>626</v>
-      </c>
-      <c r="B368" s="27" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="369" spans="1:2">
       <c r="A369" s="26" t="s">
+        <v>627</v>
+      </c>
+      <c r="B369" s="27" t="s">
         <v>628</v>
-      </c>
-      <c r="B369" s="27" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" s="26" t="s">
+        <v>629</v>
+      </c>
+      <c r="B370" s="8" t="s">
         <v>630</v>
-      </c>
-      <c r="B370" s="8" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" s="26" t="s">
+        <v>631</v>
+      </c>
+      <c r="B371" s="8" t="s">
         <v>632</v>
-      </c>
-      <c r="B371" s="8" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" s="26" t="s">
+        <v>633</v>
+      </c>
+      <c r="B372" s="8" t="s">
         <v>634</v>
-      </c>
-      <c r="B372" s="8" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" s="26" t="s">
+        <v>635</v>
+      </c>
+      <c r="B373" s="8" t="s">
         <v>636</v>
-      </c>
-      <c r="B373" s="8" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" s="26" t="s">
+        <v>637</v>
+      </c>
+      <c r="B374" s="8" t="s">
         <v>638</v>
-      </c>
-      <c r="B374" s="8" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" s="26" t="s">
+        <v>639</v>
+      </c>
+      <c r="B375" s="8" t="s">
         <v>640</v>
-      </c>
-      <c r="B375" s="8" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="376" spans="1:2">
       <c r="A376" s="26" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B376" s="8" t="s">
         <v>222</v>
@@ -7151,279 +7015,279 @@
     </row>
     <row r="377" spans="1:2">
       <c r="A377" s="26" t="s">
+        <v>642</v>
+      </c>
+      <c r="B377" s="8" t="s">
         <v>643</v>
-      </c>
-      <c r="B377" s="8" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" s="26" t="s">
+        <v>644</v>
+      </c>
+      <c r="B378" s="8" t="s">
         <v>645</v>
-      </c>
-      <c r="B378" s="8" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" s="26" t="s">
+        <v>646</v>
+      </c>
+      <c r="B379" s="8" t="s">
         <v>647</v>
-      </c>
-      <c r="B379" s="8" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" s="26" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B380" s="8" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" s="26" t="s">
+        <v>649</v>
+      </c>
+      <c r="B381" s="8" t="s">
         <v>650</v>
-      </c>
-      <c r="B381" s="8" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" s="26" t="s">
+        <v>651</v>
+      </c>
+      <c r="B382" s="8" t="s">
         <v>652</v>
-      </c>
-      <c r="B382" s="8" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" s="26" t="s">
+        <v>653</v>
+      </c>
+      <c r="B383" s="8" t="s">
         <v>654</v>
-      </c>
-      <c r="B383" s="8" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" s="26" t="s">
+        <v>655</v>
+      </c>
+      <c r="B384" s="8" t="s">
         <v>656</v>
-      </c>
-      <c r="B384" s="8" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" s="26" t="s">
+        <v>657</v>
+      </c>
+      <c r="B385" s="8" t="s">
         <v>658</v>
-      </c>
-      <c r="B385" s="8" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B386" s="8" t="s">
         <v>660</v>
-      </c>
-      <c r="B386" s="8" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" s="26" t="s">
+        <v>661</v>
+      </c>
+      <c r="B387" s="8" t="s">
         <v>662</v>
-      </c>
-      <c r="B387" s="8" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" s="26" t="s">
+        <v>663</v>
+      </c>
+      <c r="B388" s="8" t="s">
         <v>664</v>
-      </c>
-      <c r="B388" s="8" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="B389" s="8" t="s">
         <v>666</v>
-      </c>
-      <c r="B389" s="8" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" s="26" t="s">
+        <v>667</v>
+      </c>
+      <c r="B390" s="8" t="s">
         <v>668</v>
-      </c>
-      <c r="B390" s="8" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" s="26" t="s">
+        <v>669</v>
+      </c>
+      <c r="B391" s="8" t="s">
         <v>670</v>
-      </c>
-      <c r="B391" s="8" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" s="26" t="s">
+        <v>671</v>
+      </c>
+      <c r="B392" s="8" t="s">
         <v>672</v>
-      </c>
-      <c r="B392" s="8" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" s="26" t="s">
+        <v>673</v>
+      </c>
+      <c r="B393" s="8" t="s">
         <v>674</v>
-      </c>
-      <c r="B393" s="8" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" s="26" t="s">
+        <v>675</v>
+      </c>
+      <c r="B394" s="8" t="s">
         <v>676</v>
-      </c>
-      <c r="B394" s="8" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" s="26" t="s">
+        <v>677</v>
+      </c>
+      <c r="B395" s="8" t="s">
         <v>678</v>
-      </c>
-      <c r="B395" s="8" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" s="26" t="s">
+        <v>679</v>
+      </c>
+      <c r="B396" s="8" t="s">
         <v>680</v>
-      </c>
-      <c r="B396" s="8" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" s="26" t="s">
+        <v>681</v>
+      </c>
+      <c r="B397" s="8" t="s">
         <v>682</v>
-      </c>
-      <c r="B397" s="8" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" s="26" t="s">
+        <v>683</v>
+      </c>
+      <c r="B398" s="8" t="s">
         <v>684</v>
-      </c>
-      <c r="B398" s="8" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" s="26" t="s">
+        <v>685</v>
+      </c>
+      <c r="B399" s="8" t="s">
         <v>686</v>
-      </c>
-      <c r="B399" s="8" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" s="26" t="s">
+        <v>687</v>
+      </c>
+      <c r="B400" s="8" t="s">
         <v>688</v>
-      </c>
-      <c r="B400" s="8" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" s="26" t="s">
+        <v>689</v>
+      </c>
+      <c r="B401" s="8" t="s">
         <v>690</v>
-      </c>
-      <c r="B401" s="8" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" s="26" t="s">
+        <v>691</v>
+      </c>
+      <c r="B402" s="8" t="s">
         <v>692</v>
-      </c>
-      <c r="B402" s="8" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" s="26" t="s">
+        <v>693</v>
+      </c>
+      <c r="B403" s="8" t="s">
         <v>694</v>
-      </c>
-      <c r="B403" s="8" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" s="26" t="s">
+        <v>695</v>
+      </c>
+      <c r="B404" s="8" t="s">
         <v>696</v>
-      </c>
-      <c r="B404" s="8" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" s="26" t="s">
+        <v>697</v>
+      </c>
+      <c r="B405" s="8" t="s">
         <v>698</v>
-      </c>
-      <c r="B405" s="8" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" s="26" t="s">
+        <v>699</v>
+      </c>
+      <c r="B406" s="8" t="s">
         <v>700</v>
-      </c>
-      <c r="B406" s="8" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" s="26" t="s">
+        <v>701</v>
+      </c>
+      <c r="B407" s="8" t="s">
         <v>702</v>
-      </c>
-      <c r="B407" s="8" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" s="26" t="s">
+        <v>703</v>
+      </c>
+      <c r="B408" s="8" t="s">
         <v>704</v>
-      </c>
-      <c r="B408" s="8" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="409" spans="1:2">
       <c r="A409" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B409" s="8" t="s">
         <v>706</v>
-      </c>
-      <c r="B409" s="8" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B410" s="8" t="s">
         <v>708</v>
-      </c>
-      <c r="B410" s="8" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B411" s="8" t="s">
         <v>391</v>
@@ -7431,47 +7295,47 @@
     </row>
     <row r="412" spans="1:2">
       <c r="A412" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B412" s="8" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B413" s="8" t="s">
         <v>712</v>
-      </c>
-      <c r="B413" s="8" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B414" s="8" t="s">
         <v>714</v>
-      </c>
-      <c r="B414" s="8" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B415" s="8" t="s">
         <v>716</v>
-      </c>
-      <c r="B415" s="8" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B416" s="8" t="s">
         <v>718</v>
-      </c>
-      <c r="B416" s="8" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B417" s="8" t="s">
         <v>117</v>
@@ -7479,39 +7343,39 @@
     </row>
     <row r="418" spans="1:2">
       <c r="A418" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B418" s="8" t="s">
         <v>721</v>
-      </c>
-      <c r="B418" s="8" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B419" s="8" t="s">
         <v>723</v>
-      </c>
-      <c r="B419" s="8" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B420" s="8" t="s">
         <v>725</v>
-      </c>
-      <c r="B420" s="8" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B422" s="8" t="s">
         <v>568</v>
@@ -7519,151 +7383,151 @@
     </row>
     <row r="423" spans="1:2">
       <c r="A423" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B423" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B424" s="8" t="s">
         <v>730</v>
-      </c>
-      <c r="B424" s="8" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="425" spans="1:2">
       <c r="A425" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="B425" s="8" t="s">
         <v>732</v>
-      </c>
-      <c r="B425" s="8" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" s="12" t="s">
+        <v>733</v>
+      </c>
+      <c r="B426" s="14" t="s">
         <v>734</v>
-      </c>
-      <c r="B426" s="14" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="427" spans="1:2">
       <c r="A427" s="12" t="s">
+        <v>735</v>
+      </c>
+      <c r="B427" s="14" t="s">
         <v>736</v>
-      </c>
-      <c r="B427" s="14" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" s="12" t="s">
+        <v>737</v>
+      </c>
+      <c r="B428" s="14" t="s">
         <v>738</v>
-      </c>
-      <c r="B428" s="14" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="429" spans="1:2">
       <c r="A429" s="12" t="s">
+        <v>739</v>
+      </c>
+      <c r="B429" s="14" t="s">
         <v>740</v>
-      </c>
-      <c r="B429" s="14" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" s="12" t="s">
+        <v>741</v>
+      </c>
+      <c r="B430" s="14" t="s">
         <v>742</v>
-      </c>
-      <c r="B430" s="14" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" s="12" t="s">
+        <v>743</v>
+      </c>
+      <c r="B431" s="14" t="s">
         <v>744</v>
-      </c>
-      <c r="B431" s="14" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" s="12" t="s">
+        <v>745</v>
+      </c>
+      <c r="B432" s="14" t="s">
         <v>746</v>
-      </c>
-      <c r="B432" s="14" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" s="12" t="s">
+        <v>747</v>
+      </c>
+      <c r="B433" s="14" t="s">
         <v>748</v>
-      </c>
-      <c r="B433" s="14" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="B434" s="14" t="s">
         <v>750</v>
-      </c>
-      <c r="B434" s="14" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" s="12" t="s">
+        <v>751</v>
+      </c>
+      <c r="B435" s="14" t="s">
         <v>752</v>
-      </c>
-      <c r="B435" s="14" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" s="12" t="s">
+        <v>753</v>
+      </c>
+      <c r="B436" s="14" t="s">
         <v>754</v>
-      </c>
-      <c r="B436" s="14" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="B437" s="14" t="s">
         <v>756</v>
-      </c>
-      <c r="B437" s="14" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="B438" s="14" t="s">
         <v>758</v>
-      </c>
-      <c r="B438" s="14" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" s="12" t="s">
+        <v>759</v>
+      </c>
+      <c r="B439" s="14" t="s">
         <v>760</v>
-      </c>
-      <c r="B439" s="14" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" s="30" t="s">
+        <v>761</v>
+      </c>
+      <c r="B440" s="29" t="s">
         <v>762</v>
-      </c>
-      <c r="B440" s="29" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" s="50" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B441" s="51" t="s">
         <v>194</v>
@@ -7671,66 +7535,66 @@
     </row>
     <row r="442" spans="1:2">
       <c r="A442" s="50" t="s">
+        <v>764</v>
+      </c>
+      <c r="B442" s="51" t="s">
         <v>765</v>
-      </c>
-      <c r="B442" s="51" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" s="50" t="s">
+        <v>766</v>
+      </c>
+      <c r="B443" s="51" t="s">
         <v>767</v>
-      </c>
-      <c r="B443" s="51" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" s="50" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B444" s="51" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" s="50" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B445" s="51" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" s="50" t="s">
+        <v>770</v>
+      </c>
+      <c r="B446" s="52" t="s">
         <v>771</v>
-      </c>
-      <c r="B446" s="52" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" s="50" t="s">
+        <v>772</v>
+      </c>
+      <c r="B447" s="52" t="s">
         <v>773</v>
-      </c>
-      <c r="B447" s="52" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="448" spans="1:2">
       <c r="A448" s="50" t="s">
+        <v>774</v>
+      </c>
+      <c r="B448" s="51" t="s">
         <v>775</v>
-      </c>
-      <c r="B448" s="51" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" s="50" t="s">
+        <v>776</v>
+      </c>
+      <c r="B449" s="51" t="s">
         <v>777</v>
-      </c>
-      <c r="B449" s="51" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -7759,15 +7623,15 @@
     </row>
     <row r="453" spans="1:2">
       <c r="A453" s="53" t="s">
+        <v>778</v>
+      </c>
+      <c r="B453" s="54" t="s">
         <v>779</v>
-      </c>
-      <c r="B453" s="54" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" s="50" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B454" s="55" t="s">
         <v>77</v>
@@ -7775,7 +7639,7 @@
     </row>
     <row r="455" spans="1:2">
       <c r="A455" s="50" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B455" s="55" t="s">
         <v>83</v>
@@ -7791,42 +7655,42 @@
     </row>
     <row r="457" spans="1:2">
       <c r="A457" s="50" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B457" s="52" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" s="50" t="s">
+        <v>783</v>
+      </c>
+      <c r="B458" s="52" t="s">
         <v>784</v>
-      </c>
-      <c r="B458" s="52" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" s="50" t="s">
+        <v>785</v>
+      </c>
+      <c r="B459" s="51" t="s">
         <v>786</v>
-      </c>
-      <c r="B459" s="51" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" s="50" t="s">
+        <v>787</v>
+      </c>
+      <c r="B460" s="51" t="s">
         <v>788</v>
-      </c>
-      <c r="B460" s="51" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" s="50" t="s">
+        <v>789</v>
+      </c>
+      <c r="B461" s="51" t="s">
         <v>790</v>
-      </c>
-      <c r="B461" s="51" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -7871,7 +7735,7 @@
     </row>
     <row r="467" spans="1:2">
       <c r="A467" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B467" s="8" t="s">
         <v>357</v>
@@ -7879,39 +7743,39 @@
     </row>
     <row r="468" spans="1:2">
       <c r="A468" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B468" s="8" t="s">
         <v>793</v>
-      </c>
-      <c r="B468" s="8" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="B469" s="8" t="s">
         <v>795</v>
-      </c>
-      <c r="B469" s="8" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B470" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B471" s="8" t="s">
         <v>798</v>
-      </c>
-      <c r="B471" s="8" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B472" s="8" t="s">
         <v>229</v>
@@ -7919,7 +7783,7 @@
     </row>
     <row r="473" spans="1:2">
       <c r="A473" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B473" s="8" t="s">
         <v>281</v>
@@ -7927,71 +7791,71 @@
     </row>
     <row r="474" spans="1:2">
       <c r="A474" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B474" s="8" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="B475" s="8" t="s">
         <v>803</v>
-      </c>
-      <c r="B475" s="8" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B476" s="8" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B477" s="8" t="s">
         <v>805</v>
-      </c>
-      <c r="B477" s="8" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="B478" s="8" t="s">
         <v>807</v>
-      </c>
-      <c r="B478" s="8" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B479" s="45" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B480" s="8" t="s">
         <v>810</v>
-      </c>
-      <c r="B480" s="8" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="B481" s="8" t="s">
         <v>812</v>
-      </c>
-      <c r="B481" s="8" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B482" s="8" t="s">
         <v>229</v>
@@ -7999,47 +7863,47 @@
     </row>
     <row r="483" spans="1:2">
       <c r="A483" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="B483" s="8" t="s">
         <v>815</v>
-      </c>
-      <c r="B483" s="8" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B484" s="8" t="s">
         <v>817</v>
-      </c>
-      <c r="B484" s="8" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="B485" s="8" t="s">
         <v>819</v>
-      </c>
-      <c r="B485" s="8" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B486" s="8" t="s">
         <v>821</v>
-      </c>
-      <c r="B486" s="8" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B487" s="8" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B488" s="8" t="s">
         <v>229</v>
@@ -8047,7 +7911,7 @@
     </row>
     <row r="489" spans="1:2">
       <c r="A489" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B489" s="8" t="s">
         <v>148</v>
@@ -8055,135 +7919,135 @@
     </row>
     <row r="490" spans="1:2">
       <c r="A490" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B490" s="8" t="s">
         <v>826</v>
-      </c>
-      <c r="B490" s="8" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B491" s="8" t="s">
         <v>828</v>
-      </c>
-      <c r="B491" s="8" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B492" s="8" t="s">
         <v>830</v>
-      </c>
-      <c r="B492" s="8" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B493" s="8" t="s">
         <v>832</v>
-      </c>
-      <c r="B493" s="8" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B494" s="8" t="s">
         <v>834</v>
-      </c>
-      <c r="B494" s="8" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B495" s="8" t="s">
         <v>836</v>
-      </c>
-      <c r="B495" s="8" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B496" s="8" t="s">
         <v>838</v>
-      </c>
-      <c r="B496" s="8" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="497" spans="1:2">
       <c r="A497" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B497" s="8" t="s">
         <v>840</v>
-      </c>
-      <c r="B497" s="8" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B498" s="8" t="s">
         <v>842</v>
-      </c>
-      <c r="B498" s="8" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="499" spans="1:2">
       <c r="A499" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B499" s="8" t="s">
         <v>844</v>
-      </c>
-      <c r="B499" s="8" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B500" s="8" t="s">
         <v>846</v>
-      </c>
-      <c r="B500" s="8" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B501" s="8" t="s">
         <v>848</v>
-      </c>
-      <c r="B501" s="8" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="502" spans="1:2">
       <c r="A502" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B502" s="8" t="s">
         <v>850</v>
-      </c>
-      <c r="B502" s="8" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="503" spans="1:2">
       <c r="A503" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B503" s="8" t="s">
         <v>852</v>
-      </c>
-      <c r="B503" s="8" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="504" spans="1:2">
       <c r="A504" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B504" s="8" t="s">
         <v>854</v>
-      </c>
-      <c r="B504" s="8" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B505" s="8" t="s">
         <v>856</v>
-      </c>
-      <c r="B505" s="8" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="506" spans="1:2">
       <c r="A506" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B506" s="8" t="s">
         <v>7</v>
@@ -8191,15 +8055,15 @@
     </row>
     <row r="507" spans="1:2">
       <c r="A507" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B507" s="8" t="s">
         <v>859</v>
-      </c>
-      <c r="B507" s="8" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="508" spans="1:2">
       <c r="A508" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B508" s="8" t="s">
         <v>307</v>
@@ -8207,33 +8071,447 @@
     </row>
     <row r="509" spans="1:2">
       <c r="A509" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B509" s="8" t="s">
         <v>862</v>
-      </c>
-      <c r="B509" s="8" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B510" s="8" t="s">
         <v>864</v>
       </c>
-      <c r="B510" s="8" t="s">
-        <v>865</v>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B511" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" s="26" t="s">
+        <v>895</v>
+      </c>
+      <c r="B512" s="8" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="26" t="s">
+        <v>897</v>
+      </c>
+      <c r="B513" s="8" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="26" t="s">
+        <v>899</v>
+      </c>
+      <c r="B514" s="8" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="26" t="s">
+        <v>901</v>
+      </c>
+      <c r="B515" s="8" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="26" t="s">
+        <v>903</v>
+      </c>
+      <c r="B516" s="8" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" s="26" t="s">
+        <v>905</v>
+      </c>
+      <c r="B517" s="8" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="26" t="s">
+        <v>907</v>
+      </c>
+      <c r="B518" s="8" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="26" t="s">
+        <v>909</v>
+      </c>
+      <c r="B519" s="8" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="26" t="s">
+        <v>911</v>
+      </c>
+      <c r="B520" s="8" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="26" t="s">
+        <v>913</v>
+      </c>
+      <c r="B521" s="8" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="26" t="s">
+        <v>915</v>
+      </c>
+      <c r="B522" s="8" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="26" t="s">
+        <v>917</v>
+      </c>
+      <c r="B523" s="8" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="26" t="s">
+        <v>919</v>
+      </c>
+      <c r="B524" s="8" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="26" t="s">
+        <v>921</v>
+      </c>
+      <c r="B525" s="8" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" s="26" t="s">
+        <v>923</v>
+      </c>
+      <c r="B526" s="8" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" s="26" t="s">
+        <v>925</v>
+      </c>
+      <c r="B527" s="8" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" s="26" t="s">
+        <v>927</v>
+      </c>
+      <c r="B528" s="8" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" s="26" t="s">
+        <v>929</v>
+      </c>
+      <c r="B529" s="8" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" s="26" t="s">
+        <v>931</v>
+      </c>
+      <c r="B530" s="8" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="26" t="s">
+        <v>933</v>
+      </c>
+      <c r="B531" s="8" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" s="26" t="s">
+        <v>935</v>
+      </c>
+      <c r="B532" s="8" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" s="26" t="s">
+        <v>937</v>
+      </c>
+      <c r="B533" s="8" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" s="26" t="s">
+        <v>939</v>
+      </c>
+      <c r="B534" s="8" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="26" t="s">
+        <v>941</v>
+      </c>
+      <c r="B535" s="8" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" s="26" t="s">
+        <v>943</v>
+      </c>
+      <c r="B536" s="8" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" s="26" t="s">
+        <v>945</v>
+      </c>
+      <c r="B537" s="8" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" s="26" t="s">
+        <v>947</v>
+      </c>
+      <c r="B538" s="8" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="26" t="s">
+        <v>949</v>
+      </c>
+      <c r="B539" s="8" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" s="26" t="s">
+        <v>951</v>
+      </c>
+      <c r="B540" s="8" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" s="26" t="s">
+        <v>953</v>
+      </c>
+      <c r="B541" s="8" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" s="26" t="s">
+        <v>955</v>
+      </c>
+      <c r="B542" s="8" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="26" t="s">
+        <v>957</v>
+      </c>
+      <c r="B543" s="8" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" t="s">
+        <v>959</v>
+      </c>
+      <c r="B544" s="8" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" s="26" t="s">
+        <v>961</v>
+      </c>
+      <c r="B545" s="8" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" s="58" t="s">
+        <v>963</v>
+      </c>
+      <c r="B546" s="8" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" s="58" t="s">
+        <v>965</v>
+      </c>
+      <c r="B547" s="8" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" s="58" t="s">
+        <v>967</v>
+      </c>
+      <c r="B548" s="8" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" s="59" t="s">
+        <v>969</v>
+      </c>
+      <c r="B549" s="8" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" s="59" t="s">
+        <v>971</v>
+      </c>
+      <c r="B550" s="8" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" s="58" t="s">
+        <v>973</v>
+      </c>
+      <c r="B551" s="60" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" s="59" t="s">
+        <v>974</v>
+      </c>
+      <c r="B552" s="8" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" s="59" t="s">
+        <v>976</v>
+      </c>
+      <c r="B553" s="8" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="58" t="s">
+        <v>977</v>
+      </c>
+      <c r="B554" s="8" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" s="26" t="s">
+        <v>979</v>
+      </c>
+      <c r="B555" s="8" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" s="26" t="s">
+        <v>981</v>
+      </c>
+      <c r="B556" s="8" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="59" t="s">
+        <v>982</v>
+      </c>
+      <c r="B557" s="8" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="26" t="s">
+        <v>984</v>
+      </c>
+      <c r="B558" s="8" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="26" t="s">
+        <v>986</v>
+      </c>
+      <c r="B559" s="8" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="26" t="s">
+        <v>988</v>
+      </c>
+      <c r="B560" s="8" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="26" t="s">
+        <v>990</v>
+      </c>
+      <c r="B561" s="8" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="26" t="s">
+        <v>992</v>
+      </c>
+      <c r="B562" s="8" t="s">
+        <v>551</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.8518518518519" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8245,89 +8523,125 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="108.95" customHeight="1" spans="1:2">
+    <row r="2" spans="1:2" ht="108.95" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>866</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="114" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>867</v>
       </c>
-    </row>
-    <row r="3" ht="114" customHeight="1" spans="1:2">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="80.25" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>869</v>
       </c>
-    </row>
-    <row r="4" ht="80.25" customHeight="1" spans="1:2">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="69.75" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>871</v>
       </c>
-    </row>
-    <row r="5" ht="69.75" customHeight="1" spans="1:2">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="51.75" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>873</v>
       </c>
-    </row>
-    <row r="6" ht="187.2" spans="1:2">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="18" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="7" ht="409.5" spans="1:2">
-      <c r="A7" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="B7" s="4" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="39" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>877</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
+      <c r="B9" s="4" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="18" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="26.25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="28.5" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="24" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="36" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="45" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>894</v>
+      </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2"/>
@@ -8339,6 +8653,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="985">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -2626,6 +2626,327 @@
   </si>
   <si>
     <t>109</t>
+  </si>
+  <si>
+    <t>GwlDissimilarItem</t>
+  </si>
+  <si>
+    <t>GWL_Item_Dissimilar_02</t>
+  </si>
+  <si>
+    <t>POPrefix</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>GWL_Item_similar_03</t>
+  </si>
+  <si>
+    <t>SixValue</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>POAServiceSheet</t>
+  </si>
+  <si>
+    <t>SODBincludeAdvFlagColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_REQ_FLAG</t>
+  </si>
+  <si>
+    <t>SODBAdvToBeReceivedColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_TO_RCVD</t>
+  </si>
+  <si>
+    <t>SODBAdvPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_PCT</t>
+  </si>
+  <si>
+    <t>SODBAdvanceReceivedColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_RCVD</t>
+  </si>
+  <si>
+    <t>SODBAdvTaxPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_TAX_PCT</t>
+  </si>
+  <si>
+    <t>SODBAdvReceiptInProgressColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_RCPT_INPRG</t>
+  </si>
+  <si>
+    <t>SODBAdvDocumentNumberColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_DOC_NO</t>
+  </si>
+  <si>
+    <t>SODBUnitAddessColumnName</t>
+  </si>
+  <si>
+    <t>Unit State</t>
+  </si>
+  <si>
+    <t>SODBCustomerAddessColumnName</t>
+  </si>
+  <si>
+    <t>Customer State</t>
+  </si>
+  <si>
+    <t>SODBCessAmtColumnName</t>
+  </si>
+  <si>
+    <t>SOQ_CESS_AMT</t>
+  </si>
+  <si>
+    <t>SODBPaymentTermMaterialPercentageColumnName</t>
+  </si>
+  <si>
+    <t>TRLN_MTRL_PCT</t>
+  </si>
+  <si>
+    <t>SODBPaymentTermTaxPercentageColumnName</t>
+  </si>
+  <si>
+    <t>TRLN_TAX_PCT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBDOCNumberColumnName</t>
+  </si>
+  <si>
+    <t>DOC_NO</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderUnitColumnName</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderPrefixColumnName</t>
+  </si>
+  <si>
+    <t>ORD_PFX</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderNumberColumnName</t>
+  </si>
+  <si>
+    <t>ORD_NO</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderPartyIDColumnName</t>
+  </si>
+  <si>
+    <t>PARTY_ID</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderPercentageColumnName</t>
+  </si>
+  <si>
+    <t>ADV_PERCENTAGE</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderAdvAmountColumnName</t>
+  </si>
+  <si>
+    <t>ADV_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderCurrencyColumnName</t>
+  </si>
+  <si>
+    <t>CURCY</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderAmountColumnName</t>
+  </si>
+  <si>
+    <t>ORD_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderInProgressAmountColumnName</t>
+  </si>
+  <si>
+    <t>RCPT_INPROG_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderReceivedAmountColumnName</t>
+  </si>
+  <si>
+    <t>RCPT_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderClosedAmountColumnName</t>
+  </si>
+  <si>
+    <t>CLOSED_AMT</t>
+  </si>
+  <si>
+    <t>SODBHeaderDocumentStatusColumnName</t>
+  </si>
+  <si>
+    <t>SOH_STATUS</t>
+  </si>
+  <si>
+    <t>StockQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>STOCK_QTY_HAND</t>
+  </si>
+  <si>
+    <t>WH</t>
+  </si>
+  <si>
+    <t>RM KD</t>
+  </si>
+  <si>
+    <t>StockCostDBColumnName</t>
+  </si>
+  <si>
+    <t>STCOST_COST</t>
+  </si>
+  <si>
+    <t>PRRequestedQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>PRL_REQUESTED_QTY</t>
+  </si>
+  <si>
+    <t>PROrderedQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>PRL_ORDERED_QTY</t>
+  </si>
+  <si>
+    <t>SODBCGSTColumnName</t>
+  </si>
+  <si>
+    <t>CGST Amt.</t>
+  </si>
+  <si>
+    <t>SODBSGSTColumnName</t>
+  </si>
+  <si>
+    <t>SGST Amt.</t>
+  </si>
+  <si>
+    <t>SODBIGSTColumnName</t>
+  </si>
+  <si>
+    <t>IGST Amt.</t>
+  </si>
+  <si>
+    <t>PONO</t>
+  </si>
+  <si>
+    <t>${PONO}</t>
+  </si>
+  <si>
+    <t>SO_FREE_SAMPLE</t>
+  </si>
+  <si>
+    <t>SO - FREE SAMPLE</t>
+  </si>
+  <si>
+    <t>SO_FREE_REPLACEMENT</t>
+  </si>
+  <si>
+    <t>SO - FREE REPLACEMENT</t>
+  </si>
+  <si>
+    <t>SO_SCRAP</t>
+  </si>
+  <si>
+    <t>SO - SCRAP</t>
+  </si>
+  <si>
+    <t>SO_SERVICE</t>
+  </si>
+  <si>
+    <t>SO - SERVICE</t>
+  </si>
+  <si>
+    <t>SO_Local_Customer</t>
+  </si>
+  <si>
+    <t>CUS10002</t>
+  </si>
+  <si>
+    <t>SO_Local_Customer_Desc</t>
+  </si>
+  <si>
+    <t>SO_SEZ_CUSTOMER</t>
+  </si>
+  <si>
+    <t>CUS10005</t>
+  </si>
+  <si>
+    <t>SO_SEZ_CUSTOMER_DESC</t>
+  </si>
+  <si>
+    <t>SO_Demo_Exhibition</t>
+  </si>
+  <si>
+    <t>SO - DEMO / EXHN.</t>
+  </si>
+  <si>
+    <t>SODBCESSPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOQ_CESS_PCT</t>
+  </si>
+  <si>
+    <t>SODBCESSAmountColumnName</t>
+  </si>
+  <si>
+    <t>CESS_HSN_CODE</t>
+  </si>
+  <si>
+    <t>0074</t>
+  </si>
+  <si>
+    <t>SODBChargeAmountColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_CHRG_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeIGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_IGST_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeCGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_CGST_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeSGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_SGST_AMT</t>
+  </si>
+  <si>
+    <t>EntryCompletedStatus</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2993,7 +3314,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3042,6 +3363,13 @@
       <sz val="10"/>
       <name val="Consolas"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -3546,16 +3874,13 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3564,115 +3889,118 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3680,15 +4008,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3811,6 +4136,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="51" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4134,18 +4468,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B568"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="34.287037037037" customWidth="1"/>
-    <col min="2" max="2" width="59.8518518518519" style="5" customWidth="1"/>
+    <col min="2" max="2" width="59.8518518518519" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4153,7 +4487,7 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
     </row>
@@ -4161,7 +4495,7 @@
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4169,7 +4503,7 @@
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4177,7 +4511,7 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4185,7 +4519,7 @@
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4193,7 +4527,7 @@
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4201,7 +4535,7 @@
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4209,7 +4543,7 @@
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4217,7 +4551,7 @@
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4225,7 +4559,7 @@
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4233,7 +4567,7 @@
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>23</v>
       </c>
     </row>
@@ -4241,7 +4575,7 @@
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -4249,7 +4583,7 @@
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4257,7 +4591,7 @@
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>5</v>
       </c>
     </row>
@@ -4265,7 +4599,7 @@
       <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>150</v>
       </c>
     </row>
@@ -4273,7 +4607,7 @@
       <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4281,7 +4615,7 @@
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4289,7 +4623,7 @@
       <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4297,7 +4631,7 @@
       <c r="A20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4305,7 +4639,7 @@
       <c r="A21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4313,7 +4647,7 @@
       <c r="A22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4321,7 +4655,7 @@
       <c r="A23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4329,7 +4663,7 @@
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4337,7 +4671,7 @@
       <c r="A25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4345,7 +4679,7 @@
       <c r="A26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4353,7 +4687,7 @@
       <c r="A27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4361,7 +4695,7 @@
       <c r="A28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4369,7 +4703,7 @@
       <c r="A29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4377,7 +4711,7 @@
       <c r="A30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4385,7 +4719,7 @@
       <c r="A31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4393,7 +4727,7 @@
       <c r="A32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4401,7 +4735,7 @@
       <c r="A33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4409,7 +4743,7 @@
       <c r="A34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4417,7 +4751,7 @@
       <c r="A35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4425,7 +4759,7 @@
       <c r="A36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4433,7 +4767,7 @@
       <c r="A37" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>71</v>
       </c>
     </row>
@@ -4441,7 +4775,7 @@
       <c r="A38" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4449,7 +4783,7 @@
       <c r="A39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4457,7 +4791,7 @@
       <c r="A40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="7" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4465,7 +4799,7 @@
       <c r="A41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4473,7 +4807,7 @@
       <c r="A42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="7" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4481,7 +4815,7 @@
       <c r="A43" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4489,7 +4823,7 @@
       <c r="A44" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4497,7 +4831,7 @@
       <c r="A45" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4505,7 +4839,7 @@
       <c r="A46" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>89</v>
       </c>
     </row>
@@ -4513,7 +4847,7 @@
       <c r="A47" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4521,7 +4855,7 @@
       <c r="A48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>93</v>
       </c>
     </row>
@@ -4529,7 +4863,7 @@
       <c r="A49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="7">
         <v>5</v>
       </c>
     </row>
@@ -4537,7 +4871,7 @@
       <c r="A50" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4545,7 +4879,7 @@
       <c r="A51" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="7" t="s">
         <v>97</v>
       </c>
     </row>
@@ -4553,471 +4887,471 @@
       <c r="A52" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="9" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="9" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="9" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="9" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="9" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="9" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="9" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="9" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="9" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="9" t="s">
+      <c r="A64" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="9" t="s">
+      <c r="A65" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="9">
         <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="9" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="9" t="s">
+      <c r="A67" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="9" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="9" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="9">
         <v>2012</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="9" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="9" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B73" s="9" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="9" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="9" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="9">
         <v>202425</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="9" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="9" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="12" t="s">
+      <c r="A80" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="12" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="13" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="12" t="s">
+      <c r="A83" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="12" t="s">
+      <c r="A84" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="13" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="12" t="s">
+      <c r="A85" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="13" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="12" t="s">
+      <c r="A86" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="12" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="15" t="s">
+      <c r="A88" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="15" t="s">
+      <c r="A89" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="16" t="s">
+      <c r="A90" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="15" t="s">
+      <c r="A91" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="12" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="15" t="s">
+      <c r="A92" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="12" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="15" t="s">
+      <c r="A93" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="15" t="s">
+      <c r="A94" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="12" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="15" t="s">
+      <c r="A95" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B95" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="15" t="s">
+      <c r="A96" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="12" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="15" t="s">
+      <c r="A97" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="12" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="15" t="s">
+      <c r="A98" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="12" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="15" t="s">
+      <c r="A99" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="17" t="s">
+      <c r="A100" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="B100" s="18" t="s">
+      <c r="B100" s="17" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="17" t="s">
+      <c r="A101" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="B101" s="19" t="s">
+      <c r="B101" s="18" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="17" t="s">
+      <c r="A102" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B102" s="18" t="s">
+      <c r="B102" s="17" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="17" t="s">
+      <c r="A103" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B103" s="18" t="s">
+      <c r="B103" s="17" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B104" s="19">
+      <c r="B104" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="20" t="s">
+      <c r="A105" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="B105" s="21" t="s">
+      <c r="B105" s="20" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="20" t="s">
+      <c r="A106" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="B106" s="22" t="s">
+      <c r="B106" s="21" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="20" t="s">
+      <c r="A107" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="B107" s="23">
+      <c r="B107" s="22">
         <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="20" t="s">
+      <c r="A108" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="B108" s="21" t="s">
+      <c r="B108" s="20" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="20" t="s">
+      <c r="A109" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="B109" s="24" t="s">
+      <c r="B109" s="23" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="20" t="s">
+      <c r="A110" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="B110" s="23">
+      <c r="B110" s="22">
         <v>100</v>
       </c>
     </row>
@@ -5025,47 +5359,47 @@
       <c r="A111" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B111" s="25" t="s">
+      <c r="B111" s="24" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="26" t="s">
+      <c r="A112" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="B112" s="27" t="s">
+      <c r="B112" s="26" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="26" t="s">
+      <c r="A113" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="B113" s="27" t="s">
+      <c r="B113" s="26" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="26" t="s">
+      <c r="A114" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="B114" s="25" t="s">
+      <c r="B114" s="24" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="B115" s="25" t="s">
+      <c r="B115" s="24" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="26" t="s">
+      <c r="A116" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="B116" s="25" t="s">
+      <c r="B116" s="24" t="s">
         <v>214</v>
       </c>
     </row>
@@ -5073,7 +5407,7 @@
       <c r="A117" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B117" s="25" t="s">
+      <c r="B117" s="24" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5081,319 +5415,319 @@
       <c r="A118" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B118" s="25">
+      <c r="B118" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="28" t="s">
+      <c r="A119" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="B119" s="29" t="s">
+      <c r="B119" s="28" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="28" t="s">
+      <c r="A120" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="B120" s="29" t="s">
+      <c r="B120" s="28" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="28" t="s">
+      <c r="A121" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="B121" s="29" t="s">
+      <c r="B121" s="28" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="28" t="s">
+      <c r="A122" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="B122" s="29" t="s">
+      <c r="B122" s="28" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="28" t="s">
+      <c r="A123" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="B123" s="29" t="s">
+      <c r="B123" s="28" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="28" t="s">
+      <c r="A124" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="B124" s="29" t="s">
+      <c r="B124" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="28" t="s">
+      <c r="A125" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="B125" s="29" t="s">
+      <c r="B125" s="28" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="28" t="s">
+      <c r="A126" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="B126" s="29" t="s">
+      <c r="B126" s="28" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="28" t="s">
+      <c r="A127" s="27" t="s">
         <v>232</v>
       </c>
-      <c r="B127" s="29" t="s">
+      <c r="B127" s="28" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="28" t="s">
+      <c r="A128" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="B128" s="29" t="s">
+      <c r="B128" s="28" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="28" t="s">
+      <c r="A129" s="27" t="s">
         <v>236</v>
       </c>
-      <c r="B129" s="29" t="s">
+      <c r="B129" s="28" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="28" t="s">
+      <c r="A130" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="B130" s="29" t="s">
+      <c r="B130" s="28" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="28" t="s">
+      <c r="A131" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="B131" s="29" t="s">
+      <c r="B131" s="28" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="28" t="s">
+      <c r="A132" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="B132" s="29" t="s">
+      <c r="B132" s="28" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="28" t="s">
+      <c r="A133" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="B133" s="29" t="s">
+      <c r="B133" s="28" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="28" t="s">
+      <c r="A134" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="B134" s="29" t="s">
+      <c r="B134" s="28" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="28" t="s">
+      <c r="A135" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="B135" s="29" t="s">
+      <c r="B135" s="28" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="28" t="s">
+      <c r="A136" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="B136" s="29" t="s">
+      <c r="B136" s="28" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="28" t="s">
+      <c r="A137" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="B137" s="29" t="s">
+      <c r="B137" s="28" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="28" t="s">
+      <c r="A138" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="B138" s="29" t="s">
+      <c r="B138" s="28" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="28" t="s">
+      <c r="A139" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="B139" s="29" t="s">
+      <c r="B139" s="28" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="28" t="s">
+      <c r="A140" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="B140" s="29" t="s">
+      <c r="B140" s="28" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="28" t="s">
+      <c r="A141" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="B141" s="29" t="s">
+      <c r="B141" s="28" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="28" t="s">
+      <c r="A142" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="B142" s="29" t="s">
+      <c r="B142" s="28" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="28" t="s">
+      <c r="A143" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="B143" s="29" t="s">
+      <c r="B143" s="28" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="28" t="s">
+      <c r="A144" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="B144" s="29" t="s">
+      <c r="B144" s="28" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="28" t="s">
+      <c r="A145" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="B145" s="29" t="s">
+      <c r="B145" s="28" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="28" t="s">
+      <c r="A146" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="B146" s="29" t="s">
+      <c r="B146" s="28" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="28" t="s">
+      <c r="A147" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="B147" s="29" t="s">
+      <c r="B147" s="28" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="28" t="s">
+      <c r="A148" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="B148" s="29" t="s">
+      <c r="B148" s="28" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="28" t="s">
+      <c r="A149" s="27" t="s">
         <v>262</v>
       </c>
-      <c r="B149" s="29" t="s">
+      <c r="B149" s="28" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="28" t="s">
+      <c r="A150" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="B150" s="29" t="s">
+      <c r="B150" s="28" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="30" t="s">
+      <c r="A151" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="B151" s="29" t="s">
+      <c r="B151" s="28" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="30" t="s">
+      <c r="A152" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="B152" s="29" t="s">
+      <c r="B152" s="28" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="30" t="s">
+      <c r="A153" s="29" t="s">
         <v>268</v>
       </c>
-      <c r="B153" s="29" t="s">
+      <c r="B153" s="28" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="30" t="s">
+      <c r="A154" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="B154" s="29" t="s">
+      <c r="B154" s="28" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="30" t="s">
+      <c r="A155" s="29" t="s">
         <v>272</v>
       </c>
-      <c r="B155" s="29" t="s">
+      <c r="B155" s="28" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="30" t="s">
+      <c r="A156" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="B156" s="29" t="s">
+      <c r="B156" s="28" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="31" t="s">
+      <c r="A157" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="B157" s="32" t="s">
+      <c r="B157" s="31" t="s">
         <v>277</v>
       </c>
     </row>
@@ -5401,263 +5735,263 @@
       <c r="A158" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B158" s="25" t="s">
+      <c r="B158" s="24" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="12" t="s">
+      <c r="A159" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="B159" s="33" t="s">
+      <c r="B159" s="32" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="12" t="s">
+      <c r="A160" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B160" s="13" t="s">
+      <c r="B160" s="12" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="12" t="s">
+      <c r="A161" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="B161" s="14" t="s">
+      <c r="B161" s="13" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="12" t="s">
+      <c r="A162" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="B162" s="13" t="s">
+      <c r="B162" s="12" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="12" t="s">
+      <c r="A163" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B163" s="13" t="s">
+      <c r="B163" s="12" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="12" t="s">
+      <c r="A164" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="B164" s="14" t="s">
+      <c r="B164" s="13" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="12" t="s">
+      <c r="A165" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="B165" s="14" t="s">
+      <c r="B165" s="13" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="12" t="s">
+      <c r="A166" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B166" s="13" t="s">
+      <c r="B166" s="12" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="12" t="s">
+      <c r="A167" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="B167" s="13" t="s">
+      <c r="B167" s="12" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="12" t="s">
+      <c r="A168" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="B168" s="14" t="s">
+      <c r="B168" s="13" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="12" t="s">
+      <c r="A169" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="B169" s="14" t="s">
+      <c r="B169" s="13" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="12" t="s">
+      <c r="A170" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="B170" s="13" t="s">
+      <c r="B170" s="12" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="12" t="s">
+      <c r="A171" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="B171" s="13" t="s">
+      <c r="B171" s="12" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="12" t="s">
+      <c r="A172" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="B172" s="13" t="s">
+      <c r="B172" s="12" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="12" t="s">
+      <c r="A173" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="B173" s="13" t="s">
+      <c r="B173" s="12" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="12" t="s">
+      <c r="A174" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="B174" s="13" t="s">
+      <c r="B174" s="12" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="12" t="s">
+      <c r="A175" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="B175" s="13" t="s">
+      <c r="B175" s="12" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="12" t="s">
+      <c r="A176" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B176" s="13" t="s">
+      <c r="B176" s="12" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="12" t="s">
+      <c r="A177" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="B177" s="13" t="s">
+      <c r="B177" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="12" t="s">
+      <c r="A178" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="B178" s="13" t="s">
+      <c r="B178" s="12" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="12" t="s">
+      <c r="A179" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="B179" s="13" t="s">
+      <c r="B179" s="12" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="12" t="s">
+      <c r="A180" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="B180" s="13" t="s">
+      <c r="B180" s="12" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="12" t="s">
+      <c r="A181" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="B181" s="13" t="s">
+      <c r="B181" s="12" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="12" t="s">
+      <c r="A182" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="B182" s="13" t="s">
+      <c r="B182" s="12" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="12" t="s">
+      <c r="A183" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="B183" s="13" t="s">
+      <c r="B183" s="12" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="12" t="s">
+      <c r="A184" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="B184" s="13" t="s">
+      <c r="B184" s="12" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="12" t="s">
+      <c r="A185" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="B185" s="13" t="s">
+      <c r="B185" s="12" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="12" t="s">
+      <c r="A186" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="B186" s="14" t="s">
+      <c r="B186" s="13" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="12" t="s">
+      <c r="A187" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="B187" s="14" t="s">
+      <c r="B187" s="13" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="12" t="s">
+      <c r="A188" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="B188" s="13" t="s">
+      <c r="B188" s="12" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="12" t="s">
+      <c r="A189" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="B189" s="14" t="s">
+      <c r="B189" s="13" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="12" t="s">
+      <c r="A190" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="B190" s="13" t="s">
+      <c r="B190" s="12" t="s">
         <v>339</v>
       </c>
     </row>
@@ -5665,215 +5999,215 @@
       <c r="A191" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B191" s="34" t="s">
+      <c r="B191" s="33" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="35" t="s">
+      <c r="A192" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="B192" s="36" t="s">
+      <c r="B192" s="35" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="35" t="s">
+      <c r="A193" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="B193" s="37" t="s">
+      <c r="B193" s="36" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="35" t="s">
+      <c r="A194" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="B194" s="19">
+      <c r="B194" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="35" t="s">
+      <c r="A195" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="B195" s="36" t="s">
+      <c r="B195" s="35" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="35" t="s">
+      <c r="A196" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="B196" s="18" t="s">
+      <c r="B196" s="17" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="35" t="s">
+      <c r="A197" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="B197" s="19">
+      <c r="B197" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="35" t="s">
+      <c r="A198" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="B198" s="19" t="s">
+      <c r="B198" s="18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="35" t="s">
+      <c r="A199" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="B199" s="38" t="s">
+      <c r="B199" s="37" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="35" t="s">
+      <c r="A200" s="34" t="s">
         <v>346</v>
       </c>
-      <c r="B200" s="38" t="s">
+      <c r="B200" s="37" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="35" t="s">
+      <c r="A201" s="34" t="s">
         <v>348</v>
       </c>
-      <c r="B201" s="38" t="s">
+      <c r="B201" s="37" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="35" t="s">
+      <c r="A202" s="34" t="s">
         <v>350</v>
       </c>
-      <c r="B202" s="19">
+      <c r="B202" s="18">
         <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="35" t="s">
+      <c r="A203" s="34" t="s">
         <v>351</v>
       </c>
-      <c r="B203" s="19">
+      <c r="B203" s="18">
         <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="35" t="s">
+      <c r="A204" s="34" t="s">
         <v>352</v>
       </c>
-      <c r="B204" s="19" t="s">
+      <c r="B204" s="18" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="39" t="s">
+      <c r="A205" s="38" t="s">
         <v>354</v>
       </c>
-      <c r="B205" s="19">
+      <c r="B205" s="18">
         <v>150</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="39" t="s">
+      <c r="A206" s="38" t="s">
         <v>355</v>
       </c>
-      <c r="B206" s="19">
+      <c r="B206" s="18">
         <v>250</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="39" t="s">
+      <c r="A207" s="38" t="s">
         <v>356</v>
       </c>
-      <c r="B207" s="19" t="s">
+      <c r="B207" s="18" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="39" t="s">
+      <c r="A208" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="B208" s="19">
+      <c r="B208" s="18">
         <v>123562</v>
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="39" t="s">
+      <c r="A209" s="38" t="s">
         <v>359</v>
       </c>
-      <c r="B209" s="19">
+      <c r="B209" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="39" t="s">
+      <c r="A210" s="38" t="s">
         <v>360</v>
       </c>
-      <c r="B210" s="19">
+      <c r="B210" s="18">
         <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="39" t="s">
+      <c r="A211" s="38" t="s">
         <v>361</v>
       </c>
-      <c r="B211" s="19">
+      <c r="B211" s="18">
         <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="39" t="s">
+      <c r="A212" s="38" t="s">
         <v>362</v>
       </c>
-      <c r="B212" s="37" t="s">
+      <c r="B212" s="36" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="39" t="s">
+      <c r="A213" s="38" t="s">
         <v>364</v>
       </c>
-      <c r="B213" s="18" t="s">
+      <c r="B213" s="17" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="39" t="s">
+      <c r="A214" s="38" t="s">
         <v>366</v>
       </c>
-      <c r="B214" s="37" t="s">
+      <c r="B214" s="36" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="39" t="s">
+      <c r="A215" s="38" t="s">
         <v>368</v>
       </c>
-      <c r="B215" s="19">
+      <c r="B215" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="39" t="s">
+      <c r="A216" s="38" t="s">
         <v>369</v>
       </c>
-      <c r="B216" s="19">
+      <c r="B216" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="39" t="s">
+      <c r="A217" s="38" t="s">
         <v>370</v>
       </c>
-      <c r="B217" s="37" t="s">
+      <c r="B217" s="36" t="s">
         <v>71</v>
       </c>
     </row>
@@ -5881,63 +6215,63 @@
       <c r="A218" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B218" s="25" t="s">
+      <c r="B218" s="24" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="31" t="s">
+      <c r="A219" s="30" t="s">
         <v>371</v>
       </c>
-      <c r="B219" s="40" t="s">
+      <c r="B219" s="39" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="31" t="s">
+      <c r="A220" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="B220" s="25" t="s">
+      <c r="B220" s="24" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="31" t="s">
+      <c r="A221" s="30" t="s">
         <v>374</v>
       </c>
-      <c r="B221" s="25" t="s">
+      <c r="B221" s="24" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="41" t="s">
+      <c r="A222" s="40" t="s">
         <v>376</v>
       </c>
-      <c r="B222" s="40" t="s">
+      <c r="B222" s="39" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="41" t="s">
+      <c r="A223" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="B223" s="40" t="s">
+      <c r="B223" s="39" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="42" t="s">
+      <c r="A224" s="41" t="s">
         <v>380</v>
       </c>
-      <c r="B224" s="43" t="s">
+      <c r="B224" s="42" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="41" t="s">
+      <c r="A225" s="40" t="s">
         <v>382</v>
       </c>
-      <c r="B225" s="44" t="s">
+      <c r="B225" s="43" t="s">
         <v>383</v>
       </c>
     </row>
@@ -5945,7 +6279,7 @@
       <c r="A226" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B226" s="8" t="s">
+      <c r="B226" s="7" t="s">
         <v>385</v>
       </c>
     </row>
@@ -5953,7 +6287,7 @@
       <c r="A227" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B227" s="8" t="s">
+      <c r="B227" s="7" t="s">
         <v>387</v>
       </c>
     </row>
@@ -5961,7 +6295,7 @@
       <c r="A228" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B228" s="8" t="s">
+      <c r="B228" s="7" t="s">
         <v>389</v>
       </c>
     </row>
@@ -5969,7 +6303,7 @@
       <c r="A229" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B229" s="8" t="s">
+      <c r="B229" s="7" t="s">
         <v>391</v>
       </c>
     </row>
@@ -5977,7 +6311,7 @@
       <c r="A230" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B230" s="8" t="s">
+      <c r="B230" s="7" t="s">
         <v>154</v>
       </c>
     </row>
@@ -5985,7 +6319,7 @@
       <c r="A231" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B231" s="8" t="s">
+      <c r="B231" s="7" t="s">
         <v>393</v>
       </c>
     </row>
@@ -5993,7 +6327,7 @@
       <c r="A232" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B232" s="8" t="s">
+      <c r="B232" s="7" t="s">
         <v>210</v>
       </c>
     </row>
@@ -6001,7 +6335,7 @@
       <c r="A233" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B233" s="8" t="s">
+      <c r="B233" s="7" t="s">
         <v>212</v>
       </c>
     </row>
@@ -6009,7 +6343,7 @@
       <c r="A234" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B234" s="8" t="s">
+      <c r="B234" s="7" t="s">
         <v>214</v>
       </c>
     </row>
@@ -6017,7 +6351,7 @@
       <c r="A235" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B235" s="8" t="s">
+      <c r="B235" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -6025,7 +6359,7 @@
       <c r="A236" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B236" s="8" t="s">
+      <c r="B236" s="7" t="s">
         <v>395</v>
       </c>
     </row>
@@ -6033,7 +6367,7 @@
       <c r="A237" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B237" s="8" t="s">
+      <c r="B237" s="7" t="s">
         <v>397</v>
       </c>
     </row>
@@ -6041,7 +6375,7 @@
       <c r="A238" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B238" s="8" t="s">
+      <c r="B238" s="7" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6049,7 +6383,7 @@
       <c r="A239" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B239" s="8" t="s">
+      <c r="B239" s="7" t="s">
         <v>401</v>
       </c>
     </row>
@@ -6057,7 +6391,7 @@
       <c r="A240" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B240" s="8" t="s">
+      <c r="B240" s="7" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6065,7 +6399,7 @@
       <c r="A241" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B241" s="8" t="s">
+      <c r="B241" s="7" t="s">
         <v>405</v>
       </c>
     </row>
@@ -6073,7 +6407,7 @@
       <c r="A242" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B242" s="8" t="s">
+      <c r="B242" s="7" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6081,7 +6415,7 @@
       <c r="A243" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B243" s="8" t="s">
+      <c r="B243" s="7" t="s">
         <v>405</v>
       </c>
     </row>
@@ -6089,7 +6423,7 @@
       <c r="A244" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B244" s="8" t="s">
+      <c r="B244" s="7" t="s">
         <v>410</v>
       </c>
     </row>
@@ -6097,7 +6431,7 @@
       <c r="A245" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B245" s="8" t="s">
+      <c r="B245" s="7" t="s">
         <v>412</v>
       </c>
     </row>
@@ -6105,7 +6439,7 @@
       <c r="A246" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B246" s="8" t="s">
+      <c r="B246" s="7" t="s">
         <v>414</v>
       </c>
     </row>
@@ -6113,7 +6447,7 @@
       <c r="A247" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B247" s="8" t="s">
+      <c r="B247" s="7" t="s">
         <v>235</v>
       </c>
     </row>
@@ -6121,7 +6455,7 @@
       <c r="A248" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B248" s="8" t="s">
+      <c r="B248" s="7" t="s">
         <v>417</v>
       </c>
     </row>
@@ -6129,7 +6463,7 @@
       <c r="A249" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B249" s="45" t="s">
+      <c r="B249" s="44" t="s">
         <v>419</v>
       </c>
     </row>
@@ -6137,7 +6471,7 @@
       <c r="A250" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="B250" s="8" t="s">
+      <c r="B250" s="7" t="s">
         <v>65</v>
       </c>
     </row>
@@ -6145,7 +6479,7 @@
       <c r="A251" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="B251" s="8" t="s">
+      <c r="B251" s="7" t="s">
         <v>422</v>
       </c>
     </row>
@@ -6153,7 +6487,7 @@
       <c r="A252" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B252" s="8" t="s">
+      <c r="B252" s="7" t="s">
         <v>222</v>
       </c>
     </row>
@@ -6161,7 +6495,7 @@
       <c r="A253" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B253" s="8" t="s">
+      <c r="B253" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -6169,7 +6503,7 @@
       <c r="A254" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B254" s="8" t="s">
+      <c r="B254" s="7" t="s">
         <v>426</v>
       </c>
     </row>
@@ -6177,7 +6511,7 @@
       <c r="A255" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B255" s="8" t="s">
+      <c r="B255" s="7" t="s">
         <v>226</v>
       </c>
     </row>
@@ -6185,7 +6519,7 @@
       <c r="A256" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B256" s="8" t="s">
+      <c r="B256" s="7" t="s">
         <v>429</v>
       </c>
     </row>
@@ -6193,7 +6527,7 @@
       <c r="A257" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B257" s="8" t="s">
+      <c r="B257" s="7" t="s">
         <v>431</v>
       </c>
     </row>
@@ -6201,7 +6535,7 @@
       <c r="A258" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B258" s="8" t="s">
+      <c r="B258" s="7" t="s">
         <v>391</v>
       </c>
     </row>
@@ -6209,7 +6543,7 @@
       <c r="A259" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="B259" s="8" t="s">
+      <c r="B259" s="7" t="s">
         <v>434</v>
       </c>
     </row>
@@ -6217,7 +6551,7 @@
       <c r="A260" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B260" s="8" t="s">
+      <c r="B260" s="7" t="s">
         <v>436</v>
       </c>
     </row>
@@ -6225,7 +6559,7 @@
       <c r="A261" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B261" s="8" t="s">
+      <c r="B261" s="7" t="s">
         <v>330</v>
       </c>
     </row>
@@ -6233,7 +6567,7 @@
       <c r="A262" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="B262" s="8" t="s">
+      <c r="B262" s="7" t="s">
         <v>439</v>
       </c>
     </row>
@@ -6241,7 +6575,7 @@
       <c r="A263" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="B263" s="8" t="s">
+      <c r="B263" s="7" t="s">
         <v>441</v>
       </c>
     </row>
@@ -6249,7 +6583,7 @@
       <c r="A264" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="B264" s="8" t="s">
+      <c r="B264" s="7" t="s">
         <v>443</v>
       </c>
     </row>
@@ -6257,7 +6591,7 @@
       <c r="A265" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B265" s="8" t="s">
+      <c r="B265" s="7" t="s">
         <v>445</v>
       </c>
     </row>
@@ -6265,7 +6599,7 @@
       <c r="A266" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B266" s="8" t="s">
+      <c r="B266" s="7" t="s">
         <v>447</v>
       </c>
     </row>
@@ -6273,7 +6607,7 @@
       <c r="A267" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B267" s="8" t="s">
+      <c r="B267" s="7" t="s">
         <v>330</v>
       </c>
     </row>
@@ -6281,7 +6615,7 @@
       <c r="A268" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B268" s="8" t="s">
+      <c r="B268" s="7" t="s">
         <v>450</v>
       </c>
     </row>
@@ -6289,7 +6623,7 @@
       <c r="A269" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B269" s="8" t="s">
+      <c r="B269" s="7" t="s">
         <v>452</v>
       </c>
     </row>
@@ -6297,7 +6631,7 @@
       <c r="A270" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B270" s="8" t="s">
+      <c r="B270" s="7" t="s">
         <v>454</v>
       </c>
     </row>
@@ -6305,7 +6639,7 @@
       <c r="A271" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B271" s="8" t="s">
+      <c r="B271" s="7" t="s">
         <v>456</v>
       </c>
     </row>
@@ -6313,7 +6647,7 @@
       <c r="A272" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="B272" s="8" t="s">
+      <c r="B272" s="7" t="s">
         <v>458</v>
       </c>
     </row>
@@ -6321,7 +6655,7 @@
       <c r="A273" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B273" s="8" t="s">
+      <c r="B273" s="7" t="s">
         <v>460</v>
       </c>
     </row>
@@ -6329,7 +6663,7 @@
       <c r="A274" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B274" s="8" t="s">
+      <c r="B274" s="7" t="s">
         <v>462</v>
       </c>
     </row>
@@ -6337,7 +6671,7 @@
       <c r="A275" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B275" s="8" t="s">
+      <c r="B275" s="7" t="s">
         <v>332</v>
       </c>
     </row>
@@ -6345,7 +6679,7 @@
       <c r="A276" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="B276" s="8" t="s">
+      <c r="B276" s="7" t="s">
         <v>339</v>
       </c>
     </row>
@@ -6353,15 +6687,15 @@
       <c r="A277" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B277" s="8" t="s">
+      <c r="B277" s="7" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="278" spans="1:2">
-      <c r="A278" s="26" t="s">
+      <c r="A278" s="25" t="s">
         <v>467</v>
       </c>
-      <c r="B278" s="25" t="s">
+      <c r="B278" s="24" t="s">
         <v>468</v>
       </c>
     </row>
@@ -6369,7 +6703,7 @@
       <c r="A279" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B279" s="25" t="s">
+      <c r="B279" s="24" t="s">
         <v>59</v>
       </c>
     </row>
@@ -6377,95 +6711,95 @@
       <c r="A280" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="B280" s="8" t="s">
+      <c r="B280" s="7" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="281" spans="1:2">
-      <c r="A281" s="9" t="s">
+      <c r="A281" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="B281" s="10" t="s">
+      <c r="B281" s="9" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="282" spans="1:2">
-      <c r="A282" s="9" t="s">
+      <c r="A282" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="B282" s="10" t="s">
+      <c r="B282" s="9" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="283" spans="1:2">
-      <c r="A283" s="9" t="s">
+      <c r="A283" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="B283" s="10" t="s">
+      <c r="B283" s="9" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="284" spans="1:2">
-      <c r="A284" s="9" t="s">
+      <c r="A284" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="B284" s="46" t="s">
+      <c r="B284" s="45" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="285" spans="1:2">
-      <c r="A285" s="47" t="s">
+      <c r="A285" s="46" t="s">
         <v>479</v>
       </c>
-      <c r="B285" s="8" t="s">
+      <c r="B285" s="7" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="286" spans="1:2">
-      <c r="A286" s="47" t="s">
+      <c r="A286" s="46" t="s">
         <v>481</v>
       </c>
-      <c r="B286" s="8" t="s">
+      <c r="B286" s="7" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="287" spans="1:2">
-      <c r="A287" s="47" t="s">
+      <c r="A287" s="46" t="s">
         <v>483</v>
       </c>
-      <c r="B287" s="8" t="s">
+      <c r="B287" s="7" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="288" spans="1:2">
-      <c r="A288" s="47" t="s">
+      <c r="A288" s="46" t="s">
         <v>485</v>
       </c>
-      <c r="B288" s="8" t="s">
+      <c r="B288" s="7" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="289" spans="1:2">
-      <c r="A289" s="47" t="s">
+      <c r="A289" s="46" t="s">
         <v>487</v>
       </c>
-      <c r="B289" s="8" t="s">
+      <c r="B289" s="7" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="47" t="s">
+      <c r="A290" s="46" t="s">
         <v>489</v>
       </c>
-      <c r="B290" s="8" t="s">
+      <c r="B290" s="7" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="47" t="s">
+      <c r="A291" s="46" t="s">
         <v>491</v>
       </c>
-      <c r="B291" s="8" t="s">
+      <c r="B291" s="7" t="s">
         <v>492</v>
       </c>
     </row>
@@ -6473,7 +6807,7 @@
       <c r="A292" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B292" s="8" t="s">
+      <c r="B292" s="7" t="s">
         <v>494</v>
       </c>
     </row>
@@ -6481,7 +6815,7 @@
       <c r="A293" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B293" s="8" t="s">
+      <c r="B293" s="7" t="s">
         <v>496</v>
       </c>
     </row>
@@ -6489,7 +6823,7 @@
       <c r="A294" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B294" s="8" t="s">
+      <c r="B294" s="7" t="s">
         <v>498</v>
       </c>
     </row>
@@ -6497,7 +6831,7 @@
       <c r="A295" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="B295" s="8" t="s">
+      <c r="B295" s="7" t="s">
         <v>500</v>
       </c>
     </row>
@@ -6505,7 +6839,7 @@
       <c r="A296" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B296" s="8" t="s">
+      <c r="B296" s="7" t="s">
         <v>502</v>
       </c>
     </row>
@@ -6513,7 +6847,7 @@
       <c r="A297" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B297" s="8" t="s">
+      <c r="B297" s="7" t="s">
         <v>504</v>
       </c>
     </row>
@@ -6521,7 +6855,7 @@
       <c r="A298" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="B298" s="8" t="s">
+      <c r="B298" s="7" t="s">
         <v>506</v>
       </c>
     </row>
@@ -6529,7 +6863,7 @@
       <c r="A299" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="B299" s="8" t="s">
+      <c r="B299" s="7" t="s">
         <v>508</v>
       </c>
     </row>
@@ -6537,7 +6871,7 @@
       <c r="A300" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="B300" s="8" t="s">
+      <c r="B300" s="7" t="s">
         <v>510</v>
       </c>
     </row>
@@ -6545,7 +6879,7 @@
       <c r="A301" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="B301" s="8" t="s">
+      <c r="B301" s="7" t="s">
         <v>512</v>
       </c>
     </row>
@@ -6553,7 +6887,7 @@
       <c r="A302" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B302" s="8" t="s">
+      <c r="B302" s="7" t="s">
         <v>514</v>
       </c>
     </row>
@@ -6561,7 +6895,7 @@
       <c r="A303" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="B303" s="8" t="s">
+      <c r="B303" s="7" t="s">
         <v>516</v>
       </c>
     </row>
@@ -6569,7 +6903,7 @@
       <c r="A304" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="B304" s="8" t="s">
+      <c r="B304" s="7" t="s">
         <v>518</v>
       </c>
     </row>
@@ -6577,7 +6911,7 @@
       <c r="A305" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="B305" s="8" t="s">
+      <c r="B305" s="7" t="s">
         <v>419</v>
       </c>
     </row>
@@ -6585,7 +6919,7 @@
       <c r="A306" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="B306" s="8" t="s">
+      <c r="B306" s="7" t="s">
         <v>521</v>
       </c>
     </row>
@@ -6593,7 +6927,7 @@
       <c r="A307" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B307" s="8" t="s">
+      <c r="B307" s="7" t="s">
         <v>419</v>
       </c>
     </row>
@@ -6601,7 +6935,7 @@
       <c r="A308" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="B308" s="8" t="s">
+      <c r="B308" s="7" t="s">
         <v>524</v>
       </c>
     </row>
@@ -6609,7 +6943,7 @@
       <c r="A309" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="B309" s="8" t="s">
+      <c r="B309" s="7" t="s">
         <v>526</v>
       </c>
     </row>
@@ -6617,7 +6951,7 @@
       <c r="A310" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="B310" s="8" t="s">
+      <c r="B310" s="7" t="s">
         <v>528</v>
       </c>
     </row>
@@ -6625,7 +6959,7 @@
       <c r="A311" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B311" s="8" t="s">
+      <c r="B311" s="7" t="s">
         <v>528</v>
       </c>
     </row>
@@ -6633,7 +6967,7 @@
       <c r="A312" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B312" s="8" t="s">
+      <c r="B312" s="7" t="s">
         <v>528</v>
       </c>
     </row>
@@ -6641,7 +6975,7 @@
       <c r="A313" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="B313" s="8" t="s">
+      <c r="B313" s="7" t="s">
         <v>532</v>
       </c>
     </row>
@@ -6649,7 +6983,7 @@
       <c r="A314" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="B314" s="8" t="s">
+      <c r="B314" s="7" t="s">
         <v>534</v>
       </c>
     </row>
@@ -6657,7 +6991,7 @@
       <c r="A315" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B315" s="8" t="s">
+      <c r="B315" s="7" t="s">
         <v>534</v>
       </c>
     </row>
@@ -6665,7 +6999,7 @@
       <c r="A316" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="B316" s="8" t="s">
+      <c r="B316" s="7" t="s">
         <v>537</v>
       </c>
     </row>
@@ -6673,7 +7007,7 @@
       <c r="A317" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B317" s="8" t="s">
+      <c r="B317" s="7" t="s">
         <v>539</v>
       </c>
     </row>
@@ -6681,7 +7015,7 @@
       <c r="A318" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="B318" s="8" t="s">
+      <c r="B318" s="7" t="s">
         <v>541</v>
       </c>
     </row>
@@ -6689,7 +7023,7 @@
       <c r="A319" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B319" s="48" t="s">
+      <c r="B319" s="47" t="s">
         <v>543</v>
       </c>
     </row>
@@ -6697,7 +7031,7 @@
       <c r="A320" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="B320" s="8" t="s">
+      <c r="B320" s="7" t="s">
         <v>545</v>
       </c>
     </row>
@@ -6705,7 +7039,7 @@
       <c r="A321" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="B321" s="8" t="s">
+      <c r="B321" s="7" t="s">
         <v>547</v>
       </c>
     </row>
@@ -6713,7 +7047,7 @@
       <c r="A322" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="B322" s="8" t="s">
+      <c r="B322" s="7" t="s">
         <v>549</v>
       </c>
     </row>
@@ -6721,7 +7055,7 @@
       <c r="A323" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="B323" s="8" t="s">
+      <c r="B323" s="7" t="s">
         <v>551</v>
       </c>
     </row>
@@ -6729,7 +7063,7 @@
       <c r="A324" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="B324" s="8" t="s">
+      <c r="B324" s="7" t="s">
         <v>552</v>
       </c>
     </row>
@@ -6737,7 +7071,7 @@
       <c r="A325" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B325" s="8" t="s">
+      <c r="B325" s="7" t="s">
         <v>554</v>
       </c>
     </row>
@@ -6745,7 +7079,7 @@
       <c r="A326" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="B326" s="8" t="s">
+      <c r="B326" s="7" t="s">
         <v>556</v>
       </c>
     </row>
@@ -6753,7 +7087,7 @@
       <c r="A327" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B327" s="8" t="s">
+      <c r="B327" s="7" t="s">
         <v>558</v>
       </c>
     </row>
@@ -6761,7 +7095,7 @@
       <c r="A328" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B328" s="8" t="s">
+      <c r="B328" s="7" t="s">
         <v>560</v>
       </c>
     </row>
@@ -6769,7 +7103,7 @@
       <c r="A329" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B329" s="8" t="s">
+      <c r="B329" s="7" t="s">
         <v>561</v>
       </c>
     </row>
@@ -6777,7 +7111,7 @@
       <c r="A330" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="B330" s="8" t="s">
+      <c r="B330" s="7" t="s">
         <v>563</v>
       </c>
     </row>
@@ -6785,7 +7119,7 @@
       <c r="A331" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="B331" s="8" t="s">
+      <c r="B331" s="7" t="s">
         <v>564</v>
       </c>
     </row>
@@ -6793,7 +7127,7 @@
       <c r="A332" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="B332" s="8" t="s">
+      <c r="B332" s="7" t="s">
         <v>566</v>
       </c>
     </row>
@@ -6801,7 +7135,7 @@
       <c r="A333" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="B333" s="8" t="s">
+      <c r="B333" s="7" t="s">
         <v>568</v>
       </c>
     </row>
@@ -6809,7 +7143,7 @@
       <c r="A334" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B334" s="8" t="s">
+      <c r="B334" s="7" t="s">
         <v>570</v>
       </c>
     </row>
@@ -6817,63 +7151,63 @@
       <c r="A335" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B335" s="8" t="s">
+      <c r="B335" s="7" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="30" t="s">
+      <c r="A336" s="29" t="s">
         <v>573</v>
       </c>
-      <c r="B336" s="29" t="s">
+      <c r="B336" s="28" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="337" spans="1:2">
-      <c r="A337" s="30" t="s">
+      <c r="A337" s="29" t="s">
         <v>575</v>
       </c>
-      <c r="B337" s="29" t="s">
+      <c r="B337" s="28" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="338" spans="1:2">
-      <c r="A338" s="30" t="s">
+      <c r="A338" s="29" t="s">
         <v>576</v>
       </c>
-      <c r="B338" s="29" t="s">
+      <c r="B338" s="28" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="339" spans="1:2">
-      <c r="A339" s="30" t="s">
+      <c r="A339" s="29" t="s">
         <v>577</v>
       </c>
-      <c r="B339" s="29" t="s">
+      <c r="B339" s="28" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="340" spans="1:2">
-      <c r="A340" s="30" t="s">
+      <c r="A340" s="29" t="s">
         <v>578</v>
       </c>
-      <c r="B340" s="29" t="s">
+      <c r="B340" s="28" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="341" spans="1:2">
-      <c r="A341" s="30" t="s">
+      <c r="A341" s="29" t="s">
         <v>580</v>
       </c>
-      <c r="B341" s="29" t="s">
+      <c r="B341" s="28" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="342" spans="1:2">
-      <c r="A342" s="30" t="s">
+      <c r="A342" s="29" t="s">
         <v>581</v>
       </c>
-      <c r="B342" s="29" t="s">
+      <c r="B342" s="28" t="s">
         <v>579</v>
       </c>
     </row>
@@ -6881,7 +7215,7 @@
       <c r="A343" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="B343" s="8" t="s">
+      <c r="B343" s="7" t="s">
         <v>583</v>
       </c>
     </row>
@@ -6889,7 +7223,7 @@
       <c r="A344" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B344" s="8" t="s">
+      <c r="B344" s="7" t="s">
         <v>585</v>
       </c>
     </row>
@@ -6897,7 +7231,7 @@
       <c r="A345" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="B345" s="8" t="s">
+      <c r="B345" s="7" t="s">
         <v>587</v>
       </c>
     </row>
@@ -6905,7 +7239,7 @@
       <c r="A346" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="B346" s="8" t="s">
+      <c r="B346" s="7" t="s">
         <v>589</v>
       </c>
     </row>
@@ -6913,7 +7247,7 @@
       <c r="A347" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="B347" s="8" t="s">
+      <c r="B347" s="7" t="s">
         <v>591</v>
       </c>
     </row>
@@ -6921,7 +7255,7 @@
       <c r="A348" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B348" s="8" t="s">
+      <c r="B348" s="7" t="s">
         <v>593</v>
       </c>
     </row>
@@ -6929,7 +7263,7 @@
       <c r="A349" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="B349" s="8" t="s">
+      <c r="B349" s="7" t="s">
         <v>595</v>
       </c>
     </row>
@@ -6937,7 +7271,7 @@
       <c r="A350" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="B350" s="8" t="s">
+      <c r="B350" s="7" t="s">
         <v>597</v>
       </c>
     </row>
@@ -6945,7 +7279,7 @@
       <c r="A351" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B351" s="8" t="s">
+      <c r="B351" s="7" t="s">
         <v>599</v>
       </c>
     </row>
@@ -6953,7 +7287,7 @@
       <c r="A352" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="B352" s="8" t="s">
+      <c r="B352" s="7" t="s">
         <v>601</v>
       </c>
     </row>
@@ -6961,7 +7295,7 @@
       <c r="A353" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B353" s="8" t="s">
+      <c r="B353" s="7" t="s">
         <v>603</v>
       </c>
     </row>
@@ -6969,7 +7303,7 @@
       <c r="A354" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B354" s="8" t="s">
+      <c r="B354" s="7" t="s">
         <v>605</v>
       </c>
     </row>
@@ -6977,7 +7311,7 @@
       <c r="A355" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B355" s="8" t="s">
+      <c r="B355" s="7" t="s">
         <v>59</v>
       </c>
     </row>
@@ -6985,7 +7319,7 @@
       <c r="A356" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B356" s="25" t="s">
+      <c r="B356" s="24" t="s">
         <v>608</v>
       </c>
     </row>
@@ -6993,415 +7327,415 @@
       <c r="A357" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="B357" s="8" t="s">
+      <c r="B357" s="7" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="26" t="s">
+      <c r="A358" s="25" t="s">
         <v>611</v>
       </c>
-      <c r="B358" s="27" t="s">
+      <c r="B358" s="26" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="359" spans="1:2">
-      <c r="A359" s="26" t="s">
+      <c r="A359" s="25" t="s">
         <v>613</v>
       </c>
-      <c r="B359" s="27" t="s">
+      <c r="B359" s="26" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="360" spans="1:2">
-      <c r="A360" s="26" t="s">
+      <c r="A360" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="B360" s="25">
+      <c r="B360" s="24">
         <v>10</v>
       </c>
     </row>
     <row r="361" spans="1:2">
-      <c r="A361" s="26" t="s">
+      <c r="A361" s="25" t="s">
         <v>616</v>
       </c>
-      <c r="B361" s="25">
+      <c r="B361" s="24">
         <v>1000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
-      <c r="A362" s="26" t="s">
+      <c r="A362" s="25" t="s">
         <v>617</v>
       </c>
-      <c r="B362" s="49">
+      <c r="B362" s="48">
         <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:2">
-      <c r="A363" s="26" t="s">
+      <c r="A363" s="25" t="s">
         <v>618</v>
       </c>
-      <c r="B363" s="25">
+      <c r="B363" s="24">
         <v>1000</v>
       </c>
     </row>
     <row r="364" spans="1:2">
-      <c r="A364" s="26" t="s">
+      <c r="A364" s="25" t="s">
         <v>619</v>
       </c>
-      <c r="B364" s="25" t="s">
+      <c r="B364" s="24" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="26" t="s">
+      <c r="A365" s="25" t="s">
         <v>621</v>
       </c>
-      <c r="B365" s="25" t="s">
+      <c r="B365" s="24" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="26" t="s">
+      <c r="A366" s="25" t="s">
         <v>623</v>
       </c>
-      <c r="B366" s="25" t="s">
+      <c r="B366" s="24" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" s="26" t="s">
+      <c r="A367" s="25" t="s">
         <v>625</v>
       </c>
-      <c r="B367" s="25">
+      <c r="B367" s="24">
         <v>10000039</v>
       </c>
     </row>
     <row r="368" spans="1:2">
-      <c r="A368" s="26" t="s">
+      <c r="A368" s="25" t="s">
         <v>626</v>
       </c>
-      <c r="B368" s="27" t="s">
+      <c r="B368" s="26" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="369" spans="1:2">
-      <c r="A369" s="26" t="s">
+      <c r="A369" s="25" t="s">
         <v>628</v>
       </c>
-      <c r="B369" s="27" t="s">
+      <c r="B369" s="26" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="26" t="s">
+      <c r="A370" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="B370" s="8" t="s">
+      <c r="B370" s="7" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="26" t="s">
+      <c r="A371" s="25" t="s">
         <v>632</v>
       </c>
-      <c r="B371" s="8" t="s">
+      <c r="B371" s="7" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="372" spans="1:2">
-      <c r="A372" s="26" t="s">
+      <c r="A372" s="25" t="s">
         <v>634</v>
       </c>
-      <c r="B372" s="8" t="s">
+      <c r="B372" s="7" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="26" t="s">
+      <c r="A373" s="25" t="s">
         <v>636</v>
       </c>
-      <c r="B373" s="8" t="s">
+      <c r="B373" s="7" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="26" t="s">
+      <c r="A374" s="25" t="s">
         <v>638</v>
       </c>
-      <c r="B374" s="8" t="s">
+      <c r="B374" s="7" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="26" t="s">
+      <c r="A375" s="25" t="s">
         <v>640</v>
       </c>
-      <c r="B375" s="8" t="s">
+      <c r="B375" s="7" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="26" t="s">
+      <c r="A376" s="25" t="s">
         <v>642</v>
       </c>
-      <c r="B376" s="8" t="s">
+      <c r="B376" s="7" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="377" spans="1:2">
-      <c r="A377" s="26" t="s">
+      <c r="A377" s="25" t="s">
         <v>643</v>
       </c>
-      <c r="B377" s="8" t="s">
+      <c r="B377" s="7" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="378" spans="1:2">
-      <c r="A378" s="26" t="s">
+      <c r="A378" s="25" t="s">
         <v>645</v>
       </c>
-      <c r="B378" s="8" t="s">
+      <c r="B378" s="7" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="379" spans="1:2">
-      <c r="A379" s="26" t="s">
+      <c r="A379" s="25" t="s">
         <v>647</v>
       </c>
-      <c r="B379" s="8" t="s">
+      <c r="B379" s="7" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="380" spans="1:2">
-      <c r="A380" s="26" t="s">
+      <c r="A380" s="25" t="s">
         <v>649</v>
       </c>
-      <c r="B380" s="8" t="s">
+      <c r="B380" s="7" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="381" spans="1:2">
-      <c r="A381" s="26" t="s">
+      <c r="A381" s="25" t="s">
         <v>650</v>
       </c>
-      <c r="B381" s="8" t="s">
+      <c r="B381" s="7" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="26" t="s">
+      <c r="A382" s="25" t="s">
         <v>652</v>
       </c>
-      <c r="B382" s="8" t="s">
+      <c r="B382" s="7" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="26" t="s">
+      <c r="A383" s="25" t="s">
         <v>654</v>
       </c>
-      <c r="B383" s="8" t="s">
+      <c r="B383" s="7" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="26" t="s">
+      <c r="A384" s="25" t="s">
         <v>656</v>
       </c>
-      <c r="B384" s="8" t="s">
+      <c r="B384" s="7" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="26" t="s">
+      <c r="A385" s="25" t="s">
         <v>658</v>
       </c>
-      <c r="B385" s="8" t="s">
+      <c r="B385" s="7" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="26" t="s">
+      <c r="A386" s="25" t="s">
         <v>660</v>
       </c>
-      <c r="B386" s="8" t="s">
+      <c r="B386" s="7" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="26" t="s">
+      <c r="A387" s="25" t="s">
         <v>662</v>
       </c>
-      <c r="B387" s="8" t="s">
+      <c r="B387" s="7" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="388" spans="1:2">
-      <c r="A388" s="26" t="s">
+      <c r="A388" s="25" t="s">
         <v>664</v>
       </c>
-      <c r="B388" s="8" t="s">
+      <c r="B388" s="7" t="s">
         <v>665</v>
       </c>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" s="26" t="s">
+      <c r="A389" s="25" t="s">
         <v>666</v>
       </c>
-      <c r="B389" s="8" t="s">
+      <c r="B389" s="7" t="s">
         <v>667</v>
       </c>
     </row>
     <row r="390" spans="1:2">
-      <c r="A390" s="26" t="s">
+      <c r="A390" s="25" t="s">
         <v>668</v>
       </c>
-      <c r="B390" s="8" t="s">
+      <c r="B390" s="7" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="26" t="s">
+      <c r="A391" s="25" t="s">
         <v>670</v>
       </c>
-      <c r="B391" s="8" t="s">
+      <c r="B391" s="7" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="26" t="s">
+      <c r="A392" s="25" t="s">
         <v>672</v>
       </c>
-      <c r="B392" s="8" t="s">
+      <c r="B392" s="7" t="s">
         <v>673</v>
       </c>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393" s="26" t="s">
+      <c r="A393" s="25" t="s">
         <v>674</v>
       </c>
-      <c r="B393" s="8" t="s">
+      <c r="B393" s="7" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="26" t="s">
+      <c r="A394" s="25" t="s">
         <v>676</v>
       </c>
-      <c r="B394" s="8" t="s">
+      <c r="B394" s="7" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="395" spans="1:2">
-      <c r="A395" s="26" t="s">
+      <c r="A395" s="25" t="s">
         <v>678</v>
       </c>
-      <c r="B395" s="8" t="s">
+      <c r="B395" s="7" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396" s="26" t="s">
+      <c r="A396" s="25" t="s">
         <v>680</v>
       </c>
-      <c r="B396" s="8" t="s">
+      <c r="B396" s="7" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="26" t="s">
+      <c r="A397" s="25" t="s">
         <v>682</v>
       </c>
-      <c r="B397" s="8" t="s">
+      <c r="B397" s="7" t="s">
         <v>683</v>
       </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="26" t="s">
+      <c r="A398" s="25" t="s">
         <v>684</v>
       </c>
-      <c r="B398" s="8" t="s">
+      <c r="B398" s="7" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="26" t="s">
+      <c r="A399" s="25" t="s">
         <v>686</v>
       </c>
-      <c r="B399" s="8" t="s">
+      <c r="B399" s="7" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="26" t="s">
+      <c r="A400" s="25" t="s">
         <v>688</v>
       </c>
-      <c r="B400" s="8" t="s">
+      <c r="B400" s="7" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="26" t="s">
+      <c r="A401" s="25" t="s">
         <v>690</v>
       </c>
-      <c r="B401" s="8" t="s">
+      <c r="B401" s="7" t="s">
         <v>691</v>
       </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="26" t="s">
+      <c r="A402" s="25" t="s">
         <v>692</v>
       </c>
-      <c r="B402" s="8" t="s">
+      <c r="B402" s="7" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="26" t="s">
+      <c r="A403" s="25" t="s">
         <v>694</v>
       </c>
-      <c r="B403" s="8" t="s">
+      <c r="B403" s="7" t="s">
         <v>695</v>
       </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="26" t="s">
+      <c r="A404" s="25" t="s">
         <v>696</v>
       </c>
-      <c r="B404" s="8" t="s">
+      <c r="B404" s="7" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="26" t="s">
+      <c r="A405" s="25" t="s">
         <v>698</v>
       </c>
-      <c r="B405" s="8" t="s">
+      <c r="B405" s="7" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="26" t="s">
+      <c r="A406" s="25" t="s">
         <v>700</v>
       </c>
-      <c r="B406" s="8" t="s">
+      <c r="B406" s="7" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="26" t="s">
+      <c r="A407" s="25" t="s">
         <v>702</v>
       </c>
-      <c r="B407" s="8" t="s">
+      <c r="B407" s="7" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="26" t="s">
+      <c r="A408" s="25" t="s">
         <v>704</v>
       </c>
-      <c r="B408" s="8" t="s">
+      <c r="B408" s="7" t="s">
         <v>705</v>
       </c>
     </row>
@@ -7409,7 +7743,7 @@
       <c r="A409" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="B409" s="8" t="s">
+      <c r="B409" s="7" t="s">
         <v>707</v>
       </c>
     </row>
@@ -7417,7 +7751,7 @@
       <c r="A410" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="B410" s="8" t="s">
+      <c r="B410" s="7" t="s">
         <v>709</v>
       </c>
     </row>
@@ -7425,7 +7759,7 @@
       <c r="A411" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="B411" s="8" t="s">
+      <c r="B411" s="7" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7433,7 +7767,7 @@
       <c r="A412" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="B412" s="8" t="s">
+      <c r="B412" s="7" t="s">
         <v>711</v>
       </c>
     </row>
@@ -7441,7 +7775,7 @@
       <c r="A413" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="B413" s="8" t="s">
+      <c r="B413" s="7" t="s">
         <v>713</v>
       </c>
     </row>
@@ -7449,7 +7783,7 @@
       <c r="A414" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="B414" s="8" t="s">
+      <c r="B414" s="7" t="s">
         <v>715</v>
       </c>
     </row>
@@ -7457,7 +7791,7 @@
       <c r="A415" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="B415" s="8" t="s">
+      <c r="B415" s="7" t="s">
         <v>717</v>
       </c>
     </row>
@@ -7465,7 +7799,7 @@
       <c r="A416" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B416" s="8" t="s">
+      <c r="B416" s="7" t="s">
         <v>719</v>
       </c>
     </row>
@@ -7473,7 +7807,7 @@
       <c r="A417" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="B417" s="8" t="s">
+      <c r="B417" s="7" t="s">
         <v>117</v>
       </c>
     </row>
@@ -7481,7 +7815,7 @@
       <c r="A418" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B418" s="8" t="s">
+      <c r="B418" s="7" t="s">
         <v>722</v>
       </c>
     </row>
@@ -7489,7 +7823,7 @@
       <c r="A419" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="B419" s="8" t="s">
+      <c r="B419" s="7" t="s">
         <v>724</v>
       </c>
     </row>
@@ -7497,7 +7831,7 @@
       <c r="A420" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="B420" s="8" t="s">
+      <c r="B420" s="7" t="s">
         <v>726</v>
       </c>
     </row>
@@ -7505,7 +7839,7 @@
       <c r="A421" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="B421" s="8" t="s">
+      <c r="B421" s="7" t="s">
         <v>727</v>
       </c>
     </row>
@@ -7513,7 +7847,7 @@
       <c r="A422" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="B422" s="8" t="s">
+      <c r="B422" s="7" t="s">
         <v>568</v>
       </c>
     </row>
@@ -7521,7 +7855,7 @@
       <c r="A423" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="B423" s="8" t="s">
+      <c r="B423" s="7" t="s">
         <v>729</v>
       </c>
     </row>
@@ -7529,7 +7863,7 @@
       <c r="A424" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="B424" s="8" t="s">
+      <c r="B424" s="7" t="s">
         <v>731</v>
       </c>
     </row>
@@ -7537,335 +7871,335 @@
       <c r="A425" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="B425" s="8" t="s">
+      <c r="B425" s="7" t="s">
         <v>733</v>
       </c>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="12" t="s">
+      <c r="A426" s="11" t="s">
         <v>734</v>
       </c>
-      <c r="B426" s="14" t="s">
+      <c r="B426" s="13" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="427" spans="1:2">
-      <c r="A427" s="12" t="s">
+      <c r="A427" s="11" t="s">
         <v>736</v>
       </c>
-      <c r="B427" s="14" t="s">
+      <c r="B427" s="13" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="12" t="s">
+      <c r="A428" s="11" t="s">
         <v>738</v>
       </c>
-      <c r="B428" s="14" t="s">
+      <c r="B428" s="13" t="s">
         <v>739</v>
       </c>
     </row>
     <row r="429" spans="1:2">
-      <c r="A429" s="12" t="s">
+      <c r="A429" s="11" t="s">
         <v>740</v>
       </c>
-      <c r="B429" s="14" t="s">
+      <c r="B429" s="13" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="430" spans="1:2">
-      <c r="A430" s="12" t="s">
+      <c r="A430" s="11" t="s">
         <v>742</v>
       </c>
-      <c r="B430" s="14" t="s">
+      <c r="B430" s="13" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="12" t="s">
+      <c r="A431" s="11" t="s">
         <v>744</v>
       </c>
-      <c r="B431" s="14" t="s">
+      <c r="B431" s="13" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="432" spans="1:2">
-      <c r="A432" s="12" t="s">
+      <c r="A432" s="11" t="s">
         <v>746</v>
       </c>
-      <c r="B432" s="14" t="s">
+      <c r="B432" s="13" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="433" spans="1:2">
-      <c r="A433" s="12" t="s">
+      <c r="A433" s="11" t="s">
         <v>748</v>
       </c>
-      <c r="B433" s="14" t="s">
+      <c r="B433" s="13" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="434" spans="1:2">
-      <c r="A434" s="12" t="s">
+      <c r="A434" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="B434" s="14" t="s">
+      <c r="B434" s="13" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="435" spans="1:2">
-      <c r="A435" s="12" t="s">
+      <c r="A435" s="11" t="s">
         <v>752</v>
       </c>
-      <c r="B435" s="14" t="s">
+      <c r="B435" s="13" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="436" spans="1:2">
-      <c r="A436" s="12" t="s">
+      <c r="A436" s="11" t="s">
         <v>754</v>
       </c>
-      <c r="B436" s="14" t="s">
+      <c r="B436" s="13" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="437" spans="1:2">
-      <c r="A437" s="12" t="s">
+      <c r="A437" s="11" t="s">
         <v>756</v>
       </c>
-      <c r="B437" s="14" t="s">
+      <c r="B437" s="13" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="438" spans="1:2">
-      <c r="A438" s="12" t="s">
+      <c r="A438" s="11" t="s">
         <v>758</v>
       </c>
-      <c r="B438" s="14" t="s">
+      <c r="B438" s="13" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="439" spans="1:2">
-      <c r="A439" s="12" t="s">
+      <c r="A439" s="11" t="s">
         <v>760</v>
       </c>
-      <c r="B439" s="14" t="s">
+      <c r="B439" s="13" t="s">
         <v>761</v>
       </c>
     </row>
     <row r="440" spans="1:2">
-      <c r="A440" s="30" t="s">
+      <c r="A440" s="29" t="s">
         <v>762</v>
       </c>
-      <c r="B440" s="29" t="s">
+      <c r="B440" s="28" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="441" spans="1:2">
-      <c r="A441" s="50" t="s">
+      <c r="A441" s="49" t="s">
         <v>764</v>
       </c>
-      <c r="B441" s="51" t="s">
+      <c r="B441" s="50" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="442" spans="1:2">
-      <c r="A442" s="50" t="s">
+      <c r="A442" s="49" t="s">
         <v>765</v>
       </c>
-      <c r="B442" s="51" t="s">
+      <c r="B442" s="50" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="443" spans="1:2">
-      <c r="A443" s="50" t="s">
+      <c r="A443" s="49" t="s">
         <v>767</v>
       </c>
-      <c r="B443" s="51" t="s">
+      <c r="B443" s="50" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="444" spans="1:2">
-      <c r="A444" s="50" t="s">
+      <c r="A444" s="49" t="s">
         <v>769</v>
       </c>
-      <c r="B444" s="51" t="s">
+      <c r="B444" s="50" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="445" spans="1:2">
-      <c r="A445" s="50" t="s">
+      <c r="A445" s="49" t="s">
         <v>770</v>
       </c>
-      <c r="B445" s="51" t="s">
+      <c r="B445" s="50" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="446" spans="1:2">
-      <c r="A446" s="50" t="s">
+      <c r="A446" s="49" t="s">
         <v>771</v>
       </c>
-      <c r="B446" s="52" t="s">
+      <c r="B446" s="51" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="447" spans="1:2">
-      <c r="A447" s="50" t="s">
+      <c r="A447" s="49" t="s">
         <v>773</v>
       </c>
-      <c r="B447" s="52" t="s">
+      <c r="B447" s="51" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="448" spans="1:2">
-      <c r="A448" s="50" t="s">
+      <c r="A448" s="49" t="s">
         <v>775</v>
       </c>
-      <c r="B448" s="51" t="s">
+      <c r="B448" s="50" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="449" spans="1:2">
-      <c r="A449" s="50" t="s">
+      <c r="A449" s="49" t="s">
         <v>777</v>
       </c>
-      <c r="B449" s="51" t="s">
+      <c r="B449" s="50" t="s">
         <v>778</v>
       </c>
     </row>
     <row r="450" spans="1:2">
-      <c r="A450" s="50" t="s">
+      <c r="A450" s="49" t="s">
         <v>564</v>
       </c>
-      <c r="B450" s="52" t="s">
+      <c r="B450" s="51" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="451" spans="1:2">
-      <c r="A451" s="50" t="s">
+      <c r="A451" s="49" t="s">
         <v>561</v>
       </c>
-      <c r="B451" s="52" t="s">
+      <c r="B451" s="51" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="452" spans="1:2">
-      <c r="A452" s="53" t="s">
+      <c r="A452" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="B452" s="54" t="s">
+      <c r="B452" s="53" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="453" spans="1:2">
-      <c r="A453" s="53" t="s">
+      <c r="A453" s="52" t="s">
         <v>779</v>
       </c>
-      <c r="B453" s="54" t="s">
+      <c r="B453" s="53" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="454" spans="1:2">
-      <c r="A454" s="50" t="s">
+      <c r="A454" s="49" t="s">
         <v>781</v>
       </c>
-      <c r="B454" s="55" t="s">
+      <c r="B454" s="54" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="455" spans="1:2">
-      <c r="A455" s="50" t="s">
+      <c r="A455" s="49" t="s">
         <v>782</v>
       </c>
-      <c r="B455" s="55" t="s">
+      <c r="B455" s="54" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="456" spans="1:2">
-      <c r="A456" s="50" t="s">
+      <c r="A456" s="49" t="s">
         <v>371</v>
       </c>
-      <c r="B456" s="52" t="s">
+      <c r="B456" s="51" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="457" spans="1:2">
-      <c r="A457" s="50" t="s">
+      <c r="A457" s="49" t="s">
         <v>783</v>
       </c>
-      <c r="B457" s="52" t="s">
+      <c r="B457" s="51" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="458" spans="1:2">
-      <c r="A458" s="50" t="s">
+      <c r="A458" s="49" t="s">
         <v>784</v>
       </c>
-      <c r="B458" s="52" t="s">
+      <c r="B458" s="51" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="459" spans="1:2">
-      <c r="A459" s="50" t="s">
+      <c r="A459" s="49" t="s">
         <v>786</v>
       </c>
-      <c r="B459" s="51" t="s">
+      <c r="B459" s="50" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="460" spans="1:2">
-      <c r="A460" s="50" t="s">
+      <c r="A460" s="49" t="s">
         <v>788</v>
       </c>
-      <c r="B460" s="51" t="s">
+      <c r="B460" s="50" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="461" spans="1:2">
-      <c r="A461" s="50" t="s">
+      <c r="A461" s="49" t="s">
         <v>790</v>
       </c>
-      <c r="B461" s="51" t="s">
+      <c r="B461" s="50" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="462" spans="1:2">
-      <c r="A462" s="56" t="s">
+      <c r="A462" s="55" t="s">
         <v>359</v>
       </c>
-      <c r="B462" s="56">
+      <c r="B462" s="55">
         <v>2</v>
       </c>
     </row>
     <row r="463" spans="1:2">
-      <c r="A463" s="56" t="s">
+      <c r="A463" s="55" t="s">
         <v>360</v>
       </c>
-      <c r="B463" s="56">
+      <c r="B463" s="55">
         <v>3</v>
       </c>
     </row>
     <row r="464" spans="1:2">
-      <c r="A464" s="56" t="s">
+      <c r="A464" s="55" t="s">
         <v>361</v>
       </c>
-      <c r="B464" s="56">
+      <c r="B464" s="55">
         <v>4</v>
       </c>
     </row>
     <row r="465" spans="1:2">
-      <c r="A465" s="57" t="s">
+      <c r="A465" s="56" t="s">
         <v>354</v>
       </c>
-      <c r="B465" s="57">
+      <c r="B465" s="56">
         <v>150</v>
       </c>
     </row>
     <row r="466" spans="1:2">
-      <c r="A466" s="57" t="s">
+      <c r="A466" s="56" t="s">
         <v>355</v>
       </c>
-      <c r="B466" s="57">
+      <c r="B466" s="56">
         <v>250</v>
       </c>
     </row>
@@ -7873,7 +8207,7 @@
       <c r="A467" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="B467" s="8" t="s">
+      <c r="B467" s="7" t="s">
         <v>357</v>
       </c>
     </row>
@@ -7881,7 +8215,7 @@
       <c r="A468" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B468" s="8" t="s">
+      <c r="B468" s="7" t="s">
         <v>794</v>
       </c>
     </row>
@@ -7889,7 +8223,7 @@
       <c r="A469" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="B469" s="8" t="s">
+      <c r="B469" s="7" t="s">
         <v>796</v>
       </c>
     </row>
@@ -7897,7 +8231,7 @@
       <c r="A470" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="B470" s="8" t="s">
+      <c r="B470" s="7" t="s">
         <v>797</v>
       </c>
     </row>
@@ -7905,7 +8239,7 @@
       <c r="A471" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="B471" s="8" t="s">
+      <c r="B471" s="7" t="s">
         <v>799</v>
       </c>
     </row>
@@ -7913,7 +8247,7 @@
       <c r="A472" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="B472" s="8" t="s">
+      <c r="B472" s="7" t="s">
         <v>229</v>
       </c>
     </row>
@@ -7921,7 +8255,7 @@
       <c r="A473" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="B473" s="8" t="s">
+      <c r="B473" s="7" t="s">
         <v>281</v>
       </c>
     </row>
@@ -7929,7 +8263,7 @@
       <c r="A474" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="B474" s="8" t="s">
+      <c r="B474" s="7" t="s">
         <v>757</v>
       </c>
     </row>
@@ -7937,7 +8271,7 @@
       <c r="A475" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="B475" s="8" t="s">
+      <c r="B475" s="7" t="s">
         <v>804</v>
       </c>
     </row>
@@ -7945,7 +8279,7 @@
       <c r="A476" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="B476" s="8" t="s">
+      <c r="B476" s="7" t="s">
         <v>759</v>
       </c>
     </row>
@@ -7953,7 +8287,7 @@
       <c r="A477" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="B477" s="8" t="s">
+      <c r="B477" s="7" t="s">
         <v>806</v>
       </c>
     </row>
@@ -7961,7 +8295,7 @@
       <c r="A478" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="B478" s="8" t="s">
+      <c r="B478" s="7" t="s">
         <v>808</v>
       </c>
     </row>
@@ -7969,7 +8303,7 @@
       <c r="A479" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="B479" s="45" t="s">
+      <c r="B479" s="44" t="s">
         <v>809</v>
       </c>
     </row>
@@ -7977,7 +8311,7 @@
       <c r="A480" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="B480" s="8" t="s">
+      <c r="B480" s="7" t="s">
         <v>811</v>
       </c>
     </row>
@@ -7985,7 +8319,7 @@
       <c r="A481" s="2" t="s">
         <v>812</v>
       </c>
-      <c r="B481" s="8" t="s">
+      <c r="B481" s="7" t="s">
         <v>813</v>
       </c>
     </row>
@@ -7993,7 +8327,7 @@
       <c r="A482" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="B482" s="8" t="s">
+      <c r="B482" s="7" t="s">
         <v>229</v>
       </c>
     </row>
@@ -8001,7 +8335,7 @@
       <c r="A483" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="B483" s="8" t="s">
+      <c r="B483" s="7" t="s">
         <v>816</v>
       </c>
     </row>
@@ -8009,7 +8343,7 @@
       <c r="A484" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="B484" s="8" t="s">
+      <c r="B484" s="7" t="s">
         <v>818</v>
       </c>
     </row>
@@ -8017,7 +8351,7 @@
       <c r="A485" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="B485" s="8" t="s">
+      <c r="B485" s="7" t="s">
         <v>820</v>
       </c>
     </row>
@@ -8025,7 +8359,7 @@
       <c r="A486" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="B486" s="8" t="s">
+      <c r="B486" s="7" t="s">
         <v>822</v>
       </c>
     </row>
@@ -8033,7 +8367,7 @@
       <c r="A487" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="B487" s="8" t="s">
+      <c r="B487" s="7" t="s">
         <v>808</v>
       </c>
     </row>
@@ -8041,7 +8375,7 @@
       <c r="A488" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="B488" s="8" t="s">
+      <c r="B488" s="7" t="s">
         <v>229</v>
       </c>
     </row>
@@ -8049,7 +8383,7 @@
       <c r="A489" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="B489" s="8" t="s">
+      <c r="B489" s="7" t="s">
         <v>148</v>
       </c>
     </row>
@@ -8057,7 +8391,7 @@
       <c r="A490" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="B490" s="8" t="s">
+      <c r="B490" s="7" t="s">
         <v>827</v>
       </c>
     </row>
@@ -8065,7 +8399,7 @@
       <c r="A491" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="B491" s="8" t="s">
+      <c r="B491" s="7" t="s">
         <v>829</v>
       </c>
     </row>
@@ -8073,7 +8407,7 @@
       <c r="A492" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="B492" s="8" t="s">
+      <c r="B492" s="7" t="s">
         <v>831</v>
       </c>
     </row>
@@ -8081,7 +8415,7 @@
       <c r="A493" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="B493" s="8" t="s">
+      <c r="B493" s="7" t="s">
         <v>833</v>
       </c>
     </row>
@@ -8089,7 +8423,7 @@
       <c r="A494" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="B494" s="8" t="s">
+      <c r="B494" s="7" t="s">
         <v>835</v>
       </c>
     </row>
@@ -8097,7 +8431,7 @@
       <c r="A495" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="B495" s="8" t="s">
+      <c r="B495" s="7" t="s">
         <v>837</v>
       </c>
     </row>
@@ -8105,7 +8439,7 @@
       <c r="A496" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="B496" s="8" t="s">
+      <c r="B496" s="7" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8113,7 +8447,7 @@
       <c r="A497" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="B497" s="8" t="s">
+      <c r="B497" s="7" t="s">
         <v>841</v>
       </c>
     </row>
@@ -8121,7 +8455,7 @@
       <c r="A498" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="B498" s="8" t="s">
+      <c r="B498" s="7" t="s">
         <v>843</v>
       </c>
     </row>
@@ -8129,7 +8463,7 @@
       <c r="A499" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="B499" s="8" t="s">
+      <c r="B499" s="7" t="s">
         <v>845</v>
       </c>
     </row>
@@ -8137,7 +8471,7 @@
       <c r="A500" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="B500" s="8" t="s">
+      <c r="B500" s="7" t="s">
         <v>847</v>
       </c>
     </row>
@@ -8145,7 +8479,7 @@
       <c r="A501" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="B501" s="8" t="s">
+      <c r="B501" s="7" t="s">
         <v>849</v>
       </c>
     </row>
@@ -8153,7 +8487,7 @@
       <c r="A502" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="B502" s="8" t="s">
+      <c r="B502" s="7" t="s">
         <v>851</v>
       </c>
     </row>
@@ -8161,7 +8495,7 @@
       <c r="A503" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="B503" s="8" t="s">
+      <c r="B503" s="7" t="s">
         <v>853</v>
       </c>
     </row>
@@ -8169,7 +8503,7 @@
       <c r="A504" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="B504" s="8" t="s">
+      <c r="B504" s="7" t="s">
         <v>855</v>
       </c>
     </row>
@@ -8177,7 +8511,7 @@
       <c r="A505" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="B505" s="8" t="s">
+      <c r="B505" s="7" t="s">
         <v>857</v>
       </c>
     </row>
@@ -8185,7 +8519,7 @@
       <c r="A506" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="B506" s="8" t="s">
+      <c r="B506" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -8193,7 +8527,7 @@
       <c r="A507" s="2" t="s">
         <v>859</v>
       </c>
-      <c r="B507" s="8" t="s">
+      <c r="B507" s="7" t="s">
         <v>860</v>
       </c>
     </row>
@@ -8201,7 +8535,7 @@
       <c r="A508" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="B508" s="8" t="s">
+      <c r="B508" s="7" t="s">
         <v>307</v>
       </c>
     </row>
@@ -8209,7 +8543,7 @@
       <c r="A509" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="B509" s="8" t="s">
+      <c r="B509" s="7" t="s">
         <v>863</v>
       </c>
     </row>
@@ -8217,8 +8551,472 @@
       <c r="A510" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="B510" s="8" t="s">
+      <c r="B510" s="7" t="s">
         <v>865</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B511" s="7" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="B512" s="7" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B513" s="7" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="57" t="s">
+        <v>871</v>
+      </c>
+      <c r="B514" s="58" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="57" t="s">
+        <v>873</v>
+      </c>
+      <c r="B515" s="58" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="57" t="s">
+        <v>874</v>
+      </c>
+      <c r="B516" s="58" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="25" t="s">
+        <v>875</v>
+      </c>
+      <c r="B518" s="7" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="25" t="s">
+        <v>877</v>
+      </c>
+      <c r="B519" s="7" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="25" t="s">
+        <v>879</v>
+      </c>
+      <c r="B520" s="7" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="25" t="s">
+        <v>881</v>
+      </c>
+      <c r="B521" s="7" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="25" t="s">
+        <v>883</v>
+      </c>
+      <c r="B522" s="7" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="25" t="s">
+        <v>885</v>
+      </c>
+      <c r="B523" s="7" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="25" t="s">
+        <v>887</v>
+      </c>
+      <c r="B524" s="7" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="25" t="s">
+        <v>889</v>
+      </c>
+      <c r="B525" s="7" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" s="25" t="s">
+        <v>891</v>
+      </c>
+      <c r="B526" s="7" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" s="25" t="s">
+        <v>893</v>
+      </c>
+      <c r="B527" s="7" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" s="25" t="s">
+        <v>895</v>
+      </c>
+      <c r="B528" s="7" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" s="25" t="s">
+        <v>897</v>
+      </c>
+      <c r="B529" s="7" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" s="25" t="s">
+        <v>899</v>
+      </c>
+      <c r="B530" s="7" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="25" t="s">
+        <v>901</v>
+      </c>
+      <c r="B531" s="7" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" s="25" t="s">
+        <v>903</v>
+      </c>
+      <c r="B532" s="7" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" s="25" t="s">
+        <v>905</v>
+      </c>
+      <c r="B533" s="7" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" s="25" t="s">
+        <v>907</v>
+      </c>
+      <c r="B534" s="7" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="25" t="s">
+        <v>909</v>
+      </c>
+      <c r="B535" s="7" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" s="25" t="s">
+        <v>911</v>
+      </c>
+      <c r="B536" s="7" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" s="25" t="s">
+        <v>913</v>
+      </c>
+      <c r="B537" s="7" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" s="25" t="s">
+        <v>915</v>
+      </c>
+      <c r="B538" s="7" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="25" t="s">
+        <v>917</v>
+      </c>
+      <c r="B539" s="7" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" s="25" t="s">
+        <v>919</v>
+      </c>
+      <c r="B540" s="7" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" s="25" t="s">
+        <v>921</v>
+      </c>
+      <c r="B541" s="7" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" s="25" t="s">
+        <v>923</v>
+      </c>
+      <c r="B542" s="7" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="25" t="s">
+        <v>925</v>
+      </c>
+      <c r="B543" s="7" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" s="25" t="s">
+        <v>927</v>
+      </c>
+      <c r="B544" s="7" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" s="25" t="s">
+        <v>929</v>
+      </c>
+      <c r="B545" s="7" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" s="25" t="s">
+        <v>931</v>
+      </c>
+      <c r="B546" s="7" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" s="25" t="s">
+        <v>933</v>
+      </c>
+      <c r="B547" s="7" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" s="25" t="s">
+        <v>935</v>
+      </c>
+      <c r="B548" s="7" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" s="25" t="s">
+        <v>937</v>
+      </c>
+      <c r="B549" s="7" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" t="s">
+        <v>939</v>
+      </c>
+      <c r="B550" s="7" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" s="25" t="s">
+        <v>941</v>
+      </c>
+      <c r="B551" s="7" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" s="59" t="s">
+        <v>943</v>
+      </c>
+      <c r="B552" s="7" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" s="59" t="s">
+        <v>945</v>
+      </c>
+      <c r="B553" s="7" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="59" t="s">
+        <v>947</v>
+      </c>
+      <c r="B554" s="7" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" s="60" t="s">
+        <v>949</v>
+      </c>
+      <c r="B555" s="7" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" s="60" t="s">
+        <v>951</v>
+      </c>
+      <c r="B556" s="7" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="59" t="s">
+        <v>953</v>
+      </c>
+      <c r="B557" s="61" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="60" t="s">
+        <v>954</v>
+      </c>
+      <c r="B558" s="7" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="60" t="s">
+        <v>956</v>
+      </c>
+      <c r="B559" s="7" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="59" t="s">
+        <v>957</v>
+      </c>
+      <c r="B560" s="7" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="25" t="s">
+        <v>959</v>
+      </c>
+      <c r="B561" s="7" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="25" t="s">
+        <v>961</v>
+      </c>
+      <c r="B562" s="7" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="60" t="s">
+        <v>962</v>
+      </c>
+      <c r="B563" s="7" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" s="25" t="s">
+        <v>964</v>
+      </c>
+      <c r="B564" s="7" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" s="25" t="s">
+        <v>966</v>
+      </c>
+      <c r="B565" s="7" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" s="25" t="s">
+        <v>968</v>
+      </c>
+      <c r="B566" s="7" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" s="25" t="s">
+        <v>970</v>
+      </c>
+      <c r="B567" s="7" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" s="25" t="s">
+        <v>972</v>
+      </c>
+      <c r="B568" s="7" t="s">
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -8247,50 +9045,50 @@
     </row>
     <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>866</v>
+        <v>973</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>867</v>
+        <v>974</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>868</v>
+        <v>975</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>869</v>
+        <v>976</v>
       </c>
     </row>
     <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>870</v>
+        <v>977</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>871</v>
+        <v>978</v>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>872</v>
+        <v>979</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>873</v>
+        <v>980</v>
       </c>
     </row>
     <row r="6" ht="187.2" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>874</v>
+        <v>981</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>875</v>
+        <v>982</v>
       </c>
     </row>
     <row r="7" ht="409.5" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>877</v>
+        <v>983</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>984</v>
       </c>
     </row>
     <row r="8" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="5130"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="5130" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -2776,6 +2776,598 @@
     <t>SOHeaderQuery</t>
   </si>
   <si>
+    <t>SOLineQuery</t>
+  </si>
+  <si>
+    <t>SELECT soq_prod_id "Item ID",soq_prod_rev "Item Rev",
+       soq_prod_desc1 "Item Desc",
+       soq_uom "Sale UOM",
+       soq_hsn_code "HSN Code",
+       soq_tax_pct "Tax Percentage",
+       soq_price_basis "Price Basis Type",
+       DECODE (soq_price_basis,
+               'C', 'Open Order',
+               'L', 'Catalog Price',
+               'P', 'Price List',
+               'S', 'Standard Price',
+               'U', 'User Defined')
+          "Price Basis Desc",
+       soq_cont_cat_no "Contract Number",
+       soq_catalog_no "Catalog / Price List Number",
+       soq_prod_uom "Stock UOM",
+       soq_conv_factor "Conversion Factor",
+       soq_tolr_type "Tolerance Type",
+       soq_cust_prod_id "Customer Item ID",
+       soq_cust_prod_desc "Customer Item Desc",
+       (SELECT store_desc1
+          FROM stores
+         WHERE store_bu = soq_bu AND store_id = soq_store_id
+        UNION ALL
+        SELECT dept_name1
+          FROM departments
+         WHERE dept_bu = soq_bu AND dept_id = soq_store_id)
+          "Warehouse Description",
+       soq_prod_subcls_desc "SubClass Desc",
+       soq_prod_cls_desc "Class Desc",
+       (SELECT spc_class_desc
+          FROM sales_price_classes
+         WHERE spc_bu = soq_bu AND spc_class_id = soq_sales_price_class)
+          "Price Class",
+       soq_promotion_flag "Promotional",
+       soq_trd_assbl_val "Trade Ass. Val.",
+       soq_disc_pct "Trade Disc. %",
+       soq_disc_amt "Trade Disc. Amt.",
+       soq_spl_assbl_val "Spl. Ass. Val.",
+       soq_spl_disc_pct "Spl. Disc. %",
+       soq_spl_disc_amt "Spl. Disc. Amt.",
+       soq_cash_assbl_val "Cash Ass. Val.",
+       soq_cash_disc_pct "Cash Disc. %",
+       soq_cash_disc_amt "Cash Disc. Amt.",
+       soq_gross_amt "Gross Amt.",
+       soq_disc_amt_per_qty "Disc. Amt. / Qty.",
+       soq_tax_amt "Tax Amt.",
+       soq_net_amt "Net Amt.",
+       soq_gross_amt "Gross Amt.",
+       soq_disc_amt_per_qty "Disc. Amt. / Qty.",
+       soq_tax_amt "Tax Amt.",
+       soq_net_amt "Net Amt.",
+       soq_qty_ordered "Ord. Qty.",
+       soq_price "Unit Price",
+       soq_tot_disc_amt "Disc. Amt.",
+       soq_igst_amt "IGST Amt.",
+       soq_sgst_amt "SGST Amt.",
+       soq_cgst_amt "CGST Amt."
+  FROM sales_order_hd, sales_order_qtys
+ WHERE     soh_bu = soq_bu
+       AND soh_order_no = soq_order_no
+       AND soh_bu = 'TVSA'
+       AND soh_order_no = '${SONO}'</t>
+  </si>
+  <si>
+    <t>OsoaQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT srcahd_plnt_loc_id "loc id",
+       srcahd_plnt "unit",
+       srcahd_doc_no "Doc. No.",
+       srcahd_amd_no "Amd. No.",
+       srcahd_cust_id "customer id",
+       (SELECT suplr_name1
+          FROM suppliers
+         WHERE suplr_bu = srcahd_bu AND suplr_suplr_id = srcahd_cust_id)
+          "customer name",
+       srcaln_prod_id "item id",
+       srcaln_prod_rev "item rev",
+       (SELECT prod_desc11
+          FROM products
+         WHERE     prod_bu = srcaln_bu
+               AND prod_id = srcaln_prod_id
+               AND prod_rev = srcaln_prod_rev)
+          "item descripition",
+       srcaln_uom "uom",
+       srcaln_disc_pct "disc_pct",
+       srcaln_old_price "Existing Price",
+       srcaln_new_price "new_price",
+       srcaln_mrp_price "MRP Price",
+       srcaln_hsn_code "HSN code",
+       srcaln_tax_pct "Tax Percent",
+       srcaln_cgst_amt "CGST",
+       srcaln_sgst_amt "SGST",
+       srcaln_igst_amt "IGST",
+       srcaln_utgst_amt "UTGST"
+  FROM sales_rate_contr_ament_hd, sales_rate_contr_ament_ln
+ WHERE     srcahd_bu = srcaln_bu
+       AND srcahd_plnt = srcaln_plnt
+       AND srcahd_doc_no = '${OSOANO}'
+    AND srcahd_doc_no = srcaln_doc_no
+       AND srcahd_bu =  'TVSA' </t>
+  </si>
+  <si>
+    <t>SOAdvanceQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   SELECT soh_adv_pct,
+       soh_adv_rcvd,
+       soh_adv_tax_pct,
+       soh_adv_req_flag,
+       soh_adv_to_rcvd,
+       soh_adv_rcpt_inprg,
+SOH_ADV_DOC_NO
+  FROM sales_order_hd
+  WHERE soh_bu = 'TVSA'
+  and soh_order_no = '${SONO}'</t>
+  </si>
+  <si>
+    <t>SOCustomerDetailsQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  SELECT (SELECT NVL(state_name1,state_name2) FROM states WHERE state_bu = suplr_bu AND state_id = suplr_state)"Customer State"
+       FROM suppliers
+       WHERE suplr_bu = 'TVSA'
+       AND suplr_suplr_id = '${SONO}'</t>
+  </si>
+  <si>
+    <t>SOUnitDetailsQuery</t>
+  </si>
+  <si>
+    <t>SELECT  (SELECT NVL(state_name1,state_name2) FROM states WHERE state_bu = bup_bu AND state_id = BUP_STATE)"Unit State"
+      FROM bus_unit_plants
+     WHERE bup_bu ='TVSA'
+       AND bup_plant_id ='${SONO}'</t>
+  </si>
+  <si>
+    <t>SOLineDetails1&amp;2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  select soq_cess_pct,soq_cess_amt,SOQ_GST_EXEMPT_FLAG,SOQ_GST_INPUT_TYPE,SOQ_SAL_ACCT_ID,SOQ_SAL_CC_ID,SOQ_DISC_ACCT_ID,SOQ_DISC_CC_ID,SOQ_CUST_PO_NO,SOQ_CUST_PO_REV,SOQ_CUST_PO_DATE,
+  SOQ_PO_SL_SEQ_NO,SOQ_SQ_PFX,SOQ_SQ_NO,SOQ_SQ_SEQ_NO,SOQ_SQ_REV,SOQ_OPO_PO_NO,SOQ_OPO_PO_DATE,SOQ_PO_SEQ_NO,SOQ_CONT_CAT_NO,SOQ_PO_REF,SOQ_CATALOG_NO,
+  SOQ_CUST_PROD_ID,SOQ_CUST_PROD_DESC,SOQ_STORE_NAME,SOQ_PROD_EXT_DESC,SOQ_DESP_DATE,SOQ_RQRD_DATE,SOQ_PROMOTION_FLAG,SOQ_SALES_PRICE_CLASS,SOQ_SCHLD_DESC,SOQ_TOLERANCE_PCT,
+  SOQ_PROD_UOM,SOQ_CONV_FACTOR,SOQ_TOLR_QTY,SOQ_TOLR_TYPE,SOQ_BOM_NO,SOQ_BOM_NAME,SOQ_BOM_REVISION_NUM,SOQ_MARGIN_PCT,SOQ_LIST_PRICE,SOQ_MRP_PRICE,SOQ_SQ_PRICE,SOQ_INSTL_RQRD_FLAG
+         from sales_order_qtys
+         where soq_bu ='TVSA'
+           and soq_order_no ='${SONO}'</t>
+  </si>
+  <si>
+    <t>PaymentTermQuery</t>
+  </si>
+  <si>
+    <t>SELECT term_desc1,
+       trln_mtrl_pct,
+       trln_tax_pct,
+       TRLN_CLAIM_TYPE
+  FROM terms_ln,
+       terms_hd
+ WHERE  term_bu = trln_bu
+   AND term_bu = 'TVSA'
+   AND  TRLN_CLAIM_TYPE ='A'
+  AND term_term_id = trln_term_id
+  AND  term_desc1 = '${SONO}'</t>
+  </si>
+  <si>
+    <t>AdvanceReceiptQuery</t>
+  </si>
+  <si>
+    <t>SELECT
+        pard_doc_no Doc_no,
+        pard_plnt Unit,
+        pard_ord_pfx ord_pfx,
+        pard_ord_no ord_no,
+        pard_party_id Party_id,
+        pard_prop_adv_pct Adv_Percentage,
+        pard_prop_adv_amt Adv_Amt,
+        pard_curcy_id Curcy,
+        pard_ord_amt Ord_amt,
+        pard_rct_inprog_amt Rcpt_inprog_amt,
+        pard_rct_amt Rcpt_Amt,
+        pard_close_amt Closed_amt
+   FROM prop_adv_rct_doc
+  WHERE pard_bu = 'TVSA'
+    AND pard_doc_no ='${SONO}'</t>
+  </si>
+  <si>
+    <t>Stock Query</t>
+  </si>
+  <si>
+    <t>SELECT stock_qty_hand,
+      (SELECT stcost_cost
+  FROM stock_costs
+ WHERE stcost_bu = 'TVSA'
+   AND stcost_store_id = stock_store_id
+   AND stcost_prod_id = stock_prod_id
+   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
+  FROM stocks
+ WHERE stock_bu = 'TVSA'
+   AND stock_store_id = '${SONO}'
+   AND stock_prod_id = 'TVS-RM-KDK-10'
+   AND stock_prod_rev = '0'</t>
+  </si>
+  <si>
+    <t>Stock Query1</t>
+  </si>
+  <si>
+    <t>SELECT stock_qty_hand,
+      (SELECT stcost_cost
+  FROM stock_costs
+ WHERE stcost_bu = 'TVSA'
+   AND stcost_store_id = stock_store_id
+   AND stcost_prod_id = stock_prod_id
+   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
+  FROM stocks
+ WHERE stock_bu = 'TVSA'
+   AND stock_store_id = '${SONO}'
+   AND stock_prod_id ='${PONO}'
+   AND stock_prod_rev = '0'</t>
+  </si>
+  <si>
+    <t>SalesOrderChargesQuery</t>
+  </si>
+  <si>
+    <t>SELECT
+       sotc_bu,
+       sotc_ord_no,
+       sotc_seq_no,
+       sotc_prod_id,
+       (SELECT prod_desc11
+          FROM products
+         WHERE prod_bu ='TVSA'
+           AND prod_id = sotc_prod_id
+           AND prod_rev = sotc_prod_rev)ITEM_DESC,
+       sotc_prod_rev,
+       sotc_hsn_code,
+       sotc_qty,
+       sotc_chrg_basis,
+       sotc_chrg_pct,
+       sotc_chrg_pct sotc_chrg_pct1,
+       sotc_chrg_amt,
+       sotc_chrg_amt sotc_chrg_amt1,
+       sotc_gst_exempt_flag,
+       sotc_gst_input_type,
+       sotc_cre_by,
+       sotc_cre_ip_addr,
+       sotc_cre_os_user,
+       sotc_cre_date,
+       sotc_upd_by,
+       sotc_upd_ip_addr,
+       sotc_upd_os_user,
+       sotc_upd_date,
+       sotc_cre_emp_id,
+       sotc_upd_emp_id,
+       sotc_tcs_avail_flag,
+       sotc_sal_acct_id,
+       sotc_sal_cc_id,
+       sotc_tariff_code,
+       sotc_cgst_pct,
+       sotc_sgst_pct,
+       sotc_utgst_pct,
+       sotc_cess_pct,
+       sotc_igst_amt,
+       sotc_cgst_amt,
+       sotc_sgst_amt,
+       sotc_utgst_amt,
+       sotc_cess_amt,
+       sotc_tax_pct
+  FROM so_oth_tax_charges
+  WHERE sotc_bu = 'TVSA'
+    AND sotc_ord_no ='${SONO}'</t>
+  </si>
+  <si>
+    <t>ItemShipSetQuery</t>
+  </si>
+  <si>
+    <t>SELECT PS_SS_PROD_ID, PS_SS_PROD_REV,
+       ( SELECT prod_desc11
+          FROM products
+         WHERE prod_bu  = ps_bu
+           AND prod_id  = PS_SS_PROD_ID
+           AND prod_rev = PS_SS_PROD_REV) PSI_SS_PROD_DESC,
+           PS_SS_QTY,
+           (SELECT PROD_UOM
+             FROM products
+            WHERE prod_bu  = ps_bu
+              AND prod_id  = PS_SS_PROD_ID
+              AND prod_rev = PS_SS_PROD_REV)UOM
+FROM PROD_SHIPSET
+  where   PS_BU =  'TVSA'
+    and   PS_FG_PROD_ID  = '${SONO}'</t>
+  </si>
+  <si>
+    <t>SODBincludeAdvFlagColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_REQ_FLAG</t>
+  </si>
+  <si>
+    <t>SODBAdvToBeReceivedColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_TO_RCVD</t>
+  </si>
+  <si>
+    <t>SODBAdvPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_PCT</t>
+  </si>
+  <si>
+    <t>SODBAdvanceReceivedColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_RCVD</t>
+  </si>
+  <si>
+    <t>SODBAdvTaxPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_TAX_PCT</t>
+  </si>
+  <si>
+    <t>SODBAdvReceiptInProgressColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_RCPT_INPRG</t>
+  </si>
+  <si>
+    <t>SODBAdvDocumentNumberColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_DOC_NO</t>
+  </si>
+  <si>
+    <t>SODBUnitAddessColumnName</t>
+  </si>
+  <si>
+    <t>Unit State</t>
+  </si>
+  <si>
+    <t>SODBCustomerAddessColumnName</t>
+  </si>
+  <si>
+    <t>Customer State</t>
+  </si>
+  <si>
+    <t>SODBCessAmtColumnName</t>
+  </si>
+  <si>
+    <t>SOQ_CESS_AMT</t>
+  </si>
+  <si>
+    <t>SODBPaymentTermMaterialPercentageColumnName</t>
+  </si>
+  <si>
+    <t>TRLN_MTRL_PCT</t>
+  </si>
+  <si>
+    <t>SODBPaymentTermTaxPercentageColumnName</t>
+  </si>
+  <si>
+    <t>TRLN_TAX_PCT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBDOCNumberColumnName</t>
+  </si>
+  <si>
+    <t>DOC_NO</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderUnitColumnName</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderPrefixColumnName</t>
+  </si>
+  <si>
+    <t>ORD_PFX</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderNumberColumnName</t>
+  </si>
+  <si>
+    <t>ORD_NO</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderPartyIDColumnName</t>
+  </si>
+  <si>
+    <t>PARTY_ID</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderPercentageColumnName</t>
+  </si>
+  <si>
+    <t>ADV_PERCENTAGE</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderAdvAmountColumnName</t>
+  </si>
+  <si>
+    <t>ADV_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderCurrencyColumnName</t>
+  </si>
+  <si>
+    <t>CURCY</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderAmountColumnName</t>
+  </si>
+  <si>
+    <t>ORD_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderInProgressAmountColumnName</t>
+  </si>
+  <si>
+    <t>RCPT_INPROG_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderReceivedAmountColumnName</t>
+  </si>
+  <si>
+    <t>RCPT_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderClosedAmountColumnName</t>
+  </si>
+  <si>
+    <t>CLOSED_AMT</t>
+  </si>
+  <si>
+    <t>SODBHeaderDocumentStatusColumnName</t>
+  </si>
+  <si>
+    <t>SOH_STATUS</t>
+  </si>
+  <si>
+    <t>StockQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>STOCK_QTY_HAND</t>
+  </si>
+  <si>
+    <t>WH</t>
+  </si>
+  <si>
+    <t>RM KD</t>
+  </si>
+  <si>
+    <t>StockCostDBColumnName</t>
+  </si>
+  <si>
+    <t>STCOST_COST</t>
+  </si>
+  <si>
+    <t>PRRequestedQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>PRL_REQUESTED_QTY</t>
+  </si>
+  <si>
+    <t>PROrderedQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>PRL_ORDERED_QTY</t>
+  </si>
+  <si>
+    <t>SODBCGSTColumnName</t>
+  </si>
+  <si>
+    <t>CGST Amt.</t>
+  </si>
+  <si>
+    <t>SODBSGSTColumnName</t>
+  </si>
+  <si>
+    <t>SGST Amt.</t>
+  </si>
+  <si>
+    <t>SODBIGSTColumnName</t>
+  </si>
+  <si>
+    <t>IGST Amt.</t>
+  </si>
+  <si>
+    <t>PONO</t>
+  </si>
+  <si>
+    <t>${PONO}</t>
+  </si>
+  <si>
+    <t>SO_FREE_SAMPLE</t>
+  </si>
+  <si>
+    <t>SO - FREE SAMPLE</t>
+  </si>
+  <si>
+    <t>SO_FREE_REPLACEMENT</t>
+  </si>
+  <si>
+    <t>SO - FREE REPLACEMENT</t>
+  </si>
+  <si>
+    <t>SO_SCRAP</t>
+  </si>
+  <si>
+    <t>SO - SCRAP</t>
+  </si>
+  <si>
+    <t>SO_SERVICE</t>
+  </si>
+  <si>
+    <t>SO - SERVICE</t>
+  </si>
+  <si>
+    <t>SO_Local_Customer</t>
+  </si>
+  <si>
+    <t>CUS10002</t>
+  </si>
+  <si>
+    <t>SO_Local_Customer_Desc</t>
+  </si>
+  <si>
+    <t>SO_SEZ_CUSTOMER</t>
+  </si>
+  <si>
+    <t>CUS10005</t>
+  </si>
+  <si>
+    <t>SO_SEZ_CUSTOMER_DESC</t>
+  </si>
+  <si>
+    <t>SO_Demo_Exhibition</t>
+  </si>
+  <si>
+    <t>SO - DEMO / EXHN.</t>
+  </si>
+  <si>
+    <t>SODBCESSPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOQ_CESS_PCT</t>
+  </si>
+  <si>
+    <t>SODBCESSAmountColumnName</t>
+  </si>
+  <si>
+    <t>CESS_HSN_CODE</t>
+  </si>
+  <si>
+    <t>0074</t>
+  </si>
+  <si>
+    <t>SODBChargeAmountColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_CHRG_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeIGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_IGST_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeCGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_CGST_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeSGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_SGST_AMT</t>
+  </si>
+  <si>
+    <t>EntryCompletedStatus</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
     <t>SELECT soh_cust_id "Customer ID",
        soh_cust_name "Customer Description",
        soh_currency "Currency",
@@ -2846,605 +3438,14 @@
                   AND supsubgroup_bu = suplr_bu
                   AND suplr_bu = soh_bu
                   AND suplr_suplr_id = soh_cust_id) "SubGroup",
-                  func_find_employee_desc(soh_bu ,SOH_TE_MGR_ID,1) "Sales Zone Mgr"   
+                  func_find_employee_desc(soh_bu ,SOH_TE_MGR_ID,1) "Sales Zone Mgr"   ,
+                  DECODE(soh_status,'N','Draft','A','Approved','O','Entry Completed','C','Cancelled')soh_status
   FROM sales_order_hd, suppliers
  WHERE     soh_bu = suplr_bu
        AND soh_cust_id = suplr_suplr_id
        AND suplr_status = 'A'
        AND soh_bu = 'TVSA'
        AND soh_order_no ='${SONO}'</t>
-  </si>
-  <si>
-    <t>SOLineQuery</t>
-  </si>
-  <si>
-    <t>SELECT soq_prod_id "Item ID",soq_prod_rev "Item Rev",
-       soq_prod_desc1 "Item Desc",
-       soq_uom "Sale UOM",
-       soq_hsn_code "HSN Code",
-       soq_tax_pct "Tax Percentage",
-       soq_price_basis "Price Basis Type",
-       DECODE (soq_price_basis,
-               'C', 'Open Order',
-               'L', 'Catalog Price',
-               'P', 'Price List',
-               'S', 'Standard Price',
-               'U', 'User Defined')
-          "Price Basis Desc",
-       soq_cont_cat_no "Contract Number",
-       soq_catalog_no "Catalog / Price List Number",
-       soq_prod_uom "Stock UOM",
-       soq_conv_factor "Conversion Factor",
-       soq_tolr_type "Tolerance Type",
-       soq_cust_prod_id "Customer Item ID",
-       soq_cust_prod_desc "Customer Item Desc",
-       (SELECT store_desc1
-          FROM stores
-         WHERE store_bu = soq_bu AND store_id = soq_store_id
-        UNION ALL
-        SELECT dept_name1
-          FROM departments
-         WHERE dept_bu = soq_bu AND dept_id = soq_store_id)
-          "Warehouse Description",
-       soq_prod_subcls_desc "SubClass Desc",
-       soq_prod_cls_desc "Class Desc",
-       (SELECT spc_class_desc
-          FROM sales_price_classes
-         WHERE spc_bu = soq_bu AND spc_class_id = soq_sales_price_class)
-          "Price Class",
-       soq_promotion_flag "Promotional",
-       soq_trd_assbl_val "Trade Ass. Val.",
-       soq_disc_pct "Trade Disc. %",
-       soq_disc_amt "Trade Disc. Amt.",
-       soq_spl_assbl_val "Spl. Ass. Val.",
-       soq_spl_disc_pct "Spl. Disc. %",
-       soq_spl_disc_amt "Spl. Disc. Amt.",
-       soq_cash_assbl_val "Cash Ass. Val.",
-       soq_cash_disc_pct "Cash Disc. %",
-       soq_cash_disc_amt "Cash Disc. Amt.",
-       soq_gross_amt "Gross Amt.",
-       soq_disc_amt_per_qty "Disc. Amt. / Qty.",
-       soq_tax_amt "Tax Amt.",
-       soq_net_amt "Net Amt.",
-       soq_gross_amt "Gross Amt.",
-       soq_disc_amt_per_qty "Disc. Amt. / Qty.",
-       soq_tax_amt "Tax Amt.",
-       soq_net_amt "Net Amt.",
-       soq_qty_ordered "Ord. Qty.",
-       soq_price "Unit Price",
-       soq_tot_disc_amt "Disc. Amt.",
-       soq_igst_amt "IGST Amt.",
-       soq_sgst_amt "SGST Amt.",
-       soq_cgst_amt "CGST Amt."
-  FROM sales_order_hd, sales_order_qtys
- WHERE     soh_bu = soq_bu
-       AND soh_order_no = soq_order_no
-       AND soh_bu = 'TVSA'
-       AND soh_order_no = '${SONO}'</t>
-  </si>
-  <si>
-    <t>OsoaQuery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT srcahd_plnt_loc_id "loc id",
-       srcahd_plnt "unit",
-       srcahd_doc_no "Doc. No.",
-       srcahd_amd_no "Amd. No.",
-       srcahd_cust_id "customer id",
-       (SELECT suplr_name1
-          FROM suppliers
-         WHERE suplr_bu = srcahd_bu AND suplr_suplr_id = srcahd_cust_id)
-          "customer name",
-       srcaln_prod_id "item id",
-       srcaln_prod_rev "item rev",
-       (SELECT prod_desc11
-          FROM products
-         WHERE     prod_bu = srcaln_bu
-               AND prod_id = srcaln_prod_id
-               AND prod_rev = srcaln_prod_rev)
-          "item descripition",
-       srcaln_uom "uom",
-       srcaln_disc_pct "disc_pct",
-       srcaln_old_price "Existing Price",
-       srcaln_new_price "new_price",
-       srcaln_mrp_price "MRP Price",
-       srcaln_hsn_code "HSN code",
-       srcaln_tax_pct "Tax Percent",
-       srcaln_cgst_amt "CGST",
-       srcaln_sgst_amt "SGST",
-       srcaln_igst_amt "IGST",
-       srcaln_utgst_amt "UTGST"
-  FROM sales_rate_contr_ament_hd, sales_rate_contr_ament_ln
- WHERE     srcahd_bu = srcaln_bu
-       AND srcahd_plnt = srcaln_plnt
-       AND srcahd_doc_no = '${OSOANO}'
-    AND srcahd_doc_no = srcaln_doc_no
-       AND srcahd_bu =  'TVSA' </t>
-  </si>
-  <si>
-    <t>SOAdvanceQuery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   SELECT soh_adv_pct,
-       soh_adv_rcvd,
-       soh_adv_tax_pct,
-       soh_adv_req_flag,
-       soh_adv_to_rcvd,
-       soh_adv_rcpt_inprg,
-SOH_ADV_DOC_NO
-  FROM sales_order_hd
-  WHERE soh_bu = 'TVSA'
-  and soh_order_no = '${SONO}'</t>
-  </si>
-  <si>
-    <t>SOCustomerDetailsQuery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SELECT (SELECT NVL(state_name1,state_name2) FROM states WHERE state_bu = suplr_bu AND state_id = suplr_state)"Customer State"
-       FROM suppliers
-       WHERE suplr_bu = 'TVSA'
-       AND suplr_suplr_id = '${SONO}'</t>
-  </si>
-  <si>
-    <t>SOUnitDetailsQuery</t>
-  </si>
-  <si>
-    <t>SELECT  (SELECT NVL(state_name1,state_name2) FROM states WHERE state_bu = bup_bu AND state_id = BUP_STATE)"Unit State"
-      FROM bus_unit_plants
-     WHERE bup_bu ='TVSA'
-       AND bup_plant_id ='${SONO}'</t>
-  </si>
-  <si>
-    <t>SOLineDetails1&amp;2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  select soq_cess_pct,soq_cess_amt,SOQ_GST_EXEMPT_FLAG,SOQ_GST_INPUT_TYPE,SOQ_SAL_ACCT_ID,SOQ_SAL_CC_ID,SOQ_DISC_ACCT_ID,SOQ_DISC_CC_ID,SOQ_CUST_PO_NO,SOQ_CUST_PO_REV,SOQ_CUST_PO_DATE,
-  SOQ_PO_SL_SEQ_NO,SOQ_SQ_PFX,SOQ_SQ_NO,SOQ_SQ_SEQ_NO,SOQ_SQ_REV,SOQ_OPO_PO_NO,SOQ_OPO_PO_DATE,SOQ_PO_SEQ_NO,SOQ_CONT_CAT_NO,SOQ_PO_REF,SOQ_CATALOG_NO,
-  SOQ_CUST_PROD_ID,SOQ_CUST_PROD_DESC,SOQ_STORE_NAME,SOQ_PROD_EXT_DESC,SOQ_DESP_DATE,SOQ_RQRD_DATE,SOQ_PROMOTION_FLAG,SOQ_SALES_PRICE_CLASS,SOQ_SCHLD_DESC,SOQ_TOLERANCE_PCT,
-  SOQ_PROD_UOM,SOQ_CONV_FACTOR,SOQ_TOLR_QTY,SOQ_TOLR_TYPE,SOQ_BOM_NO,SOQ_BOM_NAME,SOQ_BOM_REVISION_NUM,SOQ_MARGIN_PCT,SOQ_LIST_PRICE,SOQ_MRP_PRICE,SOQ_SQ_PRICE,SOQ_INSTL_RQRD_FLAG
-         from sales_order_qtys
-         where soq_bu ='TVSA'
-           and soq_order_no ='${SONO}'</t>
-  </si>
-  <si>
-    <t>PaymentTermQuery</t>
-  </si>
-  <si>
-    <t>SELECT term_desc1,
-       trln_mtrl_pct,
-       trln_tax_pct,
-       TRLN_CLAIM_TYPE
-  FROM terms_ln,
-       terms_hd
- WHERE  term_bu = trln_bu
-   AND term_bu = 'TVSA'
-   AND  TRLN_CLAIM_TYPE ='A'
-  AND term_term_id = trln_term_id
-  AND  term_desc1 = '${SONO}'</t>
-  </si>
-  <si>
-    <t>AdvanceReceiptQuery</t>
-  </si>
-  <si>
-    <t>SELECT
-        pard_doc_no Doc_no,
-        pard_plnt Unit,
-        pard_ord_pfx ord_pfx,
-        pard_ord_no ord_no,
-        pard_party_id Party_id,
-        pard_prop_adv_pct Adv_Percentage,
-        pard_prop_adv_amt Adv_Amt,
-        pard_curcy_id Curcy,
-        pard_ord_amt Ord_amt,
-        pard_rct_inprog_amt Rcpt_inprog_amt,
-        pard_rct_amt Rcpt_Amt,
-        pard_close_amt Closed_amt
-   FROM prop_adv_rct_doc
-  WHERE pard_bu = 'TVSA'
-    AND pard_doc_no ='${SONO}'</t>
-  </si>
-  <si>
-    <t>Stock Query</t>
-  </si>
-  <si>
-    <t>SELECT stock_qty_hand,
-      (SELECT stcost_cost
-  FROM stock_costs
- WHERE stcost_bu = 'TVSA'
-   AND stcost_store_id = stock_store_id
-   AND stcost_prod_id = stock_prod_id
-   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
-  FROM stocks
- WHERE stock_bu = 'TVSA'
-   AND stock_store_id = '${SONO}'
-   AND stock_prod_id = 'TVS-RM-KDK-10'
-   AND stock_prod_rev = '0'</t>
-  </si>
-  <si>
-    <t>Stock Query1</t>
-  </si>
-  <si>
-    <t>SELECT stock_qty_hand,
-      (SELECT stcost_cost
-  FROM stock_costs
- WHERE stcost_bu = 'TVSA'
-   AND stcost_store_id = stock_store_id
-   AND stcost_prod_id = stock_prod_id
-   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
-  FROM stocks
- WHERE stock_bu = 'TVSA'
-   AND stock_store_id = '${SONO}'
-   AND stock_prod_id ='${PONO}'
-   AND stock_prod_rev = '0'</t>
-  </si>
-  <si>
-    <t>SalesOrderChargesQuery</t>
-  </si>
-  <si>
-    <t>SELECT
-       sotc_bu,
-       sotc_ord_no,
-       sotc_seq_no,
-       sotc_prod_id,
-       (SELECT prod_desc11
-          FROM products
-         WHERE prod_bu ='TVSA'
-           AND prod_id = sotc_prod_id
-           AND prod_rev = sotc_prod_rev)ITEM_DESC,
-       sotc_prod_rev,
-       sotc_hsn_code,
-       sotc_qty,
-       sotc_chrg_basis,
-       sotc_chrg_pct,
-       sotc_chrg_pct sotc_chrg_pct1,
-       sotc_chrg_amt,
-       sotc_chrg_amt sotc_chrg_amt1,
-       sotc_gst_exempt_flag,
-       sotc_gst_input_type,
-       sotc_cre_by,
-       sotc_cre_ip_addr,
-       sotc_cre_os_user,
-       sotc_cre_date,
-       sotc_upd_by,
-       sotc_upd_ip_addr,
-       sotc_upd_os_user,
-       sotc_upd_date,
-       sotc_cre_emp_id,
-       sotc_upd_emp_id,
-       sotc_tcs_avail_flag,
-       sotc_sal_acct_id,
-       sotc_sal_cc_id,
-       sotc_tariff_code,
-       sotc_cgst_pct,
-       sotc_sgst_pct,
-       sotc_utgst_pct,
-       sotc_cess_pct,
-       sotc_igst_amt,
-       sotc_cgst_amt,
-       sotc_sgst_amt,
-       sotc_utgst_amt,
-       sotc_cess_amt,
-       sotc_tax_pct
-  FROM so_oth_tax_charges
-  WHERE sotc_bu = 'TVSA'
-    AND sotc_ord_no ='${SONO}'</t>
-  </si>
-  <si>
-    <t>ItemShipSetQuery</t>
-  </si>
-  <si>
-    <t>SELECT PS_SS_PROD_ID, PS_SS_PROD_REV,
-       ( SELECT prod_desc11
-          FROM products
-         WHERE prod_bu  = ps_bu
-           AND prod_id  = PS_SS_PROD_ID
-           AND prod_rev = PS_SS_PROD_REV) PSI_SS_PROD_DESC,
-           PS_SS_QTY,
-           (SELECT PROD_UOM
-             FROM products
-            WHERE prod_bu  = ps_bu
-              AND prod_id  = PS_SS_PROD_ID
-              AND prod_rev = PS_SS_PROD_REV)UOM
-FROM PROD_SHIPSET
-  where   PS_BU =  'TVSA'
-    and   PS_FG_PROD_ID  = '${SONO}'</t>
-  </si>
-  <si>
-    <t>SODBincludeAdvFlagColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_REQ_FLAG</t>
-  </si>
-  <si>
-    <t>SODBAdvToBeReceivedColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_TO_RCVD</t>
-  </si>
-  <si>
-    <t>SODBAdvPercentageColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_PCT</t>
-  </si>
-  <si>
-    <t>SODBAdvanceReceivedColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_RCVD</t>
-  </si>
-  <si>
-    <t>SODBAdvTaxPercentageColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_TAX_PCT</t>
-  </si>
-  <si>
-    <t>SODBAdvReceiptInProgressColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_RCPT_INPRG</t>
-  </si>
-  <si>
-    <t>SODBAdvDocumentNumberColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_DOC_NO</t>
-  </si>
-  <si>
-    <t>SODBUnitAddessColumnName</t>
-  </si>
-  <si>
-    <t>Unit State</t>
-  </si>
-  <si>
-    <t>SODBCustomerAddessColumnName</t>
-  </si>
-  <si>
-    <t>Customer State</t>
-  </si>
-  <si>
-    <t>SODBCessAmtColumnName</t>
-  </si>
-  <si>
-    <t>SOQ_CESS_AMT</t>
-  </si>
-  <si>
-    <t>SODBPaymentTermMaterialPercentageColumnName</t>
-  </si>
-  <si>
-    <t>TRLN_MTRL_PCT</t>
-  </si>
-  <si>
-    <t>SODBPaymentTermTaxPercentageColumnName</t>
-  </si>
-  <si>
-    <t>TRLN_TAX_PCT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBDOCNumberColumnName</t>
-  </si>
-  <si>
-    <t>DOC_NO</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderUnitColumnName</t>
-  </si>
-  <si>
-    <t>UNIT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderOrderPrefixColumnName</t>
-  </si>
-  <si>
-    <t>ORD_PFX</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderOrderNumberColumnName</t>
-  </si>
-  <si>
-    <t>ORD_NO</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderPartyIDColumnName</t>
-  </si>
-  <si>
-    <t>PARTY_ID</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderPercentageColumnName</t>
-  </si>
-  <si>
-    <t>ADV_PERCENTAGE</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderAdvAmountColumnName</t>
-  </si>
-  <si>
-    <t>ADV_AMT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderCurrencyColumnName</t>
-  </si>
-  <si>
-    <t>CURCY</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderOrderAmountColumnName</t>
-  </si>
-  <si>
-    <t>ORD_AMT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderInProgressAmountColumnName</t>
-  </si>
-  <si>
-    <t>RCPT_INPROG_AMT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderReceivedAmountColumnName</t>
-  </si>
-  <si>
-    <t>RCPT_AMT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderClosedAmountColumnName</t>
-  </si>
-  <si>
-    <t>CLOSED_AMT</t>
-  </si>
-  <si>
-    <t>SODBHeaderDocumentStatusColumnName</t>
-  </si>
-  <si>
-    <t>SOH_STATUS</t>
-  </si>
-  <si>
-    <t>StockQtyDBColumnName</t>
-  </si>
-  <si>
-    <t>STOCK_QTY_HAND</t>
-  </si>
-  <si>
-    <t>WH</t>
-  </si>
-  <si>
-    <t>RM KD</t>
-  </si>
-  <si>
-    <t>StockCostDBColumnName</t>
-  </si>
-  <si>
-    <t>STCOST_COST</t>
-  </si>
-  <si>
-    <t>PRRequestedQtyDBColumnName</t>
-  </si>
-  <si>
-    <t>PRL_REQUESTED_QTY</t>
-  </si>
-  <si>
-    <t>PROrderedQtyDBColumnName</t>
-  </si>
-  <si>
-    <t>PRL_ORDERED_QTY</t>
-  </si>
-  <si>
-    <t>SODBCGSTColumnName</t>
-  </si>
-  <si>
-    <t>CGST Amt.</t>
-  </si>
-  <si>
-    <t>SODBSGSTColumnName</t>
-  </si>
-  <si>
-    <t>SGST Amt.</t>
-  </si>
-  <si>
-    <t>SODBIGSTColumnName</t>
-  </si>
-  <si>
-    <t>IGST Amt.</t>
-  </si>
-  <si>
-    <t>PONO</t>
-  </si>
-  <si>
-    <t>${PONO}</t>
-  </si>
-  <si>
-    <t>SO_FREE_SAMPLE</t>
-  </si>
-  <si>
-    <t>SO - FREE SAMPLE</t>
-  </si>
-  <si>
-    <t>SO_FREE_REPLACEMENT</t>
-  </si>
-  <si>
-    <t>SO - FREE REPLACEMENT</t>
-  </si>
-  <si>
-    <t>SO_SCRAP</t>
-  </si>
-  <si>
-    <t>SO - SCRAP</t>
-  </si>
-  <si>
-    <t>SO_SERVICE</t>
-  </si>
-  <si>
-    <t>SO - SERVICE</t>
-  </si>
-  <si>
-    <t>SO_Local_Customer</t>
-  </si>
-  <si>
-    <t>CUS10002</t>
-  </si>
-  <si>
-    <t>SO_Local_Customer_Desc</t>
-  </si>
-  <si>
-    <t>SO_SEZ_CUSTOMER</t>
-  </si>
-  <si>
-    <t>CUS10005</t>
-  </si>
-  <si>
-    <t>SO_SEZ_CUSTOMER_DESC</t>
-  </si>
-  <si>
-    <t>SO_Demo_Exhibition</t>
-  </si>
-  <si>
-    <t>SO - DEMO / EXHN.</t>
-  </si>
-  <si>
-    <t>SODBCESSPercentageColumnName</t>
-  </si>
-  <si>
-    <t>SOQ_CESS_PCT</t>
-  </si>
-  <si>
-    <t>SODBCESSAmountColumnName</t>
-  </si>
-  <si>
-    <t>CESS_HSN_CODE</t>
-  </si>
-  <si>
-    <t>0074</t>
-  </si>
-  <si>
-    <t>SODBChargeAmountColumnName</t>
-  </si>
-  <si>
-    <t>SOTC_CHRG_AMT</t>
-  </si>
-  <si>
-    <t>SODBChargeIGSTColumnName</t>
-  </si>
-  <si>
-    <t>SOTC_IGST_AMT</t>
-  </si>
-  <si>
-    <t>SODBChargeCGSTColumnName</t>
-  </si>
-  <si>
-    <t>SOTC_CGST_AMT</t>
-  </si>
-  <si>
-    <t>SODBChargeSGSTColumnName</t>
-  </si>
-  <si>
-    <t>SOTC_SGST_AMT</t>
-  </si>
-  <si>
-    <t>EntryCompletedStatus</t>
-  </si>
-  <si>
-    <t>%</t>
   </si>
 </sst>
 </file>
@@ -6866,7 +6867,7 @@
         <v>611</v>
       </c>
       <c r="B358" s="27" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -8095,319 +8096,319 @@
     </row>
     <row r="512" spans="1:2">
       <c r="A512" s="26" t="s">
+        <v>894</v>
+      </c>
+      <c r="B512" s="8" t="s">
         <v>895</v>
-      </c>
-      <c r="B512" s="8" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" s="26" t="s">
+        <v>896</v>
+      </c>
+      <c r="B513" s="8" t="s">
         <v>897</v>
-      </c>
-      <c r="B513" s="8" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" s="26" t="s">
+        <v>898</v>
+      </c>
+      <c r="B514" s="8" t="s">
         <v>899</v>
-      </c>
-      <c r="B514" s="8" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" s="26" t="s">
+        <v>900</v>
+      </c>
+      <c r="B515" s="8" t="s">
         <v>901</v>
-      </c>
-      <c r="B515" s="8" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" s="26" t="s">
+        <v>902</v>
+      </c>
+      <c r="B516" s="8" t="s">
         <v>903</v>
-      </c>
-      <c r="B516" s="8" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" s="26" t="s">
+        <v>904</v>
+      </c>
+      <c r="B517" s="8" t="s">
         <v>905</v>
-      </c>
-      <c r="B517" s="8" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" s="26" t="s">
+        <v>906</v>
+      </c>
+      <c r="B518" s="8" t="s">
         <v>907</v>
-      </c>
-      <c r="B518" s="8" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" s="26" t="s">
+        <v>908</v>
+      </c>
+      <c r="B519" s="8" t="s">
         <v>909</v>
-      </c>
-      <c r="B519" s="8" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" s="26" t="s">
+        <v>910</v>
+      </c>
+      <c r="B520" s="8" t="s">
         <v>911</v>
-      </c>
-      <c r="B520" s="8" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="521" spans="1:2">
       <c r="A521" s="26" t="s">
+        <v>912</v>
+      </c>
+      <c r="B521" s="8" t="s">
         <v>913</v>
-      </c>
-      <c r="B521" s="8" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" s="26" t="s">
+        <v>914</v>
+      </c>
+      <c r="B522" s="8" t="s">
         <v>915</v>
-      </c>
-      <c r="B522" s="8" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" s="26" t="s">
+        <v>916</v>
+      </c>
+      <c r="B523" s="8" t="s">
         <v>917</v>
-      </c>
-      <c r="B523" s="8" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" s="26" t="s">
+        <v>918</v>
+      </c>
+      <c r="B524" s="8" t="s">
         <v>919</v>
-      </c>
-      <c r="B524" s="8" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" s="26" t="s">
+        <v>920</v>
+      </c>
+      <c r="B525" s="8" t="s">
         <v>921</v>
-      </c>
-      <c r="B525" s="8" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" s="26" t="s">
+        <v>922</v>
+      </c>
+      <c r="B526" s="8" t="s">
         <v>923</v>
-      </c>
-      <c r="B526" s="8" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="A527" s="26" t="s">
+        <v>924</v>
+      </c>
+      <c r="B527" s="8" t="s">
         <v>925</v>
-      </c>
-      <c r="B527" s="8" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" s="26" t="s">
+        <v>926</v>
+      </c>
+      <c r="B528" s="8" t="s">
         <v>927</v>
-      </c>
-      <c r="B528" s="8" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="B529" s="8" t="s">
         <v>929</v>
-      </c>
-      <c r="B529" s="8" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" s="26" t="s">
+        <v>930</v>
+      </c>
+      <c r="B530" s="8" t="s">
         <v>931</v>
-      </c>
-      <c r="B530" s="8" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" s="26" t="s">
+        <v>932</v>
+      </c>
+      <c r="B531" s="8" t="s">
         <v>933</v>
-      </c>
-      <c r="B531" s="8" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" s="26" t="s">
+        <v>934</v>
+      </c>
+      <c r="B532" s="8" t="s">
         <v>935</v>
-      </c>
-      <c r="B532" s="8" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" s="26" t="s">
+        <v>936</v>
+      </c>
+      <c r="B533" s="8" t="s">
         <v>937</v>
-      </c>
-      <c r="B533" s="8" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" s="26" t="s">
+        <v>938</v>
+      </c>
+      <c r="B534" s="8" t="s">
         <v>939</v>
-      </c>
-      <c r="B534" s="8" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" s="26" t="s">
+        <v>940</v>
+      </c>
+      <c r="B535" s="8" t="s">
         <v>941</v>
-      </c>
-      <c r="B535" s="8" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" s="26" t="s">
+        <v>942</v>
+      </c>
+      <c r="B536" s="8" t="s">
         <v>943</v>
-      </c>
-      <c r="B536" s="8" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" s="26" t="s">
+        <v>944</v>
+      </c>
+      <c r="B537" s="8" t="s">
         <v>945</v>
-      </c>
-      <c r="B537" s="8" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" s="26" t="s">
+        <v>946</v>
+      </c>
+      <c r="B538" s="8" t="s">
         <v>947</v>
-      </c>
-      <c r="B538" s="8" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" s="26" t="s">
+        <v>948</v>
+      </c>
+      <c r="B539" s="8" t="s">
         <v>949</v>
-      </c>
-      <c r="B539" s="8" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" s="26" t="s">
+        <v>950</v>
+      </c>
+      <c r="B540" s="8" t="s">
         <v>951</v>
-      </c>
-      <c r="B540" s="8" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" s="26" t="s">
+        <v>952</v>
+      </c>
+      <c r="B541" s="8" t="s">
         <v>953</v>
-      </c>
-      <c r="B541" s="8" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" s="26" t="s">
+        <v>954</v>
+      </c>
+      <c r="B542" s="8" t="s">
         <v>955</v>
-      </c>
-      <c r="B542" s="8" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" s="26" t="s">
+        <v>956</v>
+      </c>
+      <c r="B543" s="8" t="s">
         <v>957</v>
-      </c>
-      <c r="B543" s="8" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
+        <v>958</v>
+      </c>
+      <c r="B544" s="8" t="s">
         <v>959</v>
-      </c>
-      <c r="B544" s="8" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" s="26" t="s">
+        <v>960</v>
+      </c>
+      <c r="B545" s="8" t="s">
         <v>961</v>
-      </c>
-      <c r="B545" s="8" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" s="58" t="s">
+        <v>962</v>
+      </c>
+      <c r="B546" s="8" t="s">
         <v>963</v>
-      </c>
-      <c r="B546" s="8" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" s="58" t="s">
+        <v>964</v>
+      </c>
+      <c r="B547" s="8" t="s">
         <v>965</v>
-      </c>
-      <c r="B547" s="8" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" s="58" t="s">
+        <v>966</v>
+      </c>
+      <c r="B548" s="8" t="s">
         <v>967</v>
-      </c>
-      <c r="B548" s="8" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" s="59" t="s">
+        <v>968</v>
+      </c>
+      <c r="B549" s="8" t="s">
         <v>969</v>
-      </c>
-      <c r="B549" s="8" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" s="59" t="s">
+        <v>970</v>
+      </c>
+      <c r="B550" s="8" t="s">
         <v>971</v>
-      </c>
-      <c r="B550" s="8" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" s="58" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B551" s="60" t="s">
         <v>454</v>
@@ -8415,15 +8416,15 @@
     </row>
     <row r="552" spans="1:2">
       <c r="A552" s="59" t="s">
+        <v>973</v>
+      </c>
+      <c r="B552" s="8" t="s">
         <v>974</v>
-      </c>
-      <c r="B552" s="8" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" s="59" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B553" s="8" t="s">
         <v>460</v>
@@ -8431,71 +8432,71 @@
     </row>
     <row r="554" spans="1:2">
       <c r="A554" s="58" t="s">
+        <v>976</v>
+      </c>
+      <c r="B554" s="8" t="s">
         <v>977</v>
-      </c>
-      <c r="B554" s="8" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" s="26" t="s">
+        <v>978</v>
+      </c>
+      <c r="B555" s="8" t="s">
         <v>979</v>
-      </c>
-      <c r="B555" s="8" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" s="26" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B556" s="8" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" s="59" t="s">
+        <v>981</v>
+      </c>
+      <c r="B557" s="8" t="s">
         <v>982</v>
-      </c>
-      <c r="B557" s="8" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" s="26" t="s">
+        <v>983</v>
+      </c>
+      <c r="B558" s="8" t="s">
         <v>984</v>
-      </c>
-      <c r="B558" s="8" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" s="26" t="s">
+        <v>985</v>
+      </c>
+      <c r="B559" s="8" t="s">
         <v>986</v>
-      </c>
-      <c r="B559" s="8" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" s="26" t="s">
+        <v>987</v>
+      </c>
+      <c r="B560" s="8" t="s">
         <v>988</v>
-      </c>
-      <c r="B560" s="8" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" s="26" t="s">
+        <v>989</v>
+      </c>
+      <c r="B561" s="8" t="s">
         <v>990</v>
-      </c>
-      <c r="B561" s="8" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" s="26" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B562" s="8" t="s">
         <v>551</v>
@@ -8543,104 +8544,104 @@
       <c r="A4" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>870</v>
+      <c r="B4" s="4" t="s">
+        <v>993</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="69.75" customHeight="1">
       <c r="A5" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>871</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="51.75" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>887</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1">
       <c r="A7" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>873</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>875</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="39" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>877</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="22.5" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>879</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="18" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>881</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="26.25" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>883</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="28.5" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>885</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="24" customHeight="1">
       <c r="A14" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>889</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="36" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>891</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>893</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="5130" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
     <sheet name="DBData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="1003">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -1866,6 +1866,9 @@
     <t>ChargesBasis</t>
   </si>
   <si>
+    <t>%</t>
+  </si>
+  <si>
     <t>ChargeItem</t>
   </si>
   <si>
@@ -2623,6 +2626,327 @@
   </si>
   <si>
     <t>109</t>
+  </si>
+  <si>
+    <t>SODBincludeAdvFlagColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_REQ_FLAG</t>
+  </si>
+  <si>
+    <t>SODBAdvToBeReceivedColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_TO_RCVD</t>
+  </si>
+  <si>
+    <t>SODBAdvPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_PCT</t>
+  </si>
+  <si>
+    <t>SODBAdvanceReceivedColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_RCVD</t>
+  </si>
+  <si>
+    <t>SODBAdvTaxPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_TAX_PCT</t>
+  </si>
+  <si>
+    <t>SODBAdvReceiptInProgressColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_RCPT_INPRG</t>
+  </si>
+  <si>
+    <t>SODBAdvDocumentNumberColumnName</t>
+  </si>
+  <si>
+    <t>SOH_ADV_DOC_NO</t>
+  </si>
+  <si>
+    <t>SODBUnitAddessColumnName</t>
+  </si>
+  <si>
+    <t>Unit State</t>
+  </si>
+  <si>
+    <t>SODBCustomerAddessColumnName</t>
+  </si>
+  <si>
+    <t>Customer State</t>
+  </si>
+  <si>
+    <t>SODBCessAmtColumnName</t>
+  </si>
+  <si>
+    <t>SOQ_CESS_AMT</t>
+  </si>
+  <si>
+    <t>SODBPaymentTermMaterialPercentageColumnName</t>
+  </si>
+  <si>
+    <t>TRLN_MTRL_PCT</t>
+  </si>
+  <si>
+    <t>SODBPaymentTermTaxPercentageColumnName</t>
+  </si>
+  <si>
+    <t>TRLN_TAX_PCT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBDOCNumberColumnName</t>
+  </si>
+  <si>
+    <t>DOC_NO</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderUnitColumnName</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderPrefixColumnName</t>
+  </si>
+  <si>
+    <t>ORD_PFX</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderNumberColumnName</t>
+  </si>
+  <si>
+    <t>ORD_NO</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderPartyIDColumnName</t>
+  </si>
+  <si>
+    <t>PARTY_ID</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderPercentageColumnName</t>
+  </si>
+  <si>
+    <t>ADV_PERCENTAGE</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderAdvAmountColumnName</t>
+  </si>
+  <si>
+    <t>ADV_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderCurrencyColumnName</t>
+  </si>
+  <si>
+    <t>CURCY</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderOrderAmountColumnName</t>
+  </si>
+  <si>
+    <t>ORD_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderInProgressAmountColumnName</t>
+  </si>
+  <si>
+    <t>RCPT_INPROG_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderReceivedAmountColumnName</t>
+  </si>
+  <si>
+    <t>RCPT_AMT</t>
+  </si>
+  <si>
+    <t>AdvReceiptDBHeaderClosedAmountColumnName</t>
+  </si>
+  <si>
+    <t>CLOSED_AMT</t>
+  </si>
+  <si>
+    <t>SODBHeaderDocumentStatusColumnName</t>
+  </si>
+  <si>
+    <t>SOH_STATUS</t>
+  </si>
+  <si>
+    <t>StockQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>STOCK_QTY_HAND</t>
+  </si>
+  <si>
+    <t>WH</t>
+  </si>
+  <si>
+    <t>RM KD</t>
+  </si>
+  <si>
+    <t>StockCostDBColumnName</t>
+  </si>
+  <si>
+    <t>STCOST_COST</t>
+  </si>
+  <si>
+    <t>PRRequestedQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>PRL_REQUESTED_QTY</t>
+  </si>
+  <si>
+    <t>PROrderedQtyDBColumnName</t>
+  </si>
+  <si>
+    <t>PRL_ORDERED_QTY</t>
+  </si>
+  <si>
+    <t>SODBCGSTColumnName</t>
+  </si>
+  <si>
+    <t>CGST Amt.</t>
+  </si>
+  <si>
+    <t>SODBSGSTColumnName</t>
+  </si>
+  <si>
+    <t>SGST Amt.</t>
+  </si>
+  <si>
+    <t>SODBIGSTColumnName</t>
+  </si>
+  <si>
+    <t>IGST Amt.</t>
+  </si>
+  <si>
+    <t>PONO</t>
+  </si>
+  <si>
+    <t>${PONO}</t>
+  </si>
+  <si>
+    <t>SO_FREE_SAMPLE</t>
+  </si>
+  <si>
+    <t>SO - FREE SAMPLE</t>
+  </si>
+  <si>
+    <t>SO_FREE_REPLACEMENT</t>
+  </si>
+  <si>
+    <t>SO - FREE REPLACEMENT</t>
+  </si>
+  <si>
+    <t>SO_SCRAP</t>
+  </si>
+  <si>
+    <t>SO - SCRAP</t>
+  </si>
+  <si>
+    <t>SO_SERVICE</t>
+  </si>
+  <si>
+    <t>SO - SERVICE</t>
+  </si>
+  <si>
+    <t>SO_Local_Customer</t>
+  </si>
+  <si>
+    <t>CUS10002</t>
+  </si>
+  <si>
+    <t>SO_Local_Customer_Desc</t>
+  </si>
+  <si>
+    <t>SO_SEZ_CUSTOMER</t>
+  </si>
+  <si>
+    <t>CUS10005</t>
+  </si>
+  <si>
+    <t>SO_SEZ_CUSTOMER_DESC</t>
+  </si>
+  <si>
+    <t>SO_Demo_Exhibition</t>
+  </si>
+  <si>
+    <t>SO - DEMO / EXHN.</t>
+  </si>
+  <si>
+    <t>SODBCESSPercentageColumnName</t>
+  </si>
+  <si>
+    <t>SOQ_CESS_PCT</t>
+  </si>
+  <si>
+    <t>SODBCESSAmountColumnName</t>
+  </si>
+  <si>
+    <t>CESS_HSN_CODE</t>
+  </si>
+  <si>
+    <t>0074</t>
+  </si>
+  <si>
+    <t>SODBChargeAmountColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_CHRG_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeIGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_IGST_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeCGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_CGST_AMT</t>
+  </si>
+  <si>
+    <t>SODBChargeSGSTColumnName</t>
+  </si>
+  <si>
+    <t>SOTC_SGST_AMT</t>
+  </si>
+  <si>
+    <t>EntryCompletedStatus</t>
+  </si>
+  <si>
+    <t>GwlDissimilarItem</t>
+  </si>
+  <si>
+    <t>GWL_Item_Dissimilar_02</t>
+  </si>
+  <si>
+    <t>POPrefix</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>GWL_Item_similar_03</t>
+  </si>
+  <si>
+    <t>SixValue</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>POAServiceSheet</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -2776,598 +3100,6 @@
     <t>SOHeaderQuery</t>
   </si>
   <si>
-    <t>SOLineQuery</t>
-  </si>
-  <si>
-    <t>SELECT soq_prod_id "Item ID",soq_prod_rev "Item Rev",
-       soq_prod_desc1 "Item Desc",
-       soq_uom "Sale UOM",
-       soq_hsn_code "HSN Code",
-       soq_tax_pct "Tax Percentage",
-       soq_price_basis "Price Basis Type",
-       DECODE (soq_price_basis,
-               'C', 'Open Order',
-               'L', 'Catalog Price',
-               'P', 'Price List',
-               'S', 'Standard Price',
-               'U', 'User Defined')
-          "Price Basis Desc",
-       soq_cont_cat_no "Contract Number",
-       soq_catalog_no "Catalog / Price List Number",
-       soq_prod_uom "Stock UOM",
-       soq_conv_factor "Conversion Factor",
-       soq_tolr_type "Tolerance Type",
-       soq_cust_prod_id "Customer Item ID",
-       soq_cust_prod_desc "Customer Item Desc",
-       (SELECT store_desc1
-          FROM stores
-         WHERE store_bu = soq_bu AND store_id = soq_store_id
-        UNION ALL
-        SELECT dept_name1
-          FROM departments
-         WHERE dept_bu = soq_bu AND dept_id = soq_store_id)
-          "Warehouse Description",
-       soq_prod_subcls_desc "SubClass Desc",
-       soq_prod_cls_desc "Class Desc",
-       (SELECT spc_class_desc
-          FROM sales_price_classes
-         WHERE spc_bu = soq_bu AND spc_class_id = soq_sales_price_class)
-          "Price Class",
-       soq_promotion_flag "Promotional",
-       soq_trd_assbl_val "Trade Ass. Val.",
-       soq_disc_pct "Trade Disc. %",
-       soq_disc_amt "Trade Disc. Amt.",
-       soq_spl_assbl_val "Spl. Ass. Val.",
-       soq_spl_disc_pct "Spl. Disc. %",
-       soq_spl_disc_amt "Spl. Disc. Amt.",
-       soq_cash_assbl_val "Cash Ass. Val.",
-       soq_cash_disc_pct "Cash Disc. %",
-       soq_cash_disc_amt "Cash Disc. Amt.",
-       soq_gross_amt "Gross Amt.",
-       soq_disc_amt_per_qty "Disc. Amt. / Qty.",
-       soq_tax_amt "Tax Amt.",
-       soq_net_amt "Net Amt.",
-       soq_gross_amt "Gross Amt.",
-       soq_disc_amt_per_qty "Disc. Amt. / Qty.",
-       soq_tax_amt "Tax Amt.",
-       soq_net_amt "Net Amt.",
-       soq_qty_ordered "Ord. Qty.",
-       soq_price "Unit Price",
-       soq_tot_disc_amt "Disc. Amt.",
-       soq_igst_amt "IGST Amt.",
-       soq_sgst_amt "SGST Amt.",
-       soq_cgst_amt "CGST Amt."
-  FROM sales_order_hd, sales_order_qtys
- WHERE     soh_bu = soq_bu
-       AND soh_order_no = soq_order_no
-       AND soh_bu = 'TVSA'
-       AND soh_order_no = '${SONO}'</t>
-  </si>
-  <si>
-    <t>OsoaQuery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT srcahd_plnt_loc_id "loc id",
-       srcahd_plnt "unit",
-       srcahd_doc_no "Doc. No.",
-       srcahd_amd_no "Amd. No.",
-       srcahd_cust_id "customer id",
-       (SELECT suplr_name1
-          FROM suppliers
-         WHERE suplr_bu = srcahd_bu AND suplr_suplr_id = srcahd_cust_id)
-          "customer name",
-       srcaln_prod_id "item id",
-       srcaln_prod_rev "item rev",
-       (SELECT prod_desc11
-          FROM products
-         WHERE     prod_bu = srcaln_bu
-               AND prod_id = srcaln_prod_id
-               AND prod_rev = srcaln_prod_rev)
-          "item descripition",
-       srcaln_uom "uom",
-       srcaln_disc_pct "disc_pct",
-       srcaln_old_price "Existing Price",
-       srcaln_new_price "new_price",
-       srcaln_mrp_price "MRP Price",
-       srcaln_hsn_code "HSN code",
-       srcaln_tax_pct "Tax Percent",
-       srcaln_cgst_amt "CGST",
-       srcaln_sgst_amt "SGST",
-       srcaln_igst_amt "IGST",
-       srcaln_utgst_amt "UTGST"
-  FROM sales_rate_contr_ament_hd, sales_rate_contr_ament_ln
- WHERE     srcahd_bu = srcaln_bu
-       AND srcahd_plnt = srcaln_plnt
-       AND srcahd_doc_no = '${OSOANO}'
-    AND srcahd_doc_no = srcaln_doc_no
-       AND srcahd_bu =  'TVSA' </t>
-  </si>
-  <si>
-    <t>SOAdvanceQuery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   SELECT soh_adv_pct,
-       soh_adv_rcvd,
-       soh_adv_tax_pct,
-       soh_adv_req_flag,
-       soh_adv_to_rcvd,
-       soh_adv_rcpt_inprg,
-SOH_ADV_DOC_NO
-  FROM sales_order_hd
-  WHERE soh_bu = 'TVSA'
-  and soh_order_no = '${SONO}'</t>
-  </si>
-  <si>
-    <t>SOCustomerDetailsQuery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SELECT (SELECT NVL(state_name1,state_name2) FROM states WHERE state_bu = suplr_bu AND state_id = suplr_state)"Customer State"
-       FROM suppliers
-       WHERE suplr_bu = 'TVSA'
-       AND suplr_suplr_id = '${SONO}'</t>
-  </si>
-  <si>
-    <t>SOUnitDetailsQuery</t>
-  </si>
-  <si>
-    <t>SELECT  (SELECT NVL(state_name1,state_name2) FROM states WHERE state_bu = bup_bu AND state_id = BUP_STATE)"Unit State"
-      FROM bus_unit_plants
-     WHERE bup_bu ='TVSA'
-       AND bup_plant_id ='${SONO}'</t>
-  </si>
-  <si>
-    <t>SOLineDetails1&amp;2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  select soq_cess_pct,soq_cess_amt,SOQ_GST_EXEMPT_FLAG,SOQ_GST_INPUT_TYPE,SOQ_SAL_ACCT_ID,SOQ_SAL_CC_ID,SOQ_DISC_ACCT_ID,SOQ_DISC_CC_ID,SOQ_CUST_PO_NO,SOQ_CUST_PO_REV,SOQ_CUST_PO_DATE,
-  SOQ_PO_SL_SEQ_NO,SOQ_SQ_PFX,SOQ_SQ_NO,SOQ_SQ_SEQ_NO,SOQ_SQ_REV,SOQ_OPO_PO_NO,SOQ_OPO_PO_DATE,SOQ_PO_SEQ_NO,SOQ_CONT_CAT_NO,SOQ_PO_REF,SOQ_CATALOG_NO,
-  SOQ_CUST_PROD_ID,SOQ_CUST_PROD_DESC,SOQ_STORE_NAME,SOQ_PROD_EXT_DESC,SOQ_DESP_DATE,SOQ_RQRD_DATE,SOQ_PROMOTION_FLAG,SOQ_SALES_PRICE_CLASS,SOQ_SCHLD_DESC,SOQ_TOLERANCE_PCT,
-  SOQ_PROD_UOM,SOQ_CONV_FACTOR,SOQ_TOLR_QTY,SOQ_TOLR_TYPE,SOQ_BOM_NO,SOQ_BOM_NAME,SOQ_BOM_REVISION_NUM,SOQ_MARGIN_PCT,SOQ_LIST_PRICE,SOQ_MRP_PRICE,SOQ_SQ_PRICE,SOQ_INSTL_RQRD_FLAG
-         from sales_order_qtys
-         where soq_bu ='TVSA'
-           and soq_order_no ='${SONO}'</t>
-  </si>
-  <si>
-    <t>PaymentTermQuery</t>
-  </si>
-  <si>
-    <t>SELECT term_desc1,
-       trln_mtrl_pct,
-       trln_tax_pct,
-       TRLN_CLAIM_TYPE
-  FROM terms_ln,
-       terms_hd
- WHERE  term_bu = trln_bu
-   AND term_bu = 'TVSA'
-   AND  TRLN_CLAIM_TYPE ='A'
-  AND term_term_id = trln_term_id
-  AND  term_desc1 = '${SONO}'</t>
-  </si>
-  <si>
-    <t>AdvanceReceiptQuery</t>
-  </si>
-  <si>
-    <t>SELECT
-        pard_doc_no Doc_no,
-        pard_plnt Unit,
-        pard_ord_pfx ord_pfx,
-        pard_ord_no ord_no,
-        pard_party_id Party_id,
-        pard_prop_adv_pct Adv_Percentage,
-        pard_prop_adv_amt Adv_Amt,
-        pard_curcy_id Curcy,
-        pard_ord_amt Ord_amt,
-        pard_rct_inprog_amt Rcpt_inprog_amt,
-        pard_rct_amt Rcpt_Amt,
-        pard_close_amt Closed_amt
-   FROM prop_adv_rct_doc
-  WHERE pard_bu = 'TVSA'
-    AND pard_doc_no ='${SONO}'</t>
-  </si>
-  <si>
-    <t>Stock Query</t>
-  </si>
-  <si>
-    <t>SELECT stock_qty_hand,
-      (SELECT stcost_cost
-  FROM stock_costs
- WHERE stcost_bu = 'TVSA'
-   AND stcost_store_id = stock_store_id
-   AND stcost_prod_id = stock_prod_id
-   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
-  FROM stocks
- WHERE stock_bu = 'TVSA'
-   AND stock_store_id = '${SONO}'
-   AND stock_prod_id = 'TVS-RM-KDK-10'
-   AND stock_prod_rev = '0'</t>
-  </si>
-  <si>
-    <t>Stock Query1</t>
-  </si>
-  <si>
-    <t>SELECT stock_qty_hand,
-      (SELECT stcost_cost
-  FROM stock_costs
- WHERE stcost_bu = 'TVSA'
-   AND stcost_store_id = stock_store_id
-   AND stcost_prod_id = stock_prod_id
-   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
-  FROM stocks
- WHERE stock_bu = 'TVSA'
-   AND stock_store_id = '${SONO}'
-   AND stock_prod_id ='${PONO}'
-   AND stock_prod_rev = '0'</t>
-  </si>
-  <si>
-    <t>SalesOrderChargesQuery</t>
-  </si>
-  <si>
-    <t>SELECT
-       sotc_bu,
-       sotc_ord_no,
-       sotc_seq_no,
-       sotc_prod_id,
-       (SELECT prod_desc11
-          FROM products
-         WHERE prod_bu ='TVSA'
-           AND prod_id = sotc_prod_id
-           AND prod_rev = sotc_prod_rev)ITEM_DESC,
-       sotc_prod_rev,
-       sotc_hsn_code,
-       sotc_qty,
-       sotc_chrg_basis,
-       sotc_chrg_pct,
-       sotc_chrg_pct sotc_chrg_pct1,
-       sotc_chrg_amt,
-       sotc_chrg_amt sotc_chrg_amt1,
-       sotc_gst_exempt_flag,
-       sotc_gst_input_type,
-       sotc_cre_by,
-       sotc_cre_ip_addr,
-       sotc_cre_os_user,
-       sotc_cre_date,
-       sotc_upd_by,
-       sotc_upd_ip_addr,
-       sotc_upd_os_user,
-       sotc_upd_date,
-       sotc_cre_emp_id,
-       sotc_upd_emp_id,
-       sotc_tcs_avail_flag,
-       sotc_sal_acct_id,
-       sotc_sal_cc_id,
-       sotc_tariff_code,
-       sotc_cgst_pct,
-       sotc_sgst_pct,
-       sotc_utgst_pct,
-       sotc_cess_pct,
-       sotc_igst_amt,
-       sotc_cgst_amt,
-       sotc_sgst_amt,
-       sotc_utgst_amt,
-       sotc_cess_amt,
-       sotc_tax_pct
-  FROM so_oth_tax_charges
-  WHERE sotc_bu = 'TVSA'
-    AND sotc_ord_no ='${SONO}'</t>
-  </si>
-  <si>
-    <t>ItemShipSetQuery</t>
-  </si>
-  <si>
-    <t>SELECT PS_SS_PROD_ID, PS_SS_PROD_REV,
-       ( SELECT prod_desc11
-          FROM products
-         WHERE prod_bu  = ps_bu
-           AND prod_id  = PS_SS_PROD_ID
-           AND prod_rev = PS_SS_PROD_REV) PSI_SS_PROD_DESC,
-           PS_SS_QTY,
-           (SELECT PROD_UOM
-             FROM products
-            WHERE prod_bu  = ps_bu
-              AND prod_id  = PS_SS_PROD_ID
-              AND prod_rev = PS_SS_PROD_REV)UOM
-FROM PROD_SHIPSET
-  where   PS_BU =  'TVSA'
-    and   PS_FG_PROD_ID  = '${SONO}'</t>
-  </si>
-  <si>
-    <t>SODBincludeAdvFlagColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_REQ_FLAG</t>
-  </si>
-  <si>
-    <t>SODBAdvToBeReceivedColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_TO_RCVD</t>
-  </si>
-  <si>
-    <t>SODBAdvPercentageColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_PCT</t>
-  </si>
-  <si>
-    <t>SODBAdvanceReceivedColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_RCVD</t>
-  </si>
-  <si>
-    <t>SODBAdvTaxPercentageColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_TAX_PCT</t>
-  </si>
-  <si>
-    <t>SODBAdvReceiptInProgressColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_RCPT_INPRG</t>
-  </si>
-  <si>
-    <t>SODBAdvDocumentNumberColumnName</t>
-  </si>
-  <si>
-    <t>SOH_ADV_DOC_NO</t>
-  </si>
-  <si>
-    <t>SODBUnitAddessColumnName</t>
-  </si>
-  <si>
-    <t>Unit State</t>
-  </si>
-  <si>
-    <t>SODBCustomerAddessColumnName</t>
-  </si>
-  <si>
-    <t>Customer State</t>
-  </si>
-  <si>
-    <t>SODBCessAmtColumnName</t>
-  </si>
-  <si>
-    <t>SOQ_CESS_AMT</t>
-  </si>
-  <si>
-    <t>SODBPaymentTermMaterialPercentageColumnName</t>
-  </si>
-  <si>
-    <t>TRLN_MTRL_PCT</t>
-  </si>
-  <si>
-    <t>SODBPaymentTermTaxPercentageColumnName</t>
-  </si>
-  <si>
-    <t>TRLN_TAX_PCT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBDOCNumberColumnName</t>
-  </si>
-  <si>
-    <t>DOC_NO</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderUnitColumnName</t>
-  </si>
-  <si>
-    <t>UNIT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderOrderPrefixColumnName</t>
-  </si>
-  <si>
-    <t>ORD_PFX</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderOrderNumberColumnName</t>
-  </si>
-  <si>
-    <t>ORD_NO</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderPartyIDColumnName</t>
-  </si>
-  <si>
-    <t>PARTY_ID</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderPercentageColumnName</t>
-  </si>
-  <si>
-    <t>ADV_PERCENTAGE</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderAdvAmountColumnName</t>
-  </si>
-  <si>
-    <t>ADV_AMT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderCurrencyColumnName</t>
-  </si>
-  <si>
-    <t>CURCY</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderOrderAmountColumnName</t>
-  </si>
-  <si>
-    <t>ORD_AMT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderInProgressAmountColumnName</t>
-  </si>
-  <si>
-    <t>RCPT_INPROG_AMT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderReceivedAmountColumnName</t>
-  </si>
-  <si>
-    <t>RCPT_AMT</t>
-  </si>
-  <si>
-    <t>AdvReceiptDBHeaderClosedAmountColumnName</t>
-  </si>
-  <si>
-    <t>CLOSED_AMT</t>
-  </si>
-  <si>
-    <t>SODBHeaderDocumentStatusColumnName</t>
-  </si>
-  <si>
-    <t>SOH_STATUS</t>
-  </si>
-  <si>
-    <t>StockQtyDBColumnName</t>
-  </si>
-  <si>
-    <t>STOCK_QTY_HAND</t>
-  </si>
-  <si>
-    <t>WH</t>
-  </si>
-  <si>
-    <t>RM KD</t>
-  </si>
-  <si>
-    <t>StockCostDBColumnName</t>
-  </si>
-  <si>
-    <t>STCOST_COST</t>
-  </si>
-  <si>
-    <t>PRRequestedQtyDBColumnName</t>
-  </si>
-  <si>
-    <t>PRL_REQUESTED_QTY</t>
-  </si>
-  <si>
-    <t>PROrderedQtyDBColumnName</t>
-  </si>
-  <si>
-    <t>PRL_ORDERED_QTY</t>
-  </si>
-  <si>
-    <t>SODBCGSTColumnName</t>
-  </si>
-  <si>
-    <t>CGST Amt.</t>
-  </si>
-  <si>
-    <t>SODBSGSTColumnName</t>
-  </si>
-  <si>
-    <t>SGST Amt.</t>
-  </si>
-  <si>
-    <t>SODBIGSTColumnName</t>
-  </si>
-  <si>
-    <t>IGST Amt.</t>
-  </si>
-  <si>
-    <t>PONO</t>
-  </si>
-  <si>
-    <t>${PONO}</t>
-  </si>
-  <si>
-    <t>SO_FREE_SAMPLE</t>
-  </si>
-  <si>
-    <t>SO - FREE SAMPLE</t>
-  </si>
-  <si>
-    <t>SO_FREE_REPLACEMENT</t>
-  </si>
-  <si>
-    <t>SO - FREE REPLACEMENT</t>
-  </si>
-  <si>
-    <t>SO_SCRAP</t>
-  </si>
-  <si>
-    <t>SO - SCRAP</t>
-  </si>
-  <si>
-    <t>SO_SERVICE</t>
-  </si>
-  <si>
-    <t>SO - SERVICE</t>
-  </si>
-  <si>
-    <t>SO_Local_Customer</t>
-  </si>
-  <si>
-    <t>CUS10002</t>
-  </si>
-  <si>
-    <t>SO_Local_Customer_Desc</t>
-  </si>
-  <si>
-    <t>SO_SEZ_CUSTOMER</t>
-  </si>
-  <si>
-    <t>CUS10005</t>
-  </si>
-  <si>
-    <t>SO_SEZ_CUSTOMER_DESC</t>
-  </si>
-  <si>
-    <t>SO_Demo_Exhibition</t>
-  </si>
-  <si>
-    <t>SO - DEMO / EXHN.</t>
-  </si>
-  <si>
-    <t>SODBCESSPercentageColumnName</t>
-  </si>
-  <si>
-    <t>SOQ_CESS_PCT</t>
-  </si>
-  <si>
-    <t>SODBCESSAmountColumnName</t>
-  </si>
-  <si>
-    <t>CESS_HSN_CODE</t>
-  </si>
-  <si>
-    <t>0074</t>
-  </si>
-  <si>
-    <t>SODBChargeAmountColumnName</t>
-  </si>
-  <si>
-    <t>SOTC_CHRG_AMT</t>
-  </si>
-  <si>
-    <t>SODBChargeIGSTColumnName</t>
-  </si>
-  <si>
-    <t>SOTC_IGST_AMT</t>
-  </si>
-  <si>
-    <t>SODBChargeCGSTColumnName</t>
-  </si>
-  <si>
-    <t>SOTC_CGST_AMT</t>
-  </si>
-  <si>
-    <t>SODBChargeSGSTColumnName</t>
-  </si>
-  <si>
-    <t>SOTC_SGST_AMT</t>
-  </si>
-  <si>
-    <t>EntryCompletedStatus</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
     <t>SELECT soh_cust_id "Customer ID",
        soh_cust_name "Customer Description",
        soh_currency "Currency",
@@ -3447,24 +3179,318 @@
        AND soh_bu = 'TVSA'
        AND soh_order_no ='${SONO}'</t>
   </si>
+  <si>
+    <t>SOLineQuery</t>
+  </si>
+  <si>
+    <t>SELECT soq_prod_id "Item ID",soq_prod_rev "Item Rev",
+       soq_prod_desc1 "Item Desc",
+       soq_uom "Sale UOM",
+       soq_hsn_code "HSN Code",
+       soq_tax_pct "Tax Percentage",
+       soq_price_basis "Price Basis Type",
+       DECODE (soq_price_basis,
+               'C', 'Open Order',
+               'L', 'Catalog Price',
+               'P', 'Price List',
+               'S', 'Standard Price',
+               'U', 'User Defined')
+          "Price Basis Desc",
+       soq_cont_cat_no "Contract Number",
+       soq_catalog_no "Catalog / Price List Number",
+       soq_prod_uom "Stock UOM",
+       soq_conv_factor "Conversion Factor",
+       soq_tolr_type "Tolerance Type",
+       soq_cust_prod_id "Customer Item ID",
+       soq_cust_prod_desc "Customer Item Desc",
+       (SELECT store_desc1
+          FROM stores
+         WHERE store_bu = soq_bu AND store_id = soq_store_id
+        UNION ALL
+        SELECT dept_name1
+          FROM departments
+         WHERE dept_bu = soq_bu AND dept_id = soq_store_id)
+          "Warehouse Description",
+       soq_prod_subcls_desc "SubClass Desc",
+       soq_prod_cls_desc "Class Desc",
+       (SELECT spc_class_desc
+          FROM sales_price_classes
+         WHERE spc_bu = soq_bu AND spc_class_id = soq_sales_price_class)
+          "Price Class",
+       soq_promotion_flag "Promotional",
+       soq_trd_assbl_val "Trade Ass. Val.",
+       soq_disc_pct "Trade Disc. %",
+       soq_disc_amt "Trade Disc. Amt.",
+       soq_spl_assbl_val "Spl. Ass. Val.",
+       soq_spl_disc_pct "Spl. Disc. %",
+       soq_spl_disc_amt "Spl. Disc. Amt.",
+       soq_cash_assbl_val "Cash Ass. Val.",
+       soq_cash_disc_pct "Cash Disc. %",
+       soq_cash_disc_amt "Cash Disc. Amt.",
+       soq_gross_amt "Gross Amt.",
+       soq_disc_amt_per_qty "Disc. Amt. / Qty.",
+       soq_tax_amt "Tax Amt.",
+       soq_net_amt "Net Amt.",
+       soq_gross_amt "Gross Amt.",
+       soq_disc_amt_per_qty "Disc. Amt. / Qty.",
+       soq_tax_amt "Tax Amt.",
+       soq_net_amt "Net Amt.",
+       soq_qty_ordered "Ord. Qty.",
+       soq_price "Unit Price",
+       soq_tot_disc_amt "Disc. Amt.",
+       soq_igst_amt "IGST Amt.",
+       soq_sgst_amt "SGST Amt.",
+       soq_cgst_amt "CGST Amt."
+  FROM sales_order_hd, sales_order_qtys
+ WHERE     soh_bu = soq_bu
+       AND soh_order_no = soq_order_no
+       AND soh_bu = 'TVSA'
+       AND soh_order_no = '${SONO}'</t>
+  </si>
+  <si>
+    <t>Stock Query</t>
+  </si>
+  <si>
+    <t>SELECT stock_qty_hand,
+      (SELECT stcost_cost
+  FROM stock_costs
+ WHERE stcost_bu = 'TVSA'
+   AND stcost_store_id = stock_store_id
+   AND stcost_prod_id = stock_prod_id
+   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
+  FROM stocks
+ WHERE stock_bu = 'TVSA'
+   AND stock_store_id = '${SONO}'
+   AND stock_prod_id = 'TVS-RM-KDK-10'
+   AND stock_prod_rev = '0'</t>
+  </si>
+  <si>
+    <t>OsoaQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT srcahd_plnt_loc_id "loc id",
+       srcahd_plnt "unit",
+       srcahd_doc_no "Doc. No.",
+       srcahd_amd_no "Amd. No.",
+       srcahd_cust_id "customer id",
+       (SELECT suplr_name1
+          FROM suppliers
+         WHERE suplr_bu = srcahd_bu AND suplr_suplr_id = srcahd_cust_id)
+          "customer name",
+       srcaln_prod_id "item id",
+       srcaln_prod_rev "item rev",
+       (SELECT prod_desc11
+          FROM products
+         WHERE     prod_bu = srcaln_bu
+               AND prod_id = srcaln_prod_id
+               AND prod_rev = srcaln_prod_rev)
+          "item descripition",
+       srcaln_uom "uom",
+       srcaln_disc_pct "disc_pct",
+       srcaln_old_price "Existing Price",
+       srcaln_new_price "new_price",
+       srcaln_mrp_price "MRP Price",
+       srcaln_hsn_code "HSN code",
+       srcaln_tax_pct "Tax Percent",
+       srcaln_cgst_amt "CGST",
+       srcaln_sgst_amt "SGST",
+       srcaln_igst_amt "IGST",
+       srcaln_utgst_amt "UTGST"
+  FROM sales_rate_contr_ament_hd, sales_rate_contr_ament_ln
+ WHERE     srcahd_bu = srcaln_bu
+       AND srcahd_plnt = srcaln_plnt
+       AND srcahd_doc_no = '${OSOANO}'
+    AND srcahd_doc_no = srcaln_doc_no
+       AND srcahd_bu =  'TVSA' </t>
+  </si>
+  <si>
+    <t>SOAdvanceQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   SELECT soh_adv_pct,
+       soh_adv_rcvd,
+       soh_adv_tax_pct,
+       soh_adv_req_flag,
+       soh_adv_to_rcvd,
+       soh_adv_rcpt_inprg,
+SOH_ADV_DOC_NO
+  FROM sales_order_hd
+  WHERE soh_bu = 'TVSA'
+  and soh_order_no = '${SONO}'</t>
+  </si>
+  <si>
+    <t>SOCustomerDetailsQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  SELECT (SELECT NVL(state_name1,state_name2) FROM states WHERE state_bu = suplr_bu AND state_id = suplr_state)"Customer State"
+       FROM suppliers
+       WHERE suplr_bu = 'TVSA'
+       AND suplr_suplr_id = '${SONO}'</t>
+  </si>
+  <si>
+    <t>SOUnitDetailsQuery</t>
+  </si>
+  <si>
+    <t>SELECT  (SELECT NVL(state_name1,state_name2) FROM states WHERE state_bu = bup_bu AND state_id = BUP_STATE)"Unit State"
+      FROM bus_unit_plants
+     WHERE bup_bu ='TVSA'
+       AND bup_plant_id ='${SONO}'</t>
+  </si>
+  <si>
+    <t>SOLineDetails1&amp;2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  select soq_cess_pct,soq_cess_amt,SOQ_GST_EXEMPT_FLAG,SOQ_GST_INPUT_TYPE,SOQ_SAL_ACCT_ID,SOQ_SAL_CC_ID,SOQ_DISC_ACCT_ID,SOQ_DISC_CC_ID,SOQ_CUST_PO_NO,SOQ_CUST_PO_REV,SOQ_CUST_PO_DATE,
+  SOQ_PO_SL_SEQ_NO,SOQ_SQ_PFX,SOQ_SQ_NO,SOQ_SQ_SEQ_NO,SOQ_SQ_REV,SOQ_OPO_PO_NO,SOQ_OPO_PO_DATE,SOQ_PO_SEQ_NO,SOQ_CONT_CAT_NO,SOQ_PO_REF,SOQ_CATALOG_NO,
+  SOQ_CUST_PROD_ID,SOQ_CUST_PROD_DESC,SOQ_STORE_NAME,SOQ_PROD_EXT_DESC,SOQ_DESP_DATE,SOQ_RQRD_DATE,SOQ_PROMOTION_FLAG,SOQ_SALES_PRICE_CLASS,SOQ_SCHLD_DESC,SOQ_TOLERANCE_PCT,
+  SOQ_PROD_UOM,SOQ_CONV_FACTOR,SOQ_TOLR_QTY,SOQ_TOLR_TYPE,SOQ_BOM_NO,SOQ_BOM_NAME,SOQ_BOM_REVISION_NUM,SOQ_MARGIN_PCT,SOQ_LIST_PRICE,SOQ_MRP_PRICE,SOQ_SQ_PRICE,SOQ_INSTL_RQRD_FLAG
+         from sales_order_qtys
+         where soq_bu ='TVSA'
+           and soq_order_no ='${SONO}'</t>
+  </si>
+  <si>
+    <t>PaymentTermQuery</t>
+  </si>
+  <si>
+    <t>SELECT term_desc1,
+       trln_mtrl_pct,
+       trln_tax_pct,
+       TRLN_CLAIM_TYPE
+  FROM terms_ln,
+       terms_hd
+ WHERE  term_bu = trln_bu
+   AND term_bu = 'TVSA'
+   AND  TRLN_CLAIM_TYPE ='A'
+  AND term_term_id = trln_term_id
+  AND  term_desc1 = '${SONO}'</t>
+  </si>
+  <si>
+    <t>AdvanceReceiptQuery</t>
+  </si>
+  <si>
+    <t>SELECT
+        pard_doc_no Doc_no,
+        pard_plnt Unit,
+        pard_ord_pfx ord_pfx,
+        pard_ord_no ord_no,
+        pard_party_id Party_id,
+        pard_prop_adv_pct Adv_Percentage,
+        pard_prop_adv_amt Adv_Amt,
+        pard_curcy_id Curcy,
+        pard_ord_amt Ord_amt,
+        pard_rct_inprog_amt Rcpt_inprog_amt,
+        pard_rct_amt Rcpt_Amt,
+        pard_close_amt Closed_amt
+   FROM prop_adv_rct_doc
+  WHERE pard_bu = 'TVSA'
+    AND pard_doc_no ='${SONO}'</t>
+  </si>
+  <si>
+    <t>Stock Query1</t>
+  </si>
+  <si>
+    <t>SELECT stock_qty_hand,
+      (SELECT stcost_cost
+  FROM stock_costs
+ WHERE stcost_bu = 'TVSA'
+   AND stcost_store_id = stock_store_id
+   AND stcost_prod_id = stock_prod_id
+   AND stcost_prod_rev = stock_prod_rev)  stcost_cost
+  FROM stocks
+ WHERE stock_bu = 'TVSA'
+   AND stock_store_id = '${SONO}'
+   AND stock_prod_id ='${PONO}'
+   AND stock_prod_rev = '0'</t>
+  </si>
+  <si>
+    <t>SalesOrderChargesQuery</t>
+  </si>
+  <si>
+    <t>SELECT
+       sotc_bu,
+       sotc_ord_no,
+       sotc_seq_no,
+       sotc_prod_id,
+       (SELECT prod_desc11
+          FROM products
+         WHERE prod_bu ='TVSA'
+           AND prod_id = sotc_prod_id
+           AND prod_rev = sotc_prod_rev)ITEM_DESC,
+       sotc_prod_rev,
+       sotc_hsn_code,
+       sotc_qty,
+       sotc_chrg_basis,
+       sotc_chrg_pct,
+       sotc_chrg_pct sotc_chrg_pct1,
+       sotc_chrg_amt,
+       sotc_chrg_amt sotc_chrg_amt1,
+       sotc_gst_exempt_flag,
+       sotc_gst_input_type,
+       sotc_cre_by,
+       sotc_cre_ip_addr,
+       sotc_cre_os_user,
+       sotc_cre_date,
+       sotc_upd_by,
+       sotc_upd_ip_addr,
+       sotc_upd_os_user,
+       sotc_upd_date,
+       sotc_cre_emp_id,
+       sotc_upd_emp_id,
+       sotc_tcs_avail_flag,
+       sotc_sal_acct_id,
+       sotc_sal_cc_id,
+       sotc_tariff_code,
+       sotc_cgst_pct,
+       sotc_sgst_pct,
+       sotc_utgst_pct,
+       sotc_cess_pct,
+       sotc_igst_amt,
+       sotc_cgst_amt,
+       sotc_sgst_amt,
+       sotc_utgst_amt,
+       sotc_cess_amt,
+       sotc_tax_pct
+  FROM so_oth_tax_charges
+  WHERE sotc_bu = 'TVSA'
+    AND sotc_ord_no ='${SONO}'</t>
+  </si>
+  <si>
+    <t>ItemShipSetQuery</t>
+  </si>
+  <si>
+    <t>SELECT PS_SS_PROD_ID, PS_SS_PROD_REV,
+       ( SELECT prod_desc11
+          FROM products
+         WHERE prod_bu  = ps_bu
+           AND prod_id  = PS_SS_PROD_ID
+           AND prod_rev = PS_SS_PROD_REV) PSI_SS_PROD_DESC,
+           PS_SS_QTY,
+           (SELECT PROD_UOM
+             FROM products
+            WHERE prod_bu  = ps_bu
+              AND prod_id  = PS_SS_PROD_ID
+              AND prod_rev = PS_SS_PROD_REV)UOM
+FROM PROD_SHIPSET
+  where   PS_BU =  'TVSA'
+    and   PS_FG_PROD_ID  = '${SONO}'</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3476,48 +3502,181 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3542,8 +3701,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -3579,159 +3924,423 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 2 2" xfId="3"/>
-    <cellStyle name="Normal 2 3" xfId="4"/>
-    <cellStyle name="Normal 3" xfId="2"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal 2" xfId="49"/>
+    <cellStyle name="Normal 2 2" xfId="50"/>
+    <cellStyle name="Normal 2 3" xfId="51"/>
+    <cellStyle name="Normal 3" xfId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3993,17 +4602,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B562"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B568"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" customWidth="1"/>
-    <col min="2" max="2" width="59.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="62.7777777777778" style="4" customWidth="1"/>
+    <col min="2" max="2" width="59.8518518518519" style="5" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4015,647 +4625,647 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="10">
         <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="9" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="9" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="9" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="9" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="9" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="9" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="9" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="9" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="9" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="9" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="9" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="9" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="12" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="12" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="12" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="12" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="12" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="12" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="12" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="12" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="12" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" s="12" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="9" t="s">
+      <c r="A64" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="12" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="9" t="s">
+      <c r="A65" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="12">
         <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="12" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="9" t="s">
+      <c r="A67" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="12" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="12" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="12">
         <v>2012</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="12" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="12" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="12" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B73" s="12" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="12" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="12" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="12">
         <v>202425</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="12" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="12" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="12" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="12" t="s">
+      <c r="A80" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="12" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="11" t="s">
         <v>155</v>
       </c>
       <c r="B82" s="14" t="s">
@@ -4663,15 +5273,15 @@
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="12" t="s">
+      <c r="A83" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="12" t="s">
+      <c r="A84" s="11" t="s">
         <v>158</v>
       </c>
       <c r="B84" s="14" t="s">
@@ -4679,7 +5289,7 @@
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="12" t="s">
+      <c r="A85" s="11" t="s">
         <v>160</v>
       </c>
       <c r="B85" s="14" t="s">
@@ -4687,607 +5297,607 @@
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="12" t="s">
+      <c r="A86" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="12" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="15" t="s">
+      <c r="A88" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="15" t="s">
+      <c r="A89" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="16" t="s">
+      <c r="A90" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="15" t="s">
+      <c r="A91" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="12" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="15" t="s">
+      <c r="A92" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="12" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="15" t="s">
+      <c r="A93" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="15" t="s">
+      <c r="A94" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="12" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="15" t="s">
+      <c r="A95" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B95" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="15" t="s">
+      <c r="A96" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="12" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="15" t="s">
+      <c r="A97" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="12" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="15" t="s">
+      <c r="A98" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="12" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="15" t="s">
+      <c r="A99" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="17" t="s">
+      <c r="A100" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="B100" s="18" t="s">
+      <c r="B100" s="17" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="17" t="s">
+      <c r="A101" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="B101" s="19" t="s">
+      <c r="B101" s="17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="17" t="s">
+      <c r="A102" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B102" s="18" t="s">
+      <c r="B102" s="17" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="17" t="s">
+      <c r="A103" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B103" s="18" t="s">
+      <c r="B103" s="17" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B104" s="19">
+      <c r="B104" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="20" t="s">
+      <c r="A105" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="B105" s="21" t="s">
+      <c r="B105" s="20" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="20" t="s">
+      <c r="A106" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="B106" s="22" t="s">
+      <c r="B106" s="20" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="20" t="s">
+      <c r="A107" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="B107" s="23">
+      <c r="B107" s="21">
         <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="20" t="s">
+      <c r="A108" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="B108" s="21" t="s">
+      <c r="B108" s="20" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="20" t="s">
+      <c r="A109" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="B109" s="24" t="s">
+      <c r="B109" s="22" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="20" t="s">
+      <c r="A110" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="B110" s="23">
+      <c r="B110" s="21">
         <v>100</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="B111" s="25" t="s">
+      <c r="B111" s="23" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="26" t="s">
+      <c r="A112" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="B112" s="27" t="s">
+      <c r="B112" s="25" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="26" t="s">
+      <c r="A113" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="B113" s="27" t="s">
+      <c r="B113" s="25" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="26" t="s">
+      <c r="A114" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="B114" s="25" t="s">
+      <c r="B114" s="23" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="B115" s="25" t="s">
+      <c r="B115" s="23" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="26" t="s">
+      <c r="A116" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="B116" s="25" t="s">
+      <c r="B116" s="23" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B117" s="25" t="s">
+      <c r="B117" s="23" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B118" s="25">
+      <c r="B118" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="28" t="s">
+      <c r="A119" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="B119" s="29" t="s">
+      <c r="B119" s="9" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="28" t="s">
+      <c r="A120" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="B120" s="29" t="s">
+      <c r="B120" s="9" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="28" t="s">
+      <c r="A121" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="B121" s="29" t="s">
+      <c r="B121" s="9" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="28" t="s">
+      <c r="A122" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="B122" s="29" t="s">
+      <c r="B122" s="9" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="28" t="s">
+      <c r="A123" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="B123" s="29" t="s">
+      <c r="B123" s="9" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="28" t="s">
+      <c r="A124" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="B124" s="29" t="s">
+      <c r="B124" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="28" t="s">
+      <c r="A125" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="B125" s="29" t="s">
+      <c r="B125" s="9" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="28" t="s">
+      <c r="A126" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="B126" s="29" t="s">
+      <c r="B126" s="9" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="28" t="s">
+      <c r="A127" s="27" t="s">
         <v>232</v>
       </c>
-      <c r="B127" s="29" t="s">
+      <c r="B127" s="9" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="28" t="s">
+      <c r="A128" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="B128" s="29" t="s">
+      <c r="B128" s="9" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="28" t="s">
+      <c r="A129" s="27" t="s">
         <v>236</v>
       </c>
-      <c r="B129" s="29" t="s">
+      <c r="B129" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="28" t="s">
+      <c r="A130" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="B130" s="29" t="s">
+      <c r="B130" s="9" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="28" t="s">
+      <c r="A131" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="B131" s="29" t="s">
+      <c r="B131" s="9" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="28" t="s">
+      <c r="A132" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="B132" s="29" t="s">
+      <c r="B132" s="9" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="28" t="s">
+      <c r="A133" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="B133" s="29" t="s">
+      <c r="B133" s="9" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="28" t="s">
+      <c r="A134" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="B134" s="29" t="s">
+      <c r="B134" s="9" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="28" t="s">
+      <c r="A135" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="B135" s="29" t="s">
+      <c r="B135" s="9" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="28" t="s">
+      <c r="A136" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="B136" s="29" t="s">
+      <c r="B136" s="9" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="28" t="s">
+      <c r="A137" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="B137" s="29" t="s">
+      <c r="B137" s="9" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="28" t="s">
+      <c r="A138" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="B138" s="29" t="s">
+      <c r="B138" s="9" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="28" t="s">
+      <c r="A139" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="B139" s="29" t="s">
+      <c r="B139" s="9" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="28" t="s">
+      <c r="A140" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="B140" s="29" t="s">
+      <c r="B140" s="9" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="28" t="s">
+      <c r="A141" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="B141" s="29" t="s">
+      <c r="B141" s="9" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="28" t="s">
+      <c r="A142" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="B142" s="29" t="s">
+      <c r="B142" s="9" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="28" t="s">
+      <c r="A143" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="B143" s="29" t="s">
+      <c r="B143" s="9" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="28" t="s">
+      <c r="A144" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="B144" s="29" t="s">
+      <c r="B144" s="9" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="28" t="s">
+      <c r="A145" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="B145" s="29" t="s">
+      <c r="B145" s="9" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="28" t="s">
+      <c r="A146" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="B146" s="29" t="s">
+      <c r="B146" s="9" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="28" t="s">
+      <c r="A147" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="B147" s="29" t="s">
+      <c r="B147" s="9" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="28" t="s">
+      <c r="A148" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="B148" s="29" t="s">
+      <c r="B148" s="9" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="28" t="s">
+      <c r="A149" s="27" t="s">
         <v>262</v>
       </c>
-      <c r="B149" s="29" t="s">
+      <c r="B149" s="9" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="28" t="s">
+      <c r="A150" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="B150" s="29" t="s">
+      <c r="B150" s="9" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="30" t="s">
+      <c r="A151" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="B151" s="29" t="s">
+      <c r="B151" s="9" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="30" t="s">
+      <c r="A152" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="B152" s="29" t="s">
+      <c r="B152" s="9" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="30" t="s">
+      <c r="A153" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="B153" s="29" t="s">
+      <c r="B153" s="9" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="30" t="s">
+      <c r="A154" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="B154" s="29" t="s">
+      <c r="B154" s="9" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="30" t="s">
+      <c r="A155" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="B155" s="29" t="s">
+      <c r="B155" s="9" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="30" t="s">
+      <c r="A156" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="B156" s="29" t="s">
+      <c r="B156" s="9" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="31" t="s">
+      <c r="A157" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="B157" s="32" t="s">
+      <c r="B157" s="28" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="2" t="s">
+      <c r="A158" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="B158" s="25" t="s">
+      <c r="B158" s="23" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="12" t="s">
+      <c r="A159" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="B159" s="33" t="s">
+      <c r="B159" s="29" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="12" t="s">
+      <c r="A160" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B160" s="13" t="s">
+      <c r="B160" s="12" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="12" t="s">
+      <c r="A161" s="11" t="s">
         <v>284</v>
       </c>
       <c r="B161" s="14" t="s">
@@ -5295,23 +5905,23 @@
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="12" t="s">
+      <c r="A162" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="B162" s="13" t="s">
+      <c r="B162" s="12" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="12" t="s">
+      <c r="A163" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B163" s="13" t="s">
+      <c r="B163" s="12" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="12" t="s">
+      <c r="A164" s="11" t="s">
         <v>290</v>
       </c>
       <c r="B164" s="14" t="s">
@@ -5319,7 +5929,7 @@
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="12" t="s">
+      <c r="A165" s="11" t="s">
         <v>292</v>
       </c>
       <c r="B165" s="14" t="s">
@@ -5327,23 +5937,23 @@
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="12" t="s">
+      <c r="A166" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B166" s="13" t="s">
+      <c r="B166" s="12" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="12" t="s">
+      <c r="A167" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="B167" s="13" t="s">
+      <c r="B167" s="12" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="12" t="s">
+      <c r="A168" s="11" t="s">
         <v>298</v>
       </c>
       <c r="B168" s="14" t="s">
@@ -5351,7 +5961,7 @@
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="12" t="s">
+      <c r="A169" s="11" t="s">
         <v>300</v>
       </c>
       <c r="B169" s="14" t="s">
@@ -5359,135 +5969,135 @@
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="12" t="s">
+      <c r="A170" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="B170" s="13" t="s">
+      <c r="B170" s="12" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="12" t="s">
+      <c r="A171" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="B171" s="13" t="s">
+      <c r="B171" s="12" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="12" t="s">
+      <c r="A172" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="B172" s="13" t="s">
+      <c r="B172" s="12" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="12" t="s">
+      <c r="A173" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="B173" s="13" t="s">
+      <c r="B173" s="12" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="12" t="s">
+      <c r="A174" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="B174" s="13" t="s">
+      <c r="B174" s="12" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="12" t="s">
+      <c r="A175" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="B175" s="13" t="s">
+      <c r="B175" s="12" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="12" t="s">
+      <c r="A176" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B176" s="13" t="s">
+      <c r="B176" s="12" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="12" t="s">
+      <c r="A177" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="B177" s="13" t="s">
+      <c r="B177" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="12" t="s">
+      <c r="A178" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="B178" s="13" t="s">
+      <c r="B178" s="12" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="12" t="s">
+      <c r="A179" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="B179" s="13" t="s">
+      <c r="B179" s="12" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="12" t="s">
+      <c r="A180" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="B180" s="13" t="s">
+      <c r="B180" s="12" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="12" t="s">
+      <c r="A181" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="B181" s="13" t="s">
+      <c r="B181" s="12" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="12" t="s">
+      <c r="A182" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="B182" s="13" t="s">
+      <c r="B182" s="12" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="12" t="s">
+      <c r="A183" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="B183" s="13" t="s">
+      <c r="B183" s="12" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="12" t="s">
+      <c r="A184" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="B184" s="13" t="s">
+      <c r="B184" s="12" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="12" t="s">
+      <c r="A185" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="B185" s="13" t="s">
+      <c r="B185" s="12" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="12" t="s">
+      <c r="A186" s="11" t="s">
         <v>331</v>
       </c>
       <c r="B186" s="14" t="s">
@@ -5495,7 +6105,7 @@
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="12" t="s">
+      <c r="A187" s="11" t="s">
         <v>333</v>
       </c>
       <c r="B187" s="14" t="s">
@@ -5503,15 +6113,15 @@
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="12" t="s">
+      <c r="A188" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="B188" s="13" t="s">
+      <c r="B188" s="12" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="12" t="s">
+      <c r="A189" s="11" t="s">
         <v>336</v>
       </c>
       <c r="B189" s="14" t="s">
@@ -5519,3000 +6129,3050 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="12" t="s">
+      <c r="A190" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="B190" s="13" t="s">
+      <c r="B190" s="12" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="2" t="s">
+      <c r="A191" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="B191" s="34" t="s">
+      <c r="B191" s="30" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="35" t="s">
+      <c r="A192" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="B192" s="36" t="s">
+      <c r="B192" s="32" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="35" t="s">
+      <c r="A193" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="B193" s="37" t="s">
+      <c r="B193" s="32" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="35" t="s">
+      <c r="A194" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="B194" s="19">
+      <c r="B194" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="35" t="s">
+      <c r="A195" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="B195" s="36" t="s">
+      <c r="B195" s="32" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="35" t="s">
+      <c r="A196" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="B196" s="18" t="s">
+      <c r="B196" s="17" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="35" t="s">
+      <c r="A197" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="B197" s="19">
+      <c r="B197" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="35" t="s">
+      <c r="A198" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="B198" s="19" t="s">
+      <c r="B198" s="17" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="35" t="s">
+      <c r="A199" s="31" t="s">
         <v>344</v>
       </c>
-      <c r="B199" s="38" t="s">
+      <c r="B199" s="33" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="35" t="s">
+      <c r="A200" s="31" t="s">
         <v>346</v>
       </c>
-      <c r="B200" s="38" t="s">
+      <c r="B200" s="33" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="35" t="s">
+      <c r="A201" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="B201" s="38" t="s">
+      <c r="B201" s="33" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="35" t="s">
+      <c r="A202" s="31" t="s">
         <v>350</v>
       </c>
-      <c r="B202" s="19">
+      <c r="B202" s="18">
         <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="35" t="s">
+      <c r="A203" s="31" t="s">
         <v>351</v>
       </c>
-      <c r="B203" s="19">
+      <c r="B203" s="18">
         <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="35" t="s">
+      <c r="A204" s="31" t="s">
         <v>352</v>
       </c>
-      <c r="B204" s="19" t="s">
+      <c r="B204" s="17" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="39" t="s">
+      <c r="A205" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="B205" s="19">
+      <c r="B205" s="18">
         <v>150</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="39" t="s">
+      <c r="A206" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="B206" s="19">
+      <c r="B206" s="18">
         <v>250</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="39" t="s">
+      <c r="A207" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="B207" s="19" t="s">
+      <c r="B207" s="17" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="39" t="s">
+      <c r="A208" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="B208" s="19">
+      <c r="B208" s="18">
         <v>123562</v>
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="39" t="s">
+      <c r="A209" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="B209" s="19">
+      <c r="B209" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="39" t="s">
+      <c r="A210" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="B210" s="19">
+      <c r="B210" s="18">
         <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="39" t="s">
+      <c r="A211" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="B211" s="19">
+      <c r="B211" s="18">
         <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="39" t="s">
+      <c r="A212" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="B212" s="37" t="s">
+      <c r="B212" s="32" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="39" t="s">
+      <c r="A213" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="B213" s="18" t="s">
+      <c r="B213" s="17" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="39" t="s">
+      <c r="A214" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="B214" s="37" t="s">
+      <c r="B214" s="32" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="39" t="s">
+      <c r="A215" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="B215" s="19">
+      <c r="B215" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="39" t="s">
+      <c r="A216" s="16" t="s">
         <v>369</v>
       </c>
-      <c r="B216" s="19">
+      <c r="B216" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="39" t="s">
+      <c r="A217" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="B217" s="37" t="s">
+      <c r="B217" s="32" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="2" t="s">
+      <c r="A218" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="B218" s="25" t="s">
+      <c r="B218" s="23" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="31" t="s">
+      <c r="A219" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="B219" s="40" t="s">
+      <c r="B219" s="23" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="31" t="s">
+      <c r="A220" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="B220" s="25" t="s">
+      <c r="B220" s="23" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="31" t="s">
+      <c r="A221" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="B221" s="25" t="s">
+      <c r="B221" s="23" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="41" t="s">
+      <c r="A222" s="24" t="s">
         <v>376</v>
       </c>
-      <c r="B222" s="40" t="s">
+      <c r="B222" s="23" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="41" t="s">
+      <c r="A223" s="24" t="s">
         <v>378</v>
       </c>
-      <c r="B223" s="40" t="s">
+      <c r="B223" s="23" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="42" t="s">
+      <c r="A224" s="34" t="s">
         <v>380</v>
       </c>
-      <c r="B224" s="43" t="s">
+      <c r="B224" s="35" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="41" t="s">
+      <c r="A225" s="24" t="s">
         <v>382</v>
       </c>
-      <c r="B225" s="44" t="s">
+      <c r="B225" s="25" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="2" t="s">
+      <c r="A226" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="B226" s="8" t="s">
+      <c r="B226" s="9" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="2" t="s">
+      <c r="A227" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="B227" s="8" t="s">
+      <c r="B227" s="9" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="2" t="s">
+      <c r="A228" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="B228" s="8" t="s">
+      <c r="B228" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="2" t="s">
+      <c r="A229" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="B229" s="8" t="s">
+      <c r="B229" s="9" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="2" t="s">
+      <c r="A230" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="B230" s="8" t="s">
+      <c r="B230" s="9" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="2" t="s">
+      <c r="A231" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="B231" s="8" t="s">
+      <c r="B231" s="9" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="2" t="s">
+      <c r="A232" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B232" s="8" t="s">
+      <c r="B232" s="9" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="2" t="s">
+      <c r="A233" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="B233" s="8" t="s">
+      <c r="B233" s="9" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="234" spans="1:2">
-      <c r="A234" s="2" t="s">
+      <c r="A234" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B234" s="8" t="s">
+      <c r="B234" s="9" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="235" spans="1:2">
-      <c r="A235" s="2" t="s">
+      <c r="A235" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B235" s="8" t="s">
+      <c r="B235" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="236" spans="1:2">
-      <c r="A236" s="2" t="s">
+      <c r="A236" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="B236" s="8" t="s">
+      <c r="B236" s="9" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="237" spans="1:2">
-      <c r="A237" s="2" t="s">
+      <c r="A237" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="B237" s="8" t="s">
+      <c r="B237" s="9" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="238" spans="1:2">
-      <c r="A238" s="2" t="s">
+      <c r="A238" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="B238" s="8" t="s">
+      <c r="B238" s="9" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="239" spans="1:2">
-      <c r="A239" s="2" t="s">
+      <c r="A239" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="B239" s="8" t="s">
+      <c r="B239" s="9" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="240" spans="1:2">
-      <c r="A240" s="2" t="s">
+      <c r="A240" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="B240" s="8" t="s">
+      <c r="B240" s="9" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="241" spans="1:2">
-      <c r="A241" s="2" t="s">
+      <c r="A241" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="B241" s="8" t="s">
+      <c r="B241" s="9" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="242" spans="1:2">
-      <c r="A242" s="2" t="s">
+      <c r="A242" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="B242" s="8" t="s">
+      <c r="B242" s="9" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="243" spans="1:2">
-      <c r="A243" s="2" t="s">
+      <c r="A243" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="B243" s="8" t="s">
+      <c r="B243" s="9" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="244" spans="1:2">
-      <c r="A244" s="2" t="s">
+      <c r="A244" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="B244" s="8" t="s">
+      <c r="B244" s="9" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="245" spans="1:2">
-      <c r="A245" s="2" t="s">
+      <c r="A245" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="B245" s="8" t="s">
+      <c r="B245" s="9" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="246" spans="1:2">
-      <c r="A246" s="2" t="s">
+      <c r="A246" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="B246" s="8" t="s">
+      <c r="B246" s="9" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="247" spans="1:2">
-      <c r="A247" s="2" t="s">
+      <c r="A247" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="B247" s="8" t="s">
+      <c r="B247" s="9" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="248" spans="1:2">
-      <c r="A248" s="2" t="s">
+      <c r="A248" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="B248" s="8" t="s">
+      <c r="B248" s="9" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="249" spans="1:2">
-      <c r="A249" s="2" t="s">
+      <c r="A249" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="B249" s="45" t="s">
+      <c r="B249" s="36" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="250" spans="1:2">
-      <c r="A250" s="2" t="s">
+      <c r="A250" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="B250" s="8" t="s">
+      <c r="B250" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="251" spans="1:2">
-      <c r="A251" s="2" t="s">
+      <c r="A251" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="B251" s="8" t="s">
+      <c r="B251" s="9" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="252" spans="1:2">
-      <c r="A252" s="2" t="s">
+      <c r="A252" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="B252" s="8" t="s">
+      <c r="B252" s="9" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="253" spans="1:2">
-      <c r="A253" s="2" t="s">
+      <c r="A253" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="B253" s="8" t="s">
+      <c r="B253" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="254" spans="1:2">
-      <c r="A254" s="2" t="s">
+      <c r="A254" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="B254" s="8" t="s">
+      <c r="B254" s="9" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="255" spans="1:2">
-      <c r="A255" s="2" t="s">
+      <c r="A255" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="B255" s="8" t="s">
+      <c r="B255" s="9" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="256" spans="1:2">
-      <c r="A256" s="2" t="s">
+      <c r="A256" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="B256" s="8" t="s">
+      <c r="B256" s="9" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="257" spans="1:2">
-      <c r="A257" s="2" t="s">
+      <c r="A257" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="B257" s="8" t="s">
+      <c r="B257" s="9" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="258" spans="1:2">
-      <c r="A258" s="2" t="s">
+      <c r="A258" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="B258" s="8" t="s">
+      <c r="B258" s="9" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="259" spans="1:2">
-      <c r="A259" s="2" t="s">
+      <c r="A259" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="B259" s="8" t="s">
+      <c r="B259" s="9" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="260" spans="1:2">
-      <c r="A260" s="2" t="s">
+      <c r="A260" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="B260" s="8" t="s">
+      <c r="B260" s="9" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="261" spans="1:2">
-      <c r="A261" s="2" t="s">
+      <c r="A261" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="B261" s="8" t="s">
+      <c r="B261" s="9" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="262" spans="1:2">
-      <c r="A262" s="2" t="s">
+      <c r="A262" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="B262" s="8" t="s">
+      <c r="B262" s="9" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="263" spans="1:2">
-      <c r="A263" s="2" t="s">
+      <c r="A263" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="B263" s="8" t="s">
+      <c r="B263" s="9" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="264" spans="1:2">
-      <c r="A264" s="2" t="s">
+      <c r="A264" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="B264" s="8" t="s">
+      <c r="B264" s="9" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="265" spans="1:2">
-      <c r="A265" s="2" t="s">
+      <c r="A265" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="B265" s="8" t="s">
+      <c r="B265" s="9" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="266" spans="1:2">
-      <c r="A266" s="2" t="s">
+      <c r="A266" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="B266" s="8" t="s">
+      <c r="B266" s="9" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="267" spans="1:2">
-      <c r="A267" s="2" t="s">
+      <c r="A267" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="B267" s="8" t="s">
+      <c r="B267" s="9" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="268" spans="1:2">
-      <c r="A268" s="2" t="s">
+      <c r="A268" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="B268" s="8" t="s">
+      <c r="B268" s="9" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="269" spans="1:2">
-      <c r="A269" s="2" t="s">
+      <c r="A269" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="B269" s="8" t="s">
+      <c r="B269" s="9" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="270" spans="1:2">
-      <c r="A270" s="2" t="s">
+      <c r="A270" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="B270" s="8" t="s">
+      <c r="B270" s="9" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="271" spans="1:2">
-      <c r="A271" s="2" t="s">
+      <c r="A271" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="B271" s="8" t="s">
+      <c r="B271" s="9" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="272" spans="1:2">
-      <c r="A272" s="2" t="s">
+      <c r="A272" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="B272" s="8" t="s">
+      <c r="B272" s="9" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="273" spans="1:2">
-      <c r="A273" s="2" t="s">
+      <c r="A273" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="B273" s="8" t="s">
+      <c r="B273" s="9" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="274" spans="1:2">
-      <c r="A274" s="2" t="s">
+      <c r="A274" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="B274" s="8" t="s">
+      <c r="B274" s="9" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="275" spans="1:2">
-      <c r="A275" s="2" t="s">
+      <c r="A275" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="B275" s="8" t="s">
+      <c r="B275" s="9" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="276" spans="1:2">
-      <c r="A276" s="2" t="s">
+      <c r="A276" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="B276" s="8" t="s">
+      <c r="B276" s="9" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="277" spans="1:2">
-      <c r="A277" s="2" t="s">
+      <c r="A277" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="B277" s="8" t="s">
+      <c r="B277" s="9" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="278" spans="1:2">
-      <c r="A278" s="26" t="s">
+      <c r="A278" s="24" t="s">
         <v>467</v>
       </c>
-      <c r="B278" s="25" t="s">
+      <c r="B278" s="23" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="279" spans="1:2">
-      <c r="A279" s="2" t="s">
+      <c r="A279" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B279" s="25" t="s">
+      <c r="B279" s="23" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="280" spans="1:2">
-      <c r="A280" s="2" t="s">
+      <c r="A280" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="B280" s="8" t="s">
+      <c r="B280" s="9" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="281" spans="1:2">
-      <c r="A281" s="9" t="s">
+      <c r="A281" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="B281" s="10" t="s">
+      <c r="B281" s="12" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="282" spans="1:2">
-      <c r="A282" s="9" t="s">
+      <c r="A282" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="B282" s="10" t="s">
+      <c r="B282" s="12" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="283" spans="1:2">
-      <c r="A283" s="9" t="s">
+      <c r="A283" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="B283" s="10" t="s">
+      <c r="B283" s="12" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="284" spans="1:2">
-      <c r="A284" s="9" t="s">
+      <c r="A284" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="B284" s="46" t="s">
+      <c r="B284" s="14" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="285" spans="1:2">
-      <c r="A285" s="47" t="s">
+      <c r="A285" s="37" t="s">
         <v>479</v>
       </c>
-      <c r="B285" s="8" t="s">
+      <c r="B285" s="9" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="286" spans="1:2">
-      <c r="A286" s="47" t="s">
+      <c r="A286" s="37" t="s">
         <v>481</v>
       </c>
-      <c r="B286" s="8" t="s">
+      <c r="B286" s="9" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="287" spans="1:2">
-      <c r="A287" s="47" t="s">
+      <c r="A287" s="37" t="s">
         <v>483</v>
       </c>
-      <c r="B287" s="8" t="s">
+      <c r="B287" s="9" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="288" spans="1:2">
-      <c r="A288" s="47" t="s">
+      <c r="A288" s="37" t="s">
         <v>485</v>
       </c>
-      <c r="B288" s="8" t="s">
+      <c r="B288" s="9" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="289" spans="1:2">
-      <c r="A289" s="47" t="s">
+      <c r="A289" s="37" t="s">
         <v>487</v>
       </c>
-      <c r="B289" s="8" t="s">
+      <c r="B289" s="9" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="47" t="s">
+      <c r="A290" s="37" t="s">
         <v>489</v>
       </c>
-      <c r="B290" s="8" t="s">
+      <c r="B290" s="9" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="47" t="s">
+      <c r="A291" s="37" t="s">
         <v>491</v>
       </c>
-      <c r="B291" s="8" t="s">
+      <c r="B291" s="9" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="292" spans="1:2">
-      <c r="A292" s="2" t="s">
+      <c r="A292" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="B292" s="8" t="s">
+      <c r="B292" s="9" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="293" spans="1:2">
-      <c r="A293" s="2" t="s">
+      <c r="A293" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="B293" s="8" t="s">
+      <c r="B293" s="9" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="294" spans="1:2">
-      <c r="A294" s="2" t="s">
+      <c r="A294" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="B294" s="8" t="s">
+      <c r="B294" s="9" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="295" spans="1:2">
-      <c r="A295" s="2" t="s">
+      <c r="A295" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="B295" s="8" t="s">
+      <c r="B295" s="9" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="296" spans="1:2">
-      <c r="A296" s="2" t="s">
+      <c r="A296" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="B296" s="8" t="s">
+      <c r="B296" s="9" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="297" spans="1:2">
-      <c r="A297" s="2" t="s">
+      <c r="A297" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="B297" s="8" t="s">
+      <c r="B297" s="9" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="298" spans="1:2">
-      <c r="A298" s="2" t="s">
+      <c r="A298" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="B298" s="8" t="s">
+      <c r="B298" s="9" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="299" spans="1:2">
-      <c r="A299" s="2" t="s">
+      <c r="A299" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="B299" s="8" t="s">
+      <c r="B299" s="9" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="300" spans="1:2">
-      <c r="A300" s="2" t="s">
+      <c r="A300" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="B300" s="8" t="s">
+      <c r="B300" s="9" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="301" spans="1:2">
-      <c r="A301" s="2" t="s">
+      <c r="A301" s="8" t="s">
         <v>511</v>
       </c>
-      <c r="B301" s="8" t="s">
+      <c r="B301" s="9" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="302" spans="1:2">
-      <c r="A302" s="2" t="s">
+      <c r="A302" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="B302" s="8" t="s">
+      <c r="B302" s="9" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="303" spans="1:2">
-      <c r="A303" s="2" t="s">
+      <c r="A303" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="B303" s="8" t="s">
+      <c r="B303" s="9" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="304" spans="1:2">
-      <c r="A304" s="2" t="s">
+      <c r="A304" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="B304" s="8" t="s">
+      <c r="B304" s="9" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="305" spans="1:2">
-      <c r="A305" s="2" t="s">
+      <c r="A305" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="B305" s="8" t="s">
+      <c r="B305" s="9" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="306" spans="1:2">
-      <c r="A306" s="2" t="s">
+      <c r="A306" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="B306" s="8" t="s">
+      <c r="B306" s="9" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="307" spans="1:2">
-      <c r="A307" s="2" t="s">
+      <c r="A307" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B307" s="8" t="s">
+      <c r="B307" s="9" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="308" spans="1:2">
-      <c r="A308" s="2" t="s">
+      <c r="A308" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="B308" s="8" t="s">
+      <c r="B308" s="9" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="309" spans="1:2">
-      <c r="A309" s="2" t="s">
+      <c r="A309" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="B309" s="8" t="s">
+      <c r="B309" s="9" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="310" spans="1:2">
-      <c r="A310" s="2" t="s">
+      <c r="A310" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="B310" s="8" t="s">
+      <c r="B310" s="9" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="311" spans="1:2">
-      <c r="A311" s="2" t="s">
+      <c r="A311" s="8" t="s">
         <v>529</v>
       </c>
-      <c r="B311" s="8" t="s">
+      <c r="B311" s="9" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="312" spans="1:2">
-      <c r="A312" s="2" t="s">
+      <c r="A312" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="B312" s="8" t="s">
+      <c r="B312" s="9" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="313" spans="1:2">
-      <c r="A313" s="2" t="s">
+      <c r="A313" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="B313" s="8" t="s">
+      <c r="B313" s="9" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="314" spans="1:2">
-      <c r="A314" s="2" t="s">
+      <c r="A314" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="B314" s="8" t="s">
+      <c r="B314" s="9" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="315" spans="1:2">
-      <c r="A315" s="2" t="s">
+      <c r="A315" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="B315" s="8" t="s">
+      <c r="B315" s="9" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="316" spans="1:2">
-      <c r="A316" s="2" t="s">
+      <c r="A316" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="B316" s="8" t="s">
+      <c r="B316" s="9" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="317" spans="1:2">
-      <c r="A317" s="2" t="s">
+      <c r="A317" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="B317" s="8" t="s">
+      <c r="B317" s="9" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="318" spans="1:2">
-      <c r="A318" s="2" t="s">
+      <c r="A318" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="B318" s="8" t="s">
+      <c r="B318" s="9" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="319" spans="1:2">
-      <c r="A319" s="2" t="s">
+      <c r="A319" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="B319" s="48" t="s">
+      <c r="B319" s="14" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="320" spans="1:2">
-      <c r="A320" s="2" t="s">
+      <c r="A320" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="B320" s="8" t="s">
+      <c r="B320" s="9" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="321" spans="1:2">
-      <c r="A321" s="2" t="s">
+      <c r="A321" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="B321" s="8" t="s">
+      <c r="B321" s="9" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="322" spans="1:2">
-      <c r="A322" s="2" t="s">
+      <c r="A322" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="B322" s="8" t="s">
+      <c r="B322" s="9" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="323" spans="1:2">
-      <c r="A323" s="2" t="s">
+      <c r="A323" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="B323" s="8" t="s">
+      <c r="B323" s="9" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="324" spans="1:2">
-      <c r="A324" s="2" t="s">
+      <c r="A324" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="B324" s="8" t="s">
+      <c r="B324" s="9" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="325" spans="1:2">
-      <c r="A325" s="2" t="s">
+      <c r="A325" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="B325" s="8" t="s">
+      <c r="B325" s="9" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="326" spans="1:2">
-      <c r="A326" s="2" t="s">
+      <c r="A326" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="B326" s="8" t="s">
+      <c r="B326" s="9" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="327" spans="1:2">
-      <c r="A327" s="2" t="s">
+      <c r="A327" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="B327" s="8" t="s">
+      <c r="B327" s="9" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="328" spans="1:2">
-      <c r="A328" s="2" t="s">
+      <c r="A328" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="B328" s="8" t="s">
+      <c r="B328" s="9" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="329" spans="1:2">
-      <c r="A329" s="2" t="s">
+      <c r="A329" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="B329" s="8" t="s">
+      <c r="B329" s="9" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="330" spans="1:2">
-      <c r="A330" s="2" t="s">
+      <c r="A330" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="B330" s="8" t="s">
+      <c r="B330" s="9" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="331" spans="1:2">
-      <c r="A331" s="2" t="s">
+      <c r="A331" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="B331" s="8" t="s">
+      <c r="B331" s="9" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="332" spans="1:2">
-      <c r="A332" s="2" t="s">
+      <c r="A332" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="B332" s="8" t="s">
+      <c r="B332" s="9" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="333" spans="1:2">
-      <c r="A333" s="2" t="s">
+      <c r="A333" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="B333" s="8" t="s">
+      <c r="B333" s="9" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="334" spans="1:2">
-      <c r="A334" s="2" t="s">
+      <c r="A334" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="B334" s="8" t="s">
+      <c r="B334" s="9" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="335" spans="1:2">
-      <c r="A335" s="2" t="s">
+      <c r="A335" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="B335" s="8" t="s">
+      <c r="B335" s="9" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="30" t="s">
+      <c r="A336" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="B336" s="29" t="s">
+      <c r="B336" s="9" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="337" spans="1:2">
-      <c r="A337" s="30" t="s">
+      <c r="A337" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="B337" s="29" t="s">
+      <c r="B337" s="9" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="338" spans="1:2">
-      <c r="A338" s="30" t="s">
+      <c r="A338" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="B338" s="29" t="s">
+      <c r="B338" s="9" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="339" spans="1:2">
-      <c r="A339" s="30" t="s">
+      <c r="A339" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="B339" s="29" t="s">
+      <c r="B339" s="9" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="340" spans="1:2">
-      <c r="A340" s="30" t="s">
+      <c r="A340" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="B340" s="29" t="s">
+      <c r="B340" s="9" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="341" spans="1:2">
-      <c r="A341" s="30" t="s">
+      <c r="A341" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="B341" s="29" t="s">
+      <c r="B341" s="9" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="342" spans="1:2">
-      <c r="A342" s="30" t="s">
+      <c r="A342" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="B342" s="29" t="s">
+      <c r="B342" s="9" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="343" spans="1:2">
-      <c r="A343" s="2" t="s">
+      <c r="A343" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="B343" s="8" t="s">
+      <c r="B343" s="9" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="344" spans="1:2">
-      <c r="A344" s="2" t="s">
+      <c r="A344" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="B344" s="8" t="s">
+      <c r="B344" s="9" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="345" spans="1:2">
-      <c r="A345" s="2" t="s">
+      <c r="A345" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="B345" s="8" t="s">
+      <c r="B345" s="9" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="346" spans="1:2">
-      <c r="A346" s="2" t="s">
+      <c r="A346" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="B346" s="8" t="s">
+      <c r="B346" s="9" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="347" spans="1:2">
-      <c r="A347" s="2" t="s">
+      <c r="A347" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="B347" s="8" t="s">
+      <c r="B347" s="9" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="348" spans="1:2">
-      <c r="A348" s="2" t="s">
+      <c r="A348" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="B348" s="8" t="s">
+      <c r="B348" s="9" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="349" spans="1:2">
-      <c r="A349" s="2" t="s">
+      <c r="A349" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="B349" s="8" t="s">
+      <c r="B349" s="9" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="350" spans="1:2">
-      <c r="A350" s="2" t="s">
+      <c r="A350" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="B350" s="8" t="s">
+      <c r="B350" s="9" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="351" spans="1:2">
-      <c r="A351" s="2" t="s">
+      <c r="A351" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="B351" s="8" t="s">
+      <c r="B351" s="9" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="352" spans="1:2">
-      <c r="A352" s="2" t="s">
+      <c r="A352" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="B352" s="8" t="s">
+      <c r="B352" s="9" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="353" spans="1:2">
-      <c r="A353" s="2" t="s">
+      <c r="A353" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="B353" s="8" t="s">
+      <c r="B353" s="9" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="354" spans="1:2">
-      <c r="A354" s="2" t="s">
+      <c r="A354" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="B354" s="8" t="s">
+      <c r="B354" s="9" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="355" spans="1:2">
-      <c r="A355" s="2" t="s">
+      <c r="A355" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="B355" s="8" t="s">
+      <c r="B355" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="356" spans="1:2">
-      <c r="A356" s="2" t="s">
+      <c r="A356" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="B356" s="25" t="s">
+      <c r="B356" s="23" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="357" spans="1:2">
-      <c r="A357" s="2" t="s">
+      <c r="A357" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="B357" s="8" t="s">
+      <c r="B357" s="9" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="26" t="s">
+      <c r="A358" s="24" t="s">
         <v>611</v>
       </c>
-      <c r="B358" s="27" t="s">
-        <v>992</v>
+      <c r="B358" s="25" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="359" spans="1:2">
-      <c r="A359" s="26" t="s">
-        <v>612</v>
-      </c>
-      <c r="B359" s="27" t="s">
+      <c r="A359" s="24" t="s">
         <v>613</v>
       </c>
+      <c r="B359" s="25" t="s">
+        <v>614</v>
+      </c>
     </row>
     <row r="360" spans="1:2">
-      <c r="A360" s="26" t="s">
-        <v>614</v>
-      </c>
-      <c r="B360" s="25">
+      <c r="A360" s="24" t="s">
+        <v>615</v>
+      </c>
+      <c r="B360" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="361" spans="1:2">
-      <c r="A361" s="26" t="s">
-        <v>615</v>
-      </c>
-      <c r="B361" s="25">
+      <c r="A361" s="24" t="s">
+        <v>616</v>
+      </c>
+      <c r="B361" s="26">
         <v>1000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
-      <c r="A362" s="26" t="s">
-        <v>616</v>
-      </c>
-      <c r="B362" s="49">
+      <c r="A362" s="24" t="s">
+        <v>617</v>
+      </c>
+      <c r="B362" s="38">
         <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:2">
-      <c r="A363" s="26" t="s">
-        <v>617</v>
-      </c>
-      <c r="B363" s="25">
+      <c r="A363" s="24" t="s">
+        <v>618</v>
+      </c>
+      <c r="B363" s="26">
         <v>1000</v>
       </c>
     </row>
     <row r="364" spans="1:2">
-      <c r="A364" s="26" t="s">
-        <v>618</v>
-      </c>
-      <c r="B364" s="25" t="s">
+      <c r="A364" s="24" t="s">
         <v>619</v>
       </c>
+      <c r="B364" s="23" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="26" t="s">
-        <v>620</v>
-      </c>
-      <c r="B365" s="25" t="s">
+      <c r="A365" s="24" t="s">
         <v>621</v>
       </c>
+      <c r="B365" s="23" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="26" t="s">
-        <v>622</v>
-      </c>
-      <c r="B366" s="25" t="s">
+      <c r="A366" s="24" t="s">
         <v>623</v>
       </c>
+      <c r="B366" s="23" t="s">
+        <v>624</v>
+      </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" s="26" t="s">
-        <v>624</v>
-      </c>
-      <c r="B367" s="25">
+      <c r="A367" s="24" t="s">
+        <v>625</v>
+      </c>
+      <c r="B367" s="26">
         <v>10000039</v>
       </c>
     </row>
     <row r="368" spans="1:2">
-      <c r="A368" s="26" t="s">
-        <v>625</v>
-      </c>
-      <c r="B368" s="27" t="s">
+      <c r="A368" s="24" t="s">
         <v>626</v>
       </c>
+      <c r="B368" s="25" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="369" spans="1:2">
-      <c r="A369" s="26" t="s">
-        <v>627</v>
-      </c>
-      <c r="B369" s="27" t="s">
+      <c r="A369" s="24" t="s">
         <v>628</v>
       </c>
+      <c r="B369" s="25" t="s">
+        <v>629</v>
+      </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="26" t="s">
-        <v>629</v>
-      </c>
-      <c r="B370" s="8" t="s">
+      <c r="A370" s="24" t="s">
         <v>630</v>
       </c>
+      <c r="B370" s="9" t="s">
+        <v>631</v>
+      </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="26" t="s">
-        <v>631</v>
-      </c>
-      <c r="B371" s="8" t="s">
+      <c r="A371" s="24" t="s">
         <v>632</v>
       </c>
+      <c r="B371" s="9" t="s">
+        <v>633</v>
+      </c>
     </row>
     <row r="372" spans="1:2">
-      <c r="A372" s="26" t="s">
-        <v>633</v>
-      </c>
-      <c r="B372" s="8" t="s">
+      <c r="A372" s="24" t="s">
         <v>634</v>
       </c>
+      <c r="B372" s="9" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="26" t="s">
-        <v>635</v>
-      </c>
-      <c r="B373" s="8" t="s">
+      <c r="A373" s="24" t="s">
         <v>636</v>
       </c>
+      <c r="B373" s="9" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="26" t="s">
-        <v>637</v>
-      </c>
-      <c r="B374" s="8" t="s">
+      <c r="A374" s="24" t="s">
         <v>638</v>
       </c>
+      <c r="B374" s="9" t="s">
+        <v>639</v>
+      </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="26" t="s">
-        <v>639</v>
-      </c>
-      <c r="B375" s="8" t="s">
+      <c r="A375" s="24" t="s">
         <v>640</v>
       </c>
+      <c r="B375" s="9" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="26" t="s">
+      <c r="A376" s="24" t="s">
+        <v>642</v>
+      </c>
+      <c r="B376" s="9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="24" t="s">
+        <v>643</v>
+      </c>
+      <c r="B377" s="9" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="24" t="s">
+        <v>645</v>
+      </c>
+      <c r="B378" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="24" t="s">
+        <v>647</v>
+      </c>
+      <c r="B379" s="9" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="24" t="s">
+        <v>649</v>
+      </c>
+      <c r="B380" s="9" t="s">
         <v>641</v>
       </c>
-      <c r="B376" s="8" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="377" spans="1:2">
-      <c r="A377" s="26" t="s">
-        <v>642</v>
-      </c>
-      <c r="B377" s="8" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="378" spans="1:2">
-      <c r="A378" s="26" t="s">
-        <v>644</v>
-      </c>
-      <c r="B378" s="8" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="379" spans="1:2">
-      <c r="A379" s="26" t="s">
-        <v>646</v>
-      </c>
-      <c r="B379" s="8" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="380" spans="1:2">
-      <c r="A380" s="26" t="s">
-        <v>648</v>
-      </c>
-      <c r="B380" s="8" t="s">
-        <v>640</v>
-      </c>
     </row>
     <row r="381" spans="1:2">
-      <c r="A381" s="26" t="s">
-        <v>649</v>
-      </c>
-      <c r="B381" s="8" t="s">
+      <c r="A381" s="24" t="s">
         <v>650</v>
       </c>
+      <c r="B381" s="9" t="s">
+        <v>651</v>
+      </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="26" t="s">
-        <v>651</v>
-      </c>
-      <c r="B382" s="8" t="s">
+      <c r="A382" s="24" t="s">
         <v>652</v>
       </c>
+      <c r="B382" s="9" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="26" t="s">
-        <v>653</v>
-      </c>
-      <c r="B383" s="8" t="s">
+      <c r="A383" s="24" t="s">
         <v>654</v>
       </c>
+      <c r="B383" s="9" t="s">
+        <v>655</v>
+      </c>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="26" t="s">
-        <v>655</v>
-      </c>
-      <c r="B384" s="8" t="s">
+      <c r="A384" s="24" t="s">
         <v>656</v>
       </c>
+      <c r="B384" s="9" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="26" t="s">
-        <v>657</v>
-      </c>
-      <c r="B385" s="8" t="s">
+      <c r="A385" s="24" t="s">
         <v>658</v>
       </c>
+      <c r="B385" s="9" t="s">
+        <v>659</v>
+      </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="26" t="s">
-        <v>659</v>
-      </c>
-      <c r="B386" s="8" t="s">
+      <c r="A386" s="24" t="s">
         <v>660</v>
       </c>
+      <c r="B386" s="9" t="s">
+        <v>661</v>
+      </c>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="26" t="s">
-        <v>661</v>
-      </c>
-      <c r="B387" s="8" t="s">
+      <c r="A387" s="24" t="s">
         <v>662</v>
       </c>
+      <c r="B387" s="9" t="s">
+        <v>663</v>
+      </c>
     </row>
     <row r="388" spans="1:2">
-      <c r="A388" s="26" t="s">
-        <v>663</v>
-      </c>
-      <c r="B388" s="8" t="s">
+      <c r="A388" s="24" t="s">
         <v>664</v>
       </c>
+      <c r="B388" s="9" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" s="26" t="s">
-        <v>665</v>
-      </c>
-      <c r="B389" s="8" t="s">
+      <c r="A389" s="24" t="s">
         <v>666</v>
       </c>
+      <c r="B389" s="9" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="390" spans="1:2">
-      <c r="A390" s="26" t="s">
-        <v>667</v>
-      </c>
-      <c r="B390" s="8" t="s">
+      <c r="A390" s="24" t="s">
         <v>668</v>
       </c>
+      <c r="B390" s="9" t="s">
+        <v>669</v>
+      </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="26" t="s">
-        <v>669</v>
-      </c>
-      <c r="B391" s="8" t="s">
+      <c r="A391" s="24" t="s">
         <v>670</v>
       </c>
+      <c r="B391" s="9" t="s">
+        <v>671</v>
+      </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="26" t="s">
-        <v>671</v>
-      </c>
-      <c r="B392" s="8" t="s">
+      <c r="A392" s="24" t="s">
         <v>672</v>
       </c>
+      <c r="B392" s="9" t="s">
+        <v>673</v>
+      </c>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393" s="26" t="s">
-        <v>673</v>
-      </c>
-      <c r="B393" s="8" t="s">
+      <c r="A393" s="24" t="s">
         <v>674</v>
       </c>
+      <c r="B393" s="9" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="26" t="s">
-        <v>675</v>
-      </c>
-      <c r="B394" s="8" t="s">
+      <c r="A394" s="24" t="s">
         <v>676</v>
       </c>
+      <c r="B394" s="9" t="s">
+        <v>677</v>
+      </c>
     </row>
     <row r="395" spans="1:2">
-      <c r="A395" s="26" t="s">
-        <v>677</v>
-      </c>
-      <c r="B395" s="8" t="s">
+      <c r="A395" s="24" t="s">
         <v>678</v>
       </c>
+      <c r="B395" s="9" t="s">
+        <v>679</v>
+      </c>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396" s="26" t="s">
-        <v>679</v>
-      </c>
-      <c r="B396" s="8" t="s">
+      <c r="A396" s="24" t="s">
         <v>680</v>
       </c>
+      <c r="B396" s="9" t="s">
+        <v>681</v>
+      </c>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="26" t="s">
-        <v>681</v>
-      </c>
-      <c r="B397" s="8" t="s">
+      <c r="A397" s="24" t="s">
         <v>682</v>
       </c>
+      <c r="B397" s="9" t="s">
+        <v>683</v>
+      </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="26" t="s">
-        <v>683</v>
-      </c>
-      <c r="B398" s="8" t="s">
+      <c r="A398" s="24" t="s">
         <v>684</v>
       </c>
+      <c r="B398" s="9" t="s">
+        <v>685</v>
+      </c>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="26" t="s">
-        <v>685</v>
-      </c>
-      <c r="B399" s="8" t="s">
+      <c r="A399" s="24" t="s">
         <v>686</v>
       </c>
+      <c r="B399" s="9" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="26" t="s">
-        <v>687</v>
-      </c>
-      <c r="B400" s="8" t="s">
+      <c r="A400" s="24" t="s">
         <v>688</v>
       </c>
+      <c r="B400" s="9" t="s">
+        <v>689</v>
+      </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="26" t="s">
-        <v>689</v>
-      </c>
-      <c r="B401" s="8" t="s">
+      <c r="A401" s="24" t="s">
         <v>690</v>
       </c>
+      <c r="B401" s="9" t="s">
+        <v>691</v>
+      </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="26" t="s">
-        <v>691</v>
-      </c>
-      <c r="B402" s="8" t="s">
+      <c r="A402" s="24" t="s">
         <v>692</v>
       </c>
+      <c r="B402" s="9" t="s">
+        <v>693</v>
+      </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="26" t="s">
-        <v>693</v>
-      </c>
-      <c r="B403" s="8" t="s">
+      <c r="A403" s="24" t="s">
         <v>694</v>
       </c>
+      <c r="B403" s="9" t="s">
+        <v>695</v>
+      </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="26" t="s">
-        <v>695</v>
-      </c>
-      <c r="B404" s="8" t="s">
+      <c r="A404" s="24" t="s">
         <v>696</v>
       </c>
+      <c r="B404" s="9" t="s">
+        <v>697</v>
+      </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="26" t="s">
-        <v>697</v>
-      </c>
-      <c r="B405" s="8" t="s">
+      <c r="A405" s="24" t="s">
         <v>698</v>
       </c>
+      <c r="B405" s="9" t="s">
+        <v>699</v>
+      </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="26" t="s">
-        <v>699</v>
-      </c>
-      <c r="B406" s="8" t="s">
+      <c r="A406" s="24" t="s">
         <v>700</v>
       </c>
+      <c r="B406" s="9" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="26" t="s">
-        <v>701</v>
-      </c>
-      <c r="B407" s="8" t="s">
+      <c r="A407" s="24" t="s">
         <v>702</v>
       </c>
+      <c r="B407" s="9" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="26" t="s">
-        <v>703</v>
-      </c>
-      <c r="B408" s="8" t="s">
+      <c r="A408" s="24" t="s">
         <v>704</v>
       </c>
+      <c r="B408" s="9" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="409" spans="1:2">
-      <c r="A409" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="B409" s="8" t="s">
+      <c r="A409" s="8" t="s">
         <v>706</v>
       </c>
+      <c r="B409" s="9" t="s">
+        <v>707</v>
+      </c>
     </row>
     <row r="410" spans="1:2">
-      <c r="A410" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="B410" s="8" t="s">
+      <c r="A410" s="8" t="s">
         <v>708</v>
       </c>
+      <c r="B410" s="9" t="s">
+        <v>709</v>
+      </c>
     </row>
     <row r="411" spans="1:2">
-      <c r="A411" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B411" s="8" t="s">
+      <c r="A411" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="B411" s="9" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="412" spans="1:2">
-      <c r="A412" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="B412" s="8" t="s">
-        <v>710</v>
+      <c r="A412" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="B412" s="9" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="413" spans="1:2">
-      <c r="A413" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="B413" s="8" t="s">
+      <c r="A413" s="8" t="s">
         <v>712</v>
       </c>
+      <c r="B413" s="9" t="s">
+        <v>713</v>
+      </c>
     </row>
     <row r="414" spans="1:2">
-      <c r="A414" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B414" s="8" t="s">
+      <c r="A414" s="8" t="s">
         <v>714</v>
       </c>
+      <c r="B414" s="9" t="s">
+        <v>715</v>
+      </c>
     </row>
     <row r="415" spans="1:2">
-      <c r="A415" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="B415" s="8" t="s">
+      <c r="A415" s="8" t="s">
         <v>716</v>
       </c>
+      <c r="B415" s="9" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="416" spans="1:2">
-      <c r="A416" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="B416" s="8" t="s">
+      <c r="A416" s="8" t="s">
         <v>718</v>
       </c>
+      <c r="B416" s="9" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="417" spans="1:2">
-      <c r="A417" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="B417" s="8" t="s">
+      <c r="A417" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="B417" s="9" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="418" spans="1:2">
-      <c r="A418" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="B418" s="8" t="s">
+      <c r="A418" s="8" t="s">
         <v>721</v>
       </c>
+      <c r="B418" s="9" t="s">
+        <v>722</v>
+      </c>
     </row>
     <row r="419" spans="1:2">
-      <c r="A419" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="B419" s="8" t="s">
+      <c r="A419" s="8" t="s">
         <v>723</v>
       </c>
+      <c r="B419" s="9" t="s">
+        <v>724</v>
+      </c>
     </row>
     <row r="420" spans="1:2">
-      <c r="A420" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="B420" s="8" t="s">
+      <c r="A420" s="8" t="s">
         <v>725</v>
       </c>
+      <c r="B420" s="9" t="s">
+        <v>726</v>
+      </c>
     </row>
     <row r="421" spans="1:2">
-      <c r="A421" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="B421" s="8" t="s">
-        <v>726</v>
+      <c r="A421" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="B421" s="9" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="422" spans="1:2">
-      <c r="A422" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="B422" s="8" t="s">
+      <c r="A422" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="B422" s="9" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="423" spans="1:2">
-      <c r="A423" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="B423" s="8" t="s">
-        <v>728</v>
+      <c r="A423" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="B423" s="9" t="s">
+        <v>729</v>
       </c>
     </row>
     <row r="424" spans="1:2">
-      <c r="A424" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="B424" s="8" t="s">
+      <c r="A424" s="8" t="s">
         <v>730</v>
       </c>
+      <c r="B424" s="9" t="s">
+        <v>731</v>
+      </c>
     </row>
     <row r="425" spans="1:2">
-      <c r="A425" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B425" s="8" t="s">
+      <c r="A425" s="8" t="s">
         <v>732</v>
       </c>
+      <c r="B425" s="9" t="s">
+        <v>733</v>
+      </c>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="12" t="s">
-        <v>733</v>
+      <c r="A426" s="11" t="s">
+        <v>734</v>
       </c>
       <c r="B426" s="14" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="427" spans="1:2">
-      <c r="A427" s="12" t="s">
-        <v>735</v>
+      <c r="A427" s="11" t="s">
+        <v>736</v>
       </c>
       <c r="B427" s="14" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="12" t="s">
-        <v>737</v>
+      <c r="A428" s="11" t="s">
+        <v>738</v>
       </c>
       <c r="B428" s="14" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="429" spans="1:2">
-      <c r="A429" s="12" t="s">
-        <v>739</v>
+      <c r="A429" s="11" t="s">
+        <v>740</v>
       </c>
       <c r="B429" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="430" spans="1:2">
-      <c r="A430" s="12" t="s">
-        <v>741</v>
+      <c r="A430" s="11" t="s">
+        <v>742</v>
       </c>
       <c r="B430" s="14" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="12" t="s">
-        <v>743</v>
+      <c r="A431" s="11" t="s">
+        <v>744</v>
       </c>
       <c r="B431" s="14" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="432" spans="1:2">
-      <c r="A432" s="12" t="s">
-        <v>745</v>
+      <c r="A432" s="11" t="s">
+        <v>746</v>
       </c>
       <c r="B432" s="14" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="433" spans="1:2">
-      <c r="A433" s="12" t="s">
-        <v>747</v>
+      <c r="A433" s="11" t="s">
+        <v>748</v>
       </c>
       <c r="B433" s="14" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="434" spans="1:2">
-      <c r="A434" s="12" t="s">
-        <v>749</v>
+      <c r="A434" s="11" t="s">
+        <v>750</v>
       </c>
       <c r="B434" s="14" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="435" spans="1:2">
-      <c r="A435" s="12" t="s">
-        <v>751</v>
+      <c r="A435" s="11" t="s">
+        <v>752</v>
       </c>
       <c r="B435" s="14" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="436" spans="1:2">
-      <c r="A436" s="12" t="s">
-        <v>753</v>
+      <c r="A436" s="11" t="s">
+        <v>754</v>
       </c>
       <c r="B436" s="14" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="437" spans="1:2">
-      <c r="A437" s="12" t="s">
-        <v>755</v>
+      <c r="A437" s="11" t="s">
+        <v>756</v>
       </c>
       <c r="B437" s="14" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="438" spans="1:2">
-      <c r="A438" s="12" t="s">
+      <c r="A438" s="11" t="s">
+        <v>758</v>
+      </c>
+      <c r="B438" s="14" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="11" t="s">
+        <v>760</v>
+      </c>
+      <c r="B439" s="14" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B440" s="9" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="16" t="s">
+        <v>764</v>
+      </c>
+      <c r="B441" s="17" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="16" t="s">
+        <v>765</v>
+      </c>
+      <c r="B442" s="17" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="16" t="s">
+        <v>767</v>
+      </c>
+      <c r="B443" s="17" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="16" t="s">
+        <v>769</v>
+      </c>
+      <c r="B444" s="17" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="16" t="s">
+        <v>770</v>
+      </c>
+      <c r="B445" s="17" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="16" t="s">
+        <v>771</v>
+      </c>
+      <c r="B446" s="33" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="16" t="s">
+        <v>773</v>
+      </c>
+      <c r="B447" s="33" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="16" t="s">
+        <v>775</v>
+      </c>
+      <c r="B448" s="17" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="16" t="s">
+        <v>777</v>
+      </c>
+      <c r="B449" s="17" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="B450" s="33" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="B451" s="33" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B452" s="40" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="39" t="s">
+        <v>779</v>
+      </c>
+      <c r="B453" s="40" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="16" t="s">
+        <v>781</v>
+      </c>
+      <c r="B454" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="16" t="s">
+        <v>782</v>
+      </c>
+      <c r="B455" s="41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="B456" s="33" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="16" t="s">
+        <v>783</v>
+      </c>
+      <c r="B457" s="33" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="B458" s="33" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="16" t="s">
+        <v>786</v>
+      </c>
+      <c r="B459" s="17" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="16" t="s">
+        <v>788</v>
+      </c>
+      <c r="B460" s="17" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="16" t="s">
+        <v>790</v>
+      </c>
+      <c r="B461" s="17" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="42" t="s">
+        <v>359</v>
+      </c>
+      <c r="B462" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="42" t="s">
+        <v>360</v>
+      </c>
+      <c r="B463" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="42" t="s">
+        <v>361</v>
+      </c>
+      <c r="B464" s="43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="44" t="s">
+        <v>354</v>
+      </c>
+      <c r="B465" s="45">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="44" t="s">
+        <v>355</v>
+      </c>
+      <c r="B466" s="45">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="B467" s="9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="B468" s="9" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="B469" s="9" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="B470" s="9" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="B471" s="9" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="B472" s="9" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="B473" s="9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="B474" s="9" t="s">
         <v>757</v>
       </c>
-      <c r="B438" s="14" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="439" spans="1:2">
-      <c r="A439" s="12" t="s">
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="B475" s="9" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="8" t="s">
         <v>759</v>
       </c>
-      <c r="B439" s="14" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="440" spans="1:2">
-      <c r="A440" s="30" t="s">
-        <v>761</v>
-      </c>
-      <c r="B440" s="29" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="441" spans="1:2">
-      <c r="A441" s="50" t="s">
-        <v>763</v>
-      </c>
-      <c r="B441" s="51" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="442" spans="1:2">
-      <c r="A442" s="50" t="s">
-        <v>764</v>
-      </c>
-      <c r="B442" s="51" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="443" spans="1:2">
-      <c r="A443" s="50" t="s">
-        <v>766</v>
-      </c>
-      <c r="B443" s="51" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="444" spans="1:2">
-      <c r="A444" s="50" t="s">
-        <v>768</v>
-      </c>
-      <c r="B444" s="51" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="445" spans="1:2">
-      <c r="A445" s="50" t="s">
-        <v>769</v>
-      </c>
-      <c r="B445" s="51" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="446" spans="1:2">
-      <c r="A446" s="50" t="s">
-        <v>770</v>
-      </c>
-      <c r="B446" s="52" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="447" spans="1:2">
-      <c r="A447" s="50" t="s">
-        <v>772</v>
-      </c>
-      <c r="B447" s="52" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="448" spans="1:2">
-      <c r="A448" s="50" t="s">
-        <v>774</v>
-      </c>
-      <c r="B448" s="51" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="449" spans="1:2">
-      <c r="A449" s="50" t="s">
-        <v>776</v>
-      </c>
-      <c r="B449" s="51" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="450" spans="1:2">
-      <c r="A450" s="50" t="s">
-        <v>564</v>
-      </c>
-      <c r="B450" s="52" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="451" spans="1:2">
-      <c r="A451" s="50" t="s">
-        <v>561</v>
-      </c>
-      <c r="B451" s="52" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="452" spans="1:2">
-      <c r="A452" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="B452" s="54" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="453" spans="1:2">
-      <c r="A453" s="53" t="s">
-        <v>778</v>
-      </c>
-      <c r="B453" s="54" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="454" spans="1:2">
-      <c r="A454" s="50" t="s">
-        <v>780</v>
-      </c>
-      <c r="B454" s="55" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="455" spans="1:2">
-      <c r="A455" s="50" t="s">
-        <v>781</v>
-      </c>
-      <c r="B455" s="55" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="456" spans="1:2">
-      <c r="A456" s="50" t="s">
-        <v>371</v>
-      </c>
-      <c r="B456" s="52" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="457" spans="1:2">
-      <c r="A457" s="50" t="s">
-        <v>782</v>
-      </c>
-      <c r="B457" s="52" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="458" spans="1:2">
-      <c r="A458" s="50" t="s">
-        <v>783</v>
-      </c>
-      <c r="B458" s="52" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="459" spans="1:2">
-      <c r="A459" s="50" t="s">
-        <v>785</v>
-      </c>
-      <c r="B459" s="51" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="460" spans="1:2">
-      <c r="A460" s="50" t="s">
-        <v>787</v>
-      </c>
-      <c r="B460" s="51" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="461" spans="1:2">
-      <c r="A461" s="50" t="s">
-        <v>789</v>
-      </c>
-      <c r="B461" s="51" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="462" spans="1:2">
-      <c r="A462" s="56" t="s">
-        <v>359</v>
-      </c>
-      <c r="B462" s="56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="463" spans="1:2">
-      <c r="A463" s="56" t="s">
-        <v>360</v>
-      </c>
-      <c r="B463" s="56">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="464" spans="1:2">
-      <c r="A464" s="56" t="s">
-        <v>361</v>
-      </c>
-      <c r="B464" s="56">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="465" spans="1:2">
-      <c r="A465" s="57" t="s">
-        <v>354</v>
-      </c>
-      <c r="B465" s="57">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="466" spans="1:2">
-      <c r="A466" s="57" t="s">
-        <v>355</v>
-      </c>
-      <c r="B466" s="57">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="467" spans="1:2">
-      <c r="A467" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="B467" s="8" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="468" spans="1:2">
-      <c r="A468" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="B468" s="8" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="469" spans="1:2">
-      <c r="A469" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="B469" s="8" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="470" spans="1:2">
-      <c r="A470" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="B470" s="8" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="471" spans="1:2">
-      <c r="A471" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="B471" s="8" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="472" spans="1:2">
-      <c r="A472" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="B472" s="8" t="s">
+      <c r="B476" s="9" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="B477" s="9" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="B478" s="9" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B479" s="36" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="B480" s="9" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="B481" s="9" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="B482" s="9" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="473" spans="1:2">
-      <c r="A473" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="B473" s="8" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="474" spans="1:2">
-      <c r="A474" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="B474" s="8" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="475" spans="1:2">
-      <c r="A475" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="B475" s="8" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="476" spans="1:2">
-      <c r="A476" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="B476" s="8" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="477" spans="1:2">
-      <c r="A477" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="B477" s="8" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="478" spans="1:2">
-      <c r="A478" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="B478" s="8" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="479" spans="1:2">
-      <c r="A479" s="2" t="s">
+    <row r="483" spans="1:2">
+      <c r="A483" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="B483" s="9" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="B484" s="9" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="B485" s="9" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="B486" s="9" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="B487" s="9" t="s">
         <v>808</v>
       </c>
-      <c r="B479" s="45" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="480" spans="1:2">
-      <c r="A480" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="B480" s="8" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="481" spans="1:2">
-      <c r="A481" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="B481" s="8" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="482" spans="1:2">
-      <c r="A482" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="B482" s="8" t="s">
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="8" t="s">
+        <v>824</v>
+      </c>
+      <c r="B488" s="9" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="483" spans="1:2">
-      <c r="A483" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="B483" s="8" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="484" spans="1:2">
-      <c r="A484" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="B484" s="8" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="485" spans="1:2">
-      <c r="A485" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="B485" s="8" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="486" spans="1:2">
-      <c r="A486" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="B486" s="8" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="487" spans="1:2">
-      <c r="A487" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="B487" s="8" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="488" spans="1:2">
-      <c r="A488" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="B488" s="8" t="s">
-        <v>229</v>
-      </c>
-    </row>
     <row r="489" spans="1:2">
-      <c r="A489" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="B489" s="8" t="s">
+      <c r="A489" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="B489" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="490" spans="1:2">
-      <c r="A490" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="B490" s="8" t="s">
+      <c r="A490" s="8" t="s">
         <v>826</v>
       </c>
+      <c r="B490" s="9" t="s">
+        <v>827</v>
+      </c>
     </row>
     <row r="491" spans="1:2">
-      <c r="A491" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="B491" s="8" t="s">
+      <c r="A491" s="8" t="s">
         <v>828</v>
       </c>
+      <c r="B491" s="9" t="s">
+        <v>829</v>
+      </c>
     </row>
     <row r="492" spans="1:2">
-      <c r="A492" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="B492" s="8" t="s">
+      <c r="A492" s="8" t="s">
         <v>830</v>
       </c>
+      <c r="B492" s="9" t="s">
+        <v>831</v>
+      </c>
     </row>
     <row r="493" spans="1:2">
-      <c r="A493" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="B493" s="8" t="s">
+      <c r="A493" s="8" t="s">
         <v>832</v>
       </c>
+      <c r="B493" s="9" t="s">
+        <v>833</v>
+      </c>
     </row>
     <row r="494" spans="1:2">
-      <c r="A494" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="B494" s="8" t="s">
+      <c r="A494" s="8" t="s">
         <v>834</v>
       </c>
+      <c r="B494" s="9" t="s">
+        <v>835</v>
+      </c>
     </row>
     <row r="495" spans="1:2">
-      <c r="A495" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="B495" s="8" t="s">
+      <c r="A495" s="8" t="s">
         <v>836</v>
       </c>
+      <c r="B495" s="9" t="s">
+        <v>837</v>
+      </c>
     </row>
     <row r="496" spans="1:2">
-      <c r="A496" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="B496" s="8" t="s">
+      <c r="A496" s="8" t="s">
         <v>838</v>
       </c>
+      <c r="B496" s="9" t="s">
+        <v>839</v>
+      </c>
     </row>
     <row r="497" spans="1:2">
-      <c r="A497" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="B497" s="8" t="s">
+      <c r="A497" s="8" t="s">
         <v>840</v>
       </c>
+      <c r="B497" s="9" t="s">
+        <v>841</v>
+      </c>
     </row>
     <row r="498" spans="1:2">
-      <c r="A498" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="B498" s="8" t="s">
+      <c r="A498" s="8" t="s">
         <v>842</v>
       </c>
+      <c r="B498" s="9" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="499" spans="1:2">
-      <c r="A499" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="B499" s="8" t="s">
+      <c r="A499" s="8" t="s">
         <v>844</v>
       </c>
+      <c r="B499" s="9" t="s">
+        <v>845</v>
+      </c>
     </row>
     <row r="500" spans="1:2">
-      <c r="A500" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="B500" s="8" t="s">
+      <c r="A500" s="8" t="s">
         <v>846</v>
       </c>
+      <c r="B500" s="9" t="s">
+        <v>847</v>
+      </c>
     </row>
     <row r="501" spans="1:2">
-      <c r="A501" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="B501" s="8" t="s">
+      <c r="A501" s="8" t="s">
         <v>848</v>
       </c>
+      <c r="B501" s="9" t="s">
+        <v>849</v>
+      </c>
     </row>
     <row r="502" spans="1:2">
-      <c r="A502" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="B502" s="8" t="s">
+      <c r="A502" s="8" t="s">
         <v>850</v>
       </c>
+      <c r="B502" s="9" t="s">
+        <v>851</v>
+      </c>
     </row>
     <row r="503" spans="1:2">
-      <c r="A503" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B503" s="8" t="s">
+      <c r="A503" s="8" t="s">
         <v>852</v>
       </c>
+      <c r="B503" s="9" t="s">
+        <v>853</v>
+      </c>
     </row>
     <row r="504" spans="1:2">
-      <c r="A504" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="B504" s="8" t="s">
+      <c r="A504" s="8" t="s">
         <v>854</v>
       </c>
+      <c r="B504" s="9" t="s">
+        <v>855</v>
+      </c>
     </row>
     <row r="505" spans="1:2">
-      <c r="A505" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="B505" s="8" t="s">
+      <c r="A505" s="8" t="s">
         <v>856</v>
       </c>
+      <c r="B505" s="9" t="s">
+        <v>857</v>
+      </c>
     </row>
     <row r="506" spans="1:2">
-      <c r="A506" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="B506" s="8" t="s">
+      <c r="A506" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="B506" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="507" spans="1:2">
-      <c r="A507" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="B507" s="8" t="s">
+      <c r="A507" s="8" t="s">
         <v>859</v>
       </c>
+      <c r="B507" s="9" t="s">
+        <v>860</v>
+      </c>
     </row>
     <row r="508" spans="1:2">
-      <c r="A508" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="B508" s="8" t="s">
+      <c r="A508" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B508" s="9" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="509" spans="1:2">
-      <c r="A509" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="B509" s="8" t="s">
+      <c r="A509" s="8" t="s">
         <v>862</v>
       </c>
+      <c r="B509" s="9" t="s">
+        <v>863</v>
+      </c>
     </row>
     <row r="510" spans="1:2">
-      <c r="A510" s="2" t="s">
-        <v>863</v>
-      </c>
-      <c r="B510" s="8" t="s">
+      <c r="A510" s="8" t="s">
         <v>864</v>
       </c>
+      <c r="B510" s="9" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="511" spans="1:2">
-      <c r="A511" s="2" t="s">
+      <c r="A511" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="B511" s="2" t="s">
+      <c r="B511" s="8" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="512" spans="1:2">
-      <c r="A512" s="26" t="s">
+      <c r="A512" s="24" t="s">
+        <v>866</v>
+      </c>
+      <c r="B512" s="9" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="B513" s="9" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="24" t="s">
+        <v>870</v>
+      </c>
+      <c r="B514" s="9" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="24" t="s">
+        <v>872</v>
+      </c>
+      <c r="B515" s="9" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="24" t="s">
+        <v>874</v>
+      </c>
+      <c r="B516" s="9" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" s="24" t="s">
+        <v>876</v>
+      </c>
+      <c r="B517" s="9" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="24" t="s">
+        <v>878</v>
+      </c>
+      <c r="B518" s="9" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="24" t="s">
+        <v>880</v>
+      </c>
+      <c r="B519" s="9" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="B520" s="9" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="24" t="s">
+        <v>884</v>
+      </c>
+      <c r="B521" s="9" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="24" t="s">
+        <v>886</v>
+      </c>
+      <c r="B522" s="9" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="24" t="s">
+        <v>888</v>
+      </c>
+      <c r="B523" s="9" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="24" t="s">
+        <v>890</v>
+      </c>
+      <c r="B524" s="9" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="24" t="s">
+        <v>892</v>
+      </c>
+      <c r="B525" s="9" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" s="24" t="s">
         <v>894</v>
       </c>
-      <c r="B512" s="8" t="s">
+      <c r="B526" s="9" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="513" spans="1:2">
-      <c r="A513" s="26" t="s">
+    <row r="527" spans="1:2">
+      <c r="A527" s="24" t="s">
         <v>896</v>
       </c>
-      <c r="B513" s="8" t="s">
+      <c r="B527" s="9" t="s">
         <v>897</v>
       </c>
     </row>
-    <row r="514" spans="1:2">
-      <c r="A514" s="26" t="s">
+    <row r="528" spans="1:2">
+      <c r="A528" s="24" t="s">
         <v>898</v>
       </c>
-      <c r="B514" s="8" t="s">
+      <c r="B528" s="9" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="515" spans="1:2">
-      <c r="A515" s="26" t="s">
+    <row r="529" spans="1:2">
+      <c r="A529" s="24" t="s">
         <v>900</v>
       </c>
-      <c r="B515" s="8" t="s">
+      <c r="B529" s="9" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="516" spans="1:2">
-      <c r="A516" s="26" t="s">
+    <row r="530" spans="1:2">
+      <c r="A530" s="24" t="s">
         <v>902</v>
       </c>
-      <c r="B516" s="8" t="s">
+      <c r="B530" s="9" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="517" spans="1:2">
-      <c r="A517" s="26" t="s">
+    <row r="531" spans="1:2">
+      <c r="A531" s="24" t="s">
         <v>904</v>
       </c>
-      <c r="B517" s="8" t="s">
+      <c r="B531" s="9" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="518" spans="1:2">
-      <c r="A518" s="26" t="s">
+    <row r="532" spans="1:2">
+      <c r="A532" s="24" t="s">
         <v>906</v>
       </c>
-      <c r="B518" s="8" t="s">
+      <c r="B532" s="9" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="519" spans="1:2">
-      <c r="A519" s="26" t="s">
+    <row r="533" spans="1:2">
+      <c r="A533" s="24" t="s">
         <v>908</v>
       </c>
-      <c r="B519" s="8" t="s">
+      <c r="B533" s="9" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="520" spans="1:2">
-      <c r="A520" s="26" t="s">
+    <row r="534" spans="1:2">
+      <c r="A534" s="24" t="s">
         <v>910</v>
       </c>
-      <c r="B520" s="8" t="s">
+      <c r="B534" s="9" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="521" spans="1:2">
-      <c r="A521" s="26" t="s">
+    <row r="535" spans="1:2">
+      <c r="A535" s="24" t="s">
         <v>912</v>
       </c>
-      <c r="B521" s="8" t="s">
+      <c r="B535" s="9" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="522" spans="1:2">
-      <c r="A522" s="26" t="s">
+    <row r="536" spans="1:2">
+      <c r="A536" s="24" t="s">
         <v>914</v>
       </c>
-      <c r="B522" s="8" t="s">
+      <c r="B536" s="9" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="523" spans="1:2">
-      <c r="A523" s="26" t="s">
+    <row r="537" spans="1:2">
+      <c r="A537" s="24" t="s">
         <v>916</v>
       </c>
-      <c r="B523" s="8" t="s">
+      <c r="B537" s="9" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="524" spans="1:2">
-      <c r="A524" s="26" t="s">
+    <row r="538" spans="1:2">
+      <c r="A538" s="24" t="s">
         <v>918</v>
       </c>
-      <c r="B524" s="8" t="s">
+      <c r="B538" s="9" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="525" spans="1:2">
-      <c r="A525" s="26" t="s">
+    <row r="539" spans="1:2">
+      <c r="A539" s="24" t="s">
         <v>920</v>
       </c>
-      <c r="B525" s="8" t="s">
+      <c r="B539" s="9" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="526" spans="1:2">
-      <c r="A526" s="26" t="s">
+    <row r="540" spans="1:2">
+      <c r="A540" s="24" t="s">
         <v>922</v>
       </c>
-      <c r="B526" s="8" t="s">
+      <c r="B540" s="9" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="527" spans="1:2">
-      <c r="A527" s="26" t="s">
+    <row r="541" spans="1:2">
+      <c r="A541" s="24" t="s">
         <v>924</v>
       </c>
-      <c r="B527" s="8" t="s">
+      <c r="B541" s="9" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="528" spans="1:2">
-      <c r="A528" s="26" t="s">
+    <row r="542" spans="1:2">
+      <c r="A542" s="24" t="s">
         <v>926</v>
       </c>
-      <c r="B528" s="8" t="s">
+      <c r="B542" s="9" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="529" spans="1:2">
-      <c r="A529" s="26" t="s">
+    <row r="543" spans="1:2">
+      <c r="A543" s="24" t="s">
         <v>928</v>
       </c>
-      <c r="B529" s="8" t="s">
+      <c r="B543" s="9" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="530" spans="1:2">
-      <c r="A530" s="26" t="s">
+    <row r="544" spans="1:2">
+      <c r="A544" s="46" t="s">
         <v>930</v>
       </c>
-      <c r="B530" s="8" t="s">
+      <c r="B544" s="9" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="531" spans="1:2">
-      <c r="A531" s="26" t="s">
+    <row r="545" spans="1:2">
+      <c r="A545" s="24" t="s">
         <v>932</v>
       </c>
-      <c r="B531" s="8" t="s">
+      <c r="B545" s="9" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="532" spans="1:2">
-      <c r="A532" s="26" t="s">
+    <row r="546" spans="1:2">
+      <c r="A546" s="47" t="s">
         <v>934</v>
       </c>
-      <c r="B532" s="8" t="s">
+      <c r="B546" s="9" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="533" spans="1:2">
-      <c r="A533" s="26" t="s">
+    <row r="547" spans="1:2">
+      <c r="A547" s="47" t="s">
         <v>936</v>
       </c>
-      <c r="B533" s="8" t="s">
+      <c r="B547" s="9" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="534" spans="1:2">
-      <c r="A534" s="26" t="s">
+    <row r="548" spans="1:2">
+      <c r="A548" s="47" t="s">
         <v>938</v>
       </c>
-      <c r="B534" s="8" t="s">
+      <c r="B548" s="9" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="535" spans="1:2">
-      <c r="A535" s="26" t="s">
+    <row r="549" spans="1:2">
+      <c r="A549" s="48" t="s">
         <v>940</v>
       </c>
-      <c r="B535" s="8" t="s">
+      <c r="B549" s="9" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="536" spans="1:2">
-      <c r="A536" s="26" t="s">
+    <row r="550" spans="1:2">
+      <c r="A550" s="48" t="s">
         <v>942</v>
       </c>
-      <c r="B536" s="8" t="s">
+      <c r="B550" s="9" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="537" spans="1:2">
-      <c r="A537" s="26" t="s">
+    <row r="551" spans="1:2">
+      <c r="A551" s="47" t="s">
         <v>944</v>
       </c>
-      <c r="B537" s="8" t="s">
+      <c r="B551" s="49" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" s="48" t="s">
         <v>945</v>
       </c>
-    </row>
-    <row r="538" spans="1:2">
-      <c r="A538" s="26" t="s">
+      <c r="B552" s="9" t="s">
         <v>946</v>
       </c>
-      <c r="B538" s="8" t="s">
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" s="48" t="s">
         <v>947</v>
       </c>
-    </row>
-    <row r="539" spans="1:2">
-      <c r="A539" s="26" t="s">
+      <c r="B553" s="9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="47" t="s">
         <v>948</v>
       </c>
-      <c r="B539" s="8" t="s">
+      <c r="B554" s="9" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="540" spans="1:2">
-      <c r="A540" s="26" t="s">
+    <row r="555" spans="1:2">
+      <c r="A555" s="24" t="s">
         <v>950</v>
       </c>
-      <c r="B540" s="8" t="s">
+      <c r="B555" s="9" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="541" spans="1:2">
-      <c r="A541" s="26" t="s">
+    <row r="556" spans="1:2">
+      <c r="A556" s="24" t="s">
         <v>952</v>
       </c>
-      <c r="B541" s="8" t="s">
+      <c r="B556" s="9" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="48" t="s">
         <v>953</v>
       </c>
-    </row>
-    <row r="542" spans="1:2">
-      <c r="A542" s="26" t="s">
+      <c r="B557" s="9" t="s">
         <v>954</v>
       </c>
-      <c r="B542" s="8" t="s">
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="24" t="s">
         <v>955</v>
       </c>
-    </row>
-    <row r="543" spans="1:2">
-      <c r="A543" s="26" t="s">
+      <c r="B558" s="9" t="s">
         <v>956</v>
       </c>
-      <c r="B543" s="8" t="s">
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="24" t="s">
         <v>957</v>
       </c>
-    </row>
-    <row r="544" spans="1:2">
-      <c r="A544" t="s">
+      <c r="B559" s="9" t="s">
         <v>958</v>
       </c>
-      <c r="B544" s="8" t="s">
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="24" t="s">
         <v>959</v>
       </c>
-    </row>
-    <row r="545" spans="1:2">
-      <c r="A545" s="26" t="s">
+      <c r="B560" s="9" t="s">
         <v>960</v>
       </c>
-      <c r="B545" s="8" t="s">
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="24" t="s">
         <v>961</v>
       </c>
-    </row>
-    <row r="546" spans="1:2">
-      <c r="A546" s="58" t="s">
+      <c r="B561" s="9" t="s">
         <v>962</v>
       </c>
-      <c r="B546" s="8" t="s">
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="24" t="s">
         <v>963</v>
       </c>
-    </row>
-    <row r="547" spans="1:2">
-      <c r="A547" s="58" t="s">
+      <c r="B562" s="9" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="8" t="s">
         <v>964</v>
       </c>
-      <c r="B547" s="8" t="s">
+      <c r="B563" s="9" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="548" spans="1:2">
-      <c r="A548" s="58" t="s">
+    <row r="564" spans="1:2">
+      <c r="A564" s="8" t="s">
         <v>966</v>
       </c>
-      <c r="B548" s="8" t="s">
+      <c r="B564" s="9" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="549" spans="1:2">
-      <c r="A549" s="59" t="s">
+    <row r="565" spans="1:2">
+      <c r="A565" s="8" t="s">
         <v>968</v>
       </c>
-      <c r="B549" s="8" t="s">
+      <c r="B565" s="9" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" s="50" t="s">
         <v>969</v>
       </c>
-    </row>
-    <row r="550" spans="1:2">
-      <c r="A550" s="59" t="s">
+      <c r="B566" s="51" t="s">
         <v>970</v>
       </c>
-      <c r="B550" s="8" t="s">
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" s="50" t="s">
         <v>971</v>
       </c>
-    </row>
-    <row r="551" spans="1:2">
-      <c r="A551" s="58" t="s">
+      <c r="B567" s="51" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" s="50" t="s">
         <v>972</v>
       </c>
-      <c r="B551" s="60" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="552" spans="1:2">
-      <c r="A552" s="59" t="s">
-        <v>973</v>
-      </c>
-      <c r="B552" s="8" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="553" spans="1:2">
-      <c r="A553" s="59" t="s">
-        <v>975</v>
-      </c>
-      <c r="B553" s="8" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="554" spans="1:2">
-      <c r="A554" s="58" t="s">
-        <v>976</v>
-      </c>
-      <c r="B554" s="8" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="555" spans="1:2">
-      <c r="A555" s="26" t="s">
-        <v>978</v>
-      </c>
-      <c r="B555" s="8" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="556" spans="1:2">
-      <c r="A556" s="26" t="s">
-        <v>980</v>
-      </c>
-      <c r="B556" s="8" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="557" spans="1:2">
-      <c r="A557" s="59" t="s">
-        <v>981</v>
-      </c>
-      <c r="B557" s="8" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="558" spans="1:2">
-      <c r="A558" s="26" t="s">
-        <v>983</v>
-      </c>
-      <c r="B558" s="8" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="559" spans="1:2">
-      <c r="A559" s="26" t="s">
-        <v>985</v>
-      </c>
-      <c r="B559" s="8" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="560" spans="1:2">
-      <c r="A560" s="26" t="s">
-        <v>987</v>
-      </c>
-      <c r="B560" s="8" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="561" spans="1:2">
-      <c r="A561" s="26" t="s">
-        <v>989</v>
-      </c>
-      <c r="B561" s="8" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="562" spans="1:2">
-      <c r="A562" s="26" t="s">
-        <v>991</v>
-      </c>
-      <c r="B562" s="8" t="s">
-        <v>551</v>
+      <c r="B568" s="51" t="s">
+        <v>972</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.8518518518519" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8524,124 +9184,124 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="108.95" customHeight="1">
+    <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>865</v>
+        <v>973</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="114" customHeight="1">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>867</v>
+        <v>975</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="80.25" customHeight="1">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="B4" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="5" ht="69.75" customHeight="1" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="6" ht="51.75" customHeight="1" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="9" ht="39" customHeight="1" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="12" ht="26.25" customHeight="1" spans="1:2">
+      <c r="A12" s="2" t="s">
         <v>993</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="69.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="51.75" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="39" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="18" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>880</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="26.25" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="28.5" customHeight="1">
+      <c r="B12" s="3" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="13" ht="28.5" customHeight="1" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="24" customHeight="1">
+        <v>995</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="36" customHeight="1">
+        <v>997</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="45" customHeight="1">
+        <v>999</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>893</v>
+        <v>1001</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1002</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -8654,5 +9314,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
     <sheet name="DBData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="1005">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -3474,18 +3474,18 @@
   where   PS_BU =  'TVSA'
     and   PS_FG_PROD_ID  = '${SONO}'</t>
   </si>
+  <si>
+    <t>ReturnUser</t>
+  </si>
+  <si>
+    <t>THILAK  R</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3532,151 +3532,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3701,194 +3564,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3924,255 +3601,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="53">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -4209,21 +3644,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4246,11 +3681,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4264,17 +3699,17 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4286,61 +3721,14 @@
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="53">
+  <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal 2" xfId="49"/>
-    <cellStyle name="Normal 2 2" xfId="50"/>
-    <cellStyle name="Normal 2 3" xfId="51"/>
-    <cellStyle name="Normal 3" xfId="52"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2 2" xfId="2"/>
+    <cellStyle name="Normal 2 3" xfId="3"/>
+    <cellStyle name="Normal 3" xfId="4"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4602,17 +3990,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B568"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B569"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="62.7777777777778" style="4" customWidth="1"/>
-    <col min="2" max="2" width="59.8518518518519" style="5" customWidth="1"/>
+    <col min="1" max="1" width="62.7109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="59.85546875" style="5" customWidth="1"/>
     <col min="3" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -9160,19 +8548,25 @@
         <v>972</v>
       </c>
     </row>
+    <row r="569" spans="1:2">
+      <c r="A569" s="50" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B569" s="51" t="s">
+        <v>1004</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.8518518518519" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9184,7 +8578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="108.95" customHeight="1" spans="1:2">
+    <row r="2" spans="1:2" ht="108.95" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>973</v>
       </c>
@@ -9192,7 +8586,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="3" ht="114" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="114" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>975</v>
       </c>
@@ -9200,7 +8594,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="4" ht="80.25" customHeight="1" spans="1:2">
+    <row r="4" spans="1:2" ht="80.25" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>977</v>
       </c>
@@ -9208,7 +8602,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="5" ht="69.75" customHeight="1" spans="1:2">
+    <row r="5" spans="1:2" ht="69.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>979</v>
       </c>
@@ -9216,7 +8610,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="6" ht="51.75" customHeight="1" spans="1:2">
+    <row r="6" spans="1:2" ht="51.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>981</v>
       </c>
@@ -9224,7 +8618,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:2">
+    <row r="7" spans="1:2" ht="30" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>983</v>
       </c>
@@ -9232,7 +8626,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" spans="1:2">
+    <row r="8" spans="1:2" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>985</v>
       </c>
@@ -9240,7 +8634,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="9" ht="39" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2" ht="39" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>987</v>
       </c>
@@ -9248,7 +8642,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1" spans="1:2">
+    <row r="10" spans="1:2" ht="22.5" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>989</v>
       </c>
@@ -9256,7 +8650,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:2">
+    <row r="11" spans="1:2" ht="18" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>991</v>
       </c>
@@ -9264,7 +8658,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="12" ht="26.25" customHeight="1" spans="1:2">
+    <row r="12" spans="1:2" ht="26.25" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>993</v>
       </c>
@@ -9272,7 +8666,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="13" ht="28.5" customHeight="1" spans="1:2">
+    <row r="13" spans="1:2" ht="28.5" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>995</v>
       </c>
@@ -9280,7 +8674,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:2">
+    <row r="14" spans="1:2" ht="24" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>997</v>
       </c>
@@ -9288,7 +8682,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1" spans="1:2">
+    <row r="15" spans="1:2" ht="36" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>999</v>
       </c>
@@ -9296,7 +8690,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" ht="45" customHeight="1" spans="1:2">
+    <row r="16" spans="1:2" ht="45" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>1001</v>
       </c>
@@ -9314,6 +8708,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
     <sheet name="DBData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="1005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="1037">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -2947,6 +2947,90 @@
   </si>
   <si>
     <t>POAServiceSheet</t>
+  </si>
+  <si>
+    <t>ReturnUser</t>
+  </si>
+  <si>
+    <t>THILAK  R</t>
+  </si>
+  <si>
+    <t>POID</t>
+  </si>
+  <si>
+    <t>${POID}</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>POL_TRD_DISC_AMT</t>
+  </si>
+  <si>
+    <t>POL_SPL_DISC_AMT</t>
+  </si>
+  <si>
+    <t>POL_CASH_DISC_AMT</t>
+  </si>
+  <si>
+    <t>POL_TRD_ASSBL_VAL</t>
+  </si>
+  <si>
+    <t>POL_SPL_ASSBL_VAL</t>
+  </si>
+  <si>
+    <t>POL_CASH_ASSBL_VAL</t>
+  </si>
+  <si>
+    <t>POL_TAX_PCT</t>
+  </si>
+  <si>
+    <t>POL_CGST_AMT</t>
+  </si>
+  <si>
+    <t>POL_UTGST_AMT</t>
+  </si>
+  <si>
+    <t>LINE_AMT</t>
+  </si>
+  <si>
+    <t>POL_ORDERED_QTY</t>
+  </si>
+  <si>
+    <t>ItemId</t>
+  </si>
+  <si>
+    <t>${ItemId}</t>
+  </si>
+  <si>
+    <t>Line_Amount</t>
+  </si>
+  <si>
+    <t>line_amount</t>
+  </si>
+  <si>
+    <t>PurchaseOrderGrn</t>
+  </si>
+  <si>
+    <t>Purchase Order &amp; GRN</t>
+  </si>
+  <si>
+    <t>PurchaseOrderAmendment</t>
+  </si>
+  <si>
+    <t>Purchase Order Amendment</t>
+  </si>
+  <si>
+    <t>POANO</t>
+  </si>
+  <si>
+    <t>${POANO}</t>
+  </si>
+  <si>
+    <t>FinalPO</t>
+  </si>
+  <si>
+    <t>Final Purchase Order &amp; GRN</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -3475,17 +3559,282 @@
     and   PS_FG_PROD_ID  = '${SONO}'</t>
   </si>
   <si>
-    <t>ReturnUser</t>
-  </si>
-  <si>
-    <t>THILAK  R</t>
+    <t>POQuery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  SELECT pol_order_no,
+                       pol_trd_disc_amt,
+                      pol_spl_disc_amt,
+                      pol_cash_disc_amt,
+                      pol_trd_assbl_val,
+                      pol_spl_assbl_val,
+                      pol_cash_assbl_val,
+                      pol_tax_pct,
+                      pol_cgst_amt,
+                      pol_utgst_amt,
+                      pol_cess_amt,
+                      pol_cess_pct,
+                      pol_gst_exempt_flag,
+                      pol_gst_input_type,
+                      pol_pur_acct,
+                      pol_cc_code,
+                      pol_cost_basis,
+                      pol_ordered_qty,
+                      pol_proc_qty,
+                      pol_received_qty,
+                      pol_cls_qty,
+                     ((pol_ordered_qty * pol_sc_unit_cost) - pol_disc_amt) Line_amt
+              FROM pur_order_ln
+           WHERE pol_bu ='TVSA'
+               AND pol_order_no ='${PONO}'
+               and pol_prod_id ='${POID}'</t>
+  </si>
+  <si>
+    <t>PRLineDetailsQuery</t>
+  </si>
+  <si>
+    <t>SELECT prl_bu,
+       prl_rqst_no,
+       prl_seq_no,
+       prl_prod_id,
+       prl_prod_rev,
+       prl_prod_desc1,
+       prl_class_id,
+       prl_class_desc,
+       prl_sub_cls_id,
+       prl_sub_cls_desc,
+       prl_uom,
+       prl_prod_uom,
+       prl_conv_factor,
+       prl_requested_qty,
+       (prl_requested_qty * prl_bc_unit_cost) line_amount,
+       prl_ordered_qty,
+       prl_receipt_qty,
+       prl_bc_unit_cost,
+       prl_disc_pct,
+       prl_stocked,
+       prl_qc_required,
+       prl_quote_pfx,
+       prl_quote_no,
+       prl_order_pfx,
+       prl_order_no,
+       prl_net_disc_flag,
+       prl_status,
+      case when prl_status = 'R' then 'Entry Completed'
+            when prl_status = 'A' then 'Approved'
+            when prl_status = 'C' then 'Cancelled'
+            when prl_status = 'L' then 'Close Shorted'
+            when prl_status = 'E' then 'Draft' END  STATUS, 
+       prl_prod_temp_id,
+       prl_prod_temp_rev,
+       prl_work_ord_no,
+       prl_select_flag,
+       prl_ins_plan_no,
+       prl_ins_plan_rev,
+       prl_prod_ord_no,
+       prl_sf_code,
+       prl_test_req_flag,
+       prl_cert_id,
+       prl_print_seq_no,
+       prl_prod_temp_desc1,
+       prl_ref,
+       prl_prod_ext_desc,
+       prl_cs_narr,
+       prl_drawing_no,
+       prl_drawing_rev,
+       prl_spr_type,
+       prl_rcpt_rcvd_qty,
+       prl_dim_req_flag,
+       prl_thickness,
+       prl_length,
+       prl_width,
+       prl_qty_in_nos,
+       prl_serv_prod_id,
+       prl_serv_io_type,
+       prl_amc_start_date,
+       prl_amc_end_date,
+       prl_serv_prod_desc,
+       prl_tool_wo_no,
+       prl_sugg_suplr_id,
+       prl_cls_sel_user,
+       prl_cls_qty,
+       prl_cls_proc_qty,
+       prl_cap_asset_id,
+       prl_cust_drw_no,
+       prl_cust_drw_rev,
+       prl_catalog_no,
+       prl_mchn_id,
+       prl_sub_dept_id,
+       prl_priority,
+       prl_buyer_id,
+       prl_mrp_rel_qty,
+       prl_mftr_id,
+       prl_mftr_part_no,
+       prl_eqpmt_id,
+       prl_eqpmt_desc,
+       prl_buyer_emp_id,
+       prl_lpp_rcpt_pfx,
+       prl_lpp_rcpt_no,
+       prl_mchn_grp_id,
+       prl_pr_plan_no,
+       prl_prod_outer_dia,
+       prl_cre_by,
+       prl_cre_ip_addr,
+       prl_cre_os_user,
+       prl_cre_date,
+       prl_upd_by,
+       prl_upd_ip_addr,
+       prl_upd_os_user,
+       prl_upd_date,
+       prl_cre_emp_id,
+       prl_upd_emp_id,
+       prl_last_po_price,
+       prl_prod_chng_flag,
+       prl_batch_no,
+       prl_expiry_date,
+       prl_mfg_date,
+       prl_sterilize_date,
+       prl_iss_code,
+       prl_height,
+       prl_inner_dia,
+       prl_density,
+       prl_pur_acct,
+       prl_cc_code,
+       prl_fab_item_type,
+       prl_gla_fxd_flag,
+       prl_cpc_fxd_flag,
+      prl_store_id,
+      prl_store_name,
+      prl_required_date,
+      prl_so_type,
+      prl_so_pfx,
+      prl_so_no,
+      prl_so_seq_no,
+      prl_so_sub_seq_no,
+      prl_proj_id,
+      prl_task_id,
+      prl_so_schld_desc,  
+      prl_shipto_loc_id,
+      prl_shipto_loc_name,
+      prl_rfq
+   FROM pur_req_ln
+  WHERE prl_bu       ='TVSA'                    
+    AND PRL_RQST_NO  ='${PRNO}'
+    AND PRL_PROD_ID  ='${ItemId}'</t>
+  </si>
+  <si>
+    <t>POALineDetailsQuery</t>
+  </si>
+  <si>
+    <t>SELECT
+       pah_plnt_loc_name,
+       PAH_PLNT_LOC_ID,
+       palc_prod_uom,
+       pah_bu,pah_plnt,
+       (SELECT bup_name1
+          FROM bus_unit_plants
+         WHERE bup_bu = pah_bu 
+           AND bup_plant_id = pah_plnt)pah_plnt_desc,
+       DECODE(pah_type,'ST','Standard','SE','Sample','TS','Stock Transfer','SS','Std. Service ','MS','Maint. Service',
+                 'RD','R&amp;D','PJ','Project')type_desc,      
+       pah_doc_no,
+       pah_doc_date,
+       (SELECT poh_currency
+          FROM pur_order_hd
+         WHERE poh_bu ='TVSA'
+           AND poh_order_no =pah_po_no)pah_currency,
+        'POA'  pah_sub_vou,
+       pah_po_pfx,
+       pah_po_no,
+      pah_po_pfx ||'/'||pah_po_no||'/'||palc_po_line_no po_no,
+       pah_doc_date "PO/Date",
+       pah_po_rev_no rev_no,
+       pah_suplr_id supp_id,
+       (SELECT suplr_name1
+          FROM suppliers
+         WHERE suplr_bu = pah_bu
+           AND suplr_suplr_id = pah_suplr_id) supp_name,         
+       decode(pah_status,'N','Draft','E','Entry Completed','A','Approved','C','Cancelled') status,
+       pah_exchange_rate ex_rate,
+       palc_po_line_no PO_line_no,
+       DECODE(palc_chnge_type,'A','Addition','C','Closeshort','M','Modify')ln_type,
+       palc_seq_no "Line",
+       palc_prod_id,
+       palc_prod_rev,
+       palc_prod_desc1,
+         NVL((SELECT SUM(pol_received_qty)
+            FROM pur_order_ln
+           WHERE pol_bu = pah_bu
+             AND pol_order_no = pah_po_no
+             AND pol_seq_no = palc_po_line_no),0) palc_recvd_qty,
+               NVL((SELECT SUM(pol_cls_qty)
+            FROM pur_order_ln
+           WHERE pol_bu = pah_bu
+             AND pol_order_no = pah_po_no
+             AND pol_seq_no = palc_po_line_no),0) palc_cls_qty,
+               NVL((SELECT SUM(pol_proc_qty)
+            FROM pur_order_ln
+           WHERE pol_bu = pah_bu
+             AND pol_order_no = pah_po_no
+             AND pol_seq_no = palc_po_line_no),0) palc_inproc_qty,
+       palc_old_po_qty old_qty,
+       palc_new_po_qty new_qty,
+       palc_old_unit_cost old_unit_cost_tc,
+       palc_new_unit_cost new_unit_cost_tc,
+       palc_old_disc_pct old_disc_pct,
+       palc_new_disc_pct  new_disc_pct,
+       CASE WHEN palc_gst_input_type = 'I' THEN 'Inputs'
+            WHEN palc_gst_input_type = 'C' THEN 'Capital Goods'
+            WHEN palc_gst_input_type = 'S' THEN 'Input Services'
+            WHEN palc_gst_input_type = 'N' THEN 'Ineligible'
+            WHEN palc_gst_input_type = 'A' THEN 'NA'
+            ELSE palc_gst_input_type
+       END palc_gst_input_type,
+       CASE WHEN palc_gst_exempt_flag = 'G' THEN 'GST Supply'
+            WHEN palc_gst_exempt_flag = 'R' THEN 'NIL Rated'
+            WHEN palc_gst_exempt_flag = 'Y' THEN 'Exempted'
+            WHEN palc_gst_exempt_flag = 'N' THEN 'Non-GST Supply'
+            WHEN palc_gst_exempt_flag = 'A' THEN 'NA'
+            ELSE palc_gst_exempt_flag
+       END palc_gst_exempt_flag,     
+       palc_new_suplr_prod_id suplr_prod_id,
+       (SELECT prod_desc11 FROM products WHERE prod_bu = palc_bu AND prod_id = palc_new_suplr_prod_id AND prod_rev = palc_prod_rev)suplr_prod_desc,
+       CASE WHEN palc_contr_pfx IS NOT NULL THEN palc_contr_pfx||'/'||palc_contr_id||'/'||palc_contr_amd_no ELSE NULL END open_ord_no,    
+       palc_cls_id,
+       (SELECT class_desc1 FROM classes WHERE class_bu = pah_bu AND class_id = palc_cls_id)class_desc,
+       palc_subcls_id,
+       palc_hsn_code "HSN Code",
+       (SELECT poh_buyer_id
+          FROM pur_order_hd
+         WHERE poh_bu = 'TVSA'
+           AND poh_order_pfx = pah_po_pfx
+            AND poh_order_no = pah_po_no)poh_buyer_id,
+        func_find_buyer_qry_desc('TVSA',(SELECT poh_buyer_id
+          FROM pur_order_hd
+         WHERE poh_bu = 'TVSA'
+           AND poh_order_pfx = pah_po_pfx
+            AND poh_order_no = pah_po_no),1)POH_BUYER_NAME
+  FROM po_amend_hd, 
+       po_amend_line_chnges
+ WHERE pah_bu = palc_bu
+   AND pah_plnt =  palc_plnt
+   AND pah_doc_no = palc_doc_no
+   AND pah_bu = 'TVSA'
+   AND pah_doc_no ='${POANO}'
+   AND PALC_PROD_ID = '${ItemId}'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3526,20 +3875,151 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3564,8 +4044,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -3601,18 +4267,264 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3632,9 +4544,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3644,21 +4553,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3666,9 +4569,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -3681,11 +4581,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3699,36 +4599,75 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 2 2" xfId="2"/>
-    <cellStyle name="Normal 2 3" xfId="3"/>
-    <cellStyle name="Normal 3" xfId="4"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal 2" xfId="49"/>
+    <cellStyle name="Normal 2 2" xfId="50"/>
+    <cellStyle name="Normal 2 3" xfId="51"/>
+    <cellStyle name="Normal 3" xfId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3990,846 +4929,846 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B569"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B589"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="62.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="59.85546875" style="5" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="62.712962962963" style="6" customWidth="1"/>
+    <col min="2" max="2" width="59.8518518518519" style="7" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="11">
         <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="11" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="11" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="11" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="11" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="11" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="11" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="11" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="11" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="11" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="11" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="11" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="11" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="11" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="11" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="11" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="11" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="11" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="11" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="11" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="11" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="11" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="13" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="13" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="13" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="13" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="13" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="13" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="13" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="13" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="13" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="13" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="13" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="13" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B65" s="12">
+      <c r="B65" s="13">
         <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="13" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="12">
+      <c r="B69" s="13">
         <v>2012</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="13" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="13" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="13" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="13" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="13" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="13" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="B76" s="12">
+      <c r="B76" s="13">
         <v>202425</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="13" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="13" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="13" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B81" s="12" t="s">
+      <c r="B81" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="15" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="15" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="15" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="13" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="15" t="s">
+      <c r="A90" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="13" t="s">
+      <c r="A91" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="B91" s="13" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="13" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="13" t="s">
+      <c r="A93" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="13" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="13" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="13" t="s">
+      <c r="A95" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="B95" s="13" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="13" t="s">
+      <c r="A96" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="13" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="13" t="s">
+      <c r="A97" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="B97" s="12" t="s">
+      <c r="B97" s="13" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="13" t="s">
+      <c r="A98" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="13" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="13" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="16" t="s">
+      <c r="A100" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B100" s="17" t="s">
+      <c r="B100" s="18" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="16" t="s">
+      <c r="A101" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B101" s="17" t="s">
+      <c r="B101" s="18" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="16" t="s">
+      <c r="A102" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="B102" s="17" t="s">
+      <c r="B102" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B103" s="17" t="s">
+      <c r="B103" s="18" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="16" t="s">
+      <c r="A104" s="17" t="s">
         <v>192</v>
       </c>
       <c r="B104" s="18">
@@ -4872,7 +5811,7 @@
       <c r="A109" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="B109" s="22" t="s">
+      <c r="B109" s="21" t="s">
         <v>201</v>
       </c>
     </row>
@@ -4885,671 +5824,671 @@
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="8" t="s">
+      <c r="A111" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="B111" s="23" t="s">
+      <c r="B111" s="22" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="24" t="s">
+      <c r="A112" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="B112" s="25" t="s">
+      <c r="B112" s="24" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="24" t="s">
+      <c r="A113" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="B113" s="25" t="s">
+      <c r="B113" s="24" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="24" t="s">
+      <c r="A114" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="B114" s="23" t="s">
+      <c r="B114" s="22" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="B115" s="23" t="s">
+      <c r="B115" s="22" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="24" t="s">
+      <c r="A116" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="B116" s="23" t="s">
+      <c r="B116" s="22" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="8" t="s">
+      <c r="A117" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="B117" s="23" t="s">
+      <c r="B117" s="22" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="8" t="s">
+      <c r="A118" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B118" s="26">
+      <c r="B118" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="27" t="s">
+      <c r="A119" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="B119" s="9" t="s">
+      <c r="B119" s="11" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="27" t="s">
+      <c r="A120" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="B120" s="9" t="s">
+      <c r="B120" s="11" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="27" t="s">
+      <c r="A121" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="B121" s="9" t="s">
+      <c r="B121" s="11" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="27" t="s">
+      <c r="A122" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="B122" s="9" t="s">
+      <c r="B122" s="11" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="27" t="s">
+      <c r="A123" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="B123" s="9" t="s">
+      <c r="B123" s="11" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="27" t="s">
+      <c r="A124" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="B124" s="9" t="s">
+      <c r="B124" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="27" t="s">
+      <c r="A125" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="B125" s="9" t="s">
+      <c r="B125" s="11" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="27" t="s">
+      <c r="A126" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="B126" s="9" t="s">
+      <c r="B126" s="11" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="27" t="s">
+      <c r="A127" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="B127" s="9" t="s">
+      <c r="B127" s="11" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="27" t="s">
+      <c r="A128" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="B128" s="9" t="s">
+      <c r="B128" s="11" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="27" t="s">
+      <c r="A129" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="B129" s="9" t="s">
+      <c r="B129" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="27" t="s">
+      <c r="A130" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="B130" s="9" t="s">
+      <c r="B130" s="11" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="27" t="s">
+      <c r="A131" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="B131" s="9" t="s">
+      <c r="B131" s="11" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="27" t="s">
+      <c r="A132" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="B132" s="9" t="s">
+      <c r="B132" s="11" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="27" t="s">
+      <c r="A133" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="B133" s="9" t="s">
+      <c r="B133" s="11" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="27" t="s">
+      <c r="A134" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="B134" s="9" t="s">
+      <c r="B134" s="11" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="27" t="s">
+      <c r="A135" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="B135" s="9" t="s">
+      <c r="B135" s="11" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="27" t="s">
+      <c r="A136" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="B136" s="9" t="s">
+      <c r="B136" s="11" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="27" t="s">
+      <c r="A137" s="25" t="s">
         <v>250</v>
       </c>
-      <c r="B137" s="9" t="s">
+      <c r="B137" s="11" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="27" t="s">
+      <c r="A138" s="25" t="s">
         <v>251</v>
       </c>
-      <c r="B138" s="9" t="s">
+      <c r="B138" s="11" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="27" t="s">
+      <c r="A139" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="B139" s="9" t="s">
+      <c r="B139" s="11" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="27" t="s">
+      <c r="A140" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="B140" s="9" t="s">
+      <c r="B140" s="11" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="27" t="s">
+      <c r="A141" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="B141" s="9" t="s">
+      <c r="B141" s="11" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="27" t="s">
+      <c r="A142" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="B142" s="9" t="s">
+      <c r="B142" s="11" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="27" t="s">
+      <c r="A143" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="B143" s="9" t="s">
+      <c r="B143" s="11" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="27" t="s">
+      <c r="A144" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="B144" s="9" t="s">
+      <c r="B144" s="11" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="27" t="s">
+      <c r="A145" s="25" t="s">
         <v>258</v>
       </c>
-      <c r="B145" s="9" t="s">
+      <c r="B145" s="11" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="27" t="s">
+      <c r="A146" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="B146" s="9" t="s">
+      <c r="B146" s="11" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="27" t="s">
+      <c r="A147" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="B147" s="9" t="s">
+      <c r="B147" s="11" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="27" t="s">
+      <c r="A148" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="B148" s="9" t="s">
+      <c r="B148" s="11" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="27" t="s">
+      <c r="A149" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="B149" s="9" t="s">
+      <c r="B149" s="11" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="27" t="s">
+      <c r="A150" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="B150" s="9" t="s">
+      <c r="B150" s="11" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="8" t="s">
+      <c r="A151" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B151" s="9" t="s">
+      <c r="B151" s="11" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="8" t="s">
+      <c r="A152" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="B152" s="9" t="s">
+      <c r="B152" s="11" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="8" t="s">
+      <c r="A153" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="B153" s="9" t="s">
+      <c r="B153" s="11" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="8" t="s">
+      <c r="A154" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B154" s="9" t="s">
+      <c r="B154" s="11" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="8" t="s">
+      <c r="A155" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B155" s="9" t="s">
+      <c r="B155" s="11" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="8" t="s">
+      <c r="A156" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="B156" s="9" t="s">
+      <c r="B156" s="11" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="8" t="s">
+      <c r="A157" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="B157" s="28" t="s">
+      <c r="B157" s="26" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="8" t="s">
+      <c r="A158" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B158" s="23" t="s">
+      <c r="B158" s="22" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="11" t="s">
+      <c r="A159" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="B159" s="29" t="s">
+      <c r="B159" s="27" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="11" t="s">
+      <c r="A160" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="B160" s="12" t="s">
+      <c r="B160" s="13" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="11" t="s">
+      <c r="A161" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="B161" s="14" t="s">
+      <c r="B161" s="15" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="11" t="s">
+      <c r="A162" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="B162" s="12" t="s">
+      <c r="B162" s="13" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="11" t="s">
+      <c r="A163" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="B163" s="12" t="s">
+      <c r="B163" s="13" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="11" t="s">
+      <c r="A164" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="B164" s="14" t="s">
+      <c r="B164" s="15" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="11" t="s">
+      <c r="A165" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="B165" s="14" t="s">
+      <c r="B165" s="15" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="11" t="s">
+      <c r="A166" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="B166" s="12" t="s">
+      <c r="B166" s="13" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="11" t="s">
+      <c r="A167" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="B167" s="12" t="s">
+      <c r="B167" s="13" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="11" t="s">
+      <c r="A168" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="B168" s="14" t="s">
+      <c r="B168" s="15" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="11" t="s">
+      <c r="A169" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="B169" s="14" t="s">
+      <c r="B169" s="15" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="11" t="s">
+      <c r="A170" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="B170" s="12" t="s">
+      <c r="B170" s="13" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="11" t="s">
+      <c r="A171" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B171" s="12" t="s">
+      <c r="B171" s="13" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="11" t="s">
+      <c r="A172" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="B172" s="12" t="s">
+      <c r="B172" s="13" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="11" t="s">
+      <c r="A173" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="B173" s="12" t="s">
+      <c r="B173" s="13" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="11" t="s">
+      <c r="A174" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="B174" s="12" t="s">
+      <c r="B174" s="13" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="11" t="s">
+      <c r="A175" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="B175" s="12" t="s">
+      <c r="B175" s="13" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="11" t="s">
+      <c r="A176" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="B176" s="12" t="s">
+      <c r="B176" s="13" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="11" t="s">
+      <c r="A177" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="B177" s="12" t="s">
+      <c r="B177" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="11" t="s">
+      <c r="A178" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="B178" s="12" t="s">
+      <c r="B178" s="13" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="11" t="s">
+      <c r="A179" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="B179" s="12" t="s">
+      <c r="B179" s="13" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="11" t="s">
+      <c r="A180" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="B180" s="12" t="s">
+      <c r="B180" s="13" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="11" t="s">
+      <c r="A181" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="B181" s="12" t="s">
+      <c r="B181" s="13" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="11" t="s">
+      <c r="A182" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="B182" s="12" t="s">
+      <c r="B182" s="13" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="11" t="s">
+      <c r="A183" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="B183" s="12" t="s">
+      <c r="B183" s="13" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="11" t="s">
+      <c r="A184" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="B184" s="12" t="s">
+      <c r="B184" s="13" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="11" t="s">
+      <c r="A185" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B185" s="12" t="s">
+      <c r="B185" s="13" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="11" t="s">
+      <c r="A186" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="B186" s="14" t="s">
+      <c r="B186" s="15" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="11" t="s">
+      <c r="A187" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B187" s="14" t="s">
+      <c r="B187" s="15" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="11" t="s">
+      <c r="A188" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="B188" s="12" t="s">
+      <c r="B188" s="13" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="11" t="s">
+      <c r="A189" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="B189" s="14" t="s">
+      <c r="B189" s="15" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="11" t="s">
+      <c r="A190" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="B190" s="12" t="s">
+      <c r="B190" s="13" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="8" t="s">
+      <c r="A191" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B191" s="30" t="s">
+      <c r="B191" s="28" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="31" t="s">
+      <c r="A192" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="B192" s="32" t="s">
+      <c r="B192" s="30" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="31" t="s">
+      <c r="A193" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="B193" s="32" t="s">
+      <c r="B193" s="30" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="31" t="s">
+      <c r="A194" s="29" t="s">
         <v>197</v>
       </c>
       <c r="B194" s="18">
@@ -5557,23 +6496,23 @@
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="31" t="s">
+      <c r="A195" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="B195" s="32" t="s">
+      <c r="B195" s="30" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="31" t="s">
+      <c r="A196" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="B196" s="17" t="s">
+      <c r="B196" s="18" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="31" t="s">
+      <c r="A197" s="29" t="s">
         <v>202</v>
       </c>
       <c r="B197" s="18">
@@ -5581,39 +6520,39 @@
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="31" t="s">
+      <c r="A198" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="B198" s="17" t="s">
+      <c r="B198" s="18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="31" t="s">
+      <c r="A199" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="B199" s="33" t="s">
+      <c r="B199" s="31" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="31" t="s">
+      <c r="A200" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="B200" s="33" t="s">
+      <c r="B200" s="31" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="31" t="s">
+      <c r="A201" s="29" t="s">
         <v>348</v>
       </c>
-      <c r="B201" s="33" t="s">
+      <c r="B201" s="31" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="31" t="s">
+      <c r="A202" s="29" t="s">
         <v>350</v>
       </c>
       <c r="B202" s="18">
@@ -5621,7 +6560,7 @@
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="31" t="s">
+      <c r="A203" s="29" t="s">
         <v>351</v>
       </c>
       <c r="B203" s="18">
@@ -5629,15 +6568,15 @@
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="31" t="s">
+      <c r="A204" s="29" t="s">
         <v>352</v>
       </c>
-      <c r="B204" s="17" t="s">
+      <c r="B204" s="18" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="16" t="s">
+      <c r="A205" s="17" t="s">
         <v>354</v>
       </c>
       <c r="B205" s="18">
@@ -5645,7 +6584,7 @@
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="16" t="s">
+      <c r="A206" s="17" t="s">
         <v>355</v>
       </c>
       <c r="B206" s="18">
@@ -5653,15 +6592,15 @@
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="16" t="s">
+      <c r="A207" s="17" t="s">
         <v>356</v>
       </c>
-      <c r="B207" s="17" t="s">
+      <c r="B207" s="18" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="16" t="s">
+      <c r="A208" s="17" t="s">
         <v>358</v>
       </c>
       <c r="B208" s="18">
@@ -5669,7 +6608,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="16" t="s">
+      <c r="A209" s="17" t="s">
         <v>359</v>
       </c>
       <c r="B209" s="18">
@@ -5677,7 +6616,7 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="16" t="s">
+      <c r="A210" s="17" t="s">
         <v>360</v>
       </c>
       <c r="B210" s="18">
@@ -5685,7 +6624,7 @@
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="16" t="s">
+      <c r="A211" s="17" t="s">
         <v>361</v>
       </c>
       <c r="B211" s="18">
@@ -5693,31 +6632,31 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="16" t="s">
+      <c r="A212" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="B212" s="32" t="s">
+      <c r="B212" s="30" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="16" t="s">
+      <c r="A213" s="17" t="s">
         <v>364</v>
       </c>
-      <c r="B213" s="17" t="s">
+      <c r="B213" s="18" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="16" t="s">
+      <c r="A214" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="B214" s="32" t="s">
+      <c r="B214" s="30" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="16" t="s">
+      <c r="A215" s="17" t="s">
         <v>368</v>
       </c>
       <c r="B215" s="18">
@@ -5725,7 +6664,7 @@
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="16" t="s">
+      <c r="A216" s="17" t="s">
         <v>369</v>
       </c>
       <c r="B216" s="18">
@@ -5733,2840 +6672,3002 @@
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="16" t="s">
+      <c r="A217" s="17" t="s">
         <v>370</v>
       </c>
-      <c r="B217" s="32" t="s">
+      <c r="B217" s="30" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="8" t="s">
+      <c r="A218" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B218" s="23" t="s">
+      <c r="B218" s="22" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="8" t="s">
+      <c r="A219" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="B219" s="23" t="s">
+      <c r="B219" s="22" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="8" t="s">
+      <c r="A220" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="B220" s="23" t="s">
+      <c r="B220" s="22" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="8" t="s">
+      <c r="A221" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="B221" s="23" t="s">
+      <c r="B221" s="22" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="24" t="s">
+      <c r="A222" s="23" t="s">
         <v>376</v>
       </c>
-      <c r="B222" s="23" t="s">
+      <c r="B222" s="22" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="24" t="s">
+      <c r="A223" s="23" t="s">
         <v>378</v>
       </c>
-      <c r="B223" s="23" t="s">
+      <c r="B223" s="22" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="34" t="s">
+      <c r="A224" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="B224" s="35" t="s">
+      <c r="B224" s="33" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="24" t="s">
+      <c r="A225" s="23" t="s">
         <v>382</v>
       </c>
-      <c r="B225" s="25" t="s">
+      <c r="B225" s="24" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="8" t="s">
+      <c r="A226" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B226" s="9" t="s">
+      <c r="B226" s="11" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="8" t="s">
+      <c r="A227" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="B227" s="9" t="s">
+      <c r="B227" s="11" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="8" t="s">
+      <c r="A228" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B228" s="9" t="s">
+      <c r="B228" s="11" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="8" t="s">
+      <c r="A229" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="B229" s="9" t="s">
+      <c r="B229" s="11" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="8" t="s">
+      <c r="A230" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="B230" s="9" t="s">
+      <c r="B230" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="8" t="s">
+      <c r="A231" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B231" s="9" t="s">
+      <c r="B231" s="11" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="8" t="s">
+      <c r="A232" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="B232" s="9" t="s">
+      <c r="B232" s="11" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="8" t="s">
+      <c r="A233" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="B233" s="9" t="s">
+      <c r="B233" s="11" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="234" spans="1:2">
-      <c r="A234" s="8" t="s">
+      <c r="A234" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B234" s="9" t="s">
+      <c r="B234" s="11" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="235" spans="1:2">
-      <c r="A235" s="8" t="s">
+      <c r="A235" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="B235" s="9" t="s">
+      <c r="B235" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="236" spans="1:2">
-      <c r="A236" s="8" t="s">
+      <c r="A236" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="B236" s="9" t="s">
+      <c r="B236" s="11" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="237" spans="1:2">
-      <c r="A237" s="8" t="s">
+      <c r="A237" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B237" s="9" t="s">
+      <c r="B237" s="11" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="238" spans="1:2">
-      <c r="A238" s="8" t="s">
+      <c r="A238" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="B238" s="9" t="s">
+      <c r="B238" s="11" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="239" spans="1:2">
-      <c r="A239" s="8" t="s">
+      <c r="A239" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="B239" s="9" t="s">
+      <c r="B239" s="11" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="240" spans="1:2">
-      <c r="A240" s="8" t="s">
+      <c r="A240" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="B240" s="9" t="s">
+      <c r="B240" s="11" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="241" spans="1:2">
-      <c r="A241" s="8" t="s">
+      <c r="A241" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="B241" s="9" t="s">
+      <c r="B241" s="11" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="242" spans="1:2">
-      <c r="A242" s="8" t="s">
+      <c r="A242" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="B242" s="9" t="s">
+      <c r="B242" s="11" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="243" spans="1:2">
-      <c r="A243" s="8" t="s">
+      <c r="A243" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="B243" s="9" t="s">
+      <c r="B243" s="11" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="244" spans="1:2">
-      <c r="A244" s="8" t="s">
+      <c r="A244" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="B244" s="9" t="s">
+      <c r="B244" s="11" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="245" spans="1:2">
-      <c r="A245" s="8" t="s">
+      <c r="A245" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="B245" s="9" t="s">
+      <c r="B245" s="11" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="246" spans="1:2">
-      <c r="A246" s="8" t="s">
+      <c r="A246" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="B246" s="9" t="s">
+      <c r="B246" s="11" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="247" spans="1:2">
-      <c r="A247" s="8" t="s">
+      <c r="A247" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="B247" s="9" t="s">
+      <c r="B247" s="11" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="248" spans="1:2">
-      <c r="A248" s="8" t="s">
+      <c r="A248" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="B248" s="9" t="s">
+      <c r="B248" s="11" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="249" spans="1:2">
-      <c r="A249" s="8" t="s">
+      <c r="A249" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="B249" s="36" t="s">
+      <c r="B249" s="34" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="250" spans="1:2">
-      <c r="A250" s="8" t="s">
+      <c r="A250" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="B250" s="9" t="s">
+      <c r="B250" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="251" spans="1:2">
-      <c r="A251" s="8" t="s">
+      <c r="A251" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="B251" s="9" t="s">
+      <c r="B251" s="11" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="252" spans="1:2">
-      <c r="A252" s="8" t="s">
+      <c r="A252" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="B252" s="9" t="s">
+      <c r="B252" s="11" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="253" spans="1:2">
-      <c r="A253" s="8" t="s">
+      <c r="A253" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="B253" s="9" t="s">
+      <c r="B253" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="254" spans="1:2">
-      <c r="A254" s="8" t="s">
+      <c r="A254" s="10" t="s">
         <v>425</v>
       </c>
-      <c r="B254" s="9" t="s">
+      <c r="B254" s="11" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="255" spans="1:2">
-      <c r="A255" s="8" t="s">
+      <c r="A255" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="B255" s="9" t="s">
+      <c r="B255" s="11" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="256" spans="1:2">
-      <c r="A256" s="8" t="s">
+      <c r="A256" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="B256" s="9" t="s">
+      <c r="B256" s="11" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="257" spans="1:2">
-      <c r="A257" s="8" t="s">
+      <c r="A257" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="B257" s="9" t="s">
+      <c r="B257" s="11" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="258" spans="1:2">
-      <c r="A258" s="8" t="s">
+      <c r="A258" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="B258" s="9" t="s">
+      <c r="B258" s="11" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="259" spans="1:2">
-      <c r="A259" s="8" t="s">
+      <c r="A259" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="B259" s="9" t="s">
+      <c r="B259" s="11" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="260" spans="1:2">
-      <c r="A260" s="8" t="s">
+      <c r="A260" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="B260" s="9" t="s">
+      <c r="B260" s="11" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="261" spans="1:2">
-      <c r="A261" s="8" t="s">
+      <c r="A261" s="10" t="s">
         <v>437</v>
       </c>
-      <c r="B261" s="9" t="s">
+      <c r="B261" s="11" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="262" spans="1:2">
-      <c r="A262" s="8" t="s">
+      <c r="A262" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="B262" s="9" t="s">
+      <c r="B262" s="11" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="263" spans="1:2">
-      <c r="A263" s="8" t="s">
+      <c r="A263" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="B263" s="9" t="s">
+      <c r="B263" s="11" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="264" spans="1:2">
-      <c r="A264" s="8" t="s">
+      <c r="A264" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="B264" s="9" t="s">
+      <c r="B264" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="265" spans="1:2">
-      <c r="A265" s="8" t="s">
+      <c r="A265" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="B265" s="9" t="s">
+      <c r="B265" s="11" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="266" spans="1:2">
-      <c r="A266" s="8" t="s">
+      <c r="A266" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="B266" s="9" t="s">
+      <c r="B266" s="11" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="267" spans="1:2">
-      <c r="A267" s="8" t="s">
+      <c r="A267" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="B267" s="9" t="s">
+      <c r="B267" s="11" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="268" spans="1:2">
-      <c r="A268" s="8" t="s">
+      <c r="A268" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="B268" s="9" t="s">
+      <c r="B268" s="11" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="269" spans="1:2">
-      <c r="A269" s="8" t="s">
+      <c r="A269" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="B269" s="9" t="s">
+      <c r="B269" s="11" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="270" spans="1:2">
-      <c r="A270" s="8" t="s">
+      <c r="A270" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="B270" s="9" t="s">
+      <c r="B270" s="11" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="271" spans="1:2">
-      <c r="A271" s="8" t="s">
+      <c r="A271" s="10" t="s">
         <v>455</v>
       </c>
-      <c r="B271" s="9" t="s">
+      <c r="B271" s="11" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="272" spans="1:2">
-      <c r="A272" s="8" t="s">
+      <c r="A272" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="B272" s="9" t="s">
+      <c r="B272" s="11" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="273" spans="1:2">
-      <c r="A273" s="8" t="s">
+      <c r="A273" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="B273" s="9" t="s">
+      <c r="B273" s="11" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="274" spans="1:2">
-      <c r="A274" s="8" t="s">
+      <c r="A274" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="B274" s="9" t="s">
+      <c r="B274" s="11" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="275" spans="1:2">
-      <c r="A275" s="8" t="s">
+      <c r="A275" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="B275" s="9" t="s">
+      <c r="B275" s="11" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="276" spans="1:2">
-      <c r="A276" s="8" t="s">
+      <c r="A276" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="B276" s="9" t="s">
+      <c r="B276" s="11" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="277" spans="1:2">
-      <c r="A277" s="8" t="s">
+      <c r="A277" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="B277" s="9" t="s">
+      <c r="B277" s="11" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="278" spans="1:2">
-      <c r="A278" s="24" t="s">
+      <c r="A278" s="23" t="s">
         <v>467</v>
       </c>
-      <c r="B278" s="23" t="s">
+      <c r="B278" s="22" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="279" spans="1:2">
-      <c r="A279" s="8" t="s">
+      <c r="A279" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B279" s="23" t="s">
+      <c r="B279" s="22" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="280" spans="1:2">
-      <c r="A280" s="8" t="s">
+      <c r="A280" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="B280" s="9" t="s">
+      <c r="B280" s="11" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="281" spans="1:2">
-      <c r="A281" s="11" t="s">
+      <c r="A281" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="B281" s="12" t="s">
+      <c r="B281" s="13" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="282" spans="1:2">
-      <c r="A282" s="11" t="s">
+      <c r="A282" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="B282" s="12" t="s">
+      <c r="B282" s="13" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="283" spans="1:2">
-      <c r="A283" s="11" t="s">
+      <c r="A283" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="B283" s="12" t="s">
+      <c r="B283" s="13" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="284" spans="1:2">
-      <c r="A284" s="11" t="s">
+      <c r="A284" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="B284" s="14" t="s">
+      <c r="B284" s="15" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="285" spans="1:2">
-      <c r="A285" s="37" t="s">
+      <c r="A285" s="35" t="s">
         <v>479</v>
       </c>
-      <c r="B285" s="9" t="s">
+      <c r="B285" s="11" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="286" spans="1:2">
-      <c r="A286" s="37" t="s">
+      <c r="A286" s="35" t="s">
         <v>481</v>
       </c>
-      <c r="B286" s="9" t="s">
+      <c r="B286" s="11" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="287" spans="1:2">
-      <c r="A287" s="37" t="s">
+      <c r="A287" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="B287" s="9" t="s">
+      <c r="B287" s="11" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="288" spans="1:2">
-      <c r="A288" s="37" t="s">
+      <c r="A288" s="35" t="s">
         <v>485</v>
       </c>
-      <c r="B288" s="9" t="s">
+      <c r="B288" s="11" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="289" spans="1:2">
-      <c r="A289" s="37" t="s">
+      <c r="A289" s="35" t="s">
         <v>487</v>
       </c>
-      <c r="B289" s="9" t="s">
+      <c r="B289" s="11" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="37" t="s">
+      <c r="A290" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="B290" s="9" t="s">
+      <c r="B290" s="11" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="37" t="s">
+      <c r="A291" s="35" t="s">
         <v>491</v>
       </c>
-      <c r="B291" s="9" t="s">
+      <c r="B291" s="11" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="292" spans="1:2">
-      <c r="A292" s="8" t="s">
+      <c r="A292" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="B292" s="9" t="s">
+      <c r="B292" s="11" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="293" spans="1:2">
-      <c r="A293" s="8" t="s">
+      <c r="A293" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="B293" s="9" t="s">
+      <c r="B293" s="11" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="294" spans="1:2">
-      <c r="A294" s="8" t="s">
+      <c r="A294" s="10" t="s">
         <v>497</v>
       </c>
-      <c r="B294" s="9" t="s">
+      <c r="B294" s="11" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="295" spans="1:2">
-      <c r="A295" s="8" t="s">
+      <c r="A295" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="B295" s="9" t="s">
+      <c r="B295" s="11" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="296" spans="1:2">
-      <c r="A296" s="8" t="s">
+      <c r="A296" s="10" t="s">
         <v>501</v>
       </c>
-      <c r="B296" s="9" t="s">
+      <c r="B296" s="11" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="297" spans="1:2">
-      <c r="A297" s="8" t="s">
+      <c r="A297" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="B297" s="9" t="s">
+      <c r="B297" s="11" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="298" spans="1:2">
-      <c r="A298" s="8" t="s">
+      <c r="A298" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="B298" s="9" t="s">
+      <c r="B298" s="11" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="299" spans="1:2">
-      <c r="A299" s="8" t="s">
+      <c r="A299" s="10" t="s">
         <v>507</v>
       </c>
-      <c r="B299" s="9" t="s">
+      <c r="B299" s="11" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="300" spans="1:2">
-      <c r="A300" s="8" t="s">
+      <c r="A300" s="10" t="s">
         <v>509</v>
       </c>
-      <c r="B300" s="9" t="s">
+      <c r="B300" s="11" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="301" spans="1:2">
-      <c r="A301" s="8" t="s">
+      <c r="A301" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="B301" s="9" t="s">
+      <c r="B301" s="11" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="302" spans="1:2">
-      <c r="A302" s="8" t="s">
+      <c r="A302" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="B302" s="9" t="s">
+      <c r="B302" s="11" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="303" spans="1:2">
-      <c r="A303" s="8" t="s">
+      <c r="A303" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="B303" s="9" t="s">
+      <c r="B303" s="11" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="304" spans="1:2">
-      <c r="A304" s="8" t="s">
+      <c r="A304" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="B304" s="9" t="s">
+      <c r="B304" s="11" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="305" spans="1:2">
-      <c r="A305" s="8" t="s">
+      <c r="A305" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="B305" s="9" t="s">
+      <c r="B305" s="11" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="306" spans="1:2">
-      <c r="A306" s="8" t="s">
+      <c r="A306" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="B306" s="9" t="s">
+      <c r="B306" s="11" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="307" spans="1:2">
-      <c r="A307" s="8" t="s">
+      <c r="A307" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="B307" s="9" t="s">
+      <c r="B307" s="11" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="308" spans="1:2">
-      <c r="A308" s="8" t="s">
+      <c r="A308" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="B308" s="9" t="s">
+      <c r="B308" s="11" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="309" spans="1:2">
-      <c r="A309" s="8" t="s">
+      <c r="A309" s="10" t="s">
         <v>525</v>
       </c>
-      <c r="B309" s="9" t="s">
+      <c r="B309" s="11" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="310" spans="1:2">
-      <c r="A310" s="8" t="s">
+      <c r="A310" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="B310" s="9" t="s">
+      <c r="B310" s="11" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="311" spans="1:2">
-      <c r="A311" s="8" t="s">
+      <c r="A311" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="B311" s="9" t="s">
+      <c r="B311" s="11" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="312" spans="1:2">
-      <c r="A312" s="8" t="s">
+      <c r="A312" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="B312" s="9" t="s">
+      <c r="B312" s="11" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="313" spans="1:2">
-      <c r="A313" s="8" t="s">
+      <c r="A313" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="B313" s="9" t="s">
+      <c r="B313" s="11" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="314" spans="1:2">
-      <c r="A314" s="8" t="s">
+      <c r="A314" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="B314" s="9" t="s">
+      <c r="B314" s="11" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="315" spans="1:2">
-      <c r="A315" s="8" t="s">
+      <c r="A315" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="B315" s="9" t="s">
+      <c r="B315" s="11" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="316" spans="1:2">
-      <c r="A316" s="8" t="s">
+      <c r="A316" s="10" t="s">
         <v>536</v>
       </c>
-      <c r="B316" s="9" t="s">
+      <c r="B316" s="11" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="317" spans="1:2">
-      <c r="A317" s="8" t="s">
+      <c r="A317" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="B317" s="9" t="s">
+      <c r="B317" s="11" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="318" spans="1:2">
-      <c r="A318" s="8" t="s">
+      <c r="A318" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="B318" s="9" t="s">
+      <c r="B318" s="11" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="319" spans="1:2">
-      <c r="A319" s="8" t="s">
+      <c r="A319" s="10" t="s">
         <v>542</v>
       </c>
-      <c r="B319" s="14" t="s">
+      <c r="B319" s="15" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="320" spans="1:2">
-      <c r="A320" s="8" t="s">
+      <c r="A320" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="B320" s="9" t="s">
+      <c r="B320" s="11" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="321" spans="1:2">
-      <c r="A321" s="8" t="s">
+      <c r="A321" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="B321" s="9" t="s">
+      <c r="B321" s="11" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="322" spans="1:2">
-      <c r="A322" s="8" t="s">
+      <c r="A322" s="10" t="s">
         <v>548</v>
       </c>
-      <c r="B322" s="9" t="s">
+      <c r="B322" s="11" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="323" spans="1:2">
-      <c r="A323" s="8" t="s">
+      <c r="A323" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="B323" s="9" t="s">
+      <c r="B323" s="11" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="324" spans="1:2">
-      <c r="A324" s="8" t="s">
+      <c r="A324" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="B324" s="9" t="s">
+      <c r="B324" s="11" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="325" spans="1:2">
-      <c r="A325" s="8" t="s">
+      <c r="A325" s="10" t="s">
         <v>553</v>
       </c>
-      <c r="B325" s="9" t="s">
+      <c r="B325" s="11" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="326" spans="1:2">
-      <c r="A326" s="8" t="s">
+      <c r="A326" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="B326" s="9" t="s">
+      <c r="B326" s="11" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="327" spans="1:2">
-      <c r="A327" s="8" t="s">
+      <c r="A327" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="B327" s="9" t="s">
+      <c r="B327" s="11" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="328" spans="1:2">
-      <c r="A328" s="8" t="s">
+      <c r="A328" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="B328" s="9" t="s">
+      <c r="B328" s="11" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="329" spans="1:2">
-      <c r="A329" s="8" t="s">
+      <c r="A329" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="B329" s="9" t="s">
+      <c r="B329" s="11" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="330" spans="1:2">
-      <c r="A330" s="8" t="s">
+      <c r="A330" s="10" t="s">
         <v>562</v>
       </c>
-      <c r="B330" s="9" t="s">
+      <c r="B330" s="11" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="331" spans="1:2">
-      <c r="A331" s="8" t="s">
+      <c r="A331" s="10" t="s">
         <v>564</v>
       </c>
-      <c r="B331" s="9" t="s">
+      <c r="B331" s="11" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="332" spans="1:2">
-      <c r="A332" s="8" t="s">
+      <c r="A332" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="B332" s="9" t="s">
+      <c r="B332" s="11" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="333" spans="1:2">
-      <c r="A333" s="8" t="s">
+      <c r="A333" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="B333" s="9" t="s">
+      <c r="B333" s="11" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="334" spans="1:2">
-      <c r="A334" s="8" t="s">
+      <c r="A334" s="10" t="s">
         <v>569</v>
       </c>
-      <c r="B334" s="9" t="s">
+      <c r="B334" s="11" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="335" spans="1:2">
-      <c r="A335" s="8" t="s">
+      <c r="A335" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="B335" s="9" t="s">
+      <c r="B335" s="11" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="8" t="s">
+      <c r="A336" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="B336" s="9" t="s">
+      <c r="B336" s="11" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="337" spans="1:2">
-      <c r="A337" s="8" t="s">
+      <c r="A337" s="10" t="s">
         <v>575</v>
       </c>
-      <c r="B337" s="9" t="s">
+      <c r="B337" s="11" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="338" spans="1:2">
-      <c r="A338" s="8" t="s">
+      <c r="A338" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="B338" s="9" t="s">
+      <c r="B338" s="11" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="339" spans="1:2">
-      <c r="A339" s="8" t="s">
+      <c r="A339" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="B339" s="9" t="s">
+      <c r="B339" s="11" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="340" spans="1:2">
-      <c r="A340" s="8" t="s">
+      <c r="A340" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="B340" s="9" t="s">
+      <c r="B340" s="11" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="341" spans="1:2">
-      <c r="A341" s="8" t="s">
+      <c r="A341" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="B341" s="9" t="s">
+      <c r="B341" s="11" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="342" spans="1:2">
-      <c r="A342" s="8" t="s">
+      <c r="A342" s="10" t="s">
         <v>581</v>
       </c>
-      <c r="B342" s="9" t="s">
+      <c r="B342" s="11" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="343" spans="1:2">
-      <c r="A343" s="8" t="s">
+      <c r="A343" s="10" t="s">
         <v>582</v>
       </c>
-      <c r="B343" s="9" t="s">
+      <c r="B343" s="11" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="344" spans="1:2">
-      <c r="A344" s="8" t="s">
+      <c r="A344" s="10" t="s">
         <v>584</v>
       </c>
-      <c r="B344" s="9" t="s">
+      <c r="B344" s="11" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="345" spans="1:2">
-      <c r="A345" s="8" t="s">
+      <c r="A345" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="B345" s="9" t="s">
+      <c r="B345" s="11" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="346" spans="1:2">
-      <c r="A346" s="8" t="s">
+      <c r="A346" s="10" t="s">
         <v>588</v>
       </c>
-      <c r="B346" s="9" t="s">
+      <c r="B346" s="11" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="347" spans="1:2">
-      <c r="A347" s="8" t="s">
+      <c r="A347" s="10" t="s">
         <v>590</v>
       </c>
-      <c r="B347" s="9" t="s">
+      <c r="B347" s="11" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="348" spans="1:2">
-      <c r="A348" s="8" t="s">
+      <c r="A348" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="B348" s="9" t="s">
+      <c r="B348" s="11" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="349" spans="1:2">
-      <c r="A349" s="8" t="s">
+      <c r="A349" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="B349" s="9" t="s">
+      <c r="B349" s="11" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="350" spans="1:2">
-      <c r="A350" s="8" t="s">
+      <c r="A350" s="10" t="s">
         <v>596</v>
       </c>
-      <c r="B350" s="9" t="s">
+      <c r="B350" s="11" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="351" spans="1:2">
-      <c r="A351" s="8" t="s">
+      <c r="A351" s="10" t="s">
         <v>598</v>
       </c>
-      <c r="B351" s="9" t="s">
+      <c r="B351" s="11" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="352" spans="1:2">
-      <c r="A352" s="8" t="s">
+      <c r="A352" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="B352" s="9" t="s">
+      <c r="B352" s="11" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="353" spans="1:2">
-      <c r="A353" s="8" t="s">
+      <c r="A353" s="10" t="s">
         <v>602</v>
       </c>
-      <c r="B353" s="9" t="s">
+      <c r="B353" s="11" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="354" spans="1:2">
-      <c r="A354" s="8" t="s">
+      <c r="A354" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="B354" s="9" t="s">
+      <c r="B354" s="11" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="355" spans="1:2">
-      <c r="A355" s="8" t="s">
+      <c r="A355" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="B355" s="9" t="s">
+      <c r="B355" s="11" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="356" spans="1:2">
-      <c r="A356" s="8" t="s">
+      <c r="A356" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="B356" s="23" t="s">
+      <c r="B356" s="22" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="357" spans="1:2">
-      <c r="A357" s="8" t="s">
+      <c r="A357" s="10" t="s">
         <v>609</v>
       </c>
-      <c r="B357" s="9" t="s">
+      <c r="B357" s="11" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="24" t="s">
+      <c r="A358" s="23" t="s">
         <v>611</v>
       </c>
-      <c r="B358" s="25" t="s">
+      <c r="B358" s="24" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="359" spans="1:2">
-      <c r="A359" s="24" t="s">
+      <c r="A359" s="23" t="s">
         <v>613</v>
       </c>
-      <c r="B359" s="25" t="s">
+      <c r="B359" s="24" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="360" spans="1:2">
-      <c r="A360" s="24" t="s">
+      <c r="A360" s="23" t="s">
         <v>615</v>
       </c>
-      <c r="B360" s="26">
+      <c r="B360" s="22">
         <v>10</v>
       </c>
     </row>
     <row r="361" spans="1:2">
-      <c r="A361" s="24" t="s">
+      <c r="A361" s="23" t="s">
         <v>616</v>
       </c>
-      <c r="B361" s="26">
+      <c r="B361" s="22">
         <v>1000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
-      <c r="A362" s="24" t="s">
+      <c r="A362" s="23" t="s">
         <v>617</v>
       </c>
-      <c r="B362" s="38">
+      <c r="B362" s="36">
         <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:2">
-      <c r="A363" s="24" t="s">
+      <c r="A363" s="23" t="s">
         <v>618</v>
       </c>
-      <c r="B363" s="26">
+      <c r="B363" s="22">
         <v>1000</v>
       </c>
     </row>
     <row r="364" spans="1:2">
-      <c r="A364" s="24" t="s">
+      <c r="A364" s="23" t="s">
         <v>619</v>
       </c>
-      <c r="B364" s="23" t="s">
+      <c r="B364" s="22" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="24" t="s">
+      <c r="A365" s="23" t="s">
         <v>621</v>
       </c>
-      <c r="B365" s="23" t="s">
+      <c r="B365" s="22" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="24" t="s">
+      <c r="A366" s="23" t="s">
         <v>623</v>
       </c>
-      <c r="B366" s="23" t="s">
+      <c r="B366" s="22" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" s="24" t="s">
+      <c r="A367" s="23" t="s">
         <v>625</v>
       </c>
-      <c r="B367" s="26">
+      <c r="B367" s="22">
         <v>10000039</v>
       </c>
     </row>
     <row r="368" spans="1:2">
-      <c r="A368" s="24" t="s">
+      <c r="A368" s="23" t="s">
         <v>626</v>
       </c>
-      <c r="B368" s="25" t="s">
+      <c r="B368" s="24" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="369" spans="1:2">
-      <c r="A369" s="24" t="s">
+      <c r="A369" s="23" t="s">
         <v>628</v>
       </c>
-      <c r="B369" s="25" t="s">
+      <c r="B369" s="24" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="24" t="s">
+      <c r="A370" s="23" t="s">
         <v>630</v>
       </c>
-      <c r="B370" s="9" t="s">
+      <c r="B370" s="11" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="24" t="s">
+      <c r="A371" s="23" t="s">
         <v>632</v>
       </c>
-      <c r="B371" s="9" t="s">
+      <c r="B371" s="11" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="372" spans="1:2">
-      <c r="A372" s="24" t="s">
+      <c r="A372" s="23" t="s">
         <v>634</v>
       </c>
-      <c r="B372" s="9" t="s">
+      <c r="B372" s="11" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="24" t="s">
+      <c r="A373" s="23" t="s">
         <v>636</v>
       </c>
-      <c r="B373" s="9" t="s">
+      <c r="B373" s="11" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="24" t="s">
+      <c r="A374" s="23" t="s">
         <v>638</v>
       </c>
-      <c r="B374" s="9" t="s">
+      <c r="B374" s="11" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="24" t="s">
+      <c r="A375" s="23" t="s">
         <v>640</v>
       </c>
-      <c r="B375" s="9" t="s">
+      <c r="B375" s="11" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="24" t="s">
+      <c r="A376" s="23" t="s">
         <v>642</v>
       </c>
-      <c r="B376" s="9" t="s">
+      <c r="B376" s="11" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="377" spans="1:2">
-      <c r="A377" s="24" t="s">
+      <c r="A377" s="23" t="s">
         <v>643</v>
       </c>
-      <c r="B377" s="9" t="s">
+      <c r="B377" s="11" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="378" spans="1:2">
-      <c r="A378" s="24" t="s">
+      <c r="A378" s="23" t="s">
         <v>645</v>
       </c>
-      <c r="B378" s="9" t="s">
+      <c r="B378" s="11" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="379" spans="1:2">
-      <c r="A379" s="24" t="s">
+      <c r="A379" s="23" t="s">
         <v>647</v>
       </c>
-      <c r="B379" s="9" t="s">
+      <c r="B379" s="11" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="380" spans="1:2">
-      <c r="A380" s="24" t="s">
+      <c r="A380" s="23" t="s">
         <v>649</v>
       </c>
-      <c r="B380" s="9" t="s">
+      <c r="B380" s="11" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="381" spans="1:2">
-      <c r="A381" s="24" t="s">
+      <c r="A381" s="23" t="s">
         <v>650</v>
       </c>
-      <c r="B381" s="9" t="s">
+      <c r="B381" s="11" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="24" t="s">
+      <c r="A382" s="23" t="s">
         <v>652</v>
       </c>
-      <c r="B382" s="9" t="s">
+      <c r="B382" s="11" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="24" t="s">
+      <c r="A383" s="23" t="s">
         <v>654</v>
       </c>
-      <c r="B383" s="9" t="s">
+      <c r="B383" s="11" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="24" t="s">
+      <c r="A384" s="23" t="s">
         <v>656</v>
       </c>
-      <c r="B384" s="9" t="s">
+      <c r="B384" s="11" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="24" t="s">
+      <c r="A385" s="23" t="s">
         <v>658</v>
       </c>
-      <c r="B385" s="9" t="s">
+      <c r="B385" s="11" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="24" t="s">
+      <c r="A386" s="23" t="s">
         <v>660</v>
       </c>
-      <c r="B386" s="9" t="s">
+      <c r="B386" s="11" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="24" t="s">
+      <c r="A387" s="23" t="s">
         <v>662</v>
       </c>
-      <c r="B387" s="9" t="s">
+      <c r="B387" s="11" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="388" spans="1:2">
-      <c r="A388" s="24" t="s">
+      <c r="A388" s="23" t="s">
         <v>664</v>
       </c>
-      <c r="B388" s="9" t="s">
+      <c r="B388" s="11" t="s">
         <v>665</v>
       </c>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" s="24" t="s">
+      <c r="A389" s="23" t="s">
         <v>666</v>
       </c>
-      <c r="B389" s="9" t="s">
+      <c r="B389" s="11" t="s">
         <v>667</v>
       </c>
     </row>
     <row r="390" spans="1:2">
-      <c r="A390" s="24" t="s">
+      <c r="A390" s="23" t="s">
         <v>668</v>
       </c>
-      <c r="B390" s="9" t="s">
+      <c r="B390" s="11" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="24" t="s">
+      <c r="A391" s="23" t="s">
         <v>670</v>
       </c>
-      <c r="B391" s="9" t="s">
+      <c r="B391" s="11" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="24" t="s">
+      <c r="A392" s="23" t="s">
         <v>672</v>
       </c>
-      <c r="B392" s="9" t="s">
+      <c r="B392" s="11" t="s">
         <v>673</v>
       </c>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393" s="24" t="s">
+      <c r="A393" s="23" t="s">
         <v>674</v>
       </c>
-      <c r="B393" s="9" t="s">
+      <c r="B393" s="11" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="24" t="s">
+      <c r="A394" s="23" t="s">
         <v>676</v>
       </c>
-      <c r="B394" s="9" t="s">
+      <c r="B394" s="11" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="395" spans="1:2">
-      <c r="A395" s="24" t="s">
+      <c r="A395" s="23" t="s">
         <v>678</v>
       </c>
-      <c r="B395" s="9" t="s">
+      <c r="B395" s="11" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396" s="24" t="s">
+      <c r="A396" s="23" t="s">
         <v>680</v>
       </c>
-      <c r="B396" s="9" t="s">
+      <c r="B396" s="11" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="24" t="s">
+      <c r="A397" s="23" t="s">
         <v>682</v>
       </c>
-      <c r="B397" s="9" t="s">
+      <c r="B397" s="11" t="s">
         <v>683</v>
       </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="24" t="s">
+      <c r="A398" s="23" t="s">
         <v>684</v>
       </c>
-      <c r="B398" s="9" t="s">
+      <c r="B398" s="11" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="24" t="s">
+      <c r="A399" s="23" t="s">
         <v>686</v>
       </c>
-      <c r="B399" s="9" t="s">
+      <c r="B399" s="11" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="24" t="s">
+      <c r="A400" s="23" t="s">
         <v>688</v>
       </c>
-      <c r="B400" s="9" t="s">
+      <c r="B400" s="11" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="24" t="s">
+      <c r="A401" s="23" t="s">
         <v>690</v>
       </c>
-      <c r="B401" s="9" t="s">
+      <c r="B401" s="11" t="s">
         <v>691</v>
       </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="24" t="s">
+      <c r="A402" s="23" t="s">
         <v>692</v>
       </c>
-      <c r="B402" s="9" t="s">
+      <c r="B402" s="11" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="24" t="s">
+      <c r="A403" s="23" t="s">
         <v>694</v>
       </c>
-      <c r="B403" s="9" t="s">
+      <c r="B403" s="11" t="s">
         <v>695</v>
       </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="24" t="s">
+      <c r="A404" s="23" t="s">
         <v>696</v>
       </c>
-      <c r="B404" s="9" t="s">
+      <c r="B404" s="11" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="24" t="s">
+      <c r="A405" s="23" t="s">
         <v>698</v>
       </c>
-      <c r="B405" s="9" t="s">
+      <c r="B405" s="11" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="24" t="s">
+      <c r="A406" s="23" t="s">
         <v>700</v>
       </c>
-      <c r="B406" s="9" t="s">
+      <c r="B406" s="11" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="24" t="s">
+      <c r="A407" s="23" t="s">
         <v>702</v>
       </c>
-      <c r="B407" s="9" t="s">
+      <c r="B407" s="11" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="24" t="s">
+      <c r="A408" s="23" t="s">
         <v>704</v>
       </c>
-      <c r="B408" s="9" t="s">
+      <c r="B408" s="11" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="409" spans="1:2">
-      <c r="A409" s="8" t="s">
+      <c r="A409" s="10" t="s">
         <v>706</v>
       </c>
-      <c r="B409" s="9" t="s">
+      <c r="B409" s="11" t="s">
         <v>707</v>
       </c>
     </row>
     <row r="410" spans="1:2">
-      <c r="A410" s="8" t="s">
+      <c r="A410" s="10" t="s">
         <v>708</v>
       </c>
-      <c r="B410" s="9" t="s">
+      <c r="B410" s="11" t="s">
         <v>709</v>
       </c>
     </row>
     <row r="411" spans="1:2">
-      <c r="A411" s="8" t="s">
+      <c r="A411" s="10" t="s">
         <v>710</v>
       </c>
-      <c r="B411" s="9" t="s">
+      <c r="B411" s="11" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="412" spans="1:2">
-      <c r="A412" s="8" t="s">
+      <c r="A412" s="10" t="s">
         <v>711</v>
       </c>
-      <c r="B412" s="9" t="s">
+      <c r="B412" s="11" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="413" spans="1:2">
-      <c r="A413" s="8" t="s">
+      <c r="A413" s="10" t="s">
         <v>712</v>
       </c>
-      <c r="B413" s="9" t="s">
+      <c r="B413" s="11" t="s">
         <v>713</v>
       </c>
     </row>
     <row r="414" spans="1:2">
-      <c r="A414" s="8" t="s">
+      <c r="A414" s="10" t="s">
         <v>714</v>
       </c>
-      <c r="B414" s="9" t="s">
+      <c r="B414" s="11" t="s">
         <v>715</v>
       </c>
     </row>
     <row r="415" spans="1:2">
-      <c r="A415" s="8" t="s">
+      <c r="A415" s="10" t="s">
         <v>716</v>
       </c>
-      <c r="B415" s="9" t="s">
+      <c r="B415" s="11" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="416" spans="1:2">
-      <c r="A416" s="8" t="s">
+      <c r="A416" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="B416" s="9" t="s">
+      <c r="B416" s="11" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="417" spans="1:2">
-      <c r="A417" s="8" t="s">
+      <c r="A417" s="10" t="s">
         <v>720</v>
       </c>
-      <c r="B417" s="9" t="s">
+      <c r="B417" s="11" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="418" spans="1:2">
-      <c r="A418" s="8" t="s">
+      <c r="A418" s="10" t="s">
         <v>721</v>
       </c>
-      <c r="B418" s="9" t="s">
+      <c r="B418" s="11" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="419" spans="1:2">
-      <c r="A419" s="8" t="s">
+      <c r="A419" s="10" t="s">
         <v>723</v>
       </c>
-      <c r="B419" s="9" t="s">
+      <c r="B419" s="11" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="420" spans="1:2">
-      <c r="A420" s="8" t="s">
+      <c r="A420" s="10" t="s">
         <v>725</v>
       </c>
-      <c r="B420" s="9" t="s">
+      <c r="B420" s="11" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="421" spans="1:2">
-      <c r="A421" s="8" t="s">
+      <c r="A421" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="B421" s="9" t="s">
+      <c r="B421" s="11" t="s">
         <v>727</v>
       </c>
     </row>
     <row r="422" spans="1:2">
-      <c r="A422" s="8" t="s">
+      <c r="A422" s="10" t="s">
         <v>728</v>
       </c>
-      <c r="B422" s="9" t="s">
+      <c r="B422" s="11" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="423" spans="1:2">
-      <c r="A423" s="8" t="s">
+      <c r="A423" s="10" t="s">
         <v>729</v>
       </c>
-      <c r="B423" s="9" t="s">
+      <c r="B423" s="11" t="s">
         <v>729</v>
       </c>
     </row>
     <row r="424" spans="1:2">
-      <c r="A424" s="8" t="s">
+      <c r="A424" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="B424" s="9" t="s">
+      <c r="B424" s="11" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="425" spans="1:2">
-      <c r="A425" s="8" t="s">
+      <c r="A425" s="10" t="s">
         <v>732</v>
       </c>
-      <c r="B425" s="9" t="s">
+      <c r="B425" s="11" t="s">
         <v>733</v>
       </c>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="11" t="s">
+      <c r="A426" s="12" t="s">
         <v>734</v>
       </c>
-      <c r="B426" s="14" t="s">
+      <c r="B426" s="15" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="427" spans="1:2">
-      <c r="A427" s="11" t="s">
+      <c r="A427" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="B427" s="14" t="s">
+      <c r="B427" s="15" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="11" t="s">
+      <c r="A428" s="12" t="s">
         <v>738</v>
       </c>
-      <c r="B428" s="14" t="s">
+      <c r="B428" s="15" t="s">
         <v>739</v>
       </c>
     </row>
     <row r="429" spans="1:2">
-      <c r="A429" s="11" t="s">
+      <c r="A429" s="12" t="s">
         <v>740</v>
       </c>
-      <c r="B429" s="14" t="s">
+      <c r="B429" s="15" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="430" spans="1:2">
-      <c r="A430" s="11" t="s">
+      <c r="A430" s="12" t="s">
         <v>742</v>
       </c>
-      <c r="B430" s="14" t="s">
+      <c r="B430" s="15" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="11" t="s">
+      <c r="A431" s="12" t="s">
         <v>744</v>
       </c>
-      <c r="B431" s="14" t="s">
+      <c r="B431" s="15" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="432" spans="1:2">
-      <c r="A432" s="11" t="s">
+      <c r="A432" s="12" t="s">
         <v>746</v>
       </c>
-      <c r="B432" s="14" t="s">
+      <c r="B432" s="15" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="433" spans="1:2">
-      <c r="A433" s="11" t="s">
+      <c r="A433" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="B433" s="14" t="s">
+      <c r="B433" s="15" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="434" spans="1:2">
-      <c r="A434" s="11" t="s">
+      <c r="A434" s="12" t="s">
         <v>750</v>
       </c>
-      <c r="B434" s="14" t="s">
+      <c r="B434" s="15" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="435" spans="1:2">
-      <c r="A435" s="11" t="s">
+      <c r="A435" s="12" t="s">
         <v>752</v>
       </c>
-      <c r="B435" s="14" t="s">
+      <c r="B435" s="15" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="436" spans="1:2">
-      <c r="A436" s="11" t="s">
+      <c r="A436" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="B436" s="14" t="s">
+      <c r="B436" s="15" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="437" spans="1:2">
-      <c r="A437" s="11" t="s">
+      <c r="A437" s="12" t="s">
         <v>756</v>
       </c>
-      <c r="B437" s="14" t="s">
+      <c r="B437" s="15" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="438" spans="1:2">
-      <c r="A438" s="11" t="s">
+      <c r="A438" s="12" t="s">
         <v>758</v>
       </c>
-      <c r="B438" s="14" t="s">
+      <c r="B438" s="15" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="439" spans="1:2">
-      <c r="A439" s="11" t="s">
+      <c r="A439" s="12" t="s">
         <v>760</v>
       </c>
-      <c r="B439" s="14" t="s">
+      <c r="B439" s="15" t="s">
         <v>761</v>
       </c>
     </row>
     <row r="440" spans="1:2">
-      <c r="A440" s="8" t="s">
+      <c r="A440" s="10" t="s">
         <v>762</v>
       </c>
-      <c r="B440" s="9" t="s">
+      <c r="B440" s="11" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="441" spans="1:2">
-      <c r="A441" s="16" t="s">
+      <c r="A441" s="17" t="s">
         <v>764</v>
       </c>
-      <c r="B441" s="17" t="s">
+      <c r="B441" s="18" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="442" spans="1:2">
-      <c r="A442" s="16" t="s">
+      <c r="A442" s="17" t="s">
         <v>765</v>
       </c>
-      <c r="B442" s="17" t="s">
+      <c r="B442" s="18" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="443" spans="1:2">
-      <c r="A443" s="16" t="s">
+      <c r="A443" s="17" t="s">
         <v>767</v>
       </c>
-      <c r="B443" s="17" t="s">
+      <c r="B443" s="18" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="444" spans="1:2">
-      <c r="A444" s="16" t="s">
+      <c r="A444" s="17" t="s">
         <v>769</v>
       </c>
-      <c r="B444" s="17" t="s">
+      <c r="B444" s="18" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="445" spans="1:2">
-      <c r="A445" s="16" t="s">
+      <c r="A445" s="17" t="s">
         <v>770</v>
       </c>
-      <c r="B445" s="17" t="s">
+      <c r="B445" s="18" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="446" spans="1:2">
-      <c r="A446" s="16" t="s">
+      <c r="A446" s="17" t="s">
         <v>771</v>
       </c>
-      <c r="B446" s="33" t="s">
+      <c r="B446" s="31" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="447" spans="1:2">
-      <c r="A447" s="16" t="s">
+      <c r="A447" s="17" t="s">
         <v>773</v>
       </c>
-      <c r="B447" s="33" t="s">
+      <c r="B447" s="31" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="448" spans="1:2">
-      <c r="A448" s="16" t="s">
+      <c r="A448" s="17" t="s">
         <v>775</v>
       </c>
-      <c r="B448" s="17" t="s">
+      <c r="B448" s="18" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="449" spans="1:2">
-      <c r="A449" s="16" t="s">
+      <c r="A449" s="17" t="s">
         <v>777</v>
       </c>
-      <c r="B449" s="17" t="s">
+      <c r="B449" s="18" t="s">
         <v>778</v>
       </c>
     </row>
     <row r="450" spans="1:2">
-      <c r="A450" s="16" t="s">
+      <c r="A450" s="17" t="s">
         <v>564</v>
       </c>
-      <c r="B450" s="33" t="s">
+      <c r="B450" s="31" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="451" spans="1:2">
-      <c r="A451" s="16" t="s">
+      <c r="A451" s="17" t="s">
         <v>561</v>
       </c>
-      <c r="B451" s="33" t="s">
+      <c r="B451" s="31" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="452" spans="1:2">
-      <c r="A452" s="39" t="s">
+      <c r="A452" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="B452" s="40" t="s">
+      <c r="B452" s="38" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="453" spans="1:2">
-      <c r="A453" s="39" t="s">
+      <c r="A453" s="37" t="s">
         <v>779</v>
       </c>
-      <c r="B453" s="40" t="s">
+      <c r="B453" s="38" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="454" spans="1:2">
-      <c r="A454" s="16" t="s">
+      <c r="A454" s="17" t="s">
         <v>781</v>
       </c>
-      <c r="B454" s="41" t="s">
+      <c r="B454" s="39" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="455" spans="1:2">
-      <c r="A455" s="16" t="s">
+      <c r="A455" s="17" t="s">
         <v>782</v>
       </c>
-      <c r="B455" s="41" t="s">
+      <c r="B455" s="39" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="456" spans="1:2">
-      <c r="A456" s="16" t="s">
+      <c r="A456" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="B456" s="33" t="s">
+      <c r="B456" s="31" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="457" spans="1:2">
-      <c r="A457" s="16" t="s">
+      <c r="A457" s="17" t="s">
         <v>783</v>
       </c>
-      <c r="B457" s="33" t="s">
+      <c r="B457" s="31" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="458" spans="1:2">
-      <c r="A458" s="16" t="s">
+      <c r="A458" s="17" t="s">
         <v>784</v>
       </c>
-      <c r="B458" s="33" t="s">
+      <c r="B458" s="31" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="459" spans="1:2">
-      <c r="A459" s="16" t="s">
+      <c r="A459" s="17" t="s">
         <v>786</v>
       </c>
-      <c r="B459" s="17" t="s">
+      <c r="B459" s="18" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="460" spans="1:2">
-      <c r="A460" s="16" t="s">
+      <c r="A460" s="17" t="s">
         <v>788</v>
       </c>
-      <c r="B460" s="17" t="s">
+      <c r="B460" s="18" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="461" spans="1:2">
-      <c r="A461" s="16" t="s">
+      <c r="A461" s="17" t="s">
         <v>790</v>
       </c>
-      <c r="B461" s="17" t="s">
+      <c r="B461" s="18" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="462" spans="1:2">
-      <c r="A462" s="42" t="s">
+      <c r="A462" s="40" t="s">
         <v>359</v>
       </c>
-      <c r="B462" s="43">
+      <c r="B462" s="40">
         <v>2</v>
       </c>
     </row>
     <row r="463" spans="1:2">
-      <c r="A463" s="42" t="s">
+      <c r="A463" s="40" t="s">
         <v>360</v>
       </c>
-      <c r="B463" s="43">
+      <c r="B463" s="40">
         <v>3</v>
       </c>
     </row>
     <row r="464" spans="1:2">
-      <c r="A464" s="42" t="s">
+      <c r="A464" s="40" t="s">
         <v>361</v>
       </c>
-      <c r="B464" s="43">
+      <c r="B464" s="40">
         <v>4</v>
       </c>
     </row>
     <row r="465" spans="1:2">
-      <c r="A465" s="44" t="s">
+      <c r="A465" s="41" t="s">
         <v>354</v>
       </c>
-      <c r="B465" s="45">
+      <c r="B465" s="41">
         <v>150</v>
       </c>
     </row>
     <row r="466" spans="1:2">
-      <c r="A466" s="44" t="s">
+      <c r="A466" s="41" t="s">
         <v>355</v>
       </c>
-      <c r="B466" s="45">
+      <c r="B466" s="41">
         <v>250</v>
       </c>
     </row>
     <row r="467" spans="1:2">
-      <c r="A467" s="8" t="s">
+      <c r="A467" s="10" t="s">
         <v>792</v>
       </c>
-      <c r="B467" s="9" t="s">
+      <c r="B467" s="11" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="468" spans="1:2">
-      <c r="A468" s="8" t="s">
+      <c r="A468" s="10" t="s">
         <v>793</v>
       </c>
-      <c r="B468" s="9" t="s">
+      <c r="B468" s="11" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="469" spans="1:2">
-      <c r="A469" s="8" t="s">
+      <c r="A469" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="B469" s="9" t="s">
+      <c r="B469" s="11" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="470" spans="1:2">
-      <c r="A470" s="8" t="s">
+      <c r="A470" s="10" t="s">
         <v>797</v>
       </c>
-      <c r="B470" s="9" t="s">
+      <c r="B470" s="11" t="s">
         <v>797</v>
       </c>
     </row>
     <row r="471" spans="1:2">
-      <c r="A471" s="8" t="s">
+      <c r="A471" s="10" t="s">
         <v>798</v>
       </c>
-      <c r="B471" s="9" t="s">
+      <c r="B471" s="11" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="472" spans="1:2">
-      <c r="A472" s="8" t="s">
+      <c r="A472" s="10" t="s">
         <v>800</v>
       </c>
-      <c r="B472" s="9" t="s">
+      <c r="B472" s="11" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="473" spans="1:2">
-      <c r="A473" s="8" t="s">
+      <c r="A473" s="10" t="s">
         <v>801</v>
       </c>
-      <c r="B473" s="9" t="s">
+      <c r="B473" s="11" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="474" spans="1:2">
-      <c r="A474" s="8" t="s">
+      <c r="A474" s="10" t="s">
         <v>802</v>
       </c>
-      <c r="B474" s="9" t="s">
+      <c r="B474" s="11" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="475" spans="1:2">
-      <c r="A475" s="8" t="s">
+      <c r="A475" s="10" t="s">
         <v>803</v>
       </c>
-      <c r="B475" s="9" t="s">
+      <c r="B475" s="11" t="s">
         <v>804</v>
       </c>
     </row>
     <row r="476" spans="1:2">
-      <c r="A476" s="8" t="s">
+      <c r="A476" s="10" t="s">
         <v>759</v>
       </c>
-      <c r="B476" s="9" t="s">
+      <c r="B476" s="11" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="477" spans="1:2">
-      <c r="A477" s="8" t="s">
+      <c r="A477" s="10" t="s">
         <v>805</v>
       </c>
-      <c r="B477" s="9" t="s">
+      <c r="B477" s="11" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="478" spans="1:2">
-      <c r="A478" s="8" t="s">
+      <c r="A478" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="B478" s="9" t="s">
+      <c r="B478" s="11" t="s">
         <v>808</v>
       </c>
     </row>
     <row r="479" spans="1:2">
-      <c r="A479" s="8" t="s">
+      <c r="A479" s="10" t="s">
         <v>809</v>
       </c>
-      <c r="B479" s="36" t="s">
+      <c r="B479" s="34" t="s">
         <v>809</v>
       </c>
     </row>
     <row r="480" spans="1:2">
-      <c r="A480" s="8" t="s">
+      <c r="A480" s="10" t="s">
         <v>810</v>
       </c>
-      <c r="B480" s="9" t="s">
+      <c r="B480" s="11" t="s">
         <v>811</v>
       </c>
     </row>
     <row r="481" spans="1:2">
-      <c r="A481" s="8" t="s">
+      <c r="A481" s="10" t="s">
         <v>812</v>
       </c>
-      <c r="B481" s="9" t="s">
+      <c r="B481" s="11" t="s">
         <v>813</v>
       </c>
     </row>
     <row r="482" spans="1:2">
-      <c r="A482" s="8" t="s">
+      <c r="A482" s="10" t="s">
         <v>814</v>
       </c>
-      <c r="B482" s="9" t="s">
+      <c r="B482" s="11" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="483" spans="1:2">
-      <c r="A483" s="8" t="s">
+      <c r="A483" s="10" t="s">
         <v>815</v>
       </c>
-      <c r="B483" s="9" t="s">
+      <c r="B483" s="11" t="s">
         <v>816</v>
       </c>
     </row>
     <row r="484" spans="1:2">
-      <c r="A484" s="8" t="s">
+      <c r="A484" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="B484" s="9" t="s">
+      <c r="B484" s="11" t="s">
         <v>818</v>
       </c>
     </row>
     <row r="485" spans="1:2">
-      <c r="A485" s="8" t="s">
+      <c r="A485" s="10" t="s">
         <v>819</v>
       </c>
-      <c r="B485" s="9" t="s">
+      <c r="B485" s="11" t="s">
         <v>820</v>
       </c>
     </row>
     <row r="486" spans="1:2">
-      <c r="A486" s="8" t="s">
+      <c r="A486" s="10" t="s">
         <v>821</v>
       </c>
-      <c r="B486" s="9" t="s">
+      <c r="B486" s="11" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="487" spans="1:2">
-      <c r="A487" s="8" t="s">
+      <c r="A487" s="10" t="s">
         <v>823</v>
       </c>
-      <c r="B487" s="9" t="s">
+      <c r="B487" s="11" t="s">
         <v>808</v>
       </c>
     </row>
     <row r="488" spans="1:2">
-      <c r="A488" s="8" t="s">
+      <c r="A488" s="10" t="s">
         <v>824</v>
       </c>
-      <c r="B488" s="9" t="s">
+      <c r="B488" s="11" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="489" spans="1:2">
-      <c r="A489" s="8" t="s">
+      <c r="A489" s="10" t="s">
         <v>825</v>
       </c>
-      <c r="B489" s="9" t="s">
+      <c r="B489" s="11" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="490" spans="1:2">
-      <c r="A490" s="8" t="s">
+      <c r="A490" s="10" t="s">
         <v>826</v>
       </c>
-      <c r="B490" s="9" t="s">
+      <c r="B490" s="11" t="s">
         <v>827</v>
       </c>
     </row>
     <row r="491" spans="1:2">
-      <c r="A491" s="8" t="s">
+      <c r="A491" s="10" t="s">
         <v>828</v>
       </c>
-      <c r="B491" s="9" t="s">
+      <c r="B491" s="11" t="s">
         <v>829</v>
       </c>
     </row>
     <row r="492" spans="1:2">
-      <c r="A492" s="8" t="s">
+      <c r="A492" s="10" t="s">
         <v>830</v>
       </c>
-      <c r="B492" s="9" t="s">
+      <c r="B492" s="11" t="s">
         <v>831</v>
       </c>
     </row>
     <row r="493" spans="1:2">
-      <c r="A493" s="8" t="s">
+      <c r="A493" s="10" t="s">
         <v>832</v>
       </c>
-      <c r="B493" s="9" t="s">
+      <c r="B493" s="11" t="s">
         <v>833</v>
       </c>
     </row>
     <row r="494" spans="1:2">
-      <c r="A494" s="8" t="s">
+      <c r="A494" s="10" t="s">
         <v>834</v>
       </c>
-      <c r="B494" s="9" t="s">
+      <c r="B494" s="11" t="s">
         <v>835</v>
       </c>
     </row>
     <row r="495" spans="1:2">
-      <c r="A495" s="8" t="s">
+      <c r="A495" s="10" t="s">
         <v>836</v>
       </c>
-      <c r="B495" s="9" t="s">
+      <c r="B495" s="11" t="s">
         <v>837</v>
       </c>
     </row>
     <row r="496" spans="1:2">
-      <c r="A496" s="8" t="s">
+      <c r="A496" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="B496" s="9" t="s">
+      <c r="B496" s="11" t="s">
         <v>839</v>
       </c>
     </row>
     <row r="497" spans="1:2">
-      <c r="A497" s="8" t="s">
+      <c r="A497" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="B497" s="9" t="s">
+      <c r="B497" s="11" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="498" spans="1:2">
-      <c r="A498" s="8" t="s">
+      <c r="A498" s="10" t="s">
         <v>842</v>
       </c>
-      <c r="B498" s="9" t="s">
+      <c r="B498" s="11" t="s">
         <v>843</v>
       </c>
     </row>
     <row r="499" spans="1:2">
-      <c r="A499" s="8" t="s">
+      <c r="A499" s="10" t="s">
         <v>844</v>
       </c>
-      <c r="B499" s="9" t="s">
+      <c r="B499" s="11" t="s">
         <v>845</v>
       </c>
     </row>
     <row r="500" spans="1:2">
-      <c r="A500" s="8" t="s">
+      <c r="A500" s="10" t="s">
         <v>846</v>
       </c>
-      <c r="B500" s="9" t="s">
+      <c r="B500" s="11" t="s">
         <v>847</v>
       </c>
     </row>
     <row r="501" spans="1:2">
-      <c r="A501" s="8" t="s">
+      <c r="A501" s="10" t="s">
         <v>848</v>
       </c>
-      <c r="B501" s="9" t="s">
+      <c r="B501" s="11" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="502" spans="1:2">
-      <c r="A502" s="8" t="s">
+      <c r="A502" s="10" t="s">
         <v>850</v>
       </c>
-      <c r="B502" s="9" t="s">
+      <c r="B502" s="11" t="s">
         <v>851</v>
       </c>
     </row>
     <row r="503" spans="1:2">
-      <c r="A503" s="8" t="s">
+      <c r="A503" s="10" t="s">
         <v>852</v>
       </c>
-      <c r="B503" s="9" t="s">
+      <c r="B503" s="11" t="s">
         <v>853</v>
       </c>
     </row>
     <row r="504" spans="1:2">
-      <c r="A504" s="8" t="s">
+      <c r="A504" s="10" t="s">
         <v>854</v>
       </c>
-      <c r="B504" s="9" t="s">
+      <c r="B504" s="11" t="s">
         <v>855</v>
       </c>
     </row>
     <row r="505" spans="1:2">
-      <c r="A505" s="8" t="s">
+      <c r="A505" s="10" t="s">
         <v>856</v>
       </c>
-      <c r="B505" s="9" t="s">
+      <c r="B505" s="11" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="506" spans="1:2">
-      <c r="A506" s="8" t="s">
+      <c r="A506" s="10" t="s">
         <v>858</v>
       </c>
-      <c r="B506" s="9" t="s">
+      <c r="B506" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="507" spans="1:2">
-      <c r="A507" s="8" t="s">
+      <c r="A507" s="10" t="s">
         <v>859</v>
       </c>
-      <c r="B507" s="9" t="s">
+      <c r="B507" s="11" t="s">
         <v>860</v>
       </c>
     </row>
     <row r="508" spans="1:2">
-      <c r="A508" s="8" t="s">
+      <c r="A508" s="10" t="s">
         <v>861</v>
       </c>
-      <c r="B508" s="9" t="s">
+      <c r="B508" s="11" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="509" spans="1:2">
-      <c r="A509" s="8" t="s">
+      <c r="A509" s="10" t="s">
         <v>862</v>
       </c>
-      <c r="B509" s="9" t="s">
+      <c r="B509" s="11" t="s">
         <v>863</v>
       </c>
     </row>
     <row r="510" spans="1:2">
-      <c r="A510" s="8" t="s">
+      <c r="A510" s="10" t="s">
         <v>864</v>
       </c>
-      <c r="B510" s="9" t="s">
+      <c r="B510" s="11" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="511" spans="1:2">
-      <c r="A511" s="8" t="s">
+      <c r="A511" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="B511" s="8" t="s">
+      <c r="B511" s="10" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="512" spans="1:2">
-      <c r="A512" s="24" t="s">
+      <c r="A512" s="23" t="s">
         <v>866</v>
       </c>
-      <c r="B512" s="9" t="s">
+      <c r="B512" s="11" t="s">
         <v>867</v>
       </c>
     </row>
     <row r="513" spans="1:2">
-      <c r="A513" s="24" t="s">
+      <c r="A513" s="23" t="s">
         <v>868</v>
       </c>
-      <c r="B513" s="9" t="s">
+      <c r="B513" s="11" t="s">
         <v>869</v>
       </c>
     </row>
     <row r="514" spans="1:2">
-      <c r="A514" s="24" t="s">
+      <c r="A514" s="23" t="s">
         <v>870</v>
       </c>
-      <c r="B514" s="9" t="s">
+      <c r="B514" s="11" t="s">
         <v>871</v>
       </c>
     </row>
     <row r="515" spans="1:2">
-      <c r="A515" s="24" t="s">
+      <c r="A515" s="23" t="s">
         <v>872</v>
       </c>
-      <c r="B515" s="9" t="s">
+      <c r="B515" s="11" t="s">
         <v>873</v>
       </c>
     </row>
     <row r="516" spans="1:2">
-      <c r="A516" s="24" t="s">
+      <c r="A516" s="23" t="s">
         <v>874</v>
       </c>
-      <c r="B516" s="9" t="s">
+      <c r="B516" s="11" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="517" spans="1:2">
-      <c r="A517" s="24" t="s">
+      <c r="A517" s="23" t="s">
         <v>876</v>
       </c>
-      <c r="B517" s="9" t="s">
+      <c r="B517" s="11" t="s">
         <v>877</v>
       </c>
     </row>
     <row r="518" spans="1:2">
-      <c r="A518" s="24" t="s">
+      <c r="A518" s="23" t="s">
         <v>878</v>
       </c>
-      <c r="B518" s="9" t="s">
+      <c r="B518" s="11" t="s">
         <v>879</v>
       </c>
     </row>
     <row r="519" spans="1:2">
-      <c r="A519" s="24" t="s">
+      <c r="A519" s="23" t="s">
         <v>880</v>
       </c>
-      <c r="B519" s="9" t="s">
+      <c r="B519" s="11" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="520" spans="1:2">
-      <c r="A520" s="24" t="s">
+      <c r="A520" s="23" t="s">
         <v>882</v>
       </c>
-      <c r="B520" s="9" t="s">
+      <c r="B520" s="11" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="521" spans="1:2">
-      <c r="A521" s="24" t="s">
+      <c r="A521" s="23" t="s">
         <v>884</v>
       </c>
-      <c r="B521" s="9" t="s">
+      <c r="B521" s="11" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="522" spans="1:2">
-      <c r="A522" s="24" t="s">
+      <c r="A522" s="23" t="s">
         <v>886</v>
       </c>
-      <c r="B522" s="9" t="s">
+      <c r="B522" s="11" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="523" spans="1:2">
-      <c r="A523" s="24" t="s">
+      <c r="A523" s="23" t="s">
         <v>888</v>
       </c>
-      <c r="B523" s="9" t="s">
+      <c r="B523" s="11" t="s">
         <v>889</v>
       </c>
     </row>
     <row r="524" spans="1:2">
-      <c r="A524" s="24" t="s">
+      <c r="A524" s="23" t="s">
         <v>890</v>
       </c>
-      <c r="B524" s="9" t="s">
+      <c r="B524" s="11" t="s">
         <v>891</v>
       </c>
     </row>
     <row r="525" spans="1:2">
-      <c r="A525" s="24" t="s">
+      <c r="A525" s="23" t="s">
         <v>892</v>
       </c>
-      <c r="B525" s="9" t="s">
+      <c r="B525" s="11" t="s">
         <v>893</v>
       </c>
     </row>
     <row r="526" spans="1:2">
-      <c r="A526" s="24" t="s">
+      <c r="A526" s="23" t="s">
         <v>894</v>
       </c>
-      <c r="B526" s="9" t="s">
+      <c r="B526" s="11" t="s">
         <v>895</v>
       </c>
     </row>
     <row r="527" spans="1:2">
-      <c r="A527" s="24" t="s">
+      <c r="A527" s="23" t="s">
         <v>896</v>
       </c>
-      <c r="B527" s="9" t="s">
+      <c r="B527" s="11" t="s">
         <v>897</v>
       </c>
     </row>
     <row r="528" spans="1:2">
-      <c r="A528" s="24" t="s">
+      <c r="A528" s="23" t="s">
         <v>898</v>
       </c>
-      <c r="B528" s="9" t="s">
+      <c r="B528" s="11" t="s">
         <v>899</v>
       </c>
     </row>
     <row r="529" spans="1:2">
-      <c r="A529" s="24" t="s">
+      <c r="A529" s="23" t="s">
         <v>900</v>
       </c>
-      <c r="B529" s="9" t="s">
+      <c r="B529" s="11" t="s">
         <v>901</v>
       </c>
     </row>
     <row r="530" spans="1:2">
-      <c r="A530" s="24" t="s">
+      <c r="A530" s="23" t="s">
         <v>902</v>
       </c>
-      <c r="B530" s="9" t="s">
+      <c r="B530" s="11" t="s">
         <v>903</v>
       </c>
     </row>
     <row r="531" spans="1:2">
-      <c r="A531" s="24" t="s">
+      <c r="A531" s="23" t="s">
         <v>904</v>
       </c>
-      <c r="B531" s="9" t="s">
+      <c r="B531" s="11" t="s">
         <v>905</v>
       </c>
     </row>
     <row r="532" spans="1:2">
-      <c r="A532" s="24" t="s">
+      <c r="A532" s="23" t="s">
         <v>906</v>
       </c>
-      <c r="B532" s="9" t="s">
+      <c r="B532" s="11" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="533" spans="1:2">
-      <c r="A533" s="24" t="s">
+      <c r="A533" s="23" t="s">
         <v>908</v>
       </c>
-      <c r="B533" s="9" t="s">
+      <c r="B533" s="11" t="s">
         <v>909</v>
       </c>
     </row>
     <row r="534" spans="1:2">
-      <c r="A534" s="24" t="s">
+      <c r="A534" s="23" t="s">
         <v>910</v>
       </c>
-      <c r="B534" s="9" t="s">
+      <c r="B534" s="11" t="s">
         <v>911</v>
       </c>
     </row>
     <row r="535" spans="1:2">
-      <c r="A535" s="24" t="s">
+      <c r="A535" s="23" t="s">
         <v>912</v>
       </c>
-      <c r="B535" s="9" t="s">
+      <c r="B535" s="11" t="s">
         <v>913</v>
       </c>
     </row>
     <row r="536" spans="1:2">
-      <c r="A536" s="24" t="s">
+      <c r="A536" s="23" t="s">
         <v>914</v>
       </c>
-      <c r="B536" s="9" t="s">
+      <c r="B536" s="11" t="s">
         <v>915</v>
       </c>
     </row>
     <row r="537" spans="1:2">
-      <c r="A537" s="24" t="s">
+      <c r="A537" s="23" t="s">
         <v>916</v>
       </c>
-      <c r="B537" s="9" t="s">
+      <c r="B537" s="11" t="s">
         <v>917</v>
       </c>
     </row>
     <row r="538" spans="1:2">
-      <c r="A538" s="24" t="s">
+      <c r="A538" s="23" t="s">
         <v>918</v>
       </c>
-      <c r="B538" s="9" t="s">
+      <c r="B538" s="11" t="s">
         <v>919</v>
       </c>
     </row>
     <row r="539" spans="1:2">
-      <c r="A539" s="24" t="s">
+      <c r="A539" s="23" t="s">
         <v>920</v>
       </c>
-      <c r="B539" s="9" t="s">
+      <c r="B539" s="11" t="s">
         <v>921</v>
       </c>
     </row>
     <row r="540" spans="1:2">
-      <c r="A540" s="24" t="s">
+      <c r="A540" s="23" t="s">
         <v>922</v>
       </c>
-      <c r="B540" s="9" t="s">
+      <c r="B540" s="11" t="s">
         <v>923</v>
       </c>
     </row>
     <row r="541" spans="1:2">
-      <c r="A541" s="24" t="s">
+      <c r="A541" s="23" t="s">
         <v>924</v>
       </c>
-      <c r="B541" s="9" t="s">
+      <c r="B541" s="11" t="s">
         <v>925</v>
       </c>
     </row>
     <row r="542" spans="1:2">
-      <c r="A542" s="24" t="s">
+      <c r="A542" s="23" t="s">
         <v>926</v>
       </c>
-      <c r="B542" s="9" t="s">
+      <c r="B542" s="11" t="s">
         <v>927</v>
       </c>
     </row>
     <row r="543" spans="1:2">
-      <c r="A543" s="24" t="s">
+      <c r="A543" s="23" t="s">
         <v>928</v>
       </c>
-      <c r="B543" s="9" t="s">
+      <c r="B543" s="11" t="s">
         <v>929</v>
       </c>
     </row>
     <row r="544" spans="1:2">
-      <c r="A544" s="46" t="s">
+      <c r="A544" s="6" t="s">
         <v>930</v>
       </c>
-      <c r="B544" s="9" t="s">
+      <c r="B544" s="11" t="s">
         <v>931</v>
       </c>
     </row>
     <row r="545" spans="1:2">
-      <c r="A545" s="24" t="s">
+      <c r="A545" s="23" t="s">
         <v>932</v>
       </c>
-      <c r="B545" s="9" t="s">
+      <c r="B545" s="11" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="546" spans="1:2">
-      <c r="A546" s="47" t="s">
+      <c r="A546" s="10" t="s">
         <v>934</v>
       </c>
-      <c r="B546" s="9" t="s">
+      <c r="B546" s="11" t="s">
         <v>935</v>
       </c>
     </row>
     <row r="547" spans="1:2">
-      <c r="A547" s="47" t="s">
+      <c r="A547" s="10" t="s">
         <v>936</v>
       </c>
-      <c r="B547" s="9" t="s">
+      <c r="B547" s="11" t="s">
         <v>937</v>
       </c>
     </row>
     <row r="548" spans="1:2">
-      <c r="A548" s="47" t="s">
+      <c r="A548" s="10" t="s">
         <v>938</v>
       </c>
-      <c r="B548" s="9" t="s">
+      <c r="B548" s="11" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="549" spans="1:2">
-      <c r="A549" s="48" t="s">
+      <c r="A549" s="23" t="s">
         <v>940</v>
       </c>
-      <c r="B549" s="9" t="s">
+      <c r="B549" s="11" t="s">
         <v>941</v>
       </c>
     </row>
     <row r="550" spans="1:2">
-      <c r="A550" s="48" t="s">
+      <c r="A550" s="23" t="s">
         <v>942</v>
       </c>
-      <c r="B550" s="9" t="s">
+      <c r="B550" s="11" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="551" spans="1:2">
-      <c r="A551" s="47" t="s">
+      <c r="A551" s="10" t="s">
         <v>944</v>
       </c>
-      <c r="B551" s="49" t="s">
+      <c r="B551" s="11" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="552" spans="1:2">
-      <c r="A552" s="48" t="s">
+      <c r="A552" s="23" t="s">
         <v>945</v>
       </c>
-      <c r="B552" s="9" t="s">
+      <c r="B552" s="11" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="553" spans="1:2">
-      <c r="A553" s="48" t="s">
+      <c r="A553" s="23" t="s">
         <v>947</v>
       </c>
-      <c r="B553" s="9" t="s">
+      <c r="B553" s="11" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="554" spans="1:2">
-      <c r="A554" s="47" t="s">
+      <c r="A554" s="10" t="s">
         <v>948</v>
       </c>
-      <c r="B554" s="9" t="s">
+      <c r="B554" s="11" t="s">
         <v>949</v>
       </c>
     </row>
     <row r="555" spans="1:2">
-      <c r="A555" s="24" t="s">
+      <c r="A555" s="23" t="s">
         <v>950</v>
       </c>
-      <c r="B555" s="9" t="s">
+      <c r="B555" s="11" t="s">
         <v>951</v>
       </c>
     </row>
     <row r="556" spans="1:2">
-      <c r="A556" s="24" t="s">
+      <c r="A556" s="23" t="s">
         <v>952</v>
       </c>
-      <c r="B556" s="9" t="s">
+      <c r="B556" s="11" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="557" spans="1:2">
-      <c r="A557" s="48" t="s">
+      <c r="A557" s="23" t="s">
         <v>953</v>
       </c>
-      <c r="B557" s="9" t="s">
+      <c r="B557" s="11" t="s">
         <v>954</v>
       </c>
     </row>
     <row r="558" spans="1:2">
-      <c r="A558" s="24" t="s">
+      <c r="A558" s="23" t="s">
         <v>955</v>
       </c>
-      <c r="B558" s="9" t="s">
+      <c r="B558" s="11" t="s">
         <v>956</v>
       </c>
     </row>
     <row r="559" spans="1:2">
-      <c r="A559" s="24" t="s">
+      <c r="A559" s="23" t="s">
         <v>957</v>
       </c>
-      <c r="B559" s="9" t="s">
+      <c r="B559" s="11" t="s">
         <v>958</v>
       </c>
     </row>
     <row r="560" spans="1:2">
-      <c r="A560" s="24" t="s">
+      <c r="A560" s="23" t="s">
         <v>959</v>
       </c>
-      <c r="B560" s="9" t="s">
+      <c r="B560" s="11" t="s">
         <v>960</v>
       </c>
     </row>
     <row r="561" spans="1:2">
-      <c r="A561" s="24" t="s">
+      <c r="A561" s="23" t="s">
         <v>961</v>
       </c>
-      <c r="B561" s="9" t="s">
+      <c r="B561" s="11" t="s">
         <v>962</v>
       </c>
     </row>
     <row r="562" spans="1:2">
-      <c r="A562" s="24" t="s">
+      <c r="A562" s="23" t="s">
         <v>963</v>
       </c>
-      <c r="B562" s="9" t="s">
+      <c r="B562" s="11" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="563" spans="1:2">
-      <c r="A563" s="8" t="s">
+      <c r="A563" s="10" t="s">
         <v>964</v>
       </c>
-      <c r="B563" s="9" t="s">
+      <c r="B563" s="11" t="s">
         <v>965</v>
       </c>
     </row>
     <row r="564" spans="1:2">
-      <c r="A564" s="8" t="s">
+      <c r="A564" s="10" t="s">
         <v>966</v>
       </c>
-      <c r="B564" s="9" t="s">
+      <c r="B564" s="11" t="s">
         <v>967</v>
       </c>
     </row>
     <row r="565" spans="1:2">
-      <c r="A565" s="8" t="s">
+      <c r="A565" s="10" t="s">
         <v>968</v>
       </c>
-      <c r="B565" s="9" t="s">
+      <c r="B565" s="11" t="s">
         <v>968</v>
       </c>
     </row>
     <row r="566" spans="1:2">
-      <c r="A566" s="50" t="s">
+      <c r="A566" s="10" t="s">
         <v>969</v>
       </c>
-      <c r="B566" s="51" t="s">
+      <c r="B566" s="11" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="567" spans="1:2">
-      <c r="A567" s="50" t="s">
+      <c r="A567" s="10" t="s">
         <v>971</v>
       </c>
-      <c r="B567" s="51" t="s">
+      <c r="B567" s="11" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="568" spans="1:2">
-      <c r="A568" s="50" t="s">
+      <c r="A568" s="10" t="s">
         <v>972</v>
       </c>
-      <c r="B568" s="51" t="s">
+      <c r="B568" s="11" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="569" spans="1:2">
-      <c r="A569" s="50" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B569" s="51" t="s">
-        <v>1004</v>
+      <c r="A569" s="10" t="s">
+        <v>973</v>
+      </c>
+      <c r="B569" s="11" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="B570" s="11" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="B571" s="11" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" s="10" t="s">
+        <v>977</v>
+      </c>
+      <c r="B572" s="11" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" s="10" t="s">
+        <v>978</v>
+      </c>
+      <c r="B573" s="11" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" s="10" t="s">
+        <v>979</v>
+      </c>
+      <c r="B574" s="11" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" s="10" t="s">
+        <v>980</v>
+      </c>
+      <c r="B575" s="11" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" s="10" t="s">
+        <v>981</v>
+      </c>
+      <c r="B576" s="11" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" s="10" t="s">
+        <v>982</v>
+      </c>
+      <c r="B577" s="11" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578" s="10" t="s">
+        <v>983</v>
+      </c>
+      <c r="B578" s="11" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579" s="10" t="s">
+        <v>984</v>
+      </c>
+      <c r="B579" s="11" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580" s="10" t="s">
+        <v>985</v>
+      </c>
+      <c r="B580" s="11" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581" s="10" t="s">
+        <v>986</v>
+      </c>
+      <c r="B581" s="11" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582" s="10" t="s">
+        <v>987</v>
+      </c>
+      <c r="B582" s="11" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583" s="10" t="s">
+        <v>988</v>
+      </c>
+      <c r="B583" s="11" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584" s="10" t="s">
+        <v>989</v>
+      </c>
+      <c r="B584" s="11" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585" s="10" t="s">
+        <v>991</v>
+      </c>
+      <c r="B585" s="11" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586" s="10" t="s">
+        <v>993</v>
+      </c>
+      <c r="B586" s="11" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587" s="10" t="s">
+        <v>995</v>
+      </c>
+      <c r="B587" s="11" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588" s="10" t="s">
+        <v>997</v>
+      </c>
+      <c r="B588" s="11" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589" s="42" t="s">
+        <v>999</v>
+      </c>
+      <c r="B589" s="43" t="s">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.8518518518519" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8578,135 +9679,152 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="108.95" customHeight="1">
+    <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>973</v>
+        <v>1001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="114" customHeight="1">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>975</v>
+        <v>1003</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="80.25" customHeight="1">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>977</v>
+        <v>1005</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="69.75" customHeight="1">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="5" ht="69.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>979</v>
+        <v>1007</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="51.75" customHeight="1">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="6" ht="51.75" customHeight="1" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>981</v>
+        <v>1009</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>983</v>
+        <v>1011</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>985</v>
+        <v>1013</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="39" customHeight="1">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="9" ht="39" customHeight="1" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>987</v>
+        <v>1015</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="22.5" customHeight="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>989</v>
+        <v>1017</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="18" customHeight="1">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>991</v>
+        <v>1019</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="26.25" customHeight="1">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="12" ht="26.25" customHeight="1" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>993</v>
+        <v>1021</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="28.5" customHeight="1">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="13" ht="28.5" customHeight="1" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>995</v>
+        <v>1023</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="24" customHeight="1">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>997</v>
+        <v>1025</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="36" customHeight="1">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>999</v>
+        <v>1027</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="45" customHeight="1">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>1001</v>
+        <v>1029</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="17" ht="374.4" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="18" ht="409.5" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="19" ht="409.5" spans="1:2">
+      <c r="A19" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>1036</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
     <sheet name="DBData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="1037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="1047">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -3823,18 +3823,42 @@
    AND pah_doc_no ='${POANO}'
    AND PALC_PROD_ID = '${ItemId}'</t>
   </si>
+  <si>
+    <t>EncashmentRequestDate</t>
+  </si>
+  <si>
+    <t>01-06-2024</t>
+  </si>
+  <si>
+    <t>EncashmentLeaveLOV</t>
+  </si>
+  <si>
+    <t>EARNED LEAVE</t>
+  </si>
+  <si>
+    <t>EncashDaysField</t>
+  </si>
+  <si>
+    <t>EncashReasonField</t>
+  </si>
+  <si>
+    <t>ENCASHMENT</t>
+  </si>
+  <si>
+    <t>CompOffDays</t>
+  </si>
+  <si>
+    <t>CompOffReferenceField</t>
+  </si>
+  <si>
+    <t>CompOff Request</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3875,151 +3899,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4044,194 +3931,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -4267,255 +3968,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="53">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -4553,15 +4012,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4581,11 +4040,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4599,75 +4058,28 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="53">
+  <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal 2" xfId="49"/>
-    <cellStyle name="Normal 2 2" xfId="50"/>
-    <cellStyle name="Normal 2 3" xfId="51"/>
-    <cellStyle name="Normal 3" xfId="52"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2 2" xfId="2"/>
+    <cellStyle name="Normal 2 3" xfId="3"/>
+    <cellStyle name="Normal 3" xfId="4"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4929,17 +4341,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B589"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B595"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="62.712962962963" style="6" customWidth="1"/>
-    <col min="2" max="2" width="59.8518518518519" style="7" customWidth="1"/>
+    <col min="1" max="1" width="62.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="59.85546875" style="7" customWidth="1"/>
     <col min="3" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
@@ -9655,19 +9067,65 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="590" spans="1:2">
+      <c r="A590" s="42" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B590" s="43" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591" s="42" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B591" s="43" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592" s="42" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B592" s="43" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593" s="42" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B593" s="43" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594" s="42" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B594" s="43" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" s="42" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B595" s="43" t="s">
+        <v>1046</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.8518518518519" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9679,7 +9137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="108.95" customHeight="1" spans="1:2">
+    <row r="2" spans="1:2" ht="108.95" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1001</v>
       </c>
@@ -9687,7 +9145,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="3" ht="114" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="114" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>1003</v>
       </c>
@@ -9695,7 +9153,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="4" ht="80.25" customHeight="1" spans="1:2">
+    <row r="4" spans="1:2" ht="80.25" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>1005</v>
       </c>
@@ -9703,7 +9161,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="5" ht="69.75" customHeight="1" spans="1:2">
+    <row r="5" spans="1:2" ht="69.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>1007</v>
       </c>
@@ -9711,7 +9169,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="6" ht="51.75" customHeight="1" spans="1:2">
+    <row r="6" spans="1:2" ht="51.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>1009</v>
       </c>
@@ -9719,7 +9177,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:2">
+    <row r="7" spans="1:2" ht="30" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>1011</v>
       </c>
@@ -9727,7 +9185,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" spans="1:2">
+    <row r="8" spans="1:2" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>1013</v>
       </c>
@@ -9735,7 +9193,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="9" ht="39" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2" ht="39" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>1015</v>
       </c>
@@ -9743,7 +9201,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1" spans="1:2">
+    <row r="10" spans="1:2" ht="22.5" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>1017</v>
       </c>
@@ -9751,7 +9209,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:2">
+    <row r="11" spans="1:2" ht="18" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>1019</v>
       </c>
@@ -9759,7 +9217,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="12" ht="26.25" customHeight="1" spans="1:2">
+    <row r="12" spans="1:2" ht="26.25" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>1021</v>
       </c>
@@ -9767,7 +9225,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="13" ht="28.5" customHeight="1" spans="1:2">
+    <row r="13" spans="1:2" ht="28.5" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>1023</v>
       </c>
@@ -9775,7 +9233,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:2">
+    <row r="14" spans="1:2" ht="24" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>1025</v>
       </c>
@@ -9783,7 +9241,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1" spans="1:2">
+    <row r="15" spans="1:2" ht="36" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>1027</v>
       </c>
@@ -9791,7 +9249,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="16" ht="45" customHeight="1" spans="1:2">
+    <row r="16" spans="1:2" ht="45" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>1029</v>
       </c>
@@ -9799,7 +9257,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="17" ht="374.4" spans="1:2">
+    <row r="17" spans="1:2" ht="405">
       <c r="A17" s="2" t="s">
         <v>1031</v>
       </c>
@@ -9807,7 +9265,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="18" ht="409.5" spans="1:2">
+    <row r="18" spans="1:2" ht="409.5">
       <c r="A18" s="2" t="s">
         <v>1033</v>
       </c>
@@ -9815,7 +9273,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="19" ht="409.5" spans="1:2">
+    <row r="19" spans="1:2" ht="409.5">
       <c r="A19" s="4" t="s">
         <v>1035</v>
       </c>
@@ -9825,6 +9283,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="9120"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
     <sheet name="DBData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="1047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="1060">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -3031,6 +3031,75 @@
   </si>
   <si>
     <t>Final Purchase Order &amp; GRN</t>
+  </si>
+  <si>
+    <t>EncashmentRequestDate</t>
+  </si>
+  <si>
+    <t>01-06-2024</t>
+  </si>
+  <si>
+    <t>EncashmentLeaveLOV</t>
+  </si>
+  <si>
+    <t>EARNED LEAVE</t>
+  </si>
+  <si>
+    <t>EncashDaysField</t>
+  </si>
+  <si>
+    <t>EncashReasonField</t>
+  </si>
+  <si>
+    <t>ENCASHMENT</t>
+  </si>
+  <si>
+    <t>CompOffDays</t>
+  </si>
+  <si>
+    <t>CompOffReferenceField</t>
+  </si>
+  <si>
+    <t>CompOff Request</t>
+  </si>
+  <si>
+    <t>EmpDependentName</t>
+  </si>
+  <si>
+    <t>EmpAddress</t>
+  </si>
+  <si>
+    <t>Gwl Address, Tamil Nadu, India</t>
+  </si>
+  <si>
+    <t>EmpInstitute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GWL Emp Institute </t>
+  </si>
+  <si>
+    <t>SalaryOption</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>FirstNameOptionText</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>LastNameOptionText</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>NationalityOptionText</t>
+  </si>
+  <si>
+    <t>Nationality</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -3823,42 +3892,18 @@
    AND pah_doc_no ='${POANO}'
    AND PALC_PROD_ID = '${ItemId}'</t>
   </si>
-  <si>
-    <t>EncashmentRequestDate</t>
-  </si>
-  <si>
-    <t>01-06-2024</t>
-  </si>
-  <si>
-    <t>EncashmentLeaveLOV</t>
-  </si>
-  <si>
-    <t>EARNED LEAVE</t>
-  </si>
-  <si>
-    <t>EncashDaysField</t>
-  </si>
-  <si>
-    <t>EncashReasonField</t>
-  </si>
-  <si>
-    <t>ENCASHMENT</t>
-  </si>
-  <si>
-    <t>CompOffDays</t>
-  </si>
-  <si>
-    <t>CompOffReferenceField</t>
-  </si>
-  <si>
-    <t>CompOff Request</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3899,14 +3944,151 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3931,8 +4113,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -3968,22 +4336,260 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4012,15 +4618,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4040,11 +4646,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4058,28 +4664,75 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 2 2" xfId="2"/>
-    <cellStyle name="Normal 2 3" xfId="3"/>
-    <cellStyle name="Normal 3" xfId="4"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal 2" xfId="49"/>
+    <cellStyle name="Normal 2 2" xfId="50"/>
+    <cellStyle name="Normal 2 3" xfId="51"/>
+    <cellStyle name="Normal 3" xfId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4341,4791 +4994,4849 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B595"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B602"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="62.7109375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="59.85546875" style="7" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="62.7090909090909" style="4" customWidth="1"/>
+    <col min="2" max="2" width="59.8545454545455" style="5" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="9" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="9" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="9" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="9" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="9" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="9" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="9" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="9" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="9" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="9" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="9" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="9" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="9" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="11" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="11" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="11" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="11" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="11" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="11" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="11" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="11" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="11" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="12" t="s">
+      <c r="A63" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B63" s="13" t="s">
+      <c r="B63" s="11" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="11" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="12" t="s">
+      <c r="A65" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B65" s="13">
+      <c r="B65" s="11">
         <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="11" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="11" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="12" t="s">
+      <c r="A69" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="11">
         <v>2012</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="12" t="s">
+      <c r="A70" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="11" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="11" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B72" s="11" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="14" t="s">
+      <c r="A73" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B73" s="13" t="s">
+      <c r="B73" s="11" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="11" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="11" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="14" t="s">
+      <c r="A76" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B76" s="13">
+      <c r="B76" s="11">
         <v>202425</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="11" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="11" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="12" t="s">
+      <c r="A80" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="11" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="13" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="12" t="s">
+      <c r="A83" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="12" t="s">
+      <c r="A84" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B84" s="15" t="s">
+      <c r="B84" s="13" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="12" t="s">
+      <c r="A85" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B85" s="13" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="12" t="s">
+      <c r="A86" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="14" t="s">
+      <c r="A89" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="16" t="s">
+      <c r="A90" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="14" t="s">
+      <c r="A91" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="11" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="14" t="s">
+      <c r="A92" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="11" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="14" t="s">
+      <c r="A93" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="11" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="14" t="s">
+      <c r="A94" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="11" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="14" t="s">
+      <c r="A95" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B95" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="14" t="s">
+      <c r="A96" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="11" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="14" t="s">
+      <c r="A97" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="11" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="14" t="s">
+      <c r="A98" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="11" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="14" t="s">
+      <c r="A99" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="17" t="s">
+      <c r="A100" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B100" s="18" t="s">
+      <c r="B100" s="16" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="17" t="s">
+      <c r="A101" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B101" s="18" t="s">
+      <c r="B101" s="16" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="17" t="s">
+      <c r="A102" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B102" s="18" t="s">
+      <c r="B102" s="16" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="17" t="s">
+      <c r="A103" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="B103" s="18" t="s">
+      <c r="B103" s="16" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B104" s="18">
+      <c r="B104" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="19" t="s">
+      <c r="A105" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="B105" s="20" t="s">
+      <c r="B105" s="18" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="19" t="s">
+      <c r="A106" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="B106" s="20" t="s">
+      <c r="B106" s="18" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="19" t="s">
+      <c r="A107" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="B107" s="21">
+      <c r="B107" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="19" t="s">
+      <c r="A108" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="B108" s="20" t="s">
+      <c r="B108" s="18" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="19" t="s">
+      <c r="A109" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="B109" s="21" t="s">
+      <c r="B109" s="19" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="19" t="s">
+      <c r="A110" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="B110" s="21">
+      <c r="B110" s="19">
         <v>100</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="10" t="s">
+      <c r="A111" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="B111" s="22" t="s">
+      <c r="B111" s="20" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="23" t="s">
+      <c r="A112" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="B112" s="24" t="s">
+      <c r="B112" s="22" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="23" t="s">
+      <c r="A113" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="B113" s="24" t="s">
+      <c r="B113" s="22" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="23" t="s">
+      <c r="A114" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="B114" s="22" t="s">
+      <c r="B114" s="20" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="23" t="s">
+      <c r="A115" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="B115" s="22" t="s">
+      <c r="B115" s="20" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="23" t="s">
+      <c r="A116" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="B116" s="22" t="s">
+      <c r="B116" s="20" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="10" t="s">
+      <c r="A117" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B117" s="22" t="s">
+      <c r="B117" s="20" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="10" t="s">
+      <c r="A118" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B118" s="22">
+      <c r="B118" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="25" t="s">
+      <c r="A119" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="B119" s="11" t="s">
+      <c r="B119" s="9" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="25" t="s">
+      <c r="A120" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="B120" s="11" t="s">
+      <c r="B120" s="9" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="25" t="s">
+      <c r="A121" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B121" s="9" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="25" t="s">
+      <c r="A122" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="B122" s="11" t="s">
+      <c r="B122" s="9" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="25" t="s">
+      <c r="A123" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="B123" s="11" t="s">
+      <c r="B123" s="9" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="25" t="s">
+      <c r="A124" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="B124" s="11" t="s">
+      <c r="B124" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="25" t="s">
+      <c r="A125" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="B125" s="11" t="s">
+      <c r="B125" s="9" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="25" t="s">
+      <c r="A126" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="B126" s="11" t="s">
+      <c r="B126" s="9" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="25" t="s">
+      <c r="A127" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B127" s="9" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="25" t="s">
+      <c r="A128" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="B128" s="11" t="s">
+      <c r="B128" s="9" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="25" t="s">
+      <c r="A129" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="B129" s="11" t="s">
+      <c r="B129" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="25" t="s">
+      <c r="A130" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="B130" s="11" t="s">
+      <c r="B130" s="9" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="25" t="s">
+      <c r="A131" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="B131" s="11" t="s">
+      <c r="B131" s="9" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="25" t="s">
+      <c r="A132" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="B132" s="11" t="s">
+      <c r="B132" s="9" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="25" t="s">
+      <c r="A133" s="23" t="s">
         <v>243</v>
       </c>
-      <c r="B133" s="11" t="s">
+      <c r="B133" s="9" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="25" t="s">
+      <c r="A134" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="B134" s="11" t="s">
+      <c r="B134" s="9" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="25" t="s">
+      <c r="A135" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="B135" s="11" t="s">
+      <c r="B135" s="9" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="25" t="s">
+      <c r="A136" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B136" s="11" t="s">
+      <c r="B136" s="9" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="25" t="s">
+      <c r="A137" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="B137" s="11" t="s">
+      <c r="B137" s="9" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="25" t="s">
+      <c r="A138" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="B138" s="11" t="s">
+      <c r="B138" s="9" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="25" t="s">
+      <c r="A139" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="B139" s="11" t="s">
+      <c r="B139" s="9" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="25" t="s">
+      <c r="A140" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="B140" s="11" t="s">
+      <c r="B140" s="9" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="25" t="s">
+      <c r="A141" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="B141" s="11" t="s">
+      <c r="B141" s="9" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="25" t="s">
+      <c r="A142" s="23" t="s">
         <v>255</v>
       </c>
-      <c r="B142" s="11" t="s">
+      <c r="B142" s="9" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="25" t="s">
+      <c r="A143" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="B143" s="11" t="s">
+      <c r="B143" s="9" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="25" t="s">
+      <c r="A144" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="B144" s="11" t="s">
+      <c r="B144" s="9" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="25" t="s">
+      <c r="A145" s="23" t="s">
         <v>258</v>
       </c>
-      <c r="B145" s="11" t="s">
+      <c r="B145" s="9" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="25" t="s">
+      <c r="A146" s="23" t="s">
         <v>259</v>
       </c>
-      <c r="B146" s="11" t="s">
+      <c r="B146" s="9" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="25" t="s">
+      <c r="A147" s="23" t="s">
         <v>260</v>
       </c>
-      <c r="B147" s="11" t="s">
+      <c r="B147" s="9" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="25" t="s">
+      <c r="A148" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="B148" s="11" t="s">
+      <c r="B148" s="9" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="25" t="s">
+      <c r="A149" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="B149" s="11" t="s">
+      <c r="B149" s="9" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="25" t="s">
+      <c r="A150" s="23" t="s">
         <v>263</v>
       </c>
-      <c r="B150" s="11" t="s">
+      <c r="B150" s="9" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="10" t="s">
+      <c r="A151" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="B151" s="11" t="s">
+      <c r="B151" s="9" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="10" t="s">
+      <c r="A152" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="B152" s="11" t="s">
+      <c r="B152" s="9" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="10" t="s">
+      <c r="A153" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="B153" s="11" t="s">
+      <c r="B153" s="9" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="10" t="s">
+      <c r="A154" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="B154" s="11" t="s">
+      <c r="B154" s="9" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="10" t="s">
+      <c r="A155" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="B155" s="11" t="s">
+      <c r="B155" s="9" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="10" t="s">
+      <c r="A156" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="B156" s="11" t="s">
+      <c r="B156" s="9" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="10" t="s">
+      <c r="A157" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="B157" s="26" t="s">
+      <c r="B157" s="24" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="10" t="s">
+      <c r="A158" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="B158" s="22" t="s">
+      <c r="B158" s="20" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="12" t="s">
+      <c r="A159" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="B159" s="27" t="s">
+      <c r="B159" s="25" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="12" t="s">
+      <c r="A160" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="B160" s="13" t="s">
+      <c r="B160" s="11" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="12" t="s">
+      <c r="A161" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="B161" s="15" t="s">
+      <c r="B161" s="13" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="12" t="s">
+      <c r="A162" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="B162" s="13" t="s">
+      <c r="B162" s="11" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="12" t="s">
+      <c r="A163" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B163" s="13" t="s">
+      <c r="B163" s="11" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="12" t="s">
+      <c r="A164" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B164" s="15" t="s">
+      <c r="B164" s="13" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="12" t="s">
+      <c r="A165" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="B165" s="15" t="s">
+      <c r="B165" s="13" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="12" t="s">
+      <c r="A166" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B166" s="13" t="s">
+      <c r="B166" s="11" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="12" t="s">
+      <c r="A167" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="B167" s="13" t="s">
+      <c r="B167" s="11" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="12" t="s">
+      <c r="A168" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="B168" s="15" t="s">
+      <c r="B168" s="13" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="12" t="s">
+      <c r="A169" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B169" s="15" t="s">
+      <c r="B169" s="13" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="12" t="s">
+      <c r="A170" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B170" s="13" t="s">
+      <c r="B170" s="11" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="12" t="s">
+      <c r="A171" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B171" s="13" t="s">
+      <c r="B171" s="11" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="12" t="s">
+      <c r="A172" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B172" s="13" t="s">
+      <c r="B172" s="11" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="12" t="s">
+      <c r="A173" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="B173" s="13" t="s">
+      <c r="B173" s="11" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="12" t="s">
+      <c r="A174" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B174" s="13" t="s">
+      <c r="B174" s="11" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="12" t="s">
+      <c r="A175" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="B175" s="13" t="s">
+      <c r="B175" s="11" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="12" t="s">
+      <c r="A176" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B176" s="13" t="s">
+      <c r="B176" s="11" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="12" t="s">
+      <c r="A177" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B177" s="13" t="s">
+      <c r="B177" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="12" t="s">
+      <c r="A178" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="B178" s="13" t="s">
+      <c r="B178" s="11" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="12" t="s">
+      <c r="A179" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B179" s="13" t="s">
+      <c r="B179" s="11" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="12" t="s">
+      <c r="A180" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="B180" s="13" t="s">
+      <c r="B180" s="11" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="12" t="s">
+      <c r="A181" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="B181" s="13" t="s">
+      <c r="B181" s="11" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="12" t="s">
+      <c r="A182" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="B182" s="13" t="s">
+      <c r="B182" s="11" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="12" t="s">
+      <c r="A183" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="B183" s="13" t="s">
+      <c r="B183" s="11" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="12" t="s">
+      <c r="A184" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="B184" s="13" t="s">
+      <c r="B184" s="11" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="12" t="s">
+      <c r="A185" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="B185" s="13" t="s">
+      <c r="B185" s="11" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="12" t="s">
+      <c r="A186" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="B186" s="15" t="s">
+      <c r="B186" s="13" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="12" t="s">
+      <c r="A187" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B187" s="15" t="s">
+      <c r="B187" s="13" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="12" t="s">
+      <c r="A188" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="B188" s="13" t="s">
+      <c r="B188" s="11" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="12" t="s">
+      <c r="A189" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="B189" s="15" t="s">
+      <c r="B189" s="13" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="12" t="s">
+      <c r="A190" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="B190" s="13" t="s">
+      <c r="B190" s="11" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="10" t="s">
+      <c r="A191" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="B191" s="28" t="s">
+      <c r="B191" s="26" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="29" t="s">
+      <c r="A192" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="B192" s="30" t="s">
+      <c r="B192" s="28" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="29" t="s">
+      <c r="A193" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="B193" s="30" t="s">
+      <c r="B193" s="28" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="29" t="s">
+      <c r="A194" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="B194" s="18">
+      <c r="B194" s="16">
         <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="29" t="s">
+      <c r="A195" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="B195" s="30" t="s">
+      <c r="B195" s="28" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="29" t="s">
+      <c r="A196" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="B196" s="18" t="s">
+      <c r="B196" s="16" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="29" t="s">
+      <c r="A197" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="B197" s="18">
+      <c r="B197" s="16">
         <v>100</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="29" t="s">
+      <c r="A198" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B198" s="18" t="s">
+      <c r="B198" s="16" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="29" t="s">
+      <c r="A199" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B199" s="31" t="s">
+      <c r="B199" s="29" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="29" t="s">
+      <c r="A200" s="27" t="s">
         <v>346</v>
       </c>
-      <c r="B200" s="31" t="s">
+      <c r="B200" s="29" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="29" t="s">
+      <c r="A201" s="27" t="s">
         <v>348</v>
       </c>
-      <c r="B201" s="31" t="s">
+      <c r="B201" s="29" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="29" t="s">
+      <c r="A202" s="27" t="s">
         <v>350</v>
       </c>
-      <c r="B202" s="18">
+      <c r="B202" s="16">
         <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="29" t="s">
+      <c r="A203" s="27" t="s">
         <v>351</v>
       </c>
-      <c r="B203" s="18">
+      <c r="B203" s="16">
         <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="29" t="s">
+      <c r="A204" s="27" t="s">
         <v>352</v>
       </c>
-      <c r="B204" s="18" t="s">
+      <c r="B204" s="16" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="17" t="s">
+      <c r="A205" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="B205" s="18">
+      <c r="B205" s="16">
         <v>150</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="17" t="s">
+      <c r="A206" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="B206" s="18">
+      <c r="B206" s="16">
         <v>250</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="17" t="s">
+      <c r="A207" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="B207" s="18" t="s">
+      <c r="B207" s="16" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="17" t="s">
+      <c r="A208" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="B208" s="18">
+      <c r="B208" s="16">
         <v>123562</v>
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="17" t="s">
+      <c r="A209" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="B209" s="18">
+      <c r="B209" s="16">
         <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="17" t="s">
+      <c r="A210" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="B210" s="18">
+      <c r="B210" s="16">
         <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="17" t="s">
+      <c r="A211" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="B211" s="18">
+      <c r="B211" s="16">
         <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="17" t="s">
+      <c r="A212" s="15" t="s">
         <v>362</v>
       </c>
-      <c r="B212" s="30" t="s">
+      <c r="B212" s="28" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="17" t="s">
+      <c r="A213" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="B213" s="18" t="s">
+      <c r="B213" s="16" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="17" t="s">
+      <c r="A214" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="B214" s="30" t="s">
+      <c r="B214" s="28" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="17" t="s">
+      <c r="A215" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="B215" s="18">
+      <c r="B215" s="16">
         <v>50</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="17" t="s">
+      <c r="A216" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="B216" s="18">
+      <c r="B216" s="16">
         <v>50</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="17" t="s">
+      <c r="A217" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="B217" s="30" t="s">
+      <c r="B217" s="28" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="10" t="s">
+      <c r="A218" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="B218" s="22" t="s">
+      <c r="B218" s="20" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="10" t="s">
+      <c r="A219" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="B219" s="22" t="s">
+      <c r="B219" s="20" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="10" t="s">
+      <c r="A220" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="B220" s="22" t="s">
+      <c r="B220" s="20" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="10" t="s">
+      <c r="A221" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="B221" s="22" t="s">
+      <c r="B221" s="20" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="23" t="s">
+      <c r="A222" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="B222" s="22" t="s">
+      <c r="B222" s="20" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="23" t="s">
+      <c r="A223" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="B223" s="22" t="s">
+      <c r="B223" s="20" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="32" t="s">
+      <c r="A224" s="30" t="s">
         <v>380</v>
       </c>
-      <c r="B224" s="33" t="s">
+      <c r="B224" s="31" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="23" t="s">
+      <c r="A225" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="B225" s="24" t="s">
+      <c r="B225" s="22" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="10" t="s">
+      <c r="A226" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="B226" s="11" t="s">
+      <c r="B226" s="9" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="10" t="s">
+      <c r="A227" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="B227" s="11" t="s">
+      <c r="B227" s="9" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="10" t="s">
+      <c r="A228" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="B228" s="11" t="s">
+      <c r="B228" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="10" t="s">
+      <c r="A229" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="B229" s="11" t="s">
+      <c r="B229" s="9" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="10" t="s">
+      <c r="A230" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="B230" s="11" t="s">
+      <c r="B230" s="9" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="10" t="s">
+      <c r="A231" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="B231" s="11" t="s">
+      <c r="B231" s="9" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="10" t="s">
+      <c r="A232" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B232" s="11" t="s">
+      <c r="B232" s="9" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="10" t="s">
+      <c r="A233" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="B233" s="11" t="s">
+      <c r="B233" s="9" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="234" spans="1:2">
-      <c r="A234" s="10" t="s">
+      <c r="A234" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B234" s="11" t="s">
+      <c r="B234" s="9" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="235" spans="1:2">
-      <c r="A235" s="10" t="s">
+      <c r="A235" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B235" s="11" t="s">
+      <c r="B235" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="236" spans="1:2">
-      <c r="A236" s="10" t="s">
+      <c r="A236" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="B236" s="11" t="s">
+      <c r="B236" s="9" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="237" spans="1:2">
-      <c r="A237" s="10" t="s">
+      <c r="A237" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="B237" s="11" t="s">
+      <c r="B237" s="9" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="238" spans="1:2">
-      <c r="A238" s="10" t="s">
+      <c r="A238" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="B238" s="11" t="s">
+      <c r="B238" s="9" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="239" spans="1:2">
-      <c r="A239" s="10" t="s">
+      <c r="A239" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="B239" s="11" t="s">
+      <c r="B239" s="9" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="240" spans="1:2">
-      <c r="A240" s="10" t="s">
+      <c r="A240" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="B240" s="11" t="s">
+      <c r="B240" s="9" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="241" spans="1:2">
-      <c r="A241" s="10" t="s">
+      <c r="A241" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="B241" s="11" t="s">
+      <c r="B241" s="9" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="242" spans="1:2">
-      <c r="A242" s="10" t="s">
+      <c r="A242" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="B242" s="11" t="s">
+      <c r="B242" s="9" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="243" spans="1:2">
-      <c r="A243" s="10" t="s">
+      <c r="A243" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="B243" s="11" t="s">
+      <c r="B243" s="9" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="244" spans="1:2">
-      <c r="A244" s="10" t="s">
+      <c r="A244" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="B244" s="11" t="s">
+      <c r="B244" s="9" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="245" spans="1:2">
-      <c r="A245" s="10" t="s">
+      <c r="A245" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="B245" s="11" t="s">
+      <c r="B245" s="9" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="246" spans="1:2">
-      <c r="A246" s="10" t="s">
+      <c r="A246" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="B246" s="11" t="s">
+      <c r="B246" s="9" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="247" spans="1:2">
-      <c r="A247" s="10" t="s">
+      <c r="A247" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="B247" s="11" t="s">
+      <c r="B247" s="9" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="248" spans="1:2">
-      <c r="A248" s="10" t="s">
+      <c r="A248" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="B248" s="11" t="s">
+      <c r="B248" s="9" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="249" spans="1:2">
-      <c r="A249" s="10" t="s">
+      <c r="A249" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="B249" s="34" t="s">
+      <c r="B249" s="32" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="250" spans="1:2">
-      <c r="A250" s="10" t="s">
+      <c r="A250" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="B250" s="11" t="s">
+      <c r="B250" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="251" spans="1:2">
-      <c r="A251" s="10" t="s">
+      <c r="A251" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="B251" s="11" t="s">
+      <c r="B251" s="9" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="252" spans="1:2">
-      <c r="A252" s="10" t="s">
+      <c r="A252" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="B252" s="11" t="s">
+      <c r="B252" s="9" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="253" spans="1:2">
-      <c r="A253" s="10" t="s">
+      <c r="A253" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="B253" s="11" t="s">
+      <c r="B253" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="254" spans="1:2">
-      <c r="A254" s="10" t="s">
+      <c r="A254" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="B254" s="11" t="s">
+      <c r="B254" s="9" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="255" spans="1:2">
-      <c r="A255" s="10" t="s">
+      <c r="A255" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="B255" s="11" t="s">
+      <c r="B255" s="9" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="256" spans="1:2">
-      <c r="A256" s="10" t="s">
+      <c r="A256" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="B256" s="11" t="s">
+      <c r="B256" s="9" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="257" spans="1:2">
-      <c r="A257" s="10" t="s">
+      <c r="A257" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="B257" s="11" t="s">
+      <c r="B257" s="9" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="258" spans="1:2">
-      <c r="A258" s="10" t="s">
+      <c r="A258" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="B258" s="11" t="s">
+      <c r="B258" s="9" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="259" spans="1:2">
-      <c r="A259" s="10" t="s">
+      <c r="A259" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="B259" s="11" t="s">
+      <c r="B259" s="9" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="260" spans="1:2">
-      <c r="A260" s="10" t="s">
+      <c r="A260" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="B260" s="11" t="s">
+      <c r="B260" s="9" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="261" spans="1:2">
-      <c r="A261" s="10" t="s">
+      <c r="A261" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="B261" s="11" t="s">
+      <c r="B261" s="9" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="262" spans="1:2">
-      <c r="A262" s="10" t="s">
+      <c r="A262" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="B262" s="11" t="s">
+      <c r="B262" s="9" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="263" spans="1:2">
-      <c r="A263" s="10" t="s">
+      <c r="A263" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="B263" s="11" t="s">
+      <c r="B263" s="9" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="264" spans="1:2">
-      <c r="A264" s="10" t="s">
+      <c r="A264" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="B264" s="11" t="s">
+      <c r="B264" s="9" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="265" spans="1:2">
-      <c r="A265" s="10" t="s">
+      <c r="A265" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="B265" s="11" t="s">
+      <c r="B265" s="9" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="266" spans="1:2">
-      <c r="A266" s="10" t="s">
+      <c r="A266" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="B266" s="11" t="s">
+      <c r="B266" s="9" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="267" spans="1:2">
-      <c r="A267" s="10" t="s">
+      <c r="A267" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="B267" s="11" t="s">
+      <c r="B267" s="9" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="268" spans="1:2">
-      <c r="A268" s="10" t="s">
+      <c r="A268" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="B268" s="11" t="s">
+      <c r="B268" s="9" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="269" spans="1:2">
-      <c r="A269" s="10" t="s">
+      <c r="A269" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="B269" s="11" t="s">
+      <c r="B269" s="9" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="270" spans="1:2">
-      <c r="A270" s="10" t="s">
+      <c r="A270" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="B270" s="11" t="s">
+      <c r="B270" s="9" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="271" spans="1:2">
-      <c r="A271" s="10" t="s">
+      <c r="A271" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="B271" s="11" t="s">
+      <c r="B271" s="9" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="272" spans="1:2">
-      <c r="A272" s="10" t="s">
+      <c r="A272" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="B272" s="11" t="s">
+      <c r="B272" s="9" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="273" spans="1:2">
-      <c r="A273" s="10" t="s">
+      <c r="A273" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="B273" s="11" t="s">
+      <c r="B273" s="9" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="274" spans="1:2">
-      <c r="A274" s="10" t="s">
+      <c r="A274" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="B274" s="11" t="s">
+      <c r="B274" s="9" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="275" spans="1:2">
-      <c r="A275" s="10" t="s">
+      <c r="A275" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="B275" s="11" t="s">
+      <c r="B275" s="9" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="276" spans="1:2">
-      <c r="A276" s="10" t="s">
+      <c r="A276" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="B276" s="11" t="s">
+      <c r="B276" s="9" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="277" spans="1:2">
-      <c r="A277" s="10" t="s">
+      <c r="A277" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="B277" s="11" t="s">
+      <c r="B277" s="9" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="278" spans="1:2">
-      <c r="A278" s="23" t="s">
+      <c r="A278" s="21" t="s">
         <v>467</v>
       </c>
-      <c r="B278" s="22" t="s">
+      <c r="B278" s="20" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="279" spans="1:2">
-      <c r="A279" s="10" t="s">
+      <c r="A279" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B279" s="22" t="s">
+      <c r="B279" s="20" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="280" spans="1:2">
-      <c r="A280" s="10" t="s">
+      <c r="A280" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="B280" s="11" t="s">
+      <c r="B280" s="9" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="281" spans="1:2">
-      <c r="A281" s="12" t="s">
+      <c r="A281" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="B281" s="13" t="s">
+      <c r="B281" s="11" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="282" spans="1:2">
-      <c r="A282" s="12" t="s">
+      <c r="A282" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="B282" s="13" t="s">
+      <c r="B282" s="11" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="283" spans="1:2">
-      <c r="A283" s="12" t="s">
+      <c r="A283" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="B283" s="13" t="s">
+      <c r="B283" s="11" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="284" spans="1:2">
-      <c r="A284" s="12" t="s">
+      <c r="A284" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="B284" s="15" t="s">
+      <c r="B284" s="13" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="285" spans="1:2">
-      <c r="A285" s="35" t="s">
+      <c r="A285" s="33" t="s">
         <v>479</v>
       </c>
-      <c r="B285" s="11" t="s">
+      <c r="B285" s="9" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="286" spans="1:2">
-      <c r="A286" s="35" t="s">
+      <c r="A286" s="33" t="s">
         <v>481</v>
       </c>
-      <c r="B286" s="11" t="s">
+      <c r="B286" s="9" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="287" spans="1:2">
-      <c r="A287" s="35" t="s">
+      <c r="A287" s="33" t="s">
         <v>483</v>
       </c>
-      <c r="B287" s="11" t="s">
+      <c r="B287" s="9" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="288" spans="1:2">
-      <c r="A288" s="35" t="s">
+      <c r="A288" s="33" t="s">
         <v>485</v>
       </c>
-      <c r="B288" s="11" t="s">
+      <c r="B288" s="9" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="289" spans="1:2">
-      <c r="A289" s="35" t="s">
+      <c r="A289" s="33" t="s">
         <v>487</v>
       </c>
-      <c r="B289" s="11" t="s">
+      <c r="B289" s="9" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="35" t="s">
+      <c r="A290" s="33" t="s">
         <v>489</v>
       </c>
-      <c r="B290" s="11" t="s">
+      <c r="B290" s="9" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="35" t="s">
+      <c r="A291" s="33" t="s">
         <v>491</v>
       </c>
-      <c r="B291" s="11" t="s">
+      <c r="B291" s="9" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="292" spans="1:2">
-      <c r="A292" s="10" t="s">
+      <c r="A292" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="B292" s="11" t="s">
+      <c r="B292" s="9" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="293" spans="1:2">
-      <c r="A293" s="10" t="s">
+      <c r="A293" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="B293" s="11" t="s">
+      <c r="B293" s="9" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="294" spans="1:2">
-      <c r="A294" s="10" t="s">
+      <c r="A294" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="B294" s="11" t="s">
+      <c r="B294" s="9" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="295" spans="1:2">
-      <c r="A295" s="10" t="s">
+      <c r="A295" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="B295" s="11" t="s">
+      <c r="B295" s="9" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="296" spans="1:2">
-      <c r="A296" s="10" t="s">
+      <c r="A296" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="B296" s="11" t="s">
+      <c r="B296" s="9" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="297" spans="1:2">
-      <c r="A297" s="10" t="s">
+      <c r="A297" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="B297" s="11" t="s">
+      <c r="B297" s="9" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="298" spans="1:2">
-      <c r="A298" s="10" t="s">
+      <c r="A298" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="B298" s="11" t="s">
+      <c r="B298" s="9" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="299" spans="1:2">
-      <c r="A299" s="10" t="s">
+      <c r="A299" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="B299" s="11" t="s">
+      <c r="B299" s="9" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="300" spans="1:2">
-      <c r="A300" s="10" t="s">
+      <c r="A300" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="B300" s="11" t="s">
+      <c r="B300" s="9" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="301" spans="1:2">
-      <c r="A301" s="10" t="s">
+      <c r="A301" s="8" t="s">
         <v>511</v>
       </c>
-      <c r="B301" s="11" t="s">
+      <c r="B301" s="9" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="302" spans="1:2">
-      <c r="A302" s="10" t="s">
+      <c r="A302" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="B302" s="11" t="s">
+      <c r="B302" s="9" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="303" spans="1:2">
-      <c r="A303" s="10" t="s">
+      <c r="A303" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="B303" s="11" t="s">
+      <c r="B303" s="9" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="304" spans="1:2">
-      <c r="A304" s="10" t="s">
+      <c r="A304" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="B304" s="11" t="s">
+      <c r="B304" s="9" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="305" spans="1:2">
-      <c r="A305" s="10" t="s">
+      <c r="A305" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="B305" s="11" t="s">
+      <c r="B305" s="9" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="306" spans="1:2">
-      <c r="A306" s="10" t="s">
+      <c r="A306" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="B306" s="11" t="s">
+      <c r="B306" s="9" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="307" spans="1:2">
-      <c r="A307" s="10" t="s">
+      <c r="A307" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B307" s="11" t="s">
+      <c r="B307" s="9" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="308" spans="1:2">
-      <c r="A308" s="10" t="s">
+      <c r="A308" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="B308" s="11" t="s">
+      <c r="B308" s="9" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="309" spans="1:2">
-      <c r="A309" s="10" t="s">
+      <c r="A309" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="B309" s="11" t="s">
+      <c r="B309" s="9" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="310" spans="1:2">
-      <c r="A310" s="10" t="s">
+      <c r="A310" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="B310" s="11" t="s">
+      <c r="B310" s="9" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="311" spans="1:2">
-      <c r="A311" s="10" t="s">
+      <c r="A311" s="8" t="s">
         <v>529</v>
       </c>
-      <c r="B311" s="11" t="s">
+      <c r="B311" s="9" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="312" spans="1:2">
-      <c r="A312" s="10" t="s">
+      <c r="A312" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="B312" s="11" t="s">
+      <c r="B312" s="9" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="313" spans="1:2">
-      <c r="A313" s="10" t="s">
+      <c r="A313" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="B313" s="11" t="s">
+      <c r="B313" s="9" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="314" spans="1:2">
-      <c r="A314" s="10" t="s">
+      <c r="A314" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="B314" s="11" t="s">
+      <c r="B314" s="9" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="315" spans="1:2">
-      <c r="A315" s="10" t="s">
+      <c r="A315" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="B315" s="11" t="s">
+      <c r="B315" s="9" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="316" spans="1:2">
-      <c r="A316" s="10" t="s">
+      <c r="A316" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="B316" s="11" t="s">
+      <c r="B316" s="9" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="317" spans="1:2">
-      <c r="A317" s="10" t="s">
+      <c r="A317" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="B317" s="11" t="s">
+      <c r="B317" s="9" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="318" spans="1:2">
-      <c r="A318" s="10" t="s">
+      <c r="A318" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="B318" s="11" t="s">
+      <c r="B318" s="9" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="319" spans="1:2">
-      <c r="A319" s="10" t="s">
+      <c r="A319" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="B319" s="15" t="s">
+      <c r="B319" s="13" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="320" spans="1:2">
-      <c r="A320" s="10" t="s">
+      <c r="A320" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="B320" s="11" t="s">
+      <c r="B320" s="9" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="321" spans="1:2">
-      <c r="A321" s="10" t="s">
+      <c r="A321" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="B321" s="11" t="s">
+      <c r="B321" s="9" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="322" spans="1:2">
-      <c r="A322" s="10" t="s">
+      <c r="A322" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="B322" s="11" t="s">
+      <c r="B322" s="9" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="323" spans="1:2">
-      <c r="A323" s="10" t="s">
+      <c r="A323" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="B323" s="11" t="s">
+      <c r="B323" s="9" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="324" spans="1:2">
-      <c r="A324" s="10" t="s">
+      <c r="A324" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="B324" s="11" t="s">
+      <c r="B324" s="9" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="325" spans="1:2">
-      <c r="A325" s="10" t="s">
+      <c r="A325" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="B325" s="11" t="s">
+      <c r="B325" s="9" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="326" spans="1:2">
-      <c r="A326" s="10" t="s">
+      <c r="A326" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="B326" s="11" t="s">
+      <c r="B326" s="9" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="327" spans="1:2">
-      <c r="A327" s="10" t="s">
+      <c r="A327" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="B327" s="11" t="s">
+      <c r="B327" s="9" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="328" spans="1:2">
-      <c r="A328" s="10" t="s">
+      <c r="A328" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="B328" s="11" t="s">
+      <c r="B328" s="9" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="329" spans="1:2">
-      <c r="A329" s="10" t="s">
+      <c r="A329" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="B329" s="11" t="s">
+      <c r="B329" s="9" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="330" spans="1:2">
-      <c r="A330" s="10" t="s">
+      <c r="A330" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="B330" s="11" t="s">
+      <c r="B330" s="9" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="331" spans="1:2">
-      <c r="A331" s="10" t="s">
+      <c r="A331" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="B331" s="11" t="s">
+      <c r="B331" s="9" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="332" spans="1:2">
-      <c r="A332" s="10" t="s">
+      <c r="A332" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="B332" s="11" t="s">
+      <c r="B332" s="9" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="333" spans="1:2">
-      <c r="A333" s="10" t="s">
+      <c r="A333" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="B333" s="11" t="s">
+      <c r="B333" s="9" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="334" spans="1:2">
-      <c r="A334" s="10" t="s">
+      <c r="A334" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="B334" s="11" t="s">
+      <c r="B334" s="9" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="335" spans="1:2">
-      <c r="A335" s="10" t="s">
+      <c r="A335" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="B335" s="11" t="s">
+      <c r="B335" s="9" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="10" t="s">
+      <c r="A336" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="B336" s="11" t="s">
+      <c r="B336" s="9" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="337" spans="1:2">
-      <c r="A337" s="10" t="s">
+      <c r="A337" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="B337" s="11" t="s">
+      <c r="B337" s="9" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="338" spans="1:2">
-      <c r="A338" s="10" t="s">
+      <c r="A338" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="B338" s="11" t="s">
+      <c r="B338" s="9" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="339" spans="1:2">
-      <c r="A339" s="10" t="s">
+      <c r="A339" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="B339" s="11" t="s">
+      <c r="B339" s="9" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="340" spans="1:2">
-      <c r="A340" s="10" t="s">
+      <c r="A340" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="B340" s="11" t="s">
+      <c r="B340" s="9" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="341" spans="1:2">
-      <c r="A341" s="10" t="s">
+      <c r="A341" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="B341" s="11" t="s">
+      <c r="B341" s="9" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="342" spans="1:2">
-      <c r="A342" s="10" t="s">
+      <c r="A342" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="B342" s="11" t="s">
+      <c r="B342" s="9" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="343" spans="1:2">
-      <c r="A343" s="10" t="s">
+      <c r="A343" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="B343" s="11" t="s">
+      <c r="B343" s="9" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="344" spans="1:2">
-      <c r="A344" s="10" t="s">
+      <c r="A344" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="B344" s="11" t="s">
+      <c r="B344" s="9" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="345" spans="1:2">
-      <c r="A345" s="10" t="s">
+      <c r="A345" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="B345" s="11" t="s">
+      <c r="B345" s="9" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="346" spans="1:2">
-      <c r="A346" s="10" t="s">
+      <c r="A346" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="B346" s="11" t="s">
+      <c r="B346" s="9" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="347" spans="1:2">
-      <c r="A347" s="10" t="s">
+      <c r="A347" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="B347" s="11" t="s">
+      <c r="B347" s="9" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="348" spans="1:2">
-      <c r="A348" s="10" t="s">
+      <c r="A348" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="B348" s="11" t="s">
+      <c r="B348" s="9" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="349" spans="1:2">
-      <c r="A349" s="10" t="s">
+      <c r="A349" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="B349" s="11" t="s">
+      <c r="B349" s="9" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="350" spans="1:2">
-      <c r="A350" s="10" t="s">
+      <c r="A350" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="B350" s="11" t="s">
+      <c r="B350" s="9" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="351" spans="1:2">
-      <c r="A351" s="10" t="s">
+      <c r="A351" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="B351" s="11" t="s">
+      <c r="B351" s="9" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="352" spans="1:2">
-      <c r="A352" s="10" t="s">
+      <c r="A352" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="B352" s="11" t="s">
+      <c r="B352" s="9" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="353" spans="1:2">
-      <c r="A353" s="10" t="s">
+      <c r="A353" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="B353" s="11" t="s">
+      <c r="B353" s="9" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="354" spans="1:2">
-      <c r="A354" s="10" t="s">
+      <c r="A354" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="B354" s="11" t="s">
+      <c r="B354" s="9" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="355" spans="1:2">
-      <c r="A355" s="10" t="s">
+      <c r="A355" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="B355" s="11" t="s">
+      <c r="B355" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="356" spans="1:2">
-      <c r="A356" s="10" t="s">
+      <c r="A356" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="B356" s="22" t="s">
+      <c r="B356" s="20" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="357" spans="1:2">
-      <c r="A357" s="10" t="s">
+      <c r="A357" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="B357" s="11" t="s">
+      <c r="B357" s="9" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="23" t="s">
+      <c r="A358" s="21" t="s">
         <v>611</v>
       </c>
-      <c r="B358" s="24" t="s">
+      <c r="B358" s="22" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="359" spans="1:2">
-      <c r="A359" s="23" t="s">
+      <c r="A359" s="21" t="s">
         <v>613</v>
       </c>
-      <c r="B359" s="24" t="s">
+      <c r="B359" s="22" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="360" spans="1:2">
-      <c r="A360" s="23" t="s">
+      <c r="A360" s="21" t="s">
         <v>615</v>
       </c>
-      <c r="B360" s="22">
+      <c r="B360" s="20">
         <v>10</v>
       </c>
     </row>
     <row r="361" spans="1:2">
-      <c r="A361" s="23" t="s">
+      <c r="A361" s="21" t="s">
         <v>616</v>
       </c>
-      <c r="B361" s="22">
+      <c r="B361" s="20">
         <v>1000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
-      <c r="A362" s="23" t="s">
+      <c r="A362" s="21" t="s">
         <v>617</v>
       </c>
-      <c r="B362" s="36">
+      <c r="B362" s="34">
         <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:2">
-      <c r="A363" s="23" t="s">
+      <c r="A363" s="21" t="s">
         <v>618</v>
       </c>
-      <c r="B363" s="22">
+      <c r="B363" s="20">
         <v>1000</v>
       </c>
     </row>
     <row r="364" spans="1:2">
-      <c r="A364" s="23" t="s">
+      <c r="A364" s="21" t="s">
         <v>619</v>
       </c>
-      <c r="B364" s="22" t="s">
+      <c r="B364" s="20" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="23" t="s">
+      <c r="A365" s="21" t="s">
         <v>621</v>
       </c>
-      <c r="B365" s="22" t="s">
+      <c r="B365" s="20" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="23" t="s">
+      <c r="A366" s="21" t="s">
         <v>623</v>
       </c>
-      <c r="B366" s="22" t="s">
+      <c r="B366" s="20" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" s="23" t="s">
+      <c r="A367" s="21" t="s">
         <v>625</v>
       </c>
-      <c r="B367" s="22">
+      <c r="B367" s="20">
         <v>10000039</v>
       </c>
     </row>
     <row r="368" spans="1:2">
-      <c r="A368" s="23" t="s">
+      <c r="A368" s="21" t="s">
         <v>626</v>
       </c>
-      <c r="B368" s="24" t="s">
+      <c r="B368" s="22" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="369" spans="1:2">
-      <c r="A369" s="23" t="s">
+      <c r="A369" s="21" t="s">
         <v>628</v>
       </c>
-      <c r="B369" s="24" t="s">
+      <c r="B369" s="22" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="23" t="s">
+      <c r="A370" s="21" t="s">
         <v>630</v>
       </c>
-      <c r="B370" s="11" t="s">
+      <c r="B370" s="9" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="23" t="s">
+      <c r="A371" s="21" t="s">
         <v>632</v>
       </c>
-      <c r="B371" s="11" t="s">
+      <c r="B371" s="9" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="372" spans="1:2">
-      <c r="A372" s="23" t="s">
+      <c r="A372" s="21" t="s">
         <v>634</v>
       </c>
-      <c r="B372" s="11" t="s">
+      <c r="B372" s="9" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="23" t="s">
+      <c r="A373" s="21" t="s">
         <v>636</v>
       </c>
-      <c r="B373" s="11" t="s">
+      <c r="B373" s="9" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="23" t="s">
+      <c r="A374" s="21" t="s">
         <v>638</v>
       </c>
-      <c r="B374" s="11" t="s">
+      <c r="B374" s="9" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="23" t="s">
+      <c r="A375" s="21" t="s">
         <v>640</v>
       </c>
-      <c r="B375" s="11" t="s">
+      <c r="B375" s="9" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="23" t="s">
+      <c r="A376" s="21" t="s">
         <v>642</v>
       </c>
-      <c r="B376" s="11" t="s">
+      <c r="B376" s="9" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="377" spans="1:2">
-      <c r="A377" s="23" t="s">
+      <c r="A377" s="21" t="s">
         <v>643</v>
       </c>
-      <c r="B377" s="11" t="s">
+      <c r="B377" s="9" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="378" spans="1:2">
-      <c r="A378" s="23" t="s">
+      <c r="A378" s="21" t="s">
         <v>645</v>
       </c>
-      <c r="B378" s="11" t="s">
+      <c r="B378" s="9" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="379" spans="1:2">
-      <c r="A379" s="23" t="s">
+      <c r="A379" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="B379" s="11" t="s">
+      <c r="B379" s="9" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="380" spans="1:2">
-      <c r="A380" s="23" t="s">
+      <c r="A380" s="21" t="s">
         <v>649</v>
       </c>
-      <c r="B380" s="11" t="s">
+      <c r="B380" s="9" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="381" spans="1:2">
-      <c r="A381" s="23" t="s">
+      <c r="A381" s="21" t="s">
         <v>650</v>
       </c>
-      <c r="B381" s="11" t="s">
+      <c r="B381" s="9" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="23" t="s">
+      <c r="A382" s="21" t="s">
         <v>652</v>
       </c>
-      <c r="B382" s="11" t="s">
+      <c r="B382" s="9" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="23" t="s">
+      <c r="A383" s="21" t="s">
         <v>654</v>
       </c>
-      <c r="B383" s="11" t="s">
+      <c r="B383" s="9" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="23" t="s">
+      <c r="A384" s="21" t="s">
         <v>656</v>
       </c>
-      <c r="B384" s="11" t="s">
+      <c r="B384" s="9" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="23" t="s">
+      <c r="A385" s="21" t="s">
         <v>658</v>
       </c>
-      <c r="B385" s="11" t="s">
+      <c r="B385" s="9" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="23" t="s">
+      <c r="A386" s="21" t="s">
         <v>660</v>
       </c>
-      <c r="B386" s="11" t="s">
+      <c r="B386" s="9" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="23" t="s">
+      <c r="A387" s="21" t="s">
         <v>662</v>
       </c>
-      <c r="B387" s="11" t="s">
+      <c r="B387" s="9" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="388" spans="1:2">
-      <c r="A388" s="23" t="s">
+      <c r="A388" s="21" t="s">
         <v>664</v>
       </c>
-      <c r="B388" s="11" t="s">
+      <c r="B388" s="9" t="s">
         <v>665</v>
       </c>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" s="23" t="s">
+      <c r="A389" s="21" t="s">
         <v>666</v>
       </c>
-      <c r="B389" s="11" t="s">
+      <c r="B389" s="9" t="s">
         <v>667</v>
       </c>
     </row>
     <row r="390" spans="1:2">
-      <c r="A390" s="23" t="s">
+      <c r="A390" s="21" t="s">
         <v>668</v>
       </c>
-      <c r="B390" s="11" t="s">
+      <c r="B390" s="9" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="23" t="s">
+      <c r="A391" s="21" t="s">
         <v>670</v>
       </c>
-      <c r="B391" s="11" t="s">
+      <c r="B391" s="9" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="23" t="s">
+      <c r="A392" s="21" t="s">
         <v>672</v>
       </c>
-      <c r="B392" s="11" t="s">
+      <c r="B392" s="9" t="s">
         <v>673</v>
       </c>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393" s="23" t="s">
+      <c r="A393" s="21" t="s">
         <v>674</v>
       </c>
-      <c r="B393" s="11" t="s">
+      <c r="B393" s="9" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="23" t="s">
+      <c r="A394" s="21" t="s">
         <v>676</v>
       </c>
-      <c r="B394" s="11" t="s">
+      <c r="B394" s="9" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="395" spans="1:2">
-      <c r="A395" s="23" t="s">
+      <c r="A395" s="21" t="s">
         <v>678</v>
       </c>
-      <c r="B395" s="11" t="s">
+      <c r="B395" s="9" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396" s="23" t="s">
+      <c r="A396" s="21" t="s">
         <v>680</v>
       </c>
-      <c r="B396" s="11" t="s">
+      <c r="B396" s="9" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="23" t="s">
+      <c r="A397" s="21" t="s">
         <v>682</v>
       </c>
-      <c r="B397" s="11" t="s">
+      <c r="B397" s="9" t="s">
         <v>683</v>
       </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="23" t="s">
+      <c r="A398" s="21" t="s">
         <v>684</v>
       </c>
-      <c r="B398" s="11" t="s">
+      <c r="B398" s="9" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="23" t="s">
+      <c r="A399" s="21" t="s">
         <v>686</v>
       </c>
-      <c r="B399" s="11" t="s">
+      <c r="B399" s="9" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="23" t="s">
+      <c r="A400" s="21" t="s">
         <v>688</v>
       </c>
-      <c r="B400" s="11" t="s">
+      <c r="B400" s="9" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="23" t="s">
+      <c r="A401" s="21" t="s">
         <v>690</v>
       </c>
-      <c r="B401" s="11" t="s">
+      <c r="B401" s="9" t="s">
         <v>691</v>
       </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="23" t="s">
+      <c r="A402" s="21" t="s">
         <v>692</v>
       </c>
-      <c r="B402" s="11" t="s">
+      <c r="B402" s="9" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="23" t="s">
+      <c r="A403" s="21" t="s">
         <v>694</v>
       </c>
-      <c r="B403" s="11" t="s">
+      <c r="B403" s="9" t="s">
         <v>695</v>
       </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="23" t="s">
+      <c r="A404" s="21" t="s">
         <v>696</v>
       </c>
-      <c r="B404" s="11" t="s">
+      <c r="B404" s="9" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="23" t="s">
+      <c r="A405" s="21" t="s">
         <v>698</v>
       </c>
-      <c r="B405" s="11" t="s">
+      <c r="B405" s="9" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="23" t="s">
+      <c r="A406" s="21" t="s">
         <v>700</v>
       </c>
-      <c r="B406" s="11" t="s">
+      <c r="B406" s="9" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="23" t="s">
+      <c r="A407" s="21" t="s">
         <v>702</v>
       </c>
-      <c r="B407" s="11" t="s">
+      <c r="B407" s="9" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="23" t="s">
+      <c r="A408" s="21" t="s">
         <v>704</v>
       </c>
-      <c r="B408" s="11" t="s">
+      <c r="B408" s="9" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="409" spans="1:2">
-      <c r="A409" s="10" t="s">
+      <c r="A409" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="B409" s="11" t="s">
+      <c r="B409" s="9" t="s">
         <v>707</v>
       </c>
     </row>
     <row r="410" spans="1:2">
-      <c r="A410" s="10" t="s">
+      <c r="A410" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="B410" s="11" t="s">
+      <c r="B410" s="9" t="s">
         <v>709</v>
       </c>
     </row>
     <row r="411" spans="1:2">
-      <c r="A411" s="10" t="s">
+      <c r="A411" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="B411" s="11" t="s">
+      <c r="B411" s="9" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="412" spans="1:2">
-      <c r="A412" s="10" t="s">
+      <c r="A412" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="B412" s="11" t="s">
+      <c r="B412" s="9" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="413" spans="1:2">
-      <c r="A413" s="10" t="s">
+      <c r="A413" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="B413" s="11" t="s">
+      <c r="B413" s="9" t="s">
         <v>713</v>
       </c>
     </row>
     <row r="414" spans="1:2">
-      <c r="A414" s="10" t="s">
+      <c r="A414" s="8" t="s">
         <v>714</v>
       </c>
-      <c r="B414" s="11" t="s">
+      <c r="B414" s="9" t="s">
         <v>715</v>
       </c>
     </row>
     <row r="415" spans="1:2">
-      <c r="A415" s="10" t="s">
+      <c r="A415" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="B415" s="11" t="s">
+      <c r="B415" s="9" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="416" spans="1:2">
-      <c r="A416" s="10" t="s">
+      <c r="A416" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="B416" s="11" t="s">
+      <c r="B416" s="9" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="417" spans="1:2">
-      <c r="A417" s="10" t="s">
+      <c r="A417" s="8" t="s">
         <v>720</v>
       </c>
-      <c r="B417" s="11" t="s">
+      <c r="B417" s="9" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="418" spans="1:2">
-      <c r="A418" s="10" t="s">
+      <c r="A418" s="8" t="s">
         <v>721</v>
       </c>
-      <c r="B418" s="11" t="s">
+      <c r="B418" s="9" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="419" spans="1:2">
-      <c r="A419" s="10" t="s">
+      <c r="A419" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="B419" s="11" t="s">
+      <c r="B419" s="9" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="420" spans="1:2">
-      <c r="A420" s="10" t="s">
+      <c r="A420" s="8" t="s">
         <v>725</v>
       </c>
-      <c r="B420" s="11" t="s">
+      <c r="B420" s="9" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="421" spans="1:2">
-      <c r="A421" s="10" t="s">
+      <c r="A421" s="8" t="s">
         <v>727</v>
       </c>
-      <c r="B421" s="11" t="s">
+      <c r="B421" s="9" t="s">
         <v>727</v>
       </c>
     </row>
     <row r="422" spans="1:2">
-      <c r="A422" s="10" t="s">
+      <c r="A422" s="8" t="s">
         <v>728</v>
       </c>
-      <c r="B422" s="11" t="s">
+      <c r="B422" s="9" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="423" spans="1:2">
-      <c r="A423" s="10" t="s">
+      <c r="A423" s="8" t="s">
         <v>729</v>
       </c>
-      <c r="B423" s="11" t="s">
+      <c r="B423" s="9" t="s">
         <v>729</v>
       </c>
     </row>
     <row r="424" spans="1:2">
-      <c r="A424" s="10" t="s">
+      <c r="A424" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="B424" s="11" t="s">
+      <c r="B424" s="9" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="425" spans="1:2">
-      <c r="A425" s="10" t="s">
+      <c r="A425" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="B425" s="11" t="s">
+      <c r="B425" s="9" t="s">
         <v>733</v>
       </c>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="12" t="s">
+      <c r="A426" s="10" t="s">
         <v>734</v>
       </c>
-      <c r="B426" s="15" t="s">
+      <c r="B426" s="13" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="427" spans="1:2">
-      <c r="A427" s="12" t="s">
+      <c r="A427" s="10" t="s">
         <v>736</v>
       </c>
-      <c r="B427" s="15" t="s">
+      <c r="B427" s="13" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="12" t="s">
+      <c r="A428" s="10" t="s">
         <v>738</v>
       </c>
-      <c r="B428" s="15" t="s">
+      <c r="B428" s="13" t="s">
         <v>739</v>
       </c>
     </row>
     <row r="429" spans="1:2">
-      <c r="A429" s="12" t="s">
+      <c r="A429" s="10" t="s">
         <v>740</v>
       </c>
-      <c r="B429" s="15" t="s">
+      <c r="B429" s="13" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="430" spans="1:2">
-      <c r="A430" s="12" t="s">
+      <c r="A430" s="10" t="s">
         <v>742</v>
       </c>
-      <c r="B430" s="15" t="s">
+      <c r="B430" s="13" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="12" t="s">
+      <c r="A431" s="10" t="s">
         <v>744</v>
       </c>
-      <c r="B431" s="15" t="s">
+      <c r="B431" s="13" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="432" spans="1:2">
-      <c r="A432" s="12" t="s">
+      <c r="A432" s="10" t="s">
         <v>746</v>
       </c>
-      <c r="B432" s="15" t="s">
+      <c r="B432" s="13" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="433" spans="1:2">
-      <c r="A433" s="12" t="s">
+      <c r="A433" s="10" t="s">
         <v>748</v>
       </c>
-      <c r="B433" s="15" t="s">
+      <c r="B433" s="13" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="434" spans="1:2">
-      <c r="A434" s="12" t="s">
+      <c r="A434" s="10" t="s">
         <v>750</v>
       </c>
-      <c r="B434" s="15" t="s">
+      <c r="B434" s="13" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="435" spans="1:2">
-      <c r="A435" s="12" t="s">
+      <c r="A435" s="10" t="s">
         <v>752</v>
       </c>
-      <c r="B435" s="15" t="s">
+      <c r="B435" s="13" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="436" spans="1:2">
-      <c r="A436" s="12" t="s">
+      <c r="A436" s="10" t="s">
         <v>754</v>
       </c>
-      <c r="B436" s="15" t="s">
+      <c r="B436" s="13" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="437" spans="1:2">
-      <c r="A437" s="12" t="s">
+      <c r="A437" s="10" t="s">
         <v>756</v>
       </c>
-      <c r="B437" s="15" t="s">
+      <c r="B437" s="13" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="438" spans="1:2">
-      <c r="A438" s="12" t="s">
+      <c r="A438" s="10" t="s">
         <v>758</v>
       </c>
-      <c r="B438" s="15" t="s">
+      <c r="B438" s="13" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="439" spans="1:2">
-      <c r="A439" s="12" t="s">
+      <c r="A439" s="10" t="s">
         <v>760</v>
       </c>
-      <c r="B439" s="15" t="s">
+      <c r="B439" s="13" t="s">
         <v>761</v>
       </c>
     </row>
     <row r="440" spans="1:2">
-      <c r="A440" s="10" t="s">
+      <c r="A440" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="B440" s="11" t="s">
+      <c r="B440" s="9" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="441" spans="1:2">
-      <c r="A441" s="17" t="s">
+      <c r="A441" s="15" t="s">
         <v>764</v>
       </c>
-      <c r="B441" s="18" t="s">
+      <c r="B441" s="16" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="442" spans="1:2">
-      <c r="A442" s="17" t="s">
+      <c r="A442" s="15" t="s">
         <v>765</v>
       </c>
-      <c r="B442" s="18" t="s">
+      <c r="B442" s="16" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="443" spans="1:2">
-      <c r="A443" s="17" t="s">
+      <c r="A443" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="B443" s="18" t="s">
+      <c r="B443" s="16" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="444" spans="1:2">
-      <c r="A444" s="17" t="s">
+      <c r="A444" s="15" t="s">
         <v>769</v>
       </c>
-      <c r="B444" s="18" t="s">
+      <c r="B444" s="16" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="445" spans="1:2">
-      <c r="A445" s="17" t="s">
+      <c r="A445" s="15" t="s">
         <v>770</v>
       </c>
-      <c r="B445" s="18" t="s">
+      <c r="B445" s="16" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="446" spans="1:2">
-      <c r="A446" s="17" t="s">
+      <c r="A446" s="15" t="s">
         <v>771</v>
       </c>
-      <c r="B446" s="31" t="s">
+      <c r="B446" s="29" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="447" spans="1:2">
-      <c r="A447" s="17" t="s">
+      <c r="A447" s="15" t="s">
         <v>773</v>
       </c>
-      <c r="B447" s="31" t="s">
+      <c r="B447" s="29" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="448" spans="1:2">
-      <c r="A448" s="17" t="s">
+      <c r="A448" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="B448" s="18" t="s">
+      <c r="B448" s="16" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="449" spans="1:2">
-      <c r="A449" s="17" t="s">
+      <c r="A449" s="15" t="s">
         <v>777</v>
       </c>
-      <c r="B449" s="18" t="s">
+      <c r="B449" s="16" t="s">
         <v>778</v>
       </c>
     </row>
     <row r="450" spans="1:2">
-      <c r="A450" s="17" t="s">
+      <c r="A450" s="15" t="s">
         <v>564</v>
       </c>
-      <c r="B450" s="31" t="s">
+      <c r="B450" s="29" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="451" spans="1:2">
-      <c r="A451" s="17" t="s">
+      <c r="A451" s="15" t="s">
         <v>561</v>
       </c>
-      <c r="B451" s="31" t="s">
+      <c r="B451" s="29" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="452" spans="1:2">
-      <c r="A452" s="37" t="s">
+      <c r="A452" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="B452" s="38" t="s">
+      <c r="B452" s="36" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="453" spans="1:2">
-      <c r="A453" s="37" t="s">
+      <c r="A453" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="B453" s="38" t="s">
+      <c r="B453" s="36" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="454" spans="1:2">
-      <c r="A454" s="17" t="s">
+      <c r="A454" s="15" t="s">
         <v>781</v>
       </c>
-      <c r="B454" s="39" t="s">
+      <c r="B454" s="37" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="455" spans="1:2">
-      <c r="A455" s="17" t="s">
+      <c r="A455" s="15" t="s">
         <v>782</v>
       </c>
-      <c r="B455" s="39" t="s">
+      <c r="B455" s="37" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="456" spans="1:2">
-      <c r="A456" s="17" t="s">
+      <c r="A456" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="B456" s="31" t="s">
+      <c r="B456" s="29" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="457" spans="1:2">
-      <c r="A457" s="17" t="s">
+      <c r="A457" s="15" t="s">
         <v>783</v>
       </c>
-      <c r="B457" s="31" t="s">
+      <c r="B457" s="29" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="458" spans="1:2">
-      <c r="A458" s="17" t="s">
+      <c r="A458" s="15" t="s">
         <v>784</v>
       </c>
-      <c r="B458" s="31" t="s">
+      <c r="B458" s="29" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="459" spans="1:2">
-      <c r="A459" s="17" t="s">
+      <c r="A459" s="15" t="s">
         <v>786</v>
       </c>
-      <c r="B459" s="18" t="s">
+      <c r="B459" s="16" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="460" spans="1:2">
-      <c r="A460" s="17" t="s">
+      <c r="A460" s="15" t="s">
         <v>788</v>
       </c>
-      <c r="B460" s="18" t="s">
+      <c r="B460" s="16" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="461" spans="1:2">
-      <c r="A461" s="17" t="s">
+      <c r="A461" s="15" t="s">
         <v>790</v>
       </c>
-      <c r="B461" s="18" t="s">
+      <c r="B461" s="16" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="462" spans="1:2">
-      <c r="A462" s="40" t="s">
+      <c r="A462" s="38" t="s">
         <v>359</v>
       </c>
-      <c r="B462" s="40">
+      <c r="B462" s="38">
         <v>2</v>
       </c>
     </row>
     <row r="463" spans="1:2">
-      <c r="A463" s="40" t="s">
+      <c r="A463" s="38" t="s">
         <v>360</v>
       </c>
-      <c r="B463" s="40">
+      <c r="B463" s="38">
         <v>3</v>
       </c>
     </row>
     <row r="464" spans="1:2">
-      <c r="A464" s="40" t="s">
+      <c r="A464" s="38" t="s">
         <v>361</v>
       </c>
-      <c r="B464" s="40">
+      <c r="B464" s="38">
         <v>4</v>
       </c>
     </row>
     <row r="465" spans="1:2">
-      <c r="A465" s="41" t="s">
+      <c r="A465" s="39" t="s">
         <v>354</v>
       </c>
-      <c r="B465" s="41">
+      <c r="B465" s="39">
         <v>150</v>
       </c>
     </row>
     <row r="466" spans="1:2">
-      <c r="A466" s="41" t="s">
+      <c r="A466" s="39" t="s">
         <v>355</v>
       </c>
-      <c r="B466" s="41">
+      <c r="B466" s="39">
         <v>250</v>
       </c>
     </row>
     <row r="467" spans="1:2">
-      <c r="A467" s="10" t="s">
+      <c r="A467" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="B467" s="11" t="s">
+      <c r="B467" s="9" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="468" spans="1:2">
-      <c r="A468" s="10" t="s">
+      <c r="A468" s="8" t="s">
         <v>793</v>
       </c>
-      <c r="B468" s="11" t="s">
+      <c r="B468" s="9" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="469" spans="1:2">
-      <c r="A469" s="10" t="s">
+      <c r="A469" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="B469" s="11" t="s">
+      <c r="B469" s="9" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="470" spans="1:2">
-      <c r="A470" s="10" t="s">
+      <c r="A470" s="8" t="s">
         <v>797</v>
       </c>
-      <c r="B470" s="11" t="s">
+      <c r="B470" s="9" t="s">
         <v>797</v>
       </c>
     </row>
     <row r="471" spans="1:2">
-      <c r="A471" s="10" t="s">
+      <c r="A471" s="8" t="s">
         <v>798</v>
       </c>
-      <c r="B471" s="11" t="s">
+      <c r="B471" s="9" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="472" spans="1:2">
-      <c r="A472" s="10" t="s">
+      <c r="A472" s="8" t="s">
         <v>800</v>
       </c>
-      <c r="B472" s="11" t="s">
+      <c r="B472" s="9" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="473" spans="1:2">
-      <c r="A473" s="10" t="s">
+      <c r="A473" s="8" t="s">
         <v>801</v>
       </c>
-      <c r="B473" s="11" t="s">
+      <c r="B473" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="474" spans="1:2">
-      <c r="A474" s="10" t="s">
+      <c r="A474" s="8" t="s">
         <v>802</v>
       </c>
-      <c r="B474" s="11" t="s">
+      <c r="B474" s="9" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="475" spans="1:2">
-      <c r="A475" s="10" t="s">
+      <c r="A475" s="8" t="s">
         <v>803</v>
       </c>
-      <c r="B475" s="11" t="s">
+      <c r="B475" s="9" t="s">
         <v>804</v>
       </c>
     </row>
     <row r="476" spans="1:2">
-      <c r="A476" s="10" t="s">
+      <c r="A476" s="8" t="s">
         <v>759</v>
       </c>
-      <c r="B476" s="11" t="s">
+      <c r="B476" s="9" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="477" spans="1:2">
-      <c r="A477" s="10" t="s">
+      <c r="A477" s="8" t="s">
         <v>805</v>
       </c>
-      <c r="B477" s="11" t="s">
+      <c r="B477" s="9" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="478" spans="1:2">
-      <c r="A478" s="10" t="s">
+      <c r="A478" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="B478" s="11" t="s">
+      <c r="B478" s="9" t="s">
         <v>808</v>
       </c>
     </row>
     <row r="479" spans="1:2">
-      <c r="A479" s="10" t="s">
+      <c r="A479" s="8" t="s">
         <v>809</v>
       </c>
-      <c r="B479" s="34" t="s">
+      <c r="B479" s="32" t="s">
         <v>809</v>
       </c>
     </row>
     <row r="480" spans="1:2">
-      <c r="A480" s="10" t="s">
+      <c r="A480" s="8" t="s">
         <v>810</v>
       </c>
-      <c r="B480" s="11" t="s">
+      <c r="B480" s="9" t="s">
         <v>811</v>
       </c>
     </row>
     <row r="481" spans="1:2">
-      <c r="A481" s="10" t="s">
+      <c r="A481" s="8" t="s">
         <v>812</v>
       </c>
-      <c r="B481" s="11" t="s">
+      <c r="B481" s="9" t="s">
         <v>813</v>
       </c>
     </row>
     <row r="482" spans="1:2">
-      <c r="A482" s="10" t="s">
+      <c r="A482" s="8" t="s">
         <v>814</v>
       </c>
-      <c r="B482" s="11" t="s">
+      <c r="B482" s="9" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="483" spans="1:2">
-      <c r="A483" s="10" t="s">
+      <c r="A483" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="B483" s="11" t="s">
+      <c r="B483" s="9" t="s">
         <v>816</v>
       </c>
     </row>
     <row r="484" spans="1:2">
-      <c r="A484" s="10" t="s">
+      <c r="A484" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="B484" s="11" t="s">
+      <c r="B484" s="9" t="s">
         <v>818</v>
       </c>
     </row>
     <row r="485" spans="1:2">
-      <c r="A485" s="10" t="s">
+      <c r="A485" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="B485" s="11" t="s">
+      <c r="B485" s="9" t="s">
         <v>820</v>
       </c>
     </row>
     <row r="486" spans="1:2">
-      <c r="A486" s="10" t="s">
+      <c r="A486" s="8" t="s">
         <v>821</v>
       </c>
-      <c r="B486" s="11" t="s">
+      <c r="B486" s="9" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="487" spans="1:2">
-      <c r="A487" s="10" t="s">
+      <c r="A487" s="8" t="s">
         <v>823</v>
       </c>
-      <c r="B487" s="11" t="s">
+      <c r="B487" s="9" t="s">
         <v>808</v>
       </c>
     </row>
     <row r="488" spans="1:2">
-      <c r="A488" s="10" t="s">
+      <c r="A488" s="8" t="s">
         <v>824</v>
       </c>
-      <c r="B488" s="11" t="s">
+      <c r="B488" s="9" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="489" spans="1:2">
-      <c r="A489" s="10" t="s">
+      <c r="A489" s="8" t="s">
         <v>825</v>
       </c>
-      <c r="B489" s="11" t="s">
+      <c r="B489" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="490" spans="1:2">
-      <c r="A490" s="10" t="s">
+      <c r="A490" s="8" t="s">
         <v>826</v>
       </c>
-      <c r="B490" s="11" t="s">
+      <c r="B490" s="9" t="s">
         <v>827</v>
       </c>
     </row>
     <row r="491" spans="1:2">
-      <c r="A491" s="10" t="s">
+      <c r="A491" s="8" t="s">
         <v>828</v>
       </c>
-      <c r="B491" s="11" t="s">
+      <c r="B491" s="9" t="s">
         <v>829</v>
       </c>
     </row>
     <row r="492" spans="1:2">
-      <c r="A492" s="10" t="s">
+      <c r="A492" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="B492" s="11" t="s">
+      <c r="B492" s="9" t="s">
         <v>831</v>
       </c>
     </row>
     <row r="493" spans="1:2">
-      <c r="A493" s="10" t="s">
+      <c r="A493" s="8" t="s">
         <v>832</v>
       </c>
-      <c r="B493" s="11" t="s">
+      <c r="B493" s="9" t="s">
         <v>833</v>
       </c>
     </row>
     <row r="494" spans="1:2">
-      <c r="A494" s="10" t="s">
+      <c r="A494" s="8" t="s">
         <v>834</v>
       </c>
-      <c r="B494" s="11" t="s">
+      <c r="B494" s="9" t="s">
         <v>835</v>
       </c>
     </row>
     <row r="495" spans="1:2">
-      <c r="A495" s="10" t="s">
+      <c r="A495" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="B495" s="11" t="s">
+      <c r="B495" s="9" t="s">
         <v>837</v>
       </c>
     </row>
     <row r="496" spans="1:2">
-      <c r="A496" s="10" t="s">
+      <c r="A496" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="B496" s="11" t="s">
+      <c r="B496" s="9" t="s">
         <v>839</v>
       </c>
     </row>
     <row r="497" spans="1:2">
-      <c r="A497" s="10" t="s">
+      <c r="A497" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="B497" s="11" t="s">
+      <c r="B497" s="9" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="498" spans="1:2">
-      <c r="A498" s="10" t="s">
+      <c r="A498" s="8" t="s">
         <v>842</v>
       </c>
-      <c r="B498" s="11" t="s">
+      <c r="B498" s="9" t="s">
         <v>843</v>
       </c>
     </row>
     <row r="499" spans="1:2">
-      <c r="A499" s="10" t="s">
+      <c r="A499" s="8" t="s">
         <v>844</v>
       </c>
-      <c r="B499" s="11" t="s">
+      <c r="B499" s="9" t="s">
         <v>845</v>
       </c>
     </row>
     <row r="500" spans="1:2">
-      <c r="A500" s="10" t="s">
+      <c r="A500" s="8" t="s">
         <v>846</v>
       </c>
-      <c r="B500" s="11" t="s">
+      <c r="B500" s="9" t="s">
         <v>847</v>
       </c>
     </row>
     <row r="501" spans="1:2">
-      <c r="A501" s="10" t="s">
+      <c r="A501" s="8" t="s">
         <v>848</v>
       </c>
-      <c r="B501" s="11" t="s">
+      <c r="B501" s="9" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="502" spans="1:2">
-      <c r="A502" s="10" t="s">
+      <c r="A502" s="8" t="s">
         <v>850</v>
       </c>
-      <c r="B502" s="11" t="s">
+      <c r="B502" s="9" t="s">
         <v>851</v>
       </c>
     </row>
     <row r="503" spans="1:2">
-      <c r="A503" s="10" t="s">
+      <c r="A503" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="B503" s="11" t="s">
+      <c r="B503" s="9" t="s">
         <v>853</v>
       </c>
     </row>
     <row r="504" spans="1:2">
-      <c r="A504" s="10" t="s">
+      <c r="A504" s="8" t="s">
         <v>854</v>
       </c>
-      <c r="B504" s="11" t="s">
+      <c r="B504" s="9" t="s">
         <v>855</v>
       </c>
     </row>
     <row r="505" spans="1:2">
-      <c r="A505" s="10" t="s">
+      <c r="A505" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="B505" s="11" t="s">
+      <c r="B505" s="9" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="506" spans="1:2">
-      <c r="A506" s="10" t="s">
+      <c r="A506" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="B506" s="11" t="s">
+      <c r="B506" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="507" spans="1:2">
-      <c r="A507" s="10" t="s">
+      <c r="A507" s="8" t="s">
         <v>859</v>
       </c>
-      <c r="B507" s="11" t="s">
+      <c r="B507" s="9" t="s">
         <v>860</v>
       </c>
     </row>
     <row r="508" spans="1:2">
-      <c r="A508" s="10" t="s">
+      <c r="A508" s="8" t="s">
         <v>861</v>
       </c>
-      <c r="B508" s="11" t="s">
+      <c r="B508" s="9" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="509" spans="1:2">
-      <c r="A509" s="10" t="s">
+      <c r="A509" s="8" t="s">
         <v>862</v>
       </c>
-      <c r="B509" s="11" t="s">
+      <c r="B509" s="9" t="s">
         <v>863</v>
       </c>
     </row>
     <row r="510" spans="1:2">
-      <c r="A510" s="10" t="s">
+      <c r="A510" s="8" t="s">
         <v>864</v>
       </c>
-      <c r="B510" s="11" t="s">
+      <c r="B510" s="9" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="511" spans="1:2">
-      <c r="A511" s="10" t="s">
+      <c r="A511" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="B511" s="10" t="s">
+      <c r="B511" s="8" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="512" spans="1:2">
-      <c r="A512" s="23" t="s">
+      <c r="A512" s="21" t="s">
         <v>866</v>
       </c>
-      <c r="B512" s="11" t="s">
+      <c r="B512" s="9" t="s">
         <v>867</v>
       </c>
     </row>
     <row r="513" spans="1:2">
-      <c r="A513" s="23" t="s">
+      <c r="A513" s="21" t="s">
         <v>868</v>
       </c>
-      <c r="B513" s="11" t="s">
+      <c r="B513" s="9" t="s">
         <v>869</v>
       </c>
     </row>
     <row r="514" spans="1:2">
-      <c r="A514" s="23" t="s">
+      <c r="A514" s="21" t="s">
         <v>870</v>
       </c>
-      <c r="B514" s="11" t="s">
+      <c r="B514" s="9" t="s">
         <v>871</v>
       </c>
     </row>
     <row r="515" spans="1:2">
-      <c r="A515" s="23" t="s">
+      <c r="A515" s="21" t="s">
         <v>872</v>
       </c>
-      <c r="B515" s="11" t="s">
+      <c r="B515" s="9" t="s">
         <v>873</v>
       </c>
     </row>
     <row r="516" spans="1:2">
-      <c r="A516" s="23" t="s">
+      <c r="A516" s="21" t="s">
         <v>874</v>
       </c>
-      <c r="B516" s="11" t="s">
+      <c r="B516" s="9" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="517" spans="1:2">
-      <c r="A517" s="23" t="s">
+      <c r="A517" s="21" t="s">
         <v>876</v>
       </c>
-      <c r="B517" s="11" t="s">
+      <c r="B517" s="9" t="s">
         <v>877</v>
       </c>
     </row>
     <row r="518" spans="1:2">
-      <c r="A518" s="23" t="s">
+      <c r="A518" s="21" t="s">
         <v>878</v>
       </c>
-      <c r="B518" s="11" t="s">
+      <c r="B518" s="9" t="s">
         <v>879</v>
       </c>
     </row>
     <row r="519" spans="1:2">
-      <c r="A519" s="23" t="s">
+      <c r="A519" s="21" t="s">
         <v>880</v>
       </c>
-      <c r="B519" s="11" t="s">
+      <c r="B519" s="9" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="520" spans="1:2">
-      <c r="A520" s="23" t="s">
+      <c r="A520" s="21" t="s">
         <v>882</v>
       </c>
-      <c r="B520" s="11" t="s">
+      <c r="B520" s="9" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="521" spans="1:2">
-      <c r="A521" s="23" t="s">
+      <c r="A521" s="21" t="s">
         <v>884</v>
       </c>
-      <c r="B521" s="11" t="s">
+      <c r="B521" s="9" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="522" spans="1:2">
-      <c r="A522" s="23" t="s">
+      <c r="A522" s="21" t="s">
         <v>886</v>
       </c>
-      <c r="B522" s="11" t="s">
+      <c r="B522" s="9" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="523" spans="1:2">
-      <c r="A523" s="23" t="s">
+      <c r="A523" s="21" t="s">
         <v>888</v>
       </c>
-      <c r="B523" s="11" t="s">
+      <c r="B523" s="9" t="s">
         <v>889</v>
       </c>
     </row>
     <row r="524" spans="1:2">
-      <c r="A524" s="23" t="s">
+      <c r="A524" s="21" t="s">
         <v>890</v>
       </c>
-      <c r="B524" s="11" t="s">
+      <c r="B524" s="9" t="s">
         <v>891</v>
       </c>
     </row>
     <row r="525" spans="1:2">
-      <c r="A525" s="23" t="s">
+      <c r="A525" s="21" t="s">
         <v>892</v>
       </c>
-      <c r="B525" s="11" t="s">
+      <c r="B525" s="9" t="s">
         <v>893</v>
       </c>
     </row>
     <row r="526" spans="1:2">
-      <c r="A526" s="23" t="s">
+      <c r="A526" s="21" t="s">
         <v>894</v>
       </c>
-      <c r="B526" s="11" t="s">
+      <c r="B526" s="9" t="s">
         <v>895</v>
       </c>
     </row>
     <row r="527" spans="1:2">
-      <c r="A527" s="23" t="s">
+      <c r="A527" s="21" t="s">
         <v>896</v>
       </c>
-      <c r="B527" s="11" t="s">
+      <c r="B527" s="9" t="s">
         <v>897</v>
       </c>
     </row>
     <row r="528" spans="1:2">
-      <c r="A528" s="23" t="s">
+      <c r="A528" s="21" t="s">
         <v>898</v>
       </c>
-      <c r="B528" s="11" t="s">
+      <c r="B528" s="9" t="s">
         <v>899</v>
       </c>
     </row>
     <row r="529" spans="1:2">
-      <c r="A529" s="23" t="s">
+      <c r="A529" s="21" t="s">
         <v>900</v>
       </c>
-      <c r="B529" s="11" t="s">
+      <c r="B529" s="9" t="s">
         <v>901</v>
       </c>
     </row>
     <row r="530" spans="1:2">
-      <c r="A530" s="23" t="s">
+      <c r="A530" s="21" t="s">
         <v>902</v>
       </c>
-      <c r="B530" s="11" t="s">
+      <c r="B530" s="9" t="s">
         <v>903</v>
       </c>
     </row>
     <row r="531" spans="1:2">
-      <c r="A531" s="23" t="s">
+      <c r="A531" s="21" t="s">
         <v>904</v>
       </c>
-      <c r="B531" s="11" t="s">
+      <c r="B531" s="9" t="s">
         <v>905</v>
       </c>
     </row>
     <row r="532" spans="1:2">
-      <c r="A532" s="23" t="s">
+      <c r="A532" s="21" t="s">
         <v>906</v>
       </c>
-      <c r="B532" s="11" t="s">
+      <c r="B532" s="9" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="533" spans="1:2">
-      <c r="A533" s="23" t="s">
+      <c r="A533" s="21" t="s">
         <v>908</v>
       </c>
-      <c r="B533" s="11" t="s">
+      <c r="B533" s="9" t="s">
         <v>909</v>
       </c>
     </row>
     <row r="534" spans="1:2">
-      <c r="A534" s="23" t="s">
+      <c r="A534" s="21" t="s">
         <v>910</v>
       </c>
-      <c r="B534" s="11" t="s">
+      <c r="B534" s="9" t="s">
         <v>911</v>
       </c>
     </row>
     <row r="535" spans="1:2">
-      <c r="A535" s="23" t="s">
+      <c r="A535" s="21" t="s">
         <v>912</v>
       </c>
-      <c r="B535" s="11" t="s">
+      <c r="B535" s="9" t="s">
         <v>913</v>
       </c>
     </row>
     <row r="536" spans="1:2">
-      <c r="A536" s="23" t="s">
+      <c r="A536" s="21" t="s">
         <v>914</v>
       </c>
-      <c r="B536" s="11" t="s">
+      <c r="B536" s="9" t="s">
         <v>915</v>
       </c>
     </row>
     <row r="537" spans="1:2">
-      <c r="A537" s="23" t="s">
+      <c r="A537" s="21" t="s">
         <v>916</v>
       </c>
-      <c r="B537" s="11" t="s">
+      <c r="B537" s="9" t="s">
         <v>917</v>
       </c>
     </row>
     <row r="538" spans="1:2">
-      <c r="A538" s="23" t="s">
+      <c r="A538" s="21" t="s">
         <v>918</v>
       </c>
-      <c r="B538" s="11" t="s">
+      <c r="B538" s="9" t="s">
         <v>919</v>
       </c>
     </row>
     <row r="539" spans="1:2">
-      <c r="A539" s="23" t="s">
+      <c r="A539" s="21" t="s">
         <v>920</v>
       </c>
-      <c r="B539" s="11" t="s">
+      <c r="B539" s="9" t="s">
         <v>921</v>
       </c>
     </row>
     <row r="540" spans="1:2">
-      <c r="A540" s="23" t="s">
+      <c r="A540" s="21" t="s">
         <v>922</v>
       </c>
-      <c r="B540" s="11" t="s">
+      <c r="B540" s="9" t="s">
         <v>923</v>
       </c>
     </row>
     <row r="541" spans="1:2">
-      <c r="A541" s="23" t="s">
+      <c r="A541" s="21" t="s">
         <v>924</v>
       </c>
-      <c r="B541" s="11" t="s">
+      <c r="B541" s="9" t="s">
         <v>925</v>
       </c>
     </row>
     <row r="542" spans="1:2">
-      <c r="A542" s="23" t="s">
+      <c r="A542" s="21" t="s">
         <v>926</v>
       </c>
-      <c r="B542" s="11" t="s">
+      <c r="B542" s="9" t="s">
         <v>927</v>
       </c>
     </row>
     <row r="543" spans="1:2">
-      <c r="A543" s="23" t="s">
+      <c r="A543" s="21" t="s">
         <v>928</v>
       </c>
-      <c r="B543" s="11" t="s">
+      <c r="B543" s="9" t="s">
         <v>929</v>
       </c>
     </row>
     <row r="544" spans="1:2">
-      <c r="A544" s="6" t="s">
+      <c r="A544" s="4" t="s">
         <v>930</v>
       </c>
-      <c r="B544" s="11" t="s">
+      <c r="B544" s="9" t="s">
         <v>931</v>
       </c>
     </row>
     <row r="545" spans="1:2">
-      <c r="A545" s="23" t="s">
+      <c r="A545" s="21" t="s">
         <v>932</v>
       </c>
-      <c r="B545" s="11" t="s">
+      <c r="B545" s="9" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="546" spans="1:2">
-      <c r="A546" s="10" t="s">
+      <c r="A546" s="8" t="s">
         <v>934</v>
       </c>
-      <c r="B546" s="11" t="s">
+      <c r="B546" s="9" t="s">
         <v>935</v>
       </c>
     </row>
     <row r="547" spans="1:2">
-      <c r="A547" s="10" t="s">
+      <c r="A547" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="B547" s="11" t="s">
+      <c r="B547" s="9" t="s">
         <v>937</v>
       </c>
     </row>
     <row r="548" spans="1:2">
-      <c r="A548" s="10" t="s">
+      <c r="A548" s="8" t="s">
         <v>938</v>
       </c>
-      <c r="B548" s="11" t="s">
+      <c r="B548" s="9" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="549" spans="1:2">
-      <c r="A549" s="23" t="s">
+      <c r="A549" s="21" t="s">
         <v>940</v>
       </c>
-      <c r="B549" s="11" t="s">
+      <c r="B549" s="9" t="s">
         <v>941</v>
       </c>
     </row>
     <row r="550" spans="1:2">
-      <c r="A550" s="23" t="s">
+      <c r="A550" s="21" t="s">
         <v>942</v>
       </c>
-      <c r="B550" s="11" t="s">
+      <c r="B550" s="9" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="551" spans="1:2">
-      <c r="A551" s="10" t="s">
+      <c r="A551" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="B551" s="11" t="s">
+      <c r="B551" s="9" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="552" spans="1:2">
-      <c r="A552" s="23" t="s">
+      <c r="A552" s="21" t="s">
         <v>945</v>
       </c>
-      <c r="B552" s="11" t="s">
+      <c r="B552" s="9" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="553" spans="1:2">
-      <c r="A553" s="23" t="s">
+      <c r="A553" s="21" t="s">
         <v>947</v>
       </c>
-      <c r="B553" s="11" t="s">
+      <c r="B553" s="9" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="554" spans="1:2">
-      <c r="A554" s="10" t="s">
+      <c r="A554" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="B554" s="11" t="s">
+      <c r="B554" s="9" t="s">
         <v>949</v>
       </c>
     </row>
     <row r="555" spans="1:2">
-      <c r="A555" s="23" t="s">
+      <c r="A555" s="21" t="s">
         <v>950</v>
       </c>
-      <c r="B555" s="11" t="s">
+      <c r="B555" s="9" t="s">
         <v>951</v>
       </c>
     </row>
     <row r="556" spans="1:2">
-      <c r="A556" s="23" t="s">
+      <c r="A556" s="21" t="s">
         <v>952</v>
       </c>
-      <c r="B556" s="11" t="s">
+      <c r="B556" s="9" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="557" spans="1:2">
-      <c r="A557" s="23" t="s">
+      <c r="A557" s="21" t="s">
         <v>953</v>
       </c>
-      <c r="B557" s="11" t="s">
+      <c r="B557" s="9" t="s">
         <v>954</v>
       </c>
     </row>
     <row r="558" spans="1:2">
-      <c r="A558" s="23" t="s">
+      <c r="A558" s="21" t="s">
         <v>955</v>
       </c>
-      <c r="B558" s="11" t="s">
+      <c r="B558" s="9" t="s">
         <v>956</v>
       </c>
     </row>
     <row r="559" spans="1:2">
-      <c r="A559" s="23" t="s">
+      <c r="A559" s="21" t="s">
         <v>957</v>
       </c>
-      <c r="B559" s="11" t="s">
+      <c r="B559" s="9" t="s">
         <v>958</v>
       </c>
     </row>
     <row r="560" spans="1:2">
-      <c r="A560" s="23" t="s">
+      <c r="A560" s="21" t="s">
         <v>959</v>
       </c>
-      <c r="B560" s="11" t="s">
+      <c r="B560" s="9" t="s">
         <v>960</v>
       </c>
     </row>
     <row r="561" spans="1:2">
-      <c r="A561" s="23" t="s">
+      <c r="A561" s="21" t="s">
         <v>961</v>
       </c>
-      <c r="B561" s="11" t="s">
+      <c r="B561" s="9" t="s">
         <v>962</v>
       </c>
     </row>
     <row r="562" spans="1:2">
-      <c r="A562" s="23" t="s">
+      <c r="A562" s="21" t="s">
         <v>963</v>
       </c>
-      <c r="B562" s="11" t="s">
+      <c r="B562" s="9" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="563" spans="1:2">
-      <c r="A563" s="10" t="s">
+      <c r="A563" s="8" t="s">
         <v>964</v>
       </c>
-      <c r="B563" s="11" t="s">
+      <c r="B563" s="9" t="s">
         <v>965</v>
       </c>
     </row>
     <row r="564" spans="1:2">
-      <c r="A564" s="10" t="s">
+      <c r="A564" s="8" t="s">
         <v>966</v>
       </c>
-      <c r="B564" s="11" t="s">
+      <c r="B564" s="9" t="s">
         <v>967</v>
       </c>
     </row>
     <row r="565" spans="1:2">
-      <c r="A565" s="10" t="s">
+      <c r="A565" s="8" t="s">
         <v>968</v>
       </c>
-      <c r="B565" s="11" t="s">
+      <c r="B565" s="9" t="s">
         <v>968</v>
       </c>
     </row>
     <row r="566" spans="1:2">
-      <c r="A566" s="10" t="s">
+      <c r="A566" s="8" t="s">
         <v>969</v>
       </c>
-      <c r="B566" s="11" t="s">
+      <c r="B566" s="9" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="567" spans="1:2">
-      <c r="A567" s="10" t="s">
+      <c r="A567" s="8" t="s">
         <v>971</v>
       </c>
-      <c r="B567" s="11" t="s">
+      <c r="B567" s="9" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="568" spans="1:2">
-      <c r="A568" s="10" t="s">
+      <c r="A568" s="8" t="s">
         <v>972</v>
       </c>
-      <c r="B568" s="11" t="s">
+      <c r="B568" s="9" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="569" spans="1:2">
-      <c r="A569" s="10" t="s">
+      <c r="A569" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="B569" s="11" t="s">
+      <c r="B569" s="9" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="570" spans="1:2">
-      <c r="A570" s="10" t="s">
+      <c r="A570" s="8" t="s">
         <v>932</v>
       </c>
-      <c r="B570" s="11" t="s">
+      <c r="B570" s="9" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="571" spans="1:2">
-      <c r="A571" s="10" t="s">
+      <c r="A571" s="8" t="s">
         <v>975</v>
       </c>
-      <c r="B571" s="11" t="s">
+      <c r="B571" s="9" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="572" spans="1:2">
-      <c r="A572" s="10" t="s">
+      <c r="A572" s="8" t="s">
         <v>977</v>
       </c>
-      <c r="B572" s="11" t="s">
+      <c r="B572" s="9" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="573" spans="1:2">
-      <c r="A573" s="10" t="s">
+      <c r="A573" s="8" t="s">
         <v>978</v>
       </c>
-      <c r="B573" s="11" t="s">
+      <c r="B573" s="9" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="574" spans="1:2">
-      <c r="A574" s="10" t="s">
+      <c r="A574" s="8" t="s">
         <v>979</v>
       </c>
-      <c r="B574" s="11" t="s">
+      <c r="B574" s="9" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="575" spans="1:2">
-      <c r="A575" s="10" t="s">
+      <c r="A575" s="8" t="s">
         <v>980</v>
       </c>
-      <c r="B575" s="11" t="s">
+      <c r="B575" s="9" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="576" spans="1:2">
-      <c r="A576" s="10" t="s">
+      <c r="A576" s="8" t="s">
         <v>981</v>
       </c>
-      <c r="B576" s="11" t="s">
+      <c r="B576" s="9" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="577" spans="1:2">
-      <c r="A577" s="10" t="s">
+      <c r="A577" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="B577" s="11" t="s">
+      <c r="B577" s="9" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="578" spans="1:2">
-      <c r="A578" s="10" t="s">
+      <c r="A578" s="8" t="s">
         <v>983</v>
       </c>
-      <c r="B578" s="11" t="s">
+      <c r="B578" s="9" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="579" spans="1:2">
-      <c r="A579" s="10" t="s">
+      <c r="A579" s="8" t="s">
         <v>984</v>
       </c>
-      <c r="B579" s="11" t="s">
+      <c r="B579" s="9" t="s">
         <v>984</v>
       </c>
     </row>
     <row r="580" spans="1:2">
-      <c r="A580" s="10" t="s">
+      <c r="A580" s="8" t="s">
         <v>985</v>
       </c>
-      <c r="B580" s="11" t="s">
+      <c r="B580" s="9" t="s">
         <v>985</v>
       </c>
     </row>
     <row r="581" spans="1:2">
-      <c r="A581" s="10" t="s">
+      <c r="A581" s="8" t="s">
         <v>986</v>
       </c>
-      <c r="B581" s="11" t="s">
+      <c r="B581" s="9" t="s">
         <v>986</v>
       </c>
     </row>
     <row r="582" spans="1:2">
-      <c r="A582" s="10" t="s">
+      <c r="A582" s="8" t="s">
         <v>987</v>
       </c>
-      <c r="B582" s="11" t="s">
+      <c r="B582" s="9" t="s">
         <v>987</v>
       </c>
     </row>
     <row r="583" spans="1:2">
-      <c r="A583" s="10" t="s">
+      <c r="A583" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="B583" s="11" t="s">
+      <c r="B583" s="9" t="s">
         <v>988</v>
       </c>
     </row>
     <row r="584" spans="1:2">
-      <c r="A584" s="10" t="s">
+      <c r="A584" s="8" t="s">
         <v>989</v>
       </c>
-      <c r="B584" s="11" t="s">
+      <c r="B584" s="9" t="s">
         <v>990</v>
       </c>
     </row>
     <row r="585" spans="1:2">
-      <c r="A585" s="10" t="s">
+      <c r="A585" s="8" t="s">
         <v>991</v>
       </c>
-      <c r="B585" s="11" t="s">
+      <c r="B585" s="9" t="s">
         <v>992</v>
       </c>
     </row>
     <row r="586" spans="1:2">
-      <c r="A586" s="10" t="s">
+      <c r="A586" s="8" t="s">
         <v>993</v>
       </c>
-      <c r="B586" s="11" t="s">
+      <c r="B586" s="9" t="s">
         <v>994</v>
       </c>
     </row>
     <row r="587" spans="1:2">
-      <c r="A587" s="10" t="s">
+      <c r="A587" s="8" t="s">
         <v>995</v>
       </c>
-      <c r="B587" s="11" t="s">
+      <c r="B587" s="9" t="s">
         <v>996</v>
       </c>
     </row>
     <row r="588" spans="1:2">
-      <c r="A588" s="10" t="s">
+      <c r="A588" s="8" t="s">
         <v>997</v>
       </c>
-      <c r="B588" s="11" t="s">
+      <c r="B588" s="9" t="s">
         <v>998</v>
       </c>
     </row>
     <row r="589" spans="1:2">
-      <c r="A589" s="42" t="s">
+      <c r="A589" s="8" t="s">
         <v>999</v>
       </c>
-      <c r="B589" s="43" t="s">
+      <c r="B589" s="9" t="s">
         <v>1000</v>
       </c>
     </row>
     <row r="590" spans="1:2">
-      <c r="A590" s="42" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B590" s="43" t="s">
-        <v>1038</v>
+      <c r="A590" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B590" s="9" t="s">
+        <v>1002</v>
       </c>
     </row>
     <row r="591" spans="1:2">
-      <c r="A591" s="42" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B591" s="43" t="s">
-        <v>1040</v>
+      <c r="A591" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B591" s="9" t="s">
+        <v>1004</v>
       </c>
     </row>
     <row r="592" spans="1:2">
-      <c r="A592" s="42" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B592" s="43" t="s">
+      <c r="A592" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B592" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="593" spans="1:2">
-      <c r="A593" s="42" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B593" s="43" t="s">
-        <v>1043</v>
+      <c r="A593" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B593" s="9" t="s">
+        <v>1007</v>
       </c>
     </row>
     <row r="594" spans="1:2">
-      <c r="A594" s="42" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B594" s="43" t="s">
+      <c r="A594" s="8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B594" s="9" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="595" spans="1:2">
-      <c r="A595" s="42" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B595" s="43" t="s">
-        <v>1046</v>
+      <c r="A595" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B595" s="9" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" s="40" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B596" s="41" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" s="40" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B597" s="41" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" s="40" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B598" s="41" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599" s="40" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B599" s="41" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600" s="40" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B600" s="41" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601" s="40" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B601" s="41" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602" s="40" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B602" s="41" t="s">
+        <v>1023</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85454545454546" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.8545454545455" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9137,151 +9848,152 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="108.95" customHeight="1">
+    <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>1001</v>
+        <v>1024</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="114" customHeight="1">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>1003</v>
+        <v>1026</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="80.25" customHeight="1">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>1005</v>
+        <v>1028</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="69.75" customHeight="1">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="5" ht="69.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>1007</v>
+        <v>1030</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="51.75" customHeight="1">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="6" ht="51.75" customHeight="1" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>1009</v>
+        <v>1032</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>1011</v>
+        <v>1034</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>1013</v>
+        <v>1036</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="39" customHeight="1">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="9" ht="39" customHeight="1" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>1015</v>
+        <v>1038</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="22.5" customHeight="1">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>1017</v>
+        <v>1040</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="18" customHeight="1">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>1019</v>
+        <v>1042</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="26.25" customHeight="1">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="12" ht="26.25" customHeight="1" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>1021</v>
+        <v>1044</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="28.5" customHeight="1">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="13" ht="28.5" customHeight="1" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>1023</v>
+        <v>1046</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="24" customHeight="1">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>1025</v>
+        <v>1048</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="36" customHeight="1">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>1027</v>
+        <v>1050</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="45" customHeight="1">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>1029</v>
+        <v>1052</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="405">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="17" ht="377" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>1031</v>
+        <v>1054</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="409.5">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="18" ht="409.5" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>1033</v>
+        <v>1056</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="409.5">
-      <c r="A19" s="4" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>1036</v>
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="19" ht="409.5" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1059</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="1060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="1061">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -3100,6 +3100,9 @@
   </si>
   <si>
     <t>Nationality</t>
+  </si>
+  <si>
+    <t>Cleared</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -4088,7 +4091,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4224,12 +4227,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4545,40 +4542,40 @@
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -5000,11 +4997,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B602"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B603"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="62.7090909090909" style="4" customWidth="1"/>
-    <col min="2" max="2" width="59.8545454545455" style="5" customWidth="1"/>
+    <col min="1" max="1" width="62.712962962963" style="4" customWidth="1"/>
+    <col min="2" max="2" width="59.8518518518519" style="5" customWidth="1"/>
     <col min="3" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -9769,59 +9766,67 @@
       </c>
     </row>
     <row r="596" spans="1:2">
-      <c r="A596" s="40" t="s">
+      <c r="A596" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="B596" s="41" t="s">
+      <c r="B596" s="9" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="597" spans="1:2">
-      <c r="A597" s="40" t="s">
+      <c r="A597" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="B597" s="41" t="s">
+      <c r="B597" s="9" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="598" spans="1:2">
-      <c r="A598" s="40" t="s">
+      <c r="A598" s="8" t="s">
         <v>1014</v>
       </c>
-      <c r="B598" s="41" t="s">
+      <c r="B598" s="9" t="s">
         <v>1015</v>
       </c>
     </row>
     <row r="599" spans="1:2">
-      <c r="A599" s="40" t="s">
+      <c r="A599" s="8" t="s">
         <v>1016</v>
       </c>
-      <c r="B599" s="41" t="s">
+      <c r="B599" s="9" t="s">
         <v>1017</v>
       </c>
     </row>
     <row r="600" spans="1:2">
-      <c r="A600" s="40" t="s">
+      <c r="A600" s="8" t="s">
         <v>1018</v>
       </c>
-      <c r="B600" s="41" t="s">
+      <c r="B600" s="9" t="s">
         <v>1019</v>
       </c>
     </row>
     <row r="601" spans="1:2">
-      <c r="A601" s="40" t="s">
+      <c r="A601" s="8" t="s">
         <v>1020</v>
       </c>
-      <c r="B601" s="41" t="s">
+      <c r="B601" s="9" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="602" spans="1:2">
-      <c r="A602" s="40" t="s">
+      <c r="A602" s="8" t="s">
         <v>1022</v>
       </c>
-      <c r="B602" s="41" t="s">
+      <c r="B602" s="9" t="s">
         <v>1023</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" s="40" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B603" s="41" t="s">
+        <v>1024</v>
       </c>
     </row>
   </sheetData>
@@ -9834,9 +9839,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="8.85454545454546" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.8545454545455" customWidth="1"/>
+    <col min="1" max="1" width="19.8518518518519" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9850,146 +9855,146 @@
     </row>
     <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="6" ht="51.75" customHeight="1" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="9" ht="39" customHeight="1" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="12" ht="26.25" customHeight="1" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="17" ht="377" spans="1:2">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="17" ht="374.4" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="18" ht="409.5" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="19" ht="409.5" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="19320" windowHeight="8867"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="1061">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="1066">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -3103,6 +3103,21 @@
   </si>
   <si>
     <t>Cleared</t>
+  </si>
+  <si>
+    <t>StandardPO</t>
+  </si>
+  <si>
+    <t>Standard(PO)</t>
+  </si>
+  <si>
+    <t>StandardService</t>
+  </si>
+  <si>
+    <t>Standard(Service)</t>
+  </si>
+  <si>
+    <t>StockTransferPO</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -4997,7 +5012,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B603"/>
+  <dimension ref="A1:B606"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="62.712962962963" style="4" customWidth="1"/>
@@ -9822,11 +9837,35 @@
       </c>
     </row>
     <row r="603" spans="1:2">
-      <c r="A603" s="40" t="s">
+      <c r="A603" s="8" t="s">
         <v>1024</v>
       </c>
-      <c r="B603" s="41" t="s">
+      <c r="B603" s="9" t="s">
         <v>1024</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" s="40" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B604" s="41" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" s="40" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B605" s="41" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" s="40" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B606" s="41" t="s">
+        <v>788</v>
       </c>
     </row>
   </sheetData>
@@ -9855,146 +9894,146 @@
     </row>
     <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="6" ht="51.75" customHeight="1" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="9" ht="39" customHeight="1" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="12" ht="26.25" customHeight="1" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="17" ht="374.4" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="18" ht="409.5" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="19" ht="409.5" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19320" windowHeight="8867"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="1078">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -3118,6 +3118,42 @@
   </si>
   <si>
     <t>StockTransferPO</t>
+  </si>
+  <si>
+    <t>Emp_GWP0001</t>
+  </si>
+  <si>
+    <t>GWP0001</t>
+  </si>
+  <si>
+    <t>Year202526</t>
+  </si>
+  <si>
+    <t>202526</t>
+  </si>
+  <si>
+    <t>LOP-Text</t>
+  </si>
+  <si>
+    <t>LOSS OF PAY</t>
+  </si>
+  <si>
+    <t>CasualLeave-Text</t>
+  </si>
+  <si>
+    <t>CASUAL LEAVE</t>
+  </si>
+  <si>
+    <t>CL-Text</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>FullSessionText</t>
+  </si>
+  <si>
+    <t>Full</t>
   </si>
   <si>
     <t>PRHeaderQuery</t>
@@ -5012,11 +5048,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B606"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="1"/>
+  <dimension ref="A1:B612"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="62.712962962963" style="4" customWidth="1"/>
-    <col min="2" max="2" width="59.8518518518519" style="5" customWidth="1"/>
+    <col min="1" max="1" width="62.7142857142857" style="4" customWidth="1"/>
+    <col min="2" max="2" width="59.847619047619" style="5" customWidth="1"/>
     <col min="3" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -9845,27 +9881,75 @@
       </c>
     </row>
     <row r="604" spans="1:2">
-      <c r="A604" s="40" t="s">
+      <c r="A604" s="8" t="s">
         <v>1025</v>
       </c>
-      <c r="B604" s="41" t="s">
+      <c r="B604" s="9" t="s">
         <v>1026</v>
       </c>
     </row>
     <row r="605" spans="1:2">
-      <c r="A605" s="40" t="s">
+      <c r="A605" s="8" t="s">
         <v>1027</v>
       </c>
-      <c r="B605" s="41" t="s">
+      <c r="B605" s="9" t="s">
         <v>1028</v>
       </c>
     </row>
     <row r="606" spans="1:2">
-      <c r="A606" s="40" t="s">
+      <c r="A606" s="8" t="s">
         <v>1029</v>
       </c>
-      <c r="B606" s="41" t="s">
+      <c r="B606" s="9" t="s">
         <v>788</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" s="40" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B607" s="41" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" s="40" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B608" s="41" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" s="40" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B609" s="41" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" s="40" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B610" s="41" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" s="40" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B611" s="41" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" s="40" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B612" s="41" t="s">
+        <v>1041</v>
       </c>
     </row>
   </sheetData>
@@ -9878,9 +9962,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.8518518518519" customWidth="1"/>
+    <col min="1" max="1" width="19.847619047619" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9894,146 +9978,146 @@
     </row>
     <row r="2" ht="108.95" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>1030</v>
+        <v>1042</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1031</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="3" ht="114" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>1032</v>
+        <v>1044</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1033</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="4" ht="80.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>1034</v>
+        <v>1046</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>1036</v>
+        <v>1048</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1037</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="6" ht="51.75" customHeight="1" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>1042</v>
+        <v>1054</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1043</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="9" ht="39" customHeight="1" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>1044</v>
+        <v>1056</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1045</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>1046</v>
+        <v>1058</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1047</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>1048</v>
+        <v>1060</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="12" ht="26.25" customHeight="1" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>1050</v>
+        <v>1062</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1051</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1053</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>1054</v>
+        <v>1066</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1055</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="17" ht="374.4" spans="1:2">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="17" ht="405" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="18" ht="409.5" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1063</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="19" ht="409.5" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>1064</v>
+        <v>1076</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/TestDatas.xlsx
+++ b/testdata/TestDatas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyChainManagement" sheetId="1" r:id="rId1"/>
     <sheet name="DBData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="1078">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="1361">
   <si>
     <t>Test Data Name</t>
   </si>
@@ -3663,23 +3663,6 @@
   </si>
   <si>
     <t>ItemShipSetQuery</t>
-  </si>
-  <si>
-    <t>SELECT PS_SS_PROD_ID, PS_SS_PROD_REV,
-       ( SELECT prod_desc11
-          FROM products
-         WHERE prod_bu  = ps_bu
-           AND prod_id  = PS_SS_PROD_ID
-           AND prod_rev = PS_SS_PROD_REV) PSI_SS_PROD_DESC,
-           PS_SS_QTY,
-           (SELECT PROD_UOM
-             FROM products
-            WHERE prod_bu  = ps_bu
-              AND prod_id  = PS_SS_PROD_ID
-              AND prod_rev = PS_SS_PROD_REV)UOM
-FROM PROD_SHIPSET
-  where   PS_BU =  'TVSA'
-    and   PS_FG_PROD_ID  = '${SONO}'</t>
   </si>
   <si>
     <t>POQuery</t>
@@ -3946,23 +3929,1151 @@
    AND pah_doc_no ='${POANO}'
    AND PALC_PROD_ID = '${ItemId}'</t>
   </si>
+  <si>
+    <t>SOAmendmentPrefix</t>
+  </si>
+  <si>
+    <t>SO100</t>
+  </si>
+  <si>
+    <t>SaleOrderNo</t>
+  </si>
+  <si>
+    <t>SO100/00954/25-26</t>
+  </si>
+  <si>
+    <t>NewUnitPrice</t>
+  </si>
+  <si>
+    <t>SODBTotalAmountColumnName</t>
+  </si>
+  <si>
+    <t>SO Total Amount</t>
+  </si>
+  <si>
+    <t>LocalCustomer</t>
+  </si>
+  <si>
+    <t>InterstateCustomer</t>
+  </si>
+  <si>
+    <t>ExportCustomer</t>
+  </si>
+  <si>
+    <t>SEQNO</t>
+  </si>
+  <si>
+    <t>${SEQNO}</t>
+  </si>
+  <si>
+    <t>PRC</t>
+  </si>
+  <si>
+    <t>${PRC}</t>
+  </si>
+  <si>
+    <t>SODBRateContractUnitPriceColumnName</t>
+  </si>
+  <si>
+    <t>SCDHD_PRICE</t>
+  </si>
+  <si>
+    <t>SODBRateContractDiscountPerColumnName</t>
+  </si>
+  <si>
+    <t>SCDHD_DISC_PCT</t>
+  </si>
+  <si>
+    <t>SODBShipSetProdIDColumnName</t>
+  </si>
+  <si>
+    <t>PS_SS_PROD_ID</t>
+  </si>
+  <si>
+    <t>SODBShipSetQtyColumnName</t>
+  </si>
+  <si>
+    <t>PS_SS_QTY</t>
+  </si>
+  <si>
+    <t>SODBShipSetUOMColumnName</t>
+  </si>
+  <si>
+    <t>NewQty</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>NewItem</t>
+  </si>
+  <si>
+    <t>NewTradeDiscount</t>
+  </si>
+  <si>
+    <t>NewSpecialDiscount</t>
+  </si>
+  <si>
+    <t>NewCashDiscount</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>SoAmdChargeItem</t>
+  </si>
+  <si>
+    <t>PriceClass</t>
+  </si>
+  <si>
+    <t>Spare</t>
+  </si>
+  <si>
+    <t>SOADBheaderLocationColumnName</t>
+  </si>
+  <si>
+    <t>SOA LOC</t>
+  </si>
+  <si>
+    <t>SOADBheaderUnitColumnName</t>
+  </si>
+  <si>
+    <t>SOA UNITID</t>
+  </si>
+  <si>
+    <t>SOADBheaderDocPrefixColumnName</t>
+  </si>
+  <si>
+    <t>SOA DOC PFX</t>
+  </si>
+  <si>
+    <t>SOADBheaderDocNumberColumnName</t>
+  </si>
+  <si>
+    <t>SOA DOC NO</t>
+  </si>
+  <si>
+    <t>SOADBheaderSODocNumberColumnName</t>
+  </si>
+  <si>
+    <t>SOA SO NO</t>
+  </si>
+  <si>
+    <t>SOADBheaderCustomerIDColumnName</t>
+  </si>
+  <si>
+    <t>SOH_CUST_ID</t>
+  </si>
+  <si>
+    <t>SOADBheaderCustomerDescColumnName</t>
+  </si>
+  <si>
+    <t>SOH_CUST_NAME</t>
+  </si>
+  <si>
+    <t>SOADBheaderCurrencyColumnName</t>
+  </si>
+  <si>
+    <t>SOH_CURRENCY</t>
+  </si>
+  <si>
+    <t>SOADBheaderTotalAmountColumnName</t>
+  </si>
+  <si>
+    <t>SOH_TOT_AMT</t>
+  </si>
+  <si>
+    <t>SOADBheaderStatusColumnName</t>
+  </si>
+  <si>
+    <t>SOADBLineItemIdColumnName</t>
+  </si>
+  <si>
+    <t>SALC_PROD_ID</t>
+  </si>
+  <si>
+    <t>SOADBLineSaleUOMColumnName</t>
+  </si>
+  <si>
+    <t>SALC_UOM</t>
+  </si>
+  <si>
+    <t>SOADBLineOldSOQtyColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_SO_QTY</t>
+  </si>
+  <si>
+    <t>SOADBLineOldSOUnitPriceColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_UNIT_COST</t>
+  </si>
+  <si>
+    <t>SOADBLineNewSOQtyColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_SO_QTY</t>
+  </si>
+  <si>
+    <t>SOADBLineNewSOUnitPriceColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_UNIT_COST</t>
+  </si>
+  <si>
+    <t>SOADBLineOldTDPColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_DISC_PCT</t>
+  </si>
+  <si>
+    <t>SOADBLineOldTAVColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_TRD_ASSBL_VAL</t>
+  </si>
+  <si>
+    <t>SOADBLineOldTDAColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_DISC_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineOldSAVColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_SPL_ASSBL_VAL</t>
+  </si>
+  <si>
+    <t>SOADBLineOldSDPColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_SPL_DISC_PCT</t>
+  </si>
+  <si>
+    <t>SOADBLineOldSDAColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_SPL_DISC_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineOldCAVColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_CASH_ASSBL_VAL</t>
+  </si>
+  <si>
+    <t>SOADBLineOldCDPColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_CASH_DISC_PCT</t>
+  </si>
+  <si>
+    <t>SOADBLineOldCDAColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_CASH_DISC_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineOldCGSTColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_CGST_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineOldIGSTColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_IGST_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineOldSGSTColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_SGST_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineOldDAPQColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_DISC_AMT_PER_QTY</t>
+  </si>
+  <si>
+    <t>SOADBLineNewTDPColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_DISC_PCT</t>
+  </si>
+  <si>
+    <t>SOADBLineNewTAVColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_TRD_ASSBL_VAL</t>
+  </si>
+  <si>
+    <t>SOADBLineNewTDAColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_DISC_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineNewSAVColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_SPL_ASSBL_VAL</t>
+  </si>
+  <si>
+    <t>SOADBLineNewSDPColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_SPL_DISC_PCT</t>
+  </si>
+  <si>
+    <t>SOADBLineNewSDAColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_SPL_DISC_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineNewCAVColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_CASH_ASSBL_VAL</t>
+  </si>
+  <si>
+    <t>SOADBLineNewCDPColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_CASH_DISC_PCT</t>
+  </si>
+  <si>
+    <t>SOADBLineNewCDAColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_CASH_DISC_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineNewCGSTColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_CGST_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineNewIGSTColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_IGST_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineNewSGSTColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_SGST_AMT</t>
+  </si>
+  <si>
+    <t>SOADBLineNewDAPQColumnName</t>
+  </si>
+  <si>
+    <t>SALC_NEW_DISC_AMT_PER_QTY</t>
+  </si>
+  <si>
+    <t>SOADBLineOldHSNColumnName</t>
+  </si>
+  <si>
+    <t>SALC_OLD_HSN_CODE</t>
+  </si>
+  <si>
+    <t>SOADBLineNewHSNColumnName</t>
+  </si>
+  <si>
+    <t>SALC_HSN_CODE</t>
+  </si>
+  <si>
+    <t>SOADBTotalAmountColumnName</t>
+  </si>
+  <si>
+    <t>SOA_TOT_AMT</t>
+  </si>
+  <si>
+    <t>CurrentRateContractQuery</t>
+  </si>
+  <si>
+    <t>SELECT SCDHD_PRICE,SCDHD_DISC_PCT,SALES_CONTR_BATCH_VIEW.*
+  FROM SALES_CONTR_BATCH_VIEW
+ WHERE SCDHD_BU = 'TVSA'
+   AND SCDHD_STATUS IN ('A')
+    AND SCDHD_PLNT IN(
+                      ( select wupal_plnt_id
+          from wapl_user_plnt_access_ln
+          where wupal_bu= 'TVSA' 
+          and  wupal_user_id= 'TVSAADMIN' 
+          AND  trunc(sysdate) between  wupal_date_from and  wupal_date_to))
+   AND scdhd_cust_id = '${SONO}'
+    AND scdhd_prod_id = '${PONO}'
+   AND SCDHD_PRICE_CLS_DESC = '${PRC}'</t>
+  </si>
+  <si>
+    <t>SalesOrderAmendmentHeaderQuery</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT
+       soh_plnt_loc_id "SOA LOC", 
+       soh_plnt "SOA UNITID",
+       soh_doc_pfx"SOA DOC PFX",
+       soh_doc_no"SOA DOC NO",
+       soh_so_no"SOA SO NO", 
+       (SELECT soh_cust_id
+          FROM sales_order_hd
+         WHERE sales_order_hd.soh_bu = so_amend_hd.soh_bu
+              and sales_order_hd.soh_order_pfx = so_amend_hd.SOH_SO_PFX
+               AND sales_order_hd.soh_order_no = so_amend_hd.SOH_SO_NO)
+          soh_cust_id,
+       (SELECT suplr_name1
+          FROM sales_order_hd, suppliers
+         WHERE     sales_order_hd.soh_bu = so_amend_hd.soh_bu
+              and sales_order_hd.soh_order_pfx = so_amend_hd.SOH_SO_PFX
+               AND sales_order_hd.soh_order_no = so_amend_hd.SOH_SO_NO
+               AND suplr_bu = sales_order_hd.soh_bu
+               AND suplr_suplr_id = sales_order_hd.soh_cust_id)
+          soh_cust_name,
+       (SELECT soh_currency
+          FROM sales_order_hd, so_amend_hd
+         WHERE sales_order_hd.soh_bu = so_amend_hd.soh_bu
+               AND sales_order_hd.soh_order_no = so_amend_hd.soh_doc_no)
+          soh_currency,
+       soh_tot_amt "SOA_TOT_AMT",
+        DECODE(soh_status,'N','Draft','A','Approved','E','Entry Completed','C','Cancelled')
+       soh_status 
+  FROM so_amend_hd
+ WHERE soh_bu = 'TVSA' 
+   AND soh_doc_no = '${SONO}'</t>
+  </si>
+  <si>
+    <t>SalesOrderAmendmentLineQuery</t>
+  </si>
+  <si>
+    <t>SELECT salc_seq_no,
+       salc_po_line_no,
+       DECODE(salc_chnge_type,'A','Addition','C','Closeshort','M','Modify') SALC_CHNGE_TYPE,
+       salc_prod_id,
+       salc_prod_rev,
+       (SELECT prod_desc11
+          FROM products
+         WHERE prod_bu = salc_bu
+            AND prod_id = salc_prod_id
+            AND prod_rev = salc_prod_rev) salc_prod_desc,
+       salc_uom,
+       salc_old_so_qty,
+       salc_new_so_qty,
+       salc_old_unit_cost,
+       salc_new_unit_cost,
+       salc_old_disc_pct,
+       salc_new_disc_pct,
+       salc_old_trd_assbl_val,
+       salc_old_disc_pct,
+       salc_old_disc_amt,
+       salc_old_spl_assbl_val,
+       salc_old_spl_disc_pct,
+       salc_old_spl_disc_amt,
+       salc_old_cash_assbl_val,
+       salc_old_cash_disc_pct,
+       salc_old_cash_disc_amt,
+       salc_new_trd_assbl_val,
+       salc_new_disc_pct,
+       salc_new_disc_amt,
+       salc_new_spl_assbl_val,
+       salc_new_spl_disc_pct,
+       salc_new_spl_disc_amt,
+       salc_new_cash_assbl_val,
+       salc_new_cash_disc_pct,
+       salc_new_cash_disc_amt,
+       salc_old_hsn_code,
+       salc_old_tax_pct,
+       salc_old_igst_amt,
+       salc_old_cgst_amt,
+       salc_old_sgst_amt,
+       salc_old_utgst_amt,
+       salc_old_cess_pct,
+       salc_old_cess_amt,
+       salc_old_disc_amt_per_qty,
+       salc_hsn_code,
+       salc_new_tax_pct,
+       salc_new_igst_amt,
+       salc_new_cgst_amt,
+       salc_new_sgst_amt,
+       salc_new_utgst_amt,
+       salc_new_cess_pct,
+       salc_new_cess_amt,
+       salc_new_disc_amt_per_qty,
+       DECODE(salc_price_basis,'U','User Defined','C','Open SO','S','Standard Price','P','Price List','L','Catalog Price') salc_price_basis,
+       salc_cont_cat_no,
+       salc_catalog_no,
+       salc_sales_price_class,
+       salc_promotion_flag,
+       salc_cust_prod_id,
+       salc_cust_prod_desc
+  FROM so_amend_line_chnges
+ WHERE salc_bu = 'TVSA'
+   AND salc_doc_no = '${SONO}'
+   AND salc_seq_no = '${PONO}'</t>
+  </si>
+  <si>
+    <t>WITH numbered_rows AS (
+  SELECT PS_SS_PROD_ID, PS_SS_PROD_REV, 
+         ROW_NUMBER() OVER (ORDER BY PS_SS_PROD_ID) AS seq_no,
+         (SELECT prod_desc11
+            FROM products
+           WHERE prod_bu = ps_bu
+             AND prod_id = PS_SS_PROD_ID
+             AND prod_rev = PS_SS_PROD_REV) PSI_SS_PROD_DESC,
+         PS_SS_QTY,
+         (SELECT PROD_UOM
+            FROM products
+           WHERE prod_bu = ps_bu
+             AND prod_id = PS_SS_PROD_ID
+             AND prod_rev = PS_SS_PROD_REV) UOM
+  FROM PROD_SHIPSET
+  WHERE PS_BU = 'TVSA'
+    AND PS_FG_PROD_ID = '${SONO}'
+)
+SELECT PS_SS_PROD_ID, PS_SS_PROD_REV, seq_no, PSI_SS_PROD_DESC, PS_SS_QTY, UOM
+FROM numbered_rows
+WHERE seq_no = '${PONO}'
+    and   PS_FG_PROD_ID  = '${SONO}'</t>
+  </si>
+  <si>
+    <t>Service_Invoice_Pfx</t>
+  </si>
+  <si>
+    <t>SSER1</t>
+  </si>
+  <si>
+    <t>SI_Service_Type</t>
+  </si>
+  <si>
+    <t>SI - SERVICE</t>
+  </si>
+  <si>
+    <t>SI_Service_Local_Customer</t>
+  </si>
+  <si>
+    <t>GANESH ENTERPRISE</t>
+  </si>
+  <si>
+    <t>SI_Service_Item</t>
+  </si>
+  <si>
+    <t>Service0001</t>
+  </si>
+  <si>
+    <t>SI_Ship_From_Service_WH</t>
+  </si>
+  <si>
+    <t>SI_Shipset_Item</t>
+  </si>
+  <si>
+    <t>FG_ShipSet_01</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Promotional</t>
+  </si>
+  <si>
+    <t>CreditNote_Inv_No</t>
+  </si>
+  <si>
+    <t>U100/00693/24-25</t>
+  </si>
+  <si>
+    <t>CR_CN_Prefix</t>
+  </si>
+  <si>
+    <t>CNI10</t>
+  </si>
+  <si>
+    <t>CR_Return_Reason</t>
+  </si>
+  <si>
+    <t>DAMAGED GOODS</t>
+  </si>
+  <si>
+    <t>CR_Doc_Pfx</t>
+  </si>
+  <si>
+    <t>CNl01</t>
+  </si>
+  <si>
+    <t>CR_Customer</t>
+  </si>
+  <si>
+    <t>CR_Good_Type_Text</t>
+  </si>
+  <si>
+    <t>W/O Goods</t>
+  </si>
+  <si>
+    <t>ReturnQty</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>CR_UnitPrice</t>
+  </si>
+  <si>
+    <t>CR_HSN_Code</t>
+  </si>
+  <si>
+    <t>123562</t>
+  </si>
+  <si>
+    <t>Location49</t>
+  </si>
+  <si>
+    <t>Inv_Pfx_Loc49</t>
+  </si>
+  <si>
+    <t>SI49</t>
+  </si>
+  <si>
+    <t>CPC_Loc49</t>
+  </si>
+  <si>
+    <t>C1C2C3C4C5C6-U49</t>
+  </si>
+  <si>
+    <t>SIDBStoreIDColumn</t>
+  </si>
+  <si>
+    <t>SILN_STORE_ID</t>
+  </si>
+  <si>
+    <t>SIDBUnitCostColumn</t>
+  </si>
+  <si>
+    <t>SILN_UNIT_COST</t>
+  </si>
+  <si>
+    <t>SIDBGrossAmtColumn</t>
+  </si>
+  <si>
+    <t>SILN_GROSS_AMT</t>
+  </si>
+  <si>
+    <t>SIDBTaxAmtColumn</t>
+  </si>
+  <si>
+    <t>SILN_TAX_AMT</t>
+  </si>
+  <si>
+    <t>SIDBNetAmtColumn</t>
+  </si>
+  <si>
+    <t>SILN_NET_AMT</t>
+  </si>
+  <si>
+    <t>SIDBStkInvQtyColumn</t>
+  </si>
+  <si>
+    <t>SILN_STK_INV_QTY</t>
+  </si>
+  <si>
+    <t>SINO</t>
+  </si>
+  <si>
+    <t>${SINO}</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>${PINO}</t>
+  </si>
+  <si>
+    <t>PIDBLocIDColumn</t>
+  </si>
+  <si>
+    <t>PIHD_PLNT_LOC_ID</t>
+  </si>
+  <si>
+    <t>PIDBUnitColumn</t>
+  </si>
+  <si>
+    <t>PIHD_PLNT</t>
+  </si>
+  <si>
+    <t>PIDBPITypeColumn</t>
+  </si>
+  <si>
+    <t>PIHD_TYPE</t>
+  </si>
+  <si>
+    <t>PIDBDocPfxColumn</t>
+  </si>
+  <si>
+    <t>PIHD_DOC_PFX</t>
+  </si>
+  <si>
+    <t>PIDBCustomerColumn</t>
+  </si>
+  <si>
+    <t>PIHD_CUST_ID</t>
+  </si>
+  <si>
+    <t>PIDBDocNoColumn</t>
+  </si>
+  <si>
+    <t>PIHD_DOC_NO</t>
+  </si>
+  <si>
+    <t>PIDBInvPfxColumn</t>
+  </si>
+  <si>
+    <t>PIHD_INV_PFX</t>
+  </si>
+  <si>
+    <t>PIDBInvNoColumn</t>
+  </si>
+  <si>
+    <t>PIHD_INV_NO</t>
+  </si>
+  <si>
+    <t>PIDBSORefColumn</t>
+  </si>
+  <si>
+    <t>PILN_SO_SCHLD_DESC</t>
+  </si>
+  <si>
+    <t>PIDBItemColumn</t>
+  </si>
+  <si>
+    <t>PILN_PROD_ID</t>
+  </si>
+  <si>
+    <t>PIDBPIQtyColumn</t>
+  </si>
+  <si>
+    <t>PILN_PROD_QTY</t>
+  </si>
+  <si>
+    <t>PIDBUnitPricecolumn</t>
+  </si>
+  <si>
+    <t>PILN_SALES_PRICE</t>
+  </si>
+  <si>
+    <t>PIDBDiscAmtColumn</t>
+  </si>
+  <si>
+    <t>PILN_DISC_AMT</t>
+  </si>
+  <si>
+    <t>PIDBHSNColumn</t>
+  </si>
+  <si>
+    <t>PILN_HSN_CODE</t>
+  </si>
+  <si>
+    <t>PIDBTaxColumn</t>
+  </si>
+  <si>
+    <t>PILN_TAX_PCT</t>
+  </si>
+  <si>
+    <t>PIDBIGSTAmtColumn</t>
+  </si>
+  <si>
+    <t>PILN_IGST_AMT</t>
+  </si>
+  <si>
+    <t>PIDBSGSTAmtColumn</t>
+  </si>
+  <si>
+    <t>PILN_SGST_AMT</t>
+  </si>
+  <si>
+    <t>PIDBCGSTAmtColumn</t>
+  </si>
+  <si>
+    <t>PILN_CGST_AMT</t>
+  </si>
+  <si>
+    <t>PIDBUTGSTAmtColumn</t>
+  </si>
+  <si>
+    <t>PILN_UTGST_AMT</t>
+  </si>
+  <si>
+    <t>CRDBLocationColumn</t>
+  </si>
+  <si>
+    <t>SIHD_PLNT_LOC_ID</t>
+  </si>
+  <si>
+    <t>CRDBUnitColumn</t>
+  </si>
+  <si>
+    <t>SIHD_PLANT</t>
+  </si>
+  <si>
+    <t>CRDBDocNoColumn</t>
+  </si>
+  <si>
+    <t>SIHD_DOC_NO</t>
+  </si>
+  <si>
+    <t>CRDBDocPfxColumn</t>
+  </si>
+  <si>
+    <t>SIHD_DOC_PFX</t>
+  </si>
+  <si>
+    <t>CRDBTypeColumn</t>
+  </si>
+  <si>
+    <t>SIHD_TYPE</t>
+  </si>
+  <si>
+    <t>CRDBCustIDColumn</t>
+  </si>
+  <si>
+    <t>SIHD_CUST_ID</t>
+  </si>
+  <si>
+    <t>CRDBCustNameColumn</t>
+  </si>
+  <si>
+    <t>SIHD_CUST_NAME</t>
+  </si>
+  <si>
+    <t>CRDBGoodsTypeColumn</t>
+  </si>
+  <si>
+    <t>SIHD_RTN_GOODS_DTLS</t>
+  </si>
+  <si>
+    <t>CRDBStatusColumn</t>
+  </si>
+  <si>
+    <t>SIHD_STATUS</t>
+  </si>
+  <si>
+    <t>CRNO</t>
+  </si>
+  <si>
+    <t>${CRNO}</t>
+  </si>
+  <si>
+    <t>CRHeaderDraftStatus</t>
+  </si>
+  <si>
+    <t>CRInvoicedStatus</t>
+  </si>
+  <si>
+    <t>CRDBItemColumn</t>
+  </si>
+  <si>
+    <t>SILN_PROD_ID</t>
+  </si>
+  <si>
+    <t>CRDQtyColumn</t>
+  </si>
+  <si>
+    <t>SILN_INV_QTY</t>
+  </si>
+  <si>
+    <t>CRDBUnitPriceColumn</t>
+  </si>
+  <si>
+    <t>SILN_PRICE</t>
+  </si>
+  <si>
+    <t>CRDBHSNColumn</t>
+  </si>
+  <si>
+    <t>SILN_HSN_CODE</t>
+  </si>
+  <si>
+    <t>CRDBTaxColumn</t>
+  </si>
+  <si>
+    <t>SILN_TAX_PCT</t>
+  </si>
+  <si>
+    <t>CRDBIGSTColumn</t>
+  </si>
+  <si>
+    <t>SILN_IGST_AMT</t>
+  </si>
+  <si>
+    <t>CRDBSGSTColumn</t>
+  </si>
+  <si>
+    <t>SILN_SGST_AMT</t>
+  </si>
+  <si>
+    <t>CRDBCGSTColumn</t>
+  </si>
+  <si>
+    <t>SILN_CGST_AMT</t>
+  </si>
+  <si>
+    <t>CRDBUTGSTColumn</t>
+  </si>
+  <si>
+    <t>SILN_UTGST_AMT</t>
+  </si>
+  <si>
+    <t>Cust_ID_GateEntry</t>
+  </si>
+  <si>
+    <t>SAI ENTERPRISE06</t>
+  </si>
+  <si>
+    <t>VIMAL</t>
+  </si>
+  <si>
+    <t>CR_CN_GE_Pfx</t>
+  </si>
+  <si>
+    <t>CNL3</t>
+  </si>
+  <si>
+    <t>Loc49ExportCustomer</t>
+  </si>
+  <si>
+    <t>WEGA ASSOCIATES</t>
+  </si>
+  <si>
+    <t>SIDBStatusColumn</t>
+  </si>
+  <si>
+    <t>SIInvoicedStatus</t>
+  </si>
+  <si>
+    <t>Percentage_Basis</t>
+  </si>
+  <si>
+    <t>Value_Basis</t>
+  </si>
+  <si>
+    <t>Charge_Item</t>
+  </si>
+  <si>
+    <t>Percentage_Qty</t>
+  </si>
+  <si>
+    <t>ChargeSAC</t>
+  </si>
+  <si>
+    <t>(4901)</t>
+  </si>
+  <si>
+    <t>SILineDetailQuery</t>
+  </si>
+  <si>
+    <t>SELECT siln_gst_exempt_flag,
+       siln_gst_input_type,
+       siln_dd_appl_flag,
+       siln_fob_value,
+       siln_promotion_flag,
+       siln_tac_cost,
+       siln_cess_pct,
+       siln_cess_amt,
+       siln_so_schld_desc,
+       siln_store_id,
+       siln_cust_doc_no,
+       siln_cust_doc_rev,
+       siln_cust_ln_seq_no,
+       siln_prod_ext_desc,
+       siln_class,
+       siln_sub_cls,
+       siln_conv_factor,
+       siln_tolr_pct,
+       siln_tolr_qty,
+       siln_rqrd_date,
+       siln_rqrd_qty,
+       siln_promise_date,
+       siln_sales_price_class,
+       siln_desp_date,
+       siln_cust_drw_no,
+       siln_cust_drw_rev,
+       siln_amd_no,
+       siln_amd_date,
+       siln_price_basis,
+       siln_cust_po_date,
+       siln_cust_po_no,
+       siln_cust_po_rev,
+       siln_cust_po_seq_no,
+       siln_catalog_no,
+       siln_conract_no,
+       siln_mrp_price,
+       siln_price_po_no,
+       siln_price_po_date,
+       siln_po_ref,
+       siln_trd_assbl_val,
+       siln_disc_pct,
+       siln_disc_amt,
+       siln_spl_assbl_val,
+       siln_spl_disc_pct,
+       siln_spl_disc_amt,
+       siln_cash_assbl_val,
+       siln_cash_disc_pct,
+       siln_cash_disc_amt,
+       siln_cust_prod_id,
+       siln_cust_prod_desc,
+       siln_qc_pfx,
+       siln_qc_no,
+       siln_qc_rev,
+       siln_qc_doc_seq_no,
+       siln_unit_cost,
+       siln_disc_amt_per_qty,
+       siln_gross_amt,
+       siln_tax_amt,
+       siln_net_amt,
+       siln_tot_disc_amt,
+       siln_prod_uom,
+       siln_stk_inv_qty,
+       siln_proj_lvl_id,
+       siln_proj_lvl_name,
+       siln_proj_id,
+       siln_meis_lic_no,
+       siln_lic_amt,
+       siln_meis_lic_bal_amt
+  FROM sales_invoices_ln,
+       sales_invoices_hd
+ WHERE     sihd_bu = 'TVSA'
+       AND sihd_bu = siln_bu
+       AND sihd_plant = siln_plnt
+       AND sihd_doc_no = siln_doc_no
+       AND siln_doc_no = '${SINO}'</t>
+  </si>
+  <si>
+    <t>PIHeaderQuery</t>
+  </si>
+  <si>
+    <t>SELECT pihd_plnt_loc_id ,
+       pihd_plnt ,
+       pihd_type,
+       pihd_doc_pfx,
+       pihd_doc_no,
+       pihd_inv_pfx ,
+       pihd_inv_no ,
+       pihd_cust_id,
+       pihd_currency ,
+       pihd_fob_id,
+       pihd_ship_via ,
+       pihd_pay_term ,
+       DECODE (pihd_status,'N','Draft','I','Invoiced','C','Cancelled','E','Entry Completed')
+  FROM proforma_invoices_hd
+ WHERE pihd_bu = 'TVSA'
+   AND PIHD_DOC_NO = '${PINO}'</t>
+  </si>
+  <si>
+    <t>PILineDetailQuery</t>
+  </si>
+  <si>
+    <t>SELECT piln_so_schld_desc ,
+       piln_prod_id,
+       piln_prod_desc1 ,
+       piln_sales_uom,
+       piln_prod_qty ,
+       piln_sales_price ,
+       piln_disc_amt ,
+       piln_hsn_code,
+       piln_tax_pct,
+       piln_igst_amt ,
+       piln_sgst_amt ,
+       piln_cgst_amt ,
+       piln_utgst_amt 
+  FROM proforma_invoices_ln
+ WHERE piln_bu = 'TVSA'
+   AND piln_doc_no = '${PINO}'</t>
+  </si>
+  <si>
+    <t>CreditNoteHeaderQuery</t>
+  </si>
+  <si>
+    <t>SELECT sihd_plnt_loc_id,
+       sihd_plant,
+       sihd_doc_no,
+       sihd_doc_pfx,
+       sihd_type,
+       sihd_cust_id,
+       sihd_cust_name,
+       sihd_rtn_goods_dtls,
+       sihd_ref1,
+       DECODE (sihd_status,
+               'N', 'Draft',
+               'I', 'Invoiced',
+               'C', 'Cancelled',
+               'E', 'Entry Completed')
+          sihd_status
+  FROM sales_invoices_hd
+  WHERE SIHD_BU = 'TVSA'
+    AND SIHD_DOC_NO = '${CRNO}'</t>
+  </si>
+  <si>
+    <t>CreditNoteLineQuery</t>
+  </si>
+  <si>
+    <t>SELECT siln_prod_id,
+       siln_return_qty,
+       siln_accepted_qty,
+       siln_rejected_qty,
+       siln_price,
+       siln_hsn_code,
+       siln_tax_pct,
+       siln_igst_amt,
+       siln_sgst_amt,
+       siln_cgst_amt,
+       siln_utgst_amt,
+       siln_inv_qty
+  FROM sales_invoices_ln
+ WHERE siln_bu = 'TVSA' AND siln_doc_no = '${CRNO}'</t>
+  </si>
+  <si>
+    <t>SalesInvHeaderQuery</t>
+  </si>
+  <si>
+    <t>SELECT sihd_plnt_loc_id,
+       sihd_plant,
+       sihd_doc_pfx,
+       sihd_doc_no,
+       sihd_type,
+       sihd_cust_id,
+       sihd_currency,
+              DECODE (sihd_status,
+               'N', 'Draft',
+               'I', 'Invoiced',
+               'C', 'Cancelled',
+               'E', 'Entry Completed')
+          sihd_status
+  FROM sales_invoices_hd
+where sihd_bu = 'TVSA'
+  and sihd_doc_no = '${SINO}'</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3998,151 +5109,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4167,188 +5141,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -4384,403 +5178,131 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="53">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="53">
+  <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal 2" xfId="49"/>
-    <cellStyle name="Normal 2 2" xfId="50"/>
-    <cellStyle name="Normal 2 3" xfId="51"/>
-    <cellStyle name="Normal 3" xfId="52"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2 2" xfId="2"/>
+    <cellStyle name="Normal 2 3" xfId="3"/>
+    <cellStyle name="Normal 3" xfId="4"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5042,17 +5564,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B612"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B760"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="62.7142857142857" style="4" customWidth="1"/>
-    <col min="2" max="2" width="59.847619047619" style="5" customWidth="1"/>
+    <col min="1" max="1" width="62.7109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="59.85546875" style="5" customWidth="1"/>
     <col min="3" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -9952,19 +10474,1201 @@
         <v>1041</v>
       </c>
     </row>
+    <row r="613" spans="1:2">
+      <c r="A613" s="42" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B613" s="43" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" s="42" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B614" s="44" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" s="45" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B615" s="43" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" s="45" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B616" s="43" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617" s="45" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B617" s="46" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618" s="45" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B618" s="46" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619" s="45" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B619" s="46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620" s="45" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B620" s="43" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621" s="45" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B621" s="43" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622" s="45" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B622" s="43" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623" s="45" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B623" s="43" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624" s="45" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B624" s="43" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625" s="45" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B625" s="43" t="s">
+      